--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,13 +423,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D543"/>
+  <dimension ref="A1:F543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,6 +455,16 @@
           <t>change_00:15</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>price_00:30</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>change_00:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +481,12 @@
       <c r="D2" s="2" t="n">
         <v>-0.002876956743205454</v>
       </c>
+      <c r="E2" s="1" t="n">
+        <v>70009.2</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>-0.001015975936210368</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -485,6 +503,12 @@
       <c r="D3" s="2" t="n">
         <v>-0.003471585147989018</v>
       </c>
+      <c r="E3" s="1" t="n">
+        <v>2062.56</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-0.0006540982891695418</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -501,6 +525,12 @@
       <c r="D4" s="2" t="n">
         <v>-0.005085529357373992</v>
       </c>
+      <c r="E4" s="1" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.0005808550185873276</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -517,6 +547,12 @@
       <c r="D5" s="3" t="n">
         <v>0.03214717086314232</v>
       </c>
+      <c r="E5" s="1" t="n">
+        <v>0.011253</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.01296246286794491</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -533,6 +569,12 @@
       <c r="D6" s="2" t="n">
         <v>-0.0043525571273123</v>
       </c>
+      <c r="E6" s="1" t="n">
+        <v>1.3768</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.003132969034608357</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -549,6 +591,12 @@
       <c r="D7" s="2" t="n">
         <v>-0.004572036150983518</v>
       </c>
+      <c r="E7" s="1" t="n">
+        <v>0.09379999999999999</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.001922666096987819</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -565,6 +613,12 @@
       <c r="D8" s="2" t="n">
         <v>-0.001899005028351288</v>
       </c>
+      <c r="E8" s="1" t="n">
+        <v>37.322</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.0001339871908246257</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -581,6 +635,12 @@
       <c r="D9" s="3" t="n">
         <v>0.0186513629842181</v>
       </c>
+      <c r="E9" s="1" t="n">
+        <v>0.05016</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.009255533199195212</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -597,6 +657,12 @@
       <c r="D10" s="3" t="n">
         <v>0.01321414691022151</v>
       </c>
+      <c r="E10" s="1" t="n">
+        <v>18.351</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.005589347361499278</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -613,6 +679,12 @@
       <c r="D11" s="2" t="n">
         <v>-0.0005382710733125551</v>
       </c>
+      <c r="E11" s="1" t="n">
+        <v>649.58</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-0.0004616236843724296</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -629,6 +701,12 @@
       <c r="D12" s="2" t="n">
         <v>-0.004312158182583081</v>
       </c>
+      <c r="E12" s="1" t="n">
+        <v>0.9358</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-0.01151367909580651</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -645,6 +723,12 @@
       <c r="D13" s="3" t="n">
         <v>0.001535287626541252</v>
       </c>
+      <c r="E13" s="1" t="n">
+        <v>210.29</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0.007377245508981998</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -661,6 +745,12 @@
       <c r="D14" s="2" t="n">
         <v>-0.004672755408562688</v>
       </c>
+      <c r="E14" s="1" t="n">
+        <v>0.0032913</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.003353351827576794</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -677,6 +767,12 @@
       <c r="D15" s="3" t="n">
         <v>0.0786887987623866</v>
       </c>
+      <c r="E15" s="1" t="n">
+        <v>0.25433</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-0.01418659637970463</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -693,6 +789,12 @@
       <c r="D16" s="2" t="n">
         <v>-0.0005157297576070716</v>
       </c>
+      <c r="E16" s="1" t="n">
+        <v>0.9695</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.0005159958720330815</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -709,6 +811,12 @@
       <c r="D17" s="2" t="n">
         <v>-0.00993377483443714</v>
       </c>
+      <c r="E17" s="1" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -725,6 +833,12 @@
       <c r="D18" s="2" t="n">
         <v>-0.001179634785070542</v>
       </c>
+      <c r="E18" s="1" t="n">
+        <v>213.51</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0.008645124716553213</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -741,6 +855,12 @@
       <c r="D19" s="2" t="n">
         <v>-0.002673796791443768</v>
       </c>
+      <c r="E19" s="1" t="n">
+        <v>0.2615</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0.001531980084258949</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -757,6 +877,12 @@
       <c r="D20" s="2" t="n">
         <v>-0.009848440172200299</v>
       </c>
+      <c r="E20" s="1" t="n">
+        <v>0.016974</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.01095890410958905</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -773,6 +899,12 @@
       <c r="D21" s="2" t="n">
         <v>-0.001356710498852004</v>
       </c>
+      <c r="E21" s="1" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-0.0009405371512175086</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -789,6 +921,12 @@
       <c r="D22" s="2" t="n">
         <v>-0.01237477902180313</v>
       </c>
+      <c r="E22" s="1" t="n">
+        <v>0.1684</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0.004773269689737441</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -805,6 +943,12 @@
       <c r="D23" s="2" t="n">
         <v>-0.00385449977158525</v>
       </c>
+      <c r="E23" s="1" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0.0007738828857234315</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -821,6 +965,12 @@
       <c r="D24" s="2" t="n">
         <v>-0.001164144353899885</v>
       </c>
+      <c r="E24" s="1" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0.001165501165501167</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -837,6 +987,12 @@
       <c r="D25" s="2" t="n">
         <v>-0.003543743078626803</v>
       </c>
+      <c r="E25" s="1" t="n">
+        <v>9.009</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0.001222493887530675</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -853,6 +1009,12 @@
       <c r="D26" s="2" t="n">
         <v>-0.005299015897047612</v>
       </c>
+      <c r="E26" s="1" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0.003044140030441403</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -869,6 +1031,12 @@
       <c r="D27" s="2" t="n">
         <v>-0.0006878061516759974</v>
       </c>
+      <c r="E27" s="1" t="n">
+        <v>5132.58</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0.0007506731686012647</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -885,6 +1053,12 @@
       <c r="D28" s="2" t="n">
         <v>-0.005976095617529854</v>
       </c>
+      <c r="E28" s="1" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0.003435442313197764</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -901,6 +1075,12 @@
       <c r="D29" s="2" t="n">
         <v>-0.001131221719457056</v>
       </c>
+      <c r="E29" s="1" t="n">
+        <v>2.654</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0.001887504718761757</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -917,6 +1097,12 @@
       <c r="D30" s="3" t="n">
         <v>0.00605772447919418</v>
       </c>
+      <c r="E30" s="1" t="n">
+        <v>0.56816</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-0.005513644081146814</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -933,6 +1119,12 @@
       <c r="D31" s="2" t="n">
         <v>-0.004812319538017337</v>
       </c>
+      <c r="E31" s="1" t="n">
+        <v>0.002068</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -949,6 +1141,12 @@
       <c r="D32" s="3" t="n">
         <v>0.008787487907126841</v>
       </c>
+      <c r="E32" s="1" t="n">
+        <v>1.2603</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0.007192519779429311</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -965,6 +1163,12 @@
       <c r="D33" s="3" t="n">
         <v>0.002485243864554108</v>
       </c>
+      <c r="E33" s="1" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.006817477533312783</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -981,6 +1185,12 @@
       <c r="D34" s="2" t="n">
         <v>-0.0006657789613848948</v>
       </c>
+      <c r="E34" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-0.000666222518321046</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -997,6 +1207,12 @@
       <c r="D35" s="2" t="n">
         <v>-0.001096515274457773</v>
       </c>
+      <c r="E35" s="1" t="n">
+        <v>456.12</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.001383125864453655</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1013,6 +1229,12 @@
       <c r="D36" s="3" t="n">
         <v>0.006436877076411914</v>
       </c>
+      <c r="E36" s="1" t="n">
+        <v>0.04831</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-0.00330101093459873</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1029,6 +1251,12 @@
       <c r="D37" s="2" t="n">
         <v>-0.0001418439716311901</v>
       </c>
+      <c r="E37" s="1" t="n">
+        <v>0.7074</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.003546602354944046</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1045,6 +1273,12 @@
       <c r="D38" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E38" s="1" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0.002854424357754469</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1061,6 +1295,12 @@
       <c r="D39" s="2" t="n">
         <v>-0.006475738781466561</v>
       </c>
+      <c r="E39" s="1" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0.004314697512163764</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1077,6 +1317,12 @@
       <c r="D40" s="3" t="n">
         <v>0.0200845665961946</v>
       </c>
+      <c r="E40" s="1" t="n">
+        <v>0.03814</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-0.01191709844559591</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1093,6 +1339,12 @@
       <c r="D41" s="2" t="n">
         <v>-0.01089285714285713</v>
       </c>
+      <c r="E41" s="1" t="n">
+        <v>0.05523</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-0.002888608051994953</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1109,6 +1361,12 @@
       <c r="D42" s="2" t="n">
         <v>-0.001473839351510654</v>
       </c>
+      <c r="E42" s="1" t="n">
+        <v>54.19</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-0.0001845018450185446</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1125,6 +1383,12 @@
       <c r="D43" s="2" t="n">
         <v>-0.004542013626040798</v>
       </c>
+      <c r="E43" s="1" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-0.0007604562737643858</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1141,6 +1405,12 @@
       <c r="D44" s="2" t="n">
         <v>-0.004089979550102201</v>
       </c>
+      <c r="E44" s="1" t="n">
+        <v>0.005865</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0.003593429158110915</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1157,6 +1427,12 @@
       <c r="D45" s="3" t="n">
         <v>0.01234945907328029</v>
       </c>
+      <c r="E45" s="1" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-0.007964512551668506</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1173,6 +1449,12 @@
       <c r="D46" s="2" t="n">
         <v>-0.0007267441860464316</v>
       </c>
+      <c r="E46" s="1" t="n">
+        <v>2.759</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.003272727272727235</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1189,6 +1471,12 @@
       <c r="D47" s="2" t="n">
         <v>-0.0007254888412906377</v>
       </c>
+      <c r="E47" s="1" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-0.0006568712186690527</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1205,6 +1493,12 @@
       <c r="D48" s="2" t="n">
         <v>-0.00283822138126782</v>
       </c>
+      <c r="E48" s="1" t="n">
+        <v>0.1064</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0.009487666034155606</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1221,6 +1515,12 @@
       <c r="D49" s="2" t="n">
         <v>-0.002467072539890788</v>
       </c>
+      <c r="E49" s="1" t="n">
+        <v>0.24801</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-0.01069049423590895</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1237,6 +1537,12 @@
       <c r="D50" s="3" t="n">
         <v>0.006051752921536009</v>
       </c>
+      <c r="E50" s="1" t="n">
+        <v>0.04791</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-0.006222775357809617</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1253,6 +1559,12 @@
       <c r="D51" s="2" t="n">
         <v>-0.001540832049306684</v>
       </c>
+      <c r="E51" s="1" t="n">
+        <v>3.891</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0.0007716049382716342</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1269,6 +1581,12 @@
       <c r="D52" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E52" s="1" t="n">
+        <v>0.000236</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-0.008403361344537905</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1285,6 +1603,12 @@
       <c r="D53" s="2" t="n">
         <v>-0.004845548152634737</v>
       </c>
+      <c r="E53" s="1" t="n">
+        <v>0.1649</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0.00365185636031643</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1301,6 +1625,12 @@
       <c r="D54" s="3" t="n">
         <v>0.009394313967861518</v>
       </c>
+      <c r="E54" s="1" t="n">
+        <v>0.04133</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0.01224589762429587</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1317,6 +1647,12 @@
       <c r="D55" s="3" t="n">
         <v>0.001829065513801114</v>
       </c>
+      <c r="E55" s="1" t="n">
+        <v>0.1213</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>0.006639004149377669</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1333,6 +1669,12 @@
       <c r="D56" s="2" t="n">
         <v>-0.002502345949327393</v>
       </c>
+      <c r="E56" s="1" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0.002508623392913036</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1349,6 +1691,12 @@
       <c r="D57" s="2" t="n">
         <v>-0.005867560771165036</v>
       </c>
+      <c r="E57" s="1" t="n">
+        <v>0.01182</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-0.003372681281618896</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1365,6 +1713,12 @@
       <c r="D58" s="3" t="n">
         <v>0.001012145748987883</v>
       </c>
+      <c r="E58" s="1" t="n">
+        <v>0.09909999999999999</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0.002022244691607602</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1381,6 +1735,12 @@
       <c r="D59" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E59" s="1" t="n">
+        <v>0.00335</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1397,6 +1757,12 @@
       <c r="D60" s="2" t="n">
         <v>-0.0006583278472680497</v>
       </c>
+      <c r="E60" s="1" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0.004611330698287261</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1413,6 +1779,12 @@
       <c r="D61" s="2" t="n">
         <v>-0.002329681400327298</v>
       </c>
+      <c r="E61" s="1" t="n">
+        <v>0.15888</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0.002713789839065863</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1429,6 +1801,12 @@
       <c r="D62" s="2" t="n">
         <v>-0.004937226689236772</v>
       </c>
+      <c r="E62" s="1" t="n">
+        <v>0.7073</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0.002693507229940477</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1445,6 +1823,12 @@
       <c r="D63" s="3" t="n">
         <v>0.001052077853761063</v>
       </c>
+      <c r="E63" s="1" t="n">
+        <v>5.819</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>0.01926782273603089</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1461,6 +1845,12 @@
       <c r="D64" s="2" t="n">
         <v>-0.002980837473385406</v>
       </c>
+      <c r="E64" s="1" t="n">
+        <v>0.007049</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0.003559225512528452</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1477,6 +1867,12 @@
       <c r="D65" s="3" t="n">
         <v>0.01546561368871333</v>
       </c>
+      <c r="E65" s="1" t="n">
+        <v>0.03035</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-0.01652624756966948</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1493,6 +1889,12 @@
       <c r="D66" s="2" t="n">
         <v>-0.004291845493562235</v>
       </c>
+      <c r="E66" s="1" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0.00431034482758621</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1509,6 +1911,12 @@
       <c r="D67" s="3" t="n">
         <v>0.002503128911138926</v>
       </c>
+      <c r="E67" s="1" t="n">
+        <v>1.614</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0.007490636704119856</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1525,6 +1933,12 @@
       <c r="D68" s="2" t="n">
         <v>-0.008919673111421292</v>
       </c>
+      <c r="E68" s="1" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>-0.0004525114384835341</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1541,6 +1955,12 @@
       <c r="D69" s="3" t="n">
         <v>0.002440725244072449</v>
       </c>
+      <c r="E69" s="1" t="n">
+        <v>0.5715</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-0.00608695652173904</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1557,6 +1977,12 @@
       <c r="D70" s="2" t="n">
         <v>-0.0188679245283019</v>
       </c>
+      <c r="E70" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1573,6 +1999,12 @@
       <c r="D71" s="2" t="n">
         <v>-0.0005490885130682462</v>
       </c>
+      <c r="E71" s="1" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0.003186463026041109</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1589,6 +2021,12 @@
       <c r="D72" s="2" t="n">
         <v>-0.002814919071076787</v>
       </c>
+      <c r="E72" s="1" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0.01623147494707132</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1605,6 +2043,12 @@
       <c r="D73" s="2" t="n">
         <v>-0.003080845639009865</v>
       </c>
+      <c r="E73" s="1" t="n">
+        <v>0.09393</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0.0009590792838873919</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1621,6 +2065,12 @@
       <c r="D74" s="2" t="n">
         <v>-0.002075047553173249</v>
       </c>
+      <c r="E74" s="1" t="n">
+        <v>1.1491</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-0.004418644948882241</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1637,6 +2087,12 @@
       <c r="D75" s="2" t="n">
         <v>-0.0100439422473321</v>
       </c>
+      <c r="E75" s="1" t="n">
+        <v>0.01578</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.000634115409004413</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1653,6 +2109,12 @@
       <c r="D76" s="2" t="n">
         <v>-0.01154789211421331</v>
       </c>
+      <c r="E76" s="1" t="n">
+        <v>0.1244</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>-0.004561094662719061</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1669,6 +2131,12 @@
       <c r="D77" s="3" t="n">
         <v>0.00341005967604431</v>
       </c>
+      <c r="E77" s="1" t="n">
+        <v>0.1178</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0.0008496176720476029</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1685,6 +2153,12 @@
       <c r="D78" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E78" s="1" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1701,6 +2175,12 @@
       <c r="D79" s="2" t="n">
         <v>-0.001347935973041313</v>
       </c>
+      <c r="E79" s="1" t="n">
+        <v>0.005939</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0.002024633035262335</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1717,6 +2197,12 @@
       <c r="D80" s="3" t="n">
         <v>0.009652270758569477</v>
       </c>
+      <c r="E80" s="1" t="n">
+        <v>0.008159</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1733,6 +2219,12 @@
       <c r="D81" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E81" s="1" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0.002256063169768706</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1749,6 +2241,12 @@
       <c r="D82" s="3" t="n">
         <v>0.0006242197253432521</v>
       </c>
+      <c r="E82" s="1" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1765,6 +2263,12 @@
       <c r="D83" s="2" t="n">
         <v>-0.002078747860112648</v>
       </c>
+      <c r="E83" s="1" t="n">
+        <v>8.177</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0.001960544050974147</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1781,6 +2285,12 @@
       <c r="D84" s="3" t="n">
         <v>0.0001705999431333587</v>
       </c>
+      <c r="E84" s="1" t="n">
+        <v>350.77</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>-0.002814418921992293</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1797,6 +2307,12 @@
       <c r="D85" s="3" t="n">
         <v>0.0009636232233196009</v>
       </c>
+      <c r="E85" s="1" t="n">
+        <v>0.004178</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0.005535499398315391</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1813,6 +2329,12 @@
       <c r="D86" s="3" t="n">
         <v>0.003590664272890546</v>
       </c>
+      <c r="E86" s="1" t="n">
+        <v>0.13338</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>-0.005813953488372115</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1829,6 +2351,12 @@
       <c r="D87" s="3" t="n">
         <v>0.03746701846965693</v>
       </c>
+      <c r="E87" s="1" t="n">
+        <v>0.01942</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>-0.01220752797558498</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1845,6 +2373,12 @@
       <c r="D88" s="3" t="n">
         <v>0.001785714285714287</v>
       </c>
+      <c r="E88" s="1" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1861,6 +2395,12 @@
       <c r="D89" s="2" t="n">
         <v>-0.001014884979702189</v>
       </c>
+      <c r="E89" s="1" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.002370470707754752</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1877,6 +2417,12 @@
       <c r="D90" s="2" t="n">
         <v>-0.002346499804458308</v>
       </c>
+      <c r="E90" s="1" t="n">
+        <v>0.2555</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0.001568012544100398</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1893,6 +2439,12 @@
       <c r="D91" s="3" t="n">
         <v>0.001703867779860332</v>
       </c>
+      <c r="E91" s="1" t="n">
+        <v>0.05796</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>-0.01411804728695364</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1909,6 +2461,12 @@
       <c r="D92" s="2" t="n">
         <v>-0.001525902189669643</v>
       </c>
+      <c r="E92" s="1" t="n">
+        <v>1.3077</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>-0.0007641170627339267</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1925,6 +2483,12 @@
       <c r="D93" s="2" t="n">
         <v>-0.00413223140495884</v>
       </c>
+      <c r="E93" s="1" t="n">
+        <v>0.06279</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0.00207468879668058</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1941,6 +2505,12 @@
       <c r="D94" s="2" t="n">
         <v>-0.008978675645342335</v>
       </c>
+      <c r="E94" s="1" t="n">
+        <v>0.00891</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.00906002265005665</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1957,6 +2527,12 @@
       <c r="D95" s="2" t="n">
         <v>-0.001208459214501545</v>
       </c>
+      <c r="E95" s="1" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0.003327283726557743</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1973,6 +2549,12 @@
       <c r="D96" s="2" t="n">
         <v>-0.005291005291005228</v>
       </c>
+      <c r="E96" s="1" t="n">
+        <v>0.02262</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0.002659574468085152</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1989,6 +2571,12 @@
       <c r="D97" s="2" t="n">
         <v>-0.003674219228413884</v>
       </c>
+      <c r="E97" s="1" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>0.004609711124769471</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2005,6 +2593,12 @@
       <c r="D98" s="2" t="n">
         <v>-0.002734731084776565</v>
       </c>
+      <c r="E98" s="1" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>0.0009140767824496251</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2021,6 +2615,12 @@
       <c r="D99" s="2" t="n">
         <v>-0.002006688963210778</v>
       </c>
+      <c r="E99" s="1" t="n">
+        <v>2.987</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>0.001005361930294944</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2037,6 +2637,12 @@
       <c r="D100" s="2" t="n">
         <v>-0.008623167576889959</v>
       </c>
+      <c r="E100" s="1" t="n">
+        <v>0.03442</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>-0.002029573789504222</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2053,6 +2659,12 @@
       <c r="D101" s="3" t="n">
         <v>0.002207505518763799</v>
       </c>
+      <c r="E101" s="1" t="n">
+        <v>1.817</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0.0005506607929514812</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2069,6 +2681,12 @@
       <c r="D102" s="3" t="n">
         <v>0.002960969044414578</v>
       </c>
+      <c r="E102" s="1" t="n">
+        <v>0.007513</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0.008185721953837818</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2085,6 +2703,12 @@
       <c r="D103" s="3" t="n">
         <v>0.004477611940298428</v>
       </c>
+      <c r="E103" s="1" t="n">
+        <v>0.06794</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>0.009509658246656786</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2101,6 +2725,12 @@
       <c r="D104" s="3" t="n">
         <v>0.0004856726566293783</v>
       </c>
+      <c r="E104" s="1" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>0.0063106796116506</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2117,6 +2747,12 @@
       <c r="D105" s="2" t="n">
         <v>-0.00615901455767084</v>
       </c>
+      <c r="E105" s="1" t="n">
+        <v>1.782</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0.003943661971831052</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2133,6 +2769,12 @@
       <c r="D106" s="2" t="n">
         <v>-0.009225092250922559</v>
       </c>
+      <c r="E106" s="1" t="n">
+        <v>0.008088</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>0.004096834264432035</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2149,6 +2791,12 @@
       <c r="D107" s="3" t="n">
         <v>0.001098901098901054</v>
       </c>
+      <c r="E107" s="1" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2165,6 +2813,12 @@
       <c r="D108" s="3" t="n">
         <v>0.005233111322549904</v>
       </c>
+      <c r="E108" s="1" t="n">
+        <v>0.02129</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0.007572172266919092</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2181,6 +2835,12 @@
       <c r="D109" s="2" t="n">
         <v>-0.0008857395925598128</v>
       </c>
+      <c r="E109" s="1" t="n">
+        <v>0.05624</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>-0.002836879432624121</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2197,6 +2857,12 @@
       <c r="D110" s="2" t="n">
         <v>-0.01827352406151814</v>
       </c>
+      <c r="E110" s="1" t="n">
+        <v>0.11989</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0.009770066537522061</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2213,6 +2879,12 @@
       <c r="D111" s="2" t="n">
         <v>-0.004542242858584899</v>
       </c>
+      <c r="E111" s="1" t="n">
+        <v>0.09912</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0.00506996552423444</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2229,6 +2901,12 @@
       <c r="D112" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E112" s="1" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2245,6 +2923,12 @@
       <c r="D113" s="2" t="n">
         <v>-0.002042900919305472</v>
       </c>
+      <c r="E113" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0.001023541453428893</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2261,6 +2945,12 @@
       <c r="D114" s="3" t="n">
         <v>0.00988947062245484</v>
       </c>
+      <c r="E114" s="1" t="n">
+        <v>0.001726</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>-0.00576036866359436</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2277,6 +2967,12 @@
       <c r="D115" s="3" t="n">
         <v>0.002274204028589923</v>
       </c>
+      <c r="E115" s="1" t="n">
+        <v>1.2361</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0.001701782820097237</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2293,6 +2989,12 @@
       <c r="D116" s="3" t="n">
         <v>0.005439330543933152</v>
       </c>
+      <c r="E116" s="1" t="n">
+        <v>0.2387</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>-0.006658343736995497</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2309,6 +3011,12 @@
       <c r="D117" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E117" s="1" t="n">
+        <v>0.06091</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0.009446470003314569</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2325,6 +3033,12 @@
       <c r="D118" s="2" t="n">
         <v>-0.00718590635141395</v>
       </c>
+      <c r="E118" s="1" t="n">
+        <v>0.04314</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0.007237917347653462</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2341,6 +3055,12 @@
       <c r="D119" s="2" t="n">
         <v>-0.008856473039854174</v>
       </c>
+      <c r="E119" s="1" t="n">
+        <v>0.003803</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>-0.0005256241787121766</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2357,6 +3077,12 @@
       <c r="D120" s="2" t="n">
         <v>-0.001272264631043258</v>
       </c>
+      <c r="E120" s="1" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0.003821656050955417</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2373,6 +3099,12 @@
       <c r="D121" s="2" t="n">
         <v>-0.00337268128161889</v>
       </c>
+      <c r="E121" s="1" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0.001692047377326567</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2389,6 +3121,12 @@
       <c r="D122" s="2" t="n">
         <v>-0.001401296198983906</v>
       </c>
+      <c r="E122" s="1" t="n">
+        <v>0.5696</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>-0.0008770391159446692</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2405,6 +3143,12 @@
       <c r="D123" s="3" t="n">
         <v>0.01426313015984543</v>
       </c>
+      <c r="E123" s="1" t="n">
+        <v>0.028964</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0.003221225451144724</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2421,6 +3165,12 @@
       <c r="D124" s="2" t="n">
         <v>-0.003384306843820586</v>
       </c>
+      <c r="E124" s="1" t="n">
+        <v>0.07914</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>-0.004653502704062324</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2437,6 +3187,12 @@
       <c r="D125" s="2" t="n">
         <v>-0.0009878494517435825</v>
       </c>
+      <c r="E125" s="1" t="n">
+        <v>0.10159</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0.004548600810837557</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2453,6 +3209,12 @@
       <c r="D126" s="3" t="n">
         <v>0.007301935012778342</v>
       </c>
+      <c r="E126" s="1" t="n">
+        <v>0.02731</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>-0.01014860456687202</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2469,6 +3231,12 @@
       <c r="D127" s="2" t="n">
         <v>-0.0009078529278258127</v>
       </c>
+      <c r="E127" s="1" t="n">
+        <v>0.02215</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>0.006360745115856485</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2485,6 +3253,12 @@
       <c r="D128" s="2" t="n">
         <v>-0.003715170278637877</v>
       </c>
+      <c r="E128" s="1" t="n">
+        <v>0.1608</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>-0.0006215040397761902</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2501,6 +3275,12 @@
       <c r="D129" s="2" t="n">
         <v>-0.003152723806730799</v>
       </c>
+      <c r="E129" s="1" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>-0.005589879376287222</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2517,6 +3297,12 @@
       <c r="D130" s="2" t="n">
         <v>-0.005245901639344201</v>
       </c>
+      <c r="E130" s="1" t="n">
+        <v>0.054237</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>-0.006866622720281263</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2533,6 +3319,12 @@
       <c r="D131" s="2" t="n">
         <v>-0.003306797305572643</v>
       </c>
+      <c r="E131" s="1" t="n">
+        <v>0.08147</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0.001105922831162531</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2549,6 +3341,12 @@
       <c r="D132" s="2" t="n">
         <v>-0.002309468822170807</v>
       </c>
+      <c r="E132" s="1" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2565,6 +3363,12 @@
       <c r="D133" s="3" t="n">
         <v>0.000519031141868647</v>
       </c>
+      <c r="E133" s="1" t="n">
+        <v>0.5793</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>0.001729206294310913</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2581,6 +3385,12 @@
       <c r="D134" s="2" t="n">
         <v>-0.006851549755301855</v>
       </c>
+      <c r="E134" s="1" t="n">
+        <v>0.03038</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>-0.001971090670170747</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2597,6 +3407,12 @@
       <c r="D135" s="3" t="n">
         <v>0.001133786848072516</v>
       </c>
+      <c r="E135" s="1" t="n">
+        <v>0.01765</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>-0.000566251415628516</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2613,6 +3429,12 @@
       <c r="D136" s="2" t="n">
         <v>-0.001348799568384177</v>
       </c>
+      <c r="E136" s="1" t="n">
+        <v>0.03703</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>0.0002701242571583755</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2629,6 +3451,12 @@
       <c r="D137" s="2" t="n">
         <v>-0.0003724394785847148</v>
       </c>
+      <c r="E137" s="1" t="n">
+        <v>0.02691</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>0.002608047690014926</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2645,6 +3473,12 @@
       <c r="D138" s="2" t="n">
         <v>-0.002012882447665013</v>
       </c>
+      <c r="E138" s="1" t="n">
+        <v>2.483</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>0.001613553852359824</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2661,6 +3495,12 @@
       <c r="D139" s="3" t="n">
         <v>0.005912162162162215</v>
       </c>
+      <c r="E139" s="1" t="n">
+        <v>0.01191</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2677,6 +3517,12 @@
       <c r="D140" s="2" t="n">
         <v>-0.005769230769230757</v>
       </c>
+      <c r="E140" s="1" t="n">
+        <v>0.01511</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>-0.02578981302385553</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2693,6 +3539,12 @@
       <c r="D141" s="3" t="n">
         <v>6.248437890512805e-05</v>
       </c>
+      <c r="E141" s="1" t="n">
+        <v>16.042</v>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>0.00231177756950969</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2709,6 +3561,12 @@
       <c r="D142" s="3" t="n">
         <v>0.001612903225806526</v>
       </c>
+      <c r="E142" s="1" t="n">
+        <v>0.01244</v>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>0.001610305958131979</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2725,6 +3583,12 @@
       <c r="D143" s="2" t="n">
         <v>-0.001514577811435001</v>
       </c>
+      <c r="E143" s="1" t="n">
+        <v>0.02641</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>0.001516875237011694</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2741,6 +3605,12 @@
       <c r="D144" s="3" t="n">
         <v>0.001508945893511546</v>
       </c>
+      <c r="E144" s="1" t="n">
+        <v>0.004662</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>0.003443822643133962</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2757,6 +3627,12 @@
       <c r="D145" s="2" t="n">
         <v>-0.001564155608254757</v>
       </c>
+      <c r="E145" s="1" t="n">
+        <v>1.9867</v>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>0.003992318576915311</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2773,6 +3649,12 @@
       <c r="D146" s="2" t="n">
         <v>-0.002625820568927683</v>
       </c>
+      <c r="E146" s="1" t="n">
+        <v>0.02292</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>0.00570425625274235</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2789,6 +3671,12 @@
       <c r="D147" s="3" t="n">
         <v>0.004034517538944292</v>
       </c>
+      <c r="E147" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>0.00569259962049332</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2805,6 +3693,12 @@
       <c r="D148" s="3" t="n">
         <v>0.02363823227132578</v>
       </c>
+      <c r="E148" s="1" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>0.01070950468540833</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2821,6 +3715,12 @@
       <c r="D149" s="2" t="n">
         <v>-0.001690617075232508</v>
       </c>
+      <c r="E149" s="1" t="n">
+        <v>0.05902</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>-0.0005080440304825624</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2837,6 +3737,12 @@
       <c r="D150" s="2" t="n">
         <v>-0.005568240996675088</v>
       </c>
+      <c r="E150" s="1" t="n">
+        <v>0.24954</v>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>0.005236867547534738</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2853,6 +3759,12 @@
       <c r="D151" s="2" t="n">
         <v>-0.001791579575992918</v>
       </c>
+      <c r="E151" s="1" t="n">
+        <v>6.708e-05</v>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>0.003290457672749149</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2869,6 +3781,12 @@
       <c r="D152" s="2" t="n">
         <v>-0.004502476361999103</v>
       </c>
+      <c r="E152" s="1" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>-0.002713704206241472</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2885,6 +3803,12 @@
       <c r="D153" s="3" t="n">
         <v>0.007902535396772992</v>
       </c>
+      <c r="E153" s="1" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>0.003920287487749214</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2901,6 +3825,12 @@
       <c r="D154" s="2" t="n">
         <v>-0.01793842034805886</v>
       </c>
+      <c r="E154" s="1" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>0.007088331515812407</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2917,6 +3847,12 @@
       <c r="D155" s="3" t="n">
         <v>0.0004344048653345645</v>
       </c>
+      <c r="E155" s="1" t="n">
+        <v>0.2303</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2933,6 +3869,12 @@
       <c r="D156" s="2" t="n">
         <v>-0.009674259123193718</v>
       </c>
+      <c r="E156" s="1" t="n">
+        <v>0.08130999999999999</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>0.005440830963274341</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2949,6 +3891,12 @@
       <c r="D157" s="3" t="n">
         <v>0.009253799047402977</v>
       </c>
+      <c r="E157" s="1" t="n">
+        <v>0.22985</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>0.03308013843318804</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2965,6 +3913,12 @@
       <c r="D158" s="2" t="n">
         <v>-0.004417670682730883</v>
       </c>
+      <c r="E158" s="1" t="n">
+        <v>0.2489</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>0.00403388463089956</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2981,6 +3935,12 @@
       <c r="D159" s="2" t="n">
         <v>-0.002714625042416019</v>
       </c>
+      <c r="E159" s="1" t="n">
+        <v>2.936</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>-0.001020755358965673</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2997,6 +3957,12 @@
       <c r="D160" s="2" t="n">
         <v>-0.003992015968063849</v>
       </c>
+      <c r="E160" s="1" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>0.001002004008016061</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3013,6 +3979,12 @@
       <c r="D161" s="2" t="n">
         <v>-0.003558718861209914</v>
       </c>
+      <c r="E161" s="1" t="n">
+        <v>0.14613</v>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>0.003640109890109908</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3029,6 +4001,12 @@
       <c r="D162" s="3" t="n">
         <v>0.001848428835489812</v>
       </c>
+      <c r="E162" s="1" t="n">
+        <v>0.003261</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>0.00276752767527672</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3045,6 +4023,12 @@
       <c r="D163" s="2" t="n">
         <v>-0.003011443485243978</v>
       </c>
+      <c r="E163" s="1" t="n">
+        <v>0.004971</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>0.001006846556584735</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3061,6 +4045,12 @@
       <c r="D164" s="3" t="n">
         <v>0.005252100840335993</v>
       </c>
+      <c r="E164" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3077,6 +4067,12 @@
       <c r="D165" s="2" t="n">
         <v>-0.005225342913128823</v>
       </c>
+      <c r="E165" s="1" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>-0.001969796454366348</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3093,6 +4089,12 @@
       <c r="D166" s="2" t="n">
         <v>-0.001368481705560366</v>
       </c>
+      <c r="E166" s="1" t="n">
+        <v>1.3859</v>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>-0.0004327443202309094</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3109,6 +4111,12 @@
       <c r="D167" s="3" t="n">
         <v>0.000722804481387705</v>
       </c>
+      <c r="E167" s="1" t="n">
+        <v>0.2766</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>-0.001083423618634767</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3125,6 +4133,12 @@
       <c r="D168" s="2" t="n">
         <v>-0.006349206349206354</v>
       </c>
+      <c r="E168" s="1" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>0.003194888178913741</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3141,6 +4155,12 @@
       <c r="D169" s="2" t="n">
         <v>-0.002716468590831926</v>
       </c>
+      <c r="E169" s="1" t="n">
+        <v>0.02942</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>0.00170241743275456</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3157,6 +4177,12 @@
       <c r="D170" s="2" t="n">
         <v>-0.006648936170212802</v>
       </c>
+      <c r="E170" s="1" t="n">
+        <v>0.04411</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>-0.01584114234716634</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3173,6 +4199,12 @@
       <c r="D171" s="2" t="n">
         <v>-0.006024096385542133</v>
       </c>
+      <c r="E171" s="1" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3189,6 +4221,12 @@
       <c r="D172" s="2" t="n">
         <v>-0.008130081300813068</v>
       </c>
+      <c r="E172" s="1" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>-0.008196721311475471</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3205,6 +4243,12 @@
       <c r="D173" s="2" t="n">
         <v>-0.0009546539379474551</v>
       </c>
+      <c r="E173" s="1" t="n">
+        <v>0.02093</v>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3221,6 +4265,12 @@
       <c r="D174" s="3" t="n">
         <v>0.004279279279279183</v>
       </c>
+      <c r="E174" s="1" t="n">
+        <v>0.09014999999999999</v>
+      </c>
+      <c r="F174" s="3" t="n">
+        <v>0.01087687822381699</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3237,6 +4287,12 @@
       <c r="D175" s="2" t="n">
         <v>-0.002501389660922768</v>
       </c>
+      <c r="E175" s="1" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>-0.001114516578434136</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3253,6 +4309,12 @@
       <c r="D176" s="3" t="n">
         <v>0.0009319664492077905</v>
       </c>
+      <c r="E176" s="1" t="n">
+        <v>0.02145</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>-0.001396648044692681</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3269,6 +4331,12 @@
       <c r="D177" s="3" t="n">
         <v>0.002525252525252422</v>
       </c>
+      <c r="E177" s="1" t="n">
+        <v>0.00796</v>
+      </c>
+      <c r="F177" s="3" t="n">
+        <v>0.002518891687657547</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3285,6 +4353,12 @@
       <c r="D178" s="2" t="n">
         <v>-0.005060728744939285</v>
       </c>
+      <c r="E178" s="1" t="n">
+        <v>0.00098</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>-0.0030518819938962</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3301,6 +4375,12 @@
       <c r="D179" s="3" t="n">
         <v>0.0009176717357103966</v>
       </c>
+      <c r="E179" s="1" t="n">
+        <v>0.022911</v>
+      </c>
+      <c r="F179" s="3" t="n">
+        <v>0.0002619515389654019</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3317,6 +4397,12 @@
       <c r="D180" s="2" t="n">
         <v>-0.02341717259323516</v>
       </c>
+      <c r="E180" s="1" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>-0.02753108348134984</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3333,6 +4419,12 @@
       <c r="D181" s="2" t="n">
         <v>-0.006149641270925944</v>
       </c>
+      <c r="E181" s="1" t="n">
+        <v>0.5760999999999999</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>-0.009797181161911375</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3349,6 +4441,12 @@
       <c r="D182" s="2" t="n">
         <v>-0.003059351417499437</v>
       </c>
+      <c r="E182" s="1" t="n">
+        <v>0.04907</v>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>0.003887070376432133</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3365,6 +4463,12 @@
       <c r="D183" s="2" t="n">
         <v>-0.002202238942925228</v>
       </c>
+      <c r="E183" s="1" t="n">
+        <v>5.447</v>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>0.001839249586168804</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3381,6 +4485,12 @@
       <c r="D184" s="2" t="n">
         <v>-0.001758087201125201</v>
       </c>
+      <c r="E184" s="1" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>-0.0003522367030645144</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3397,6 +4507,12 @@
       <c r="D185" s="2" t="n">
         <v>-0.02194860813704482</v>
       </c>
+      <c r="E185" s="1" t="n">
+        <v>0.01832</v>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>0.002736726874657797</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3413,6 +4529,12 @@
       <c r="D186" s="2" t="n">
         <v>-0.003194888178913816</v>
       </c>
+      <c r="E186" s="1" t="n">
+        <v>3.14e-05</v>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>0.006410256410256349</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3429,6 +4551,12 @@
       <c r="D187" s="2" t="n">
         <v>-0.002492211838006129</v>
       </c>
+      <c r="E187" s="1" t="n">
+        <v>0.01614</v>
+      </c>
+      <c r="F187" s="3" t="n">
+        <v>0.008119925046845824</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3445,6 +4573,12 @@
       <c r="D188" s="3" t="n">
         <v>0.0002487562189055488</v>
       </c>
+      <c r="E188" s="1" t="n">
+        <v>0.04023</v>
+      </c>
+      <c r="F188" s="3" t="n">
+        <v>0.0004973887092762792</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -3461,6 +4595,12 @@
       <c r="D189" s="2" t="n">
         <v>-0.005509641873278246</v>
       </c>
+      <c r="E189" s="1" t="n">
+        <v>0.0004345</v>
+      </c>
+      <c r="F189" s="3" t="n">
+        <v>0.003000923361034112</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -3477,6 +4617,12 @@
       <c r="D190" s="2" t="n">
         <v>-0.0060527453523563</v>
       </c>
+      <c r="E190" s="1" t="n">
+        <v>0.02296</v>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>-0.001304915180513214</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3493,6 +4639,12 @@
       <c r="D191" s="3" t="n">
         <v>0.001272264631043205</v>
       </c>
+      <c r="E191" s="1" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>-0.002541296060991222</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3509,6 +4661,12 @@
       <c r="D192" s="2" t="n">
         <v>-0.0008984725965858299</v>
       </c>
+      <c r="E192" s="1" t="n">
+        <v>0.05561</v>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>0.0001798561151079688</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -3525,6 +4683,12 @@
       <c r="D193" s="2" t="n">
         <v>-0.002145922746781177</v>
       </c>
+      <c r="E193" s="1" t="n">
+        <v>0.1863</v>
+      </c>
+      <c r="F193" s="3" t="n">
+        <v>0.001612903225806423</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -3541,6 +4705,12 @@
       <c r="D194" s="2" t="n">
         <v>-0.001055408970976393</v>
       </c>
+      <c r="E194" s="1" t="n">
+        <v>0.01904</v>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>0.005810882197570125</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -3557,6 +4727,12 @@
       <c r="D195" s="3" t="n">
         <v>0.01658222017503464</v>
       </c>
+      <c r="E195" s="1" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>0.005210693248753894</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -3573,6 +4749,12 @@
       <c r="D196" s="3" t="n">
         <v>0.004827031375703885</v>
       </c>
+      <c r="E196" s="1" t="n">
+        <v>0.01255</v>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>0.00480384307445965</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -3589,6 +4771,12 @@
       <c r="D197" s="2" t="n">
         <v>-0.002421840598855108</v>
       </c>
+      <c r="E197" s="1" t="n">
+        <v>0.04545</v>
+      </c>
+      <c r="F197" s="3" t="n">
+        <v>0.003089825645552732</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3605,6 +4793,12 @@
       <c r="D198" s="3" t="n">
         <v>0.004711425206124988</v>
       </c>
+      <c r="E198" s="1" t="n">
+        <v>0.5109</v>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>-0.001758499413833552</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -3621,6 +4815,12 @@
       <c r="D199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E199" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -3637,6 +4837,12 @@
       <c r="D200" s="2" t="n">
         <v>-0.001355932203389802</v>
       </c>
+      <c r="E200" s="1" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>0.005431093007467758</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -3653,6 +4859,12 @@
       <c r="D201" s="2" t="n">
         <v>-0.00265486725663706</v>
       </c>
+      <c r="E201" s="1" t="n">
+        <v>0.005644</v>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>0.001597160603371687</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -3669,6 +4881,12 @@
       <c r="D202" s="2" t="n">
         <v>-0.006414172266340923</v>
       </c>
+      <c r="E202" s="1" t="n">
+        <v>0.022619</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>-0.006675156997935943</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -3685,6 +4903,12 @@
       <c r="D203" s="3" t="n">
         <v>0.007326007326007281</v>
       </c>
+      <c r="E203" s="1" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="F203" s="2" t="n">
+        <v>-0.007272727272727228</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -3701,6 +4925,12 @@
       <c r="D204" s="2" t="n">
         <v>-0.003213555360794595</v>
       </c>
+      <c r="E204" s="1" t="n">
+        <v>0.03415</v>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>0.0008792497069168303</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -3717,6 +4947,12 @@
       <c r="D205" s="2" t="n">
         <v>-0.001171508903467641</v>
       </c>
+      <c r="E205" s="1" t="n">
+        <v>4.269</v>
+      </c>
+      <c r="F205" s="3" t="n">
+        <v>0.001407459535538407</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -3733,6 +4969,12 @@
       <c r="D206" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E206" s="1" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>-0.00277777777777778</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -3749,6 +4991,12 @@
       <c r="D207" s="3" t="n">
         <v>0.01215259431469936</v>
       </c>
+      <c r="E207" s="1" t="n">
+        <v>0.0009722</v>
+      </c>
+      <c r="F207" s="3" t="n">
+        <v>0.01503445395698478</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -3765,6 +5013,12 @@
       <c r="D208" s="2" t="n">
         <v>-0.002317655078391346</v>
       </c>
+      <c r="E208" s="1" t="n">
+        <v>0.007298</v>
+      </c>
+      <c r="F208" s="2" t="n">
+        <v>-0.002732987154960379</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -3781,6 +5035,12 @@
       <c r="D209" s="2" t="n">
         <v>-0.003333333333333313</v>
       </c>
+      <c r="E209" s="1" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="F209" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -3797,6 +5057,12 @@
       <c r="D210" s="2" t="n">
         <v>-0.0007745933384972036</v>
       </c>
+      <c r="E210" s="1" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>0.000775193798449527</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -3813,6 +5079,12 @@
       <c r="D211" s="2" t="n">
         <v>-0.002685891998869209</v>
       </c>
+      <c r="E211" s="1" t="n">
+        <v>0.007063</v>
+      </c>
+      <c r="F211" s="3" t="n">
+        <v>0.001133947554925612</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -3829,6 +5101,12 @@
       <c r="D212" s="3" t="n">
         <v>0.01418181818181803</v>
       </c>
+      <c r="E212" s="1" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>0.01505916098960214</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -3845,6 +5123,12 @@
       <c r="D213" s="3" t="n">
         <v>0.003628196268141013</v>
       </c>
+      <c r="E213" s="1" t="n">
+        <v>0.05751</v>
+      </c>
+      <c r="F213" s="2" t="n">
+        <v>-0.009984506799793494</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -3861,6 +5145,12 @@
       <c r="D214" s="3" t="n">
         <v>0.00106496272630461</v>
       </c>
+      <c r="E214" s="1" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="F214" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -3877,6 +5167,12 @@
       <c r="D215" s="2" t="n">
         <v>-0.003441024660676727</v>
       </c>
+      <c r="E215" s="1" t="n">
+        <v>0.05223</v>
+      </c>
+      <c r="F215" s="3" t="n">
+        <v>0.001918281220026778</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -3893,6 +5189,12 @@
       <c r="D216" s="2" t="n">
         <v>-0.003813155386082076</v>
       </c>
+      <c r="E216" s="1" t="n">
+        <v>0.002091</v>
+      </c>
+      <c r="F216" s="3" t="n">
+        <v>0.0004784688995215946</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -3909,6 +5211,12 @@
       <c r="D217" s="2" t="n">
         <v>-0.00116783450116778</v>
       </c>
+      <c r="E217" s="1" t="n">
+        <v>5.998</v>
+      </c>
+      <c r="F217" s="3" t="n">
+        <v>0.001837314180724924</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -3925,6 +5233,12 @@
       <c r="D218" s="2" t="n">
         <v>-0.002684563758389165</v>
       </c>
+      <c r="E218" s="1" t="n">
+        <v>4.437</v>
+      </c>
+      <c r="F218" s="2" t="n">
+        <v>-0.004710632570659468</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -3941,6 +5255,12 @@
       <c r="D219" s="3" t="n">
         <v>0.002249297094657893</v>
       </c>
+      <c r="E219" s="1" t="n">
+        <v>0.005353</v>
+      </c>
+      <c r="F219" s="3" t="n">
+        <v>0.001122124555825683</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -3957,6 +5277,12 @@
       <c r="D220" s="3" t="n">
         <v>0.002196729314132287</v>
       </c>
+      <c r="E220" s="1" t="n">
+        <v>0.04116</v>
+      </c>
+      <c r="F220" s="3" t="n">
+        <v>0.002435460301997147</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -3973,6 +5299,12 @@
       <c r="D221" s="2" t="n">
         <v>-0.001392030624673777</v>
       </c>
+      <c r="E221" s="1" t="n">
+        <v>0.005764</v>
+      </c>
+      <c r="F221" s="3" t="n">
+        <v>0.004356159609688073</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -3989,6 +5321,12 @@
       <c r="D222" s="2" t="n">
         <v>-0.002209944751381125</v>
       </c>
+      <c r="E222" s="1" t="n">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="F222" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4005,6 +5343,12 @@
       <c r="D223" s="2" t="n">
         <v>-0.0008896797153025577</v>
       </c>
+      <c r="E223" s="1" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="F223" s="2" t="n">
+        <v>-0.0008904719501334728</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4021,6 +5365,12 @@
       <c r="D224" s="2" t="n">
         <v>-0.003699421965317897</v>
       </c>
+      <c r="E224" s="1" t="n">
+        <v>0.4314</v>
+      </c>
+      <c r="F224" s="3" t="n">
+        <v>0.001160362032954283</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4037,6 +5387,12 @@
       <c r="D225" s="2" t="n">
         <v>-0.0003606202668590245</v>
       </c>
+      <c r="E225" s="1" t="n">
+        <v>0.08327</v>
+      </c>
+      <c r="F225" s="3" t="n">
+        <v>0.001322751322751311</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4053,6 +5409,12 @@
       <c r="D226" s="2" t="n">
         <v>-0.009984235417761387</v>
       </c>
+      <c r="E226" s="1" t="n">
+        <v>0.01879</v>
+      </c>
+      <c r="F226" s="2" t="n">
+        <v>-0.002653927813163374</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4069,6 +5431,12 @@
       <c r="D227" s="2" t="n">
         <v>-0.002796901893287396</v>
       </c>
+      <c r="E227" s="1" t="n">
+        <v>0.04655</v>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>0.004314994606256716</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4085,6 +5453,12 @@
       <c r="D228" s="2" t="n">
         <v>-0.0008613264427219058</v>
       </c>
+      <c r="E228" s="1" t="n">
+        <v>0.02326</v>
+      </c>
+      <c r="F228" s="3" t="n">
+        <v>0.002586206896551768</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4101,6 +5475,12 @@
       <c r="D229" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E229" s="1" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="F229" s="3" t="n">
+        <v>0.003748828491096509</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4117,6 +5497,12 @@
       <c r="D230" s="3" t="n">
         <v>0.004211793020457318</v>
       </c>
+      <c r="E230" s="1" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="F230" s="2" t="n">
+        <v>-0.001198322348711838</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4133,6 +5519,12 @@
       <c r="D231" s="3" t="n">
         <v>0.0003284072249589357</v>
       </c>
+      <c r="E231" s="1" t="n">
+        <v>0.03044</v>
+      </c>
+      <c r="F231" s="2" t="n">
+        <v>-0.0006565988181222145</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4149,6 +5541,12 @@
       <c r="D232" s="3" t="n">
         <v>0.0008646779074794286</v>
       </c>
+      <c r="E232" s="1" t="n">
+        <v>0.02307</v>
+      </c>
+      <c r="F232" s="2" t="n">
+        <v>-0.00345572354211664</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4165,6 +5563,12 @@
       <c r="D233" s="2" t="n">
         <v>-0.0700248475265418</v>
       </c>
+      <c r="E233" s="1" t="n">
+        <v>0.12771</v>
+      </c>
+      <c r="F233" s="3" t="n">
+        <v>0.03400534369686661</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4181,6 +5585,12 @@
       <c r="D234" s="2" t="n">
         <v>-0.002384737678855284</v>
       </c>
+      <c r="E234" s="1" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>-0.00239043824701191</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4197,6 +5607,12 @@
       <c r="D235" s="2" t="n">
         <v>-0.0008704482808647104</v>
       </c>
+      <c r="E235" s="1" t="n">
+        <v>0.06919</v>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>0.00464643531290839</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4213,6 +5629,12 @@
       <c r="D236" s="2" t="n">
         <v>-0.006675350048844035</v>
       </c>
+      <c r="E236" s="1" t="n">
+        <v>0.12225</v>
+      </c>
+      <c r="F236" s="3" t="n">
+        <v>0.001884936895590838</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4229,6 +5651,12 @@
       <c r="D237" s="2" t="n">
         <v>-0.004794885455514108</v>
       </c>
+      <c r="E237" s="1" t="n">
+        <v>0.03792</v>
+      </c>
+      <c r="F237" s="3" t="n">
+        <v>0.0149892933618845</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4245,6 +5673,12 @@
       <c r="D238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E238" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4261,6 +5695,12 @@
       <c r="D239" s="2" t="n">
         <v>-0.006482174021441033</v>
       </c>
+      <c r="E239" s="1" t="n">
+        <v>0.004005</v>
+      </c>
+      <c r="F239" s="3" t="n">
+        <v>0.00501882057716438</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4277,6 +5717,12 @@
       <c r="D240" s="3" t="n">
         <v>0.0007304601899196196</v>
       </c>
+      <c r="E240" s="1" t="n">
+        <v>0.01369</v>
+      </c>
+      <c r="F240" s="2" t="n">
+        <v>-0.0007299270072992403</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4293,6 +5739,12 @@
       <c r="D241" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E241" s="1" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="F241" s="2" t="n">
+        <v>-0.002801774457156279</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4309,6 +5761,12 @@
       <c r="D242" s="2" t="n">
         <v>-0.004081632653061176</v>
       </c>
+      <c r="E242" s="1" t="n">
+        <v>0.00734</v>
+      </c>
+      <c r="F242" s="3" t="n">
+        <v>0.002732240437158477</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4325,6 +5783,12 @@
       <c r="D243" s="2" t="n">
         <v>-0.004347826086956496</v>
       </c>
+      <c r="E243" s="1" t="n">
+        <v>0.02301</v>
+      </c>
+      <c r="F243" s="3" t="n">
+        <v>0.004803493449781615</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4341,6 +5805,12 @@
       <c r="D244" s="3" t="n">
         <v>0.00361228175797721</v>
       </c>
+      <c r="E244" s="1" t="n">
+        <v>0.001678</v>
+      </c>
+      <c r="F244" s="3" t="n">
+        <v>0.006598680263947176</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4357,6 +5827,12 @@
       <c r="D245" s="2" t="n">
         <v>-0.0007616146230006777</v>
       </c>
+      <c r="E245" s="1" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="F245" s="3" t="n">
+        <v>0.002286585365853618</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4373,6 +5849,12 @@
       <c r="D246" s="3" t="n">
         <v>0.003816793893129615</v>
       </c>
+      <c r="E246" s="1" t="n">
+        <v>0.03144</v>
+      </c>
+      <c r="F246" s="2" t="n">
+        <v>-0.003802281368821138</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -4389,6 +5871,12 @@
       <c r="D247" s="2" t="n">
         <v>-0.00615556799104639</v>
       </c>
+      <c r="E247" s="1" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>0.000563063063063001</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -4405,6 +5893,12 @@
       <c r="D248" s="3" t="n">
         <v>0.005597629239380968</v>
       </c>
+      <c r="E248" s="1" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="F248" s="2" t="n">
+        <v>-0.00458415193189264</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -4421,6 +5915,12 @@
       <c r="D249" s="2" t="n">
         <v>-0.007066728452270654</v>
       </c>
+      <c r="E249" s="1" t="n">
+        <v>0.008547000000000001</v>
+      </c>
+      <c r="F249" s="2" t="n">
+        <v>-0.002800140007000317</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4437,6 +5937,12 @@
       <c r="D250" s="3" t="n">
         <v>0.0004828585224529017</v>
       </c>
+      <c r="E250" s="1" t="n">
+        <v>0.02085</v>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>0.006274131274131354</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -4453,6 +5959,12 @@
       <c r="D251" s="2" t="n">
         <v>-0.001066780456582066</v>
       </c>
+      <c r="E251" s="1" t="n">
+        <v>0.04676</v>
+      </c>
+      <c r="F251" s="2" t="n">
+        <v>-0.001281503630926902</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -4469,6 +5981,12 @@
       <c r="D252" s="2" t="n">
         <v>-0.004313443565779964</v>
       </c>
+      <c r="E252" s="1" t="n">
+        <v>0.008333</v>
+      </c>
+      <c r="F252" s="3" t="n">
+        <v>0.002767749699157696</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -4485,6 +6003,12 @@
       <c r="D253" s="2" t="n">
         <v>-0.008293541090726237</v>
       </c>
+      <c r="E253" s="1" t="n">
+        <v>0.03941</v>
+      </c>
+      <c r="F253" s="2" t="n">
+        <v>-0.001267105930055789</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -4501,6 +6025,12 @@
       <c r="D254" s="3" t="n">
         <v>0.001150937191713262</v>
       </c>
+      <c r="E254" s="1" t="n">
+        <v>0.06097</v>
+      </c>
+      <c r="F254" s="3" t="n">
+        <v>0.001313844637871632</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -4517,6 +6047,12 @@
       <c r="D255" s="3" t="n">
         <v>0.0136791108577942</v>
       </c>
+      <c r="E255" s="1" t="n">
+        <v>0.003605</v>
+      </c>
+      <c r="F255" s="3" t="n">
+        <v>0.01349451785212266</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -4533,6 +6069,12 @@
       <c r="D256" s="3" t="n">
         <v>0.0108586830958799</v>
       </c>
+      <c r="E256" s="1" t="n">
+        <v>0.013109</v>
+      </c>
+      <c r="F256" s="2" t="n">
+        <v>-0.001295139417949082</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -4549,6 +6091,12 @@
       <c r="D257" s="2" t="n">
         <v>-1.000626392150242e-06</v>
       </c>
+      <c r="E257" s="1" t="n">
+        <v>0.999374</v>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>1.00062739340442e-06</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -4565,6 +6113,12 @@
       <c r="D258" s="2" t="n">
         <v>-0.0008092485549131415</v>
       </c>
+      <c r="E258" s="1" t="n">
+        <v>0.08591</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>-0.00601642948050453</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -4581,6 +6135,12 @@
       <c r="D259" s="3" t="n">
         <v>0.0009027307605506289</v>
       </c>
+      <c r="E259" s="1" t="n">
+        <v>0.08949</v>
+      </c>
+      <c r="F259" s="3" t="n">
+        <v>0.008906426155580597</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -4597,6 +6157,12 @@
       <c r="D260" s="3" t="n">
         <v>0.002218387971407439</v>
       </c>
+      <c r="E260" s="1" t="n">
+        <v>0.08101999999999999</v>
+      </c>
+      <c r="F260" s="2" t="n">
+        <v>-0.003689129365469855</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -4613,6 +6179,12 @@
       <c r="D261" s="3" t="n">
         <v>0.005376344086021509</v>
       </c>
+      <c r="E261" s="1" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>-0.002673796791443951</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -4629,6 +6201,12 @@
       <c r="D262" s="2" t="n">
         <v>-0.00465116279069758</v>
       </c>
+      <c r="E262" s="1" t="n">
+        <v>0.003643</v>
+      </c>
+      <c r="F262" s="3" t="n">
+        <v>0.001374381528312203</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -4645,6 +6223,12 @@
       <c r="D263" s="3" t="n">
         <v>0.009523809523809436</v>
       </c>
+      <c r="E263" s="1" t="n">
+        <v>0.1178</v>
+      </c>
+      <c r="F263" s="3" t="n">
+        <v>0.01029159519725563</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -4661,6 +6245,12 @@
       <c r="D264" s="2" t="n">
         <v>-0.004015363128491623</v>
       </c>
+      <c r="E264" s="1" t="n">
+        <v>0.0005710999999999999</v>
+      </c>
+      <c r="F264" s="3" t="n">
+        <v>0.001051709027168985</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -4677,6 +6267,12 @@
       <c r="D265" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E265" s="1" t="n">
+        <v>0.01504</v>
+      </c>
+      <c r="F265" s="3" t="n">
+        <v>0.005347593582887715</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -4693,6 +6289,12 @@
       <c r="D266" s="2" t="n">
         <v>-0.001574803149606344</v>
       </c>
+      <c r="E266" s="1" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="F266" s="3" t="n">
+        <v>0.001577287066246102</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -4709,6 +6311,12 @@
       <c r="D267" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E267" s="1" t="n">
+        <v>0.01643</v>
+      </c>
+      <c r="F267" s="2" t="n">
+        <v>-0.003033980582524359</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -4725,6 +6333,12 @@
       <c r="D268" s="2" t="n">
         <v>-0.0002343566908835304</v>
       </c>
+      <c r="E268" s="1" t="n">
+        <v>0.000426</v>
+      </c>
+      <c r="F268" s="2" t="n">
+        <v>-0.001406469760900175</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -4741,6 +6355,12 @@
       <c r="D269" s="2" t="n">
         <v>-0.00479386385426651</v>
       </c>
+      <c r="E269" s="1" t="n">
+        <v>0.02082</v>
+      </c>
+      <c r="F269" s="3" t="n">
+        <v>0.002890173410404674</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -4757,6 +6377,12 @@
       <c r="D270" s="2" t="n">
         <v>-0.00277777777777778</v>
       </c>
+      <c r="E270" s="1" t="n">
+        <v>0.1792</v>
+      </c>
+      <c r="F270" s="2" t="n">
+        <v>-0.001671309192200528</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -4773,6 +6399,12 @@
       <c r="D271" s="2" t="n">
         <v>-0.003399048266485387</v>
       </c>
+      <c r="E271" s="1" t="n">
+        <v>0.1462</v>
+      </c>
+      <c r="F271" s="2" t="n">
+        <v>-0.00272851296043664</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -4789,6 +6421,12 @@
       <c r="D272" s="2" t="n">
         <v>-0.0007602635580335085</v>
       </c>
+      <c r="E272" s="1" t="n">
+        <v>0.03952</v>
+      </c>
+      <c r="F272" s="3" t="n">
+        <v>0.002282525995434943</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -4805,6 +6443,12 @@
       <c r="D273" s="3" t="n">
         <v>0.001081081081081082</v>
       </c>
+      <c r="E273" s="1" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="F273" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -4821,6 +6465,12 @@
       <c r="D274" s="2" t="n">
         <v>-0.0007933989209775351</v>
       </c>
+      <c r="E274" s="1" t="n">
+        <v>63.08</v>
+      </c>
+      <c r="F274" s="3" t="n">
+        <v>0.001746863585834515</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -4837,6 +6487,12 @@
       <c r="D275" s="2" t="n">
         <v>-0.001734605377276749</v>
       </c>
+      <c r="E275" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="F275" s="2" t="n">
+        <v>-0.0008688097306689481</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -4853,6 +6509,12 @@
       <c r="D276" s="2" t="n">
         <v>-0.0003869969040247252</v>
       </c>
+      <c r="E276" s="1" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="F276" s="3" t="n">
+        <v>0.0007742934572202012</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -4869,6 +6531,12 @@
       <c r="D277" s="3" t="n">
         <v>0.001438503955885987</v>
       </c>
+      <c r="E277" s="1" t="n">
+        <v>0.04182</v>
+      </c>
+      <c r="F277" s="3" t="n">
+        <v>0.001197031362221724</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -4885,6 +6553,12 @@
       <c r="D278" s="2" t="n">
         <v>-0.003177966101694969</v>
       </c>
+      <c r="E278" s="1" t="n">
+        <v>0.01896</v>
+      </c>
+      <c r="F278" s="3" t="n">
+        <v>0.007438894792773711</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -4901,6 +6575,12 @@
       <c r="D279" s="2" t="n">
         <v>-0.01735624123422162</v>
       </c>
+      <c r="E279" s="1" t="n">
+        <v>0.005651</v>
+      </c>
+      <c r="F279" s="3" t="n">
+        <v>0.00820695807314898</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -4917,6 +6597,12 @@
       <c r="D280" s="3" t="n">
         <v>0.003452855245683882</v>
       </c>
+      <c r="E280" s="1" t="n">
+        <v>0.03801</v>
+      </c>
+      <c r="F280" s="3" t="n">
+        <v>0.006087877183695104</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -4933,6 +6619,12 @@
       <c r="D281" s="3" t="n">
         <v>0.001109877913429524</v>
       </c>
+      <c r="E281" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F281" s="2" t="n">
+        <v>-0.002217294900221731</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -4949,6 +6641,12 @@
       <c r="D282" s="3" t="n">
         <v>0.001254705144291122</v>
       </c>
+      <c r="E282" s="1" t="n">
+        <v>0.0004002</v>
+      </c>
+      <c r="F282" s="3" t="n">
+        <v>0.003007518796992554</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -4965,6 +6663,12 @@
       <c r="D283" s="3" t="n">
         <v>0.02616726526423807</v>
       </c>
+      <c r="E283" s="1" t="n">
+        <v>0.0393</v>
+      </c>
+      <c r="F283" s="2" t="n">
+        <v>-0.01749999999999998</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -4981,6 +6685,12 @@
       <c r="D284" s="2" t="n">
         <v>-0.004066985645932932</v>
       </c>
+      <c r="E284" s="1" t="n">
+        <v>0.04162</v>
+      </c>
+      <c r="F284" s="2" t="n">
+        <v>-0.0002402113860197709</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -4997,6 +6707,12 @@
       <c r="D285" s="3" t="n">
         <v>0.003547754644757776</v>
       </c>
+      <c r="E285" s="1" t="n">
+        <v>0.10738</v>
+      </c>
+      <c r="F285" s="2" t="n">
+        <v>-0.001023351009396213</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -5013,6 +6729,12 @@
       <c r="D286" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E286" s="1" t="n">
+        <v>0.00414</v>
+      </c>
+      <c r="F286" s="2" t="n">
+        <v>-0.002409638554216978</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -5029,6 +6751,12 @@
       <c r="D287" s="2" t="n">
         <v>-0.006908349233502174</v>
       </c>
+      <c r="E287" s="1" t="n">
+        <v>0.15148</v>
+      </c>
+      <c r="F287" s="3" t="n">
+        <v>0.003577580495561234</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -5045,6 +6773,12 @@
       <c r="D288" s="3" t="n">
         <v>0.004395604395604369</v>
       </c>
+      <c r="E288" s="1" t="n">
+        <v>0.1827</v>
+      </c>
+      <c r="F288" s="2" t="n">
+        <v>-0.000547045951859896</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5061,6 +6795,12 @@
       <c r="D289" s="3" t="n">
         <v>0.0002437835202338971</v>
       </c>
+      <c r="E289" s="1" t="n">
+        <v>4.124</v>
+      </c>
+      <c r="F289" s="3" t="n">
+        <v>0.005118206190592227</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -5077,6 +6817,12 @@
       <c r="D290" s="2" t="n">
         <v>-0.003766478342749376</v>
       </c>
+      <c r="E290" s="1" t="n">
+        <v>0.08477</v>
+      </c>
+      <c r="F290" s="3" t="n">
+        <v>0.001535916824196494</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -5093,6 +6839,12 @@
       <c r="D291" s="3" t="n">
         <v>0.001703577512776762</v>
       </c>
+      <c r="E291" s="1" t="n">
+        <v>0.03528</v>
+      </c>
+      <c r="F291" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -5109,6 +6861,12 @@
       <c r="D292" s="3" t="n">
         <v>0.003415300546448166</v>
       </c>
+      <c r="E292" s="1" t="n">
+        <v>1.4653</v>
+      </c>
+      <c r="F292" s="2" t="n">
+        <v>-0.002518720217835287</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -5125,6 +6883,12 @@
       <c r="D293" s="3" t="n">
         <v>0.0005152868430093435</v>
       </c>
+      <c r="E293" s="1" t="n">
+        <v>0.005837</v>
+      </c>
+      <c r="F293" s="3" t="n">
+        <v>0.002060085836909847</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -5141,6 +6905,12 @@
       <c r="D294" s="2" t="n">
         <v>-0.000582241630276642</v>
       </c>
+      <c r="E294" s="1" t="n">
+        <v>0.003435</v>
+      </c>
+      <c r="F294" s="3" t="n">
+        <v>0.0005825808330906687</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -5157,6 +6927,12 @@
       <c r="D295" s="2" t="n">
         <v>-0.004460137520907022</v>
       </c>
+      <c r="E295" s="1" t="n">
+        <v>0.5365</v>
+      </c>
+      <c r="F295" s="3" t="n">
+        <v>0.001493373156617553</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -5173,6 +6949,12 @@
       <c r="D296" s="2" t="n">
         <v>-0.002672605790645981</v>
       </c>
+      <c r="E296" s="1" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="F296" s="3" t="n">
+        <v>0.0004466279589103769</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -5189,6 +6971,12 @@
       <c r="D297" s="2" t="n">
         <v>-0.004100761570005692</v>
       </c>
+      <c r="E297" s="1" t="n">
+        <v>0.01695</v>
+      </c>
+      <c r="F297" s="2" t="n">
+        <v>-0.002941176470588319</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -5205,6 +6993,12 @@
       <c r="D298" s="3" t="n">
         <v>0.007220216606498325</v>
       </c>
+      <c r="E298" s="1" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="F298" s="3" t="n">
+        <v>0.001654259718775819</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -5221,6 +7015,12 @@
       <c r="D299" s="3" t="n">
         <v>0.0009066183136898996</v>
       </c>
+      <c r="E299" s="1" t="n">
+        <v>0.01107</v>
+      </c>
+      <c r="F299" s="3" t="n">
+        <v>0.002717391304347872</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5237,6 +7037,12 @@
       <c r="D300" s="2" t="n">
         <v>-0.002890173410404674</v>
       </c>
+      <c r="E300" s="1" t="n">
+        <v>0.02072</v>
+      </c>
+      <c r="F300" s="3" t="n">
+        <v>0.0009661835748791877</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5253,6 +7059,12 @@
       <c r="D301" s="3" t="n">
         <v>0.009695753928452068</v>
       </c>
+      <c r="E301" s="1" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="F301" s="2" t="n">
+        <v>-0.0003311258278145331</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5269,6 +7081,12 @@
       <c r="D302" s="2" t="n">
         <v>-0.002214022140221312</v>
       </c>
+      <c r="E302" s="1" t="n">
+        <v>0.01351</v>
+      </c>
+      <c r="F302" s="2" t="n">
+        <v>-0.0007396449704142993</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5285,6 +7103,12 @@
       <c r="D303" s="3" t="n">
         <v>0.003117798563101452</v>
       </c>
+      <c r="E303" s="1" t="n">
+        <v>0.07386</v>
+      </c>
+      <c r="F303" s="2" t="n">
+        <v>-0.001891891891891909</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -5301,6 +7125,12 @@
       <c r="D304" s="2" t="n">
         <v>-0.001885606536769469</v>
       </c>
+      <c r="E304" s="1" t="n">
+        <v>0.01591</v>
+      </c>
+      <c r="F304" s="3" t="n">
+        <v>0.001889168765743215</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -5317,6 +7147,12 @@
       <c r="D305" s="2" t="n">
         <v>-0.001226053639846693</v>
       </c>
+      <c r="E305" s="1" t="n">
+        <v>0.06537</v>
+      </c>
+      <c r="F305" s="3" t="n">
+        <v>0.003068896731624856</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -5333,6 +7169,12 @@
       <c r="D306" s="3" t="n">
         <v>0.001204335608189433</v>
       </c>
+      <c r="E306" s="1" t="n">
+        <v>0.05002</v>
+      </c>
+      <c r="F306" s="3" t="n">
+        <v>0.002806736166800345</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -5349,6 +7191,12 @@
       <c r="D307" s="2" t="n">
         <v>-0.005347593582887705</v>
       </c>
+      <c r="E307" s="1" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="F307" s="3" t="n">
+        <v>0.003225806451612906</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -5365,6 +7213,12 @@
       <c r="D308" s="3" t="n">
         <v>0.0005080010160020112</v>
       </c>
+      <c r="E308" s="1" t="n">
+        <v>0.03971</v>
+      </c>
+      <c r="F308" s="3" t="n">
+        <v>0.008123889312008145</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -5381,6 +7235,12 @@
       <c r="D309" s="3" t="n">
         <v>0.007575757575757486</v>
       </c>
+      <c r="E309" s="1" t="n">
+        <v>0.01582</v>
+      </c>
+      <c r="F309" s="2" t="n">
+        <v>-0.008771929824561264</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -5397,6 +7257,12 @@
       <c r="D310" s="2" t="n">
         <v>-0.0007406035919275191</v>
       </c>
+      <c r="E310" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="F310" s="3" t="n">
+        <v>0.0005558643690939828</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -5413,6 +7279,12 @@
       <c r="D311" s="3" t="n">
         <v>0.004942709503482435</v>
       </c>
+      <c r="E311" s="1" t="n">
+        <v>0.004486</v>
+      </c>
+      <c r="F311" s="3" t="n">
+        <v>0.00290632684998882</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -5429,6 +7301,12 @@
       <c r="D312" s="2" t="n">
         <v>-0.003679525222551985</v>
       </c>
+      <c r="E312" s="1" t="n">
+        <v>0.08427999999999999</v>
+      </c>
+      <c r="F312" s="3" t="n">
+        <v>0.004050512270669443</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -5445,6 +7323,12 @@
       <c r="D313" s="3" t="n">
         <v>0.0006728569506122258</v>
       </c>
+      <c r="E313" s="1" t="n">
+        <v>0.07459</v>
+      </c>
+      <c r="F313" s="3" t="n">
+        <v>0.003093060785368585</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -5461,6 +7345,12 @@
       <c r="D314" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E314" s="1" t="n">
+        <v>0.1528</v>
+      </c>
+      <c r="F314" s="3" t="n">
+        <v>0.0006548788474131564</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -5477,6 +7367,12 @@
       <c r="D315" s="2" t="n">
         <v>-0.003128911138923658</v>
       </c>
+      <c r="E315" s="1" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="F315" s="2" t="n">
+        <v>-0.001255492780916546</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -5493,6 +7389,12 @@
       <c r="D316" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E316" s="1" t="n">
+        <v>0.1797</v>
+      </c>
+      <c r="F316" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -5509,6 +7411,12 @@
       <c r="D317" s="2" t="n">
         <v>-0.001594896331738533</v>
       </c>
+      <c r="E317" s="1" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="F317" s="3" t="n">
+        <v>0.002396166134185391</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -5525,6 +7433,12 @@
       <c r="D318" s="3" t="n">
         <v>0.001603849238171547</v>
       </c>
+      <c r="E318" s="1" t="n">
+        <v>0.04998</v>
+      </c>
+      <c r="F318" s="3" t="n">
+        <v>0.0004003202562049477</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -5541,6 +7455,12 @@
       <c r="D319" s="3" t="n">
         <v>0.001284888286101888</v>
       </c>
+      <c r="E319" s="1" t="n">
+        <v>0.28153</v>
+      </c>
+      <c r="F319" s="3" t="n">
+        <v>0.003528908533542421</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -5557,6 +7477,12 @@
       <c r="D320" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E320" s="1" t="n">
+        <v>0.4379</v>
+      </c>
+      <c r="F320" s="2" t="n">
+        <v>-0.0004565167769915042</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -5573,6 +7499,12 @@
       <c r="D321" s="2" t="n">
         <v>-0.00364251333420045</v>
       </c>
+      <c r="E321" s="1" t="n">
+        <v>0.07650999999999999</v>
+      </c>
+      <c r="F321" s="2" t="n">
+        <v>-0.001044522783653357</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -5589,6 +7521,12 @@
       <c r="D322" s="3" t="n">
         <v>0.003095975232198145</v>
       </c>
+      <c r="E322" s="1" t="n">
+        <v>0.1622</v>
+      </c>
+      <c r="F322" s="3" t="n">
+        <v>0.001234567901234603</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -5605,6 +7543,12 @@
       <c r="D323" s="2" t="n">
         <v>-0.003522898842476154</v>
       </c>
+      <c r="E323" s="1" t="n">
+        <v>1.987</v>
+      </c>
+      <c r="F323" s="3" t="n">
+        <v>0.003535353535353595</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -5621,6 +7565,12 @@
       <c r="D324" s="3" t="n">
         <v>0.001328323655546712</v>
       </c>
+      <c r="E324" s="1" t="n">
+        <v>0.053046</v>
+      </c>
+      <c r="F324" s="3" t="n">
+        <v>0.005268344451182544</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -5637,6 +7587,12 @@
       <c r="D325" s="3" t="n">
         <v>0.001112929623567944</v>
       </c>
+      <c r="E325" s="1" t="n">
+        <v>0.15292</v>
+      </c>
+      <c r="F325" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -5653,6 +7609,12 @@
       <c r="D326" s="2" t="n">
         <v>-0.0009165902841429773</v>
       </c>
+      <c r="E326" s="1" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="F326" s="2" t="n">
+        <v>-0.006116207951070353</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -5669,6 +7631,12 @@
       <c r="D327" s="2" t="n">
         <v>-0.0009920634920634517</v>
       </c>
+      <c r="E327" s="1" t="n">
+        <v>0.015046</v>
+      </c>
+      <c r="F327" s="2" t="n">
+        <v>-0.003905991393578287</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -5685,6 +7653,12 @@
       <c r="D328" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E328" s="1" t="n">
+        <v>0.0939</v>
+      </c>
+      <c r="F328" s="3" t="n">
+        <v>0.001066098081023485</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -5701,6 +7675,12 @@
       <c r="D329" s="2" t="n">
         <v>-0.0043181818181818</v>
       </c>
+      <c r="E329" s="1" t="n">
+        <v>0.004395</v>
+      </c>
+      <c r="F329" s="3" t="n">
+        <v>0.003195617438940711</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -5717,6 +7697,12 @@
       <c r="D330" s="2" t="n">
         <v>-0.003881987577639863</v>
       </c>
+      <c r="E330" s="1" t="n">
+        <v>0.05122</v>
+      </c>
+      <c r="F330" s="2" t="n">
+        <v>-0.001948558067030318</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -5733,6 +7719,12 @@
       <c r="D331" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E331" s="1" t="n">
+        <v>0.03629</v>
+      </c>
+      <c r="F331" s="3" t="n">
+        <v>0.002209334438000654</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -5749,6 +7741,12 @@
       <c r="D332" s="2" t="n">
         <v>-0.007422402159244197</v>
       </c>
+      <c r="E332" s="1" t="n">
+        <v>0.1476</v>
+      </c>
+      <c r="F332" s="3" t="n">
+        <v>0.003399048266485387</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -5765,6 +7763,12 @@
       <c r="D333" s="2" t="n">
         <v>-0.004153686396677026</v>
       </c>
+      <c r="E333" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="F333" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -5781,6 +7785,12 @@
       <c r="D334" s="2" t="n">
         <v>-0.007587951253161736</v>
       </c>
+      <c r="E334" s="1" t="n">
+        <v>0.04382</v>
+      </c>
+      <c r="F334" s="3" t="n">
+        <v>0.01529193697868399</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -5797,6 +7807,12 @@
       <c r="D335" s="3" t="n">
         <v>0.001113447977236258</v>
       </c>
+      <c r="E335" s="1" t="n">
+        <v>0.08105</v>
+      </c>
+      <c r="F335" s="3" t="n">
+        <v>0.001606524962926239</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -5813,6 +7829,12 @@
       <c r="D336" s="2" t="n">
         <v>-0.001962708537782196</v>
       </c>
+      <c r="E336" s="1" t="n">
+        <v>0.2037</v>
+      </c>
+      <c r="F336" s="3" t="n">
+        <v>0.00147492625368729</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -5829,6 +7851,12 @@
       <c r="D337" s="3" t="n">
         <v>0.001974333662388863</v>
       </c>
+      <c r="E337" s="1" t="n">
+        <v>0.01024</v>
+      </c>
+      <c r="F337" s="3" t="n">
+        <v>0.008866995073891777</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -5845,6 +7873,12 @@
       <c r="D338" s="2" t="n">
         <v>-0.001771479185119626</v>
       </c>
+      <c r="E338" s="1" t="n">
+        <v>0.1127</v>
+      </c>
+      <c r="F338" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -5861,6 +7895,12 @@
       <c r="D339" s="2" t="n">
         <v>-0.005428881650379989</v>
       </c>
+      <c r="E339" s="1" t="n">
+        <v>0.01827</v>
+      </c>
+      <c r="F339" s="2" t="n">
+        <v>-0.002729257641921286</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -5877,6 +7917,12 @@
       <c r="D340" s="2" t="n">
         <v>-0.004918547458750365</v>
       </c>
+      <c r="E340" s="1" t="n">
+        <v>0.28421</v>
+      </c>
+      <c r="F340" s="2" t="n">
+        <v>-0.003680852555563329</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -5893,6 +7939,12 @@
       <c r="D341" s="3" t="n">
         <v>0.01889400921658989</v>
       </c>
+      <c r="E341" s="1" t="n">
+        <v>0.04353</v>
+      </c>
+      <c r="F341" s="2" t="n">
+        <v>-0.01560379918588881</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -5909,6 +7961,12 @@
       <c r="D342" s="3" t="n">
         <v>0.0005100739607242842</v>
       </c>
+      <c r="E342" s="1" t="n">
+        <v>0.07826</v>
+      </c>
+      <c r="F342" s="2" t="n">
+        <v>-0.002549069589599869</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -5925,6 +7983,12 @@
       <c r="D343" s="2" t="n">
         <v>-0.001704024118495203</v>
       </c>
+      <c r="E343" s="1" t="n">
+        <v>7.618</v>
+      </c>
+      <c r="F343" s="3" t="n">
+        <v>0.0002626050420168944</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -5941,6 +8005,12 @@
       <c r="D344" s="2" t="n">
         <v>-0.003313452617627571</v>
       </c>
+      <c r="E344" s="1" t="n">
+        <v>0.6012</v>
+      </c>
+      <c r="F344" s="2" t="n">
+        <v>-0.0006648936170213879</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -5957,6 +8027,12 @@
       <c r="D345" s="2" t="n">
         <v>-0.003794037940379437</v>
       </c>
+      <c r="E345" s="1" t="n">
+        <v>0.03684</v>
+      </c>
+      <c r="F345" s="3" t="n">
+        <v>0.002176278563656059</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -5973,6 +8049,12 @@
       <c r="D346" s="2" t="n">
         <v>-0.002427184466019487</v>
       </c>
+      <c r="E346" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="F346" s="2" t="n">
+        <v>-0.002433090024330801</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -5989,6 +8071,12 @@
       <c r="D347" s="2" t="n">
         <v>-0.001156069364161722</v>
       </c>
+      <c r="E347" s="1" t="n">
+        <v>0.1732</v>
+      </c>
+      <c r="F347" s="3" t="n">
+        <v>0.002314814814814721</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -6005,6 +8093,12 @@
       <c r="D348" s="3" t="n">
         <v>0.0005783021050196623</v>
       </c>
+      <c r="E348" s="1" t="n">
+        <v>5184.3</v>
+      </c>
+      <c r="F348" s="2" t="n">
+        <v>-0.001213732516472119</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -6021,6 +8115,12 @@
       <c r="D349" s="2" t="n">
         <v>-0.006666666666666652</v>
       </c>
+      <c r="E349" s="1" t="n">
+        <v>0.01345</v>
+      </c>
+      <c r="F349" s="3" t="n">
+        <v>0.002982848620432521</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -6037,6 +8137,12 @@
       <c r="D350" s="2" t="n">
         <v>-0.00201072386058973</v>
       </c>
+      <c r="E350" s="1" t="n">
+        <v>0.01493</v>
+      </c>
+      <c r="F350" s="3" t="n">
+        <v>0.002686366689053063</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -6053,6 +8159,12 @@
       <c r="D351" s="2" t="n">
         <v>-0.005942555298778441</v>
       </c>
+      <c r="E351" s="1" t="n">
+        <v>0.0006036</v>
+      </c>
+      <c r="F351" s="3" t="n">
+        <v>0.00232480903354373</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -6069,6 +8181,12 @@
       <c r="D352" s="2" t="n">
         <v>-0.001017293997965371</v>
       </c>
+      <c r="E352" s="1" t="n">
+        <v>0.01968</v>
+      </c>
+      <c r="F352" s="3" t="n">
+        <v>0.002036659877800324</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -6085,6 +8203,12 @@
       <c r="D353" s="3" t="n">
         <v>0.005150214592274617</v>
       </c>
+      <c r="E353" s="1" t="n">
+        <v>0.09354999999999999</v>
+      </c>
+      <c r="F353" s="2" t="n">
+        <v>-0.001387702818104239</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -6101,6 +8225,12 @@
       <c r="D354" s="3" t="n">
         <v>0.002217294900221639</v>
       </c>
+      <c r="E354" s="1" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="F354" s="3" t="n">
+        <v>0.003318584070796556</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -6117,6 +8247,12 @@
       <c r="D355" s="2" t="n">
         <v>-0.0004999999999999218</v>
       </c>
+      <c r="E355" s="1" t="n">
+        <v>0.0006002</v>
+      </c>
+      <c r="F355" s="3" t="n">
+        <v>0.000833750208437482</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -6133,6 +8269,12 @@
       <c r="D356" s="2" t="n">
         <v>-0.002877697841726515</v>
       </c>
+      <c r="E356" s="1" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="F356" s="3" t="n">
+        <v>0.001924001924001926</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -6149,6 +8291,12 @@
       <c r="D357" s="3" t="n">
         <v>0.00257731958762891</v>
       </c>
+      <c r="E357" s="1" t="n">
+        <v>0.02312</v>
+      </c>
+      <c r="F357" s="2" t="n">
+        <v>-0.009425878320479777</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -6165,6 +8313,12 @@
       <c r="D358" s="2" t="n">
         <v>-0.002463054187192178</v>
       </c>
+      <c r="E358" s="1" t="n">
+        <v>0.000407</v>
+      </c>
+      <c r="F358" s="3" t="n">
+        <v>0.004938271604938392</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -6181,6 +8335,12 @@
       <c r="D359" s="2" t="n">
         <v>-0.00137080191912275</v>
       </c>
+      <c r="E359" s="1" t="n">
+        <v>0.01456</v>
+      </c>
+      <c r="F359" s="2" t="n">
+        <v>-0.0006863417982154833</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -6197,6 +8357,12 @@
       <c r="D360" s="3" t="n">
         <v>0.001187648456057036</v>
       </c>
+      <c r="E360" s="1" t="n">
+        <v>0.003384</v>
+      </c>
+      <c r="F360" s="3" t="n">
+        <v>0.003558718861209922</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -6213,6 +8379,12 @@
       <c r="D361" s="3" t="n">
         <v>0.00797872340425531</v>
       </c>
+      <c r="E361" s="1" t="n">
+        <v>0.6439</v>
+      </c>
+      <c r="F361" s="2" t="n">
+        <v>-0.0006208288064565512</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -6229,6 +8401,12 @@
       <c r="D362" s="3" t="n">
         <v>0.006454388984509502</v>
       </c>
+      <c r="E362" s="1" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F362" s="2" t="n">
+        <v>-0.003847798204360829</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -6245,6 +8423,12 @@
       <c r="D363" s="3" t="n">
         <v>0.001530924678505861</v>
       </c>
+      <c r="E363" s="1" t="n">
+        <v>0.06533</v>
+      </c>
+      <c r="F363" s="2" t="n">
+        <v>-0.001375726077652197</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -6261,6 +8445,12 @@
       <c r="D364" s="3" t="n">
         <v>0.002344915796205526</v>
       </c>
+      <c r="E364" s="1" t="n">
+        <v>4.715</v>
+      </c>
+      <c r="F364" s="3" t="n">
+        <v>0.002764780944279009</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -6277,6 +8467,12 @@
       <c r="D365" s="3" t="n">
         <v>0.003523608174770969</v>
       </c>
+      <c r="E365" s="1" t="n">
+        <v>0.07111000000000001</v>
+      </c>
+      <c r="F365" s="2" t="n">
+        <v>-0.001264044943820124</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -6293,6 +8489,12 @@
       <c r="D366" s="2" t="n">
         <v>-0.0003640334910812909</v>
       </c>
+      <c r="E366" s="1" t="n">
+        <v>0.05504</v>
+      </c>
+      <c r="F366" s="3" t="n">
+        <v>0.00218499635833944</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -6309,6 +8511,12 @@
       <c r="D367" s="2" t="n">
         <v>-0.002049530315969173</v>
       </c>
+      <c r="E367" s="1" t="n">
+        <v>0.05849</v>
+      </c>
+      <c r="F367" s="3" t="n">
+        <v>0.001026869758685565</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -6325,6 +8533,12 @@
       <c r="D368" s="2" t="n">
         <v>-0.005614035087719313</v>
       </c>
+      <c r="E368" s="1" t="n">
+        <v>0.05681</v>
+      </c>
+      <c r="F368" s="3" t="n">
+        <v>0.002293577981651344</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -6341,6 +8555,12 @@
       <c r="D369" s="2" t="n">
         <v>-0.001944894651539629</v>
       </c>
+      <c r="E369" s="1" t="n">
+        <v>0.03082</v>
+      </c>
+      <c r="F369" s="3" t="n">
+        <v>0.0009743423189346793</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -6357,6 +8577,12 @@
       <c r="D370" s="3" t="n">
         <v>0.001235330450895645</v>
       </c>
+      <c r="E370" s="1" t="n">
+        <v>0.000162</v>
+      </c>
+      <c r="F370" s="2" t="n">
+        <v>-0.0006169031462060606</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -6373,6 +8599,12 @@
       <c r="D371" s="2" t="n">
         <v>-0.002651738361814936</v>
       </c>
+      <c r="E371" s="1" t="n">
+        <v>0.00677</v>
+      </c>
+      <c r="F371" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -6389,6 +8621,12 @@
       <c r="D372" s="2" t="n">
         <v>-0.006595927731574424</v>
       </c>
+      <c r="E372" s="1" t="n">
+        <v>0.006906</v>
+      </c>
+      <c r="F372" s="2" t="n">
+        <v>-0.003175519630485034</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -6405,6 +8643,12 @@
       <c r="D373" s="3" t="n">
         <v>0.00158436757327706</v>
       </c>
+      <c r="E373" s="1" t="n">
+        <v>3.784</v>
+      </c>
+      <c r="F373" s="2" t="n">
+        <v>-0.002372791985236051</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -6421,6 +8665,12 @@
       <c r="D374" s="3" t="n">
         <v>0.004138127853881258</v>
       </c>
+      <c r="E374" s="1" t="n">
+        <v>0.07066</v>
+      </c>
+      <c r="F374" s="3" t="n">
+        <v>0.004121074321443777</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -6437,6 +8687,12 @@
       <c r="D375" s="3" t="n">
         <v>0.00220007764979927</v>
       </c>
+      <c r="E375" s="1" t="n">
+        <v>0.07738</v>
+      </c>
+      <c r="F375" s="2" t="n">
+        <v>-0.000774793388429631</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -6453,6 +8709,12 @@
       <c r="D376" s="3" t="n">
         <v>0.002070723160241976</v>
       </c>
+      <c r="E376" s="1" t="n">
+        <v>0.06271</v>
+      </c>
+      <c r="F376" s="2" t="n">
+        <v>-0.003179144810045968</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -6469,6 +8731,12 @@
       <c r="D377" s="2" t="n">
         <v>-0.003409836065573723</v>
       </c>
+      <c r="E377" s="1" t="n">
+        <v>0.07622</v>
+      </c>
+      <c r="F377" s="3" t="n">
+        <v>0.003026714041321149</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -6485,6 +8753,12 @@
       <c r="D378" s="3" t="n">
         <v>0.004715810374782805</v>
       </c>
+      <c r="E378" s="1" t="n">
+        <v>0.0004032</v>
+      </c>
+      <c r="F378" s="2" t="n">
+        <v>-0.003952569169960437</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -6501,6 +8775,12 @@
       <c r="D379" s="3" t="n">
         <v>0.000941366325981719</v>
       </c>
+      <c r="E379" s="1" t="n">
+        <v>0.07417</v>
+      </c>
+      <c r="F379" s="2" t="n">
+        <v>-0.003493215101437543</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -6517,6 +8797,12 @@
       <c r="D380" s="3" t="n">
         <v>0.01043219076005954</v>
       </c>
+      <c r="E380" s="1" t="n">
+        <v>0.001354</v>
+      </c>
+      <c r="F380" s="2" t="n">
+        <v>-0.001474926253687351</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -6533,6 +8819,12 @@
       <c r="D381" s="2" t="n">
         <v>-0.002453987730061352</v>
       </c>
+      <c r="E381" s="1" t="n">
+        <v>6.472</v>
+      </c>
+      <c r="F381" s="2" t="n">
+        <v>-0.004920049200491873</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -6549,6 +8841,12 @@
       <c r="D382" s="3" t="n">
         <v>0.003023431594860174</v>
       </c>
+      <c r="E382" s="1" t="n">
+        <v>0.01327</v>
+      </c>
+      <c r="F382" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -6565,6 +8863,12 @@
       <c r="D383" s="3" t="n">
         <v>0.002863688430698822</v>
       </c>
+      <c r="E383" s="1" t="n">
+        <v>0.01755</v>
+      </c>
+      <c r="F383" s="3" t="n">
+        <v>0.002284408909194653</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -6581,6 +8885,12 @@
       <c r="D384" s="3" t="n">
         <v>0.006910167818361227</v>
       </c>
+      <c r="E384" s="1" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="F384" s="2" t="n">
+        <v>-0.00196078431372541</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -6597,6 +8907,12 @@
       <c r="D385" s="2" t="n">
         <v>-0.004016960499888372</v>
       </c>
+      <c r="E385" s="1" t="n">
+        <v>4.473</v>
+      </c>
+      <c r="F385" s="3" t="n">
+        <v>0.002240645305848036</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -6613,6 +8929,12 @@
       <c r="D386" s="2" t="n">
         <v>-0.002323780015491839</v>
       </c>
+      <c r="E386" s="1" t="n">
+        <v>0.001286</v>
+      </c>
+      <c r="F386" s="2" t="n">
+        <v>-0.001552795031055938</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -6629,6 +8951,12 @@
       <c r="D387" s="2" t="n">
         <v>-0.0005087332541969698</v>
       </c>
+      <c r="E387" s="1" t="n">
+        <v>0.0005892</v>
+      </c>
+      <c r="F387" s="2" t="n">
+        <v>-0.0003393281303020103</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -6645,6 +8973,12 @@
       <c r="D388" s="2" t="n">
         <v>-0.003536693191865615</v>
       </c>
+      <c r="E388" s="1" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="F388" s="2" t="n">
+        <v>-0.001774622892635397</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -6661,6 +8995,12 @@
       <c r="D389" s="3" t="n">
         <v>0.002202643171806269</v>
       </c>
+      <c r="E389" s="1" t="n">
+        <v>0.00911</v>
+      </c>
+      <c r="F389" s="3" t="n">
+        <v>0.001098901098901054</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -6677,6 +9017,12 @@
       <c r="D390" s="2" t="n">
         <v>-0.001274859765425663</v>
       </c>
+      <c r="E390" s="1" t="n">
+        <v>0.0786</v>
+      </c>
+      <c r="F390" s="3" t="n">
+        <v>0.003318866479448511</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -6693,6 +9039,12 @@
       <c r="D391" s="2" t="n">
         <v>-0.001766437684003921</v>
       </c>
+      <c r="E391" s="1" t="n">
+        <v>0.05083</v>
+      </c>
+      <c r="F391" s="2" t="n">
+        <v>-0.0005898545025560803</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -6709,6 +9061,12 @@
       <c r="D392" s="3" t="n">
         <v>0.004219409282700433</v>
       </c>
+      <c r="E392" s="1" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="F392" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -6725,6 +9083,12 @@
       <c r="D393" s="3" t="n">
         <v>0.006594441827602508</v>
       </c>
+      <c r="E393" s="1" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="F393" s="2" t="n">
+        <v>-0.01263453439401027</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -6741,6 +9105,12 @@
       <c r="D394" s="3" t="n">
         <v>0.0009722897423432461</v>
       </c>
+      <c r="E394" s="1" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="F394" s="2" t="n">
+        <v>-0.002914035939776539</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -6757,6 +9127,12 @@
       <c r="D395" s="2" t="n">
         <v>-0.001031991744066077</v>
       </c>
+      <c r="E395" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="F395" s="3" t="n">
+        <v>0.002066115702479398</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -6773,6 +9149,12 @@
       <c r="D396" s="2" t="n">
         <v>-0.001480932987782304</v>
       </c>
+      <c r="E396" s="1" t="n">
+        <v>2.696</v>
+      </c>
+      <c r="F396" s="2" t="n">
+        <v>-0.000370782350760063</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -6789,6 +9171,12 @@
       <c r="D397" s="2" t="n">
         <v>-0.001581027667984191</v>
       </c>
+      <c r="E397" s="1" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="F397" s="3" t="n">
+        <v>0.001583531274742678</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -6805,6 +9193,12 @@
       <c r="D398" s="2" t="n">
         <v>-0.001239328008813044</v>
       </c>
+      <c r="E398" s="1" t="n">
+        <v>0.007229</v>
+      </c>
+      <c r="F398" s="2" t="n">
+        <v>-0.003308975596304938</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -6821,6 +9215,12 @@
       <c r="D399" s="2" t="n">
         <v>-0.0003859513701273215</v>
       </c>
+      <c r="E399" s="1" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="F399" s="3" t="n">
+        <v>0.0007722007722006871</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -6837,6 +9237,12 @@
       <c r="D400" s="2" t="n">
         <v>-0.00219780219780213</v>
       </c>
+      <c r="E400" s="1" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="F400" s="3" t="n">
+        <v>0.0003146633102579892</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -6853,6 +9259,12 @@
       <c r="D401" s="3" t="n">
         <v>0.003259175286949192</v>
       </c>
+      <c r="E401" s="1" t="n">
+        <v>0.00738</v>
+      </c>
+      <c r="F401" s="3" t="n">
+        <v>0.04237288135593219</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -6869,6 +9281,12 @@
       <c r="D402" s="2" t="n">
         <v>-0.001753232522463334</v>
       </c>
+      <c r="E402" s="1" t="n">
+        <v>0.004556</v>
+      </c>
+      <c r="F402" s="3" t="n">
+        <v>0.0002195389681668788</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -6885,6 +9303,12 @@
       <c r="D403" s="2" t="n">
         <v>-0.0007584376185057944</v>
       </c>
+      <c r="E403" s="1" t="n">
+        <v>0.2644</v>
+      </c>
+      <c r="F403" s="3" t="n">
+        <v>0.00341555977229606</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -6901,6 +9325,12 @@
       <c r="D404" s="2" t="n">
         <v>-0.002910602910602821</v>
       </c>
+      <c r="E404" s="1" t="n">
+        <v>0.2398</v>
+      </c>
+      <c r="F404" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -6917,6 +9347,12 @@
       <c r="D405" s="2" t="n">
         <v>-0.000114889705882418</v>
       </c>
+      <c r="E405" s="1" t="n">
+        <v>0.0008693</v>
+      </c>
+      <c r="F405" s="2" t="n">
+        <v>-0.001149029070435385</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -6933,6 +9369,12 @@
       <c r="D406" s="2" t="n">
         <v>-0.00137389597644751</v>
       </c>
+      <c r="E406" s="1" t="n">
+        <v>0.005098</v>
+      </c>
+      <c r="F406" s="3" t="n">
+        <v>0.001965408805031537</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -6949,6 +9391,12 @@
       <c r="D407" s="2" t="n">
         <v>-0.0008264462809917019</v>
       </c>
+      <c r="E407" s="1" t="n">
+        <v>0.01212</v>
+      </c>
+      <c r="F407" s="3" t="n">
+        <v>0.002481389578163814</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -6965,6 +9413,12 @@
       <c r="D408" s="3" t="n">
         <v>0.006232686980609495</v>
       </c>
+      <c r="E408" s="1" t="n">
+        <v>0.00144</v>
+      </c>
+      <c r="F408" s="2" t="n">
+        <v>-0.008947006194081205</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -6981,6 +9435,12 @@
       <c r="D409" s="3" t="n">
         <v>0.001102839812517378</v>
       </c>
+      <c r="E409" s="1" t="n">
+        <v>0.03643</v>
+      </c>
+      <c r="F409" s="3" t="n">
+        <v>0.003304874690167863</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -6997,6 +9457,12 @@
       <c r="D410" s="2" t="n">
         <v>-0.003676470588235357</v>
       </c>
+      <c r="E410" s="1" t="n">
+        <v>0.01631</v>
+      </c>
+      <c r="F410" s="3" t="n">
+        <v>0.003075030750307591</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -7013,6 +9479,12 @@
       <c r="D411" s="3" t="n">
         <v>0.00157232704402513</v>
       </c>
+      <c r="E411" s="1" t="n">
+        <v>0.1922</v>
+      </c>
+      <c r="F411" s="3" t="n">
+        <v>0.005756148613291563</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -7029,6 +9501,12 @@
       <c r="D412" s="3" t="n">
         <v>0.002367914755068721</v>
       </c>
+      <c r="E412" s="1" t="n">
+        <v>0.06766</v>
+      </c>
+      <c r="F412" s="2" t="n">
+        <v>-0.001033515428908912</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -7045,6 +9523,12 @@
       <c r="D413" s="2" t="n">
         <v>-0.001188118811881188</v>
       </c>
+      <c r="E413" s="1" t="n">
+        <v>2530</v>
+      </c>
+      <c r="F413" s="3" t="n">
+        <v>0.00317208564631245</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -7061,6 +9545,12 @@
       <c r="D414" s="2" t="n">
         <v>-0.005176380368098149</v>
       </c>
+      <c r="E414" s="1" t="n">
+        <v>0.05206</v>
+      </c>
+      <c r="F414" s="3" t="n">
+        <v>0.003276161110040538</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -7077,6 +9567,12 @@
       <c r="D415" s="2" t="n">
         <v>-0.003416856492027338</v>
       </c>
+      <c r="E415" s="1" t="n">
+        <v>1.731</v>
+      </c>
+      <c r="F415" s="2" t="n">
+        <v>-0.0108571428571428</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -7093,6 +9589,12 @@
       <c r="D416" s="2" t="n">
         <v>-0.00247632920611804</v>
       </c>
+      <c r="E416" s="1" t="n">
+        <v>0.06855</v>
+      </c>
+      <c r="F416" s="3" t="n">
+        <v>0.001022196261682252</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -7109,6 +9611,12 @@
       <c r="D417" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E417" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F417" s="3" t="n">
+        <v>0.01351351351351353</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -7125,6 +9633,12 @@
       <c r="D418" s="2" t="n">
         <v>-0.005208333333333303</v>
       </c>
+      <c r="E418" s="1" t="n">
+        <v>0.1532</v>
+      </c>
+      <c r="F418" s="3" t="n">
+        <v>0.002617801047120494</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -7141,6 +9655,12 @@
       <c r="D419" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E419" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="F419" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -7157,6 +9677,12 @@
       <c r="D420" s="2" t="n">
         <v>-0.002090956612650384</v>
       </c>
+      <c r="E420" s="1" t="n">
+        <v>0.01912</v>
+      </c>
+      <c r="F420" s="3" t="n">
+        <v>0.001571503404924162</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -7173,6 +9699,12 @@
       <c r="D421" s="3" t="n">
         <v>0.005647944775651071</v>
       </c>
+      <c r="E421" s="1" t="n">
+        <v>0.1932</v>
+      </c>
+      <c r="F421" s="3" t="n">
+        <v>0.004680187207488361</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -7189,6 +9721,12 @@
       <c r="D422" s="3" t="n">
         <v>0.004676995030692793</v>
       </c>
+      <c r="E422" s="1" t="n">
+        <v>0.03413</v>
+      </c>
+      <c r="F422" s="2" t="n">
+        <v>-0.006982833866744171</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -7205,6 +9743,12 @@
       <c r="D423" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E423" s="1" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="F423" s="3" t="n">
+        <v>0.001407459535538394</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -7221,6 +9765,12 @@
       <c r="D424" s="2" t="n">
         <v>-0.005681818181818114</v>
       </c>
+      <c r="E424" s="1" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="F424" s="3" t="n">
+        <v>0.007619047619047639</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -7237,6 +9787,12 @@
       <c r="D425" s="2" t="n">
         <v>-0.003809523809523787</v>
       </c>
+      <c r="E425" s="1" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="F425" s="3" t="n">
+        <v>0.002868068833651957</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -7253,6 +9809,12 @@
       <c r="D426" s="2" t="n">
         <v>-0.00295441755768139</v>
       </c>
+      <c r="E426" s="1" t="n">
+        <v>0.00705</v>
+      </c>
+      <c r="F426" s="2" t="n">
+        <v>-0.005220826866092927</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -7269,6 +9831,12 @@
       <c r="D427" s="2" t="n">
         <v>-0.0007770007770007453</v>
       </c>
+      <c r="E427" s="1" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="F427" s="2" t="n">
+        <v>-0.004665629860031049</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -7285,6 +9853,12 @@
       <c r="D428" s="3" t="n">
         <v>0.002605782355130933</v>
       </c>
+      <c r="E428" s="1" t="n">
+        <v>0.008081</v>
+      </c>
+      <c r="F428" s="3" t="n">
+        <v>0.0001237623762375328</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -7301,6 +9875,12 @@
       <c r="D429" s="3" t="n">
         <v>0.00412881915772101</v>
       </c>
+      <c r="E429" s="1" t="n">
+        <v>0.01225</v>
+      </c>
+      <c r="F429" s="3" t="n">
+        <v>0.007401315789473667</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -7317,6 +9897,12 @@
       <c r="D430" s="2" t="n">
         <v>-0.0002994460248541117</v>
       </c>
+      <c r="E430" s="1" t="n">
+        <v>0.06686</v>
+      </c>
+      <c r="F430" s="3" t="n">
+        <v>0.00134791073835565</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -7333,6 +9919,12 @@
       <c r="D431" s="3" t="n">
         <v>0.001848428835489919</v>
       </c>
+      <c r="E431" s="1" t="n">
+        <v>0.00542</v>
+      </c>
+      <c r="F431" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -7349,6 +9941,12 @@
       <c r="D432" s="3" t="n">
         <v>0.001049979000420131</v>
       </c>
+      <c r="E432" s="1" t="n">
+        <v>0.009564</v>
+      </c>
+      <c r="F432" s="3" t="n">
+        <v>0.003146633102580111</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -7365,6 +9963,12 @@
       <c r="D433" s="2" t="n">
         <v>-0.004583835946924069</v>
       </c>
+      <c r="E433" s="1" t="n">
+        <v>0.04139</v>
+      </c>
+      <c r="F433" s="3" t="n">
+        <v>0.003150751333010303</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -7381,6 +9985,12 @@
       <c r="D434" s="2" t="n">
         <v>-0.00382043935052532</v>
       </c>
+      <c r="E434" s="1" t="n">
+        <v>0.04188</v>
+      </c>
+      <c r="F434" s="3" t="n">
+        <v>0.003835091083413241</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -7397,6 +10007,12 @@
       <c r="D435" s="3" t="n">
         <v>0.001964636542239663</v>
       </c>
+      <c r="E435" s="1" t="n">
+        <v>0.00153</v>
+      </c>
+      <c r="F435" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -7413,6 +10029,12 @@
       <c r="D436" s="3" t="n">
         <v>0.0003649635036496202</v>
       </c>
+      <c r="E436" s="1" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F436" s="3" t="n">
+        <v>0.003283473184968982</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -7429,6 +10051,12 @@
       <c r="D437" s="2" t="n">
         <v>-0.00706925473280622</v>
       </c>
+      <c r="E437" s="1" t="n">
+        <v>0.08355</v>
+      </c>
+      <c r="F437" s="3" t="n">
+        <v>0.008205623265355377</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -7445,6 +10073,12 @@
       <c r="D438" s="2" t="n">
         <v>-0.002608695652173988</v>
       </c>
+      <c r="E438" s="1" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="F438" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -7461,6 +10095,12 @@
       <c r="D439" s="3" t="n">
         <v>0.0006489292667100012</v>
       </c>
+      <c r="E439" s="1" t="n">
+        <v>1.541</v>
+      </c>
+      <c r="F439" s="2" t="n">
+        <v>-0.0006485084306096704</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -7477,6 +10117,12 @@
       <c r="D440" s="2" t="n">
         <v>-0.0005599104143337809</v>
       </c>
+      <c r="E440" s="1" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="F440" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -7493,6 +10139,12 @@
       <c r="D441" s="2" t="n">
         <v>-0.004594594594594502</v>
       </c>
+      <c r="E441" s="1" t="n">
+        <v>0.03679</v>
+      </c>
+      <c r="F441" s="2" t="n">
+        <v>-0.001086071137659472</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -7509,6 +10161,12 @@
       <c r="D442" s="2" t="n">
         <v>-0.001084598698481706</v>
       </c>
+      <c r="E442" s="1" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="F442" s="2" t="n">
+        <v>-0.00108577633007596</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -7525,6 +10183,12 @@
       <c r="D443" s="2" t="n">
         <v>-0.001645123384253942</v>
       </c>
+      <c r="E443" s="1" t="n">
+        <v>0.12754</v>
+      </c>
+      <c r="F443" s="3" t="n">
+        <v>0.0007846829880727322</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -7541,6 +10205,12 @@
       <c r="D444" s="3" t="n">
         <v>0.007128033925832284</v>
       </c>
+      <c r="E444" s="1" t="n">
+        <v>0.011189</v>
+      </c>
+      <c r="F444" s="3" t="n">
+        <v>0.002418921340261534</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -7557,6 +10227,12 @@
       <c r="D445" s="3" t="n">
         <v>0.0001248751248750765</v>
       </c>
+      <c r="E445" s="1" t="n">
+        <v>0.08021</v>
+      </c>
+      <c r="F445" s="3" t="n">
+        <v>0.00149831439630427</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -7573,6 +10249,12 @@
       <c r="D446" s="2" t="n">
         <v>-0.00805305542396975</v>
       </c>
+      <c r="E446" s="1" t="n">
+        <v>0.0002107</v>
+      </c>
+      <c r="F446" s="3" t="n">
+        <v>0.006208213944603651</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -7589,6 +10271,12 @@
       <c r="D447" s="2" t="n">
         <v>-0.003072196620583725</v>
       </c>
+      <c r="E447" s="1" t="n">
+        <v>0.00651</v>
+      </c>
+      <c r="F447" s="3" t="n">
+        <v>0.003081664098613259</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -7605,6 +10293,12 @@
       <c r="D448" s="2" t="n">
         <v>-0.006167873424510559</v>
       </c>
+      <c r="E448" s="1" t="n">
+        <v>0.11164</v>
+      </c>
+      <c r="F448" s="3" t="n">
+        <v>0.004137434790429952</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -7621,6 +10315,12 @@
       <c r="D449" s="2" t="n">
         <v>-0.0005917159763314395</v>
       </c>
+      <c r="E449" s="1" t="n">
+        <v>0.001686</v>
+      </c>
+      <c r="F449" s="2" t="n">
+        <v>-0.001776198934280618</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -7637,6 +10337,12 @@
       <c r="D450" s="2" t="n">
         <v>-0.001937046004842662</v>
       </c>
+      <c r="E450" s="1" t="n">
+        <v>0.0002064</v>
+      </c>
+      <c r="F450" s="3" t="n">
+        <v>0.001455604075691447</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -7653,6 +10359,12 @@
       <c r="D451" s="2" t="n">
         <v>-0.004543733434305225</v>
       </c>
+      <c r="E451" s="1" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="F451" s="3" t="n">
+        <v>0.005325218714340075</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -7669,6 +10381,12 @@
       <c r="D452" s="3" t="n">
         <v>0.002257336343115294</v>
       </c>
+      <c r="E452" s="1" t="n">
+        <v>0.1334</v>
+      </c>
+      <c r="F452" s="3" t="n">
+        <v>0.001501501501501336</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -7685,6 +10403,12 @@
       <c r="D453" s="2" t="n">
         <v>-0.003436426116838416</v>
       </c>
+      <c r="E453" s="1" t="n">
+        <v>0.0001742</v>
+      </c>
+      <c r="F453" s="3" t="n">
+        <v>0.00114942528735635</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -7701,6 +10425,12 @@
       <c r="D454" s="3" t="n">
         <v>0.00729455216989855</v>
       </c>
+      <c r="E454" s="1" t="n">
+        <v>0.10919</v>
+      </c>
+      <c r="F454" s="3" t="n">
+        <v>0.0009166743056191125</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -7717,6 +10447,12 @@
       <c r="D455" s="2" t="n">
         <v>-0.0004012841091493449</v>
       </c>
+      <c r="E455" s="1" t="n">
+        <v>0.4984</v>
+      </c>
+      <c r="F455" s="3" t="n">
+        <v>0.0004014452027298946</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -7733,6 +10469,12 @@
       <c r="D456" s="2" t="n">
         <v>-0.0005641572118096028</v>
       </c>
+      <c r="E456" s="1" t="n">
+        <v>0.015956</v>
+      </c>
+      <c r="F456" s="3" t="n">
+        <v>0.000752634219769292</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -7749,6 +10491,12 @@
       <c r="D457" s="3" t="n">
         <v>0.0003012048192771484</v>
       </c>
+      <c r="E457" s="1" t="n">
+        <v>0.006651</v>
+      </c>
+      <c r="F457" s="3" t="n">
+        <v>0.00135501355013542</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -7765,6 +10513,12 @@
       <c r="D458" s="2" t="n">
         <v>-0.00373831775700928</v>
       </c>
+      <c r="E458" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F458" s="3" t="n">
+        <v>0.0006253908692932395</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -7781,6 +10535,12 @@
       <c r="D459" s="3" t="n">
         <v>0.0007861635220125466</v>
       </c>
+      <c r="E459" s="1" t="n">
+        <v>0.006366</v>
+      </c>
+      <c r="F459" s="3" t="n">
+        <v>0.0001571091908876878</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -7797,6 +10557,12 @@
       <c r="D460" s="2" t="n">
         <v>-0.002184996358339364</v>
       </c>
+      <c r="E460" s="1" t="n">
+        <v>0.1373</v>
+      </c>
+      <c r="F460" s="3" t="n">
+        <v>0.002189781021897771</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -7813,6 +10579,12 @@
       <c r="D461" s="3" t="n">
         <v>0.0008986744551785749</v>
       </c>
+      <c r="E461" s="1" t="n">
+        <v>0.08913</v>
+      </c>
+      <c r="F461" s="3" t="n">
+        <v>0.0003367003367003619</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -7829,6 +10601,12 @@
       <c r="D462" s="3" t="n">
         <v>0.008244206773618434</v>
       </c>
+      <c r="E462" s="1" t="n">
+        <v>0.04539</v>
+      </c>
+      <c r="F462" s="3" t="n">
+        <v>0.003093922651933729</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -7845,6 +10623,12 @@
       <c r="D463" s="2" t="n">
         <v>-0.001434720229555178</v>
       </c>
+      <c r="E463" s="1" t="n">
+        <v>0.00696</v>
+      </c>
+      <c r="F463" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -7861,6 +10645,12 @@
       <c r="D464" s="3" t="n">
         <v>0.0007674597083653968</v>
       </c>
+      <c r="E464" s="1" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="F464" s="3" t="n">
+        <v>0.0007668711656440873</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -7877,6 +10667,12 @@
       <c r="D465" s="2" t="n">
         <v>-0.002839900603478959</v>
       </c>
+      <c r="E465" s="1" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="F465" s="2" t="n">
+        <v>-0.00498398006407959</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -7893,6 +10689,12 @@
       <c r="D466" s="2" t="n">
         <v>-0.00141043723554302</v>
       </c>
+      <c r="E466" s="1" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="F466" s="3" t="n">
+        <v>0.00211864406779669</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -7909,6 +10711,12 @@
       <c r="D467" s="2" t="n">
         <v>-0.00260960334029235</v>
       </c>
+      <c r="E467" s="1" t="n">
+        <v>0.01916</v>
+      </c>
+      <c r="F467" s="3" t="n">
+        <v>0.002616431187859834</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -7925,6 +10733,12 @@
       <c r="D468" s="2" t="n">
         <v>-0.005050505050505195</v>
       </c>
+      <c r="E468" s="1" t="n">
+        <v>0.00988</v>
+      </c>
+      <c r="F468" s="3" t="n">
+        <v>0.00304568527918787</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -7941,6 +10755,12 @@
       <c r="D469" s="2" t="n">
         <v>-0.001505646173149423</v>
       </c>
+      <c r="E469" s="1" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="F469" s="3" t="n">
+        <v>0.006031666247800989</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -7957,6 +10777,12 @@
       <c r="D470" s="2" t="n">
         <v>-0.001135073779795688</v>
       </c>
+      <c r="E470" s="1" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="F470" s="3" t="n">
+        <v>0.001136363636363637</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -7973,6 +10799,12 @@
       <c r="D471" s="2" t="n">
         <v>-0.003401360544217724</v>
       </c>
+      <c r="E471" s="1" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="F471" s="3" t="n">
+        <v>0.002171889543903232</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -7989,6 +10821,12 @@
       <c r="D472" s="2" t="n">
         <v>-0.007814407814407835</v>
       </c>
+      <c r="E472" s="1" t="n">
+        <v>0.04064</v>
+      </c>
+      <c r="F472" s="3" t="n">
+        <v>0.0002461235540241955</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -8005,6 +10843,12 @@
       <c r="D473" s="2" t="n">
         <v>-0.002423263327948216</v>
       </c>
+      <c r="E473" s="1" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="F473" s="3" t="n">
+        <v>0.005668016194331898</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -8021,6 +10865,12 @@
       <c r="D474" s="3" t="n">
         <v>0.001760563380281618</v>
       </c>
+      <c r="E474" s="1" t="n">
+        <v>0.008518</v>
+      </c>
+      <c r="F474" s="2" t="n">
+        <v>-0.001991798476859948</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -8037,6 +10887,12 @@
       <c r="D475" s="3" t="n">
         <v>0.000971109492595419</v>
       </c>
+      <c r="E475" s="1" t="n">
+        <v>0.04085</v>
+      </c>
+      <c r="F475" s="2" t="n">
+        <v>-0.00921658986175128</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -8053,6 +10909,12 @@
       <c r="D476" s="2" t="n">
         <v>-0.002144298688193787</v>
       </c>
+      <c r="E476" s="1" t="n">
+        <v>0.07901</v>
+      </c>
+      <c r="F476" s="2" t="n">
+        <v>-0.001264062697509833</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -8069,6 +10931,12 @@
       <c r="D477" s="2" t="n">
         <v>-0.002758420441347209</v>
       </c>
+      <c r="E477" s="1" t="n">
+        <v>0.13737</v>
+      </c>
+      <c r="F477" s="2" t="n">
+        <v>-7.279079924304848e-05</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -8085,6 +10953,12 @@
       <c r="D478" s="2" t="n">
         <v>-0.001053296819043637</v>
       </c>
+      <c r="E478" s="1" t="n">
+        <v>0.04747</v>
+      </c>
+      <c r="F478" s="3" t="n">
+        <v>0.001054407423028288</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -8101,6 +10975,12 @@
       <c r="D479" s="2" t="n">
         <v>-0.0001898253606682105</v>
       </c>
+      <c r="E479" s="1" t="n">
+        <v>0.005271</v>
+      </c>
+      <c r="F479" s="3" t="n">
+        <v>0.0007594456047084989</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -8117,6 +10997,12 @@
       <c r="D480" s="3" t="n">
         <v>0.001074498567335324</v>
       </c>
+      <c r="E480" s="1" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="F480" s="2" t="n">
+        <v>-0.004651162790697758</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -8133,6 +11019,12 @@
       <c r="D481" s="2" t="n">
         <v>-0.001313715186547412</v>
       </c>
+      <c r="E481" s="1" t="n">
+        <v>0.07605000000000001</v>
+      </c>
+      <c r="F481" s="3" t="n">
+        <v>0.0003946329913181037</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -8149,6 +11041,12 @@
       <c r="D482" s="2" t="n">
         <v>-0.006040268456375826</v>
       </c>
+      <c r="E482" s="1" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="F482" s="2" t="n">
+        <v>-0.0006752194463200265</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -8165,6 +11063,12 @@
       <c r="D483" s="3" t="n">
         <v>0.003999999999999976</v>
       </c>
+      <c r="E483" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F483" s="2" t="n">
+        <v>-0.003984063745019896</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -8181,6 +11085,12 @@
       <c r="D484" s="2" t="n">
         <v>-0.001844167819271638</v>
       </c>
+      <c r="E484" s="1" t="n">
+        <v>0.02168</v>
+      </c>
+      <c r="F484" s="3" t="n">
+        <v>0.001385681293302644</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -8197,6 +11107,12 @@
       <c r="D485" s="3" t="n">
         <v>0.004719264278799504</v>
       </c>
+      <c r="E485" s="1" t="n">
+        <v>0.00834</v>
+      </c>
+      <c r="F485" s="3" t="n">
+        <v>0.004456220643141102</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -8213,6 +11129,12 @@
       <c r="D486" s="2" t="n">
         <v>-0.005087014725568921</v>
       </c>
+      <c r="E486" s="1" t="n">
+        <v>0.00744</v>
+      </c>
+      <c r="F486" s="3" t="n">
+        <v>0.001076426264800887</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -8229,6 +11151,12 @@
       <c r="D487" s="3" t="n">
         <v>0.002729754322111088</v>
       </c>
+      <c r="E487" s="1" t="n">
+        <v>0.1104</v>
+      </c>
+      <c r="F487" s="3" t="n">
+        <v>0.001814882032667803</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -8245,6 +11173,12 @@
       <c r="D488" s="2" t="n">
         <v>-0.005087440381558152</v>
       </c>
+      <c r="E488" s="1" t="n">
+        <v>0.009391</v>
+      </c>
+      <c r="F488" s="3" t="n">
+        <v>0.0004261212314904156</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -8261,6 +11195,12 @@
       <c r="D489" s="2" t="n">
         <v>-0.0005134788189986954</v>
       </c>
+      <c r="E489" s="1" t="n">
+        <v>0.03869</v>
+      </c>
+      <c r="F489" s="2" t="n">
+        <v>-0.006164911379398849</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -8277,6 +11217,12 @@
       <c r="D490" s="2" t="n">
         <v>-0.001205857019810519</v>
       </c>
+      <c r="E490" s="1" t="n">
+        <v>0.05839</v>
+      </c>
+      <c r="F490" s="3" t="n">
+        <v>0.007071403932390491</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -8293,6 +11239,12 @@
       <c r="D491" s="2" t="n">
         <v>-0.00207039337474126</v>
       </c>
+      <c r="E491" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="F491" s="2" t="n">
+        <v>-0.004149377593360971</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -8309,6 +11261,12 @@
       <c r="D492" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E492" s="1" t="n">
+        <v>1.326</v>
+      </c>
+      <c r="F492" s="2" t="n">
+        <v>-0.007485029940119767</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -8325,6 +11283,12 @@
       <c r="D493" s="2" t="n">
         <v>-0.001418439716311901</v>
       </c>
+      <c r="E493" s="1" t="n">
+        <v>0.03525</v>
+      </c>
+      <c r="F493" s="3" t="n">
+        <v>0.001420454545454389</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -8341,6 +11305,12 @@
       <c r="D494" s="3" t="n">
         <v>0.001178550383029031</v>
       </c>
+      <c r="E494" s="1" t="n">
+        <v>0.01695</v>
+      </c>
+      <c r="F494" s="2" t="n">
+        <v>-0.002354326074161379</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -8357,6 +11327,12 @@
       <c r="D495" s="2" t="n">
         <v>-0.000633044946191227</v>
       </c>
+      <c r="E495" s="1" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="F495" s="3" t="n">
+        <v>0.002956081081081107</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -8373,6 +11349,12 @@
       <c r="D496" s="2" t="n">
         <v>-0.00124429697221065</v>
       </c>
+      <c r="E496" s="1" t="n">
+        <v>0.04832</v>
+      </c>
+      <c r="F496" s="3" t="n">
+        <v>0.003322259136212633</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -8389,6 +11371,12 @@
       <c r="D497" s="2" t="n">
         <v>-0.001398880895283785</v>
       </c>
+      <c r="E497" s="1" t="n">
+        <v>0.05006</v>
+      </c>
+      <c r="F497" s="3" t="n">
+        <v>0.001801080648389029</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -8405,6 +11393,12 @@
       <c r="D498" s="2" t="n">
         <v>-0.003468609087755813</v>
       </c>
+      <c r="E498" s="1" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="F498" s="3" t="n">
+        <v>0.0003480682213713504</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -8421,6 +11415,12 @@
       <c r="D499" s="2" t="n">
         <v>-0.002560351133869709</v>
       </c>
+      <c r="E499" s="1" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="F499" s="3" t="n">
+        <v>0.0007334066740006526</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -8437,6 +11437,12 @@
       <c r="D500" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E500" s="1" t="n">
+        <v>0.00265</v>
+      </c>
+      <c r="F500" s="2" t="n">
+        <v>-0.003759398496240611</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -8453,6 +11459,12 @@
       <c r="D501" s="3" t="n">
         <v>0.001941209095951209</v>
       </c>
+      <c r="E501" s="1" t="n">
+        <v>0.03608</v>
+      </c>
+      <c r="F501" s="2" t="n">
+        <v>-0.001383891502906212</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -8469,6 +11481,12 @@
       <c r="D502" s="3" t="n">
         <v>0.001572821642025839</v>
       </c>
+      <c r="E502" s="1" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="F502" s="3" t="n">
+        <v>0.001884422110552687</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -8485,6 +11503,12 @@
       <c r="D503" s="3" t="n">
         <v>0.00581395348837208</v>
       </c>
+      <c r="E503" s="1" t="n">
+        <v>0.007774</v>
+      </c>
+      <c r="F503" s="2" t="n">
+        <v>-0.001412973667309004</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -8501,6 +11525,12 @@
       <c r="D504" s="3" t="n">
         <v>0.0006555227794165125</v>
       </c>
+      <c r="E504" s="1" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="F504" s="2" t="n">
+        <v>-0.00131018670160498</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -8517,6 +11547,12 @@
       <c r="D505" s="3" t="n">
         <v>0.0002723311546841025</v>
       </c>
+      <c r="E505" s="1" t="n">
+        <v>0.0007360999999999999</v>
+      </c>
+      <c r="F505" s="3" t="n">
+        <v>0.002041927579635152</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -8533,6 +11569,12 @@
       <c r="D506" s="3" t="n">
         <v>0.001688618709895307</v>
       </c>
+      <c r="E506" s="1" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="F506" s="2" t="n">
+        <v>-0.002022926500337119</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -8549,6 +11591,12 @@
       <c r="D507" s="2" t="n">
         <v>-0.004922644163150535</v>
       </c>
+      <c r="E507" s="1" t="n">
+        <v>0.002838</v>
+      </c>
+      <c r="F507" s="3" t="n">
+        <v>0.002826855123674827</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -8565,6 +11613,12 @@
       <c r="D508" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E508" s="1" t="n">
+        <v>0.06338000000000001</v>
+      </c>
+      <c r="F508" s="3" t="n">
+        <v>0.001896933291179402</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -8581,6 +11635,12 @@
       <c r="D509" s="3" t="n">
         <v>0.0008936550491511278</v>
       </c>
+      <c r="E509" s="1" t="n">
+        <v>2.243</v>
+      </c>
+      <c r="F509" s="3" t="n">
+        <v>0.001339285714285567</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -8597,6 +11657,12 @@
       <c r="D510" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E510" s="1" t="n">
+        <v>0.0007275</v>
+      </c>
+      <c r="F510" s="2" t="n">
+        <v>-0.002331321996708853</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -8613,6 +11679,12 @@
       <c r="D511" s="2" t="n">
         <v>-0.002184996358339364</v>
       </c>
+      <c r="E511" s="1" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F511" s="3" t="n">
+        <v>0.003649635036496353</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -8629,6 +11701,12 @@
       <c r="D512" s="2" t="n">
         <v>-0.007288629737609393</v>
       </c>
+      <c r="E512" s="1" t="n">
+        <v>0.0004765</v>
+      </c>
+      <c r="F512" s="2" t="n">
+        <v>-0.0004195510803440421</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -8645,6 +11723,12 @@
       <c r="D513" s="2" t="n">
         <v>-0.0032673806498457</v>
       </c>
+      <c r="E513" s="1" t="n">
+        <v>0.05506</v>
+      </c>
+      <c r="F513" s="3" t="n">
+        <v>0.002731742851939489</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -8661,6 +11745,12 @@
       <c r="D514" s="3" t="n">
         <v>0.0006594131223211073</v>
       </c>
+      <c r="E514" s="1" t="n">
+        <v>0.03037</v>
+      </c>
+      <c r="F514" s="3" t="n">
+        <v>0.0006589785831961336</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -8677,6 +11767,12 @@
       <c r="D515" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E515" s="1" t="n">
+        <v>0.001145</v>
+      </c>
+      <c r="F515" s="3" t="n">
+        <v>0.003505696757230394</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -8693,6 +11789,12 @@
       <c r="D516" s="2" t="n">
         <v>-0.000303214069132848</v>
       </c>
+      <c r="E516" s="1" t="n">
+        <v>0.006607</v>
+      </c>
+      <c r="F516" s="3" t="n">
+        <v>0.001971489232635728</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -8709,6 +11811,12 @@
       <c r="D517" s="2" t="n">
         <v>-0.001506780512305487</v>
       </c>
+      <c r="E517" s="1" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="F517" s="3" t="n">
+        <v>0.0007545271629779238</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -8725,6 +11833,12 @@
       <c r="D518" s="2" t="n">
         <v>-0.00194552529182885</v>
       </c>
+      <c r="E518" s="1" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="F518" s="3" t="n">
+        <v>0.001949317738791479</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -8741,6 +11855,12 @@
       <c r="D519" s="2" t="n">
         <v>-0.004550625711035082</v>
       </c>
+      <c r="E519" s="1" t="n">
+        <v>0.008829999999999999</v>
+      </c>
+      <c r="F519" s="3" t="n">
+        <v>0.009142857142856968</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -8757,6 +11877,12 @@
       <c r="D520" s="2" t="n">
         <v>-0.004978220286247809</v>
       </c>
+      <c r="E520" s="1" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="F520" s="2" t="n">
+        <v>-0.005003126954346437</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -8773,6 +11899,12 @@
       <c r="D521" s="3" t="n">
         <v>0.003923766816143337</v>
       </c>
+      <c r="E521" s="1" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="F521" s="2" t="n">
+        <v>-0.003350083752093666</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -8789,6 +11921,12 @@
       <c r="D522" s="3" t="n">
         <v>0.0006045949214026356</v>
       </c>
+      <c r="E522" s="1" t="n">
+        <v>0.01655</v>
+      </c>
+      <c r="F522" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -8805,6 +11943,12 @@
       <c r="D523" s="2" t="n">
         <v>-0.0004768717215067711</v>
       </c>
+      <c r="E523" s="1" t="n">
+        <v>0.004194</v>
+      </c>
+      <c r="F523" s="3" t="n">
+        <v>0.0004770992366410778</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -8821,6 +11965,12 @@
       <c r="D524" s="2" t="n">
         <v>-0.002115655853314564</v>
       </c>
+      <c r="E524" s="1" t="n">
+        <v>0.01418</v>
+      </c>
+      <c r="F524" s="3" t="n">
+        <v>0.00212014134275622</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -8837,6 +11987,12 @@
       <c r="D525" s="3" t="n">
         <v>0.002008032128514114</v>
       </c>
+      <c r="E525" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F525" s="3" t="n">
+        <v>0.002004008016032122</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -8853,6 +12009,12 @@
       <c r="D526" s="2" t="n">
         <v>-0.003319502074688777</v>
       </c>
+      <c r="E526" s="1" t="n">
+        <v>0.1202</v>
+      </c>
+      <c r="F526" s="3" t="n">
+        <v>0.0008326394671107649</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -8869,6 +12031,12 @@
       <c r="D527" s="2" t="n">
         <v>-0.001536312849161997</v>
       </c>
+      <c r="E527" s="1" t="n">
+        <v>0.07151</v>
+      </c>
+      <c r="F527" s="3" t="n">
+        <v>0.000279759406910143</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -8885,6 +12053,12 @@
       <c r="D528" s="2" t="n">
         <v>-0.004639294827186401</v>
       </c>
+      <c r="E528" s="1" t="n">
+        <v>0.04305</v>
+      </c>
+      <c r="F528" s="3" t="n">
+        <v>0.003262642740619931</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -8901,6 +12075,12 @@
       <c r="D529" s="2" t="n">
         <v>-0.002213088839709157</v>
       </c>
+      <c r="E529" s="1" t="n">
+        <v>0.06302000000000001</v>
+      </c>
+      <c r="F529" s="2" t="n">
+        <v>-0.001584283903675364</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -8917,6 +12097,12 @@
       <c r="D530" s="3" t="n">
         <v>0.002203525641025586</v>
       </c>
+      <c r="E530" s="1" t="n">
+        <v>0.005005</v>
+      </c>
+      <c r="F530" s="3" t="n">
+        <v>0.0003997601439137049</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -8933,6 +12119,12 @@
       <c r="D531" s="2" t="n">
         <v>-0.001532567049808473</v>
       </c>
+      <c r="E531" s="1" t="n">
+        <v>0.1303</v>
+      </c>
+      <c r="F531" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -8949,6 +12141,12 @@
       <c r="D532" s="2" t="n">
         <v>-0.004868913857677964</v>
       </c>
+      <c r="E532" s="1" t="n">
+        <v>0.05334</v>
+      </c>
+      <c r="F532" s="3" t="n">
+        <v>0.003763643206623989</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -8965,6 +12163,12 @@
       <c r="D533" s="3" t="n">
         <v>0.01329433661260307</v>
       </c>
+      <c r="E533" s="1" t="n">
+        <v>0.003773</v>
+      </c>
+      <c r="F533" s="2" t="n">
+        <v>-0.00997113618472849</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -8981,6 +12185,12 @@
       <c r="D534" s="3" t="n">
         <v>0.000583430571762058</v>
       </c>
+      <c r="E534" s="1" t="n">
+        <v>0.1716</v>
+      </c>
+      <c r="F534" s="3" t="n">
+        <v>0.0005830903790086821</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -8997,6 +12207,12 @@
       <c r="D535" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="E535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="F535" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -9013,6 +12229,12 @@
       <c r="D536" s="3" t="n">
         <v>0.00448229493500671</v>
       </c>
+      <c r="E536" s="1" t="n">
+        <v>0.0004483</v>
+      </c>
+      <c r="F536" s="3" t="n">
+        <v>0.0002231146809460117</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -9029,6 +12251,12 @@
       <c r="D537" s="2" t="n">
         <v>-0.004132231404958689</v>
       </c>
+      <c r="E537" s="1" t="n">
+        <v>0.009679999999999999</v>
+      </c>
+      <c r="F537" s="3" t="n">
+        <v>0.004149377593361007</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -9045,6 +12273,12 @@
       <c r="D538" s="3" t="n">
         <v>0.0007354293068578483</v>
       </c>
+      <c r="E538" s="1" t="n">
+        <v>0.05433</v>
+      </c>
+      <c r="F538" s="2" t="n">
+        <v>-0.001837222120154252</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -9061,6 +12295,12 @@
       <c r="D539" s="3" t="n">
         <v>0.001169932728868124</v>
       </c>
+      <c r="E539" s="1" t="n">
+        <v>0.6833</v>
+      </c>
+      <c r="F539" s="2" t="n">
+        <v>-0.00189891907683314</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -9077,6 +12317,12 @@
       <c r="D540" s="3" t="n">
         <v>0.0006631299734749122</v>
       </c>
+      <c r="E540" s="1" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="F540" s="3" t="n">
+        <v>0.001988071570576506</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -9093,6 +12339,12 @@
       <c r="D541" s="2" t="n">
         <v>-0.005327245053272497</v>
       </c>
+      <c r="E541" s="1" t="n">
+        <v>0.01309</v>
+      </c>
+      <c r="F541" s="3" t="n">
+        <v>0.001530221882172853</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -9109,6 +12361,12 @@
       <c r="D542" s="3" t="n">
         <v>0.02444444444444448</v>
       </c>
+      <c r="E542" s="1" t="n">
+        <v>0.01423</v>
+      </c>
+      <c r="F542" s="3" t="n">
+        <v>0.02892263195950827</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -9124,6 +12382,12 @@
       </c>
       <c r="D543" s="2" t="n">
         <v>-0.002451409560497307</v>
+      </c>
+      <c r="E543" s="1" t="n">
+        <v>0.05719</v>
+      </c>
+      <c r="F543" s="3" t="n">
+        <v>0.003861681586800035</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F543"/>
+  <dimension ref="A1:H543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,8 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>change_00:30</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>price_00:45</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change_00:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,6 +499,12 @@
       <c r="F2" s="2" t="n">
         <v>-0.001015975936210368</v>
       </c>
+      <c r="G2" s="1" t="n">
+        <v>70339.3</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.004715094587568574</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -509,6 +527,12 @@
       <c r="F3" s="2" t="n">
         <v>-0.0006540982891695418</v>
       </c>
+      <c r="G3" s="1" t="n">
+        <v>2070.21</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0.003708983011403349</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -531,6 +555,12 @@
       <c r="F4" s="3" t="n">
         <v>0.0005808550185873276</v>
       </c>
+      <c r="G4" s="1" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0.007662835249042271</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -553,6 +583,12 @@
       <c r="F5" s="3" t="n">
         <v>0.01296246286794491</v>
       </c>
+      <c r="G5" s="1" t="n">
+        <v>0.010898</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>-0.03154714298409323</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -575,6 +611,12 @@
       <c r="F6" s="3" t="n">
         <v>0.003132969034608357</v>
       </c>
+      <c r="G6" s="1" t="n">
+        <v>1.3836</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0.004938988959906971</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -597,6 +639,12 @@
       <c r="F7" s="3" t="n">
         <v>0.001922666096987819</v>
       </c>
+      <c r="G7" s="1" t="n">
+        <v>0.09461</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.008635394456290035</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -619,6 +667,12 @@
       <c r="F8" s="3" t="n">
         <v>0.0001339871908246257</v>
       </c>
+      <c r="G8" s="1" t="n">
+        <v>37.508</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.004983655752639192</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -641,6 +695,12 @@
       <c r="F9" s="3" t="n">
         <v>0.009255533199195212</v>
       </c>
+      <c r="G9" s="1" t="n">
+        <v>0.05033</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0.003389154704944109</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -663,6 +723,12 @@
       <c r="F10" s="3" t="n">
         <v>0.005589347361499278</v>
       </c>
+      <c r="G10" s="1" t="n">
+        <v>18.306</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>-0.002452182442373612</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -685,6 +751,12 @@
       <c r="F11" s="2" t="n">
         <v>-0.0004616236843724296</v>
       </c>
+      <c r="G11" s="1" t="n">
+        <v>651.89</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0.003556143969949729</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -707,6 +779,12 @@
       <c r="F12" s="2" t="n">
         <v>-0.01151367909580651</v>
       </c>
+      <c r="G12" s="1" t="n">
+        <v>0.8963</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>-0.04220987390468046</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -729,6 +807,12 @@
       <c r="F13" s="3" t="n">
         <v>0.007377245508981998</v>
       </c>
+      <c r="G13" s="1" t="n">
+        <v>210.73</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0.00209234866137238</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -751,6 +835,12 @@
       <c r="F14" s="3" t="n">
         <v>0.003353351827576794</v>
       </c>
+      <c r="G14" s="1" t="n">
+        <v>0.0033199</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.008689575547655988</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -773,6 +863,12 @@
       <c r="F15" s="2" t="n">
         <v>-0.01418659637970463</v>
       </c>
+      <c r="G15" s="1" t="n">
+        <v>0.25708</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.010812723626784</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -795,6 +891,12 @@
       <c r="F16" s="3" t="n">
         <v>0.0005159958720330815</v>
       </c>
+      <c r="G16" s="1" t="n">
+        <v>0.9772999999999999</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.008045384218669332</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -817,6 +919,12 @@
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G17" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.003344481605351151</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -839,6 +947,12 @@
       <c r="F18" s="3" t="n">
         <v>0.008645124716553213</v>
       </c>
+      <c r="G18" s="1" t="n">
+        <v>216.21</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0.01264577771532957</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -861,6 +975,12 @@
       <c r="F19" s="3" t="n">
         <v>0.001531980084258949</v>
       </c>
+      <c r="G19" s="1" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0.006118546845124246</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -883,6 +1003,12 @@
       <c r="F20" s="3" t="n">
         <v>0.01095890410958905</v>
       </c>
+      <c r="G20" s="1" t="n">
+        <v>0.017101</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0.007482031342052675</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -905,6 +1031,12 @@
       <c r="F21" s="2" t="n">
         <v>-0.0009405371512175086</v>
       </c>
+      <c r="G21" s="1" t="n">
+        <v>9.606999999999999</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0.004916317991631675</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -927,6 +1059,12 @@
       <c r="F22" s="3" t="n">
         <v>0.004773269689737441</v>
       </c>
+      <c r="G22" s="1" t="n">
+        <v>0.1689</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0.002969121140142521</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -949,6 +1087,12 @@
       <c r="F23" s="3" t="n">
         <v>0.0007738828857234315</v>
       </c>
+      <c r="G23" s="1" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>-0.002148012372551347</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -971,6 +1115,12 @@
       <c r="F24" s="3" t="n">
         <v>0.001165501165501167</v>
       </c>
+      <c r="G24" s="1" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>0.003492433061699654</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -993,6 +1143,12 @@
       <c r="F25" s="3" t="n">
         <v>0.001222493887530675</v>
       </c>
+      <c r="G25" s="1" t="n">
+        <v>9.055</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0.005106005106005037</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1015,6 +1171,12 @@
       <c r="F26" s="3" t="n">
         <v>0.003044140030441403</v>
       </c>
+      <c r="G26" s="1" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>0.003793626707131937</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1037,6 +1199,12 @@
       <c r="F27" s="3" t="n">
         <v>0.0007506731686012647</v>
       </c>
+      <c r="G27" s="1" t="n">
+        <v>5137.43</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0.0009449438683859509</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1059,6 +1227,12 @@
       <c r="F28" s="3" t="n">
         <v>0.003435442313197764</v>
       </c>
+      <c r="G28" s="1" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0.009129814550642044</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1081,6 +1255,12 @@
       <c r="F29" s="3" t="n">
         <v>0.001887504718761757</v>
       </c>
+      <c r="G29" s="1" t="n">
+        <v>2.651</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>-0.001130369253956335</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1103,6 +1283,12 @@
       <c r="F30" s="2" t="n">
         <v>-0.005513644081146814</v>
       </c>
+      <c r="G30" s="1" t="n">
+        <v>0.5762</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0.0141509433962265</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1125,6 +1311,12 @@
       <c r="F31" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G31" s="1" t="n">
+        <v>0.002084</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0.007736943907156651</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1147,6 +1339,12 @@
       <c r="F32" s="3" t="n">
         <v>0.007192519779429311</v>
       </c>
+      <c r="G32" s="1" t="n">
+        <v>1.2547</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>-0.004443386495278941</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1169,6 +1367,12 @@
       <c r="F33" s="3" t="n">
         <v>0.006817477533312783</v>
       </c>
+      <c r="G33" s="1" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>-0.006155740227762394</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1191,6 +1395,12 @@
       <c r="F34" s="2" t="n">
         <v>-0.000666222518321046</v>
       </c>
+      <c r="G34" s="1" t="n">
+        <v>1.507</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0.004666666666666597</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1213,6 +1423,12 @@
       <c r="F35" s="3" t="n">
         <v>0.001383125864453655</v>
       </c>
+      <c r="G35" s="1" t="n">
+        <v>457.79</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0.003661317197228834</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1235,6 +1451,12 @@
       <c r="F36" s="2" t="n">
         <v>-0.00330101093459873</v>
       </c>
+      <c r="G36" s="1" t="n">
+        <v>0.04796</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>-0.007244876837093689</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1257,6 +1479,12 @@
       <c r="F37" s="3" t="n">
         <v>0.003546602354944046</v>
       </c>
+      <c r="G37" s="1" t="n">
+        <v>0.7079</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0.0007068136839128426</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1279,6 +1507,12 @@
       <c r="F38" s="3" t="n">
         <v>0.002854424357754469</v>
       </c>
+      <c r="G38" s="1" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0.006641366223908977</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1301,6 +1535,12 @@
       <c r="F39" s="3" t="n">
         <v>0.004314697512163764</v>
       </c>
+      <c r="G39" s="1" t="n">
+        <v>110.14</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0.006764168190127924</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1323,6 +1563,12 @@
       <c r="F40" s="2" t="n">
         <v>-0.01191709844559591</v>
       </c>
+      <c r="G40" s="1" t="n">
+        <v>0.03813</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>-0.000262191924488806</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1345,6 +1591,12 @@
       <c r="F41" s="2" t="n">
         <v>-0.002888608051994953</v>
       </c>
+      <c r="G41" s="1" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0.005975013579576262</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1367,6 +1619,12 @@
       <c r="F42" s="2" t="n">
         <v>-0.0001845018450185446</v>
       </c>
+      <c r="G42" s="1" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>0.003506181952389829</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1389,6 +1647,12 @@
       <c r="F43" s="2" t="n">
         <v>-0.0007604562737643858</v>
       </c>
+      <c r="G43" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0.003044140030441488</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1411,6 +1675,12 @@
       <c r="F44" s="3" t="n">
         <v>0.003593429158110915</v>
       </c>
+      <c r="G44" s="1" t="n">
+        <v>0.005886</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0.003580562659846431</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1433,6 +1703,12 @@
       <c r="F45" s="2" t="n">
         <v>-0.007964512551668506</v>
       </c>
+      <c r="G45" s="1" t="n">
+        <v>0.09861</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0.002134146341463433</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1455,6 +1731,12 @@
       <c r="F46" s="3" t="n">
         <v>0.003272727272727235</v>
       </c>
+      <c r="G46" s="1" t="n">
+        <v>2.776</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0.006161652772743713</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1477,6 +1759,12 @@
       <c r="F47" s="2" t="n">
         <v>-0.0006568712186690527</v>
       </c>
+      <c r="G47" s="1" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0.0003459489379367224</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1499,6 +1787,12 @@
       <c r="F48" s="3" t="n">
         <v>0.009487666034155606</v>
       </c>
+      <c r="G48" s="1" t="n">
+        <v>0.1081</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.01597744360902262</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1521,6 +1815,12 @@
       <c r="F49" s="2" t="n">
         <v>-0.01069049423590895</v>
       </c>
+      <c r="G49" s="1" t="n">
+        <v>0.24927</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0.005080440304826351</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1543,6 +1843,12 @@
       <c r="F50" s="2" t="n">
         <v>-0.006222775357809617</v>
       </c>
+      <c r="G50" s="1" t="n">
+        <v>0.0474</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>-0.01064495929868511</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1565,6 +1871,12 @@
       <c r="F51" s="3" t="n">
         <v>0.0007716049382716342</v>
       </c>
+      <c r="G51" s="1" t="n">
+        <v>3.919</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0.007196093549216146</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1587,6 +1899,12 @@
       <c r="F52" s="2" t="n">
         <v>-0.008403361344537905</v>
       </c>
+      <c r="G52" s="1" t="n">
+        <v>0.000235</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>-0.004237288135593209</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1609,6 +1927,12 @@
       <c r="F53" s="3" t="n">
         <v>0.00365185636031643</v>
       </c>
+      <c r="G53" s="1" t="n">
+        <v>0.1659</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0.006064281382656161</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1631,6 +1955,12 @@
       <c r="F54" s="3" t="n">
         <v>0.01224589762429587</v>
       </c>
+      <c r="G54" s="1" t="n">
+        <v>0.04137</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>0.0009678199854826608</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1653,6 +1983,12 @@
       <c r="F55" s="3" t="n">
         <v>0.006639004149377669</v>
       </c>
+      <c r="G55" s="1" t="n">
+        <v>0.12117</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>-0.001071723000824444</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1675,6 +2011,12 @@
       <c r="F56" s="3" t="n">
         <v>0.002508623392913036</v>
       </c>
+      <c r="G56" s="1" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>0.02064435408195181</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1697,6 +2039,12 @@
       <c r="F57" s="2" t="n">
         <v>-0.003372681281618896</v>
       </c>
+      <c r="G57" s="1" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>-0.001692047377326643</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1719,6 +2067,12 @@
       <c r="F58" s="3" t="n">
         <v>0.002022244691607602</v>
       </c>
+      <c r="G58" s="1" t="n">
+        <v>0.0997</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>0.006054490413723545</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1741,6 +2095,12 @@
       <c r="F59" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G59" s="1" t="n">
+        <v>0.00337</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>0.005970149253731359</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1763,6 +2123,12 @@
       <c r="F60" s="3" t="n">
         <v>0.004611330698287261</v>
       </c>
+      <c r="G60" s="1" t="n">
+        <v>0.1543</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>0.01180327868852456</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1785,6 +2151,12 @@
       <c r="F61" s="3" t="n">
         <v>0.002713789839065863</v>
       </c>
+      <c r="G61" s="1" t="n">
+        <v>0.15992</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>0.006545820745216598</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1807,6 +2179,12 @@
       <c r="F62" s="3" t="n">
         <v>0.002693507229940477</v>
       </c>
+      <c r="G62" s="1" t="n">
+        <v>0.7136</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0.008907111550968431</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1829,6 +2207,12 @@
       <c r="F63" s="3" t="n">
         <v>0.01926782273603089</v>
       </c>
+      <c r="G63" s="1" t="n">
+        <v>5.895</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0.01306066334421715</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1851,6 +2235,12 @@
       <c r="F64" s="3" t="n">
         <v>0.003559225512528452</v>
       </c>
+      <c r="G64" s="1" t="n">
+        <v>0.007129</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>0.01134912753582071</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1873,6 +2263,12 @@
       <c r="F65" s="2" t="n">
         <v>-0.01652624756966948</v>
       </c>
+      <c r="G65" s="1" t="n">
+        <v>0.03033</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>-0.0006589785831960193</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1895,6 +2291,12 @@
       <c r="F66" s="3" t="n">
         <v>0.00431034482758621</v>
       </c>
+      <c r="G66" s="1" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>0.01716738197424882</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1917,6 +2319,12 @@
       <c r="F67" s="3" t="n">
         <v>0.007490636704119856</v>
       </c>
+      <c r="G67" s="1" t="n">
+        <v>1.629</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0.009293680297397709</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1939,6 +2347,12 @@
       <c r="F68" s="2" t="n">
         <v>-0.0004525114384835341</v>
       </c>
+      <c r="G68" s="1" t="n">
+        <v>2.0073</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>0.009708249496981828</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1961,6 +2375,12 @@
       <c r="F69" s="2" t="n">
         <v>-0.00608695652173904</v>
       </c>
+      <c r="G69" s="1" t="n">
+        <v>0.5747</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>0.00559930008748903</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1983,6 +2403,12 @@
       <c r="F70" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G70" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2005,6 +2431,12 @@
       <c r="F71" s="3" t="n">
         <v>0.003186463026041109</v>
       </c>
+      <c r="G71" s="1" t="n">
+        <v>0.9166</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>0.003943044906900259</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2027,6 +2459,12 @@
       <c r="F72" s="3" t="n">
         <v>0.01623147494707132</v>
       </c>
+      <c r="G72" s="1" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>-0.01250000000000004</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2049,6 +2487,12 @@
       <c r="F73" s="3" t="n">
         <v>0.0009590792838873919</v>
       </c>
+      <c r="G73" s="1" t="n">
+        <v>0.09445000000000001</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>0.005536037474715283</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2071,6 +2515,12 @@
       <c r="F74" s="2" t="n">
         <v>-0.004418644948882241</v>
       </c>
+      <c r="G74" s="1" t="n">
+        <v>1.1455</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>-0.003132886606909797</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2093,6 +2543,12 @@
       <c r="F75" s="3" t="n">
         <v>0.000634115409004413</v>
       </c>
+      <c r="G75" s="1" t="n">
+        <v>0.01587</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>0.005703422053231927</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2115,6 +2571,12 @@
       <c r="F76" s="2" t="n">
         <v>-0.004561094662719061</v>
       </c>
+      <c r="G76" s="1" t="n">
+        <v>0.12505</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>0.005225080385852073</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2137,6 +2599,12 @@
       <c r="F77" s="3" t="n">
         <v>0.0008496176720476029</v>
       </c>
+      <c r="G77" s="1" t="n">
+        <v>0.1183</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>0.004244482173174876</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2159,6 +2627,12 @@
       <c r="F78" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G78" s="1" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>0.003968253968253945</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2181,6 +2655,12 @@
       <c r="F79" s="3" t="n">
         <v>0.002024633035262335</v>
       </c>
+      <c r="G79" s="1" t="n">
+        <v>0.00599</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>0.008587304259976399</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2203,6 +2683,12 @@
       <c r="F80" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G80" s="1" t="n">
+        <v>0.008185</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0.003186665032479468</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2225,6 +2711,12 @@
       <c r="F81" s="3" t="n">
         <v>0.002256063169768706</v>
       </c>
+      <c r="G81" s="1" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>0.003939223410241997</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2247,6 +2739,12 @@
       <c r="F82" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G82" s="1" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>0.009357454772301942</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2269,6 +2767,12 @@
       <c r="F83" s="3" t="n">
         <v>0.001960544050974147</v>
       </c>
+      <c r="G83" s="1" t="n">
+        <v>8.215</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>0.004647181117769385</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2291,6 +2795,12 @@
       <c r="F84" s="2" t="n">
         <v>-0.002814418921992293</v>
       </c>
+      <c r="G84" s="1" t="n">
+        <v>351.13</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>0.001026313538786138</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2313,6 +2823,12 @@
       <c r="F85" s="3" t="n">
         <v>0.005535499398315391</v>
       </c>
+      <c r="G85" s="1" t="n">
+        <v>0.004198</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0.004786979415988523</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2335,6 +2851,12 @@
       <c r="F86" s="2" t="n">
         <v>-0.005813953488372115</v>
       </c>
+      <c r="G86" s="1" t="n">
+        <v>0.13258</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>-0.005997900734742804</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2357,6 +2879,12 @@
       <c r="F87" s="2" t="n">
         <v>-0.01220752797558498</v>
       </c>
+      <c r="G87" s="1" t="n">
+        <v>0.01934</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>-0.004119464469618961</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2379,6 +2907,12 @@
       <c r="F88" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G88" s="1" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0.005347593582887507</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2401,6 +2935,12 @@
       <c r="F89" s="3" t="n">
         <v>0.002370470707754752</v>
       </c>
+      <c r="G89" s="1" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0.00270270270270278</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2423,6 +2963,12 @@
       <c r="F90" s="3" t="n">
         <v>0.001568012544100398</v>
       </c>
+      <c r="G90" s="1" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0.005870841487279848</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2445,6 +2991,12 @@
       <c r="F91" s="2" t="n">
         <v>-0.01411804728695364</v>
       </c>
+      <c r="G91" s="1" t="n">
+        <v>0.05785</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>-0.00189786059351275</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2467,6 +3019,12 @@
       <c r="F92" s="2" t="n">
         <v>-0.0007641170627339267</v>
       </c>
+      <c r="G92" s="1" t="n">
+        <v>1.3122</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0.003441156228492734</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2489,6 +3047,12 @@
       <c r="F93" s="3" t="n">
         <v>0.00207468879668058</v>
       </c>
+      <c r="G93" s="1" t="n">
+        <v>0.06304999999999999</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>0.004140786749482344</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2511,6 +3075,12 @@
       <c r="F94" s="3" t="n">
         <v>0.00906002265005665</v>
       </c>
+      <c r="G94" s="1" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>-0.001122334455667743</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2533,6 +3103,12 @@
       <c r="F95" s="3" t="n">
         <v>0.003327283726557743</v>
       </c>
+      <c r="G95" s="1" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>0.007235453723243935</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2555,6 +3131,12 @@
       <c r="F96" s="3" t="n">
         <v>0.002659574468085152</v>
       </c>
+      <c r="G96" s="1" t="n">
+        <v>0.02275</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>0.005747126436781528</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2577,6 +3159,12 @@
       <c r="F97" s="3" t="n">
         <v>0.004609711124769471</v>
       </c>
+      <c r="G97" s="1" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>0.003364943407769943</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2599,6 +3187,12 @@
       <c r="F98" s="3" t="n">
         <v>0.0009140767824496251</v>
       </c>
+      <c r="G98" s="1" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>0.01004566210045673</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2621,6 +3215,12 @@
       <c r="F99" s="3" t="n">
         <v>0.001005361930294944</v>
       </c>
+      <c r="G99" s="1" t="n">
+        <v>3.005</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>0.006026113157013657</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2643,6 +3243,12 @@
       <c r="F100" s="2" t="n">
         <v>-0.002029573789504222</v>
       </c>
+      <c r="G100" s="1" t="n">
+        <v>0.0346</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>0.005229517722254492</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2665,6 +3271,12 @@
       <c r="F101" s="3" t="n">
         <v>0.0005506607929514812</v>
       </c>
+      <c r="G101" s="1" t="n">
+        <v>1.822</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>0.002751788662630773</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2687,6 +3299,12 @@
       <c r="F102" s="3" t="n">
         <v>0.008185721953837818</v>
       </c>
+      <c r="G102" s="1" t="n">
+        <v>0.007555</v>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>0.005590310129109593</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2709,6 +3327,12 @@
       <c r="F103" s="3" t="n">
         <v>0.009509658246656786</v>
       </c>
+      <c r="G103" s="1" t="n">
+        <v>0.06781</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>-0.001913453046806081</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2731,6 +3355,12 @@
       <c r="F104" s="3" t="n">
         <v>0.0063106796116506</v>
       </c>
+      <c r="G104" s="1" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>-0.003135552339604494</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2753,6 +3383,12 @@
       <c r="F105" s="3" t="n">
         <v>0.003943661971831052</v>
       </c>
+      <c r="G105" s="1" t="n">
+        <v>1.786</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>0.00224466891133558</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2775,6 +3411,12 @@
       <c r="F106" s="3" t="n">
         <v>0.004096834264432035</v>
       </c>
+      <c r="G106" s="1" t="n">
+        <v>0.008083999999999999</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>-0.0004945598417409163</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2797,6 +3439,12 @@
       <c r="F107" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G107" s="1" t="n">
+        <v>0.01824</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>0.001097694840834203</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2819,6 +3467,12 @@
       <c r="F108" s="3" t="n">
         <v>0.007572172266919092</v>
       </c>
+      <c r="G108" s="1" t="n">
+        <v>0.02145</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>0.00751526538280885</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2841,6 +3495,12 @@
       <c r="F109" s="2" t="n">
         <v>-0.002836879432624121</v>
       </c>
+      <c r="G109" s="1" t="n">
+        <v>0.05618</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>-0.001066856330014181</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2863,6 +3523,12 @@
       <c r="F110" s="3" t="n">
         <v>0.009770066537522061</v>
       </c>
+      <c r="G110" s="1" t="n">
+        <v>0.12049</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>0.005004587538577057</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2885,6 +3551,12 @@
       <c r="F111" s="3" t="n">
         <v>0.00506996552423444</v>
       </c>
+      <c r="G111" s="1" t="n">
+        <v>0.09873</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>-0.003934624697336577</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2907,6 +3579,12 @@
       <c r="F112" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G112" s="1" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>0.00268817204301083</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2929,6 +3607,12 @@
       <c r="F113" s="3" t="n">
         <v>0.001023541453428893</v>
       </c>
+      <c r="G113" s="1" t="n">
+        <v>0.09828000000000001</v>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>0.004907975460122783</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2951,6 +3635,12 @@
       <c r="F114" s="2" t="n">
         <v>-0.00576036866359436</v>
       </c>
+      <c r="G114" s="1" t="n">
+        <v>0.001707</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>-0.01100811123986103</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2973,6 +3663,12 @@
       <c r="F115" s="3" t="n">
         <v>0.001701782820097237</v>
       </c>
+      <c r="G115" s="1" t="n">
+        <v>1.2447</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>0.006957365908906998</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2995,6 +3691,12 @@
       <c r="F116" s="2" t="n">
         <v>-0.006658343736995497</v>
       </c>
+      <c r="G116" s="1" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>0.00167574361122753</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3017,6 +3719,12 @@
       <c r="F117" s="3" t="n">
         <v>0.009446470003314569</v>
       </c>
+      <c r="G117" s="1" t="n">
+        <v>0.06127</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>0.005910359546872422</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3039,6 +3747,12 @@
       <c r="F118" s="3" t="n">
         <v>0.007237917347653462</v>
       </c>
+      <c r="G118" s="1" t="n">
+        <v>0.04397</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>0.01923968474733436</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3061,6 +3775,12 @@
       <c r="F119" s="2" t="n">
         <v>-0.0005256241787121766</v>
       </c>
+      <c r="G119" s="1" t="n">
+        <v>0.003776</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>-0.007099658164606919</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3083,6 +3803,12 @@
       <c r="F120" s="3" t="n">
         <v>0.003821656050955417</v>
       </c>
+      <c r="G120" s="1" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>0.00253807106598985</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3105,6 +3831,12 @@
       <c r="F121" s="3" t="n">
         <v>0.001692047377326567</v>
       </c>
+      <c r="G121" s="1" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>0.005067567567567572</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3127,6 +3859,12 @@
       <c r="F122" s="2" t="n">
         <v>-0.0008770391159446692</v>
       </c>
+      <c r="G122" s="1" t="n">
+        <v>0.5724</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>0.004915730337078695</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3149,6 +3887,12 @@
       <c r="F123" s="3" t="n">
         <v>0.003221225451144724</v>
       </c>
+      <c r="G123" s="1" t="n">
+        <v>0.028729</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>-0.008113520232012122</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3171,6 +3915,12 @@
       <c r="F124" s="2" t="n">
         <v>-0.004653502704062324</v>
       </c>
+      <c r="G124" s="1" t="n">
+        <v>0.07914</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3193,6 +3943,12 @@
       <c r="F125" s="3" t="n">
         <v>0.004548600810837557</v>
       </c>
+      <c r="G125" s="1" t="n">
+        <v>0.10243</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>0.008268530367162059</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3215,6 +3971,12 @@
       <c r="F126" s="2" t="n">
         <v>-0.01014860456687202</v>
       </c>
+      <c r="G126" s="1" t="n">
+        <v>0.02736</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>0.001830831197363529</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3237,6 +3999,12 @@
       <c r="F127" s="3" t="n">
         <v>0.006360745115856485</v>
       </c>
+      <c r="G127" s="1" t="n">
+        <v>0.02222</v>
+      </c>
+      <c r="H127" s="3" t="n">
+        <v>0.003160270880361202</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3259,6 +4027,12 @@
       <c r="F128" s="2" t="n">
         <v>-0.0006215040397761902</v>
       </c>
+      <c r="G128" s="1" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>0.004975124378109422</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3281,6 +4055,12 @@
       <c r="F129" s="2" t="n">
         <v>-0.005589879376287222</v>
       </c>
+      <c r="G129" s="1" t="n">
+        <v>0.1339</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>-0.009615384615384583</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3303,6 +4083,12 @@
       <c r="F130" s="2" t="n">
         <v>-0.006866622720281263</v>
       </c>
+      <c r="G130" s="1" t="n">
+        <v>0.05418</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>-0.001050943083135157</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3325,6 +4111,12 @@
       <c r="F131" s="3" t="n">
         <v>0.001105922831162531</v>
       </c>
+      <c r="G131" s="1" t="n">
+        <v>0.08205999999999999</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>0.007241929544617568</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3347,6 +4139,12 @@
       <c r="F132" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G132" s="1" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>0.008101851851851763</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3369,6 +4167,12 @@
       <c r="F133" s="3" t="n">
         <v>0.001729206294310913</v>
       </c>
+      <c r="G133" s="1" t="n">
+        <v>0.5800999999999999</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>0.001380977041256537</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3391,6 +4195,12 @@
       <c r="F134" s="2" t="n">
         <v>-0.001971090670170747</v>
       </c>
+      <c r="G134" s="1" t="n">
+        <v>0.03055</v>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>0.005595786701777485</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3413,6 +4223,12 @@
       <c r="F135" s="2" t="n">
         <v>-0.000566251415628516</v>
       </c>
+      <c r="G135" s="1" t="n">
+        <v>0.01779</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>0.007932011331444829</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3435,6 +4251,12 @@
       <c r="F136" s="3" t="n">
         <v>0.0002701242571583755</v>
       </c>
+      <c r="G136" s="1" t="n">
+        <v>0.03712</v>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>0.002430461787739665</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3457,6 +4279,12 @@
       <c r="F137" s="3" t="n">
         <v>0.002608047690014926</v>
       </c>
+      <c r="G137" s="1" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>0.007060572277963553</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3479,6 +4307,12 @@
       <c r="F138" s="3" t="n">
         <v>0.001613553852359824</v>
       </c>
+      <c r="G138" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>0.006846556584776441</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3501,6 +4335,12 @@
       <c r="F139" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G139" s="1" t="n">
+        <v>0.01195</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>0.003358522250209916</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3523,6 +4363,12 @@
       <c r="F140" s="2" t="n">
         <v>-0.02578981302385553</v>
       </c>
+      <c r="G140" s="1" t="n">
+        <v>0.01519</v>
+      </c>
+      <c r="H140" s="3" t="n">
+        <v>0.005294506949040385</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3545,6 +4391,12 @@
       <c r="F141" s="3" t="n">
         <v>0.00231177756950969</v>
       </c>
+      <c r="G141" s="1" t="n">
+        <v>16.122</v>
+      </c>
+      <c r="H141" s="3" t="n">
+        <v>0.004986909362922222</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3567,6 +4419,12 @@
       <c r="F142" s="3" t="n">
         <v>0.001610305958131979</v>
       </c>
+      <c r="G142" s="1" t="n">
+        <v>0.01245</v>
+      </c>
+      <c r="H142" s="3" t="n">
+        <v>0.0008038585209002888</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3589,6 +4447,12 @@
       <c r="F143" s="3" t="n">
         <v>0.001516875237011694</v>
       </c>
+      <c r="G143" s="1" t="n">
+        <v>0.02667</v>
+      </c>
+      <c r="H143" s="3" t="n">
+        <v>0.009844755774327899</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3611,6 +4475,12 @@
       <c r="F144" s="3" t="n">
         <v>0.003443822643133962</v>
       </c>
+      <c r="G144" s="1" t="n">
+        <v>0.004648</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>-0.003003003003003029</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3633,6 +4503,12 @@
       <c r="F145" s="3" t="n">
         <v>0.003992318576915311</v>
       </c>
+      <c r="G145" s="1" t="n">
+        <v>1.9939</v>
+      </c>
+      <c r="H145" s="3" t="n">
+        <v>0.003624100266774095</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3655,6 +4531,12 @@
       <c r="F146" s="3" t="n">
         <v>0.00570425625274235</v>
       </c>
+      <c r="G146" s="1" t="n">
+        <v>0.02304</v>
+      </c>
+      <c r="H146" s="3" t="n">
+        <v>0.005235602094240927</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3677,6 +4559,12 @@
       <c r="F147" s="3" t="n">
         <v>0.00569259962049332</v>
       </c>
+      <c r="G147" s="1" t="n">
+        <v>0.08986</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>-0.0026637069922309</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3699,6 +4587,12 @@
       <c r="F148" s="3" t="n">
         <v>0.01070950468540833</v>
       </c>
+      <c r="G148" s="1" t="n">
+        <v>0.06098</v>
+      </c>
+      <c r="H148" s="3" t="n">
+        <v>0.009602649006622469</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3721,6 +4615,12 @@
       <c r="F149" s="2" t="n">
         <v>-0.0005080440304825624</v>
       </c>
+      <c r="G149" s="1" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="H149" s="3" t="n">
+        <v>0.00304981362250084</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3743,6 +4643,12 @@
       <c r="F150" s="3" t="n">
         <v>0.005236867547534738</v>
       </c>
+      <c r="G150" s="1" t="n">
+        <v>0.24947</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>-0.0002805161497155345</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3765,6 +4671,12 @@
       <c r="F151" s="3" t="n">
         <v>0.003290457672749149</v>
       </c>
+      <c r="G151" s="1" t="n">
+        <v>6.768e-05</v>
+      </c>
+      <c r="H151" s="3" t="n">
+        <v>0.008944543828264774</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3787,6 +4699,12 @@
       <c r="F152" s="2" t="n">
         <v>-0.002713704206241472</v>
       </c>
+      <c r="G152" s="1" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="H152" s="3" t="n">
+        <v>0.005215419501133842</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3809,6 +4727,12 @@
       <c r="F153" s="3" t="n">
         <v>0.003920287487749214</v>
       </c>
+      <c r="G153" s="1" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>-0.001952489424015766</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3831,6 +4755,12 @@
       <c r="F154" s="3" t="n">
         <v>0.007088331515812407</v>
       </c>
+      <c r="G154" s="1" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>-0.007850568489442376</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3853,6 +4783,12 @@
       <c r="F155" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G155" s="1" t="n">
+        <v>0.2313</v>
+      </c>
+      <c r="H155" s="3" t="n">
+        <v>0.004342162396873647</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3875,6 +4811,12 @@
       <c r="F156" s="3" t="n">
         <v>0.005440830963274341</v>
       </c>
+      <c r="G156" s="1" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>-0.005042430205386714</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3897,6 +4839,12 @@
       <c r="F157" s="3" t="n">
         <v>0.03308013843318804</v>
       </c>
+      <c r="G157" s="1" t="n">
+        <v>0.22862</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>-0.005351316075701583</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3919,6 +4867,12 @@
       <c r="F158" s="3" t="n">
         <v>0.00403388463089956</v>
       </c>
+      <c r="G158" s="1" t="n">
+        <v>0.2498</v>
+      </c>
+      <c r="H158" s="3" t="n">
+        <v>0.003615910004017614</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3941,6 +4895,12 @@
       <c r="F159" s="2" t="n">
         <v>-0.001020755358965673</v>
       </c>
+      <c r="G159" s="1" t="n">
+        <v>2.936</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3963,6 +4923,12 @@
       <c r="F160" s="3" t="n">
         <v>0.001002004008016061</v>
       </c>
+      <c r="G160" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>0.00100100100100103</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3985,6 +4951,12 @@
       <c r="F161" s="3" t="n">
         <v>0.003640109890109908</v>
       </c>
+      <c r="G161" s="1" t="n">
+        <v>0.14616</v>
+      </c>
+      <c r="H161" s="3" t="n">
+        <v>0.0002052966536645606</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4007,6 +4979,12 @@
       <c r="F162" s="3" t="n">
         <v>0.00276752767527672</v>
       </c>
+      <c r="G162" s="1" t="n">
+        <v>0.003271</v>
+      </c>
+      <c r="H162" s="3" t="n">
+        <v>0.003066544004906478</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4029,6 +5007,12 @@
       <c r="F163" s="3" t="n">
         <v>0.001006846556584735</v>
       </c>
+      <c r="G163" s="1" t="n">
+        <v>0.004992</v>
+      </c>
+      <c r="H163" s="3" t="n">
+        <v>0.004224502112251094</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4051,6 +5035,12 @@
       <c r="F164" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G164" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="H164" s="3" t="n">
+        <v>0.007314524555903932</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4073,6 +5063,12 @@
       <c r="F165" s="2" t="n">
         <v>-0.001969796454366348</v>
       </c>
+      <c r="G165" s="1" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="H165" s="3" t="n">
+        <v>0.01151315789473685</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4095,6 +5091,12 @@
       <c r="F166" s="2" t="n">
         <v>-0.0004327443202309094</v>
       </c>
+      <c r="G166" s="1" t="n">
+        <v>1.3928</v>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>0.004978714192943307</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4117,6 +5119,12 @@
       <c r="F167" s="2" t="n">
         <v>-0.001083423618634767</v>
       </c>
+      <c r="G167" s="1" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="H167" s="3" t="n">
+        <v>0.004338394793926171</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4139,6 +5147,12 @@
       <c r="F168" s="3" t="n">
         <v>0.003194888178913741</v>
       </c>
+      <c r="G168" s="1" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="H168" s="3" t="n">
+        <v>0.003184713375796181</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4161,6 +5175,12 @@
       <c r="F169" s="3" t="n">
         <v>0.00170241743275456</v>
       </c>
+      <c r="G169" s="1" t="n">
+        <v>0.02965</v>
+      </c>
+      <c r="H169" s="3" t="n">
+        <v>0.007817811012916301</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4183,6 +5203,12 @@
       <c r="F170" s="2" t="n">
         <v>-0.01584114234716634</v>
       </c>
+      <c r="G170" s="1" t="n">
+        <v>0.04373</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>-0.008614826569938909</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4205,6 +5231,12 @@
       <c r="F171" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G171" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="H171" s="3" t="n">
+        <v>0.006060606060606023</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4227,6 +5259,12 @@
       <c r="F172" s="2" t="n">
         <v>-0.008196721311475471</v>
       </c>
+      <c r="G172" s="1" t="n">
+        <v>1.22e-05</v>
+      </c>
+      <c r="H172" s="3" t="n">
+        <v>0.008264462809917416</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4249,6 +5287,12 @@
       <c r="F173" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G173" s="1" t="n">
+        <v>0.02108</v>
+      </c>
+      <c r="H173" s="3" t="n">
+        <v>0.007166746297181119</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4271,6 +5315,12 @@
       <c r="F174" s="3" t="n">
         <v>0.01087687822381699</v>
       </c>
+      <c r="G174" s="1" t="n">
+        <v>0.09038</v>
+      </c>
+      <c r="H174" s="3" t="n">
+        <v>0.002551303383250227</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4293,6 +5343,12 @@
       <c r="F175" s="2" t="n">
         <v>-0.001114516578434136</v>
       </c>
+      <c r="G175" s="1" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="H175" s="3" t="n">
+        <v>0.008368200836820092</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4315,6 +5371,12 @@
       <c r="F176" s="2" t="n">
         <v>-0.001396648044692681</v>
       </c>
+      <c r="G176" s="1" t="n">
+        <v>0.02149</v>
+      </c>
+      <c r="H176" s="3" t="n">
+        <v>0.001864801864801789</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4337,6 +5399,12 @@
       <c r="F177" s="3" t="n">
         <v>0.002518891687657547</v>
       </c>
+      <c r="G177" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H177" s="3" t="n">
+        <v>0.005025125628140717</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4359,6 +5427,12 @@
       <c r="F178" s="2" t="n">
         <v>-0.0030518819938962</v>
       </c>
+      <c r="G178" s="1" t="n">
+        <v>0.00098</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4381,6 +5455,12 @@
       <c r="F179" s="3" t="n">
         <v>0.0002619515389654019</v>
       </c>
+      <c r="G179" s="1" t="n">
+        <v>0.022954</v>
+      </c>
+      <c r="H179" s="3" t="n">
+        <v>0.001876827724673646</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4403,6 +5483,12 @@
       <c r="F180" s="2" t="n">
         <v>-0.02753108348134984</v>
       </c>
+      <c r="G180" s="1" t="n">
+        <v>4.324</v>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>-0.01278538812785389</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4425,6 +5511,12 @@
       <c r="F181" s="2" t="n">
         <v>-0.009797181161911375</v>
       </c>
+      <c r="G181" s="1" t="n">
+        <v>0.5790999999999999</v>
+      </c>
+      <c r="H181" s="3" t="n">
+        <v>0.005207429265752479</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4447,6 +5539,12 @@
       <c r="F182" s="3" t="n">
         <v>0.003887070376432133</v>
       </c>
+      <c r="G182" s="1" t="n">
+        <v>0.04964</v>
+      </c>
+      <c r="H182" s="3" t="n">
+        <v>0.01161605869166485</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4469,6 +5567,12 @@
       <c r="F183" s="3" t="n">
         <v>0.001839249586168804</v>
       </c>
+      <c r="G183" s="1" t="n">
+        <v>5.471</v>
+      </c>
+      <c r="H183" s="3" t="n">
+        <v>0.004406095098219207</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4491,6 +5595,12 @@
       <c r="F184" s="2" t="n">
         <v>-0.0003522367030645144</v>
       </c>
+      <c r="G184" s="1" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="H184" s="3" t="n">
+        <v>0.008104298801973235</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4513,6 +5623,12 @@
       <c r="F185" s="3" t="n">
         <v>0.002736726874657797</v>
       </c>
+      <c r="G185" s="1" t="n">
+        <v>0.01851</v>
+      </c>
+      <c r="H185" s="3" t="n">
+        <v>0.01037117903930127</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4535,6 +5651,12 @@
       <c r="F186" s="3" t="n">
         <v>0.006410256410256349</v>
       </c>
+      <c r="G186" s="1" t="n">
+        <v>3.16e-05</v>
+      </c>
+      <c r="H186" s="3" t="n">
+        <v>0.006369426751592512</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4557,6 +5679,12 @@
       <c r="F187" s="3" t="n">
         <v>0.008119925046845824</v>
       </c>
+      <c r="G187" s="1" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="H187" s="3" t="n">
+        <v>0.003717472118958956</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4579,6 +5707,12 @@
       <c r="F188" s="3" t="n">
         <v>0.0004973887092762792</v>
       </c>
+      <c r="G188" s="1" t="n">
+        <v>0.04045</v>
+      </c>
+      <c r="H188" s="3" t="n">
+        <v>0.005468555804126223</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4601,6 +5735,12 @@
       <c r="F189" s="3" t="n">
         <v>0.003000923361034112</v>
       </c>
+      <c r="G189" s="1" t="n">
+        <v>0.0004375</v>
+      </c>
+      <c r="H189" s="3" t="n">
+        <v>0.006904487917146188</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4623,6 +5763,12 @@
       <c r="F190" s="2" t="n">
         <v>-0.001304915180513214</v>
       </c>
+      <c r="G190" s="1" t="n">
+        <v>0.02292</v>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>-0.001742160278745725</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4645,6 +5791,12 @@
       <c r="F191" s="2" t="n">
         <v>-0.002541296060991222</v>
       </c>
+      <c r="G191" s="1" t="n">
+        <v>0.01577</v>
+      </c>
+      <c r="H191" s="3" t="n">
+        <v>0.004458598726114689</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4667,6 +5819,12 @@
       <c r="F192" s="3" t="n">
         <v>0.0001798561151079688</v>
       </c>
+      <c r="G192" s="1" t="n">
+        <v>0.05576</v>
+      </c>
+      <c r="H192" s="3" t="n">
+        <v>0.002697356590541222</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4689,6 +5847,12 @@
       <c r="F193" s="3" t="n">
         <v>0.001612903225806423</v>
       </c>
+      <c r="G193" s="1" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="H193" s="3" t="n">
+        <v>0.005904455179817593</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4711,6 +5875,12 @@
       <c r="F194" s="3" t="n">
         <v>0.005810882197570125</v>
       </c>
+      <c r="G194" s="1" t="n">
+        <v>0.01921</v>
+      </c>
+      <c r="H194" s="3" t="n">
+        <v>0.008928571428571428</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4733,6 +5903,12 @@
       <c r="F195" s="3" t="n">
         <v>0.005210693248753894</v>
       </c>
+      <c r="G195" s="1" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>-0.02163624070317782</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4755,6 +5931,12 @@
       <c r="F196" s="3" t="n">
         <v>0.00480384307445965</v>
       </c>
+      <c r="G196" s="1" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="H196" s="3" t="n">
+        <v>0.003984063745019896</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4777,6 +5959,12 @@
       <c r="F197" s="3" t="n">
         <v>0.003089825645552732</v>
       </c>
+      <c r="G197" s="1" t="n">
+        <v>0.04581</v>
+      </c>
+      <c r="H197" s="3" t="n">
+        <v>0.007920792079207904</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4799,6 +5987,12 @@
       <c r="F198" s="2" t="n">
         <v>-0.001758499413833552</v>
       </c>
+      <c r="G198" s="1" t="n">
+        <v>0.5087</v>
+      </c>
+      <c r="H198" s="2" t="n">
+        <v>-0.004306126443530984</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4821,6 +6015,12 @@
       <c r="F199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G199" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="H199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4843,6 +6043,12 @@
       <c r="F200" s="3" t="n">
         <v>0.005431093007467758</v>
       </c>
+      <c r="G200" s="1" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="H200" s="3" t="n">
+        <v>0.0006752194463200396</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4865,6 +6071,12 @@
       <c r="F201" s="3" t="n">
         <v>0.001597160603371687</v>
       </c>
+      <c r="G201" s="1" t="n">
+        <v>0.005678</v>
+      </c>
+      <c r="H201" s="3" t="n">
+        <v>0.0060240963855422</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4887,6 +6099,12 @@
       <c r="F202" s="2" t="n">
         <v>-0.006675156997935943</v>
       </c>
+      <c r="G202" s="1" t="n">
+        <v>0.02264</v>
+      </c>
+      <c r="H202" s="3" t="n">
+        <v>0.0009284230072063391</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4909,6 +6127,12 @@
       <c r="F203" s="2" t="n">
         <v>-0.007272727272727228</v>
       </c>
+      <c r="G203" s="1" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="H203" s="3" t="n">
+        <v>0.01465201465201456</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4931,6 +6155,12 @@
       <c r="F204" s="3" t="n">
         <v>0.0008792497069168303</v>
       </c>
+      <c r="G204" s="1" t="n">
+        <v>0.03411</v>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v>-0.001171303074670523</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4953,6 +6183,12 @@
       <c r="F205" s="3" t="n">
         <v>0.001407459535538407</v>
       </c>
+      <c r="G205" s="1" t="n">
+        <v>4.293</v>
+      </c>
+      <c r="H205" s="3" t="n">
+        <v>0.005621925509487005</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4975,6 +6211,12 @@
       <c r="F206" s="2" t="n">
         <v>-0.00277777777777778</v>
       </c>
+      <c r="G206" s="1" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="H206" s="3" t="n">
+        <v>0.008356545961002793</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4997,6 +6239,12 @@
       <c r="F207" s="3" t="n">
         <v>0.01503445395698478</v>
       </c>
+      <c r="G207" s="1" t="n">
+        <v>0.0009806999999999999</v>
+      </c>
+      <c r="H207" s="3" t="n">
+        <v>0.008743056984159572</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5019,6 +6267,12 @@
       <c r="F208" s="2" t="n">
         <v>-0.002732987154960379</v>
       </c>
+      <c r="G208" s="1" t="n">
+        <v>0.007301</v>
+      </c>
+      <c r="H208" s="3" t="n">
+        <v>0.0004110715264456561</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5041,6 +6295,12 @@
       <c r="F209" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G209" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H209" s="3" t="n">
+        <v>0.003344481605351151</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5063,6 +6323,12 @@
       <c r="F210" s="3" t="n">
         <v>0.000775193798449527</v>
       </c>
+      <c r="G210" s="1" t="n">
+        <v>0.1296</v>
+      </c>
+      <c r="H210" s="3" t="n">
+        <v>0.003872966692486448</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5085,6 +6351,12 @@
       <c r="F211" s="3" t="n">
         <v>0.001133947554925612</v>
       </c>
+      <c r="G211" s="1" t="n">
+        <v>0.007119</v>
+      </c>
+      <c r="H211" s="3" t="n">
+        <v>0.007928642220019893</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5107,6 +6379,12 @@
       <c r="F212" s="3" t="n">
         <v>0.01505916098960214</v>
       </c>
+      <c r="G212" s="1" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="H212" s="3" t="n">
+        <v>0.03285058283292114</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5129,6 +6407,12 @@
       <c r="F213" s="2" t="n">
         <v>-0.009984506799793494</v>
       </c>
+      <c r="G213" s="1" t="n">
+        <v>0.05733</v>
+      </c>
+      <c r="H213" s="2" t="n">
+        <v>-0.003129890453834109</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5151,6 +6435,12 @@
       <c r="F214" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G214" s="1" t="n">
+        <v>0.1883</v>
+      </c>
+      <c r="H214" s="3" t="n">
+        <v>0.001595744680851036</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5173,6 +6463,12 @@
       <c r="F215" s="3" t="n">
         <v>0.001918281220026778</v>
       </c>
+      <c r="G215" s="1" t="n">
+        <v>0.05259</v>
+      </c>
+      <c r="H215" s="3" t="n">
+        <v>0.006892590465249842</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5195,6 +6491,12 @@
       <c r="F216" s="3" t="n">
         <v>0.0004784688995215946</v>
       </c>
+      <c r="G216" s="1" t="n">
+        <v>0.002102</v>
+      </c>
+      <c r="H216" s="3" t="n">
+        <v>0.005260640841702611</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5217,6 +6519,12 @@
       <c r="F217" s="3" t="n">
         <v>0.001837314180724924</v>
       </c>
+      <c r="G217" s="1" t="n">
+        <v>6.029</v>
+      </c>
+      <c r="H217" s="3" t="n">
+        <v>0.005168389463154333</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5239,6 +6547,12 @@
       <c r="F218" s="2" t="n">
         <v>-0.004710632570659468</v>
       </c>
+      <c r="G218" s="1" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="H218" s="2" t="n">
+        <v>-0.003831417624521151</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5261,6 +6575,12 @@
       <c r="F219" s="3" t="n">
         <v>0.001122124555825683</v>
       </c>
+      <c r="G219" s="1" t="n">
+        <v>0.005382</v>
+      </c>
+      <c r="H219" s="3" t="n">
+        <v>0.005417522884363817</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5283,6 +6603,12 @@
       <c r="F220" s="3" t="n">
         <v>0.002435460301997147</v>
       </c>
+      <c r="G220" s="1" t="n">
+        <v>0.04125</v>
+      </c>
+      <c r="H220" s="3" t="n">
+        <v>0.002186588921282794</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5305,6 +6631,12 @@
       <c r="F221" s="3" t="n">
         <v>0.004356159609688073</v>
       </c>
+      <c r="G221" s="1" t="n">
+        <v>0.005787</v>
+      </c>
+      <c r="H221" s="3" t="n">
+        <v>0.003990284524635597</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5327,6 +6659,12 @@
       <c r="F222" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G222" s="1" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="H222" s="3" t="n">
+        <v>0.005537098560354379</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5349,6 +6687,12 @@
       <c r="F223" s="2" t="n">
         <v>-0.0008904719501334728</v>
       </c>
+      <c r="G223" s="1" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="H223" s="3" t="n">
+        <v>0.005050505050504988</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5371,6 +6715,12 @@
       <c r="F224" s="3" t="n">
         <v>0.001160362032954283</v>
       </c>
+      <c r="G224" s="1" t="n">
+        <v>0.4337</v>
+      </c>
+      <c r="H224" s="3" t="n">
+        <v>0.005331478905887734</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5393,6 +6743,12 @@
       <c r="F225" s="3" t="n">
         <v>0.001322751322751311</v>
       </c>
+      <c r="G225" s="1" t="n">
+        <v>0.08341</v>
+      </c>
+      <c r="H225" s="3" t="n">
+        <v>0.001681277771106055</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5415,6 +6771,12 @@
       <c r="F226" s="2" t="n">
         <v>-0.002653927813163374</v>
       </c>
+      <c r="G226" s="1" t="n">
+        <v>0.01874</v>
+      </c>
+      <c r="H226" s="2" t="n">
+        <v>-0.002660989888238501</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5437,6 +6799,12 @@
       <c r="F227" s="3" t="n">
         <v>0.004314994606256716</v>
       </c>
+      <c r="G227" s="1" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="H227" s="3" t="n">
+        <v>0.005370569280343721</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5459,6 +6827,12 @@
       <c r="F228" s="3" t="n">
         <v>0.002586206896551768</v>
       </c>
+      <c r="G228" s="1" t="n">
+        <v>0.02329</v>
+      </c>
+      <c r="H228" s="3" t="n">
+        <v>0.001289767841788575</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5481,6 +6855,12 @@
       <c r="F229" s="3" t="n">
         <v>0.003748828491096509</v>
       </c>
+      <c r="G229" s="1" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="H229" s="3" t="n">
+        <v>0.006535947712418358</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5503,6 +6883,12 @@
       <c r="F230" s="2" t="n">
         <v>-0.001198322348711838</v>
       </c>
+      <c r="G230" s="1" t="n">
+        <v>0.1679</v>
+      </c>
+      <c r="H230" s="3" t="n">
+        <v>0.007198560287942452</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5525,6 +6911,12 @@
       <c r="F231" s="2" t="n">
         <v>-0.0006565988181222145</v>
       </c>
+      <c r="G231" s="1" t="n">
+        <v>0.03058</v>
+      </c>
+      <c r="H231" s="3" t="n">
+        <v>0.004599211563731972</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5547,6 +6939,12 @@
       <c r="F232" s="2" t="n">
         <v>-0.00345572354211664</v>
       </c>
+      <c r="G232" s="1" t="n">
+        <v>0.02319</v>
+      </c>
+      <c r="H232" s="3" t="n">
+        <v>0.005201560468140381</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5569,6 +6967,12 @@
       <c r="F233" s="3" t="n">
         <v>0.03400534369686661</v>
       </c>
+      <c r="G233" s="1" t="n">
+        <v>0.12011</v>
+      </c>
+      <c r="H233" s="2" t="n">
+        <v>-0.05950982695168739</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5591,6 +6995,12 @@
       <c r="F234" s="2" t="n">
         <v>-0.00239043824701191</v>
       </c>
+      <c r="G234" s="1" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="H234" s="3" t="n">
+        <v>0.008386581469648526</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5613,6 +7023,12 @@
       <c r="F235" s="3" t="n">
         <v>0.00464643531290839</v>
       </c>
+      <c r="G235" s="1" t="n">
+        <v>0.06950000000000001</v>
+      </c>
+      <c r="H235" s="3" t="n">
+        <v>0.004480416245122195</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5635,6 +7051,12 @@
       <c r="F236" s="3" t="n">
         <v>0.001884936895590838</v>
       </c>
+      <c r="G236" s="1" t="n">
+        <v>0.12219</v>
+      </c>
+      <c r="H236" s="2" t="n">
+        <v>-0.0004907975460123067</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5657,6 +7079,12 @@
       <c r="F237" s="3" t="n">
         <v>0.0149892933618845</v>
       </c>
+      <c r="G237" s="1" t="n">
+        <v>0.03836</v>
+      </c>
+      <c r="H237" s="3" t="n">
+        <v>0.01160337552742605</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5679,6 +7107,12 @@
       <c r="F238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G238" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5701,6 +7135,12 @@
       <c r="F239" s="3" t="n">
         <v>0.00501882057716438</v>
       </c>
+      <c r="G239" s="1" t="n">
+        <v>0.00405</v>
+      </c>
+      <c r="H239" s="3" t="n">
+        <v>0.01123595505617975</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5723,6 +7163,12 @@
       <c r="F240" s="2" t="n">
         <v>-0.0007299270072992403</v>
       </c>
+      <c r="G240" s="1" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="H240" s="3" t="n">
+        <v>0.003652300949598225</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5745,6 +7191,12 @@
       <c r="F241" s="2" t="n">
         <v>-0.002801774457156279</v>
       </c>
+      <c r="G241" s="1" t="n">
+        <v>0.4293</v>
+      </c>
+      <c r="H241" s="3" t="n">
+        <v>0.005151018496839231</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5767,6 +7219,12 @@
       <c r="F242" s="3" t="n">
         <v>0.002732240437158477</v>
       </c>
+      <c r="G242" s="1" t="n">
+        <v>0.00738</v>
+      </c>
+      <c r="H242" s="3" t="n">
+        <v>0.005449591280653966</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5789,6 +7247,12 @@
       <c r="F243" s="3" t="n">
         <v>0.004803493449781615</v>
       </c>
+      <c r="G243" s="1" t="n">
+        <v>0.02308</v>
+      </c>
+      <c r="H243" s="3" t="n">
+        <v>0.003042155584528493</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5811,6 +7275,12 @@
       <c r="F244" s="3" t="n">
         <v>0.006598680263947176</v>
       </c>
+      <c r="G244" s="1" t="n">
+        <v>0.001689</v>
+      </c>
+      <c r="H244" s="3" t="n">
+        <v>0.006555423122765162</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5833,6 +7303,12 @@
       <c r="F245" s="3" t="n">
         <v>0.002286585365853618</v>
       </c>
+      <c r="G245" s="1" t="n">
+        <v>0.1321</v>
+      </c>
+      <c r="H245" s="3" t="n">
+        <v>0.004562737642585471</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5855,6 +7331,12 @@
       <c r="F246" s="2" t="n">
         <v>-0.003802281368821138</v>
       </c>
+      <c r="G246" s="1" t="n">
+        <v>0.03136</v>
+      </c>
+      <c r="H246" s="2" t="n">
+        <v>-0.002544529262086631</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5877,6 +7359,12 @@
       <c r="F247" s="3" t="n">
         <v>0.000563063063063001</v>
       </c>
+      <c r="G247" s="1" t="n">
+        <v>0.1784</v>
+      </c>
+      <c r="H247" s="3" t="n">
+        <v>0.003939223410242016</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5899,6 +7387,12 @@
       <c r="F248" s="2" t="n">
         <v>-0.00458415193189264</v>
       </c>
+      <c r="G248" s="1" t="n">
+        <v>0.03073</v>
+      </c>
+      <c r="H248" s="3" t="n">
+        <v>0.01085526315789475</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5921,6 +7415,12 @@
       <c r="F249" s="2" t="n">
         <v>-0.002800140007000317</v>
       </c>
+      <c r="G249" s="1" t="n">
+        <v>0.008652999999999999</v>
+      </c>
+      <c r="H249" s="3" t="n">
+        <v>0.01240201240201222</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5943,6 +7443,12 @@
       <c r="F250" s="3" t="n">
         <v>0.006274131274131354</v>
       </c>
+      <c r="G250" s="1" t="n">
+        <v>0.02102</v>
+      </c>
+      <c r="H250" s="3" t="n">
+        <v>0.00815347721822542</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5965,6 +7471,12 @@
       <c r="F251" s="2" t="n">
         <v>-0.001281503630926902</v>
       </c>
+      <c r="G251" s="1" t="n">
+        <v>0.04686</v>
+      </c>
+      <c r="H251" s="3" t="n">
+        <v>0.002138579982891273</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5987,6 +7499,12 @@
       <c r="F252" s="3" t="n">
         <v>0.002767749699157696</v>
       </c>
+      <c r="G252" s="1" t="n">
+        <v>0.008425</v>
+      </c>
+      <c r="H252" s="3" t="n">
+        <v>0.01104044161766471</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -6009,6 +7527,12 @@
       <c r="F253" s="2" t="n">
         <v>-0.001267105930055789</v>
       </c>
+      <c r="G253" s="1" t="n">
+        <v>0.03964</v>
+      </c>
+      <c r="H253" s="3" t="n">
+        <v>0.005836082212636413</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -6031,6 +7555,12 @@
       <c r="F254" s="3" t="n">
         <v>0.001313844637871632</v>
       </c>
+      <c r="G254" s="1" t="n">
+        <v>0.06118</v>
+      </c>
+      <c r="H254" s="3" t="n">
+        <v>0.003444316877152614</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6053,6 +7583,12 @@
       <c r="F255" s="3" t="n">
         <v>0.01349451785212266</v>
       </c>
+      <c r="G255" s="1" t="n">
+        <v>0.003556</v>
+      </c>
+      <c r="H255" s="2" t="n">
+        <v>-0.01359223300970874</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -6075,6 +7611,12 @@
       <c r="F256" s="2" t="n">
         <v>-0.001295139417949082</v>
       </c>
+      <c r="G256" s="1" t="n">
+        <v>0.013171</v>
+      </c>
+      <c r="H256" s="3" t="n">
+        <v>0.004729575101075563</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6097,6 +7639,12 @@
       <c r="F257" s="3" t="n">
         <v>1.00062739340442e-06</v>
       </c>
+      <c r="G257" s="1" t="n">
+        <v>0.999374</v>
+      </c>
+      <c r="H257" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6119,6 +7667,12 @@
       <c r="F258" s="2" t="n">
         <v>-0.00601642948050453</v>
       </c>
+      <c r="G258" s="1" t="n">
+        <v>0.08578</v>
+      </c>
+      <c r="H258" s="2" t="n">
+        <v>-0.001513211500407463</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -6141,6 +7695,12 @@
       <c r="F259" s="3" t="n">
         <v>0.008906426155580597</v>
       </c>
+      <c r="G259" s="1" t="n">
+        <v>0.08937</v>
+      </c>
+      <c r="H259" s="2" t="n">
+        <v>-0.001340931947703599</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -6163,6 +7723,12 @@
       <c r="F260" s="2" t="n">
         <v>-0.003689129365469855</v>
       </c>
+      <c r="G260" s="1" t="n">
+        <v>0.08216</v>
+      </c>
+      <c r="H260" s="3" t="n">
+        <v>0.01407059985188845</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6185,6 +7751,12 @@
       <c r="F261" s="2" t="n">
         <v>-0.002673796791443951</v>
       </c>
+      <c r="G261" s="1" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="H261" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -6207,6 +7779,12 @@
       <c r="F262" s="3" t="n">
         <v>0.001374381528312203</v>
       </c>
+      <c r="G262" s="1" t="n">
+        <v>0.003674</v>
+      </c>
+      <c r="H262" s="3" t="n">
+        <v>0.008509470216854298</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -6229,6 +7807,12 @@
       <c r="F263" s="3" t="n">
         <v>0.01029159519725563</v>
       </c>
+      <c r="G263" s="1" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="H263" s="2" t="n">
+        <v>-0.0008488964346349988</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -6251,6 +7835,12 @@
       <c r="F264" s="3" t="n">
         <v>0.001051709027168985</v>
       </c>
+      <c r="G264" s="1" t="n">
+        <v>0.0005751</v>
+      </c>
+      <c r="H264" s="3" t="n">
+        <v>0.007004027315706702</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -6273,6 +7863,12 @@
       <c r="F265" s="3" t="n">
         <v>0.005347593582887715</v>
       </c>
+      <c r="G265" s="1" t="n">
+        <v>0.01506</v>
+      </c>
+      <c r="H265" s="3" t="n">
+        <v>0.001329787234042614</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -6295,6 +7891,12 @@
       <c r="F266" s="3" t="n">
         <v>0.001577287066246102</v>
       </c>
+      <c r="G266" s="1" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="H266" s="3" t="n">
+        <v>0.003149606299212689</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6317,6 +7919,12 @@
       <c r="F267" s="2" t="n">
         <v>-0.003033980582524359</v>
       </c>
+      <c r="G267" s="1" t="n">
+        <v>0.01643</v>
+      </c>
+      <c r="H267" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6339,6 +7947,12 @@
       <c r="F268" s="2" t="n">
         <v>-0.001406469760900175</v>
       </c>
+      <c r="G268" s="1" t="n">
+        <v>0.0004288</v>
+      </c>
+      <c r="H268" s="3" t="n">
+        <v>0.006572769953051676</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6361,6 +7975,12 @@
       <c r="F269" s="3" t="n">
         <v>0.002890173410404674</v>
       </c>
+      <c r="G269" s="1" t="n">
+        <v>0.02082</v>
+      </c>
+      <c r="H269" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6383,6 +8003,12 @@
       <c r="F270" s="2" t="n">
         <v>-0.001671309192200528</v>
       </c>
+      <c r="G270" s="1" t="n">
+        <v>0.1806</v>
+      </c>
+      <c r="H270" s="3" t="n">
+        <v>0.007812500000000069</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6405,6 +8031,12 @@
       <c r="F271" s="2" t="n">
         <v>-0.00272851296043664</v>
       </c>
+      <c r="G271" s="1" t="n">
+        <v>0.1467</v>
+      </c>
+      <c r="H271" s="3" t="n">
+        <v>0.003419972640218881</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6427,6 +8059,12 @@
       <c r="F272" s="3" t="n">
         <v>0.002282525995434943</v>
       </c>
+      <c r="G272" s="1" t="n">
+        <v>0.03963</v>
+      </c>
+      <c r="H272" s="3" t="n">
+        <v>0.002783400809716573</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6449,6 +8087,12 @@
       <c r="F273" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G273" s="1" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="H273" s="3" t="n">
+        <v>0.006479481641468688</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6471,6 +8115,12 @@
       <c r="F274" s="3" t="n">
         <v>0.001746863585834515</v>
       </c>
+      <c r="G274" s="1" t="n">
+        <v>63.24</v>
+      </c>
+      <c r="H274" s="3" t="n">
+        <v>0.002536461636017814</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -6493,6 +8143,12 @@
       <c r="F275" s="2" t="n">
         <v>-0.0008688097306689481</v>
       </c>
+      <c r="G275" s="1" t="n">
+        <v>0.01156</v>
+      </c>
+      <c r="H275" s="3" t="n">
+        <v>0.005217391304347915</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -6515,6 +8171,12 @@
       <c r="F276" s="3" t="n">
         <v>0.0007742934572202012</v>
       </c>
+      <c r="G276" s="1" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="H276" s="3" t="n">
+        <v>0.004642166344294008</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -6537,6 +8199,12 @@
       <c r="F277" s="3" t="n">
         <v>0.001197031362221724</v>
       </c>
+      <c r="G277" s="1" t="n">
+        <v>0.04208</v>
+      </c>
+      <c r="H277" s="3" t="n">
+        <v>0.006217120994739271</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -6559,6 +8227,12 @@
       <c r="F278" s="3" t="n">
         <v>0.007438894792773711</v>
       </c>
+      <c r="G278" s="1" t="n">
+        <v>0.01916</v>
+      </c>
+      <c r="H278" s="3" t="n">
+        <v>0.01054852320675099</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6581,6 +8255,12 @@
       <c r="F279" s="3" t="n">
         <v>0.00820695807314898</v>
       </c>
+      <c r="G279" s="1" t="n">
+        <v>0.005588</v>
+      </c>
+      <c r="H279" s="2" t="n">
+        <v>-0.01114846929746942</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6603,6 +8283,12 @@
       <c r="F280" s="3" t="n">
         <v>0.006087877183695104</v>
       </c>
+      <c r="G280" s="1" t="n">
+        <v>0.03824</v>
+      </c>
+      <c r="H280" s="3" t="n">
+        <v>0.006051039200210498</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6625,6 +8311,12 @@
       <c r="F281" s="2" t="n">
         <v>-0.002217294900221731</v>
       </c>
+      <c r="G281" s="1" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="H281" s="3" t="n">
+        <v>0.003333333333333336</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6647,6 +8339,12 @@
       <c r="F282" s="3" t="n">
         <v>0.003007518796992554</v>
       </c>
+      <c r="G282" s="1" t="n">
+        <v>0.0004018</v>
+      </c>
+      <c r="H282" s="3" t="n">
+        <v>0.003998000999500212</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6669,6 +8367,12 @@
       <c r="F283" s="2" t="n">
         <v>-0.01749999999999998</v>
       </c>
+      <c r="G283" s="1" t="n">
+        <v>0.03946</v>
+      </c>
+      <c r="H283" s="3" t="n">
+        <v>0.004071246819338433</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6691,6 +8395,12 @@
       <c r="F284" s="2" t="n">
         <v>-0.0002402113860197709</v>
       </c>
+      <c r="G284" s="1" t="n">
+        <v>0.04192</v>
+      </c>
+      <c r="H284" s="3" t="n">
+        <v>0.007208073041806864</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6713,6 +8423,12 @@
       <c r="F285" s="2" t="n">
         <v>-0.001023351009396213</v>
       </c>
+      <c r="G285" s="1" t="n">
+        <v>0.10717</v>
+      </c>
+      <c r="H285" s="2" t="n">
+        <v>-0.001955671447196888</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -6735,6 +8451,12 @@
       <c r="F286" s="2" t="n">
         <v>-0.002409638554216978</v>
       </c>
+      <c r="G286" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="H286" s="3" t="n">
+        <v>0.009661835748792296</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -6757,6 +8479,12 @@
       <c r="F287" s="3" t="n">
         <v>0.003577580495561234</v>
       </c>
+      <c r="G287" s="1" t="n">
+        <v>0.15145</v>
+      </c>
+      <c r="H287" s="2" t="n">
+        <v>-0.0001980459466596399</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -6779,6 +8507,12 @@
       <c r="F288" s="2" t="n">
         <v>-0.000547045951859896</v>
       </c>
+      <c r="G288" s="1" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="H288" s="2" t="n">
+        <v>-0.001642036124794717</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -6801,6 +8535,12 @@
       <c r="F289" s="3" t="n">
         <v>0.005118206190592227</v>
       </c>
+      <c r="G289" s="1" t="n">
+        <v>4.139</v>
+      </c>
+      <c r="H289" s="3" t="n">
+        <v>0.003637245392822641</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -6823,6 +8563,12 @@
       <c r="F290" s="3" t="n">
         <v>0.001535916824196494</v>
       </c>
+      <c r="G290" s="1" t="n">
+        <v>0.08520999999999999</v>
+      </c>
+      <c r="H290" s="3" t="n">
+        <v>0.00519051551256336</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -6845,6 +8591,12 @@
       <c r="F291" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G291" s="1" t="n">
+        <v>0.03537</v>
+      </c>
+      <c r="H291" s="3" t="n">
+        <v>0.00255102040816326</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -6867,6 +8619,12 @@
       <c r="F292" s="2" t="n">
         <v>-0.002518720217835287</v>
       </c>
+      <c r="G292" s="1" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="H292" s="2" t="n">
+        <v>-0.002252098546372811</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -6889,6 +8647,12 @@
       <c r="F293" s="3" t="n">
         <v>0.002060085836909847</v>
       </c>
+      <c r="G293" s="1" t="n">
+        <v>0.005875</v>
+      </c>
+      <c r="H293" s="3" t="n">
+        <v>0.00651019359259891</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -6911,6 +8675,12 @@
       <c r="F294" s="3" t="n">
         <v>0.0005825808330906687</v>
       </c>
+      <c r="G294" s="1" t="n">
+        <v>0.003436</v>
+      </c>
+      <c r="H294" s="3" t="n">
+        <v>0.0002911208151381948</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6933,6 +8703,12 @@
       <c r="F295" s="3" t="n">
         <v>0.001493373156617553</v>
       </c>
+      <c r="G295" s="1" t="n">
+        <v>0.5386</v>
+      </c>
+      <c r="H295" s="3" t="n">
+        <v>0.003914259086672863</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -6955,6 +8731,12 @@
       <c r="F296" s="3" t="n">
         <v>0.0004466279589103769</v>
       </c>
+      <c r="G296" s="1" t="n">
+        <v>2.249</v>
+      </c>
+      <c r="H296" s="3" t="n">
+        <v>0.004017857142857096</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -6977,6 +8759,12 @@
       <c r="F297" s="2" t="n">
         <v>-0.002941176470588319</v>
       </c>
+      <c r="G297" s="1" t="n">
+        <v>0.01699</v>
+      </c>
+      <c r="H297" s="3" t="n">
+        <v>0.002359882005899813</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6999,6 +8787,12 @@
       <c r="F298" s="3" t="n">
         <v>0.001654259718775819</v>
       </c>
+      <c r="G298" s="1" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="H298" s="2" t="n">
+        <v>-0.005505092210294527</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -7021,6 +8815,12 @@
       <c r="F299" s="3" t="n">
         <v>0.002717391304347872</v>
       </c>
+      <c r="G299" s="1" t="n">
+        <v>0.01111</v>
+      </c>
+      <c r="H299" s="3" t="n">
+        <v>0.003613369467028013</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -7043,6 +8843,12 @@
       <c r="F300" s="3" t="n">
         <v>0.0009661835748791877</v>
       </c>
+      <c r="G300" s="1" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="H300" s="3" t="n">
+        <v>0.003861003861003872</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -7065,6 +8871,12 @@
       <c r="F301" s="2" t="n">
         <v>-0.0003311258278145331</v>
       </c>
+      <c r="G301" s="1" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="H301" s="2" t="n">
+        <v>-0.000331235508446469</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -7087,6 +8899,12 @@
       <c r="F302" s="2" t="n">
         <v>-0.0007396449704142993</v>
       </c>
+      <c r="G302" s="1" t="n">
+        <v>0.01357</v>
+      </c>
+      <c r="H302" s="3" t="n">
+        <v>0.004441154700222134</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -7109,6 +8927,12 @@
       <c r="F303" s="2" t="n">
         <v>-0.001891891891891909</v>
       </c>
+      <c r="G303" s="1" t="n">
+        <v>0.07392</v>
+      </c>
+      <c r="H303" s="3" t="n">
+        <v>0.0008123476848091592</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -7131,6 +8955,12 @@
       <c r="F304" s="3" t="n">
         <v>0.001889168765743215</v>
       </c>
+      <c r="G304" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="H304" s="3" t="n">
+        <v>0.003771213073538719</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -7153,6 +8983,12 @@
       <c r="F305" s="3" t="n">
         <v>0.003068896731624856</v>
       </c>
+      <c r="G305" s="1" t="n">
+        <v>0.06519</v>
+      </c>
+      <c r="H305" s="2" t="n">
+        <v>-0.002753556677374937</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -7175,6 +9011,12 @@
       <c r="F306" s="3" t="n">
         <v>0.002806736166800345</v>
       </c>
+      <c r="G306" s="1" t="n">
+        <v>0.05031</v>
+      </c>
+      <c r="H306" s="3" t="n">
+        <v>0.00579768092762892</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -7197,6 +9039,12 @@
       <c r="F307" s="3" t="n">
         <v>0.003225806451612906</v>
       </c>
+      <c r="G307" s="1" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="H307" s="2" t="n">
+        <v>-0.00107181136120043</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -7219,6 +9067,12 @@
       <c r="F308" s="3" t="n">
         <v>0.008123889312008145</v>
       </c>
+      <c r="G308" s="1" t="n">
+        <v>0.03973</v>
+      </c>
+      <c r="H308" s="3" t="n">
+        <v>0.0005036514731805385</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -7241,6 +9095,12 @@
       <c r="F309" s="2" t="n">
         <v>-0.008771929824561264</v>
       </c>
+      <c r="G309" s="1" t="n">
+        <v>0.01599</v>
+      </c>
+      <c r="H309" s="3" t="n">
+        <v>0.01074589127686473</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -7263,6 +9123,12 @@
       <c r="F310" s="3" t="n">
         <v>0.0005558643690939828</v>
       </c>
+      <c r="G310" s="1" t="n">
+        <v>0.05425</v>
+      </c>
+      <c r="H310" s="3" t="n">
+        <v>0.004629629629629634</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -7285,6 +9151,12 @@
       <c r="F311" s="3" t="n">
         <v>0.00290632684998882</v>
       </c>
+      <c r="G311" s="1" t="n">
+        <v>0.004484</v>
+      </c>
+      <c r="H311" s="2" t="n">
+        <v>-0.0004458314757022437</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -7307,6 +9179,12 @@
       <c r="F312" s="3" t="n">
         <v>0.004050512270669443</v>
       </c>
+      <c r="G312" s="1" t="n">
+        <v>0.08449</v>
+      </c>
+      <c r="H312" s="3" t="n">
+        <v>0.00249169435215949</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -7329,6 +9207,12 @@
       <c r="F313" s="3" t="n">
         <v>0.003093060785368585</v>
       </c>
+      <c r="G313" s="1" t="n">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="H313" s="3" t="n">
+        <v>0.004156053090226449</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -7351,6 +9235,12 @@
       <c r="F314" s="3" t="n">
         <v>0.0006548788474131564</v>
       </c>
+      <c r="G314" s="1" t="n">
+        <v>0.1534</v>
+      </c>
+      <c r="H314" s="3" t="n">
+        <v>0.003926701570680741</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -7373,6 +9263,12 @@
       <c r="F315" s="2" t="n">
         <v>-0.001255492780916546</v>
       </c>
+      <c r="G315" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="H315" s="3" t="n">
+        <v>0.00502828409805151</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -7395,6 +9291,12 @@
       <c r="F316" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G316" s="1" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="H316" s="3" t="n">
+        <v>0.007234279354479664</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -7417,6 +9319,12 @@
       <c r="F317" s="3" t="n">
         <v>0.002396166134185391</v>
       </c>
+      <c r="G317" s="1" t="n">
+        <v>0.007562</v>
+      </c>
+      <c r="H317" s="3" t="n">
+        <v>0.004249667994687903</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -7439,6 +9347,12 @@
       <c r="F318" s="3" t="n">
         <v>0.0004003202562049477</v>
       </c>
+      <c r="G318" s="1" t="n">
+        <v>0.04981</v>
+      </c>
+      <c r="H318" s="2" t="n">
+        <v>-0.003401360544217618</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -7461,6 +9375,12 @@
       <c r="F319" s="3" t="n">
         <v>0.003528908533542421</v>
       </c>
+      <c r="G319" s="1" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="H319" s="2" t="n">
+        <v>-0.002948176038077638</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -7483,6 +9403,12 @@
       <c r="F320" s="2" t="n">
         <v>-0.0004565167769915042</v>
       </c>
+      <c r="G320" s="1" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="H320" s="3" t="n">
+        <v>0.004567252797442342</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -7505,6 +9431,12 @@
       <c r="F321" s="2" t="n">
         <v>-0.001044522783653357</v>
       </c>
+      <c r="G321" s="1" t="n">
+        <v>0.07770000000000001</v>
+      </c>
+      <c r="H321" s="3" t="n">
+        <v>0.01555352241537068</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7527,6 +9459,12 @@
       <c r="F322" s="3" t="n">
         <v>0.001234567901234603</v>
       </c>
+      <c r="G322" s="1" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="H322" s="3" t="n">
+        <v>0.005548705302096079</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -7549,6 +9487,12 @@
       <c r="F323" s="3" t="n">
         <v>0.003535353535353595</v>
       </c>
+      <c r="G323" s="1" t="n">
+        <v>1.996</v>
+      </c>
+      <c r="H323" s="3" t="n">
+        <v>0.004529441368897784</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -7571,6 +9515,12 @@
       <c r="F324" s="3" t="n">
         <v>0.005268344451182544</v>
       </c>
+      <c r="G324" s="1" t="n">
+        <v>0.053064</v>
+      </c>
+      <c r="H324" s="3" t="n">
+        <v>0.0003393281303019489</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7593,6 +9543,12 @@
       <c r="F325" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G325" s="1" t="n">
+        <v>0.15394</v>
+      </c>
+      <c r="H325" s="3" t="n">
+        <v>0.006670154329060902</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -7615,6 +9571,12 @@
       <c r="F326" s="2" t="n">
         <v>-0.006116207951070353</v>
       </c>
+      <c r="G326" s="1" t="n">
+        <v>0.006497</v>
+      </c>
+      <c r="H326" s="2" t="n">
+        <v>-0.0004615384615383894</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -7637,6 +9599,12 @@
       <c r="F327" s="2" t="n">
         <v>-0.003905991393578287</v>
       </c>
+      <c r="G327" s="1" t="n">
+        <v>0.015069</v>
+      </c>
+      <c r="H327" s="3" t="n">
+        <v>0.0015286454871727</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -7659,6 +9627,12 @@
       <c r="F328" s="3" t="n">
         <v>0.001066098081023485</v>
       </c>
+      <c r="G328" s="1" t="n">
+        <v>0.09429999999999999</v>
+      </c>
+      <c r="H328" s="3" t="n">
+        <v>0.004259850905218292</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -7681,6 +9655,12 @@
       <c r="F329" s="3" t="n">
         <v>0.003195617438940711</v>
       </c>
+      <c r="G329" s="1" t="n">
+        <v>0.004416</v>
+      </c>
+      <c r="H329" s="3" t="n">
+        <v>0.004778156996587074</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -7703,6 +9683,12 @@
       <c r="F330" s="2" t="n">
         <v>-0.001948558067030318</v>
       </c>
+      <c r="G330" s="1" t="n">
+        <v>0.05105</v>
+      </c>
+      <c r="H330" s="2" t="n">
+        <v>-0.003319016009371407</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -7725,6 +9711,12 @@
       <c r="F331" s="3" t="n">
         <v>0.002209334438000654</v>
       </c>
+      <c r="G331" s="1" t="n">
+        <v>0.03656</v>
+      </c>
+      <c r="H331" s="3" t="n">
+        <v>0.007440066133921173</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -7747,6 +9739,12 @@
       <c r="F332" s="3" t="n">
         <v>0.003399048266485387</v>
       </c>
+      <c r="G332" s="1" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="H332" s="3" t="n">
+        <v>0.000677506775067676</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -7769,6 +9767,12 @@
       <c r="F333" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G333" s="1" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="H333" s="3" t="n">
+        <v>0.007299270072992766</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -7791,6 +9795,12 @@
       <c r="F334" s="3" t="n">
         <v>0.01529193697868399</v>
       </c>
+      <c r="G334" s="1" t="n">
+        <v>0.04364</v>
+      </c>
+      <c r="H334" s="2" t="n">
+        <v>-0.004107713372889083</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -7813,6 +9823,12 @@
       <c r="F335" s="3" t="n">
         <v>0.001606524962926239</v>
       </c>
+      <c r="G335" s="1" t="n">
+        <v>0.08136</v>
+      </c>
+      <c r="H335" s="3" t="n">
+        <v>0.003824799506477541</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -7835,6 +9851,12 @@
       <c r="F336" s="3" t="n">
         <v>0.00147492625368729</v>
       </c>
+      <c r="G336" s="1" t="n">
+        <v>0.2051</v>
+      </c>
+      <c r="H336" s="3" t="n">
+        <v>0.006872852233677037</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -7857,6 +9879,12 @@
       <c r="F337" s="3" t="n">
         <v>0.008866995073891777</v>
       </c>
+      <c r="G337" s="1" t="n">
+        <v>0.01017</v>
+      </c>
+      <c r="H337" s="2" t="n">
+        <v>-0.00683593750000006</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -7879,6 +9907,12 @@
       <c r="F338" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G338" s="1" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="H338" s="3" t="n">
+        <v>0.005323868677905974</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -7901,6 +9935,12 @@
       <c r="F339" s="2" t="n">
         <v>-0.002729257641921286</v>
       </c>
+      <c r="G339" s="1" t="n">
+        <v>0.01834</v>
+      </c>
+      <c r="H339" s="3" t="n">
+        <v>0.003831417624520916</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -7923,6 +9963,12 @@
       <c r="F340" s="2" t="n">
         <v>-0.003680852555563329</v>
       </c>
+      <c r="G340" s="1" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="H340" s="3" t="n">
+        <v>0.002955561028816746</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -7945,6 +9991,12 @@
       <c r="F341" s="2" t="n">
         <v>-0.01560379918588881</v>
       </c>
+      <c r="G341" s="1" t="n">
+        <v>0.04382</v>
+      </c>
+      <c r="H341" s="3" t="n">
+        <v>0.006662072134160317</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -7967,6 +10019,12 @@
       <c r="F342" s="2" t="n">
         <v>-0.002549069589599869</v>
       </c>
+      <c r="G342" s="1" t="n">
+        <v>0.07821</v>
+      </c>
+      <c r="H342" s="2" t="n">
+        <v>-0.0006388959877331267</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -7989,6 +10047,12 @@
       <c r="F343" s="3" t="n">
         <v>0.0002626050420168944</v>
       </c>
+      <c r="G343" s="1" t="n">
+        <v>7.639</v>
+      </c>
+      <c r="H343" s="3" t="n">
+        <v>0.002756629036492506</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -8011,6 +10075,12 @@
       <c r="F344" s="2" t="n">
         <v>-0.0006648936170213879</v>
       </c>
+      <c r="G344" s="1" t="n">
+        <v>0.6052999999999999</v>
+      </c>
+      <c r="H344" s="3" t="n">
+        <v>0.006819693945442437</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -8033,6 +10103,12 @@
       <c r="F345" s="3" t="n">
         <v>0.002176278563656059</v>
       </c>
+      <c r="G345" s="1" t="n">
+        <v>0.03716</v>
+      </c>
+      <c r="H345" s="3" t="n">
+        <v>0.008686210640608058</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -8055,6 +10131,12 @@
       <c r="F346" s="2" t="n">
         <v>-0.002433090024330801</v>
       </c>
+      <c r="G346" s="1" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="H346" s="3" t="n">
+        <v>0.009756097560975551</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -8077,6 +10159,12 @@
       <c r="F347" s="3" t="n">
         <v>0.002314814814814721</v>
       </c>
+      <c r="G347" s="1" t="n">
+        <v>0.1737</v>
+      </c>
+      <c r="H347" s="3" t="n">
+        <v>0.002886836027713629</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -8099,6 +10187,12 @@
       <c r="F348" s="2" t="n">
         <v>-0.001213732516472119</v>
       </c>
+      <c r="G348" s="1" t="n">
+        <v>5180.3</v>
+      </c>
+      <c r="H348" s="2" t="n">
+        <v>-0.0007715602877919873</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -8121,6 +10215,12 @@
       <c r="F349" s="3" t="n">
         <v>0.002982848620432521</v>
       </c>
+      <c r="G349" s="1" t="n">
+        <v>0.01351</v>
+      </c>
+      <c r="H349" s="3" t="n">
+        <v>0.004460966542750877</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -8143,6 +10243,12 @@
       <c r="F350" s="3" t="n">
         <v>0.002686366689053063</v>
       </c>
+      <c r="G350" s="1" t="n">
+        <v>0.01504</v>
+      </c>
+      <c r="H350" s="3" t="n">
+        <v>0.00736771600803744</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -8165,6 +10271,12 @@
       <c r="F351" s="3" t="n">
         <v>0.00232480903354373</v>
       </c>
+      <c r="G351" s="1" t="n">
+        <v>0.0006089999999999999</v>
+      </c>
+      <c r="H351" s="3" t="n">
+        <v>0.008946322067594291</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -8187,6 +10299,12 @@
       <c r="F352" s="3" t="n">
         <v>0.002036659877800324</v>
       </c>
+      <c r="G352" s="1" t="n">
+        <v>0.01975</v>
+      </c>
+      <c r="H352" s="3" t="n">
+        <v>0.003556910569105723</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -8209,6 +10327,12 @@
       <c r="F353" s="2" t="n">
         <v>-0.001387702818104239</v>
       </c>
+      <c r="G353" s="1" t="n">
+        <v>0.09432</v>
+      </c>
+      <c r="H353" s="3" t="n">
+        <v>0.008230892570817818</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -8231,6 +10355,12 @@
       <c r="F354" s="3" t="n">
         <v>0.003318584070796556</v>
       </c>
+      <c r="G354" s="1" t="n">
+        <v>0.09130000000000001</v>
+      </c>
+      <c r="H354" s="3" t="n">
+        <v>0.006615214994487357</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -8253,6 +10383,12 @@
       <c r="F355" s="3" t="n">
         <v>0.000833750208437482</v>
       </c>
+      <c r="G355" s="1" t="n">
+        <v>0.0006053</v>
+      </c>
+      <c r="H355" s="3" t="n">
+        <v>0.008497167610796517</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -8275,6 +10411,12 @@
       <c r="F356" s="3" t="n">
         <v>0.001924001924001926</v>
       </c>
+      <c r="G356" s="1" t="n">
+        <v>2.091</v>
+      </c>
+      <c r="H356" s="3" t="n">
+        <v>0.003840614498319734</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -8297,6 +10439,12 @@
       <c r="F357" s="2" t="n">
         <v>-0.009425878320479777</v>
       </c>
+      <c r="G357" s="1" t="n">
+        <v>0.02306</v>
+      </c>
+      <c r="H357" s="2" t="n">
+        <v>-0.002595155709342605</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -8319,6 +10467,12 @@
       <c r="F358" s="3" t="n">
         <v>0.004938271604938392</v>
       </c>
+      <c r="G358" s="1" t="n">
+        <v>0.000406</v>
+      </c>
+      <c r="H358" s="2" t="n">
+        <v>-0.002457002457002516</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -8341,6 +10495,12 @@
       <c r="F359" s="2" t="n">
         <v>-0.0006863417982154833</v>
       </c>
+      <c r="G359" s="1" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="H359" s="3" t="n">
+        <v>0.009615384615384581</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -8363,6 +10523,12 @@
       <c r="F360" s="3" t="n">
         <v>0.003558718861209922</v>
       </c>
+      <c r="G360" s="1" t="n">
+        <v>0.003389</v>
+      </c>
+      <c r="H360" s="3" t="n">
+        <v>0.00147754137115846</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -8385,6 +10551,12 @@
       <c r="F361" s="2" t="n">
         <v>-0.0006208288064565512</v>
       </c>
+      <c r="G361" s="1" t="n">
+        <v>0.6411</v>
+      </c>
+      <c r="H361" s="2" t="n">
+        <v>-0.004348501320080796</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -8407,6 +10579,12 @@
       <c r="F362" s="2" t="n">
         <v>-0.003847798204360829</v>
       </c>
+      <c r="G362" s="1" t="n">
+        <v>0.02345</v>
+      </c>
+      <c r="H362" s="3" t="n">
+        <v>0.006437768240343234</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -8429,6 +10607,12 @@
       <c r="F363" s="2" t="n">
         <v>-0.001375726077652197</v>
       </c>
+      <c r="G363" s="1" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="H363" s="3" t="n">
+        <v>0.002602173580284762</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -8451,6 +10635,12 @@
       <c r="F364" s="3" t="n">
         <v>0.002764780944279009</v>
       </c>
+      <c r="G364" s="1" t="n">
+        <v>4.713</v>
+      </c>
+      <c r="H364" s="2" t="n">
+        <v>-0.0004241781548249798</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -8473,6 +10663,12 @@
       <c r="F365" s="2" t="n">
         <v>-0.001264044943820124</v>
       </c>
+      <c r="G365" s="1" t="n">
+        <v>0.07073</v>
+      </c>
+      <c r="H365" s="2" t="n">
+        <v>-0.005343833497398471</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -8495,6 +10691,12 @@
       <c r="F366" s="3" t="n">
         <v>0.00218499635833944</v>
       </c>
+      <c r="G366" s="1" t="n">
+        <v>0.05539</v>
+      </c>
+      <c r="H366" s="3" t="n">
+        <v>0.006359011627907033</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -8517,6 +10719,12 @@
       <c r="F367" s="3" t="n">
         <v>0.001026869758685565</v>
       </c>
+      <c r="G367" s="1" t="n">
+        <v>0.05868</v>
+      </c>
+      <c r="H367" s="3" t="n">
+        <v>0.003248418533082624</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -8539,6 +10747,12 @@
       <c r="F368" s="3" t="n">
         <v>0.002293577981651344</v>
       </c>
+      <c r="G368" s="1" t="n">
+        <v>0.0571</v>
+      </c>
+      <c r="H368" s="3" t="n">
+        <v>0.005104735081851762</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -8561,6 +10775,12 @@
       <c r="F369" s="3" t="n">
         <v>0.0009743423189346793</v>
       </c>
+      <c r="G369" s="1" t="n">
+        <v>0.03105</v>
+      </c>
+      <c r="H369" s="3" t="n">
+        <v>0.007462686567164213</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -8583,6 +10803,12 @@
       <c r="F370" s="2" t="n">
         <v>-0.0006169031462060606</v>
       </c>
+      <c r="G370" s="1" t="n">
+        <v>0.0001629</v>
+      </c>
+      <c r="H370" s="3" t="n">
+        <v>0.005555555555555523</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -8605,6 +10831,12 @@
       <c r="F371" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G371" s="1" t="n">
+        <v>0.006795</v>
+      </c>
+      <c r="H371" s="3" t="n">
+        <v>0.003692762186115192</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -8627,6 +10859,12 @@
       <c r="F372" s="2" t="n">
         <v>-0.003175519630485034</v>
       </c>
+      <c r="G372" s="1" t="n">
+        <v>0.006886</v>
+      </c>
+      <c r="H372" s="2" t="n">
+        <v>-0.002896032435563286</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -8649,6 +10887,12 @@
       <c r="F373" s="2" t="n">
         <v>-0.002372791985236051</v>
       </c>
+      <c r="G373" s="1" t="n">
+        <v>3.808</v>
+      </c>
+      <c r="H373" s="3" t="n">
+        <v>0.006342494714587744</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -8671,6 +10915,12 @@
       <c r="F374" s="3" t="n">
         <v>0.004121074321443777</v>
       </c>
+      <c r="G374" s="1" t="n">
+        <v>0.07093000000000001</v>
+      </c>
+      <c r="H374" s="3" t="n">
+        <v>0.003821115199547217</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -8693,6 +10943,12 @@
       <c r="F375" s="2" t="n">
         <v>-0.000774793388429631</v>
       </c>
+      <c r="G375" s="1" t="n">
+        <v>0.0781</v>
+      </c>
+      <c r="H375" s="3" t="n">
+        <v>0.009304729904368033</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -8715,6 +10971,12 @@
       <c r="F376" s="2" t="n">
         <v>-0.003179144810045968</v>
       </c>
+      <c r="G376" s="1" t="n">
+        <v>0.06282</v>
+      </c>
+      <c r="H376" s="3" t="n">
+        <v>0.001754106203157375</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -8737,6 +10999,12 @@
       <c r="F377" s="3" t="n">
         <v>0.003026714041321149</v>
       </c>
+      <c r="G377" s="1" t="n">
+        <v>0.07652</v>
+      </c>
+      <c r="H377" s="3" t="n">
+        <v>0.00393597480976133</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -8759,6 +11027,12 @@
       <c r="F378" s="2" t="n">
         <v>-0.003952569169960437</v>
       </c>
+      <c r="G378" s="1" t="n">
+        <v>0.0004032</v>
+      </c>
+      <c r="H378" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -8781,6 +11055,12 @@
       <c r="F379" s="2" t="n">
         <v>-0.003493215101437543</v>
       </c>
+      <c r="G379" s="1" t="n">
+        <v>0.07444000000000001</v>
+      </c>
+      <c r="H379" s="3" t="n">
+        <v>0.003640285829850429</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -8803,6 +11083,12 @@
       <c r="F380" s="2" t="n">
         <v>-0.001474926253687351</v>
       </c>
+      <c r="G380" s="1" t="n">
+        <v>0.001352</v>
+      </c>
+      <c r="H380" s="2" t="n">
+        <v>-0.001477104874446122</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -8825,6 +11111,12 @@
       <c r="F381" s="2" t="n">
         <v>-0.004920049200491873</v>
       </c>
+      <c r="G381" s="1" t="n">
+        <v>6.502</v>
+      </c>
+      <c r="H381" s="3" t="n">
+        <v>0.004635352286773696</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -8847,6 +11139,12 @@
       <c r="F382" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G382" s="1" t="n">
+        <v>0.01333</v>
+      </c>
+      <c r="H382" s="3" t="n">
+        <v>0.004521477015825116</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -8869,6 +11167,12 @@
       <c r="F383" s="3" t="n">
         <v>0.002284408909194653</v>
       </c>
+      <c r="G383" s="1" t="n">
+        <v>0.01765</v>
+      </c>
+      <c r="H383" s="3" t="n">
+        <v>0.005698005698005664</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -8891,6 +11195,12 @@
       <c r="F384" s="2" t="n">
         <v>-0.00196078431372541</v>
       </c>
+      <c r="G384" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="H384" s="3" t="n">
+        <v>0.001964636542239606</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -8913,6 +11223,12 @@
       <c r="F385" s="3" t="n">
         <v>0.002240645305848036</v>
       </c>
+      <c r="G385" s="1" t="n">
+        <v>4.499</v>
+      </c>
+      <c r="H385" s="3" t="n">
+        <v>0.005812653699977599</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -8935,6 +11251,12 @@
       <c r="F386" s="2" t="n">
         <v>-0.001552795031055938</v>
       </c>
+      <c r="G386" s="1" t="n">
+        <v>0.00129</v>
+      </c>
+      <c r="H386" s="3" t="n">
+        <v>0.00311041990668731</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -8957,6 +11279,12 @@
       <c r="F387" s="2" t="n">
         <v>-0.0003393281303020103</v>
       </c>
+      <c r="G387" s="1" t="n">
+        <v>0.0005913</v>
+      </c>
+      <c r="H387" s="3" t="n">
+        <v>0.003564154786150707</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -8979,6 +11307,12 @@
       <c r="F388" s="2" t="n">
         <v>-0.001774622892635397</v>
       </c>
+      <c r="G388" s="1" t="n">
+        <v>0.01131</v>
+      </c>
+      <c r="H388" s="3" t="n">
+        <v>0.005333333333333424</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -9001,6 +11335,12 @@
       <c r="F389" s="3" t="n">
         <v>0.001098901098901054</v>
       </c>
+      <c r="G389" s="1" t="n">
+        <v>0.00912</v>
+      </c>
+      <c r="H389" s="3" t="n">
+        <v>0.001097694840834203</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -9023,6 +11363,12 @@
       <c r="F390" s="3" t="n">
         <v>0.003318866479448511</v>
       </c>
+      <c r="G390" s="1" t="n">
+        <v>0.07908999999999999</v>
+      </c>
+      <c r="H390" s="3" t="n">
+        <v>0.006234096692111837</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -9045,6 +11391,12 @@
       <c r="F391" s="2" t="n">
         <v>-0.0005898545025560803</v>
       </c>
+      <c r="G391" s="1" t="n">
+        <v>0.05129</v>
+      </c>
+      <c r="H391" s="3" t="n">
+        <v>0.009049773755656149</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -9067,6 +11419,12 @@
       <c r="F392" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G392" s="1" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="H392" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -9089,6 +11447,12 @@
       <c r="F393" s="2" t="n">
         <v>-0.01263453439401027</v>
       </c>
+      <c r="G393" s="1" t="n">
+        <v>0.02116</v>
+      </c>
+      <c r="H393" s="3" t="n">
+        <v>0.002843601895734646</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -9111,6 +11475,12 @@
       <c r="F394" s="2" t="n">
         <v>-0.002914035939776539</v>
       </c>
+      <c r="G394" s="1" t="n">
+        <v>0.2067</v>
+      </c>
+      <c r="H394" s="3" t="n">
+        <v>0.006819288845591741</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -9133,6 +11503,12 @@
       <c r="F395" s="3" t="n">
         <v>0.002066115702479398</v>
       </c>
+      <c r="G395" s="1" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="H395" s="3" t="n">
+        <v>0.006185567010309312</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -9155,6 +11531,12 @@
       <c r="F396" s="2" t="n">
         <v>-0.000370782350760063</v>
       </c>
+      <c r="G396" s="1" t="n">
+        <v>2.719</v>
+      </c>
+      <c r="H396" s="3" t="n">
+        <v>0.008531157270029557</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -9177,6 +11559,12 @@
       <c r="F397" s="3" t="n">
         <v>0.001583531274742678</v>
       </c>
+      <c r="G397" s="1" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="H397" s="2" t="n">
+        <v>-0.0007905138339920079</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -9199,6 +11587,12 @@
       <c r="F398" s="2" t="n">
         <v>-0.003308975596304938</v>
       </c>
+      <c r="G398" s="1" t="n">
+        <v>0.007314</v>
+      </c>
+      <c r="H398" s="3" t="n">
+        <v>0.0117581961543782</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -9221,6 +11615,12 @@
       <c r="F399" s="3" t="n">
         <v>0.0007722007722006871</v>
       </c>
+      <c r="G399" s="1" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H399" s="3" t="n">
+        <v>0.003086419753086508</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -9243,6 +11643,12 @@
       <c r="F400" s="3" t="n">
         <v>0.0003146633102579892</v>
       </c>
+      <c r="G400" s="1" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="H400" s="3" t="n">
+        <v>0.001572821642025796</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -9265,6 +11671,12 @@
       <c r="F401" s="3" t="n">
         <v>0.04237288135593219</v>
       </c>
+      <c r="G401" s="1" t="n">
+        <v>0.007417</v>
+      </c>
+      <c r="H401" s="3" t="n">
+        <v>0.005013550135501315</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -9287,6 +11699,12 @@
       <c r="F402" s="3" t="n">
         <v>0.0002195389681668788</v>
       </c>
+      <c r="G402" s="1" t="n">
+        <v>0.004575</v>
+      </c>
+      <c r="H402" s="3" t="n">
+        <v>0.004170324846356435</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -9309,6 +11727,12 @@
       <c r="F403" s="3" t="n">
         <v>0.00341555977229606</v>
       </c>
+      <c r="G403" s="1" t="n">
+        <v>0.2644</v>
+      </c>
+      <c r="H403" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -9331,6 +11755,12 @@
       <c r="F404" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G404" s="1" t="n">
+        <v>0.2398</v>
+      </c>
+      <c r="H404" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -9353,6 +11783,12 @@
       <c r="F405" s="2" t="n">
         <v>-0.001149029070435385</v>
       </c>
+      <c r="G405" s="1" t="n">
+        <v>0.0008721</v>
+      </c>
+      <c r="H405" s="3" t="n">
+        <v>0.003220982399631841</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -9375,6 +11811,12 @@
       <c r="F406" s="3" t="n">
         <v>0.001965408805031537</v>
       </c>
+      <c r="G406" s="1" t="n">
+        <v>0.005103</v>
+      </c>
+      <c r="H406" s="3" t="n">
+        <v>0.0009807767752059232</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -9397,6 +11839,12 @@
       <c r="F407" s="3" t="n">
         <v>0.002481389578163814</v>
       </c>
+      <c r="G407" s="1" t="n">
+        <v>0.01214</v>
+      </c>
+      <c r="H407" s="3" t="n">
+        <v>0.001650165016501583</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -9419,6 +11867,12 @@
       <c r="F408" s="2" t="n">
         <v>-0.008947006194081205</v>
       </c>
+      <c r="G408" s="1" t="n">
+        <v>0.001442</v>
+      </c>
+      <c r="H408" s="3" t="n">
+        <v>0.001388888888888772</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -9441,6 +11895,12 @@
       <c r="F409" s="3" t="n">
         <v>0.003304874690167863</v>
       </c>
+      <c r="G409" s="1" t="n">
+        <v>0.03705</v>
+      </c>
+      <c r="H409" s="3" t="n">
+        <v>0.01701894043370855</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -9463,6 +11923,12 @@
       <c r="F410" s="3" t="n">
         <v>0.003075030750307591</v>
       </c>
+      <c r="G410" s="1" t="n">
+        <v>0.01637</v>
+      </c>
+      <c r="H410" s="3" t="n">
+        <v>0.003678724708767477</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -9485,6 +11951,12 @@
       <c r="F411" s="3" t="n">
         <v>0.005756148613291563</v>
       </c>
+      <c r="G411" s="1" t="n">
+        <v>0.1913</v>
+      </c>
+      <c r="H411" s="2" t="n">
+        <v>-0.004682622268470405</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -9507,6 +11979,12 @@
       <c r="F412" s="2" t="n">
         <v>-0.001033515428908912</v>
       </c>
+      <c r="G412" s="1" t="n">
+        <v>0.06722</v>
+      </c>
+      <c r="H412" s="2" t="n">
+        <v>-0.00650310375406438</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -9529,6 +12007,12 @@
       <c r="F413" s="3" t="n">
         <v>0.00317208564631245</v>
       </c>
+      <c r="G413" s="1" t="n">
+        <v>2544</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0.005533596837944664</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -9551,6 +12035,12 @@
       <c r="F414" s="3" t="n">
         <v>0.003276161110040538</v>
       </c>
+      <c r="G414" s="1" t="n">
+        <v>0.05219</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>0.002497118709181678</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -9573,6 +12063,12 @@
       <c r="F415" s="2" t="n">
         <v>-0.0108571428571428</v>
       </c>
+      <c r="G415" s="1" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>-0.004043905257076902</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -9595,6 +12091,12 @@
       <c r="F416" s="3" t="n">
         <v>0.001022196261682252</v>
       </c>
+      <c r="G416" s="1" t="n">
+        <v>0.06906</v>
+      </c>
+      <c r="H416" s="3" t="n">
+        <v>0.007439824945295354</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -9617,6 +12119,12 @@
       <c r="F417" s="3" t="n">
         <v>0.01351351351351353</v>
       </c>
+      <c r="G417" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H417" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -9639,6 +12147,12 @@
       <c r="F418" s="3" t="n">
         <v>0.002617801047120494</v>
       </c>
+      <c r="G418" s="1" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="H418" s="3" t="n">
+        <v>0.003916449086161811</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -9661,6 +12175,12 @@
       <c r="F419" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G419" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="H419" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -9683,6 +12203,12 @@
       <c r="F420" s="3" t="n">
         <v>0.001571503404924162</v>
       </c>
+      <c r="G420" s="1" t="n">
+        <v>0.01923</v>
+      </c>
+      <c r="H420" s="3" t="n">
+        <v>0.005753138075313754</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -9705,6 +12231,12 @@
       <c r="F421" s="3" t="n">
         <v>0.004680187207488361</v>
       </c>
+      <c r="G421" s="1" t="n">
+        <v>0.19426</v>
+      </c>
+      <c r="H421" s="3" t="n">
+        <v>0.005486542443064066</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -9727,6 +12259,12 @@
       <c r="F422" s="2" t="n">
         <v>-0.006982833866744171</v>
       </c>
+      <c r="G422" s="1" t="n">
+        <v>0.03421</v>
+      </c>
+      <c r="H422" s="3" t="n">
+        <v>0.002343978904189767</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -9749,6 +12287,12 @@
       <c r="F423" s="3" t="n">
         <v>0.001407459535538394</v>
       </c>
+      <c r="G423" s="1" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="H423" s="3" t="n">
+        <v>0.001405481377371595</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -9771,6 +12315,12 @@
       <c r="F424" s="3" t="n">
         <v>0.007619047619047639</v>
       </c>
+      <c r="G424" s="1" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="H424" s="3" t="n">
+        <v>0.001890359168241889</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -9793,6 +12343,12 @@
       <c r="F425" s="3" t="n">
         <v>0.002868068833651957</v>
       </c>
+      <c r="G425" s="1" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="H425" s="3" t="n">
+        <v>0.003813155386082092</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -9815,6 +12371,12 @@
       <c r="F426" s="2" t="n">
         <v>-0.005220826866092927</v>
       </c>
+      <c r="G426" s="1" t="n">
+        <v>0.007073</v>
+      </c>
+      <c r="H426" s="3" t="n">
+        <v>0.003262411347517795</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -9837,6 +12399,12 @@
       <c r="F427" s="2" t="n">
         <v>-0.004665629860031049</v>
       </c>
+      <c r="G427" s="1" t="n">
+        <v>0.02565</v>
+      </c>
+      <c r="H427" s="3" t="n">
+        <v>0.00195312499999992</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -9859,6 +12427,12 @@
       <c r="F428" s="3" t="n">
         <v>0.0001237623762375328</v>
       </c>
+      <c r="G428" s="1" t="n">
+        <v>0.008121</v>
+      </c>
+      <c r="H428" s="3" t="n">
+        <v>0.004949882440292056</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -9881,6 +12455,12 @@
       <c r="F429" s="3" t="n">
         <v>0.007401315789473667</v>
       </c>
+      <c r="G429" s="1" t="n">
+        <v>0.01227</v>
+      </c>
+      <c r="H429" s="3" t="n">
+        <v>0.001632653061224423</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -9903,6 +12483,12 @@
       <c r="F430" s="3" t="n">
         <v>0.00134791073835565</v>
       </c>
+      <c r="G430" s="1" t="n">
+        <v>0.06708</v>
+      </c>
+      <c r="H430" s="3" t="n">
+        <v>0.003290457672748997</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -9925,6 +12511,12 @@
       <c r="F431" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G431" s="1" t="n">
+        <v>0.00543</v>
+      </c>
+      <c r="H431" s="3" t="n">
+        <v>0.001845018450184427</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -9947,6 +12539,12 @@
       <c r="F432" s="3" t="n">
         <v>0.003146633102580111</v>
       </c>
+      <c r="G432" s="1" t="n">
+        <v>0.009613</v>
+      </c>
+      <c r="H432" s="3" t="n">
+        <v>0.005123379339188669</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -9969,6 +12567,12 @@
       <c r="F433" s="3" t="n">
         <v>0.003150751333010303</v>
       </c>
+      <c r="G433" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="H433" s="3" t="n">
+        <v>0.005073689296931503</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -9991,6 +12595,12 @@
       <c r="F434" s="3" t="n">
         <v>0.003835091083413241</v>
       </c>
+      <c r="G434" s="1" t="n">
+        <v>0.0419</v>
+      </c>
+      <c r="H434" s="3" t="n">
+        <v>0.0004775549188156443</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -10013,6 +12623,12 @@
       <c r="F435" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G435" s="1" t="n">
+        <v>0.001539</v>
+      </c>
+      <c r="H435" s="3" t="n">
+        <v>0.005882352941176543</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -10035,6 +12651,12 @@
       <c r="F436" s="3" t="n">
         <v>0.003283473184968982</v>
       </c>
+      <c r="G436" s="1" t="n">
+        <v>0.02761</v>
+      </c>
+      <c r="H436" s="3" t="n">
+        <v>0.003999999999999963</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -10057,6 +12679,12 @@
       <c r="F437" s="3" t="n">
         <v>0.008205623265355377</v>
       </c>
+      <c r="G437" s="1" t="n">
+        <v>0.08266999999999999</v>
+      </c>
+      <c r="H437" s="2" t="n">
+        <v>-0.01053261520047882</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -10079,6 +12707,12 @@
       <c r="F438" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G438" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="H438" s="3" t="n">
+        <v>0.002615518744551078</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -10101,6 +12735,12 @@
       <c r="F439" s="2" t="n">
         <v>-0.0006485084306096704</v>
       </c>
+      <c r="G439" s="1" t="n">
+        <v>1.547</v>
+      </c>
+      <c r="H439" s="3" t="n">
+        <v>0.003893575600259575</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -10123,6 +12763,12 @@
       <c r="F440" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G440" s="1" t="n">
+        <v>0.001792</v>
+      </c>
+      <c r="H440" s="3" t="n">
+        <v>0.003921568627451015</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -10145,6 +12791,12 @@
       <c r="F441" s="2" t="n">
         <v>-0.001086071137659472</v>
       </c>
+      <c r="G441" s="1" t="n">
+        <v>0.03693</v>
+      </c>
+      <c r="H441" s="3" t="n">
+        <v>0.003805381897254533</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -10167,6 +12819,12 @@
       <c r="F442" s="2" t="n">
         <v>-0.00108577633007596</v>
       </c>
+      <c r="G442" s="1" t="n">
+        <v>0.01848</v>
+      </c>
+      <c r="H442" s="3" t="n">
+        <v>0.004347826086956533</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -10189,6 +12847,12 @@
       <c r="F443" s="3" t="n">
         <v>0.0007846829880727322</v>
       </c>
+      <c r="G443" s="1" t="n">
+        <v>0.12786</v>
+      </c>
+      <c r="H443" s="3" t="n">
+        <v>0.002509016779049826</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -10211,6 +12875,12 @@
       <c r="F444" s="3" t="n">
         <v>0.002418921340261534</v>
       </c>
+      <c r="G444" s="1" t="n">
+        <v>0.011165</v>
+      </c>
+      <c r="H444" s="2" t="n">
+        <v>-0.002144963803735787</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -10233,6 +12903,12 @@
       <c r="F445" s="3" t="n">
         <v>0.00149831439630427</v>
       </c>
+      <c r="G445" s="1" t="n">
+        <v>0.08073</v>
+      </c>
+      <c r="H445" s="3" t="n">
+        <v>0.006482982171798936</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -10255,6 +12931,12 @@
       <c r="F446" s="3" t="n">
         <v>0.006208213944603651</v>
       </c>
+      <c r="G446" s="1" t="n">
+        <v>0.0002123</v>
+      </c>
+      <c r="H446" s="3" t="n">
+        <v>0.007593735168486055</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -10277,6 +12959,12 @@
       <c r="F447" s="3" t="n">
         <v>0.003081664098613259</v>
       </c>
+      <c r="G447" s="1" t="n">
+        <v>0.00652</v>
+      </c>
+      <c r="H447" s="3" t="n">
+        <v>0.001536098310291796</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -10299,6 +12987,12 @@
       <c r="F448" s="3" t="n">
         <v>0.004137434790429952</v>
       </c>
+      <c r="G448" s="1" t="n">
+        <v>0.11187</v>
+      </c>
+      <c r="H448" s="3" t="n">
+        <v>0.002060193479039718</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -10321,6 +13015,12 @@
       <c r="F449" s="2" t="n">
         <v>-0.001776198934280618</v>
       </c>
+      <c r="G449" s="1" t="n">
+        <v>0.001689</v>
+      </c>
+      <c r="H449" s="3" t="n">
+        <v>0.001779359430604961</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -10343,6 +13043,12 @@
       <c r="F450" s="3" t="n">
         <v>0.001455604075691447</v>
       </c>
+      <c r="G450" s="1" t="n">
+        <v>0.000207</v>
+      </c>
+      <c r="H450" s="3" t="n">
+        <v>0.002906976744185986</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -10365,6 +13071,12 @@
       <c r="F451" s="3" t="n">
         <v>0.005325218714340075</v>
       </c>
+      <c r="G451" s="1" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="H451" s="3" t="n">
+        <v>0.003783579265985676</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -10387,6 +13099,12 @@
       <c r="F452" s="3" t="n">
         <v>0.001501501501501336</v>
       </c>
+      <c r="G452" s="1" t="n">
+        <v>0.1338</v>
+      </c>
+      <c r="H452" s="3" t="n">
+        <v>0.002998500749625274</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -10409,6 +13127,12 @@
       <c r="F453" s="3" t="n">
         <v>0.00114942528735635</v>
       </c>
+      <c r="G453" s="1" t="n">
+        <v>0.0001747</v>
+      </c>
+      <c r="H453" s="3" t="n">
+        <v>0.002870264064293829</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -10431,6 +13155,12 @@
       <c r="F454" s="3" t="n">
         <v>0.0009166743056191125</v>
       </c>
+      <c r="G454" s="1" t="n">
+        <v>0.10999</v>
+      </c>
+      <c r="H454" s="3" t="n">
+        <v>0.007326678267240673</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -10453,6 +13183,12 @@
       <c r="F455" s="3" t="n">
         <v>0.0004014452027298946</v>
       </c>
+      <c r="G455" s="1" t="n">
+        <v>0.5014</v>
+      </c>
+      <c r="H455" s="3" t="n">
+        <v>0.006019261637239059</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -10475,6 +13211,12 @@
       <c r="F456" s="3" t="n">
         <v>0.000752634219769292</v>
       </c>
+      <c r="G456" s="1" t="n">
+        <v>0.015982</v>
+      </c>
+      <c r="H456" s="3" t="n">
+        <v>0.001629481072950504</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -10497,6 +13239,12 @@
       <c r="F457" s="3" t="n">
         <v>0.00135501355013542</v>
       </c>
+      <c r="G457" s="1" t="n">
+        <v>0.006661</v>
+      </c>
+      <c r="H457" s="3" t="n">
+        <v>0.001503533303262736</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -10519,6 +13267,12 @@
       <c r="F458" s="3" t="n">
         <v>0.0006253908692932395</v>
       </c>
+      <c r="G458" s="1" t="n">
+        <v>0.4816</v>
+      </c>
+      <c r="H458" s="3" t="n">
+        <v>0.003333333333333313</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -10541,6 +13295,12 @@
       <c r="F459" s="3" t="n">
         <v>0.0001571091908876878</v>
       </c>
+      <c r="G459" s="1" t="n">
+        <v>0.00638</v>
+      </c>
+      <c r="H459" s="3" t="n">
+        <v>0.00219918316054039</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -10563,6 +13323,12 @@
       <c r="F460" s="3" t="n">
         <v>0.002189781021897771</v>
       </c>
+      <c r="G460" s="1" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="H460" s="3" t="n">
+        <v>0.005098324836125318</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -10585,6 +13351,12 @@
       <c r="F461" s="3" t="n">
         <v>0.0003367003367003619</v>
       </c>
+      <c r="G461" s="1" t="n">
+        <v>0.08918</v>
+      </c>
+      <c r="H461" s="3" t="n">
+        <v>0.0005609783462357735</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -10607,6 +13379,12 @@
       <c r="F462" s="3" t="n">
         <v>0.003093922651933729</v>
       </c>
+      <c r="G462" s="1" t="n">
+        <v>0.04535</v>
+      </c>
+      <c r="H462" s="2" t="n">
+        <v>-0.0008812513769552406</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -10629,6 +13407,12 @@
       <c r="F463" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G463" s="1" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="H463" s="3" t="n">
+        <v>0.004310344827586156</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -10651,6 +13435,12 @@
       <c r="F464" s="3" t="n">
         <v>0.0007668711656440873</v>
       </c>
+      <c r="G464" s="1" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="H464" s="3" t="n">
+        <v>0.003065134099616861</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -10673,6 +13463,12 @@
       <c r="F465" s="2" t="n">
         <v>-0.00498398006407959</v>
       </c>
+      <c r="G465" s="1" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="H465" s="3" t="n">
+        <v>0.005366726296958859</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -10695,6 +13491,12 @@
       <c r="F466" s="3" t="n">
         <v>0.00211864406779669</v>
       </c>
+      <c r="G466" s="1" t="n">
+        <v>1.421</v>
+      </c>
+      <c r="H466" s="3" t="n">
+        <v>0.001409443269908387</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -10717,6 +13519,12 @@
       <c r="F467" s="3" t="n">
         <v>0.002616431187859834</v>
       </c>
+      <c r="G467" s="1" t="n">
+        <v>0.01926</v>
+      </c>
+      <c r="H467" s="3" t="n">
+        <v>0.00521920668058452</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -10739,6 +13547,12 @@
       <c r="F468" s="3" t="n">
         <v>0.00304568527918787</v>
       </c>
+      <c r="G468" s="1" t="n">
+        <v>0.009939999999999999</v>
+      </c>
+      <c r="H468" s="3" t="n">
+        <v>0.006072874493927054</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -10761,6 +13575,12 @@
       <c r="F469" s="3" t="n">
         <v>0.006031666247800989</v>
       </c>
+      <c r="G469" s="1" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="H469" s="3" t="n">
+        <v>0.001498875843117635</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -10783,6 +13603,12 @@
       <c r="F470" s="3" t="n">
         <v>0.001136363636363637</v>
       </c>
+      <c r="G470" s="1" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="H470" s="3" t="n">
+        <v>0.002270147559591376</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -10805,6 +13631,12 @@
       <c r="F471" s="3" t="n">
         <v>0.002171889543903232</v>
       </c>
+      <c r="G471" s="1" t="n">
+        <v>3.248</v>
+      </c>
+      <c r="H471" s="3" t="n">
+        <v>0.00557275541795673</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -10827,6 +13659,12 @@
       <c r="F472" s="3" t="n">
         <v>0.0002461235540241955</v>
       </c>
+      <c r="G472" s="1" t="n">
+        <v>0.04069</v>
+      </c>
+      <c r="H472" s="3" t="n">
+        <v>0.001230314960629786</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -10849,6 +13687,12 @@
       <c r="F473" s="3" t="n">
         <v>0.005668016194331898</v>
       </c>
+      <c r="G473" s="1" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="H473" s="3" t="n">
+        <v>0.003220611916264093</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -10871,6 +13715,12 @@
       <c r="F474" s="2" t="n">
         <v>-0.001991798476859948</v>
       </c>
+      <c r="G474" s="1" t="n">
+        <v>0.008543</v>
+      </c>
+      <c r="H474" s="3" t="n">
+        <v>0.002934961258511472</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -10893,6 +13743,12 @@
       <c r="F475" s="2" t="n">
         <v>-0.00921658986175128</v>
       </c>
+      <c r="G475" s="1" t="n">
+        <v>0.04196</v>
+      </c>
+      <c r="H475" s="3" t="n">
+        <v>0.02717258261933904</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -10915,6 +13771,12 @@
       <c r="F476" s="2" t="n">
         <v>-0.001264062697509833</v>
       </c>
+      <c r="G476" s="1" t="n">
+        <v>0.0793</v>
+      </c>
+      <c r="H476" s="3" t="n">
+        <v>0.003670421465637243</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -10937,6 +13799,12 @@
       <c r="F477" s="2" t="n">
         <v>-7.279079924304848e-05</v>
       </c>
+      <c r="G477" s="1" t="n">
+        <v>0.13663</v>
+      </c>
+      <c r="H477" s="2" t="n">
+        <v>-0.005386911261556313</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -10959,6 +13827,12 @@
       <c r="F478" s="3" t="n">
         <v>0.001054407423028288</v>
       </c>
+      <c r="G478" s="1" t="n">
+        <v>0.04764</v>
+      </c>
+      <c r="H478" s="3" t="n">
+        <v>0.003581209184748336</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -10981,6 +13855,12 @@
       <c r="F479" s="3" t="n">
         <v>0.0007594456047084989</v>
       </c>
+      <c r="G479" s="1" t="n">
+        <v>0.005299</v>
+      </c>
+      <c r="H479" s="3" t="n">
+        <v>0.005312084993359941</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -11003,6 +13883,12 @@
       <c r="F480" s="2" t="n">
         <v>-0.004651162790697758</v>
       </c>
+      <c r="G480" s="1" t="n">
+        <v>0.2789</v>
+      </c>
+      <c r="H480" s="3" t="n">
+        <v>0.002516175413371598</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -11025,6 +13911,12 @@
       <c r="F481" s="3" t="n">
         <v>0.0003946329913181037</v>
       </c>
+      <c r="G481" s="1" t="n">
+        <v>0.07615</v>
+      </c>
+      <c r="H481" s="3" t="n">
+        <v>0.001314924391847324</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -11047,6 +13939,12 @@
       <c r="F482" s="2" t="n">
         <v>-0.0006752194463200265</v>
       </c>
+      <c r="G482" s="1" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="H482" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -11069,6 +13967,12 @@
       <c r="F483" s="2" t="n">
         <v>-0.003984063745019896</v>
       </c>
+      <c r="G483" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="H483" s="3" t="n">
+        <v>0.003999999999999976</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -11091,6 +13995,12 @@
       <c r="F484" s="3" t="n">
         <v>0.001385681293302644</v>
       </c>
+      <c r="G484" s="1" t="n">
+        <v>0.02171</v>
+      </c>
+      <c r="H484" s="3" t="n">
+        <v>0.00138376383763832</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -11113,6 +14023,12 @@
       <c r="F485" s="3" t="n">
         <v>0.004456220643141102</v>
       </c>
+      <c r="G485" s="1" t="n">
+        <v>0.008366</v>
+      </c>
+      <c r="H485" s="3" t="n">
+        <v>0.003117505995203835</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -11135,6 +14051,12 @@
       <c r="F486" s="3" t="n">
         <v>0.001076426264800887</v>
       </c>
+      <c r="G486" s="1" t="n">
+        <v>0.007461</v>
+      </c>
+      <c r="H486" s="3" t="n">
+        <v>0.002822580645161199</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -11157,6 +14079,12 @@
       <c r="F487" s="3" t="n">
         <v>0.001814882032667803</v>
       </c>
+      <c r="G487" s="1" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="H487" s="3" t="n">
+        <v>0.003623188405797079</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -11179,6 +14107,12 @@
       <c r="F488" s="3" t="n">
         <v>0.0004261212314904156</v>
       </c>
+      <c r="G488" s="1" t="n">
+        <v>0.009377</v>
+      </c>
+      <c r="H488" s="2" t="n">
+        <v>-0.001490789053348964</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -11201,6 +14135,12 @@
       <c r="F489" s="2" t="n">
         <v>-0.006164911379398849</v>
       </c>
+      <c r="G489" s="1" t="n">
+        <v>0.03872</v>
+      </c>
+      <c r="H489" s="3" t="n">
+        <v>0.0007753941586972165</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -11223,6 +14163,12 @@
       <c r="F490" s="3" t="n">
         <v>0.007071403932390491</v>
       </c>
+      <c r="G490" s="1" t="n">
+        <v>0.05869</v>
+      </c>
+      <c r="H490" s="3" t="n">
+        <v>0.005137866072957727</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -11245,6 +14191,12 @@
       <c r="F491" s="2" t="n">
         <v>-0.004149377593360971</v>
       </c>
+      <c r="G491" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="H491" s="3" t="n">
+        <v>0.003124999999999945</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -11267,6 +14219,12 @@
       <c r="F492" s="2" t="n">
         <v>-0.007485029940119767</v>
       </c>
+      <c r="G492" s="1" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H492" s="3" t="n">
+        <v>0.003016591251885372</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -11289,6 +14247,12 @@
       <c r="F493" s="3" t="n">
         <v>0.001420454545454389</v>
       </c>
+      <c r="G493" s="1" t="n">
+        <v>0.03545</v>
+      </c>
+      <c r="H493" s="3" t="n">
+        <v>0.00567375886524839</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -11311,6 +14275,12 @@
       <c r="F494" s="2" t="n">
         <v>-0.002354326074161379</v>
       </c>
+      <c r="G494" s="1" t="n">
+        <v>0.0171</v>
+      </c>
+      <c r="H494" s="3" t="n">
+        <v>0.008849557522123942</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -11333,6 +14303,12 @@
       <c r="F495" s="3" t="n">
         <v>0.002956081081081107</v>
       </c>
+      <c r="G495" s="1" t="n">
+        <v>0.04763</v>
+      </c>
+      <c r="H495" s="3" t="n">
+        <v>0.00273684210526312</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -11355,6 +14331,12 @@
       <c r="F496" s="3" t="n">
         <v>0.003322259136212633</v>
       </c>
+      <c r="G496" s="1" t="n">
+        <v>0.04835</v>
+      </c>
+      <c r="H496" s="3" t="n">
+        <v>0.0006208609271522208</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -11377,6 +14359,12 @@
       <c r="F497" s="3" t="n">
         <v>0.001801080648389029</v>
       </c>
+      <c r="G497" s="1" t="n">
+        <v>0.05012</v>
+      </c>
+      <c r="H497" s="3" t="n">
+        <v>0.001198561725928836</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -11399,6 +14387,12 @@
       <c r="F498" s="3" t="n">
         <v>0.0003480682213713504</v>
       </c>
+      <c r="G498" s="1" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="H498" s="3" t="n">
+        <v>0.006263048016701544</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -11421,6 +14415,12 @@
       <c r="F499" s="3" t="n">
         <v>0.0007334066740006526</v>
       </c>
+      <c r="G499" s="1" t="n">
+        <v>0.2736</v>
+      </c>
+      <c r="H499" s="3" t="n">
+        <v>0.002565042139978138</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -11443,6 +14443,12 @@
       <c r="F500" s="2" t="n">
         <v>-0.003759398496240611</v>
       </c>
+      <c r="G500" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="H500" s="3" t="n">
+        <v>0.007547169811320775</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -11465,6 +14471,12 @@
       <c r="F501" s="2" t="n">
         <v>-0.001383891502906212</v>
       </c>
+      <c r="G501" s="1" t="n">
+        <v>0.03584</v>
+      </c>
+      <c r="H501" s="2" t="n">
+        <v>-0.006651884700665302</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -11487,6 +14499,12 @@
       <c r="F502" s="3" t="n">
         <v>0.001884422110552687</v>
       </c>
+      <c r="G502" s="1" t="n">
+        <v>0.03192</v>
+      </c>
+      <c r="H502" s="3" t="n">
+        <v>0.0006269592476488773</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -11509,6 +14527,12 @@
       <c r="F503" s="2" t="n">
         <v>-0.001412973667309004</v>
       </c>
+      <c r="G503" s="1" t="n">
+        <v>0.007804</v>
+      </c>
+      <c r="H503" s="3" t="n">
+        <v>0.003859017236943724</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -11531,6 +14555,12 @@
       <c r="F504" s="2" t="n">
         <v>-0.00131018670160498</v>
       </c>
+      <c r="G504" s="1" t="n">
+        <v>3.058</v>
+      </c>
+      <c r="H504" s="3" t="n">
+        <v>0.002951787471302033</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -11553,6 +14583,12 @@
       <c r="F505" s="3" t="n">
         <v>0.002041927579635152</v>
       </c>
+      <c r="G505" s="1" t="n">
+        <v>0.0007399</v>
+      </c>
+      <c r="H505" s="3" t="n">
+        <v>0.005162342073088021</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -11575,6 +14611,12 @@
       <c r="F506" s="2" t="n">
         <v>-0.002022926500337119</v>
       </c>
+      <c r="G506" s="1" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="H506" s="3" t="n">
+        <v>0.004729729729729772</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -11597,6 +14639,12 @@
       <c r="F507" s="3" t="n">
         <v>0.002826855123674827</v>
       </c>
+      <c r="G507" s="1" t="n">
+        <v>0.002853</v>
+      </c>
+      <c r="H507" s="3" t="n">
+        <v>0.005285412262156538</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -11619,6 +14667,12 @@
       <c r="F508" s="3" t="n">
         <v>0.001896933291179402</v>
       </c>
+      <c r="G508" s="1" t="n">
+        <v>0.06347999999999999</v>
+      </c>
+      <c r="H508" s="3" t="n">
+        <v>0.001577784790154449</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -11641,6 +14695,12 @@
       <c r="F509" s="3" t="n">
         <v>0.001339285714285567</v>
       </c>
+      <c r="G509" s="1" t="n">
+        <v>2.256</v>
+      </c>
+      <c r="H509" s="3" t="n">
+        <v>0.005795809184128356</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -11663,6 +14723,12 @@
       <c r="F510" s="2" t="n">
         <v>-0.002331321996708853</v>
       </c>
+      <c r="G510" s="1" t="n">
+        <v>0.0007309</v>
+      </c>
+      <c r="H510" s="3" t="n">
+        <v>0.004673539518900457</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -11685,6 +14751,12 @@
       <c r="F511" s="3" t="n">
         <v>0.003649635036496353</v>
       </c>
+      <c r="G511" s="1" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="H511" s="3" t="n">
+        <v>0.003272727272727114</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -11707,6 +14779,12 @@
       <c r="F512" s="2" t="n">
         <v>-0.0004195510803440421</v>
       </c>
+      <c r="G512" s="1" t="n">
+        <v>0.0004814</v>
+      </c>
+      <c r="H512" s="3" t="n">
+        <v>0.01028331584470097</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -11729,6 +14807,12 @@
       <c r="F513" s="3" t="n">
         <v>0.002731742851939489</v>
       </c>
+      <c r="G513" s="1" t="n">
+        <v>0.05517</v>
+      </c>
+      <c r="H513" s="3" t="n">
+        <v>0.001997820559389739</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -11751,6 +14835,12 @@
       <c r="F514" s="3" t="n">
         <v>0.0006589785831961336</v>
       </c>
+      <c r="G514" s="1" t="n">
+        <v>0.03044</v>
+      </c>
+      <c r="H514" s="3" t="n">
+        <v>0.002304906157392069</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -11773,6 +14863,12 @@
       <c r="F515" s="3" t="n">
         <v>0.003505696757230394</v>
       </c>
+      <c r="G515" s="1" t="n">
+        <v>0.001143</v>
+      </c>
+      <c r="H515" s="2" t="n">
+        <v>-0.001746724890829737</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -11795,6 +14891,12 @@
       <c r="F516" s="3" t="n">
         <v>0.001971489232635728</v>
       </c>
+      <c r="G516" s="1" t="n">
+        <v>0.00664</v>
+      </c>
+      <c r="H516" s="3" t="n">
+        <v>0.004994702588164075</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -11817,6 +14919,12 @@
       <c r="F517" s="3" t="n">
         <v>0.0007545271629779238</v>
       </c>
+      <c r="G517" s="1" t="n">
+        <v>0.03987</v>
+      </c>
+      <c r="H517" s="3" t="n">
+        <v>0.002010555415933744</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -11839,6 +14947,12 @@
       <c r="F518" s="3" t="n">
         <v>0.001949317738791479</v>
       </c>
+      <c r="G518" s="1" t="n">
+        <v>0.1029</v>
+      </c>
+      <c r="H518" s="3" t="n">
+        <v>0.0009727626459144248</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -11861,6 +14975,12 @@
       <c r="F519" s="3" t="n">
         <v>0.009142857142856968</v>
       </c>
+      <c r="G519" s="1" t="n">
+        <v>0.008829999999999999</v>
+      </c>
+      <c r="H519" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -11883,6 +15003,12 @@
       <c r="F520" s="2" t="n">
         <v>-0.005003126954346437</v>
       </c>
+      <c r="G520" s="1" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="H520" s="3" t="n">
+        <v>0.006913890634820979</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -11905,6 +15031,12 @@
       <c r="F521" s="2" t="n">
         <v>-0.003350083752093666</v>
       </c>
+      <c r="G521" s="1" t="n">
+        <v>0.01789</v>
+      </c>
+      <c r="H521" s="3" t="n">
+        <v>0.002240896358543326</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -11927,6 +15059,12 @@
       <c r="F522" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G522" s="1" t="n">
+        <v>0.01664</v>
+      </c>
+      <c r="H522" s="3" t="n">
+        <v>0.005438066465256786</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -11949,6 +15087,12 @@
       <c r="F523" s="3" t="n">
         <v>0.0004770992366410778</v>
       </c>
+      <c r="G523" s="1" t="n">
+        <v>0.004197</v>
+      </c>
+      <c r="H523" s="3" t="n">
+        <v>0.0007153075822604669</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -11971,6 +15115,12 @@
       <c r="F524" s="3" t="n">
         <v>0.00212014134275622</v>
       </c>
+      <c r="G524" s="1" t="n">
+        <v>0.01425</v>
+      </c>
+      <c r="H524" s="3" t="n">
+        <v>0.004936530324400608</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -11993,6 +15143,12 @@
       <c r="F525" s="3" t="n">
         <v>0.002004008016032122</v>
       </c>
+      <c r="G525" s="1" t="n">
+        <v>0.02502</v>
+      </c>
+      <c r="H525" s="3" t="n">
+        <v>0.0007999999999999674</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -12015,6 +15171,12 @@
       <c r="F526" s="3" t="n">
         <v>0.0008326394671107649</v>
       </c>
+      <c r="G526" s="1" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="H526" s="3" t="n">
+        <v>0.002495840266222918</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -12037,6 +15199,12 @@
       <c r="F527" s="3" t="n">
         <v>0.000279759406910143</v>
       </c>
+      <c r="G527" s="1" t="n">
+        <v>0.07156999999999999</v>
+      </c>
+      <c r="H527" s="3" t="n">
+        <v>0.0008390434904207889</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -12059,6 +15227,12 @@
       <c r="F528" s="3" t="n">
         <v>0.003262642740619931</v>
       </c>
+      <c r="G528" s="1" t="n">
+        <v>0.04331</v>
+      </c>
+      <c r="H528" s="3" t="n">
+        <v>0.006039488966318311</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -12081,6 +15255,12 @@
       <c r="F529" s="2" t="n">
         <v>-0.001584283903675364</v>
       </c>
+      <c r="G529" s="1" t="n">
+        <v>0.06311</v>
+      </c>
+      <c r="H529" s="3" t="n">
+        <v>0.001428118057759328</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -12103,6 +15283,12 @@
       <c r="F530" s="3" t="n">
         <v>0.0003997601439137049</v>
       </c>
+      <c r="G530" s="1" t="n">
+        <v>0.005026</v>
+      </c>
+      <c r="H530" s="3" t="n">
+        <v>0.004195804195804233</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -12125,6 +15311,12 @@
       <c r="F531" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G531" s="1" t="n">
+        <v>0.1306</v>
+      </c>
+      <c r="H531" s="3" t="n">
+        <v>0.002302379125095892</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -12147,6 +15339,12 @@
       <c r="F532" s="3" t="n">
         <v>0.003763643206623989</v>
       </c>
+      <c r="G532" s="1" t="n">
+        <v>0.05344</v>
+      </c>
+      <c r="H532" s="3" t="n">
+        <v>0.001874765654293267</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -12169,6 +15367,12 @@
       <c r="F533" s="2" t="n">
         <v>-0.00997113618472849</v>
       </c>
+      <c r="G533" s="1" t="n">
+        <v>0.00377</v>
+      </c>
+      <c r="H533" s="2" t="n">
+        <v>-0.0007951232441028265</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -12191,6 +15395,12 @@
       <c r="F534" s="3" t="n">
         <v>0.0005830903790086821</v>
       </c>
+      <c r="G534" s="1" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="H534" s="3" t="n">
+        <v>0.001748251748251717</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -12213,6 +15423,12 @@
       <c r="F535" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G535" s="1" t="n">
+        <v>1.13e-05</v>
+      </c>
+      <c r="H535" s="3" t="n">
+        <v>0.008928571428571494</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -12235,6 +15451,12 @@
       <c r="F536" s="3" t="n">
         <v>0.0002231146809460117</v>
       </c>
+      <c r="G536" s="1" t="n">
+        <v>0.0004466</v>
+      </c>
+      <c r="H536" s="2" t="n">
+        <v>-0.003792103502119088</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -12257,6 +15479,12 @@
       <c r="F537" s="3" t="n">
         <v>0.004149377593361007</v>
       </c>
+      <c r="G537" s="1" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="H537" s="3" t="n">
+        <v>0.002066115702479434</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -12279,6 +15507,12 @@
       <c r="F538" s="2" t="n">
         <v>-0.001837222120154252</v>
       </c>
+      <c r="G538" s="1" t="n">
+        <v>0.05459</v>
+      </c>
+      <c r="H538" s="3" t="n">
+        <v>0.00478556966685066</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -12301,6 +15535,12 @@
       <c r="F539" s="2" t="n">
         <v>-0.00189891907683314</v>
       </c>
+      <c r="G539" s="1" t="n">
+        <v>0.6846</v>
+      </c>
+      <c r="H539" s="3" t="n">
+        <v>0.001902531830820969</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -12323,6 +15563,12 @@
       <c r="F540" s="3" t="n">
         <v>0.001988071570576506</v>
       </c>
+      <c r="G540" s="1" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="H540" s="3" t="n">
+        <v>0.00462962962962967</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -12345,6 +15591,12 @@
       <c r="F541" s="3" t="n">
         <v>0.001530221882172853</v>
       </c>
+      <c r="G541" s="1" t="n">
+        <v>0.01315</v>
+      </c>
+      <c r="H541" s="3" t="n">
+        <v>0.00458365164247525</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -12367,6 +15619,12 @@
       <c r="F542" s="3" t="n">
         <v>0.02892263195950827</v>
       </c>
+      <c r="G542" s="1" t="n">
+        <v>0.01402</v>
+      </c>
+      <c r="H542" s="2" t="n">
+        <v>-0.01475755446240338</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -12388,6 +15646,12 @@
       </c>
       <c r="F543" s="3" t="n">
         <v>0.003861681586800035</v>
+      </c>
+      <c r="G543" s="1" t="n">
+        <v>0.05735</v>
+      </c>
+      <c r="H543" s="3" t="n">
+        <v>0.00279769190417906</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J543"/>
+  <dimension ref="A1:L543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -436,6 +436,8 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,6 +491,16 @@
           <t>change_01:00</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>price_01:15</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>change_01:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -523,6 +535,12 @@
       <c r="J2" s="2" t="n">
         <v>-9.240922215603511e-05</v>
       </c>
+      <c r="K2" s="1" t="n">
+        <v>70382</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.0006995313708539556</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -557,6 +575,12 @@
       <c r="J3" s="2" t="n">
         <v>-0.0008549857260857506</v>
       </c>
+      <c r="K3" s="1" t="n">
+        <v>2068.77</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.0001595405232928812</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -591,6 +615,12 @@
       <c r="J4" s="2" t="n">
         <v>-0.0003456619426201306</v>
       </c>
+      <c r="K4" s="1" t="n">
+        <v>86.73</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>-0.0003457814661134294</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,6 +655,12 @@
       <c r="J5" s="3" t="n">
         <v>0.01982015048632785</v>
       </c>
+      <c r="K5" s="1" t="n">
+        <v>0.010995</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>-0.0107072161238079</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -659,6 +695,12 @@
       <c r="J6" s="2" t="n">
         <v>-0.001734605377276639</v>
       </c>
+      <c r="K6" s="1" t="n">
+        <v>1.3819</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.0005068056762235179</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -693,6 +735,12 @@
       <c r="J7" s="3" t="n">
         <v>0.000845576577528768</v>
       </c>
+      <c r="K7" s="1" t="n">
+        <v>0.09462</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>-0.0007392544091245181</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -727,6 +775,12 @@
       <c r="J8" s="3" t="n">
         <v>0.001333048949557352</v>
       </c>
+      <c r="K8" s="1" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.001650780126737249</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -761,6 +815,12 @@
       <c r="J9" s="2" t="n">
         <v>-0.004967216371945166</v>
       </c>
+      <c r="K9" s="1" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.002396166134185345</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -795,6 +855,12 @@
       <c r="J10" s="3" t="n">
         <v>0.00874030372555447</v>
       </c>
+      <c r="K10" s="1" t="n">
+        <v>18.387</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>-0.004278132784577094</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -829,6 +895,12 @@
       <c r="J11" s="2" t="n">
         <v>-0.0002914602156804689</v>
       </c>
+      <c r="K11" s="1" t="n">
+        <v>651.39</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>-0.0004756789934019627</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -863,6 +935,12 @@
       <c r="J12" s="2" t="n">
         <v>-0.06482204618989182</v>
       </c>
+      <c r="K12" s="1" t="n">
+        <v>0.8346</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>-0.004294917680744377</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -897,6 +975,12 @@
       <c r="J13" s="2" t="n">
         <v>-0.00180325535044842</v>
       </c>
+      <c r="K13" s="1" t="n">
+        <v>209.94</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>-0.00194913239838363</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -931,6 +1015,12 @@
       <c r="J14" s="2" t="n">
         <v>-0.002138618633091459</v>
       </c>
+      <c r="K14" s="1" t="n">
+        <v>0.0033113</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>-0.0004527891813570893</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -965,6 +1055,12 @@
       <c r="J15" s="2" t="n">
         <v>-0.01065816088377145</v>
       </c>
+      <c r="K15" s="1" t="n">
+        <v>0.2539</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>-0.001729967759691735</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -999,6 +1095,12 @@
       <c r="J16" s="2" t="n">
         <v>-0.0003069681776322183</v>
       </c>
+      <c r="K16" s="1" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>-0.00153531218014324</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1033,6 +1135,12 @@
       <c r="J17" s="2" t="n">
         <v>-0.01333333333333325</v>
       </c>
+      <c r="K17" s="1" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>-0.03378378378378381</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1067,6 +1175,12 @@
       <c r="J18" s="2" t="n">
         <v>-0.001202534572869059</v>
       </c>
+      <c r="K18" s="1" t="n">
+        <v>215.57</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>-0.001759666589488287</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1101,6 +1215,12 @@
       <c r="J19" s="2" t="n">
         <v>-0.0003800836183960053</v>
       </c>
+      <c r="K19" s="1" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>-0.0007604562737643858</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,6 +1255,12 @@
       <c r="J20" s="2" t="n">
         <v>-0.01017484357639907</v>
       </c>
+      <c r="K20" s="1" t="n">
+        <v>0.01674</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>-0.01104743900277661</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1169,6 +1295,12 @@
       <c r="J21" s="2" t="n">
         <v>-0.00135317997293639</v>
       </c>
+      <c r="K21" s="1" t="n">
+        <v>9.589</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>-0.0005211590577443199</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1203,6 +1335,12 @@
       <c r="J22" s="2" t="n">
         <v>-0.009473060982830021</v>
       </c>
+      <c r="K22" s="1" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>-0.00358637178720871</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1237,6 +1375,12 @@
       <c r="J23" s="3" t="n">
         <v>0.004534887058350868</v>
       </c>
+      <c r="K23" s="1" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>-0.0003142946941341152</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1271,6 +1415,12 @@
       <c r="J24" s="2" t="n">
         <v>-0.001160092807424595</v>
       </c>
+      <c r="K24" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>-0.001161440185830431</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1305,6 +1455,12 @@
       <c r="J25" s="2" t="n">
         <v>-0.001104362230811683</v>
       </c>
+      <c r="K25" s="1" t="n">
+        <v>9.035</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>-0.00110558319513541</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1339,6 +1495,12 @@
       <c r="J26" s="2" t="n">
         <v>-0.002267573696145043</v>
       </c>
+      <c r="K26" s="1" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0.008333333333333257</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1373,6 +1535,12 @@
       <c r="J27" s="2" t="n">
         <v>-0.002189810858736761</v>
       </c>
+      <c r="K27" s="1" t="n">
+        <v>5124.23</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>-0.0003804002200470385</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1407,6 +1575,12 @@
       <c r="J28" s="2" t="n">
         <v>-0.003109980209216822</v>
       </c>
+      <c r="K28" s="1" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>-0.0005672149744754211</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1441,6 +1615,12 @@
       <c r="J29" s="2" t="n">
         <v>-0.007167106752168874</v>
       </c>
+      <c r="K29" s="1" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>-0.0007598784194529725</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1475,6 +1655,12 @@
       <c r="J30" s="3" t="n">
         <v>0.001232211037834065</v>
       </c>
+      <c r="K30" s="1" t="n">
+        <v>0.57457</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>-0.004056091938083945</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1509,6 +1695,12 @@
       <c r="J31" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K31" s="1" t="n">
+        <v>0.002085</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0.0004798464491363401</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1543,6 +1735,12 @@
       <c r="J32" s="3" t="n">
         <v>0.01259265162987171</v>
       </c>
+      <c r="K32" s="1" t="n">
+        <v>1.2836</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.01031090121999222</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1577,6 +1775,12 @@
       <c r="J33" s="3" t="n">
         <v>0.006193868070610101</v>
       </c>
+      <c r="K33" s="1" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>-0.001538935056940598</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1611,6 +1815,12 @@
       <c r="J34" s="2" t="n">
         <v>-0.003981420039814204</v>
       </c>
+      <c r="K34" s="1" t="n">
+        <v>1.499</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>-0.001332445036642092</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1645,6 +1855,12 @@
       <c r="J35" s="2" t="n">
         <v>-0.002424692544616557</v>
       </c>
+      <c r="K35" s="1" t="n">
+        <v>456.47</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>-0.0004598405885959086</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1679,6 +1895,12 @@
       <c r="J36" s="3" t="n">
         <v>0.01626355296080058</v>
       </c>
+      <c r="K36" s="1" t="n">
+        <v>0.04832</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>-0.008617152236356109</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1713,6 +1935,12 @@
       <c r="J37" s="3" t="n">
         <v>0.001271366012148625</v>
       </c>
+      <c r="K37" s="1" t="n">
+        <v>0.7092000000000001</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>0.0005643340857788755</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1747,6 +1975,12 @@
       <c r="J38" s="2" t="n">
         <v>-0.003770028275212041</v>
       </c>
+      <c r="K38" s="1" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>-0.0009460737937559401</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1781,6 +2015,12 @@
       <c r="J39" s="2" t="n">
         <v>-0.001815870710005473</v>
       </c>
+      <c r="K39" s="1" t="n">
+        <v>109.92</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>-0.0001819174094960526</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1815,6 +2055,12 @@
       <c r="J40" s="3" t="n">
         <v>0.01075268817204303</v>
       </c>
+      <c r="K40" s="1" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>-0.02439024390243893</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1849,6 +2095,12 @@
       <c r="J41" s="3" t="n">
         <v>0.001259899208063366</v>
       </c>
+      <c r="K41" s="1" t="n">
+        <v>0.05572</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>0.001617832104979324</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1883,6 +2135,12 @@
       <c r="J42" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K42" s="1" t="n">
+        <v>54.34</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>-0.0007355645457888773</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1917,6 +2175,12 @@
       <c r="J43" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K43" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1951,6 +2215,12 @@
       <c r="J44" s="2" t="n">
         <v>-0.001359157322459961</v>
       </c>
+      <c r="K44" s="1" t="n">
+        <v>0.005872</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>-0.00102075535896577</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1985,6 +2255,12 @@
       <c r="J45" s="2" t="n">
         <v>-0.00192678227360318</v>
       </c>
+      <c r="K45" s="1" t="n">
+        <v>0.10013</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0.01737451737451741</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2019,6 +2295,12 @@
       <c r="J46" s="2" t="n">
         <v>-0.0007204610951007853</v>
       </c>
+      <c r="K46" s="1" t="n">
+        <v>2.768</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>-0.002162941600576866</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2053,6 +2335,12 @@
       <c r="J47" s="2" t="n">
         <v>-0.0006916585973162885</v>
       </c>
+      <c r="K47" s="1" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>0.0002076411960133046</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2087,6 +2375,12 @@
       <c r="J48" s="3" t="n">
         <v>0.003700277520814039</v>
       </c>
+      <c r="K48" s="1" t="n">
+        <v>0.1089</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0.003686635944700439</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2121,6 +2415,12 @@
       <c r="J49" s="2" t="n">
         <v>-0.005736751313836349</v>
       </c>
+      <c r="K49" s="1" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2155,6 +2455,12 @@
       <c r="J50" s="2" t="n">
         <v>-0.003797468354430372</v>
       </c>
+      <c r="K50" s="1" t="n">
+        <v>0.04737</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0.003176620076238973</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2189,6 +2495,12 @@
       <c r="J51" s="2" t="n">
         <v>-0.001275835672365372</v>
       </c>
+      <c r="K51" s="1" t="n">
+        <v>3.915</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>0.0002554931016862263</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2223,6 +2535,12 @@
       <c r="J52" s="2" t="n">
         <v>-0.004255319148936158</v>
       </c>
+      <c r="K52" s="1" t="n">
+        <v>0.000235</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>0.004273504273504262</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2257,6 +2575,12 @@
       <c r="J53" s="2" t="n">
         <v>-0.0006027727546714225</v>
       </c>
+      <c r="K53" s="1" t="n">
+        <v>0.1661</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>0.001809408926417338</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2291,6 +2615,12 @@
       <c r="J54" s="3" t="n">
         <v>0.004109257916364599</v>
       </c>
+      <c r="K54" s="1" t="n">
+        <v>0.04129</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>-0.006018295618680795</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2325,6 +2655,12 @@
       <c r="J55" s="2" t="n">
         <v>-0.000165057357431758</v>
       </c>
+      <c r="K55" s="1" t="n">
+        <v>0.12255</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>0.01155592241023535</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2359,6 +2695,12 @@
       <c r="J56" s="2" t="n">
         <v>-0.01348452344468268</v>
       </c>
+      <c r="K56" s="1" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>-0.01988195091643373</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2393,6 +2735,12 @@
       <c r="J57" s="2" t="n">
         <v>-0.01101694915254237</v>
       </c>
+      <c r="K57" s="1" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>0.002570694087403643</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2427,6 +2775,12 @@
       <c r="J58" s="2" t="n">
         <v>-0.002006018054162406</v>
       </c>
+      <c r="K58" s="1" t="n">
+        <v>0.09950000000000001</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2461,6 +2815,12 @@
       <c r="J59" s="2" t="n">
         <v>-0.002967359050445111</v>
       </c>
+      <c r="K59" s="1" t="n">
+        <v>0.00335</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>-0.002976190476190484</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2495,6 +2855,12 @@
       <c r="J60" s="2" t="n">
         <v>-0.003888528839922161</v>
       </c>
+      <c r="K60" s="1" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>0.002602472348731189</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2529,6 +2895,12 @@
       <c r="J61" s="3" t="n">
         <v>0.0004377188594296319</v>
       </c>
+      <c r="K61" s="1" t="n">
+        <v>0.15953</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>-0.002875179698731097</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2563,6 +2935,12 @@
       <c r="J62" s="2" t="n">
         <v>-0.002242152466367777</v>
       </c>
+      <c r="K62" s="1" t="n">
+        <v>0.7108</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>-0.001685393258426937</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2597,6 +2975,12 @@
       <c r="J63" s="3" t="n">
         <v>0.003731976251060262</v>
       </c>
+      <c r="K63" s="1" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>-0.001183031941862375</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2631,6 +3015,12 @@
       <c r="J64" s="2" t="n">
         <v>-0.002244354046850824</v>
       </c>
+      <c r="K64" s="1" t="n">
+        <v>0.007096</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>-0.002389990158864125</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2665,6 +3055,12 @@
       <c r="J65" s="2" t="n">
         <v>-0.007583250906693078</v>
       </c>
+      <c r="K65" s="1" t="n">
+        <v>0.03066</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>0.01860465116279075</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2699,6 +3095,12 @@
       <c r="J66" s="2" t="n">
         <v>-0.008438818565400852</v>
       </c>
+      <c r="K66" s="1" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>0.004255319148936175</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2733,6 +3135,12 @@
       <c r="J67" s="2" t="n">
         <v>-0.003683241252302029</v>
       </c>
+      <c r="K67" s="1" t="n">
+        <v>1.629</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>0.003696857670979671</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2767,6 +3175,12 @@
       <c r="J68" s="3" t="n">
         <v>0.003437453295471704</v>
       </c>
+      <c r="K68" s="1" t="n">
+        <v>2.0112</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>-0.001489425081918436</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2801,6 +3215,12 @@
       <c r="J69" s="2" t="n">
         <v>-0.002088045937010577</v>
       </c>
+      <c r="K69" s="1" t="n">
+        <v>0.5737</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>0.0003487358326067619</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2835,6 +3255,12 @@
       <c r="J70" s="2" t="n">
         <v>-0.009615384615384625</v>
       </c>
+      <c r="K70" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>0.01941747572815536</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2869,6 +3295,12 @@
       <c r="J71" s="2" t="n">
         <v>-0.000654593061313478</v>
       </c>
+      <c r="K71" s="1" t="n">
+        <v>0.9131</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>-0.003165938864628836</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2903,6 +3335,12 @@
       <c r="J72" s="2" t="n">
         <v>-0.006094702297233923</v>
       </c>
+      <c r="K72" s="1" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>0.006132075471698093</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2937,6 +3375,12 @@
       <c r="J73" s="2" t="n">
         <v>-0.002011646373742822</v>
       </c>
+      <c r="K73" s="1" t="n">
+        <v>0.09444</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>0.001909611712285165</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2971,6 +3415,12 @@
       <c r="J74" s="3" t="n">
         <v>0.003404626800523802</v>
       </c>
+      <c r="K74" s="1" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>0.004611101444231845</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3005,6 +3455,12 @@
       <c r="J75" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K75" s="1" t="n">
+        <v>0.01587</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3039,6 +3495,12 @@
       <c r="J76" s="2" t="n">
         <v>-0.007357057177129071</v>
       </c>
+      <c r="K76" s="1" t="n">
+        <v>0.12364</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>-0.003947474421976994</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3073,6 +3535,12 @@
       <c r="J77" s="2" t="n">
         <v>-0.004226542688081153</v>
       </c>
+      <c r="K77" s="1" t="n">
+        <v>0.1178</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3107,6 +3575,12 @@
       <c r="J78" s="2" t="n">
         <v>-0.0009881422924901469</v>
       </c>
+      <c r="K78" s="1" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>0.0009891196834817297</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3141,6 +3615,12 @@
       <c r="J79" s="2" t="n">
         <v>-0.001001669449081791</v>
       </c>
+      <c r="K79" s="1" t="n">
+        <v>0.005976</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>-0.001336898395721813</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3175,6 +3655,12 @@
       <c r="J80" s="3" t="n">
         <v>0.00256566890653637</v>
       </c>
+      <c r="K80" s="1" t="n">
+        <v>0.00817</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>-0.004387033877650448</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3209,6 +3695,12 @@
       <c r="J81" s="2" t="n">
         <v>-0.0005605381165920158</v>
       </c>
+      <c r="K81" s="1" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>0.001682557487380883</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3243,6 +3735,12 @@
       <c r="J82" s="2" t="n">
         <v>-0.003090234857849199</v>
       </c>
+      <c r="K82" s="1" t="n">
+        <v>0.1612</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>-0.0006199628022317979</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3277,6 +3775,12 @@
       <c r="J83" s="2" t="n">
         <v>-0.002434570906877611</v>
       </c>
+      <c r="K83" s="1" t="n">
+        <v>8.202999999999999</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>0.0009762050030505331</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3311,6 +3815,12 @@
       <c r="J84" s="3" t="n">
         <v>0.001480932987782251</v>
       </c>
+      <c r="K84" s="1" t="n">
+        <v>351.16</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>-0.001393430968292201</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3345,6 +3855,12 @@
       <c r="J85" s="2" t="n">
         <v>-0.007860886136255369</v>
       </c>
+      <c r="K85" s="1" t="n">
+        <v>0.004173</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>0.001920768307322767</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3379,6 +3895,12 @@
       <c r="J86" s="3" t="n">
         <v>0.003092472469452359</v>
       </c>
+      <c r="K86" s="1" t="n">
+        <v>0.13317</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>0.001353485224453068</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3413,6 +3935,12 @@
       <c r="J87" s="3" t="n">
         <v>0.0501551189245089</v>
       </c>
+      <c r="K87" s="1" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>-0.04480551452486465</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3447,6 +3975,12 @@
       <c r="J88" s="2" t="n">
         <v>-0.0008865248226949379</v>
       </c>
+      <c r="K88" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>0.002661934338952877</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3481,6 +4015,12 @@
       <c r="J89" s="2" t="n">
         <v>-0.001684636118598384</v>
       </c>
+      <c r="K89" s="1" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>-0.00843739453256835</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3515,6 +4055,12 @@
       <c r="J90" s="3" t="n">
         <v>0.0003891050583657159</v>
       </c>
+      <c r="K90" s="1" t="n">
+        <v>0.2571</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3549,6 +4095,12 @@
       <c r="J91" s="2" t="n">
         <v>-0.005531547104580827</v>
       </c>
+      <c r="K91" s="1" t="n">
+        <v>0.05694</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>-0.01025551885972537</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3583,6 +4135,12 @@
       <c r="J92" s="2" t="n">
         <v>-0.001295534217344943</v>
       </c>
+      <c r="K92" s="1" t="n">
+        <v>1.3073</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>-0.002441816100724984</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3617,6 +4175,12 @@
       <c r="J93" s="3" t="n">
         <v>0.0001586042823157811</v>
       </c>
+      <c r="K93" s="1" t="n">
+        <v>0.06317</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>0.001744370440849968</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3651,6 +4215,12 @@
       <c r="J94" s="2" t="n">
         <v>-0.001123595505617932</v>
       </c>
+      <c r="K94" s="1" t="n">
+        <v>0.008840000000000001</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>-0.005624296962879606</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3685,6 +4255,12 @@
       <c r="J95" s="2" t="n">
         <v>-0.003891050583657657</v>
       </c>
+      <c r="K95" s="1" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>0.0006009615384616391</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3719,6 +4295,12 @@
       <c r="J96" s="2" t="n">
         <v>-0.0008791208791208433</v>
       </c>
+      <c r="K96" s="1" t="n">
+        <v>0.02271</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>-0.0008798944126704437</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3753,6 +4335,12 @@
       <c r="J97" s="2" t="n">
         <v>-0.002439024390243851</v>
       </c>
+      <c r="K97" s="1" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="L97" s="3" t="n">
+        <v>0.002750611246943869</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3787,6 +4375,12 @@
       <c r="J98" s="2" t="n">
         <v>-0.003616636528028936</v>
       </c>
+      <c r="K98" s="1" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3821,6 +4415,12 @@
       <c r="J99" s="2" t="n">
         <v>-0.001331114808652248</v>
       </c>
+      <c r="K99" s="1" t="n">
+        <v>2.998</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>-0.0009996667777406431</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3855,6 +4455,12 @@
       <c r="J100" s="2" t="n">
         <v>-0.003468208092485609</v>
       </c>
+      <c r="K100" s="1" t="n">
+        <v>0.03435</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>-0.003770301624129878</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3889,6 +4495,12 @@
       <c r="J101" s="2" t="n">
         <v>-0.002744237102085683</v>
       </c>
+      <c r="K101" s="1" t="n">
+        <v>1.818</v>
+      </c>
+      <c r="L101" s="3" t="n">
+        <v>0.0005503577325262036</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3923,6 +4535,12 @@
       <c r="J102" s="2" t="n">
         <v>-0.0156187954996691</v>
       </c>
+      <c r="K102" s="1" t="n">
+        <v>0.007462</v>
+      </c>
+      <c r="L102" s="3" t="n">
+        <v>0.00336157052574961</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3957,6 +4575,12 @@
       <c r="J103" s="3" t="n">
         <v>0.0014747087450229</v>
       </c>
+      <c r="K103" s="1" t="n">
+        <v>0.06787</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>-0.0005890148726255098</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3991,6 +4615,12 @@
       <c r="J104" s="3" t="n">
         <v>0.002903459956448049</v>
       </c>
+      <c r="K104" s="1" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>-0.005307599517490904</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4025,6 +4655,12 @@
       <c r="J105" s="2" t="n">
         <v>-0.00615901455767084</v>
       </c>
+      <c r="K105" s="1" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="L105" s="3" t="n">
+        <v>0.004507042253521131</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4059,6 +4695,12 @@
       <c r="J106" s="3" t="n">
         <v>0.002721425037110488</v>
       </c>
+      <c r="K106" s="1" t="n">
+        <v>0.008132</v>
+      </c>
+      <c r="L106" s="3" t="n">
+        <v>0.003207500616827039</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4093,6 +4735,12 @@
       <c r="J107" s="2" t="n">
         <v>-0.004385964912280714</v>
       </c>
+      <c r="K107" s="1" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4127,6 +4775,12 @@
       <c r="J108" s="3" t="n">
         <v>0.003263403263403292</v>
       </c>
+      <c r="K108" s="1" t="n">
+        <v>0.02144</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>-0.003717472118959118</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4161,6 +4815,12 @@
       <c r="J109" s="2" t="n">
         <v>-0.003559985760056938</v>
       </c>
+      <c r="K109" s="1" t="n">
+        <v>0.0559</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>-0.001429081814933971</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4195,6 +4855,12 @@
       <c r="J110" s="2" t="n">
         <v>-0.03784546435388825</v>
       </c>
+      <c r="K110" s="1" t="n">
+        <v>0.11627</v>
+      </c>
+      <c r="L110" s="3" t="n">
+        <v>0.002932804278443829</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4229,6 +4895,12 @@
       <c r="J111" s="2" t="n">
         <v>-0.001924440392990942</v>
       </c>
+      <c r="K111" s="1" t="n">
+        <v>0.09864000000000001</v>
+      </c>
+      <c r="L111" s="3" t="n">
+        <v>0.001014816318246426</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4263,6 +4935,12 @@
       <c r="J112" s="2" t="n">
         <v>-0.005361930294906134</v>
       </c>
+      <c r="K112" s="1" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4297,6 +4975,12 @@
       <c r="J113" s="2" t="n">
         <v>-0.000814000814000922</v>
       </c>
+      <c r="K113" s="1" t="n">
+        <v>0.09814000000000001</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>-0.0006109979633400266</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4331,6 +5015,12 @@
       <c r="J114" s="2" t="n">
         <v>-0.06151142355008791</v>
       </c>
+      <c r="K114" s="1" t="n">
+        <v>0.001722</v>
+      </c>
+      <c r="L114" s="3" t="n">
+        <v>0.07490636704119857</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4365,6 +5055,12 @@
       <c r="J115" s="3" t="n">
         <v>0.002972603840282829</v>
       </c>
+      <c r="K115" s="1" t="n">
+        <v>1.2517</v>
+      </c>
+      <c r="L115" s="3" t="n">
+        <v>0.002643383530919642</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4399,6 +5095,12 @@
       <c r="J116" s="2" t="n">
         <v>-0.003764115432873325</v>
       </c>
+      <c r="K116" s="1" t="n">
+        <v>0.2369</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>-0.005457598656591082</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4433,6 +5135,12 @@
       <c r="J117" s="2" t="n">
         <v>-0.008650236657417917</v>
       </c>
+      <c r="K117" s="1" t="n">
+        <v>0.06058</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>-0.002634178465591051</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4467,6 +5175,12 @@
       <c r="J118" s="3" t="n">
         <v>0.00864225608369339</v>
       </c>
+      <c r="K118" s="1" t="n">
+        <v>0.04387</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>-0.01082299887260431</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4501,6 +5215,12 @@
       <c r="J119" s="2" t="n">
         <v>-0.00529661016949154</v>
       </c>
+      <c r="K119" s="1" t="n">
+        <v>0.003727</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>-0.007720979765708186</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4535,6 +5255,12 @@
       <c r="J120" s="2" t="n">
         <v>-0.003797468354430383</v>
       </c>
+      <c r="K120" s="1" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="L120" s="3" t="n">
+        <v>0.001270648030495554</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4569,6 +5295,12 @@
       <c r="J121" s="3" t="n">
         <v>0.00201680672268904</v>
       </c>
+      <c r="K121" s="1" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>-0.001677289500167731</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4603,6 +5335,12 @@
       <c r="J122" s="3" t="n">
         <v>0.003144654088050356</v>
       </c>
+      <c r="K122" s="1" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>-0.002089864158829832</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4637,6 +5375,12 @@
       <c r="J123" s="2" t="n">
         <v>-0.001253089212990404</v>
       </c>
+      <c r="K123" s="1" t="n">
+        <v>0.02864</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>-0.001847140417523471</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4671,6 +5415,12 @@
       <c r="J124" s="2" t="n">
         <v>-0.006823351023502638</v>
       </c>
+      <c r="K124" s="1" t="n">
+        <v>0.07846</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>-0.001781170483460575</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4705,6 +5455,12 @@
       <c r="J125" s="2" t="n">
         <v>-0.001562042370399233</v>
       </c>
+      <c r="K125" s="1" t="n">
+        <v>0.10184</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>-0.004204556565952868</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4739,6 +5495,12 @@
       <c r="J126" s="3" t="n">
         <v>0.002192982456140388</v>
       </c>
+      <c r="K126" s="1" t="n">
+        <v>0.02739</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>-0.001094091903719868</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4773,6 +5535,12 @@
       <c r="J127" s="2" t="n">
         <v>-0.008550855085508515</v>
       </c>
+      <c r="K127" s="1" t="n">
+        <v>0.02201</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>-0.0009078529278258127</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4807,6 +5575,12 @@
       <c r="J128" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K128" s="1" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="L128" s="3" t="n">
+        <v>0.001237623762376273</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4841,6 +5615,12 @@
       <c r="J129" s="3" t="n">
         <v>0.03233756534727409</v>
       </c>
+      <c r="K129" s="1" t="n">
+        <v>0.14082</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>0.01873688779570288</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4875,6 +5655,12 @@
       <c r="J130" s="3" t="n">
         <v>0.0003506829088224102</v>
       </c>
+      <c r="K130" s="1" t="n">
+        <v>0.053772</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>-0.007878374139744218</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4909,6 +5695,12 @@
       <c r="J131" s="2" t="n">
         <v>-0.002680965147453058</v>
       </c>
+      <c r="K131" s="1" t="n">
+        <v>0.08180999999999999</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>-0.0003665689149560392</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4943,6 +5735,12 @@
       <c r="J132" s="2" t="n">
         <v>-0.001148105625717599</v>
       </c>
+      <c r="K132" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4977,6 +5775,12 @@
       <c r="J133" s="3" t="n">
         <v>0.000517152215135456</v>
       </c>
+      <c r="K133" s="1" t="n">
+        <v>0.5804</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5011,6 +5815,12 @@
       <c r="J134" s="2" t="n">
         <v>-0.005564648117839607</v>
       </c>
+      <c r="K134" s="1" t="n">
+        <v>0.03019</v>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>-0.006254114549045398</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5045,6 +5855,12 @@
       <c r="J135" s="2" t="n">
         <v>-0.004496908375491861</v>
       </c>
+      <c r="K135" s="1" t="n">
+        <v>0.01783</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>0.006775832862789304</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5079,6 +5895,12 @@
       <c r="J136" s="2" t="n">
         <v>-0.004579741379310439</v>
       </c>
+      <c r="K136" s="1" t="n">
+        <v>0.03695</v>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5113,6 +5935,12 @@
       <c r="J137" s="2" t="n">
         <v>-0.005166051660516523</v>
       </c>
+      <c r="K137" s="1" t="n">
+        <v>0.02684</v>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>-0.004451038575667731</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5147,6 +5975,12 @@
       <c r="J138" s="2" t="n">
         <v>-0.001600000000000001</v>
       </c>
+      <c r="K138" s="1" t="n">
+        <v>2.522</v>
+      </c>
+      <c r="L138" s="3" t="n">
+        <v>0.01041666666666659</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5181,6 +6015,12 @@
       <c r="J139" s="2" t="n">
         <v>-0.004184100418410016</v>
       </c>
+      <c r="K139" s="1" t="n">
+        <v>0.01186</v>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>-0.003361344537815134</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5215,6 +6055,12 @@
       <c r="J140" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K140" s="1" t="n">
+        <v>0.01514</v>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>-0.003291639236339677</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5249,6 +6095,12 @@
       <c r="J141" s="2" t="n">
         <v>-0.001302567919613001</v>
       </c>
+      <c r="K141" s="1" t="n">
+        <v>16.113</v>
+      </c>
+      <c r="L141" s="3" t="n">
+        <v>0.0007452953232718747</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5283,6 +6135,12 @@
       <c r="J142" s="3" t="n">
         <v>0.0008032128514057291</v>
       </c>
+      <c r="K142" s="1" t="n">
+        <v>0.01248</v>
+      </c>
+      <c r="L142" s="3" t="n">
+        <v>0.001605136436597045</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5317,6 +6175,12 @@
       <c r="J143" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K143" s="1" t="n">
+        <v>0.02663</v>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>-0.00149981252343451</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5351,6 +6215,12 @@
       <c r="J144" s="3" t="n">
         <v>0.001721170395869233</v>
       </c>
+      <c r="K144" s="1" t="n">
+        <v>0.00472</v>
+      </c>
+      <c r="L144" s="3" t="n">
+        <v>0.01374570446735391</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5385,6 +6255,12 @@
       <c r="J145" s="2" t="n">
         <v>-0.001855659762274957</v>
       </c>
+      <c r="K145" s="1" t="n">
+        <v>1.9793</v>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>-0.005476836498844292</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5419,6 +6295,12 @@
       <c r="J146" s="3" t="n">
         <v>0.00260416666666656</v>
       </c>
+      <c r="K146" s="1" t="n">
+        <v>0.02301</v>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>-0.003896103896103888</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5453,6 +6335,12 @@
       <c r="J147" s="3" t="n">
         <v>0.003894947696416683</v>
       </c>
+      <c r="K147" s="1" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>-0.006761999778295083</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5487,6 +6375,12 @@
       <c r="J148" s="2" t="n">
         <v>-0.01689078386356176</v>
       </c>
+      <c r="K148" s="1" t="n">
+        <v>0.06156</v>
+      </c>
+      <c r="L148" s="3" t="n">
+        <v>0.02685571309424509</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5521,6 +6415,12 @@
       <c r="J149" s="2" t="n">
         <v>-0.001013513513513589</v>
       </c>
+      <c r="K149" s="1" t="n">
+        <v>0.05915</v>
+      </c>
+      <c r="L149" s="3" t="n">
+        <v>0.0001690902942171637</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5555,6 +6455,12 @@
       <c r="J150" s="2" t="n">
         <v>-0.006373511845111669</v>
       </c>
+      <c r="K150" s="1" t="n">
+        <v>0.2446</v>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>-0.01323220913345158</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5589,6 +6495,12 @@
       <c r="J151" s="2" t="n">
         <v>-0.002807328605200894</v>
       </c>
+      <c r="K151" s="1" t="n">
+        <v>6.75e-05</v>
+      </c>
+      <c r="L151" s="3" t="n">
+        <v>0.0001481700992738898</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5623,6 +6535,12 @@
       <c r="J152" s="3" t="n">
         <v>0.001127904353710681</v>
       </c>
+      <c r="K152" s="1" t="n">
+        <v>0.4448</v>
+      </c>
+      <c r="L152" s="3" t="n">
+        <v>0.002253267237494369</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5657,6 +6575,12 @@
       <c r="J153" s="2" t="n">
         <v>-0.00228236061297678</v>
       </c>
+      <c r="K153" s="1" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="L153" s="3" t="n">
+        <v>0.005228758169934609</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5691,6 +6615,12 @@
       <c r="J154" s="3" t="n">
         <v>0.002455661664392938</v>
       </c>
+      <c r="K154" s="1" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>-0.0002721829069134158</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5725,6 +6655,12 @@
       <c r="J155" s="3" t="n">
         <v>0.005188067444876812</v>
       </c>
+      <c r="K155" s="1" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>-0.007311827956989278</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5759,6 +6695,12 @@
       <c r="J156" s="2" t="n">
         <v>-0.0006180469715697713</v>
       </c>
+      <c r="K156" s="1" t="n">
+        <v>0.08065</v>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>-0.002473716759431116</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5793,6 +6735,12 @@
       <c r="J157" s="2" t="n">
         <v>-0.004242848394716117</v>
       </c>
+      <c r="K157" s="1" t="n">
+        <v>0.22609</v>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>-0.00685262464309237</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5827,6 +6775,12 @@
       <c r="J158" s="2" t="n">
         <v>-0.001601281024819791</v>
       </c>
+      <c r="K158" s="1" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="L158" s="3" t="n">
+        <v>0.006415396952686408</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5861,6 +6815,12 @@
       <c r="J159" s="2" t="n">
         <v>-0.003065395095367812</v>
       </c>
+      <c r="K159" s="1" t="n">
+        <v>2.927</v>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5895,6 +6855,12 @@
       <c r="J160" s="3" t="n">
         <v>0.01399999999999998</v>
       </c>
+      <c r="K160" s="1" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>-0.00197238658777126</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5929,6 +6895,12 @@
       <c r="J161" s="3" t="n">
         <v>0.001642036124794678</v>
       </c>
+      <c r="K161" s="1" t="n">
+        <v>0.14615</v>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>-0.001707650273224045</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5963,6 +6935,12 @@
       <c r="J162" s="2" t="n">
         <v>-0.001834301436869437</v>
       </c>
+      <c r="K162" s="1" t="n">
+        <v>0.003268</v>
+      </c>
+      <c r="L162" s="3" t="n">
+        <v>0.0009188361408881974</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5997,6 +6975,12 @@
       <c r="J163" s="2" t="n">
         <v>-0.002804487179487204</v>
       </c>
+      <c r="K163" s="1" t="n">
+        <v>0.004999</v>
+      </c>
+      <c r="L163" s="3" t="n">
+        <v>0.004218561671353995</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6031,6 +7015,12 @@
       <c r="J164" s="2" t="n">
         <v>-0.006224066390041528</v>
       </c>
+      <c r="K164" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="L164" s="3" t="n">
+        <v>0.00104384133611694</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6065,6 +7055,12 @@
       <c r="J165" s="2" t="n">
         <v>-0.002276422764227572</v>
       </c>
+      <c r="K165" s="1" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="L165" s="3" t="n">
+        <v>0.00130378096479777</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6099,6 +7095,12 @@
       <c r="J166" s="2" t="n">
         <v>-0.0006461803561172623</v>
       </c>
+      <c r="K166" s="1" t="n">
+        <v>1.3916</v>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>-0.0002155327250520634</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6133,6 +7135,12 @@
       <c r="J167" s="2" t="n">
         <v>-0.001439884809215304</v>
       </c>
+      <c r="K167" s="1" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>-0.001441961067051031</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6167,6 +7175,12 @@
       <c r="J168" s="2" t="n">
         <v>-0.003174603174603177</v>
       </c>
+      <c r="K168" s="1" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>-0.003184713375796181</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6201,6 +7215,12 @@
       <c r="J169" s="2" t="n">
         <v>-0.001686340640809375</v>
       </c>
+      <c r="K169" s="1" t="n">
+        <v>0.02961</v>
+      </c>
+      <c r="L169" s="3" t="n">
+        <v>0.000337837837837824</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6235,6 +7255,12 @@
       <c r="J170" s="3" t="n">
         <v>0.0006860278984679224</v>
       </c>
+      <c r="K170" s="1" t="n">
+        <v>0.04345</v>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>-0.007084095063985324</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6269,6 +7295,12 @@
       <c r="J171" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K171" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6303,6 +7335,12 @@
       <c r="J172" s="3" t="n">
         <v>0.02459016393442627</v>
       </c>
+      <c r="K172" s="1" t="n">
+        <v>1.4e-05</v>
+      </c>
+      <c r="L172" s="3" t="n">
+        <v>0.1199999999999999</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6337,6 +7375,12 @@
       <c r="J173" s="2" t="n">
         <v>-0.0004743833017079251</v>
       </c>
+      <c r="K173" s="1" t="n">
+        <v>0.02107</v>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6371,6 +7415,12 @@
       <c r="J174" s="2" t="n">
         <v>-0.002102235007745029</v>
       </c>
+      <c r="K174" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>-0.003215434083601424</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6405,6 +7455,12 @@
       <c r="J175" s="2" t="n">
         <v>-0.001106500691562964</v>
       </c>
+      <c r="K175" s="1" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="L175" s="3" t="n">
+        <v>0.002769315978953201</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6439,6 +7495,12 @@
       <c r="J176" s="2" t="n">
         <v>-0.0004653327128896972</v>
       </c>
+      <c r="K176" s="1" t="n">
+        <v>0.02142</v>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>-0.002793296089385361</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6473,6 +7535,12 @@
       <c r="J177" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K177" s="1" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>-0.006249999999999962</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6507,6 +7575,12 @@
       <c r="J178" s="2" t="n">
         <v>-0.003061224489795882</v>
       </c>
+      <c r="K178" s="1" t="n">
+        <v>0.000973</v>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>-0.004094165813715444</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6541,6 +7615,12 @@
       <c r="J179" s="3" t="n">
         <v>0.0007406116580987912</v>
       </c>
+      <c r="K179" s="1" t="n">
+        <v>0.022936</v>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>-0.001523660267293407</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6575,6 +7655,12 @@
       <c r="J180" s="2" t="n">
         <v>-0.01665124884366329</v>
       </c>
+      <c r="K180" s="1" t="n">
+        <v>4.228</v>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>-0.005644402634054568</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6609,6 +7695,12 @@
       <c r="J181" s="3" t="n">
         <v>0.01053358659989657</v>
       </c>
+      <c r="K181" s="1" t="n">
+        <v>0.5782</v>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>-0.01196172248803829</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6643,6 +7735,12 @@
       <c r="J182" s="2" t="n">
         <v>-0.003021756647864572</v>
       </c>
+      <c r="K182" s="1" t="n">
+        <v>0.04945</v>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>-0.0008082440897150611</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6677,6 +7775,12 @@
       <c r="J183" s="2" t="n">
         <v>-0.000182781941144276</v>
       </c>
+      <c r="K183" s="1" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>-0.0005484460694698563</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6711,6 +7815,12 @@
       <c r="J184" s="3" t="n">
         <v>0.003844809507165307</v>
       </c>
+      <c r="K184" s="1" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="L184" s="2" t="n">
+        <v>-0.005571030640668529</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6745,6 +7855,12 @@
       <c r="J185" s="2" t="n">
         <v>-0.0005402485143165636</v>
       </c>
+      <c r="K185" s="1" t="n">
+        <v>0.01861</v>
+      </c>
+      <c r="L185" s="3" t="n">
+        <v>0.005945945945946079</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6779,6 +7895,12 @@
       <c r="J186" s="2" t="n">
         <v>-0.006329113924050786</v>
       </c>
+      <c r="K186" s="1" t="n">
+        <v>3.14e-05</v>
+      </c>
+      <c r="L186" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6813,6 +7935,12 @@
       <c r="J187" s="2" t="n">
         <v>-0.005555555555555544</v>
       </c>
+      <c r="K187" s="1" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="L187" s="2" t="n">
+        <v>-0.000620732464307858</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6847,6 +7975,12 @@
       <c r="J188" s="2" t="n">
         <v>-0.001977750309023405</v>
       </c>
+      <c r="K188" s="1" t="n">
+        <v>0.04036</v>
+      </c>
+      <c r="L188" s="2" t="n">
+        <v>-0.0002477086945752554</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6881,6 +8015,12 @@
       <c r="J189" s="2" t="n">
         <v>-0.002057142857142907</v>
       </c>
+      <c r="K189" s="1" t="n">
+        <v>0.0004367</v>
+      </c>
+      <c r="L189" s="3" t="n">
+        <v>0.0002290426019239634</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6915,6 +8055,12 @@
       <c r="J190" s="3" t="n">
         <v>0.001745200698080359</v>
       </c>
+      <c r="K190" s="1" t="n">
+        <v>0.02314</v>
+      </c>
+      <c r="L190" s="3" t="n">
+        <v>0.007839721254355383</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6949,6 +8095,12 @@
       <c r="J191" s="2" t="n">
         <v>-0.000634115409004413</v>
       </c>
+      <c r="K191" s="1" t="n">
+        <v>0.01571</v>
+      </c>
+      <c r="L191" s="2" t="n">
+        <v>-0.003172588832487401</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6983,6 +8135,12 @@
       <c r="J192" s="3" t="n">
         <v>0.001076040172166508</v>
       </c>
+      <c r="K192" s="1" t="n">
+        <v>0.05595</v>
+      </c>
+      <c r="L192" s="3" t="n">
+        <v>0.002328914367610143</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7017,6 +8175,12 @@
       <c r="J193" s="2" t="n">
         <v>-0.003735325506937066</v>
       </c>
+      <c r="K193" s="1" t="n">
+        <v>0.1864</v>
+      </c>
+      <c r="L193" s="2" t="n">
+        <v>-0.001606855918585938</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7051,6 +8215,12 @@
       <c r="J194" s="2" t="n">
         <v>-0.002602811035918867</v>
       </c>
+      <c r="K194" s="1" t="n">
+        <v>0.01912</v>
+      </c>
+      <c r="L194" s="2" t="n">
+        <v>-0.002087682672233735</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7085,6 +8255,12 @@
       <c r="J195" s="2" t="n">
         <v>-0.00598940336328033</v>
       </c>
+      <c r="K195" s="1" t="n">
+        <v>0.4338</v>
+      </c>
+      <c r="L195" s="3" t="n">
+        <v>0.005330243337195885</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7119,6 +8295,12 @@
       <c r="J196" s="2" t="n">
         <v>-0.0007936507936507613</v>
       </c>
+      <c r="K196" s="1" t="n">
+        <v>0.01253</v>
+      </c>
+      <c r="L196" s="2" t="n">
+        <v>-0.00476568705321692</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7153,6 +8335,12 @@
       <c r="J197" s="2" t="n">
         <v>-0.001746343593101872</v>
       </c>
+      <c r="K197" s="1" t="n">
+        <v>0.0457</v>
+      </c>
+      <c r="L197" s="2" t="n">
+        <v>-0.0006560244915810681</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7187,6 +8375,12 @@
       <c r="J198" s="3" t="n">
         <v>0.0007863180656574718</v>
       </c>
+      <c r="K198" s="1" t="n">
+        <v>0.5124</v>
+      </c>
+      <c r="L198" s="3" t="n">
+        <v>0.00648202710665875</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7221,6 +8415,12 @@
       <c r="J199" s="3" t="n">
         <v>0.0116279069767442</v>
       </c>
+      <c r="K199" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="L199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7255,6 +8455,12 @@
       <c r="J200" s="2" t="n">
         <v>-0.002024291497975785</v>
       </c>
+      <c r="K200" s="1" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="L200" s="3" t="n">
+        <v>0.0006761325219744127</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7289,6 +8495,12 @@
       <c r="J201" s="2" t="n">
         <v>-0.001937301866854478</v>
       </c>
+      <c r="K201" s="1" t="n">
+        <v>0.005657</v>
+      </c>
+      <c r="L201" s="2" t="n">
+        <v>-0.001764602082230538</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7323,6 +8535,12 @@
       <c r="J202" s="2" t="n">
         <v>-0.0001325088339222408</v>
       </c>
+      <c r="K202" s="1" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="L202" s="3" t="n">
+        <v>0.02487078676503059</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7357,6 +8575,12 @@
       <c r="J203" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K203" s="1" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="L203" s="2" t="n">
+        <v>-0.003610108303249076</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7391,6 +8615,12 @@
       <c r="J204" s="2" t="n">
         <v>-0.005277044854881255</v>
       </c>
+      <c r="K204" s="1" t="n">
+        <v>0.03388</v>
+      </c>
+      <c r="L204" s="2" t="n">
+        <v>-0.001473622163277378</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7425,6 +8655,12 @@
       <c r="J205" s="2" t="n">
         <v>-0.000698812019566763</v>
       </c>
+      <c r="K205" s="1" t="n">
+        <v>4.257</v>
+      </c>
+      <c r="L205" s="2" t="n">
+        <v>-0.007692307692307777</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7459,6 +8695,12 @@
       <c r="J206" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K206" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="L206" s="2" t="n">
+        <v>-0.002762430939226522</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7493,6 +8735,12 @@
       <c r="J207" s="3" t="n">
         <v>0.005200367084735464</v>
       </c>
+      <c r="K207" s="1" t="n">
+        <v>0.0009736</v>
+      </c>
+      <c r="L207" s="2" t="n">
+        <v>-0.01237573544329476</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7527,6 +8775,12 @@
       <c r="J208" s="2" t="n">
         <v>-0.0008218052321599683</v>
       </c>
+      <c r="K208" s="1" t="n">
+        <v>0.007311</v>
+      </c>
+      <c r="L208" s="3" t="n">
+        <v>0.002193283070596233</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7561,6 +8815,12 @@
       <c r="J209" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K209" s="1" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="L209" s="2" t="n">
+        <v>-0.001666666666666599</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7595,6 +8855,12 @@
       <c r="J210" s="2" t="n">
         <v>-0.001543209876543254</v>
       </c>
+      <c r="K210" s="1" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="L210" s="3" t="n">
+        <v>0.002318392581143914</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7629,6 +8895,12 @@
       <c r="J211" s="2" t="n">
         <v>-0.001545160837196319</v>
       </c>
+      <c r="K211" s="1" t="n">
+        <v>0.007109</v>
+      </c>
+      <c r="L211" s="3" t="n">
+        <v>0.0001406865503658037</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7663,6 +8935,12 @@
       <c r="J212" s="2" t="n">
         <v>-0.01162790697674423</v>
       </c>
+      <c r="K212" s="1" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="L212" s="2" t="n">
+        <v>-0.009342560553633149</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7697,6 +8975,12 @@
       <c r="J213" s="2" t="n">
         <v>-0.003139717425431704</v>
       </c>
+      <c r="K213" s="1" t="n">
+        <v>0.05716</v>
+      </c>
+      <c r="L213" s="3" t="n">
+        <v>0.0001749781277340868</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7731,6 +9015,12 @@
       <c r="J214" s="2" t="n">
         <v>-0.001062134891131204</v>
       </c>
+      <c r="K214" s="1" t="n">
+        <v>0.1881</v>
+      </c>
+      <c r="L214" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7765,6 +9055,12 @@
       <c r="J215" s="2" t="n">
         <v>-0.002852253280091222</v>
       </c>
+      <c r="K215" s="1" t="n">
+        <v>0.05242</v>
+      </c>
+      <c r="L215" s="2" t="n">
+        <v>-0.0003813882532417846</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7799,6 +9095,12 @@
       <c r="J216" s="2" t="n">
         <v>-0.005233111322550028</v>
       </c>
+      <c r="K216" s="1" t="n">
+        <v>0.002086</v>
+      </c>
+      <c r="L216" s="2" t="n">
+        <v>-0.002391200382591964</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7833,6 +9135,12 @@
       <c r="J217" s="2" t="n">
         <v>-0.001161054901310279</v>
       </c>
+      <c r="K217" s="1" t="n">
+        <v>6.021</v>
+      </c>
+      <c r="L217" s="2" t="n">
+        <v>-0.0001660577881103178</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7867,6 +9175,12 @@
       <c r="J218" s="2" t="n">
         <v>-0.001357466063348468</v>
       </c>
+      <c r="K218" s="1" t="n">
+        <v>4.417</v>
+      </c>
+      <c r="L218" s="3" t="n">
+        <v>0.0006796556411418473</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7901,6 +9215,12 @@
       <c r="J219" s="2" t="n">
         <v>-0.004087699739873552</v>
       </c>
+      <c r="K219" s="1" t="n">
+        <v>0.005354</v>
+      </c>
+      <c r="L219" s="2" t="n">
+        <v>-0.001119402985074613</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7935,6 +9255,12 @@
       <c r="J220" s="2" t="n">
         <v>-0.002181818181818177</v>
       </c>
+      <c r="K220" s="1" t="n">
+        <v>0.04114</v>
+      </c>
+      <c r="L220" s="2" t="n">
+        <v>-0.0004859086491739355</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7969,6 +9295,12 @@
       <c r="J221" s="2" t="n">
         <v>-0.0005184033177811528</v>
       </c>
+      <c r="K221" s="1" t="n">
+        <v>0.005778</v>
+      </c>
+      <c r="L221" s="2" t="n">
+        <v>-0.001037344398340237</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8003,6 +9335,12 @@
       <c r="J222" s="2" t="n">
         <v>-0.00220264317180623</v>
       </c>
+      <c r="K222" s="1" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="L222" s="3" t="n">
+        <v>0.003311258278145637</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8037,6 +9375,12 @@
       <c r="J223" s="2" t="n">
         <v>-0.001477978125923738</v>
       </c>
+      <c r="K223" s="1" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="L223" s="2" t="n">
+        <v>-0.001480165778567201</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8071,6 +9415,12 @@
       <c r="J224" s="2" t="n">
         <v>-0.0009222965183305418</v>
       </c>
+      <c r="K224" s="1" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="L224" s="2" t="n">
+        <v>-0.0002307869836142268</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8105,6 +9455,12 @@
       <c r="J225" s="3" t="n">
         <v>0.000599448507373317</v>
       </c>
+      <c r="K225" s="1" t="n">
+        <v>0.08352999999999999</v>
+      </c>
+      <c r="L225" s="3" t="n">
+        <v>0.0008387251377903994</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8139,6 +9495,12 @@
       <c r="J226" s="2" t="n">
         <v>-0.001067235859124823</v>
       </c>
+      <c r="K226" s="1" t="n">
+        <v>0.01881</v>
+      </c>
+      <c r="L226" s="3" t="n">
+        <v>0.004807692307692297</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8173,6 +9535,12 @@
       <c r="J227" s="2" t="n">
         <v>-0.004273504273504248</v>
       </c>
+      <c r="K227" s="1" t="n">
+        <v>0.04667</v>
+      </c>
+      <c r="L227" s="3" t="n">
+        <v>0.001502145922746794</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8207,6 +9575,12 @@
       <c r="J228" s="2" t="n">
         <v>-0.003434950622584809</v>
       </c>
+      <c r="K228" s="1" t="n">
+        <v>0.02319</v>
+      </c>
+      <c r="L228" s="2" t="n">
+        <v>-0.0008616975441621135</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8241,6 +9615,12 @@
       <c r="J229" s="2" t="n">
         <v>-0.003710575139146674</v>
       </c>
+      <c r="K229" s="1" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="L229" s="3" t="n">
+        <v>0.001862197392923703</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8275,6 +9655,12 @@
       <c r="J230" s="2" t="n">
         <v>-0.004764740917212597</v>
       </c>
+      <c r="K230" s="1" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="L230" s="2" t="n">
+        <v>-0.0005984440454816815</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8309,6 +9695,12 @@
       <c r="J231" s="2" t="n">
         <v>-0.004578155657292388</v>
       </c>
+      <c r="K231" s="1" t="n">
+        <v>0.03045</v>
+      </c>
+      <c r="L231" s="3" t="n">
+        <v>0.0003285151116952386</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8343,6 +9735,12 @@
       <c r="J232" s="2" t="n">
         <v>-0.003018542475204707</v>
       </c>
+      <c r="K232" s="1" t="n">
+        <v>0.02314</v>
+      </c>
+      <c r="L232" s="3" t="n">
+        <v>0.0008650519031141515</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8377,6 +9775,12 @@
       <c r="J233" s="3" t="n">
         <v>0.04595787195071183</v>
       </c>
+      <c r="K233" s="1" t="n">
+        <v>0.12873</v>
+      </c>
+      <c r="L233" s="3" t="n">
+        <v>0.02467563480060511</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8411,6 +9815,12 @@
       <c r="J234" s="3" t="n">
         <v>0.0003960396039603524</v>
       </c>
+      <c r="K234" s="1" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="L234" s="3" t="n">
+        <v>0.001979414093428347</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8445,6 +9855,12 @@
       <c r="J235" s="2" t="n">
         <v>-0.00028776978417275</v>
       </c>
+      <c r="K235" s="1" t="n">
+        <v>0.06937</v>
+      </c>
+      <c r="L235" s="2" t="n">
+        <v>-0.001583189407023589</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8479,6 +9895,12 @@
       <c r="J236" s="2" t="n">
         <v>-0.0006547180620345098</v>
       </c>
+      <c r="K236" s="1" t="n">
+        <v>0.12511</v>
+      </c>
+      <c r="L236" s="3" t="n">
+        <v>0.024568012447793</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8513,6 +9935,12 @@
       <c r="J237" s="3" t="n">
         <v>0.00573514077163725</v>
       </c>
+      <c r="K237" s="1" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="L237" s="3" t="n">
+        <v>0.002073613271124851</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8547,6 +9975,12 @@
       <c r="J238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K238" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8581,6 +10015,12 @@
       <c r="J239" s="2" t="n">
         <v>-0.01185185185185171</v>
       </c>
+      <c r="K239" s="1" t="n">
+        <v>0.003998</v>
+      </c>
+      <c r="L239" s="2" t="n">
+        <v>-0.0009995002498751951</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8615,6 +10055,12 @@
       <c r="J240" s="2" t="n">
         <v>-0.001455604075691479</v>
       </c>
+      <c r="K240" s="1" t="n">
+        <v>0.01376</v>
+      </c>
+      <c r="L240" s="3" t="n">
+        <v>0.00291545189504374</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8649,6 +10095,12 @@
       <c r="J241" s="3" t="n">
         <v>0.0006988120195666595</v>
       </c>
+      <c r="K241" s="1" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="L241" s="3" t="n">
+        <v>0.001629422718808273</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8683,6 +10135,12 @@
       <c r="J242" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K242" s="1" t="n">
+        <v>0.00739</v>
+      </c>
+      <c r="L242" s="3" t="n">
+        <v>0.001355013550135446</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8717,6 +10175,12 @@
       <c r="J243" s="2" t="n">
         <v>-0.001733102253032858</v>
       </c>
+      <c r="K243" s="1" t="n">
+        <v>0.02301</v>
+      </c>
+      <c r="L243" s="2" t="n">
+        <v>-0.001302083333333431</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8751,6 +10215,12 @@
       <c r="J244" s="2" t="n">
         <v>-0.002960331557134407</v>
       </c>
+      <c r="K244" s="1" t="n">
+        <v>0.001676</v>
+      </c>
+      <c r="L244" s="2" t="n">
+        <v>-0.004750593824228016</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8785,6 +10255,12 @@
       <c r="J245" s="2" t="n">
         <v>-0.001514004542013669</v>
       </c>
+      <c r="K245" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="L245" s="2" t="n">
+        <v>-0.0007581501137224336</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8819,6 +10295,12 @@
       <c r="J246" s="3" t="n">
         <v>0.01243622448979597</v>
       </c>
+      <c r="K246" s="1" t="n">
+        <v>0.03187</v>
+      </c>
+      <c r="L246" s="3" t="n">
+        <v>0.003779527559055183</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8853,6 +10335,12 @@
       <c r="J247" s="2" t="n">
         <v>-0.004484304932735399</v>
       </c>
+      <c r="K247" s="1" t="n">
+        <v>0.1772</v>
+      </c>
+      <c r="L247" s="2" t="n">
+        <v>-0.002252252252252317</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8887,6 +10375,12 @@
       <c r="J248" s="2" t="n">
         <v>-0.0006508298080051801</v>
       </c>
+      <c r="K248" s="1" t="n">
+        <v>0.03086</v>
+      </c>
+      <c r="L248" s="3" t="n">
+        <v>0.004884402474763835</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8921,6 +10415,12 @@
       <c r="J249" s="3" t="n">
         <v>0.005200508494163863</v>
       </c>
+      <c r="K249" s="1" t="n">
+        <v>0.008474000000000001</v>
+      </c>
+      <c r="L249" s="2" t="n">
+        <v>-0.02575304667739693</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8955,6 +10455,12 @@
       <c r="J250" s="2" t="n">
         <v>-0.01189343482397717</v>
       </c>
+      <c r="K250" s="1" t="n">
+        <v>0.02063</v>
+      </c>
+      <c r="L250" s="2" t="n">
+        <v>-0.006740491092922543</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8989,6 +10495,12 @@
       <c r="J251" s="2" t="n">
         <v>-0.001707212974818539</v>
       </c>
+      <c r="K251" s="1" t="n">
+        <v>0.04686</v>
+      </c>
+      <c r="L251" s="3" t="n">
+        <v>0.001710132535271414</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9023,6 +10535,12 @@
       <c r="J252" s="2" t="n">
         <v>-0.003204747774480828</v>
       </c>
+      <c r="K252" s="1" t="n">
+        <v>0.00844</v>
+      </c>
+      <c r="L252" s="3" t="n">
+        <v>0.005001190759704737</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9057,6 +10575,12 @@
       <c r="J253" s="2" t="n">
         <v>-0.03380423814328963</v>
       </c>
+      <c r="K253" s="1" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="L253" s="3" t="n">
+        <v>0.009399477806788492</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9091,6 +10615,12 @@
       <c r="J254" s="2" t="n">
         <v>-0.0001634521085321367</v>
       </c>
+      <c r="K254" s="1" t="n">
+        <v>0.06111</v>
+      </c>
+      <c r="L254" s="2" t="n">
+        <v>-0.0009808729769495584</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9125,6 +10655,12 @@
       <c r="J255" s="3" t="n">
         <v>0.006186726659167571</v>
       </c>
+      <c r="K255" s="1" t="n">
+        <v>0.003572</v>
+      </c>
+      <c r="L255" s="2" t="n">
+        <v>-0.001676914477361635</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9159,6 +10695,12 @@
       <c r="J256" s="3" t="n">
         <v>0.005238782172955707</v>
       </c>
+      <c r="K256" s="1" t="n">
+        <v>0.013284</v>
+      </c>
+      <c r="L256" s="3" t="n">
+        <v>0.003323262839879202</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9193,6 +10735,12 @@
       <c r="J257" s="2" t="n">
         <v>-1.000626392150242e-06</v>
       </c>
+      <c r="K257" s="1" t="n">
+        <v>0.999373</v>
+      </c>
+      <c r="L257" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9227,6 +10775,12 @@
       <c r="J258" s="3" t="n">
         <v>0.005945441827932041</v>
       </c>
+      <c r="K258" s="1" t="n">
+        <v>0.08723</v>
+      </c>
+      <c r="L258" s="3" t="n">
+        <v>0.01089349866728469</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9261,6 +10815,12 @@
       <c r="J259" s="2" t="n">
         <v>-0.001790309947409728</v>
       </c>
+      <c r="K259" s="1" t="n">
+        <v>0.08928</v>
+      </c>
+      <c r="L259" s="3" t="n">
+        <v>0.000784665396256032</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9295,6 +10855,12 @@
       <c r="J260" s="2" t="n">
         <v>-0.008641674780915315</v>
       </c>
+      <c r="K260" s="1" t="n">
+        <v>0.08153000000000001</v>
+      </c>
+      <c r="L260" s="3" t="n">
+        <v>0.0009821976672806706</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9329,6 +10895,12 @@
       <c r="J261" s="3" t="n">
         <v>0.002680965147453185</v>
       </c>
+      <c r="K261" s="1" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="L261" s="3" t="n">
+        <v>0.004456327985739655</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9363,6 +10935,12 @@
       <c r="J262" s="3" t="n">
         <v>0.004899292324441967</v>
       </c>
+      <c r="K262" s="1" t="n">
+        <v>0.003657</v>
+      </c>
+      <c r="L262" s="2" t="n">
+        <v>-0.009479956663055221</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9397,6 +10975,12 @@
       <c r="J263" s="2" t="n">
         <v>-0.001699235344095206</v>
       </c>
+      <c r="K263" s="1" t="n">
+        <v>0.1166</v>
+      </c>
+      <c r="L263" s="2" t="n">
+        <v>-0.00765957446808509</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9431,6 +11015,12 @@
       <c r="J264" s="2" t="n">
         <v>-0.0001738828029908827</v>
       </c>
+      <c r="K264" s="1" t="n">
+        <v>0.0005767</v>
+      </c>
+      <c r="L264" s="3" t="n">
+        <v>0.002956521739130412</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9465,6 +11055,12 @@
       <c r="J265" s="2" t="n">
         <v>-0.005312084993359907</v>
       </c>
+      <c r="K265" s="1" t="n">
+        <v>0.01494</v>
+      </c>
+      <c r="L265" s="2" t="n">
+        <v>-0.002670226969292397</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9499,6 +11095,12 @@
       <c r="J266" s="2" t="n">
         <v>-0.0015698587127159</v>
       </c>
+      <c r="K266" s="1" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="L266" s="2" t="n">
+        <v>-0.001572327044025202</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9533,6 +11135,12 @@
       <c r="J267" s="2" t="n">
         <v>-0.0006086427267193909</v>
       </c>
+      <c r="K267" s="1" t="n">
+        <v>0.01634</v>
+      </c>
+      <c r="L267" s="2" t="n">
+        <v>-0.004872107186358113</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9567,6 +11175,12 @@
       <c r="J268" s="2" t="n">
         <v>-0.003031716417910522</v>
       </c>
+      <c r="K268" s="1" t="n">
+        <v>0.0004317</v>
+      </c>
+      <c r="L268" s="3" t="n">
+        <v>0.009824561403508757</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9601,6 +11215,12 @@
       <c r="J269" s="3" t="n">
         <v>0.0004803073967338901</v>
       </c>
+      <c r="K269" s="1" t="n">
+        <v>0.02075</v>
+      </c>
+      <c r="L269" s="2" t="n">
+        <v>-0.003840614498319741</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9635,6 +11255,12 @@
       <c r="J270" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K270" s="1" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="L270" s="3" t="n">
+        <v>0.0005537098560353764</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9669,6 +11295,12 @@
       <c r="J271" s="2" t="n">
         <v>-0.0006816632583502998</v>
       </c>
+      <c r="K271" s="1" t="n">
+        <v>0.1468</v>
+      </c>
+      <c r="L271" s="3" t="n">
+        <v>0.00136425648021832</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9703,6 +11335,12 @@
       <c r="J272" s="3" t="n">
         <v>0.001009336361342376</v>
       </c>
+      <c r="K272" s="1" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="L272" s="3" t="n">
+        <v>0.003024955886060047</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9737,6 +11375,12 @@
       <c r="J273" s="3" t="n">
         <v>0.001072961373390559</v>
       </c>
+      <c r="K273" s="1" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="L273" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9771,6 +11415,12 @@
       <c r="J274" s="3" t="n">
         <v>0.000632511068943693</v>
       </c>
+      <c r="K274" s="1" t="n">
+        <v>63.13</v>
+      </c>
+      <c r="L274" s="2" t="n">
+        <v>-0.002370417193426021</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9805,6 +11455,12 @@
       <c r="J275" s="2" t="n">
         <v>-0.003460207612456756</v>
       </c>
+      <c r="K275" s="1" t="n">
+        <v>0.01145</v>
+      </c>
+      <c r="L275" s="2" t="n">
+        <v>-0.006076388888888942</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9839,6 +11495,12 @@
       <c r="J276" s="2" t="n">
         <v>-0.002695417789757458</v>
       </c>
+      <c r="K276" s="1" t="n">
+        <v>2.587</v>
+      </c>
+      <c r="L276" s="2" t="n">
+        <v>-0.001158301158301031</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9873,6 +11535,12 @@
       <c r="J277" s="2" t="n">
         <v>-0.001901140684410569</v>
       </c>
+      <c r="K277" s="1" t="n">
+        <v>0.04202</v>
+      </c>
+      <c r="L277" s="3" t="n">
+        <v>0.0004761904761904568</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9907,6 +11575,12 @@
       <c r="J278" s="2" t="n">
         <v>-0.001565762004175302</v>
       </c>
+      <c r="K278" s="1" t="n">
+        <v>0.01931</v>
+      </c>
+      <c r="L278" s="3" t="n">
+        <v>0.009409304756926272</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9941,6 +11615,12 @@
       <c r="J279" s="3" t="n">
         <v>0.004115962777380026</v>
       </c>
+      <c r="K279" s="1" t="n">
+        <v>0.005594</v>
+      </c>
+      <c r="L279" s="2" t="n">
+        <v>-0.003029762965603218</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9975,6 +11655,12 @@
       <c r="J280" s="3" t="n">
         <v>0.003922594142259345</v>
       </c>
+      <c r="K280" s="1" t="n">
+        <v>0.03828</v>
+      </c>
+      <c r="L280" s="2" t="n">
+        <v>-0.002865329512893956</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10009,6 +11695,12 @@
       <c r="J281" s="2" t="n">
         <v>-0.001107419712070876</v>
       </c>
+      <c r="K281" s="1" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="L281" s="3" t="n">
+        <v>0.001108647450110866</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10043,6 +11735,12 @@
       <c r="J282" s="2" t="n">
         <v>-0.002986560477849749</v>
       </c>
+      <c r="K282" s="1" t="n">
+        <v>0.000401</v>
+      </c>
+      <c r="L282" s="3" t="n">
+        <v>0.0009985022466300793</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10077,6 +11775,12 @@
       <c r="J283" s="3" t="n">
         <v>0.001520527116066841</v>
       </c>
+      <c r="K283" s="1" t="n">
+        <v>0.04002</v>
+      </c>
+      <c r="L283" s="3" t="n">
+        <v>0.01265182186234819</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10111,6 +11815,12 @@
       <c r="J284" s="2" t="n">
         <v>-0.002624045801526693</v>
       </c>
+      <c r="K284" s="1" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="L284" s="2" t="n">
+        <v>-0.0004783544606553261</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10145,6 +11855,12 @@
       <c r="J285" s="3" t="n">
         <v>0.005691891387515157</v>
       </c>
+      <c r="K285" s="1" t="n">
+        <v>0.10789</v>
+      </c>
+      <c r="L285" s="3" t="n">
+        <v>0.001020597513453321</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10179,6 +11895,12 @@
       <c r="J286" s="2" t="n">
         <v>-0.002392344497607558</v>
       </c>
+      <c r="K286" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="L286" s="3" t="n">
+        <v>0.002398081534772085</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10213,6 +11935,12 @@
       <c r="J287" s="2" t="n">
         <v>-0.002046880158468172</v>
       </c>
+      <c r="K287" s="1" t="n">
+        <v>0.1511</v>
+      </c>
+      <c r="L287" s="2" t="n">
+        <v>-0.000264655286489245</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -10247,6 +11975,12 @@
       <c r="J288" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K288" s="1" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="L288" s="2" t="n">
+        <v>-0.00328947368421062</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -10281,6 +12015,12 @@
       <c r="J289" s="2" t="n">
         <v>-0.002174438270113636</v>
       </c>
+      <c r="K289" s="1" t="n">
+        <v>4.132</v>
+      </c>
+      <c r="L289" s="3" t="n">
+        <v>0.0004842615012106004</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10315,6 +12055,12 @@
       <c r="J290" s="2" t="n">
         <v>-0.002347142354183686</v>
       </c>
+      <c r="K290" s="1" t="n">
+        <v>0.08505</v>
+      </c>
+      <c r="L290" s="3" t="n">
+        <v>0.0004705328784848649</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10349,6 +12095,12 @@
       <c r="J291" s="3" t="n">
         <v>0.001979078314956195</v>
       </c>
+      <c r="K291" s="1" t="n">
+        <v>0.03541</v>
+      </c>
+      <c r="L291" s="2" t="n">
+        <v>-0.000846501128668235</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10383,6 +12135,12 @@
       <c r="J292" s="2" t="n">
         <v>-0.004514363885088878</v>
       </c>
+      <c r="K292" s="1" t="n">
+        <v>1.4589</v>
+      </c>
+      <c r="L292" s="3" t="n">
+        <v>0.002404837158169616</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10417,6 +12175,12 @@
       <c r="J293" s="2" t="n">
         <v>-0.002042553191489337</v>
       </c>
+      <c r="K293" s="1" t="n">
+        <v>0.005852</v>
+      </c>
+      <c r="L293" s="2" t="n">
+        <v>-0.001876172607879878</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10451,6 +12215,12 @@
       <c r="J294" s="2" t="n">
         <v>-0.002619324796274707</v>
       </c>
+      <c r="K294" s="1" t="n">
+        <v>0.003407</v>
+      </c>
+      <c r="L294" s="2" t="n">
+        <v>-0.005836008170411454</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10485,6 +12255,12 @@
       <c r="J295" s="2" t="n">
         <v>-0.001485332343111814</v>
       </c>
+      <c r="K295" s="1" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="L295" s="3" t="n">
+        <v>0.00223131275567142</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -10519,6 +12295,12 @@
       <c r="J296" s="2" t="n">
         <v>-0.000444642063139124</v>
       </c>
+      <c r="K296" s="1" t="n">
+        <v>2.249</v>
+      </c>
+      <c r="L296" s="3" t="n">
+        <v>0.0004448398576511965</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -10553,6 +12335,12 @@
       <c r="J297" s="3" t="n">
         <v>0.0005885815185402938</v>
       </c>
+      <c r="K297" s="1" t="n">
+        <v>0.01707</v>
+      </c>
+      <c r="L297" s="3" t="n">
+        <v>0.004117647058823361</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -10587,6 +12375,12 @@
       <c r="J298" s="2" t="n">
         <v>-0.000276778300581204</v>
       </c>
+      <c r="K298" s="1" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="L298" s="2" t="n">
+        <v>-0.004152823920265785</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -10621,6 +12415,12 @@
       <c r="J299" s="2" t="n">
         <v>-0.00360036003600361</v>
       </c>
+      <c r="K299" s="1" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="L299" s="2" t="n">
+        <v>-0.0009033423667569641</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -10655,6 +12455,12 @@
       <c r="J300" s="2" t="n">
         <v>-0.002403846153846056</v>
       </c>
+      <c r="K300" s="1" t="n">
+        <v>0.02068</v>
+      </c>
+      <c r="L300" s="2" t="n">
+        <v>-0.003373493975903644</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10689,6 +12495,12 @@
       <c r="J301" s="2" t="n">
         <v>-0.0006626905235256245</v>
       </c>
+      <c r="K301" s="1" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="L301" s="2" t="n">
+        <v>-0.000331564986737364</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -10723,6 +12535,12 @@
       <c r="J302" s="2" t="n">
         <v>-0.0007369196757554405</v>
       </c>
+      <c r="K302" s="1" t="n">
+        <v>0.01356</v>
+      </c>
+      <c r="L302" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10757,6 +12575,12 @@
       <c r="J303" s="2" t="n">
         <v>-0.0005411255411255191</v>
       </c>
+      <c r="K303" s="1" t="n">
+        <v>0.07396999999999999</v>
+      </c>
+      <c r="L303" s="3" t="n">
+        <v>0.001218191662154749</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -10791,6 +12615,12 @@
       <c r="J304" s="2" t="n">
         <v>-0.001878522229179852</v>
       </c>
+      <c r="K304" s="1" t="n">
+        <v>0.01589</v>
+      </c>
+      <c r="L304" s="2" t="n">
+        <v>-0.003136762860727601</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10825,6 +12655,12 @@
       <c r="J305" s="2" t="n">
         <v>-0.002607761926675924</v>
       </c>
+      <c r="K305" s="1" t="n">
+        <v>0.06508</v>
+      </c>
+      <c r="L305" s="3" t="n">
+        <v>0.0009227929867733697</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -10859,6 +12695,12 @@
       <c r="J306" s="2" t="n">
         <v>-0.005366726296958843</v>
       </c>
+      <c r="K306" s="1" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="L306" s="2" t="n">
+        <v>-0.002797761790567571</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10893,6 +12735,12 @@
       <c r="J307" s="2" t="n">
         <v>-0.002145922746781118</v>
       </c>
+      <c r="K307" s="1" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="L307" s="2" t="n">
+        <v>-0.003225806451612906</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -10927,6 +12775,12 @@
       <c r="J308" s="2" t="n">
         <v>-0.003523785552479266</v>
       </c>
+      <c r="K308" s="1" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="L308" s="3" t="n">
+        <v>0.005051780752715301</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -10961,6 +12815,12 @@
       <c r="J309" s="2" t="n">
         <v>-0.001250781738586566</v>
       </c>
+      <c r="K309" s="1" t="n">
+        <v>0.01581</v>
+      </c>
+      <c r="L309" s="2" t="n">
+        <v>-0.01001878522229182</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -10995,6 +12855,12 @@
       <c r="J310" s="2" t="n">
         <v>-0.002580645161290346</v>
       </c>
+      <c r="K310" s="1" t="n">
+        <v>0.05427</v>
+      </c>
+      <c r="L310" s="3" t="n">
+        <v>0.002956939567547596</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -11029,6 +12895,12 @@
       <c r="J311" s="2" t="n">
         <v>-0.005129348795718209</v>
       </c>
+      <c r="K311" s="1" t="n">
+        <v>0.004465</v>
+      </c>
+      <c r="L311" s="3" t="n">
+        <v>0.0008966599417172228</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11063,6 +12935,12 @@
       <c r="J312" s="2" t="n">
         <v>-0.001301929222393171</v>
       </c>
+      <c r="K312" s="1" t="n">
+        <v>0.08457000000000001</v>
+      </c>
+      <c r="L312" s="3" t="n">
+        <v>0.002251718416686533</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11097,6 +12975,12 @@
       <c r="J313" s="3" t="n">
         <v>0.0004005340453938885</v>
       </c>
+      <c r="K313" s="1" t="n">
+        <v>0.07487000000000001</v>
+      </c>
+      <c r="L313" s="2" t="n">
+        <v>-0.0008007473642064676</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11131,6 +13015,12 @@
       <c r="J314" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K314" s="1" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="L314" s="2" t="n">
+        <v>-0.001955671447196836</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11165,6 +13055,12 @@
       <c r="J315" s="2" t="n">
         <v>-0.0006253908692932395</v>
       </c>
+      <c r="K315" s="1" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="L315" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -11199,6 +13095,12 @@
       <c r="J316" s="2" t="n">
         <v>-0.003314917127071765</v>
       </c>
+      <c r="K316" s="1" t="n">
+        <v>0.1806</v>
+      </c>
+      <c r="L316" s="3" t="n">
+        <v>0.001108647450110896</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11233,6 +13135,12 @@
       <c r="J317" s="2" t="n">
         <v>-0.002777043110288308</v>
       </c>
+      <c r="K317" s="1" t="n">
+        <v>0.007534</v>
+      </c>
+      <c r="L317" s="2" t="n">
+        <v>-0.0009282588516112003</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11267,6 +13175,12 @@
       <c r="J318" s="2" t="n">
         <v>-0.003212206384260197</v>
       </c>
+      <c r="K318" s="1" t="n">
+        <v>0.05028</v>
+      </c>
+      <c r="L318" s="3" t="n">
+        <v>0.01268882175226583</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11301,6 +13215,12 @@
       <c r="J319" s="2" t="n">
         <v>-0.01036693979337379</v>
       </c>
+      <c r="K319" s="1" t="n">
+        <v>0.27865</v>
+      </c>
+      <c r="L319" s="3" t="n">
+        <v>0.003095863781993691</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -11335,6 +13255,12 @@
       <c r="J320" s="3" t="n">
         <v>0.0006819731757216798</v>
       </c>
+      <c r="K320" s="1" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="L320" s="3" t="n">
+        <v>0.0006815084052703827</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11369,6 +13295,12 @@
       <c r="J321" s="3" t="n">
         <v>0.00167310167310156</v>
       </c>
+      <c r="K321" s="1" t="n">
+        <v>0.07769</v>
+      </c>
+      <c r="L321" s="2" t="n">
+        <v>-0.001798792239496354</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -11403,6 +13335,12 @@
       <c r="J322" s="2" t="n">
         <v>-0.002452483139178318</v>
       </c>
+      <c r="K322" s="1" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="L322" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -11437,6 +13375,12 @@
       <c r="J323" s="2" t="n">
         <v>-0.006513026052104159</v>
       </c>
+      <c r="K323" s="1" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="L323" s="3" t="n">
+        <v>0.0005042864346948511</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -11471,6 +13415,12 @@
       <c r="J324" s="3" t="n">
         <v>0.00113071008593392</v>
       </c>
+      <c r="K324" s="1" t="n">
+        <v>0.053398</v>
+      </c>
+      <c r="L324" s="3" t="n">
+        <v>0.00515774414577222</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -11505,6 +13455,12 @@
       <c r="J325" s="2" t="n">
         <v>-0.001169286735091501</v>
       </c>
+      <c r="K325" s="1" t="n">
+        <v>0.15363</v>
+      </c>
+      <c r="L325" s="2" t="n">
+        <v>-0.0008454734651406022</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -11539,6 +13495,12 @@
       <c r="J326" s="2" t="n">
         <v>-0.004001847006310602</v>
       </c>
+      <c r="K326" s="1" t="n">
+        <v>0.006425</v>
+      </c>
+      <c r="L326" s="2" t="n">
+        <v>-0.007108638541183748</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -11573,6 +13535,12 @@
       <c r="J327" s="2" t="n">
         <v>-0.002389010551463356</v>
       </c>
+      <c r="K327" s="1" t="n">
+        <v>0.015099</v>
+      </c>
+      <c r="L327" s="3" t="n">
+        <v>0.004390341249251652</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -11607,6 +13575,12 @@
       <c r="J328" s="3" t="n">
         <v>0.001060445387062597</v>
       </c>
+      <c r="K328" s="1" t="n">
+        <v>0.0946</v>
+      </c>
+      <c r="L328" s="3" t="n">
+        <v>0.002118644067796671</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -11641,6 +13615,12 @@
       <c r="J329" s="2" t="n">
         <v>-0.001585144927536246</v>
       </c>
+      <c r="K329" s="1" t="n">
+        <v>0.004419</v>
+      </c>
+      <c r="L329" s="3" t="n">
+        <v>0.002268088001814575</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -11675,6 +13655,12 @@
       <c r="J330" s="3" t="n">
         <v>0.001175318315377169</v>
       </c>
+      <c r="K330" s="1" t="n">
+        <v>0.05108</v>
+      </c>
+      <c r="L330" s="2" t="n">
+        <v>-0.0005869692819409557</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -11709,6 +13695,12 @@
       <c r="J331" s="3" t="n">
         <v>0.0002735229759298721</v>
       </c>
+      <c r="K331" s="1" t="n">
+        <v>0.03667</v>
+      </c>
+      <c r="L331" s="3" t="n">
+        <v>0.002734481815696004</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -11743,6 +13735,12 @@
       <c r="J332" s="2" t="n">
         <v>-0.002708192281652075</v>
       </c>
+      <c r="K332" s="1" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="L332" s="2" t="n">
+        <v>-0.005431093007467721</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11777,6 +13775,12 @@
       <c r="J333" s="2" t="n">
         <v>-0.00103519668737063</v>
       </c>
+      <c r="K333" s="1" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="L333" s="3" t="n">
+        <v>0.001036269430051843</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11811,6 +13815,12 @@
       <c r="J334" s="3" t="n">
         <v>0.002978918423464828</v>
       </c>
+      <c r="K334" s="1" t="n">
+        <v>0.04375</v>
+      </c>
+      <c r="L334" s="2" t="n">
+        <v>-0.0004569339730410355</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11845,6 +13855,12 @@
       <c r="J335" s="2" t="n">
         <v>-0.000983284169124837</v>
       </c>
+      <c r="K335" s="1" t="n">
+        <v>0.08128000000000001</v>
+      </c>
+      <c r="L335" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11879,6 +13895,12 @@
       <c r="J336" s="2" t="n">
         <v>-0.002437835202340324</v>
       </c>
+      <c r="K336" s="1" t="n">
+        <v>0.2051</v>
+      </c>
+      <c r="L336" s="3" t="n">
+        <v>0.002443792766373414</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11913,6 +13935,12 @@
       <c r="J337" s="3" t="n">
         <v>0.002949852507374682</v>
       </c>
+      <c r="K337" s="1" t="n">
+        <v>0.01019</v>
+      </c>
+      <c r="L337" s="2" t="n">
+        <v>-0.0009803921568628752</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11947,6 +13975,12 @@
       <c r="J338" s="2" t="n">
         <v>-0.0008826125330979953</v>
       </c>
+      <c r="K338" s="1" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="L338" s="2" t="n">
+        <v>-0.002650176678445183</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11981,6 +14015,12 @@
       <c r="J339" s="3" t="n">
         <v>0.0005452562704472771</v>
       </c>
+      <c r="K339" s="1" t="n">
+        <v>0.01832</v>
+      </c>
+      <c r="L339" s="2" t="n">
+        <v>-0.001634877384196308</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -12015,6 +14055,12 @@
       <c r="J340" s="3" t="n">
         <v>0.0003858972110156077</v>
       </c>
+      <c r="K340" s="1" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="L340" s="2" t="n">
+        <v>-0.01002945714686502</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -12049,6 +14095,12 @@
       <c r="J341" s="2" t="n">
         <v>-0.01346417161113647</v>
       </c>
+      <c r="K341" s="1" t="n">
+        <v>0.04322</v>
+      </c>
+      <c r="L341" s="2" t="n">
+        <v>-0.0002313208420077752</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -12083,6 +14135,12 @@
       <c r="J342" s="3" t="n">
         <v>0.001406469760900128</v>
       </c>
+      <c r="K342" s="1" t="n">
+        <v>0.07836</v>
+      </c>
+      <c r="L342" s="3" t="n">
+        <v>0.0005107252298263326</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -12117,6 +14175,12 @@
       <c r="J343" s="2" t="n">
         <v>-0.002879958109700254</v>
       </c>
+      <c r="K343" s="1" t="n">
+        <v>7.627</v>
+      </c>
+      <c r="L343" s="3" t="n">
+        <v>0.001312852829197819</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -12151,6 +14215,12 @@
       <c r="J344" s="2" t="n">
         <v>-0.002808524698496487</v>
       </c>
+      <c r="K344" s="1" t="n">
+        <v>0.6028</v>
+      </c>
+      <c r="L344" s="2" t="n">
+        <v>-0.001325381047051065</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -12185,6 +14255,12 @@
       <c r="J345" s="2" t="n">
         <v>-0.002152852529601634</v>
       </c>
+      <c r="K345" s="1" t="n">
+        <v>0.03715</v>
+      </c>
+      <c r="L345" s="3" t="n">
+        <v>0.001887810140237341</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -12219,6 +14295,12 @@
       <c r="J346" s="2" t="n">
         <v>-0.002415458937197969</v>
       </c>
+      <c r="K346" s="1" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="L346" s="3" t="n">
+        <v>0.004842615012106507</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -12253,6 +14335,12 @@
       <c r="J347" s="2" t="n">
         <v>-0.004029936672423755</v>
       </c>
+      <c r="K347" s="1" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="L347" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -12287,6 +14375,12 @@
       <c r="J348" s="3" t="n">
         <v>0.0006563326448274494</v>
       </c>
+      <c r="K348" s="1" t="n">
+        <v>5187.2</v>
+      </c>
+      <c r="L348" s="3" t="n">
+        <v>0.0006751933946794761</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -12321,6 +14415,12 @@
       <c r="J349" s="3" t="n">
         <v>0.002960769800148047</v>
       </c>
+      <c r="K349" s="1" t="n">
+        <v>0.01358</v>
+      </c>
+      <c r="L349" s="3" t="n">
+        <v>0.00221402214022144</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -12355,6 +14455,12 @@
       <c r="J350" s="2" t="n">
         <v>-0.001994680851063749</v>
       </c>
+      <c r="K350" s="1" t="n">
+        <v>0.01497</v>
+      </c>
+      <c r="L350" s="2" t="n">
+        <v>-0.002664890073284484</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -12389,6 +14495,12 @@
       <c r="J351" s="2" t="n">
         <v>-0.001477832512315218</v>
       </c>
+      <c r="K351" s="1" t="n">
+        <v>0.0006087</v>
+      </c>
+      <c r="L351" s="3" t="n">
+        <v>0.0009866798223976559</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -12423,6 +14535,12 @@
       <c r="J352" s="2" t="n">
         <v>-0.002025316455696295</v>
       </c>
+      <c r="K352" s="1" t="n">
+        <v>0.01975</v>
+      </c>
+      <c r="L352" s="3" t="n">
+        <v>0.002029426686961027</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -12457,6 +14575,12 @@
       <c r="J353" s="2" t="n">
         <v>-0.003180661577608086</v>
       </c>
+      <c r="K353" s="1" t="n">
+        <v>0.0939</v>
+      </c>
+      <c r="L353" s="2" t="n">
+        <v>-0.001276324186343427</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -12491,6 +14615,12 @@
       <c r="J354" s="2" t="n">
         <v>-0.002190580503833578</v>
       </c>
+      <c r="K354" s="1" t="n">
+        <v>0.0911</v>
+      </c>
+      <c r="L354" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -12525,6 +14655,12 @@
       <c r="J355" s="3" t="n">
         <v>0.008260366760284178</v>
       </c>
+      <c r="K355" s="1" t="n">
+        <v>0.0006135</v>
+      </c>
+      <c r="L355" s="3" t="n">
+        <v>0.005243322955923266</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -12559,6 +14695,12 @@
       <c r="J356" s="2" t="n">
         <v>-0.003347680535628941</v>
       </c>
+      <c r="K356" s="1" t="n">
+        <v>2.074</v>
+      </c>
+      <c r="L356" s="2" t="n">
+        <v>-0.004798464491362875</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -12593,6 +14735,12 @@
       <c r="J357" s="3" t="n">
         <v>0.004770164787510797</v>
       </c>
+      <c r="K357" s="1" t="n">
+        <v>0.02315</v>
+      </c>
+      <c r="L357" s="2" t="n">
+        <v>-0.0008631851532153296</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -12627,6 +14775,12 @@
       <c r="J358" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K358" s="1" t="n">
+        <v>0.000405</v>
+      </c>
+      <c r="L358" s="2" t="n">
+        <v>-0.002463054187192178</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -12661,6 +14815,12 @@
       <c r="J359" s="2" t="n">
         <v>-0.001360544217687019</v>
       </c>
+      <c r="K359" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="L359" s="3" t="n">
+        <v>0.0006811989100817161</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -12695,6 +14855,12 @@
       <c r="J360" s="2" t="n">
         <v>-0.007081735025081188</v>
       </c>
+      <c r="K360" s="1" t="n">
+        <v>0.003357</v>
+      </c>
+      <c r="L360" s="2" t="n">
+        <v>-0.002377414561664119</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -12729,6 +14895,12 @@
       <c r="J361" s="3" t="n">
         <v>0.001715800967087802</v>
       </c>
+      <c r="K361" s="1" t="n">
+        <v>0.6421</v>
+      </c>
+      <c r="L361" s="2" t="n">
+        <v>-0.0001557147306134989</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -12763,6 +14935,12 @@
       <c r="J362" s="3" t="n">
         <v>0.0008528784648188766</v>
       </c>
+      <c r="K362" s="1" t="n">
+        <v>0.02344</v>
+      </c>
+      <c r="L362" s="2" t="n">
+        <v>-0.001278227524499457</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -12797,6 +14975,12 @@
       <c r="J363" s="2" t="n">
         <v>-0.002290076335877822</v>
       </c>
+      <c r="K363" s="1" t="n">
+        <v>0.06539</v>
+      </c>
+      <c r="L363" s="3" t="n">
+        <v>0.0006120887528691411</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -12831,6 +15015,12 @@
       <c r="J364" s="2" t="n">
         <v>-0.001273074474856827</v>
       </c>
+      <c r="K364" s="1" t="n">
+        <v>4.704</v>
+      </c>
+      <c r="L364" s="2" t="n">
+        <v>-0.0006373486297004703</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -12865,6 +15055,12 @@
       <c r="J365" s="3" t="n">
         <v>0.005513926198218598</v>
       </c>
+      <c r="K365" s="1" t="n">
+        <v>0.07116</v>
+      </c>
+      <c r="L365" s="3" t="n">
+        <v>0.0005624296962879411</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -12899,6 +15095,12 @@
       <c r="J366" s="3" t="n">
         <v>0.001444304025997414</v>
       </c>
+      <c r="K366" s="1" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="L366" s="3" t="n">
+        <v>0.002343609158103447</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -12933,6 +15135,12 @@
       <c r="J367" s="2" t="n">
         <v>-0.0001704158145876459</v>
       </c>
+      <c r="K367" s="1" t="n">
+        <v>0.05852</v>
+      </c>
+      <c r="L367" s="2" t="n">
+        <v>-0.002556672916311528</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -12967,6 +15175,12 @@
       <c r="J368" s="3" t="n">
         <v>0.001225919439579696</v>
       </c>
+      <c r="K368" s="1" t="n">
+        <v>0.05721</v>
+      </c>
+      <c r="L368" s="3" t="n">
+        <v>0.0006996676578624868</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -13001,6 +15215,12 @@
       <c r="J369" s="2" t="n">
         <v>-0.0006441223832529035</v>
       </c>
+      <c r="K369" s="1" t="n">
+        <v>0.03106</v>
+      </c>
+      <c r="L369" s="3" t="n">
+        <v>0.0009668063164680067</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -13035,6 +15255,12 @@
       <c r="J370" s="2" t="n">
         <v>-0.004297114794352301</v>
       </c>
+      <c r="K370" s="1" t="n">
+        <v>0.0001625</v>
+      </c>
+      <c r="L370" s="3" t="n">
+        <v>0.001849568434031937</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -13069,6 +15295,12 @@
       <c r="J371" s="2" t="n">
         <v>-0.001324503311258199</v>
       </c>
+      <c r="K371" s="1" t="n">
+        <v>0.006787</v>
+      </c>
+      <c r="L371" s="3" t="n">
+        <v>0.0001473622163276253</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -13103,6 +15335,12 @@
       <c r="J372" s="3" t="n">
         <v>0.001742666279407473</v>
       </c>
+      <c r="K372" s="1" t="n">
+        <v>0.006944</v>
+      </c>
+      <c r="L372" s="3" t="n">
+        <v>0.006668599594085247</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -13137,6 +15375,12 @@
       <c r="J373" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K373" s="1" t="n">
+        <v>3.863</v>
+      </c>
+      <c r="L373" s="3" t="n">
+        <v>0.01444327731092441</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -13171,6 +15415,12 @@
       <c r="J374" s="2" t="n">
         <v>-0.001832792894403004</v>
       </c>
+      <c r="K374" s="1" t="n">
+        <v>0.07086000000000001</v>
+      </c>
+      <c r="L374" s="3" t="n">
+        <v>0.0008474576271187075</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -13205,6 +15455,12 @@
       <c r="J375" s="3" t="n">
         <v>0.007426376440460911</v>
       </c>
+      <c r="K375" s="1" t="n">
+        <v>0.07822999999999999</v>
+      </c>
+      <c r="L375" s="2" t="n">
+        <v>-0.005719369598373233</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -13239,6 +15495,12 @@
       <c r="J376" s="2" t="n">
         <v>-0.001591849729385592</v>
       </c>
+      <c r="K376" s="1" t="n">
+        <v>0.06267</v>
+      </c>
+      <c r="L376" s="2" t="n">
+        <v>-0.0007971938775509326</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -13273,6 +15535,12 @@
       <c r="J377" s="2" t="n">
         <v>-0.002483010977522342</v>
       </c>
+      <c r="K377" s="1" t="n">
+        <v>0.07647</v>
+      </c>
+      <c r="L377" s="3" t="n">
+        <v>0.00183414122887464</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -13307,6 +15575,12 @@
       <c r="J378" s="2" t="n">
         <v>-0.001240079365079395</v>
       </c>
+      <c r="K378" s="1" t="n">
+        <v>0.0004015</v>
+      </c>
+      <c r="L378" s="2" t="n">
+        <v>-0.002979885771045381</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -13341,6 +15615,12 @@
       <c r="J379" s="2" t="n">
         <v>-0.000940354648038697</v>
       </c>
+      <c r="K379" s="1" t="n">
+        <v>0.07452</v>
+      </c>
+      <c r="L379" s="3" t="n">
+        <v>0.002016942315449743</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -13375,6 +15655,12 @@
       <c r="J380" s="2" t="n">
         <v>-0.004437869822485155</v>
       </c>
+      <c r="K380" s="1" t="n">
+        <v>0.00135</v>
+      </c>
+      <c r="L380" s="3" t="n">
+        <v>0.00297176820208031</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -13409,6 +15695,12 @@
       <c r="J381" s="2" t="n">
         <v>-0.001845585973546534</v>
       </c>
+      <c r="K381" s="1" t="n">
+        <v>6.486</v>
+      </c>
+      <c r="L381" s="2" t="n">
+        <v>-0.0006163328197227192</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -13443,6 +15735,12 @@
       <c r="J382" s="3" t="n">
         <v>0.0007501875468866911</v>
       </c>
+      <c r="K382" s="1" t="n">
+        <v>0.01335</v>
+      </c>
+      <c r="L382" s="3" t="n">
+        <v>0.0007496251874063964</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -13477,6 +15775,12 @@
       <c r="J383" s="3" t="n">
         <v>0.001699716713881147</v>
       </c>
+      <c r="K383" s="1" t="n">
+        <v>0.01769</v>
+      </c>
+      <c r="L383" s="3" t="n">
+        <v>0.0005656108597284837</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -13511,6 +15815,12 @@
       <c r="J384" s="2" t="n">
         <v>-0.0009803921568626371</v>
       </c>
+      <c r="K384" s="1" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="L384" s="2" t="n">
+        <v>-0.001962708537782196</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -13545,6 +15855,12 @@
       <c r="J385" s="2" t="n">
         <v>-0.002667259390975676</v>
       </c>
+      <c r="K385" s="1" t="n">
+        <v>4.481</v>
+      </c>
+      <c r="L385" s="2" t="n">
+        <v>-0.001337196344996708</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -13579,6 +15895,12 @@
       <c r="J386" s="2" t="n">
         <v>-0.003875968992248072</v>
       </c>
+      <c r="K386" s="1" t="n">
+        <v>0.001286</v>
+      </c>
+      <c r="L386" s="3" t="n">
+        <v>0.0007782101167316209</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -13613,6 +15935,12 @@
       <c r="J387" s="3" t="n">
         <v>0.001352951124640655</v>
       </c>
+      <c r="K387" s="1" t="n">
+        <v>0.0005925</v>
+      </c>
+      <c r="L387" s="3" t="n">
+        <v>0.0006755615605472212</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -13647,6 +15975,12 @@
       <c r="J388" s="2" t="n">
         <v>-0.0008841732979665187</v>
       </c>
+      <c r="K388" s="1" t="n">
+        <v>0.01128</v>
+      </c>
+      <c r="L388" s="2" t="n">
+        <v>-0.001769911504424707</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -13681,6 +16015,12 @@
       <c r="J389" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K389" s="1" t="n">
+        <v>0.009090000000000001</v>
+      </c>
+      <c r="L389" s="2" t="n">
+        <v>-0.003289473684210393</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -13715,6 +16055,12 @@
       <c r="J390" s="2" t="n">
         <v>-0.001770135288911207</v>
       </c>
+      <c r="K390" s="1" t="n">
+        <v>0.07868</v>
+      </c>
+      <c r="L390" s="2" t="n">
+        <v>-0.003419886003799953</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -13749,6 +16095,12 @@
       <c r="J391" s="2" t="n">
         <v>-0.001169818678104981</v>
       </c>
+      <c r="K391" s="1" t="n">
+        <v>0.0512</v>
+      </c>
+      <c r="L391" s="2" t="n">
+        <v>-0.0005855943782938768</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -13783,6 +16135,12 @@
       <c r="J392" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K392" s="1" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="L392" s="3" t="n">
+        <v>0.004201680672268919</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -13817,6 +16175,12 @@
       <c r="J393" s="2" t="n">
         <v>-0.004253308128544578</v>
       </c>
+      <c r="K393" s="1" t="n">
+        <v>0.02117</v>
+      </c>
+      <c r="L393" s="3" t="n">
+        <v>0.004746084480303885</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -13851,6 +16215,12 @@
       <c r="J394" s="3" t="n">
         <v>0.001935171746492557</v>
       </c>
+      <c r="K394" s="1" t="n">
+        <v>0.2057</v>
+      </c>
+      <c r="L394" s="2" t="n">
+        <v>-0.006760019314340958</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -13885,6 +16255,12 @@
       <c r="J395" s="2" t="n">
         <v>-0.001024590163934456</v>
       </c>
+      <c r="K395" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="L395" s="2" t="n">
+        <v>-0.001025641025641055</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -13919,6 +16295,12 @@
       <c r="J396" s="2" t="n">
         <v>-0.002942258183155575</v>
       </c>
+      <c r="K396" s="1" t="n">
+        <v>2.707</v>
+      </c>
+      <c r="L396" s="2" t="n">
+        <v>-0.00147547030616009</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -13953,6 +16335,12 @@
       <c r="J397" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K397" s="1" t="n">
+        <v>1.262</v>
+      </c>
+      <c r="L397" s="2" t="n">
+        <v>-0.00158227848101266</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -13987,6 +16375,12 @@
       <c r="J398" s="2" t="n">
         <v>-0.001093792726278397</v>
       </c>
+      <c r="K398" s="1" t="n">
+        <v>0.007319</v>
+      </c>
+      <c r="L398" s="3" t="n">
+        <v>0.001779359430604981</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -14021,6 +16415,12 @@
       <c r="J399" s="2" t="n">
         <v>-0.0003846153846153422</v>
       </c>
+      <c r="K399" s="1" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L399" s="3" t="n">
+        <v>0.0003847633705270834</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -14055,6 +16455,12 @@
       <c r="J400" s="2" t="n">
         <v>-0.0009422110552764525</v>
       </c>
+      <c r="K400" s="1" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="L400" s="2" t="n">
+        <v>-0.003458032065388211</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -14089,6 +16495,12 @@
       <c r="J401" s="2" t="n">
         <v>-0.001752730214372386</v>
       </c>
+      <c r="K401" s="1" t="n">
+        <v>0.007312</v>
+      </c>
+      <c r="L401" s="2" t="n">
+        <v>-0.01242571582928148</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -14123,6 +16535,12 @@
       <c r="J402" s="2" t="n">
         <v>-0.001748633879781463</v>
       </c>
+      <c r="K402" s="1" t="n">
+        <v>0.004572</v>
+      </c>
+      <c r="L402" s="3" t="n">
+        <v>0.001094810597766542</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -14157,6 +16575,12 @@
       <c r="J403" s="2" t="n">
         <v>-0.001512859304084763</v>
       </c>
+      <c r="K403" s="1" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="L403" s="3" t="n">
+        <v>0.001893939393939396</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -14191,6 +16615,12 @@
       <c r="J404" s="2" t="n">
         <v>-0.0008340283569641606</v>
       </c>
+      <c r="K404" s="1" t="n">
+        <v>0.2394</v>
+      </c>
+      <c r="L404" s="2" t="n">
+        <v>-0.0008347245409015264</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -14225,6 +16655,12 @@
       <c r="J405" s="2" t="n">
         <v>-0.00126132324274736</v>
       </c>
+      <c r="K405" s="1" t="n">
+        <v>0.0008688</v>
+      </c>
+      <c r="L405" s="2" t="n">
+        <v>-0.002525832376578707</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -14259,6 +16695,12 @@
       <c r="J406" s="2" t="n">
         <v>-0.001959631589261139</v>
       </c>
+      <c r="K406" s="1" t="n">
+        <v>0.005084</v>
+      </c>
+      <c r="L406" s="2" t="n">
+        <v>-0.00176713135676425</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -14293,6 +16735,12 @@
       <c r="J407" s="2" t="n">
         <v>-0.0008237232289950241</v>
       </c>
+      <c r="K407" s="1" t="n">
+        <v>0.01212</v>
+      </c>
+      <c r="L407" s="2" t="n">
+        <v>-0.0008244023083264297</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -14327,6 +16775,12 @@
       <c r="J408" s="3" t="n">
         <v>0.00138696255201113</v>
       </c>
+      <c r="K408" s="1" t="n">
+        <v>0.001447</v>
+      </c>
+      <c r="L408" s="3" t="n">
+        <v>0.002077562326869781</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -14361,6 +16815,12 @@
       <c r="J409" s="3" t="n">
         <v>0.005937921727395357</v>
       </c>
+      <c r="K409" s="1" t="n">
+        <v>0.03736</v>
+      </c>
+      <c r="L409" s="3" t="n">
+        <v>0.002414810839817543</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -14395,6 +16855,12 @@
       <c r="J410" s="2" t="n">
         <v>-0.0006108735491752959</v>
       </c>
+      <c r="K410" s="1" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="L410" s="2" t="n">
+        <v>-0.002444987775061025</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -14429,6 +16895,12 @@
       <c r="J411" s="2" t="n">
         <v>-0.001568217459487688</v>
       </c>
+      <c r="K411" s="1" t="n">
+        <v>0.1902</v>
+      </c>
+      <c r="L411" s="2" t="n">
+        <v>-0.004188481675392645</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -14463,6 +16935,12 @@
       <c r="J412" s="2" t="n">
         <v>-0.0005950609937518353</v>
       </c>
+      <c r="K412" s="1" t="n">
+        <v>0.06732</v>
+      </c>
+      <c r="L412" s="3" t="n">
+        <v>0.002083953557606449</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -14497,6 +16975,12 @@
       <c r="J413" s="3" t="n">
         <v>0.0003930817610062893</v>
       </c>
+      <c r="K413" s="1" t="n">
+        <v>2538</v>
+      </c>
+      <c r="L413" s="2" t="n">
+        <v>-0.00275049115913556</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -14531,6 +17015,12 @@
       <c r="J414" s="2" t="n">
         <v>-0.0009580379383023842</v>
       </c>
+      <c r="K414" s="1" t="n">
+        <v>0.05218</v>
+      </c>
+      <c r="L414" s="3" t="n">
+        <v>0.0007671653241273182</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -14565,6 +17055,12 @@
       <c r="J415" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K415" s="1" t="n">
+        <v>1.745</v>
+      </c>
+      <c r="L415" s="3" t="n">
+        <v>0.01218097447795831</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -14599,6 +17095,12 @@
       <c r="J416" s="2" t="n">
         <v>-0.003620040544454101</v>
       </c>
+      <c r="K416" s="1" t="n">
+        <v>0.0689</v>
+      </c>
+      <c r="L416" s="3" t="n">
+        <v>0.001307949425955628</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -14633,6 +17135,12 @@
       <c r="J417" s="2" t="n">
         <v>-0.01333333333333335</v>
       </c>
+      <c r="K417" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="L417" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -14667,6 +17175,12 @@
       <c r="J418" s="2" t="n">
         <v>-0.002600780234070115</v>
       </c>
+      <c r="K418" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="L418" s="2" t="n">
+        <v>-0.002607561929595902</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -14701,6 +17215,12 @@
       <c r="J419" s="3" t="n">
         <v>0.008130081300812959</v>
       </c>
+      <c r="K419" s="1" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="L419" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -14735,6 +17255,12 @@
       <c r="J420" s="2" t="n">
         <v>-0.004160166406656277</v>
       </c>
+      <c r="K420" s="1" t="n">
+        <v>0.01912</v>
+      </c>
+      <c r="L420" s="2" t="n">
+        <v>-0.001566579634464688</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -14769,6 +17295,12 @@
       <c r="J421" s="2" t="n">
         <v>-0.007927519818799475</v>
       </c>
+      <c r="K421" s="1" t="n">
+        <v>0.19203</v>
+      </c>
+      <c r="L421" s="2" t="n">
+        <v>-0.003580323785803218</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -14803,6 +17335,12 @@
       <c r="J422" s="3" t="n">
         <v>0.0005846243788365737</v>
       </c>
+      <c r="K422" s="1" t="n">
+        <v>0.03416</v>
+      </c>
+      <c r="L422" s="2" t="n">
+        <v>-0.00204498977505094</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -14837,6 +17375,12 @@
       <c r="J423" s="2" t="n">
         <v>-0.0021052631578947</v>
       </c>
+      <c r="K423" s="1" t="n">
+        <v>0.1419</v>
+      </c>
+      <c r="L423" s="2" t="n">
+        <v>-0.002109704641350174</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -14871,6 +17415,12 @@
       <c r="J424" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K424" s="1" t="n">
+        <v>0.00528</v>
+      </c>
+      <c r="L424" s="2" t="n">
+        <v>-0.003773584905660387</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -14905,6 +17455,12 @@
       <c r="J425" s="2" t="n">
         <v>-0.00189933523266862</v>
       </c>
+      <c r="K425" s="1" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="L425" s="2" t="n">
+        <v>-0.001902949571836401</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -14939,6 +17495,12 @@
       <c r="J426" s="2" t="n">
         <v>-0.001413827230312521</v>
       </c>
+      <c r="K426" s="1" t="n">
+        <v>0.007048</v>
+      </c>
+      <c r="L426" s="2" t="n">
+        <v>-0.00212374345179106</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -14973,6 +17535,12 @@
       <c r="J427" s="2" t="n">
         <v>-0.003118908382066285</v>
       </c>
+      <c r="K427" s="1" t="n">
+        <v>0.02559</v>
+      </c>
+      <c r="L427" s="3" t="n">
+        <v>0.0007821666014862204</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -15007,6 +17575,12 @@
       <c r="J428" s="2" t="n">
         <v>-0.00381726388375813</v>
       </c>
+      <c r="K428" s="1" t="n">
+        <v>0.008057999999999999</v>
+      </c>
+      <c r="L428" s="2" t="n">
+        <v>-0.003955500618047067</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -15041,6 +17615,12 @@
       <c r="J429" s="3" t="n">
         <v>0.004889975550122333</v>
       </c>
+      <c r="K429" s="1" t="n">
+        <v>0.01235</v>
+      </c>
+      <c r="L429" s="3" t="n">
+        <v>0.001622060016220534</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -15075,6 +17655,12 @@
       <c r="J430" s="3" t="n">
         <v>0.0004472271914132714</v>
       </c>
+      <c r="K430" s="1" t="n">
+        <v>0.06707</v>
+      </c>
+      <c r="L430" s="2" t="n">
+        <v>-0.000596036358217827</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -15109,6 +17695,12 @@
       <c r="J431" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K431" s="1" t="n">
+        <v>0.00542</v>
+      </c>
+      <c r="L431" s="2" t="n">
+        <v>-0.001841620626150938</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -15143,6 +17735,12 @@
       <c r="J432" s="3" t="n">
         <v>0.005305315718298211</v>
       </c>
+      <c r="K432" s="1" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="L432" s="3" t="n">
+        <v>0.003725165562913863</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -15177,6 +17775,12 @@
       <c r="J433" s="2" t="n">
         <v>-0.0009615384615384225</v>
       </c>
+      <c r="K433" s="1" t="n">
+        <v>0.04145</v>
+      </c>
+      <c r="L433" s="2" t="n">
+        <v>-0.002646775745909504</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -15211,6 +17815,12 @@
       <c r="J434" s="2" t="n">
         <v>-0.0002386634844869466</v>
       </c>
+      <c r="K434" s="1" t="n">
+        <v>0.04173</v>
+      </c>
+      <c r="L434" s="2" t="n">
+        <v>-0.003819527333492325</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -15245,6 +17855,12 @@
       <c r="J435" s="2" t="n">
         <v>-0.001299545159194314</v>
       </c>
+      <c r="K435" s="1" t="n">
+        <v>0.001538</v>
+      </c>
+      <c r="L435" s="3" t="n">
+        <v>0.00065061808718291</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -15279,6 +17895,12 @@
       <c r="J436" s="2" t="n">
         <v>-0.003259688518652655</v>
       </c>
+      <c r="K436" s="1" t="n">
+        <v>0.02746</v>
+      </c>
+      <c r="L436" s="2" t="n">
+        <v>-0.002180232558139572</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -15313,6 +17935,12 @@
       <c r="J437" s="3" t="n">
         <v>0.003870811660820139</v>
       </c>
+      <c r="K437" s="1" t="n">
+        <v>0.08229</v>
+      </c>
+      <c r="L437" s="2" t="n">
+        <v>-0.008434751174840251</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -15347,6 +17975,12 @@
       <c r="J438" s="2" t="n">
         <v>-0.0008695652173913292</v>
       </c>
+      <c r="K438" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="L438" s="3" t="n">
+        <v>0.0008703220191471093</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -15381,6 +18015,12 @@
       <c r="J439" s="2" t="n">
         <v>-0.001292824822236588</v>
       </c>
+      <c r="K439" s="1" t="n">
+        <v>1.547</v>
+      </c>
+      <c r="L439" s="3" t="n">
+        <v>0.001294498381877024</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -15415,6 +18055,12 @@
       <c r="J440" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K440" s="1" t="n">
+        <v>0.00179</v>
+      </c>
+      <c r="L440" s="2" t="n">
+        <v>-0.001116071428571456</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -15449,6 +18095,12 @@
       <c r="J441" s="2" t="n">
         <v>-0.004603303547251463</v>
       </c>
+      <c r="K441" s="1" t="n">
+        <v>0.03685</v>
+      </c>
+      <c r="L441" s="3" t="n">
+        <v>0.002448313384113161</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -15483,6 +18135,12 @@
       <c r="J442" s="3" t="n">
         <v>0.001082251082251038</v>
       </c>
+      <c r="K442" s="1" t="n">
+        <v>0.01857</v>
+      </c>
+      <c r="L442" s="3" t="n">
+        <v>0.003783783783783817</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -15517,6 +18175,12 @@
       <c r="J443" s="2" t="n">
         <v>-7.821054278124512e-05</v>
       </c>
+      <c r="K443" s="1" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="L443" s="3" t="n">
+        <v>0.001173249902229263</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -15551,6 +18215,12 @@
       <c r="J444" s="3" t="n">
         <v>0.01021047917599653</v>
       </c>
+      <c r="K444" s="1" t="n">
+        <v>0.011461</v>
+      </c>
+      <c r="L444" s="3" t="n">
+        <v>0.01613618228566361</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -15585,6 +18255,12 @@
       <c r="J445" s="3" t="n">
         <v>0.001734175647219141</v>
       </c>
+      <c r="K445" s="1" t="n">
+        <v>0.08054</v>
+      </c>
+      <c r="L445" s="2" t="n">
+        <v>-0.004080623222455755</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -15619,6 +18295,12 @@
       <c r="J446" s="2" t="n">
         <v>-0.007536504945831426</v>
       </c>
+      <c r="K446" s="1" t="n">
+        <v>0.0002105</v>
+      </c>
+      <c r="L446" s="2" t="n">
+        <v>-0.000949216896060773</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -15653,6 +18335,12 @@
       <c r="J447" s="2" t="n">
         <v>-0.001533742331288281</v>
       </c>
+      <c r="K447" s="1" t="n">
+        <v>0.00653</v>
+      </c>
+      <c r="L447" s="3" t="n">
+        <v>0.003072196620583725</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -15687,6 +18375,12 @@
       <c r="J448" s="3" t="n">
         <v>0.0008938946992044593</v>
       </c>
+      <c r="K448" s="1" t="n">
+        <v>0.11178</v>
+      </c>
+      <c r="L448" s="2" t="n">
+        <v>-0.00169688309368577</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -15721,6 +18415,12 @@
       <c r="J449" s="2" t="n">
         <v>-0.001776198934280618</v>
       </c>
+      <c r="K449" s="1" t="n">
+        <v>0.001685</v>
+      </c>
+      <c r="L449" s="2" t="n">
+        <v>-0.0005931198102016108</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -15755,6 +18455,12 @@
       <c r="J450" s="2" t="n">
         <v>-0.0009661835748791197</v>
       </c>
+      <c r="K450" s="1" t="n">
+        <v>0.0002067</v>
+      </c>
+      <c r="L450" s="2" t="n">
+        <v>-0.0004835589941973038</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -15789,6 +18495,12 @@
       <c r="J451" s="2" t="n">
         <v>-0.006407840180927316</v>
       </c>
+      <c r="K451" s="1" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="L451" s="3" t="n">
+        <v>0.0007587253414263875</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -15823,6 +18535,12 @@
       <c r="J452" s="2" t="n">
         <v>-0.000747384155455822</v>
       </c>
+      <c r="K452" s="1" t="n">
+        <v>0.1338</v>
+      </c>
+      <c r="L452" s="3" t="n">
+        <v>0.0007479431563200373</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -15857,6 +18575,12 @@
       <c r="J453" s="2" t="n">
         <v>-0.0005724098454493557</v>
       </c>
+      <c r="K453" s="1" t="n">
+        <v>0.0001744</v>
+      </c>
+      <c r="L453" s="2" t="n">
+        <v>-0.001145475372279369</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -15891,6 +18615,12 @@
       <c r="J454" s="2" t="n">
         <v>-0.001636512410219107</v>
       </c>
+      <c r="K454" s="1" t="n">
+        <v>0.10919</v>
+      </c>
+      <c r="L454" s="2" t="n">
+        <v>-0.005646116018577629</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -15925,6 +18655,12 @@
       <c r="J455" s="2" t="n">
         <v>-0.0007977662544873474</v>
       </c>
+      <c r="K455" s="1" t="n">
+        <v>0.5007</v>
+      </c>
+      <c r="L455" s="2" t="n">
+        <v>-0.0005988023952095149</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -15959,6 +18695,12 @@
       <c r="J456" s="3" t="n">
         <v>0.0001877111750719266</v>
       </c>
+      <c r="K456" s="1" t="n">
+        <v>0.015973</v>
+      </c>
+      <c r="L456" s="2" t="n">
+        <v>-0.000750703784798131</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -15993,6 +18735,12 @@
       <c r="J457" s="3" t="n">
         <v>0.001801531301606344</v>
       </c>
+      <c r="K457" s="1" t="n">
+        <v>0.006688</v>
+      </c>
+      <c r="L457" s="3" t="n">
+        <v>0.002247864528697776</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -16027,6 +18775,12 @@
       <c r="J458" s="2" t="n">
         <v>-0.001453488372092979</v>
       </c>
+      <c r="K458" s="1" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="L458" s="3" t="n">
+        <v>0.0002079434393844645</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -16061,6 +18815,12 @@
       <c r="J459" s="2" t="n">
         <v>-0.001253918495297836</v>
       </c>
+      <c r="K459" s="1" t="n">
+        <v>0.006376</v>
+      </c>
+      <c r="L459" s="3" t="n">
+        <v>0.0006277463904582021</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -16095,6 +18855,12 @@
       <c r="J460" s="3" t="n">
         <v>0.001449275362318681</v>
       </c>
+      <c r="K460" s="1" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="L460" s="2" t="n">
+        <v>-0.0007235890014470984</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -16129,6 +18895,12 @@
       <c r="J461" s="2" t="n">
         <v>-0.001794124243103762</v>
       </c>
+      <c r="K461" s="1" t="n">
+        <v>0.08902</v>
+      </c>
+      <c r="L461" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -16163,6 +18935,12 @@
       <c r="J462" s="2" t="n">
         <v>-0.0006615214994487816</v>
       </c>
+      <c r="K462" s="1" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="L462" s="3" t="n">
+        <v>0.006178287731685845</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -16197,6 +18975,12 @@
       <c r="J463" s="2" t="n">
         <v>-0.001430615164520686</v>
       </c>
+      <c r="K463" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="L463" s="3" t="n">
+        <v>0.00286532951289399</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -16231,6 +19015,12 @@
       <c r="J464" s="3" t="n">
         <v>0.002291825821237673</v>
       </c>
+      <c r="K464" s="1" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="L464" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -16265,6 +19055,12 @@
       <c r="J465" s="2" t="n">
         <v>-0.002491103202847096</v>
       </c>
+      <c r="K465" s="1" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="L465" s="3" t="n">
+        <v>0.001070281840884847</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -16299,6 +19095,12 @@
       <c r="J466" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K466" s="1" t="n">
+        <v>1.422</v>
+      </c>
+      <c r="L466" s="3" t="n">
+        <v>0.0007037297677690991</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -16333,6 +19135,12 @@
       <c r="J467" s="2" t="n">
         <v>-0.003634475597092452</v>
       </c>
+      <c r="K467" s="1" t="n">
+        <v>0.01915</v>
+      </c>
+      <c r="L467" s="2" t="n">
+        <v>-0.002084418968212526</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -16367,6 +19175,12 @@
       <c r="J468" s="2" t="n">
         <v>-0.002012072434607564</v>
       </c>
+      <c r="K468" s="1" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="L468" s="2" t="n">
+        <v>-0.002016129032257982</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -16401,6 +19215,12 @@
       <c r="J469" s="3" t="n">
         <v>0.0007483162883512659</v>
       </c>
+      <c r="K469" s="1" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="L469" s="2" t="n">
+        <v>-0.0009970089730807863</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -16435,6 +19255,12 @@
       <c r="J470" s="2" t="n">
         <v>-0.002265005662514158</v>
       </c>
+      <c r="K470" s="1" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="L470" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -16469,6 +19295,12 @@
       <c r="J471" s="2" t="n">
         <v>-0.004618226600985259</v>
       </c>
+      <c r="K471" s="1" t="n">
+        <v>3.219</v>
+      </c>
+      <c r="L471" s="2" t="n">
+        <v>-0.00433034333436444</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -16503,6 +19335,12 @@
       <c r="J472" s="3" t="n">
         <v>0.0176947652985993</v>
       </c>
+      <c r="K472" s="1" t="n">
+        <v>0.04104</v>
+      </c>
+      <c r="L472" s="2" t="n">
+        <v>-0.008935039845448014</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -16537,6 +19375,12 @@
       <c r="J473" s="2" t="n">
         <v>-0.001605136436597112</v>
       </c>
+      <c r="K473" s="1" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="L473" s="3" t="n">
+        <v>0.0008038585209004115</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -16571,6 +19415,12 @@
       <c r="J474" s="2" t="n">
         <v>-0.00222404307620273</v>
       </c>
+      <c r="K474" s="1" t="n">
+        <v>0.008532</v>
+      </c>
+      <c r="L474" s="3" t="n">
+        <v>0.0009385265133739238</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -16605,6 +19455,12 @@
       <c r="J475" s="2" t="n">
         <v>-0.005958055290753104</v>
       </c>
+      <c r="K475" s="1" t="n">
+        <v>0.04196</v>
+      </c>
+      <c r="L475" s="3" t="n">
+        <v>0.005993766482857834</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -16639,6 +19495,12 @@
       <c r="J476" s="2" t="n">
         <v>-0.000504413619167697</v>
       </c>
+      <c r="K476" s="1" t="n">
+        <v>0.07901</v>
+      </c>
+      <c r="L476" s="2" t="n">
+        <v>-0.003154176129195057</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -16673,6 +19535,12 @@
       <c r="J477" s="3" t="n">
         <v>7.319036814762498e-05</v>
       </c>
+      <c r="K477" s="1" t="n">
+        <v>0.13673</v>
+      </c>
+      <c r="L477" s="3" t="n">
+        <v>0.000658665105386263</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -16707,6 +19575,12 @@
       <c r="J478" s="2" t="n">
         <v>-0.001679261125105031</v>
       </c>
+      <c r="K478" s="1" t="n">
+        <v>0.04753</v>
+      </c>
+      <c r="L478" s="2" t="n">
+        <v>-0.0006307821698905658</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -16741,6 +19615,12 @@
       <c r="J479" s="2" t="n">
         <v>-0.0005661445555764353</v>
       </c>
+      <c r="K479" s="1" t="n">
+        <v>0.005292</v>
+      </c>
+      <c r="L479" s="2" t="n">
+        <v>-0.0007552870090635443</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -16775,6 +19655,12 @@
       <c r="J480" s="2" t="n">
         <v>-0.001075654356400025</v>
       </c>
+      <c r="K480" s="1" t="n">
+        <v>0.2788</v>
+      </c>
+      <c r="L480" s="3" t="n">
+        <v>0.0007178750897343071</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -16809,6 +19695,12 @@
       <c r="J481" s="2" t="n">
         <v>-0.001707156927117416</v>
       </c>
+      <c r="K481" s="1" t="n">
+        <v>0.07589</v>
+      </c>
+      <c r="L481" s="2" t="n">
+        <v>-0.001710076295711722</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -16843,6 +19735,12 @@
       <c r="J482" s="3" t="n">
         <v>0.002027027027026944</v>
       </c>
+      <c r="K482" s="1" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="L482" s="2" t="n">
+        <v>-0.002022926500337072</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -16877,6 +19775,12 @@
       <c r="J483" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K483" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="L483" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -16911,6 +19815,12 @@
       <c r="J484" s="2" t="n">
         <v>-0.001381851681252823</v>
       </c>
+      <c r="K484" s="1" t="n">
+        <v>0.02164</v>
+      </c>
+      <c r="L484" s="2" t="n">
+        <v>-0.001845018450184587</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -16945,6 +19855,12 @@
       <c r="J485" s="2" t="n">
         <v>-0.0003585943103035537</v>
       </c>
+      <c r="K485" s="1" t="n">
+        <v>0.008338999999999999</v>
+      </c>
+      <c r="L485" s="2" t="n">
+        <v>-0.002869783570489232</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -16979,6 +19895,12 @@
       <c r="J486" s="3" t="n">
         <v>0.0002680605816914978</v>
       </c>
+      <c r="K486" s="1" t="n">
+        <v>0.007461</v>
+      </c>
+      <c r="L486" s="2" t="n">
+        <v>-0.0002679887444727677</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -17013,6 +19935,12 @@
       <c r="J487" s="3" t="n">
         <v>0.0018050541516246</v>
       </c>
+      <c r="K487" s="1" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="L487" s="3" t="n">
+        <v>0.0009009009009009267</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -17047,6 +19975,12 @@
       <c r="J488" s="2" t="n">
         <v>-0.001493014823504332</v>
       </c>
+      <c r="K488" s="1" t="n">
+        <v>0.009361</v>
+      </c>
+      <c r="L488" s="2" t="n">
+        <v>-0.0002136067499733275</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -17081,6 +20015,12 @@
       <c r="J489" s="2" t="n">
         <v>-0.002840909090909065</v>
       </c>
+      <c r="K489" s="1" t="n">
+        <v>0.03855</v>
+      </c>
+      <c r="L489" s="2" t="n">
+        <v>-0.001554001554001491</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -17115,6 +20055,12 @@
       <c r="J490" s="2" t="n">
         <v>-0.0008519338899301658</v>
       </c>
+      <c r="K490" s="1" t="n">
+        <v>0.05865</v>
+      </c>
+      <c r="L490" s="3" t="n">
+        <v>0.0001705320600273374</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -17149,6 +20095,12 @@
       <c r="J491" s="3" t="n">
         <v>0.001038421599169292</v>
       </c>
+      <c r="K491" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="L491" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -17183,6 +20135,12 @@
       <c r="J492" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K492" s="1" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L492" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -17217,6 +20175,12 @@
       <c r="J493" s="2" t="n">
         <v>-0.006770098730606603</v>
       </c>
+      <c r="K493" s="1" t="n">
+        <v>0.03524</v>
+      </c>
+      <c r="L493" s="3" t="n">
+        <v>0.0008520306731042956</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -17251,6 +20215,12 @@
       <c r="J494" s="2" t="n">
         <v>-0.002923976608187218</v>
       </c>
+      <c r="K494" s="1" t="n">
+        <v>0.01703</v>
+      </c>
+      <c r="L494" s="2" t="n">
+        <v>-0.00117302052785919</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -17285,6 +20255,12 @@
       <c r="J495" s="2" t="n">
         <v>-0.002309468822170879</v>
       </c>
+      <c r="K495" s="1" t="n">
+        <v>0.04749</v>
+      </c>
+      <c r="L495" s="2" t="n">
+        <v>-0.0006313131313131786</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -17319,6 +20295,12 @@
       <c r="J496" s="2" t="n">
         <v>-0.003102378490175747</v>
       </c>
+      <c r="K496" s="1" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="L496" s="3" t="n">
+        <v>0.002074688796680557</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -17353,6 +20335,12 @@
       <c r="J497" s="2" t="n">
         <v>-0.002194732641659996</v>
       </c>
+      <c r="K497" s="1" t="n">
+        <v>0.04986</v>
+      </c>
+      <c r="L497" s="2" t="n">
+        <v>-0.002999400119975952</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -17387,6 +20375,12 @@
       <c r="J498" s="2" t="n">
         <v>-0.002420470262794031</v>
       </c>
+      <c r="K498" s="1" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="L498" s="3" t="n">
+        <v>0.0006932409012132877</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -17421,6 +20415,12 @@
       <c r="J499" s="2" t="n">
         <v>-0.001827485380116961</v>
       </c>
+      <c r="K499" s="1" t="n">
+        <v>0.2732</v>
+      </c>
+      <c r="L499" s="3" t="n">
+        <v>0.0003661662394726803</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -17455,6 +20455,12 @@
       <c r="J500" s="2" t="n">
         <v>-0.007490636704119869</v>
       </c>
+      <c r="K500" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="L500" s="3" t="n">
+        <v>0.007547169811320775</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -17489,6 +20495,12 @@
       <c r="J501" s="3" t="n">
         <v>0.001953125000000017</v>
       </c>
+      <c r="K501" s="1" t="n">
+        <v>0.03616</v>
+      </c>
+      <c r="L501" s="3" t="n">
+        <v>0.006961849067112232</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -17523,6 +20535,12 @@
       <c r="J502" s="2" t="n">
         <v>-0.003132832080200374</v>
       </c>
+      <c r="K502" s="1" t="n">
+        <v>0.03188</v>
+      </c>
+      <c r="L502" s="3" t="n">
+        <v>0.001885606536769251</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -17557,6 +20575,12 @@
       <c r="J503" s="2" t="n">
         <v>-0.006278831368529015</v>
       </c>
+      <c r="K503" s="1" t="n">
+        <v>0.007729</v>
+      </c>
+      <c r="L503" s="2" t="n">
+        <v>-0.003352675693101223</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -17591,6 +20615,12 @@
       <c r="J504" s="2" t="n">
         <v>-0.00294310006540219</v>
       </c>
+      <c r="K504" s="1" t="n">
+        <v>3.063</v>
+      </c>
+      <c r="L504" s="3" t="n">
+        <v>0.004591669399803291</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -17625,6 +20655,12 @@
       <c r="J505" s="3" t="n">
         <v>0.002567914583051753</v>
       </c>
+      <c r="K505" s="1" t="n">
+        <v>0.0007415</v>
+      </c>
+      <c r="L505" s="2" t="n">
+        <v>-0.0004044216770019702</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -17659,6 +20695,12 @@
       <c r="J506" s="2" t="n">
         <v>-0.003698722259583019</v>
       </c>
+      <c r="K506" s="1" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="L506" s="3" t="n">
+        <v>0.003712453594330037</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -17693,6 +20735,12 @@
       <c r="J507" s="2" t="n">
         <v>-0.001402032947774307</v>
       </c>
+      <c r="K507" s="1" t="n">
+        <v>0.002847</v>
+      </c>
+      <c r="L507" s="2" t="n">
+        <v>-0.000702000702000643</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -17727,6 +20775,12 @@
       <c r="J508" s="2" t="n">
         <v>-0.001102709514807823</v>
       </c>
+      <c r="K508" s="1" t="n">
+        <v>0.06353</v>
+      </c>
+      <c r="L508" s="3" t="n">
+        <v>0.001892445986437612</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -17761,6 +20815,12 @@
       <c r="J509" s="2" t="n">
         <v>-0.002216312056737542</v>
       </c>
+      <c r="K509" s="1" t="n">
+        <v>2.246</v>
+      </c>
+      <c r="L509" s="2" t="n">
+        <v>-0.002221235006663658</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -17795,6 +20855,12 @@
       <c r="J510" s="2" t="n">
         <v>-0.001231358598987654</v>
       </c>
+      <c r="K510" s="1" t="n">
+        <v>0.0007313</v>
+      </c>
+      <c r="L510" s="3" t="n">
+        <v>0.001780821917808337</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -17829,6 +20895,12 @@
       <c r="J511" s="2" t="n">
         <v>-0.003262051467923003</v>
       </c>
+      <c r="K511" s="1" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="L511" s="3" t="n">
+        <v>0.003636363636363639</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -17863,6 +20935,12 @@
       <c r="J512" s="3" t="n">
         <v>0.0004154549231408493</v>
       </c>
+      <c r="K512" s="1" t="n">
+        <v>0.0004808</v>
+      </c>
+      <c r="L512" s="2" t="n">
+        <v>-0.001661129568106353</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -17897,6 +20975,12 @@
       <c r="J513" s="3" t="n">
         <v>0.001087547580206715</v>
       </c>
+      <c r="K513" s="1" t="n">
+        <v>0.05517</v>
+      </c>
+      <c r="L513" s="2" t="n">
+        <v>-0.001086366105377594</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -17931,6 +21015,12 @@
       <c r="J514" s="2" t="n">
         <v>-0.0006570302233902492</v>
       </c>
+      <c r="K514" s="1" t="n">
+        <v>0.03032</v>
+      </c>
+      <c r="L514" s="2" t="n">
+        <v>-0.003287310979618652</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -17965,6 +21055,12 @@
       <c r="J515" s="2" t="n">
         <v>-0.0008748906386700927</v>
       </c>
+      <c r="K515" s="1" t="n">
+        <v>0.001142</v>
+      </c>
+      <c r="L515" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -17999,6 +21095,12 @@
       <c r="J516" s="2" t="n">
         <v>-0.001957831325301203</v>
       </c>
+      <c r="K516" s="1" t="n">
+        <v>0.00664</v>
+      </c>
+      <c r="L516" s="3" t="n">
+        <v>0.001961671948091141</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -18033,6 +21135,12 @@
       <c r="J517" s="2" t="n">
         <v>-0.0005016302984701812</v>
       </c>
+      <c r="K517" s="1" t="n">
+        <v>0.03987</v>
+      </c>
+      <c r="L517" s="3" t="n">
+        <v>0.0005018820577165903</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -18067,6 +21175,12 @@
       <c r="J518" s="3" t="n">
         <v>0.0009718172983478035</v>
       </c>
+      <c r="K518" s="1" t="n">
+        <v>0.1027</v>
+      </c>
+      <c r="L518" s="2" t="n">
+        <v>-0.00291262135922325</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -18101,6 +21215,12 @@
       <c r="J519" s="2" t="n">
         <v>-0.007927519818799422</v>
       </c>
+      <c r="K519" s="1" t="n">
+        <v>0.008789999999999999</v>
+      </c>
+      <c r="L519" s="3" t="n">
+        <v>0.003424657534246436</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -18135,6 +21255,12 @@
       <c r="J520" s="3" t="n">
         <v>0.001872659176029929</v>
       </c>
+      <c r="K520" s="1" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="L520" s="2" t="n">
+        <v>-0.000623052959501662</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -18169,6 +21295,12 @@
       <c r="J521" s="2" t="n">
         <v>-0.005030743432084953</v>
       </c>
+      <c r="K521" s="1" t="n">
+        <v>0.01793</v>
+      </c>
+      <c r="L521" s="3" t="n">
+        <v>0.007303370786516946</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -18203,6 +21335,12 @@
       <c r="J522" s="2" t="n">
         <v>-0.002403846153846056</v>
       </c>
+      <c r="K522" s="1" t="n">
+        <v>0.01651</v>
+      </c>
+      <c r="L522" s="2" t="n">
+        <v>-0.00542168674698794</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -18237,6 +21375,12 @@
       <c r="J523" s="2" t="n">
         <v>-0.002382654276864537</v>
       </c>
+      <c r="K523" s="1" t="n">
+        <v>0.004194</v>
+      </c>
+      <c r="L523" s="3" t="n">
+        <v>0.001671841413900182</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -18271,6 +21415,12 @@
       <c r="J524" s="2" t="n">
         <v>-0.0007017543859650054</v>
       </c>
+      <c r="K524" s="1" t="n">
+        <v>0.01422</v>
+      </c>
+      <c r="L524" s="2" t="n">
+        <v>-0.001404494382022415</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -18305,6 +21455,12 @@
       <c r="J525" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K525" s="1" t="n">
+        <v>0.02495</v>
+      </c>
+      <c r="L525" s="2" t="n">
+        <v>-0.002797761790567571</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -18339,6 +21495,12 @@
       <c r="J526" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K526" s="1" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="L526" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -18373,6 +21535,12 @@
       <c r="J527" s="3" t="n">
         <v>0.001816403521028435</v>
       </c>
+      <c r="K527" s="1" t="n">
+        <v>0.07167999999999999</v>
+      </c>
+      <c r="L527" s="2" t="n">
+        <v>-0.0002789400278940882</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -18407,6 +21575,12 @@
       <c r="J528" s="2" t="n">
         <v>-0.001616254906488123</v>
       </c>
+      <c r="K528" s="1" t="n">
+        <v>0.04318</v>
+      </c>
+      <c r="L528" s="2" t="n">
+        <v>-0.001387604070305216</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -18441,6 +21615,12 @@
       <c r="J529" s="2" t="n">
         <v>-0.0007922674694976152</v>
       </c>
+      <c r="K529" s="1" t="n">
+        <v>0.06306</v>
+      </c>
+      <c r="L529" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -18475,6 +21655,12 @@
       <c r="J530" s="2" t="n">
         <v>-0.0007958615200954365</v>
       </c>
+      <c r="K530" s="1" t="n">
+        <v>0.005028</v>
+      </c>
+      <c r="L530" s="3" t="n">
+        <v>0.001194743130226987</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -18509,6 +21695,12 @@
       <c r="J531" s="2" t="n">
         <v>-0.001531393568147058</v>
       </c>
+      <c r="K531" s="1" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="L531" s="3" t="n">
+        <v>0.0007668711656443003</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -18543,6 +21735,12 @@
       <c r="J532" s="2" t="n">
         <v>-0.001497005988024021</v>
       </c>
+      <c r="K532" s="1" t="n">
+        <v>0.05339</v>
+      </c>
+      <c r="L532" s="3" t="n">
+        <v>0.0005622188905547648</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -18577,6 +21775,12 @@
       <c r="J533" s="2" t="n">
         <v>-0.0007957559681697518</v>
       </c>
+      <c r="K533" s="1" t="n">
+        <v>0.003772</v>
+      </c>
+      <c r="L533" s="3" t="n">
+        <v>0.001327316166710972</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -18611,6 +21815,12 @@
       <c r="J534" s="2" t="n">
         <v>-0.001745200698080248</v>
       </c>
+      <c r="K534" s="1" t="n">
+        <v>0.1716</v>
+      </c>
+      <c r="L534" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -18645,6 +21855,12 @@
       <c r="J535" s="2" t="n">
         <v>-0.00884955752212396</v>
       </c>
+      <c r="K535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="L535" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -18679,6 +21895,12 @@
       <c r="J536" s="2" t="n">
         <v>-0.001343484102104824</v>
       </c>
+      <c r="K536" s="1" t="n">
+        <v>0.0004466</v>
+      </c>
+      <c r="L536" s="3" t="n">
+        <v>0.001345291479820661</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -18713,6 +21935,12 @@
       <c r="J537" s="3" t="n">
         <v>0.001030927835051504</v>
       </c>
+      <c r="K537" s="1" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="L537" s="2" t="n">
+        <v>-0.001029866117404695</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -18747,6 +21975,12 @@
       <c r="J538" s="3" t="n">
         <v>0.001648653599560355</v>
       </c>
+      <c r="K538" s="1" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="L538" s="2" t="n">
+        <v>-0.001463057790782676</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -18781,6 +22015,12 @@
       <c r="J539" s="2" t="n">
         <v>-0.002191060473268983</v>
       </c>
+      <c r="K539" s="1" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L539" s="3" t="n">
+        <v>0.001317523056653509</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -18815,6 +22055,12 @@
       <c r="J540" s="2" t="n">
         <v>-0.001316655694535917</v>
       </c>
+      <c r="K540" s="1" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="L540" s="3" t="n">
+        <v>0.0006591957811469281</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -18849,6 +22095,12 @@
       <c r="J541" s="2" t="n">
         <v>-0.003041825095057042</v>
       </c>
+      <c r="K541" s="1" t="n">
+        <v>0.01309</v>
+      </c>
+      <c r="L541" s="2" t="n">
+        <v>-0.001525553012967271</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -18883,6 +22135,12 @@
       <c r="J542" s="3" t="n">
         <v>0.007132667617689097</v>
       </c>
+      <c r="K542" s="1" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="L542" s="2" t="n">
+        <v>-0.01416430594900854</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -18916,6 +22174,12 @@
       </c>
       <c r="J543" s="3" t="n">
         <v>0.0006974716652135723</v>
+      </c>
+      <c r="K543" s="1" t="n">
+        <v>0.05734</v>
+      </c>
+      <c r="L543" s="2" t="n">
+        <v>-0.0008712319219375239</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P543"/>
+  <dimension ref="A1:R543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,8 @@
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,6 +527,16 @@
           <t>change_01:45</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>price_02:00</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>change_02:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -577,6 +589,12 @@
       <c r="P2" s="3" t="n">
         <v>0.001033424007037615</v>
       </c>
+      <c r="Q2" s="1" t="n">
+        <v>70167.2</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>-0.002236773812824875</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -629,6 +647,12 @@
       <c r="P3" s="3" t="n">
         <v>0.001946139025183436</v>
       </c>
+      <c r="Q3" s="1" t="n">
+        <v>2057.2</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>-0.003535965124727625</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -681,6 +705,12 @@
       <c r="P4" s="3" t="n">
         <v>0.00439662154344551</v>
       </c>
+      <c r="Q4" s="1" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>-0.002995046653611394</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -733,6 +763,12 @@
       <c r="P5" s="2" t="n">
         <v>-0.006282916012196121</v>
       </c>
+      <c r="Q5" s="1" t="n">
+        <v>0.010819</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.005950720595072042</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -785,6 +821,12 @@
       <c r="P6" s="3" t="n">
         <v>0.0018865186475112</v>
       </c>
+      <c r="Q6" s="1" t="n">
+        <v>1.3795</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>-0.0009414831981460595</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -837,6 +879,12 @@
       <c r="P7" s="3" t="n">
         <v>0.004033113988537522</v>
       </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.09431</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>-0.003065539112050725</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -889,6 +937,12 @@
       <c r="P8" s="3" t="n">
         <v>0.00512669888654509</v>
       </c>
+      <c r="Q8" s="1" t="n">
+        <v>37.702</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.0015673564806205</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -941,6 +995,12 @@
       <c r="P9" s="2" t="n">
         <v>-0.005234548016911543</v>
       </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.04917</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>-0.004857316332726251</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -993,6 +1053,12 @@
       <c r="P10" s="3" t="n">
         <v>0.0007016786311868151</v>
       </c>
+      <c r="Q10" s="1" t="n">
+        <v>18.808</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.01445523193096012</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1045,6 +1111,12 @@
       <c r="P11" s="3" t="n">
         <v>0.002413528055342121</v>
       </c>
+      <c r="Q11" s="1" t="n">
+        <v>650.63</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>-0.002208351864063758</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1097,6 +1169,12 @@
       <c r="P12" s="2" t="n">
         <v>-0.02196607220530665</v>
       </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.8694</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>-0.03335557038025353</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1149,6 +1227,12 @@
       <c r="P13" s="3" t="n">
         <v>0.005008586147681795</v>
       </c>
+      <c r="Q13" s="1" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>-0.0004746309744173635</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1201,6 +1285,12 @@
       <c r="P14" s="3" t="n">
         <v>0.004952288923782989</v>
       </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.0033167</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>-0.003395432692307596</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1253,6 +1343,12 @@
       <c r="P15" s="3" t="n">
         <v>0.04084720121028735</v>
       </c>
+      <c r="Q15" s="1" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>0.06762354651162797</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1305,6 +1401,12 @@
       <c r="P16" s="3" t="n">
         <v>0.003085784817938699</v>
       </c>
+      <c r="Q16" s="1" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>-0.001230516817063145</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1357,6 +1459,12 @@
       <c r="P17" s="2" t="n">
         <v>-0.03103448275862074</v>
       </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1409,6 +1517,12 @@
       <c r="P18" s="3" t="n">
         <v>0.001444817300522009</v>
       </c>
+      <c r="Q18" s="1" t="n">
+        <v>213.66</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>-0.005631311956066496</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1461,6 +1575,12 @@
       <c r="P19" s="3" t="n">
         <v>0.002289202594429566</v>
       </c>
+      <c r="Q19" s="1" t="n">
+        <v>0.2622</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>-0.001903311762466694</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1513,6 +1633,12 @@
       <c r="P20" s="2" t="n">
         <v>-0.007740029542097441</v>
       </c>
+      <c r="Q20" s="1" t="n">
+        <v>0.01699</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>0.01167083482196033</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1565,6 +1691,12 @@
       <c r="P21" s="3" t="n">
         <v>0.0007324474207386913</v>
       </c>
+      <c r="Q21" s="1" t="n">
+        <v>9.547000000000001</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>-0.001777498954412323</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1617,6 +1749,12 @@
       <c r="P22" s="3" t="n">
         <v>0.005980861244019145</v>
       </c>
+      <c r="Q22" s="1" t="n">
+        <v>0.1682</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1669,6 +1807,12 @@
       <c r="P23" s="2" t="n">
         <v>-0.004081749157960801</v>
       </c>
+      <c r="Q23" s="1" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>0.00702186810352242</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1721,6 +1865,12 @@
       <c r="P24" s="3" t="n">
         <v>0.009324009324009333</v>
       </c>
+      <c r="Q24" s="1" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>0.003464203233256354</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1773,6 +1923,12 @@
       <c r="P25" s="3" t="n">
         <v>0.001443482123029081</v>
       </c>
+      <c r="Q25" s="1" t="n">
+        <v>9.004</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>-0.001663155560483487</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1825,6 +1981,12 @@
       <c r="P26" s="3" t="n">
         <v>0.002248875562218809</v>
       </c>
+      <c r="Q26" s="1" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>0.001495886312640241</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1877,6 +2039,12 @@
       <c r="P27" s="2" t="n">
         <v>-0.001341720879090811</v>
       </c>
+      <c r="Q27" s="1" t="n">
+        <v>5108.04</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>-0.001052133405822348</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1929,6 +2097,12 @@
       <c r="P28" s="3" t="n">
         <v>0.004821327283040213</v>
       </c>
+      <c r="Q28" s="1" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>0.0002822466836014366</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1981,6 +2155,12 @@
       <c r="P29" s="3" t="n">
         <v>0.003056935422239208</v>
       </c>
+      <c r="Q29" s="1" t="n">
+        <v>2.628</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>0.001142857142857186</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2033,6 +2213,12 @@
       <c r="P30" s="2" t="n">
         <v>-0.002460493484890451</v>
       </c>
+      <c r="Q30" s="1" t="n">
+        <v>0.57281</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>-0.005019975681778614</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2085,6 +2271,12 @@
       <c r="P31" s="3" t="n">
         <v>0.009610764055742457</v>
       </c>
+      <c r="Q31" s="1" t="n">
+        <v>0.002093</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>-0.003807710613993429</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2137,6 +2329,12 @@
       <c r="P32" s="2" t="n">
         <v>-0.004265219077161737</v>
       </c>
+      <c r="Q32" s="1" t="n">
+        <v>1.2964</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>0.009657320872274116</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2189,6 +2387,12 @@
       <c r="P33" s="3" t="n">
         <v>0.009239297813366193</v>
       </c>
+      <c r="Q33" s="1" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>-0.003661885871223616</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2241,6 +2445,12 @@
       <c r="P34" s="3" t="n">
         <v>0.002008032128514132</v>
       </c>
+      <c r="Q34" s="1" t="n">
+        <v>1.494</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>-0.00200400801603214</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2293,6 +2503,12 @@
       <c r="P35" s="3" t="n">
         <v>0.0003955696202531795</v>
       </c>
+      <c r="Q35" s="1" t="n">
+        <v>454.58</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>-0.001405913624181809</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2345,6 +2561,12 @@
       <c r="P36" s="2" t="n">
         <v>-0.01169710650523294</v>
       </c>
+      <c r="Q36" s="1" t="n">
+        <v>0.04805</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>-0.002284053156146158</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2397,6 +2619,12 @@
       <c r="P37" s="3" t="n">
         <v>0.001983283751239648</v>
       </c>
+      <c r="Q37" s="1" t="n">
+        <v>0.7069</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>-0.000565530892125077</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2449,6 +2677,12 @@
       <c r="P38" s="3" t="n">
         <v>0.003798670465337109</v>
       </c>
+      <c r="Q38" s="1" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>-0.003784295175023629</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2501,6 +2735,12 @@
       <c r="P39" s="3" t="n">
         <v>0.003553854565336255</v>
       </c>
+      <c r="Q39" s="1" t="n">
+        <v>109.84</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>-0.002633251611731518</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2553,6 +2793,12 @@
       <c r="P40" s="2" t="n">
         <v>-0.01567065073041169</v>
       </c>
+      <c r="Q40" s="1" t="n">
+        <v>0.03746</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>0.01079330814894759</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2605,6 +2851,12 @@
       <c r="P41" s="2" t="n">
         <v>-0.007021966150522172</v>
       </c>
+      <c r="Q41" s="1" t="n">
+        <v>0.05528</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>0.002357207615593928</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2657,6 +2909,12 @@
       <c r="P42" s="3" t="n">
         <v>0.00202914591403799</v>
       </c>
+      <c r="Q42" s="1" t="n">
+        <v>54.18</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>-0.002577319587628876</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2709,6 +2967,12 @@
       <c r="P43" s="2" t="n">
         <v>-0.005311077389984873</v>
       </c>
+      <c r="Q43" s="1" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>0.002288329519450761</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2761,6 +3025,12 @@
       <c r="P44" s="3" t="n">
         <v>0.005114217524718806</v>
       </c>
+      <c r="Q44" s="1" t="n">
+        <v>0.005888</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>-0.001356852103120793</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2813,6 +3083,12 @@
       <c r="P45" s="3" t="n">
         <v>0.007073122135883665</v>
       </c>
+      <c r="Q45" s="1" t="n">
+        <v>0.09995</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>-0.01127707982985461</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2865,6 +3141,12 @@
       <c r="P46" s="3" t="n">
         <v>0.006123919308357474</v>
       </c>
+      <c r="Q46" s="1" t="n">
+        <v>2.787</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>-0.002148227712137568</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2917,6 +3199,12 @@
       <c r="P47" s="3" t="n">
         <v>0.0004496402877698498</v>
       </c>
+      <c r="Q47" s="1" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>-0.0008988764044943213</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2969,6 +3257,12 @@
       <c r="P48" s="2" t="n">
         <v>-0.001862197392923574</v>
       </c>
+      <c r="Q48" s="1" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>-0.000932835820895549</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3021,6 +3315,12 @@
       <c r="P49" s="3" t="n">
         <v>0.0003634454629891643</v>
       </c>
+      <c r="Q49" s="1" t="n">
+        <v>0.24692</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>-0.003229452607782961</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3073,6 +3373,12 @@
       <c r="P50" s="3" t="n">
         <v>0.005726405090137845</v>
       </c>
+      <c r="Q50" s="1" t="n">
+        <v>0.04716</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>-0.005482918599746866</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3125,6 +3431,12 @@
       <c r="P51" s="3" t="n">
         <v>0.001280409731114043</v>
       </c>
+      <c r="Q51" s="1" t="n">
+        <v>3.895</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>-0.003836317135549904</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3177,6 +3489,12 @@
       <c r="P52" s="2" t="n">
         <v>-0.01282051282051279</v>
       </c>
+      <c r="Q52" s="1" t="n">
+        <v>0.000231</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3229,6 +3547,12 @@
       <c r="P53" s="3" t="n">
         <v>0.009052504526252272</v>
       </c>
+      <c r="Q53" s="1" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>-0.007177033492822841</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3281,6 +3605,12 @@
       <c r="P54" s="2" t="n">
         <v>-0.007142857142857182</v>
       </c>
+      <c r="Q54" s="1" t="n">
+        <v>0.04208</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>0.009112709832134254</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3333,6 +3663,12 @@
       <c r="P55" s="3" t="n">
         <v>0.009844601741111292</v>
       </c>
+      <c r="Q55" s="1" t="n">
+        <v>0.12391</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>-0.001691911053818788</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3385,6 +3721,12 @@
       <c r="P56" s="2" t="n">
         <v>-0.007509386733416812</v>
       </c>
+      <c r="Q56" s="1" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>-0.0009457755359393663</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3437,6 +3779,12 @@
       <c r="P57" s="2" t="n">
         <v>-0.01112061591103506</v>
       </c>
+      <c r="Q57" s="1" t="n">
+        <v>0.01161</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>0.004325259515570908</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3489,6 +3837,12 @@
       <c r="P58" s="3" t="n">
         <v>0.003024193548387183</v>
       </c>
+      <c r="Q58" s="1" t="n">
+        <v>0.0992</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>-0.003015075376884508</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3541,6 +3895,12 @@
       <c r="P59" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q59" s="1" t="n">
+        <v>0.00334</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>-0.005952380952380968</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3593,6 +3953,12 @@
       <c r="P60" s="3" t="n">
         <v>0.007152145643693223</v>
       </c>
+      <c r="Q60" s="1" t="n">
+        <v>0.1539</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>-0.006455777921239515</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3645,6 +4011,12 @@
       <c r="P61" s="3" t="n">
         <v>0.002639517345399547</v>
       </c>
+      <c r="Q61" s="1" t="n">
+        <v>0.15945</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>-0.0005641218503195373</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3697,6 +4069,12 @@
       <c r="P62" s="3" t="n">
         <v>0.00423549343498518</v>
       </c>
+      <c r="Q62" s="1" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>-0.007029382820188394</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3749,6 +4127,12 @@
       <c r="P63" s="3" t="n">
         <v>0.003594044155399607</v>
       </c>
+      <c r="Q63" s="1" t="n">
+        <v>5.866</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>0.0003410641200545327</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3801,6 +4185,12 @@
       <c r="P64" s="3" t="n">
         <v>0.01114874400225798</v>
       </c>
+      <c r="Q64" s="1" t="n">
+        <v>0.007121</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>-0.00614096301465466</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3853,6 +4243,12 @@
       <c r="P65" s="2" t="n">
         <v>-0.004464285714285643</v>
       </c>
+      <c r="Q65" s="1" t="n">
+        <v>0.03164</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>0.01345291479820629</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3905,6 +4301,12 @@
       <c r="P66" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q66" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3957,6 +4359,12 @@
       <c r="P67" s="3" t="n">
         <v>0.001232285890326557</v>
       </c>
+      <c r="Q67" s="1" t="n">
+        <v>1.609</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>-0.009846153846153855</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4009,6 +4417,12 @@
       <c r="P68" s="3" t="n">
         <v>0.007125294796527668</v>
       </c>
+      <c r="Q68" s="1" t="n">
+        <v>2.0039</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>-0.001594340092671064</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4061,6 +4475,12 @@
       <c r="P69" s="3" t="n">
         <v>0.004543071815481278</v>
       </c>
+      <c r="Q69" s="1" t="n">
+        <v>0.5752</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>0.0005218298834581284</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4113,6 +4533,12 @@
       <c r="P70" s="3" t="n">
         <v>0.009615384615384625</v>
       </c>
+      <c r="Q70" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4165,6 +4591,12 @@
       <c r="P71" s="3" t="n">
         <v>0.0005492694716028298</v>
       </c>
+      <c r="Q71" s="1" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>-0.001976284584980263</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4217,6 +4649,12 @@
       <c r="P72" s="3" t="n">
         <v>0.00589483612355577</v>
       </c>
+      <c r="Q72" s="1" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>-0.002812939521800232</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4269,6 +4707,12 @@
       <c r="P73" s="3" t="n">
         <v>0.003189792663476966</v>
       </c>
+      <c r="Q73" s="1" t="n">
+        <v>0.09406</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>-0.003073661897191294</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4321,6 +4765,12 @@
       <c r="P74" s="2" t="n">
         <v>-0.01867791358237223</v>
       </c>
+      <c r="Q74" s="1" t="n">
+        <v>1.1433</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>0.002806771335847813</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4373,6 +4823,12 @@
       <c r="P75" s="3" t="n">
         <v>0.00314070351758803</v>
       </c>
+      <c r="Q75" s="1" t="n">
+        <v>0.01591</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>-0.003757044458359488</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4425,6 +4881,12 @@
       <c r="P76" s="2" t="n">
         <v>-0.004680816721814309</v>
       </c>
+      <c r="Q76" s="1" t="n">
+        <v>0.12415</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>0.006648828346712084</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4477,6 +4939,12 @@
       <c r="P77" s="2" t="n">
         <v>-0.001702127659574399</v>
       </c>
+      <c r="Q77" s="1" t="n">
+        <v>0.1169</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>-0.00341005967604431</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4529,6 +4997,12 @@
       <c r="P78" s="3" t="n">
         <v>0.001976284584980294</v>
       </c>
+      <c r="Q78" s="1" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>-0.002958579881656889</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4581,6 +5055,12 @@
       <c r="P79" s="3" t="n">
         <v>0.009571788413098196</v>
       </c>
+      <c r="Q79" s="1" t="n">
+        <v>0.005978</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>-0.005655355954757181</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4633,6 +5113,12 @@
       <c r="P80" s="2" t="n">
         <v>-0.005948692526954943</v>
       </c>
+      <c r="Q80" s="1" t="n">
+        <v>0.007990000000000001</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>-0.003864854756264777</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4685,6 +5171,12 @@
       <c r="P81" s="3" t="n">
         <v>0.00224089635854337</v>
       </c>
+      <c r="Q81" s="1" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>-0.001676914477361718</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4737,6 +5229,12 @@
       <c r="P82" s="3" t="n">
         <v>0.003111387678904794</v>
       </c>
+      <c r="Q82" s="1" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>0.003722084367245592</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4789,6 +5287,12 @@
       <c r="P83" s="3" t="n">
         <v>0.002074688796680432</v>
       </c>
+      <c r="Q83" s="1" t="n">
+        <v>8.186999999999999</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>-0.002922908293752394</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4841,6 +5345,12 @@
       <c r="P84" s="3" t="n">
         <v>0.003452211126961425</v>
       </c>
+      <c r="Q84" s="1" t="n">
+        <v>352.02</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>0.0008814079781638347</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4893,6 +5403,12 @@
       <c r="P85" s="2" t="n">
         <v>-0.01058710298363806</v>
       </c>
+      <c r="Q85" s="1" t="n">
+        <v>0.004092</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>-0.004863813229571997</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4945,6 +5461,12 @@
       <c r="P86" s="2" t="n">
         <v>-0.004733283245679878</v>
       </c>
+      <c r="Q86" s="1" t="n">
+        <v>0.1322</v>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>-0.00203819732769678</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4997,6 +5519,12 @@
       <c r="P87" s="2" t="n">
         <v>-0.01401869158878502</v>
       </c>
+      <c r="Q87" s="1" t="n">
+        <v>0.01905</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>0.003159557661927384</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5049,6 +5577,12 @@
       <c r="P88" s="3" t="n">
         <v>0.00443262411347528</v>
       </c>
+      <c r="Q88" s="1" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>-0.003530450132391883</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5101,6 +5635,12 @@
       <c r="P89" s="3" t="n">
         <v>0.001022146507666175</v>
       </c>
+      <c r="Q89" s="1" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>0.00272294077603801</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5153,6 +5693,12 @@
       <c r="P90" s="3" t="n">
         <v>0.004685669660288867</v>
       </c>
+      <c r="Q90" s="1" t="n">
+        <v>0.2568</v>
+      </c>
+      <c r="R90" s="2" t="n">
+        <v>-0.001943256898561992</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5205,6 +5751,12 @@
       <c r="P91" s="2" t="n">
         <v>-0.01217360621030351</v>
       </c>
+      <c r="Q91" s="1" t="n">
+        <v>0.05632</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>0.005893909626719127</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5257,6 +5809,12 @@
       <c r="P92" s="2" t="n">
         <v>-0.001455381080045969</v>
       </c>
+      <c r="Q92" s="1" t="n">
+        <v>1.3008</v>
+      </c>
+      <c r="R92" s="2" t="n">
+        <v>-0.002147898128260307</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5309,6 +5867,12 @@
       <c r="P93" s="3" t="n">
         <v>0.003340757238307379</v>
       </c>
+      <c r="Q93" s="1" t="n">
+        <v>0.06296</v>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>-0.001744093863960663</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5361,6 +5925,12 @@
       <c r="P94" s="2" t="n">
         <v>-0.003386004514672744</v>
       </c>
+      <c r="Q94" s="1" t="n">
+        <v>0.00881</v>
+      </c>
+      <c r="R94" s="2" t="n">
+        <v>-0.002265005662514064</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5413,6 +5983,12 @@
       <c r="P95" s="3" t="n">
         <v>0.002706766917293102</v>
       </c>
+      <c r="Q95" s="1" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>-0.002999400119976008</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5465,6 +6041,12 @@
       <c r="P96" s="2" t="n">
         <v>-0.003519577650681927</v>
       </c>
+      <c r="Q96" s="1" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="R96" s="2" t="n">
+        <v>-0.00220750551876386</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5517,6 +6099,12 @@
       <c r="P97" s="3" t="n">
         <v>0.003064664419245918</v>
       </c>
+      <c r="Q97" s="1" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>-0.00152765047357156</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5569,6 +6157,12 @@
       <c r="P98" s="3" t="n">
         <v>0.005479452054794526</v>
       </c>
+      <c r="Q98" s="1" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="R98" s="3" t="n">
+        <v>0.002724795640327079</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5621,6 +6215,12 @@
       <c r="P99" s="3" t="n">
         <v>0.004009355162044775</v>
       </c>
+      <c r="Q99" s="1" t="n">
+        <v>2.998</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>-0.002329450915141322</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5673,6 +6273,12 @@
       <c r="P100" s="3" t="n">
         <v>0.004938988959907132</v>
       </c>
+      <c r="Q100" s="1" t="n">
+        <v>0.03439</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>-0.005782017924255731</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5725,6 +6331,12 @@
       <c r="P101" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q101" s="1" t="n">
+        <v>1.814</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>-0.001101321585903085</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5777,6 +6389,12 @@
       <c r="P102" s="2" t="n">
         <v>-0.02966218071958254</v>
       </c>
+      <c r="Q102" s="1" t="n">
+        <v>0.006947</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>-0.01684121143504107</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5829,6 +6447,12 @@
       <c r="P103" s="2" t="n">
         <v>-0.002222551489109459</v>
       </c>
+      <c r="Q103" s="1" t="n">
+        <v>0.06705999999999999</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>-0.004158004158004195</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5881,6 +6505,12 @@
       <c r="P104" s="2" t="n">
         <v>-0.004362578768783383</v>
       </c>
+      <c r="Q104" s="1" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="R104" s="2" t="n">
+        <v>-0.0002434274586173052</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5933,6 +6563,12 @@
       <c r="P105" s="3" t="n">
         <v>0.003376477208778844</v>
       </c>
+      <c r="Q105" s="1" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="R105" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5985,6 +6621,12 @@
       <c r="P106" s="3" t="n">
         <v>0.009435118245313158</v>
       </c>
+      <c r="Q106" s="1" t="n">
+        <v>0.008135</v>
+      </c>
+      <c r="R106" s="2" t="n">
+        <v>-0.01250303471716444</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6037,6 +6679,12 @@
       <c r="P107" s="3" t="n">
         <v>0.002760905577029153</v>
       </c>
+      <c r="Q107" s="1" t="n">
+        <v>0.01812</v>
+      </c>
+      <c r="R107" s="2" t="n">
+        <v>-0.002202643171806078</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6089,6 +6737,12 @@
       <c r="P108" s="3" t="n">
         <v>0.004705882352941147</v>
       </c>
+      <c r="Q108" s="1" t="n">
+        <v>0.02127</v>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>-0.003747072599531625</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6141,6 +6795,12 @@
       <c r="P109" s="3" t="n">
         <v>0.003735325506937066</v>
       </c>
+      <c r="Q109" s="1" t="n">
+        <v>0.05585</v>
+      </c>
+      <c r="R109" s="2" t="n">
+        <v>-0.01027822080453667</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6193,6 +6853,12 @@
       <c r="P110" s="2" t="n">
         <v>-0.004531076344361825</v>
       </c>
+      <c r="Q110" s="1" t="n">
+        <v>0.11611</v>
+      </c>
+      <c r="R110" s="2" t="n">
+        <v>-0.002834077636550987</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6245,6 +6911,12 @@
       <c r="P111" s="3" t="n">
         <v>0.001527028402728264</v>
       </c>
+      <c r="Q111" s="1" t="n">
+        <v>0.09826</v>
+      </c>
+      <c r="R111" s="2" t="n">
+        <v>-0.001219760113844228</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6297,6 +6969,12 @@
       <c r="P112" s="3" t="n">
         <v>0.00270270270270278</v>
       </c>
+      <c r="Q112" s="1" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="R112" s="2" t="n">
+        <v>-0.005390835579514792</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6349,6 +7027,12 @@
       <c r="P113" s="3" t="n">
         <v>0.002756789871349871</v>
       </c>
+      <c r="Q113" s="1" t="n">
+        <v>0.09798999999999999</v>
+      </c>
+      <c r="R113" s="2" t="n">
+        <v>-0.002240097749720108</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6401,6 +7085,12 @@
       <c r="P114" s="3" t="n">
         <v>0.01376936316695349</v>
       </c>
+      <c r="Q114" s="1" t="n">
+        <v>0.001722</v>
+      </c>
+      <c r="R114" s="2" t="n">
+        <v>-0.02546689303904918</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6453,6 +7143,12 @@
       <c r="P115" s="3" t="n">
         <v>0.003277116137798731</v>
       </c>
+      <c r="Q115" s="1" t="n">
+        <v>1.2527</v>
+      </c>
+      <c r="R115" s="2" t="n">
+        <v>-0.001991714467814028</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6505,6 +7201,12 @@
       <c r="P116" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q116" s="1" t="n">
+        <v>0.2362</v>
+      </c>
+      <c r="R116" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6557,6 +7259,12 @@
       <c r="P117" s="3" t="n">
         <v>0.004128819157720895</v>
       </c>
+      <c r="Q117" s="1" t="n">
+        <v>0.06105</v>
+      </c>
+      <c r="R117" s="3" t="n">
+        <v>0.004111842105263161</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6609,6 +7317,12 @@
       <c r="P118" s="2" t="n">
         <v>-0.002501705708437548</v>
       </c>
+      <c r="Q118" s="1" t="n">
+        <v>0.04379</v>
+      </c>
+      <c r="R118" s="2" t="n">
+        <v>-0.001595987232102157</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6661,6 +7375,12 @@
       <c r="P119" s="3" t="n">
         <v>0.003772568040959344</v>
       </c>
+      <c r="Q119" s="1" t="n">
+        <v>0.003724</v>
+      </c>
+      <c r="R119" s="2" t="n">
+        <v>-0.0002684563758389618</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6713,6 +7433,12 @@
       <c r="P120" s="2" t="n">
         <v>-0.001273885350318472</v>
       </c>
+      <c r="Q120" s="1" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="R120" s="3" t="n">
+        <v>0.003826530612244901</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6765,6 +7491,12 @@
       <c r="P121" s="3" t="n">
         <v>0.005059021922428335</v>
       </c>
+      <c r="Q121" s="1" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="R121" s="2" t="n">
+        <v>-0.004026845637583822</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6817,6 +7549,12 @@
       <c r="P122" s="2" t="n">
         <v>-0.0008759635599158111</v>
       </c>
+      <c r="Q122" s="1" t="n">
+        <v>0.5691000000000001</v>
+      </c>
+      <c r="R122" s="2" t="n">
+        <v>-0.002104155707522319</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6869,6 +7607,12 @@
       <c r="P123" s="3" t="n">
         <v>0.01067280527362145</v>
       </c>
+      <c r="Q123" s="1" t="n">
+        <v>0.029104</v>
+      </c>
+      <c r="R123" s="3" t="n">
+        <v>0.00438278634779315</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6921,6 +7665,12 @@
       <c r="P124" s="3" t="n">
         <v>0.0005121638924455617</v>
       </c>
+      <c r="Q124" s="1" t="n">
+        <v>0.07803</v>
+      </c>
+      <c r="R124" s="2" t="n">
+        <v>-0.001407729715894535</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6973,6 +7723,12 @@
       <c r="P125" s="3" t="n">
         <v>0.003128054740957975</v>
       </c>
+      <c r="Q125" s="1" t="n">
+        <v>0.10231</v>
+      </c>
+      <c r="R125" s="2" t="n">
+        <v>-0.003020853634769097</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7025,6 +7781,12 @@
       <c r="P126" s="2" t="n">
         <v>-0.009985207100591822</v>
       </c>
+      <c r="Q126" s="1" t="n">
+        <v>0.02667</v>
+      </c>
+      <c r="R126" s="2" t="n">
+        <v>-0.003735524841240172</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7077,6 +7839,12 @@
       <c r="P127" s="2" t="n">
         <v>-0.003184713375796207</v>
       </c>
+      <c r="Q127" s="1" t="n">
+        <v>0.02195</v>
+      </c>
+      <c r="R127" s="3" t="n">
+        <v>0.001825650387950792</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7129,6 +7897,12 @@
       <c r="P128" s="3" t="n">
         <v>0.005579665220086869</v>
       </c>
+      <c r="Q128" s="1" t="n">
+        <v>0.1617</v>
+      </c>
+      <c r="R128" s="2" t="n">
+        <v>-0.003082614056720101</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7181,6 +7955,12 @@
       <c r="P129" s="3" t="n">
         <v>0.003586497890295432</v>
       </c>
+      <c r="Q129" s="1" t="n">
+        <v>0.1384</v>
+      </c>
+      <c r="R129" s="2" t="n">
+        <v>-0.03020110714035462</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7233,6 +8013,12 @@
       <c r="P130" s="2" t="n">
         <v>-0.01253072168019662</v>
       </c>
+      <c r="Q130" s="1" t="n">
+        <v>0.053718</v>
+      </c>
+      <c r="R130" s="3" t="n">
+        <v>0.01287828792306973</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7285,6 +8071,12 @@
       <c r="P131" s="3" t="n">
         <v>0.003307202351788247</v>
       </c>
+      <c r="Q131" s="1" t="n">
+        <v>0.08173</v>
+      </c>
+      <c r="R131" s="2" t="n">
+        <v>-0.002197533878647291</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7337,6 +8129,12 @@
       <c r="P132" s="3" t="n">
         <v>0.00689655172413797</v>
       </c>
+      <c r="Q132" s="1" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="R132" s="2" t="n">
+        <v>-0.00570776255707763</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7389,6 +8187,12 @@
       <c r="P133" s="3" t="n">
         <v>0.002592912705272162</v>
       </c>
+      <c r="Q133" s="1" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="R133" s="2" t="n">
+        <v>-0.005172413793103453</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7441,6 +8245,12 @@
       <c r="P134" s="2" t="n">
         <v>-0.003312355084465149</v>
       </c>
+      <c r="Q134" s="1" t="n">
+        <v>0.02991</v>
+      </c>
+      <c r="R134" s="2" t="n">
+        <v>-0.005982053838484534</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7493,6 +8303,12 @@
       <c r="P135" s="2" t="n">
         <v>-0.001139601139601093</v>
       </c>
+      <c r="Q135" s="1" t="n">
+        <v>0.01755</v>
+      </c>
+      <c r="R135" s="3" t="n">
+        <v>0.001140901312036462</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7545,6 +8361,12 @@
       <c r="P136" s="3" t="n">
         <v>0.003777657852131524</v>
       </c>
+      <c r="Q136" s="1" t="n">
+        <v>0.03721</v>
+      </c>
+      <c r="R136" s="3" t="n">
+        <v>0.0002688172043011576</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7597,6 +8419,12 @@
       <c r="P137" s="3" t="n">
         <v>0.01831775700934583</v>
       </c>
+      <c r="Q137" s="1" t="n">
+        <v>0.02706</v>
+      </c>
+      <c r="R137" s="2" t="n">
+        <v>-0.006607929515418488</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7649,6 +8477,12 @@
       <c r="P138" s="2" t="n">
         <v>-0.0007892659826360615</v>
       </c>
+      <c r="Q138" s="1" t="n">
+        <v>2.512</v>
+      </c>
+      <c r="R138" s="2" t="n">
+        <v>-0.007898894154818332</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7701,6 +8535,12 @@
       <c r="P139" s="3" t="n">
         <v>0.0008438818565401964</v>
       </c>
+      <c r="Q139" s="1" t="n">
+        <v>0.01182</v>
+      </c>
+      <c r="R139" s="2" t="n">
+        <v>-0.003372681281618896</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7753,6 +8593,12 @@
       <c r="P140" s="2" t="n">
         <v>-0.003315649867373986</v>
       </c>
+      <c r="Q140" s="1" t="n">
+        <v>0.01499</v>
+      </c>
+      <c r="R140" s="2" t="n">
+        <v>-0.002661343978709255</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7805,6 +8651,12 @@
       <c r="P141" s="3" t="n">
         <v>6.176270767718005e-05</v>
       </c>
+      <c r="Q141" s="1" t="n">
+        <v>16.139</v>
+      </c>
+      <c r="R141" s="2" t="n">
+        <v>-0.003273221343873569</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7857,6 +8709,12 @@
       <c r="P142" s="3" t="n">
         <v>0.0008019246190857733</v>
       </c>
+      <c r="Q142" s="1" t="n">
+        <v>0.01241</v>
+      </c>
+      <c r="R142" s="2" t="n">
+        <v>-0.005608974358974408</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7909,6 +8767,12 @@
       <c r="P143" s="2" t="n">
         <v>-0.001883948756593874</v>
       </c>
+      <c r="Q143" s="1" t="n">
+        <v>0.02661</v>
+      </c>
+      <c r="R143" s="3" t="n">
+        <v>0.00453001132502839</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7961,6 +8825,12 @@
       <c r="P144" s="3" t="n">
         <v>0.0004419889502761101</v>
       </c>
+      <c r="Q144" s="1" t="n">
+        <v>0.004567</v>
+      </c>
+      <c r="R144" s="3" t="n">
+        <v>0.008835873647006871</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8013,6 +8883,12 @@
       <c r="P145" s="3" t="n">
         <v>0.001215312943082822</v>
       </c>
+      <c r="Q145" s="1" t="n">
+        <v>1.9622</v>
+      </c>
+      <c r="R145" s="2" t="n">
+        <v>-0.007586485939712788</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8065,6 +8941,12 @@
       <c r="P146" s="3" t="n">
         <v>0.002171081198436884</v>
       </c>
+      <c r="Q146" s="1" t="n">
+        <v>0.02308</v>
+      </c>
+      <c r="R146" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8117,6 +8999,12 @@
       <c r="P147" s="3" t="n">
         <v>0.001006711409396049</v>
       </c>
+      <c r="Q147" s="1" t="n">
+        <v>0.08952</v>
+      </c>
+      <c r="R147" s="3" t="n">
+        <v>0.0003352329869259386</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8169,6 +9057,12 @@
       <c r="P148" s="3" t="n">
         <v>0.01293809367834915</v>
       </c>
+      <c r="Q148" s="1" t="n">
+        <v>0.06281</v>
+      </c>
+      <c r="R148" s="3" t="n">
+        <v>0.01552142279708977</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8221,6 +9115,12 @@
       <c r="P149" s="2" t="n">
         <v>-0.0006721559401780939</v>
       </c>
+      <c r="Q149" s="1" t="n">
+        <v>0.05938</v>
+      </c>
+      <c r="R149" s="2" t="n">
+        <v>-0.001513368084748609</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8273,6 +9173,12 @@
       <c r="P150" s="3" t="n">
         <v>0.001670129129496084</v>
       </c>
+      <c r="Q150" s="1" t="n">
+        <v>0.2462</v>
+      </c>
+      <c r="R150" s="3" t="n">
+        <v>0.001220008133387534</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8325,6 +9231,12 @@
       <c r="P151" s="3" t="n">
         <v>0.02440828402366863</v>
       </c>
+      <c r="Q151" s="1" t="n">
+        <v>6.85e-05</v>
+      </c>
+      <c r="R151" s="2" t="n">
+        <v>-0.01083032490974736</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8377,6 +9289,12 @@
       <c r="P152" s="2" t="n">
         <v>-0.004267744833782474</v>
       </c>
+      <c r="Q152" s="1" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="R152" s="3" t="n">
+        <v>0.003834874802616691</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8429,6 +9347,12 @@
       <c r="P153" s="2" t="n">
         <v>-0.0003269042170643641</v>
       </c>
+      <c r="Q153" s="1" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="R153" s="2" t="n">
+        <v>-0.001635055591890126</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8481,6 +9405,12 @@
       <c r="P154" s="2" t="n">
         <v>-0.001646542261251343</v>
       </c>
+      <c r="Q154" s="1" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="R154" s="2" t="n">
+        <v>-0.003573391973611939</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8533,6 +9463,12 @@
       <c r="P155" s="3" t="n">
         <v>0.001733102253032858</v>
       </c>
+      <c r="Q155" s="1" t="n">
+        <v>0.2305</v>
+      </c>
+      <c r="R155" s="2" t="n">
+        <v>-0.003027681660899561</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8585,6 +9521,12 @@
       <c r="P156" s="2" t="n">
         <v>-0.006208095356344679</v>
       </c>
+      <c r="Q156" s="1" t="n">
+        <v>0.08096</v>
+      </c>
+      <c r="R156" s="3" t="n">
+        <v>0.01149425287356327</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8637,6 +9579,12 @@
       <c r="P157" s="3" t="n">
         <v>0.005275189027606852</v>
       </c>
+      <c r="Q157" s="1" t="n">
+        <v>0.22938</v>
+      </c>
+      <c r="R157" s="3" t="n">
+        <v>0.003061046003148531</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8689,6 +9637,12 @@
       <c r="P158" s="2" t="n">
         <v>-0.0008003201280512434</v>
       </c>
+      <c r="Q158" s="1" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="R158" s="2" t="n">
+        <v>-0.002803364036844238</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8741,6 +9695,12 @@
       <c r="P159" s="3" t="n">
         <v>0.001710571330824459</v>
       </c>
+      <c r="Q159" s="1" t="n">
+        <v>2.934</v>
+      </c>
+      <c r="R159" s="3" t="n">
+        <v>0.00204918032786893</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8793,6 +9753,12 @@
       <c r="P160" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q160" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R160" s="2" t="n">
+        <v>-0.001996007984031855</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8845,6 +9811,12 @@
       <c r="P161" s="3" t="n">
         <v>0.001096491228070131</v>
       </c>
+      <c r="Q161" s="1" t="n">
+        <v>0.14569</v>
+      </c>
+      <c r="R161" s="2" t="n">
+        <v>-0.002669769989047108</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8897,6 +9869,12 @@
       <c r="P162" s="3" t="n">
         <v>0.006443694384780531</v>
       </c>
+      <c r="Q162" s="1" t="n">
+        <v>0.003269</v>
+      </c>
+      <c r="R162" s="2" t="n">
+        <v>-0.003353658536585282</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8949,6 +9927,12 @@
       <c r="P163" s="3" t="n">
         <v>0.002208835341365407</v>
       </c>
+      <c r="Q163" s="1" t="n">
+        <v>0.004995</v>
+      </c>
+      <c r="R163" s="3" t="n">
+        <v>0.0008014425966741196</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9001,6 +9985,12 @@
       <c r="P164" s="3" t="n">
         <v>0.00209643605870027</v>
       </c>
+      <c r="Q164" s="1" t="n">
+        <v>0.0951</v>
+      </c>
+      <c r="R164" s="2" t="n">
+        <v>-0.005230125523012556</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9053,6 +10043,12 @@
       <c r="P165" s="3" t="n">
         <v>0.005553740607644675</v>
       </c>
+      <c r="Q165" s="1" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="R165" s="2" t="n">
+        <v>-0.005198180636777096</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9105,6 +10101,12 @@
       <c r="P166" s="3" t="n">
         <v>0.002732829917295955</v>
       </c>
+      <c r="Q166" s="1" t="n">
+        <v>1.3911</v>
+      </c>
+      <c r="R166" s="2" t="n">
+        <v>-0.002295058452270022</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9157,6 +10159,12 @@
       <c r="P167" s="3" t="n">
         <v>0.001446654611211414</v>
       </c>
+      <c r="Q167" s="1" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="R167" s="2" t="n">
+        <v>-0.0007222824124231779</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9209,6 +10217,12 @@
       <c r="P168" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q168" s="1" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="R168" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9261,6 +10275,12 @@
       <c r="P169" s="3" t="n">
         <v>0.0111599594183294</v>
       </c>
+      <c r="Q169" s="1" t="n">
+        <v>0.02971</v>
+      </c>
+      <c r="R169" s="2" t="n">
+        <v>-0.006354515050167197</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9313,6 +10333,12 @@
       <c r="P170" s="3" t="n">
         <v>0.004370830457786881</v>
       </c>
+      <c r="Q170" s="1" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="R170" s="2" t="n">
+        <v>-0.005267979844250896</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9365,6 +10391,12 @@
       <c r="P171" s="2" t="n">
         <v>-0.005988023952095772</v>
       </c>
+      <c r="Q171" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="R171" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9417,6 +10449,12 @@
       <c r="P172" s="2" t="n">
         <v>-0.04285714285714281</v>
       </c>
+      <c r="Q172" s="1" t="n">
+        <v>1.33e-05</v>
+      </c>
+      <c r="R172" s="2" t="n">
+        <v>-0.007462686567164234</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9469,6 +10507,12 @@
       <c r="P173" s="3" t="n">
         <v>0.003328578221588236</v>
       </c>
+      <c r="Q173" s="1" t="n">
+        <v>0.02108</v>
+      </c>
+      <c r="R173" s="2" t="n">
+        <v>-0.0009478672985781604</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9521,6 +10565,12 @@
       <c r="P174" s="3" t="n">
         <v>0.001109385400488161</v>
       </c>
+      <c r="Q174" s="1" t="n">
+        <v>0.08986</v>
+      </c>
+      <c r="R174" s="2" t="n">
+        <v>-0.004210992907801477</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9573,6 +10623,12 @@
       <c r="P175" s="3" t="n">
         <v>0.001661129568106283</v>
       </c>
+      <c r="Q175" s="1" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="R175" s="2" t="n">
+        <v>-0.0002763957987838281</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9625,6 +10681,12 @@
       <c r="P176" s="3" t="n">
         <v>0.003741814780168392</v>
       </c>
+      <c r="Q176" s="1" t="n">
+        <v>0.02142</v>
+      </c>
+      <c r="R176" s="2" t="n">
+        <v>-0.001863932898415581</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9677,6 +10739,12 @@
       <c r="P177" s="2" t="n">
         <v>-0.001264222503160505</v>
       </c>
+      <c r="Q177" s="1" t="n">
+        <v>0.00788</v>
+      </c>
+      <c r="R177" s="2" t="n">
+        <v>-0.002531645569620369</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9729,6 +10797,12 @@
       <c r="P178" s="3" t="n">
         <v>0.001027749229188103</v>
       </c>
+      <c r="Q178" s="1" t="n">
+        <v>0.000964</v>
+      </c>
+      <c r="R178" s="2" t="n">
+        <v>-0.01026694045174541</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9781,6 +10855,12 @@
       <c r="P179" s="3" t="n">
         <v>0.0007865757734660542</v>
       </c>
+      <c r="Q179" s="1" t="n">
+        <v>0.022803</v>
+      </c>
+      <c r="R179" s="2" t="n">
+        <v>-0.004322766570605117</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9833,6 +10913,12 @@
       <c r="P180" s="2" t="n">
         <v>-0.01361182820934049</v>
       </c>
+      <c r="Q180" s="1" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="R180" s="2" t="n">
+        <v>-0.01498929336188451</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9885,6 +10971,12 @@
       <c r="P181" s="3" t="n">
         <v>0.003603912819632728</v>
       </c>
+      <c r="Q181" s="1" t="n">
+        <v>0.5754</v>
+      </c>
+      <c r="R181" s="2" t="n">
+        <v>-0.01607387140902867</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9937,6 +11029,12 @@
       <c r="P182" s="3" t="n">
         <v>0.01535353535353529</v>
       </c>
+      <c r="Q182" s="1" t="n">
+        <v>0.04997</v>
+      </c>
+      <c r="R182" s="2" t="n">
+        <v>-0.005769996020692372</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9989,6 +11087,12 @@
       <c r="P183" s="3" t="n">
         <v>0.004950495049504976</v>
       </c>
+      <c r="Q183" s="1" t="n">
+        <v>5.472</v>
+      </c>
+      <c r="R183" s="2" t="n">
+        <v>-0.001642036124794646</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10041,6 +11145,12 @@
       <c r="P184" s="3" t="n">
         <v>0.00420315236427324</v>
       </c>
+      <c r="Q184" s="1" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="R184" s="3" t="n">
+        <v>0.001743983257760626</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10093,6 +11203,12 @@
       <c r="P185" s="2" t="n">
         <v>-0.007970244420828949</v>
       </c>
+      <c r="Q185" s="1" t="n">
+        <v>0.01868</v>
+      </c>
+      <c r="R185" s="3" t="n">
+        <v>0.0005356186395286338</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10145,6 +11261,12 @@
       <c r="P186" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q186" s="1" t="n">
+        <v>3.14e-05</v>
+      </c>
+      <c r="R186" s="2" t="n">
+        <v>-0.003174603174603252</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10197,6 +11319,12 @@
       <c r="P187" s="2" t="n">
         <v>-0.0006238303181534369</v>
       </c>
+      <c r="Q187" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="R187" s="2" t="n">
+        <v>-0.001248439450686591</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10249,6 +11377,12 @@
       <c r="P188" s="3" t="n">
         <v>0.003717472118959215</v>
       </c>
+      <c r="Q188" s="1" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="R188" s="2" t="n">
+        <v>-0.002469135802469206</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10301,6 +11435,12 @@
       <c r="P189" s="3" t="n">
         <v>0.01536697247706422</v>
       </c>
+      <c r="Q189" s="1" t="n">
+        <v>0.0004392</v>
+      </c>
+      <c r="R189" s="2" t="n">
+        <v>-0.007906031172351549</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10353,6 +11493,12 @@
       <c r="P190" s="3" t="n">
         <v>0.00560828300258851</v>
       </c>
+      <c r="Q190" s="1" t="n">
+        <v>0.02336</v>
+      </c>
+      <c r="R190" s="3" t="n">
+        <v>0.002145002145002058</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10405,6 +11551,12 @@
       <c r="P191" s="3" t="n">
         <v>0.001907183725365466</v>
       </c>
+      <c r="Q191" s="1" t="n">
+        <v>0.01579</v>
+      </c>
+      <c r="R191" s="3" t="n">
+        <v>0.001903553299492308</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10457,6 +11609,12 @@
       <c r="P192" s="3" t="n">
         <v>0.002321014104624266</v>
       </c>
+      <c r="Q192" s="1" t="n">
+        <v>0.05627</v>
+      </c>
+      <c r="R192" s="3" t="n">
+        <v>0.002315639472746672</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10509,6 +11667,12 @@
       <c r="P193" s="3" t="n">
         <v>0.009693053311793194</v>
       </c>
+      <c r="Q193" s="1" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="R193" s="2" t="n">
+        <v>-0.002133333333333395</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10561,6 +11725,12 @@
       <c r="P194" s="3" t="n">
         <v>0.005762179151388109</v>
       </c>
+      <c r="Q194" s="1" t="n">
+        <v>0.01914</v>
+      </c>
+      <c r="R194" s="2" t="n">
+        <v>-0.003124999999999873</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10613,6 +11783,12 @@
       <c r="P195" s="3" t="n">
         <v>0.0009308820107050405</v>
       </c>
+      <c r="Q195" s="1" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="R195" s="2" t="n">
+        <v>-0.005580097651708807</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10665,6 +11841,12 @@
       <c r="P196" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q196" s="1" t="n">
+        <v>0.01246</v>
+      </c>
+      <c r="R196" s="2" t="n">
+        <v>-0.001602564102564037</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10717,6 +11899,12 @@
       <c r="P197" s="3" t="n">
         <v>0.01509516517173477</v>
       </c>
+      <c r="Q197" s="1" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="R197" s="2" t="n">
+        <v>-0.006465517241379197</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10769,6 +11957,12 @@
       <c r="P198" s="2" t="n">
         <v>-0.001367989056087617</v>
       </c>
+      <c r="Q198" s="1" t="n">
+        <v>0.5091</v>
+      </c>
+      <c r="R198" s="2" t="n">
+        <v>-0.003718199608610593</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10821,6 +12015,12 @@
       <c r="P199" s="3" t="n">
         <v>0.01149425287356323</v>
       </c>
+      <c r="Q199" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="R199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10873,6 +12073,12 @@
       <c r="P200" s="3" t="n">
         <v>0.002020202020202097</v>
       </c>
+      <c r="Q200" s="1" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="R200" s="3" t="n">
+        <v>0.006048387096774184</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10925,6 +12131,12 @@
       <c r="P201" s="3" t="n">
         <v>0.00529193861351202</v>
       </c>
+      <c r="Q201" s="1" t="n">
+        <v>0.005716</v>
+      </c>
+      <c r="R201" s="3" t="n">
+        <v>0.00298297947008241</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10977,6 +12189,12 @@
       <c r="P202" s="3" t="n">
         <v>0.004721067221067134</v>
       </c>
+      <c r="Q202" s="1" t="n">
+        <v>0.023106</v>
+      </c>
+      <c r="R202" s="2" t="n">
+        <v>-0.003922921067379288</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11029,6 +12247,12 @@
       <c r="P203" s="3" t="n">
         <v>0.003649635036496328</v>
       </c>
+      <c r="Q203" s="1" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="R203" s="3" t="n">
+        <v>0.003636363636363614</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11081,6 +12305,12 @@
       <c r="P204" s="3" t="n">
         <v>0.002353633421594695</v>
       </c>
+      <c r="Q204" s="1" t="n">
+        <v>0.0338</v>
+      </c>
+      <c r="R204" s="2" t="n">
+        <v>-0.007924860581156629</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11133,6 +12363,12 @@
       <c r="P205" s="2" t="n">
         <v>-0.007294117647058751</v>
       </c>
+      <c r="Q205" s="1" t="n">
+        <v>4.213</v>
+      </c>
+      <c r="R205" s="2" t="n">
+        <v>-0.00142213794738095</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11185,6 +12421,12 @@
       <c r="P206" s="3" t="n">
         <v>0.005555555555555561</v>
       </c>
+      <c r="Q206" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="R206" s="2" t="n">
+        <v>-0.002762430939226522</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -11237,6 +12479,12 @@
       <c r="P207" s="3" t="n">
         <v>0.1455696202531644</v>
       </c>
+      <c r="Q207" s="1" t="n">
+        <v>0.0011102</v>
+      </c>
+      <c r="R207" s="2" t="n">
+        <v>-0.02639656230816445</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11289,6 +12537,12 @@
       <c r="P208" s="3" t="n">
         <v>0.0008238363311821954</v>
       </c>
+      <c r="Q208" s="1" t="n">
+        <v>0.007294</v>
+      </c>
+      <c r="R208" s="3" t="n">
+        <v>0.0006859651529702011</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11341,6 +12595,12 @@
       <c r="P209" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q209" s="1" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="R209" s="2" t="n">
+        <v>-0.001666666666666599</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11393,6 +12653,12 @@
       <c r="P210" s="3" t="n">
         <v>0.002318392581143914</v>
       </c>
+      <c r="Q210" s="1" t="n">
+        <v>0.1296</v>
+      </c>
+      <c r="R210" s="2" t="n">
+        <v>-0.0007710100231304297</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11445,6 +12711,12 @@
       <c r="P211" s="3" t="n">
         <v>0.003804424404678049</v>
       </c>
+      <c r="Q211" s="1" t="n">
+        <v>0.007107</v>
+      </c>
+      <c r="R211" s="2" t="n">
+        <v>-0.002386299831555379</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11497,6 +12769,12 @@
       <c r="P212" s="3" t="n">
         <v>0.01815008726003504</v>
       </c>
+      <c r="Q212" s="1" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="R212" s="3" t="n">
+        <v>0.02262598560164551</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11549,6 +12827,12 @@
       <c r="P213" s="2" t="n">
         <v>-0.0001763979537836677</v>
       </c>
+      <c r="Q213" s="1" t="n">
+        <v>0.05633</v>
+      </c>
+      <c r="R213" s="2" t="n">
+        <v>-0.006175017642907605</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11601,6 +12885,12 @@
       <c r="P214" s="3" t="n">
         <v>0.003725385843533679</v>
       </c>
+      <c r="Q214" s="1" t="n">
+        <v>0.1883</v>
+      </c>
+      <c r="R214" s="2" t="n">
+        <v>-0.001590668080593821</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11653,6 +12943,12 @@
       <c r="P215" s="3" t="n">
         <v>0.003817522427944241</v>
       </c>
+      <c r="Q215" s="1" t="n">
+        <v>0.05246</v>
+      </c>
+      <c r="R215" s="2" t="n">
+        <v>-0.002471952842745735</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11705,6 +13001,12 @@
       <c r="P216" s="2" t="n">
         <v>-0.0009569377990429818</v>
       </c>
+      <c r="Q216" s="1" t="n">
+        <v>0.002084</v>
+      </c>
+      <c r="R216" s="2" t="n">
+        <v>-0.001915708812260583</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11757,6 +13059,12 @@
       <c r="P217" s="3" t="n">
         <v>0.00299650407857511</v>
       </c>
+      <c r="Q217" s="1" t="n">
+        <v>6.007</v>
+      </c>
+      <c r="R217" s="2" t="n">
+        <v>-0.00298755186722003</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11809,6 +13117,12 @@
       <c r="P218" s="3" t="n">
         <v>0.002265005662514108</v>
       </c>
+      <c r="Q218" s="1" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="R218" s="2" t="n">
+        <v>-0.002259887005649669</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11861,6 +13175,12 @@
       <c r="P219" s="3" t="n">
         <v>0.003361972357116135</v>
       </c>
+      <c r="Q219" s="1" t="n">
+        <v>0.00538</v>
+      </c>
+      <c r="R219" s="3" t="n">
+        <v>0.001489203276247244</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11913,6 +13233,12 @@
       <c r="P220" s="2" t="n">
         <v>-0.0002425418384672098</v>
       </c>
+      <c r="Q220" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="R220" s="2" t="n">
+        <v>-0.0004852013585637842</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11965,6 +13291,12 @@
       <c r="P221" s="3" t="n">
         <v>0.004847645429362924</v>
       </c>
+      <c r="Q221" s="1" t="n">
+        <v>0.005783</v>
+      </c>
+      <c r="R221" s="2" t="n">
+        <v>-0.003618194348725049</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -12017,6 +13349,12 @@
       <c r="P222" s="3" t="n">
         <v>0.003311258278145637</v>
       </c>
+      <c r="Q222" s="1" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="R222" s="2" t="n">
+        <v>-0.003300330033003242</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12069,6 +13407,12 @@
       <c r="P223" s="3" t="n">
         <v>0.0005941770647652346</v>
       </c>
+      <c r="Q223" s="1" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="R223" s="2" t="n">
+        <v>-0.002375296912113918</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -12121,6 +13465,12 @@
       <c r="P224" s="3" t="n">
         <v>0.003010653080129615</v>
       </c>
+      <c r="Q224" s="1" t="n">
+        <v>0.4321</v>
+      </c>
+      <c r="R224" s="2" t="n">
+        <v>-0.002308935580697301</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -12173,6 +13523,12 @@
       <c r="P225" s="3" t="n">
         <v>0.0008380222674488283</v>
       </c>
+      <c r="Q225" s="1" t="n">
+        <v>0.0837</v>
+      </c>
+      <c r="R225" s="3" t="n">
+        <v>0.001196172248803862</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -12225,6 +13581,12 @@
       <c r="P226" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q226" s="1" t="n">
+        <v>0.01882</v>
+      </c>
+      <c r="R226" s="3" t="n">
+        <v>0.001063829787233999</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12277,6 +13639,12 @@
       <c r="P227" s="3" t="n">
         <v>0.006660936828534696</v>
       </c>
+      <c r="Q227" s="1" t="n">
+        <v>0.04667</v>
+      </c>
+      <c r="R227" s="2" t="n">
+        <v>-0.003842049092849511</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -12329,6 +13697,12 @@
       <c r="P228" s="3" t="n">
         <v>0.003879310344827728</v>
       </c>
+      <c r="Q228" s="1" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="R228" s="2" t="n">
+        <v>-0.00386431945040804</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -12381,6 +13755,12 @@
       <c r="P229" s="3" t="n">
         <v>0.003724394785847406</v>
       </c>
+      <c r="Q229" s="1" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="R229" s="2" t="n">
+        <v>-0.001855287569573337</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -12433,6 +13813,12 @@
       <c r="P230" s="3" t="n">
         <v>0.006626506024096324</v>
       </c>
+      <c r="Q230" s="1" t="n">
+        <v>0.1662</v>
+      </c>
+      <c r="R230" s="2" t="n">
+        <v>-0.005385996409335798</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12485,6 +13871,12 @@
       <c r="P231" s="3" t="n">
         <v>0.002953724975385619</v>
       </c>
+      <c r="Q231" s="1" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="R231" s="2" t="n">
+        <v>-0.001963350785340347</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -12537,6 +13929,12 @@
       <c r="P232" s="2" t="n">
         <v>-0.008232235701906378</v>
       </c>
+      <c r="Q232" s="1" t="n">
+        <v>0.02277</v>
+      </c>
+      <c r="R232" s="2" t="n">
+        <v>-0.005242463958060378</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12589,6 +13987,12 @@
       <c r="P233" s="2" t="n">
         <v>-0.001498002663115842</v>
       </c>
+      <c r="Q233" s="1" t="n">
+        <v>0.11973</v>
+      </c>
+      <c r="R233" s="2" t="n">
+        <v>-0.002083680613435575</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -12641,6 +14045,12 @@
       <c r="P234" s="3" t="n">
         <v>0.004748713889988264</v>
       </c>
+      <c r="Q234" s="1" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="R234" s="2" t="n">
+        <v>-0.003544702638834233</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -12693,6 +14103,12 @@
       <c r="P235" s="2" t="n">
         <v>-0.0004335260115607261</v>
       </c>
+      <c r="Q235" s="1" t="n">
+        <v>0.06926</v>
+      </c>
+      <c r="R235" s="3" t="n">
+        <v>0.001301142113633175</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -12745,6 +14161,12 @@
       <c r="P236" s="3" t="n">
         <v>0.008191455187921675</v>
       </c>
+      <c r="Q236" s="1" t="n">
+        <v>0.12553</v>
+      </c>
+      <c r="R236" s="2" t="n">
+        <v>-7.965588657009718e-05</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12797,6 +14219,12 @@
       <c r="P237" s="3" t="n">
         <v>0.01249024199843875</v>
       </c>
+      <c r="Q237" s="1" t="n">
+        <v>0.03882</v>
+      </c>
+      <c r="R237" s="2" t="n">
+        <v>-0.002313030069390897</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12849,6 +14277,12 @@
       <c r="P238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q238" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12901,6 +14335,12 @@
       <c r="P239" s="3" t="n">
         <v>0.02289493767489206</v>
       </c>
+      <c r="Q239" s="1" t="n">
+        <v>0.003995</v>
+      </c>
+      <c r="R239" s="2" t="n">
+        <v>-0.006466053220591888</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -12953,6 +14393,12 @@
       <c r="P240" s="3" t="n">
         <v>0.001457725947521933</v>
       </c>
+      <c r="Q240" s="1" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="R240" s="2" t="n">
+        <v>-0.002911208151382831</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13005,6 +14451,12 @@
       <c r="P241" s="3" t="n">
         <v>0.0002312673450508533</v>
       </c>
+      <c r="Q241" s="1" t="n">
+        <v>0.4377</v>
+      </c>
+      <c r="R241" s="3" t="n">
+        <v>0.0120231213872832</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -13057,6 +14509,12 @@
       <c r="P242" s="3" t="n">
         <v>0.008119079837618426</v>
       </c>
+      <c r="Q242" s="1" t="n">
+        <v>0.00745</v>
+      </c>
+      <c r="R242" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -13109,6 +14567,12 @@
       <c r="P243" s="3" t="n">
         <v>0.002181500872600411</v>
       </c>
+      <c r="Q243" s="1" t="n">
+        <v>0.02305</v>
+      </c>
+      <c r="R243" s="3" t="n">
+        <v>0.003482803656943849</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -13161,6 +14625,12 @@
       <c r="P244" s="3" t="n">
         <v>0.005389221556886164</v>
       </c>
+      <c r="Q244" s="1" t="n">
+        <v>0.001674</v>
+      </c>
+      <c r="R244" s="2" t="n">
+        <v>-0.002977963073257899</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -13213,6 +14683,12 @@
       <c r="P245" s="3" t="n">
         <v>0.0007604562737641748</v>
       </c>
+      <c r="Q245" s="1" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="R245" s="2" t="n">
+        <v>-0.002279635258358623</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -13265,6 +14741,12 @@
       <c r="P246" s="3" t="n">
         <v>0.0082618366698444</v>
       </c>
+      <c r="Q246" s="1" t="n">
+        <v>0.03127</v>
+      </c>
+      <c r="R246" s="2" t="n">
+        <v>-0.01449732114717939</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -13317,6 +14799,12 @@
       <c r="P247" s="3" t="n">
         <v>0.003954802259887041</v>
       </c>
+      <c r="Q247" s="1" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="R247" s="2" t="n">
+        <v>-0.001125492402926313</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -13369,6 +14857,12 @@
       <c r="P248" s="3" t="n">
         <v>0.004276315789473738</v>
       </c>
+      <c r="Q248" s="1" t="n">
+        <v>0.03061</v>
+      </c>
+      <c r="R248" s="3" t="n">
+        <v>0.002620373403209851</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -13421,6 +14915,12 @@
       <c r="P249" s="2" t="n">
         <v>-0.00607973810358938</v>
       </c>
+      <c r="Q249" s="1" t="n">
+        <v>0.008447</v>
+      </c>
+      <c r="R249" s="2" t="n">
+        <v>-0.006352193859545963</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13473,6 +14973,12 @@
       <c r="P250" s="2" t="n">
         <v>-0.002928257686676477</v>
       </c>
+      <c r="Q250" s="1" t="n">
+        <v>0.02031</v>
+      </c>
+      <c r="R250" s="2" t="n">
+        <v>-0.005873715124816377</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -13525,6 +15031,12 @@
       <c r="P251" s="3" t="n">
         <v>0.0002144542140253713</v>
       </c>
+      <c r="Q251" s="1" t="n">
+        <v>0.04653</v>
+      </c>
+      <c r="R251" s="2" t="n">
+        <v>-0.002358490566037714</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13577,6 +15089,12 @@
       <c r="P252" s="3" t="n">
         <v>0.004260859273286729</v>
       </c>
+      <c r="Q252" s="1" t="n">
+        <v>0.008455000000000001</v>
+      </c>
+      <c r="R252" s="2" t="n">
+        <v>-0.00353565114908648</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13629,6 +15147,12 @@
       <c r="P253" s="3" t="n">
         <v>0.004423627374447138</v>
       </c>
+      <c r="Q253" s="1" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="R253" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13681,6 +15205,12 @@
       <c r="P254" s="3" t="n">
         <v>0.0006547716483875981</v>
       </c>
+      <c r="Q254" s="1" t="n">
+        <v>0.06124</v>
+      </c>
+      <c r="R254" s="3" t="n">
+        <v>0.001799443808277539</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -13733,6 +15263,12 @@
       <c r="P255" s="2" t="n">
         <v>-0.001117942984907797</v>
       </c>
+      <c r="Q255" s="1" t="n">
+        <v>0.003566</v>
+      </c>
+      <c r="R255" s="2" t="n">
+        <v>-0.002238388360380459</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -13785,6 +15321,12 @@
       <c r="P256" s="2" t="n">
         <v>-0.002442375209891679</v>
       </c>
+      <c r="Q256" s="1" t="n">
+        <v>0.013088</v>
+      </c>
+      <c r="R256" s="3" t="n">
+        <v>0.001377199693955674</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -13837,6 +15379,12 @@
       <c r="P257" s="3" t="n">
         <v>5.303325184899008e-05</v>
       </c>
+      <c r="Q257" s="1" t="n">
+        <v>0.999426</v>
+      </c>
+      <c r="R257" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -13889,6 +15437,12 @@
       <c r="P258" s="3" t="n">
         <v>0.003565677478720851</v>
       </c>
+      <c r="Q258" s="1" t="n">
+        <v>0.08711000000000001</v>
+      </c>
+      <c r="R258" s="2" t="n">
+        <v>-0.001604584527220486</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -13941,6 +15495,12 @@
       <c r="P259" s="3" t="n">
         <v>0.01645583790439941</v>
       </c>
+      <c r="Q259" s="1" t="n">
+        <v>0.09046</v>
+      </c>
+      <c r="R259" s="2" t="n">
+        <v>-0.003744493392070561</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -13993,6 +15553,12 @@
       <c r="P260" s="3" t="n">
         <v>0.002702370716128215</v>
       </c>
+      <c r="Q260" s="1" t="n">
+        <v>0.08153000000000001</v>
+      </c>
+      <c r="R260" s="2" t="n">
+        <v>-0.001225039813793813</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -14045,6 +15611,12 @@
       <c r="P261" s="3" t="n">
         <v>0.01232394366197184</v>
       </c>
+      <c r="Q261" s="1" t="n">
+        <v>1.141</v>
+      </c>
+      <c r="R261" s="2" t="n">
+        <v>-0.00782608695652165</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -14097,6 +15669,12 @@
       <c r="P262" s="3" t="n">
         <v>0.01679761582227039</v>
       </c>
+      <c r="Q262" s="1" t="n">
+        <v>0.003786</v>
+      </c>
+      <c r="R262" s="3" t="n">
+        <v>0.008792965627498013</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -14149,6 +15727,12 @@
       <c r="P263" s="3" t="n">
         <v>0.01117798796216677</v>
       </c>
+      <c r="Q263" s="1" t="n">
+        <v>0.1173</v>
+      </c>
+      <c r="R263" s="2" t="n">
+        <v>-0.00255102040816322</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -14201,6 +15785,12 @@
       <c r="P264" s="3" t="n">
         <v>0.01073221395187821</v>
       </c>
+      <c r="Q264" s="1" t="n">
+        <v>0.0005868</v>
+      </c>
+      <c r="R264" s="3" t="n">
+        <v>0.004966603870525617</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -14253,6 +15843,12 @@
       <c r="P265" s="2" t="n">
         <v>-0.002691790040376858</v>
       </c>
+      <c r="Q265" s="1" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="R265" s="2" t="n">
+        <v>-0.001349527665317084</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -14305,6 +15901,12 @@
       <c r="P266" s="3" t="n">
         <v>0.001572327044025202</v>
       </c>
+      <c r="Q266" s="1" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="R266" s="2" t="n">
+        <v>-0.004709576138147701</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -14357,6 +15959,12 @@
       <c r="P267" s="2" t="n">
         <v>-0.004289215686274547</v>
       </c>
+      <c r="Q267" s="1" t="n">
+        <v>0.01628</v>
+      </c>
+      <c r="R267" s="3" t="n">
+        <v>0.001846153846153771</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -14409,6 +16017,12 @@
       <c r="P268" s="3" t="n">
         <v>0.0315911730545877</v>
       </c>
+      <c r="Q268" s="1" t="n">
+        <v>0.0004361</v>
+      </c>
+      <c r="R268" s="2" t="n">
+        <v>-0.01801396081963529</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -14461,6 +16075,12 @@
       <c r="P269" s="2" t="n">
         <v>-0.0009643201542913527</v>
       </c>
+      <c r="Q269" s="1" t="n">
+        <v>0.02072</v>
+      </c>
+      <c r="R269" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -14513,6 +16133,12 @@
       <c r="P270" s="3" t="n">
         <v>0.006124721603563418</v>
       </c>
+      <c r="Q270" s="1" t="n">
+        <v>0.1805</v>
+      </c>
+      <c r="R270" s="2" t="n">
+        <v>-0.001106806862202577</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -14565,6 +16191,12 @@
       <c r="P271" s="3" t="n">
         <v>0.002044989775051089</v>
       </c>
+      <c r="Q271" s="1" t="n">
+        <v>0.1469</v>
+      </c>
+      <c r="R271" s="2" t="n">
+        <v>-0.0006802721088434626</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -14617,6 +16249,12 @@
       <c r="P272" s="3" t="n">
         <v>0.007790902236742845</v>
       </c>
+      <c r="Q272" s="1" t="n">
+        <v>0.03978</v>
+      </c>
+      <c r="R272" s="2" t="n">
+        <v>-0.007980049875311569</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -14669,6 +16307,12 @@
       <c r="P273" s="3" t="n">
         <v>0.003232758620689658</v>
       </c>
+      <c r="Q273" s="1" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="R273" s="2" t="n">
+        <v>-0.004296455424274977</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14721,6 +16365,12 @@
       <c r="P274" s="3" t="n">
         <v>0.001109701965757772</v>
       </c>
+      <c r="Q274" s="1" t="n">
+        <v>63.13</v>
+      </c>
+      <c r="R274" s="2" t="n">
+        <v>-0.0003167062549484722</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14773,6 +16423,12 @@
       <c r="P275" s="3" t="n">
         <v>0.006156552330694866</v>
       </c>
+      <c r="Q275" s="1" t="n">
+        <v>0.01137</v>
+      </c>
+      <c r="R275" s="2" t="n">
+        <v>-0.006118881118881173</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -14825,6 +16481,12 @@
       <c r="P276" s="3" t="n">
         <v>0.003481624758220463</v>
       </c>
+      <c r="Q276" s="1" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="R276" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14877,6 +16539,12 @@
       <c r="P277" s="3" t="n">
         <v>0.003099666189795067</v>
       </c>
+      <c r="Q277" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="R277" s="2" t="n">
+        <v>-0.001663893510815322</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14929,6 +16597,12 @@
       <c r="P278" s="3" t="n">
         <v>0.02296450939457199</v>
       </c>
+      <c r="Q278" s="1" t="n">
+        <v>0.01972</v>
+      </c>
+      <c r="R278" s="3" t="n">
+        <v>0.006122448979591941</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14981,6 +16655,12 @@
       <c r="P279" s="2" t="n">
         <v>-0.001610882405584451</v>
       </c>
+      <c r="Q279" s="1" t="n">
+        <v>0.005612</v>
+      </c>
+      <c r="R279" s="3" t="n">
+        <v>0.006095374686267511</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -15033,6 +16713,12 @@
       <c r="P280" s="3" t="n">
         <v>0.006520605112154414</v>
       </c>
+      <c r="Q280" s="1" t="n">
+        <v>0.03856</v>
+      </c>
+      <c r="R280" s="2" t="n">
+        <v>-0.0007774034724022349</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -15085,6 +16771,12 @@
       <c r="P281" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q281" s="1" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="R281" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -15137,6 +16829,12 @@
       <c r="P282" s="3" t="n">
         <v>0.008210997760636904</v>
       </c>
+      <c r="Q282" s="1" t="n">
+        <v>0.0004034</v>
+      </c>
+      <c r="R282" s="2" t="n">
+        <v>-0.004442250740375098</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -15189,6 +16887,12 @@
       <c r="P283" s="2" t="n">
         <v>-0.00324270391618853</v>
       </c>
+      <c r="Q283" s="1" t="n">
+        <v>0.03995</v>
+      </c>
+      <c r="R283" s="2" t="n">
+        <v>-0.0002502502502503268</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -15241,6 +16945,12 @@
       <c r="P284" s="3" t="n">
         <v>0.006240998559769475</v>
       </c>
+      <c r="Q284" s="1" t="n">
+        <v>0.04184</v>
+      </c>
+      <c r="R284" s="2" t="n">
+        <v>-0.001908396946564808</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -15293,6 +17003,12 @@
       <c r="P285" s="2" t="n">
         <v>-0.001019745990544164</v>
       </c>
+      <c r="Q285" s="1" t="n">
+        <v>0.10761</v>
+      </c>
+      <c r="R285" s="2" t="n">
+        <v>-0.001391982182628038</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -15345,6 +17061,12 @@
       <c r="P286" s="3" t="n">
         <v>0.002386634844868638</v>
       </c>
+      <c r="Q286" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="R286" s="2" t="n">
+        <v>-0.004761904761904774</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -15397,6 +17119,12 @@
       <c r="P287" s="3" t="n">
         <v>0.008488626566748481</v>
       </c>
+      <c r="Q287" s="1" t="n">
+        <v>0.15227</v>
+      </c>
+      <c r="R287" s="3" t="n">
+        <v>0.001315183796935477</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -15449,6 +17177,12 @@
       <c r="P288" s="3" t="n">
         <v>0.003893214682981125</v>
       </c>
+      <c r="Q288" s="1" t="n">
+        <v>0.1811</v>
+      </c>
+      <c r="R288" s="3" t="n">
+        <v>0.003324099722991785</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -15501,6 +17235,12 @@
       <c r="P289" s="3" t="n">
         <v>0.005818181818181823</v>
       </c>
+      <c r="Q289" s="1" t="n">
+        <v>4.137</v>
+      </c>
+      <c r="R289" s="2" t="n">
+        <v>-0.002892263195950941</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -15553,6 +17293,12 @@
       <c r="P290" s="2" t="n">
         <v>-0.0003517823639773496</v>
       </c>
+      <c r="Q290" s="1" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="R290" s="2" t="n">
+        <v>-0.001759530791788988</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -15605,6 +17351,12 @@
       <c r="P291" s="3" t="n">
         <v>0.003394625176803453</v>
       </c>
+      <c r="Q291" s="1" t="n">
+        <v>0.03542</v>
+      </c>
+      <c r="R291" s="2" t="n">
+        <v>-0.0014096419509445</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -15657,6 +17409,12 @@
       <c r="P292" s="3" t="n">
         <v>0.001095290251916637</v>
       </c>
+      <c r="Q292" s="1" t="n">
+        <v>1.4615</v>
+      </c>
+      <c r="R292" s="2" t="n">
+        <v>-0.000615426695842383</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -15709,6 +17467,12 @@
       <c r="P293" s="3" t="n">
         <v>0.002053388090349052</v>
       </c>
+      <c r="Q293" s="1" t="n">
+        <v>0.005834</v>
+      </c>
+      <c r="R293" s="2" t="n">
+        <v>-0.00375683060109295</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -15761,6 +17525,12 @@
       <c r="P294" s="3" t="n">
         <v>0.0002937720329025067</v>
       </c>
+      <c r="Q294" s="1" t="n">
+        <v>0.003417</v>
+      </c>
+      <c r="R294" s="3" t="n">
+        <v>0.003524229074889826</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -15813,6 +17583,12 @@
       <c r="P295" s="3" t="n">
         <v>0.003163967988088656</v>
       </c>
+      <c r="Q295" s="1" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="R295" s="2" t="n">
+        <v>-0.001855287569573285</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -15865,6 +17641,12 @@
       <c r="P296" s="3" t="n">
         <v>0.003119429590017679</v>
       </c>
+      <c r="Q296" s="1" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="R296" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -15917,6 +17699,12 @@
       <c r="P297" s="3" t="n">
         <v>0.002357100766057857</v>
       </c>
+      <c r="Q297" s="1" t="n">
+        <v>0.01689</v>
+      </c>
+      <c r="R297" s="2" t="n">
+        <v>-0.007054673721340508</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -15969,6 +17757,12 @@
       <c r="P298" s="3" t="n">
         <v>0.0005580357142856528</v>
       </c>
+      <c r="Q298" s="1" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="R298" s="3" t="n">
+        <v>0.007808142777468</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -16021,6 +17815,12 @@
       <c r="P299" s="3" t="n">
         <v>0.002714932126696722</v>
       </c>
+      <c r="Q299" s="1" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="R299" s="2" t="n">
+        <v>-0.001805054151624475</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -16073,6 +17873,12 @@
       <c r="P300" s="3" t="n">
         <v>0.002422480620155108</v>
       </c>
+      <c r="Q300" s="1" t="n">
+        <v>0.02066</v>
+      </c>
+      <c r="R300" s="2" t="n">
+        <v>-0.001449975833736045</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -16125,6 +17931,12 @@
       <c r="P301" s="3" t="n">
         <v>0.0116279069767442</v>
       </c>
+      <c r="Q301" s="1" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="R301" s="3" t="n">
+        <v>0.005254515599343154</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -16177,6 +17989,12 @@
       <c r="P302" s="3" t="n">
         <v>0.01478196600147811</v>
       </c>
+      <c r="Q302" s="1" t="n">
+        <v>0.01368</v>
+      </c>
+      <c r="R302" s="2" t="n">
+        <v>-0.003641660597232316</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -16229,6 +18047,12 @@
       <c r="P303" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q303" s="1" t="n">
+        <v>0.07387000000000001</v>
+      </c>
+      <c r="R303" s="2" t="n">
+        <v>-0.001351899418683101</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -16281,6 +18105,12 @@
       <c r="P304" s="3" t="n">
         <v>0.001259445843828883</v>
       </c>
+      <c r="Q304" s="1" t="n">
+        <v>0.01592</v>
+      </c>
+      <c r="R304" s="3" t="n">
+        <v>0.001257861635220075</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -16333,6 +18163,12 @@
       <c r="P305" s="2" t="n">
         <v>-0.00123266563944525</v>
       </c>
+      <c r="Q305" s="1" t="n">
+        <v>0.06475</v>
+      </c>
+      <c r="R305" s="2" t="n">
+        <v>-0.001079913606911456</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -16385,6 +18221,12 @@
       <c r="P306" s="3" t="n">
         <v>0.002807862013638212</v>
       </c>
+      <c r="Q306" s="1" t="n">
+        <v>0.04976</v>
+      </c>
+      <c r="R306" s="2" t="n">
+        <v>-0.004800000000000082</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -16437,6 +18279,12 @@
       <c r="P307" s="3" t="n">
         <v>0.006486486486486492</v>
       </c>
+      <c r="Q307" s="1" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="R307" s="2" t="n">
+        <v>-0.006444683136412465</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -16489,6 +18337,12 @@
       <c r="P308" s="2" t="n">
         <v>-0.001006795872136883</v>
       </c>
+      <c r="Q308" s="1" t="n">
+        <v>0.03975</v>
+      </c>
+      <c r="R308" s="3" t="n">
+        <v>0.001511715797430021</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -16541,6 +18395,12 @@
       <c r="P309" s="2" t="n">
         <v>-0.004433185560481137</v>
       </c>
+      <c r="Q309" s="1" t="n">
+        <v>0.01561</v>
+      </c>
+      <c r="R309" s="2" t="n">
+        <v>-0.006997455470737959</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -16593,6 +18453,12 @@
       <c r="P310" s="3" t="n">
         <v>0.001845018450184555</v>
       </c>
+      <c r="Q310" s="1" t="n">
+        <v>0.05418</v>
+      </c>
+      <c r="R310" s="2" t="n">
+        <v>-0.002209944751381253</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -16645,6 +18511,12 @@
       <c r="P311" s="3" t="n">
         <v>0.0006732495511670553</v>
       </c>
+      <c r="Q311" s="1" t="n">
+        <v>0.004471</v>
+      </c>
+      <c r="R311" s="3" t="n">
+        <v>0.00269118636465572</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -16697,6 +18569,12 @@
       <c r="P312" s="3" t="n">
         <v>0.001776198934280608</v>
       </c>
+      <c r="Q312" s="1" t="n">
+        <v>0.08450000000000001</v>
+      </c>
+      <c r="R312" s="2" t="n">
+        <v>-0.001182033096926584</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -16749,6 +18627,12 @@
       <c r="P313" s="3" t="n">
         <v>0.003209414281893609</v>
       </c>
+      <c r="Q313" s="1" t="n">
+        <v>0.07488</v>
+      </c>
+      <c r="R313" s="2" t="n">
+        <v>-0.001866169021594258</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -16801,6 +18685,12 @@
       <c r="P314" s="3" t="n">
         <v>0.001958224543080905</v>
       </c>
+      <c r="Q314" s="1" t="n">
+        <v>0.1532</v>
+      </c>
+      <c r="R314" s="2" t="n">
+        <v>-0.001954397394136773</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -16853,6 +18743,12 @@
       <c r="P315" s="3" t="n">
         <v>0.001879699248120268</v>
       </c>
+      <c r="Q315" s="1" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="R315" s="2" t="n">
+        <v>-0.001876172607879892</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -16905,6 +18801,12 @@
       <c r="P316" s="3" t="n">
         <v>0.003873824017708944</v>
       </c>
+      <c r="Q316" s="1" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="R316" s="3" t="n">
+        <v>0.01047409040793817</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -16957,6 +18859,12 @@
       <c r="P317" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q317" s="1" t="n">
+        <v>0.007497</v>
+      </c>
+      <c r="R317" s="2" t="n">
+        <v>-0.0006664889362836305</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -17009,6 +18917,12 @@
       <c r="P318" s="2" t="n">
         <v>-0.008735358348223069</v>
       </c>
+      <c r="Q318" s="1" t="n">
+        <v>0.04993</v>
+      </c>
+      <c r="R318" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -17061,6 +18975,12 @@
       <c r="P319" s="3" t="n">
         <v>0.002234153724190154</v>
       </c>
+      <c r="Q319" s="1" t="n">
+        <v>0.27776</v>
+      </c>
+      <c r="R319" s="2" t="n">
+        <v>-0.001330313162909364</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -17113,6 +19033,12 @@
       <c r="P320" s="3" t="n">
         <v>0.00386803185437993</v>
       </c>
+      <c r="Q320" s="1" t="n">
+        <v>0.4403</v>
+      </c>
+      <c r="R320" s="2" t="n">
+        <v>-0.002039891205802258</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -17165,6 +19091,12 @@
       <c r="P321" s="3" t="n">
         <v>0.0003875468285749692</v>
       </c>
+      <c r="Q321" s="1" t="n">
+        <v>0.07747999999999999</v>
+      </c>
+      <c r="R321" s="3" t="n">
+        <v>0.0005165289256198137</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -17217,6 +19149,12 @@
       <c r="P322" s="3" t="n">
         <v>0.0006146281499692009</v>
       </c>
+      <c r="Q322" s="1" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="R322" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -17269,6 +19207,12 @@
       <c r="P323" s="3" t="n">
         <v>0.001012145748987855</v>
       </c>
+      <c r="Q323" s="1" t="n">
+        <v>1.982</v>
+      </c>
+      <c r="R323" s="3" t="n">
+        <v>0.002022244691607686</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -17321,6 +19265,12 @@
       <c r="P324" s="3" t="n">
         <v>0.0008069964717363819</v>
       </c>
+      <c r="Q324" s="1" t="n">
+        <v>0.053254</v>
+      </c>
+      <c r="R324" s="2" t="n">
+        <v>-0.001368912558366244</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -17373,6 +19323,12 @@
       <c r="P325" s="3" t="n">
         <v>0.002284148012791158</v>
       </c>
+      <c r="Q325" s="1" t="n">
+        <v>0.15314</v>
+      </c>
+      <c r="R325" s="2" t="n">
+        <v>-0.002864956374527907</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -17425,6 +19381,12 @@
       <c r="P326" s="3" t="n">
         <v>0.00666666666666661</v>
       </c>
+      <c r="Q326" s="1" t="n">
+        <v>0.006494</v>
+      </c>
+      <c r="R326" s="3" t="n">
+        <v>0.0001540120129370295</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -17477,6 +19439,12 @@
       <c r="P327" s="3" t="n">
         <v>0.001453776514901173</v>
       </c>
+      <c r="Q327" s="1" t="n">
+        <v>0.015181</v>
+      </c>
+      <c r="R327" s="3" t="n">
+        <v>0.001715605410755525</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -17529,6 +19497,12 @@
       <c r="P328" s="3" t="n">
         <v>0.004223864836325212</v>
       </c>
+      <c r="Q328" s="1" t="n">
+        <v>0.0948</v>
+      </c>
+      <c r="R328" s="2" t="n">
+        <v>-0.003154574132492204</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -17581,6 +19555,12 @@
       <c r="P329" s="3" t="n">
         <v>0.003173164097914806</v>
       </c>
+      <c r="Q329" s="1" t="n">
+        <v>0.004422</v>
+      </c>
+      <c r="R329" s="2" t="n">
+        <v>-0.000903750564844223</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -17633,6 +19613,12 @@
       <c r="P330" s="3" t="n">
         <v>0.002519868191510082</v>
       </c>
+      <c r="Q330" s="1" t="n">
+        <v>0.05158</v>
+      </c>
+      <c r="R330" s="2" t="n">
+        <v>-0.002706883217324076</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -17685,6 +19671,12 @@
       <c r="P331" s="2" t="n">
         <v>-0.008759923350670705</v>
       </c>
+      <c r="Q331" s="1" t="n">
+        <v>0.03627</v>
+      </c>
+      <c r="R331" s="3" t="n">
+        <v>0.001657000828500347</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -17737,6 +19729,12 @@
       <c r="P332" s="3" t="n">
         <v>0.0006839945280438901</v>
       </c>
+      <c r="Q332" s="1" t="n">
+        <v>0.1461</v>
+      </c>
+      <c r="R332" s="2" t="n">
+        <v>-0.001367053998632985</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -17789,6 +19787,12 @@
       <c r="P333" s="3" t="n">
         <v>0.003112033195020692</v>
       </c>
+      <c r="Q333" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="R333" s="2" t="n">
+        <v>-0.003102378490175747</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -17841,6 +19845,12 @@
       <c r="P334" s="2" t="n">
         <v>-0.0004576659038903003</v>
       </c>
+      <c r="Q334" s="1" t="n">
+        <v>0.04382</v>
+      </c>
+      <c r="R334" s="3" t="n">
+        <v>0.003205128205128234</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -17893,6 +19903,12 @@
       <c r="P335" s="2" t="n">
         <v>-0.0002461538461539215</v>
       </c>
+      <c r="Q335" s="1" t="n">
+        <v>0.08104</v>
+      </c>
+      <c r="R335" s="2" t="n">
+        <v>-0.002339037301489545</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -17945,6 +19961,12 @@
       <c r="P336" s="3" t="n">
         <v>0.001466992665036785</v>
       </c>
+      <c r="Q336" s="1" t="n">
+        <v>0.2044</v>
+      </c>
+      <c r="R336" s="2" t="n">
+        <v>-0.001953125000000056</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -17997,6 +20019,12 @@
       <c r="P337" s="3" t="n">
         <v>0.002946954813359579</v>
       </c>
+      <c r="Q337" s="1" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="R337" s="2" t="n">
+        <v>-0.0009794319294808612</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -18049,6 +20077,12 @@
       <c r="P338" s="3" t="n">
         <v>0.003542958370239128</v>
       </c>
+      <c r="Q338" s="1" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="R338" s="2" t="n">
+        <v>-0.002647837599293863</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -18101,6 +20135,12 @@
       <c r="P339" s="3" t="n">
         <v>0.001638448935008125</v>
       </c>
+      <c r="Q339" s="1" t="n">
+        <v>0.01832</v>
+      </c>
+      <c r="R339" s="2" t="n">
+        <v>-0.001090512540894176</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -18153,6 +20193,12 @@
       <c r="P340" s="2" t="n">
         <v>-0.003670051665775987</v>
       </c>
+      <c r="Q340" s="1" t="n">
+        <v>0.27947</v>
+      </c>
+      <c r="R340" s="2" t="n">
+        <v>-0.0005364423145697142</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -18205,6 +20251,12 @@
       <c r="P341" s="3" t="n">
         <v>0.0002323960027888232</v>
       </c>
+      <c r="Q341" s="1" t="n">
+        <v>0.04305</v>
+      </c>
+      <c r="R341" s="3" t="n">
+        <v>0.0002323420074348542</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -18257,6 +20309,12 @@
       <c r="P342" s="2" t="n">
         <v>-0.003312101910827979</v>
       </c>
+      <c r="Q342" s="1" t="n">
+        <v>0.07686</v>
+      </c>
+      <c r="R342" s="2" t="n">
+        <v>-0.01763803680981603</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -18309,6 +20367,12 @@
       <c r="P343" s="3" t="n">
         <v>0.001571709233791808</v>
       </c>
+      <c r="Q343" s="1" t="n">
+        <v>7.647</v>
+      </c>
+      <c r="R343" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -18361,6 +20425,12 @@
       <c r="P344" s="3" t="n">
         <v>0.004160426027625325</v>
       </c>
+      <c r="Q344" s="1" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="R344" s="2" t="n">
+        <v>-0.003148823334438204</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -18413,6 +20483,12 @@
       <c r="P345" s="3" t="n">
         <v>0.007021334053470061</v>
       </c>
+      <c r="Q345" s="1" t="n">
+        <v>0.03722</v>
+      </c>
+      <c r="R345" s="2" t="n">
+        <v>-0.001877178868329141</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -18465,6 +20541,12 @@
       <c r="P346" s="3" t="n">
         <v>0.002415458937198137</v>
       </c>
+      <c r="Q346" s="1" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="R346" s="2" t="n">
+        <v>-0.002409638554216936</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -18517,6 +20599,12 @@
       <c r="P347" s="3" t="n">
         <v>0.008111239860950085</v>
       </c>
+      <c r="Q347" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="R347" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -18569,6 +20657,12 @@
       <c r="P348" s="2" t="n">
         <v>-0.0006738803958565982</v>
       </c>
+      <c r="Q348" s="1" t="n">
+        <v>5189.9</v>
+      </c>
+      <c r="R348" s="2" t="n">
+        <v>-7.706683621381148e-05</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -18621,6 +20715,12 @@
       <c r="P349" s="3" t="n">
         <v>0.002945508100147283</v>
       </c>
+      <c r="Q349" s="1" t="n">
+        <v>0.01409</v>
+      </c>
+      <c r="R349" s="3" t="n">
+        <v>0.03450807635829662</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -18673,6 +20773,12 @@
       <c r="P350" s="3" t="n">
         <v>0.01005361930294912</v>
       </c>
+      <c r="Q350" s="1" t="n">
+        <v>0.01509</v>
+      </c>
+      <c r="R350" s="3" t="n">
+        <v>0.001327140013271346</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -18725,6 +20831,12 @@
       <c r="P351" s="3" t="n">
         <v>0.007404969557347467</v>
       </c>
+      <c r="Q351" s="1" t="n">
+        <v>0.0006101</v>
+      </c>
+      <c r="R351" s="2" t="n">
+        <v>-0.003430251551780459</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -18777,6 +20889,12 @@
       <c r="P352" s="3" t="n">
         <v>0.00304568527918787</v>
       </c>
+      <c r="Q352" s="1" t="n">
+        <v>0.01969</v>
+      </c>
+      <c r="R352" s="2" t="n">
+        <v>-0.003542510121457521</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -18829,6 +20947,12 @@
       <c r="P353" s="3" t="n">
         <v>0.003007841873455673</v>
       </c>
+      <c r="Q353" s="1" t="n">
+        <v>0.0934</v>
+      </c>
+      <c r="R353" s="3" t="n">
+        <v>0.0003213023455071463</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -18881,6 +21005,12 @@
       <c r="P354" s="3" t="n">
         <v>0.004419889502762404</v>
       </c>
+      <c r="Q354" s="1" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="R354" s="2" t="n">
+        <v>-0.001100110011000979</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -18933,6 +21063,12 @@
       <c r="P355" s="3" t="n">
         <v>0.008484255180290452</v>
       </c>
+      <c r="Q355" s="1" t="n">
+        <v>0.0006214</v>
+      </c>
+      <c r="R355" s="3" t="n">
+        <v>0.00533894191878341</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -18985,6 +21121,12 @@
       <c r="P356" s="3" t="n">
         <v>0.00243190661478594</v>
       </c>
+      <c r="Q356" s="1" t="n">
+        <v>2.051</v>
+      </c>
+      <c r="R356" s="2" t="n">
+        <v>-0.004852013585637936</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -19037,6 +21179,12 @@
       <c r="P357" s="2" t="n">
         <v>-0.008643042350907617</v>
       </c>
+      <c r="Q357" s="1" t="n">
+        <v>0.02278</v>
+      </c>
+      <c r="R357" s="2" t="n">
+        <v>-0.006974716652135875</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -19089,6 +21237,12 @@
       <c r="P358" s="3" t="n">
         <v>0.002475247524752401</v>
       </c>
+      <c r="Q358" s="1" t="n">
+        <v>0.000405</v>
+      </c>
+      <c r="R358" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -19141,6 +21295,12 @@
       <c r="P359" s="3" t="n">
         <v>0.002730375426621168</v>
       </c>
+      <c r="Q359" s="1" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="R359" s="3" t="n">
+        <v>0.0006807351940095026</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -19193,6 +21353,12 @@
       <c r="P360" s="2" t="n">
         <v>-0.0008965929468021412</v>
       </c>
+      <c r="Q360" s="1" t="n">
+        <v>0.003343</v>
+      </c>
+      <c r="R360" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -19245,6 +21411,12 @@
       <c r="P361" s="2" t="n">
         <v>-0.0004686767692547523</v>
       </c>
+      <c r="Q361" s="1" t="n">
+        <v>0.6392</v>
+      </c>
+      <c r="R361" s="2" t="n">
+        <v>-0.0009377930603314237</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -19297,6 +21469,12 @@
       <c r="P362" s="3" t="n">
         <v>0.002575107296137234</v>
       </c>
+      <c r="Q362" s="1" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="R362" s="2" t="n">
+        <v>-0.002568493150684827</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -19349,6 +21527,12 @@
       <c r="P363" s="3" t="n">
         <v>0.0007633587786258701</v>
       </c>
+      <c r="Q363" s="1" t="n">
+        <v>0.0654</v>
+      </c>
+      <c r="R363" s="2" t="n">
+        <v>-0.002288329519450761</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -19401,6 +21585,12 @@
       <c r="P364" s="3" t="n">
         <v>0.0002125850340136764</v>
       </c>
+      <c r="Q364" s="1" t="n">
+        <v>4.708</v>
+      </c>
+      <c r="R364" s="3" t="n">
+        <v>0.0006376195536663366</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -19453,6 +21643,12 @@
       <c r="P365" s="3" t="n">
         <v>0.001684210526315916</v>
       </c>
+      <c r="Q365" s="1" t="n">
+        <v>0.07131999999999999</v>
+      </c>
+      <c r="R365" s="2" t="n">
+        <v>-0.0007005744710663917</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -19505,6 +21701,12 @@
       <c r="P366" s="3" t="n">
         <v>0.008817707396076973</v>
       </c>
+      <c r="Q366" s="1" t="n">
+        <v>0.05595</v>
+      </c>
+      <c r="R366" s="2" t="n">
+        <v>-0.001962183374955387</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -19557,6 +21759,12 @@
       <c r="P367" s="3" t="n">
         <v>0.000513434879342723</v>
       </c>
+      <c r="Q367" s="1" t="n">
+        <v>0.05841</v>
+      </c>
+      <c r="R367" s="2" t="n">
+        <v>-0.0008552856654122722</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -19609,6 +21817,12 @@
       <c r="P368" s="3" t="n">
         <v>0.006305832895428258</v>
       </c>
+      <c r="Q368" s="1" t="n">
+        <v>0.05734</v>
+      </c>
+      <c r="R368" s="2" t="n">
+        <v>-0.001914708442123568</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -19661,6 +21875,12 @@
       <c r="P369" s="2" t="n">
         <v>-0.001291155584247961</v>
       </c>
+      <c r="Q369" s="1" t="n">
+        <v>0.03099</v>
+      </c>
+      <c r="R369" s="3" t="n">
+        <v>0.00161603102779578</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -19713,6 +21933,12 @@
       <c r="P370" s="3" t="n">
         <v>0.001847290640394134</v>
       </c>
+      <c r="Q370" s="1" t="n">
+        <v>0.0001624</v>
+      </c>
+      <c r="R370" s="2" t="n">
+        <v>-0.001843884449907851</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -19765,6 +21991,12 @@
       <c r="P371" s="3" t="n">
         <v>0.003388332351208081</v>
       </c>
+      <c r="Q371" s="1" t="n">
+        <v>0.006842</v>
+      </c>
+      <c r="R371" s="3" t="n">
+        <v>0.004551460872118599</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -19817,6 +22049,12 @@
       <c r="P372" s="3" t="n">
         <v>0.007794457274826823</v>
       </c>
+      <c r="Q372" s="1" t="n">
+        <v>0.006971</v>
+      </c>
+      <c r="R372" s="2" t="n">
+        <v>-0.001575479805213491</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -19869,6 +22107,12 @@
       <c r="P373" s="2" t="n">
         <v>-0.003143830233167411</v>
       </c>
+      <c r="Q373" s="1" t="n">
+        <v>3.803</v>
+      </c>
+      <c r="R373" s="2" t="n">
+        <v>-0.0005256241787122796</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -19921,6 +22165,12 @@
       <c r="P374" s="3" t="n">
         <v>0.0001415628539072763</v>
       </c>
+      <c r="Q374" s="1" t="n">
+        <v>0.07069</v>
+      </c>
+      <c r="R374" s="3" t="n">
+        <v>0.0005661712668081864</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -19973,6 +22223,12 @@
       <c r="P375" s="3" t="n">
         <v>0.00627963603742156</v>
       </c>
+      <c r="Q375" s="1" t="n">
+        <v>0.07835</v>
+      </c>
+      <c r="R375" s="2" t="n">
+        <v>-0.002165053489556845</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -20025,6 +22281,12 @@
       <c r="P376" s="3" t="n">
         <v>0.0006380602966980121</v>
       </c>
+      <c r="Q376" s="1" t="n">
+        <v>0.06268</v>
+      </c>
+      <c r="R376" s="2" t="n">
+        <v>-0.000797066794197266</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -20077,6 +22339,12 @@
       <c r="P377" s="3" t="n">
         <v>0.002623983206507554</v>
       </c>
+      <c r="Q377" s="1" t="n">
+        <v>0.07629</v>
+      </c>
+      <c r="R377" s="2" t="n">
+        <v>-0.001701125359853508</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -20129,6 +22397,12 @@
       <c r="P378" s="2" t="n">
         <v>-0.001244400199104062</v>
       </c>
+      <c r="Q378" s="1" t="n">
+        <v>0.0004024</v>
+      </c>
+      <c r="R378" s="3" t="n">
+        <v>0.002741091452778537</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -20181,6 +22455,12 @@
       <c r="P379" s="3" t="n">
         <v>0.002691427802449276</v>
       </c>
+      <c r="Q379" s="1" t="n">
+        <v>0.07439999999999999</v>
+      </c>
+      <c r="R379" s="2" t="n">
+        <v>-0.001476311904442529</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -20233,6 +22513,12 @@
       <c r="P380" s="3" t="n">
         <v>0.007446016381236058</v>
       </c>
+      <c r="Q380" s="1" t="n">
+        <v>0.001357</v>
+      </c>
+      <c r="R380" s="3" t="n">
+        <v>0.002956393200295551</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -20285,6 +22571,12 @@
       <c r="P381" s="3" t="n">
         <v>0.004679457182966815</v>
       </c>
+      <c r="Q381" s="1" t="n">
+        <v>6.385</v>
+      </c>
+      <c r="R381" s="2" t="n">
+        <v>-0.008694302126998921</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -20337,6 +22629,12 @@
       <c r="P382" s="3" t="n">
         <v>0.02923538230884556</v>
       </c>
+      <c r="Q382" s="1" t="n">
+        <v>0.01366</v>
+      </c>
+      <c r="R382" s="2" t="n">
+        <v>-0.005098324836125192</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -20389,6 +22687,12 @@
       <c r="P383" s="2" t="n">
         <v>-0.003968253968254004</v>
       </c>
+      <c r="Q383" s="1" t="n">
+        <v>0.01757</v>
+      </c>
+      <c r="R383" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -20441,6 +22745,12 @@
       <c r="P384" s="3" t="n">
         <v>0.0009842519685039652</v>
       </c>
+      <c r="Q384" s="1" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="R384" s="3" t="n">
+        <v>0.001966568338249811</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -20493,6 +22803,12 @@
       <c r="P385" s="3" t="n">
         <v>0.003349709691826836</v>
       </c>
+      <c r="Q385" s="1" t="n">
+        <v>4.478</v>
+      </c>
+      <c r="R385" s="2" t="n">
+        <v>-0.003338526596928682</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -20545,6 +22861,12 @@
       <c r="P386" s="3" t="n">
         <v>0.01016419077404221</v>
       </c>
+      <c r="Q386" s="1" t="n">
+        <v>0.001284</v>
+      </c>
+      <c r="R386" s="2" t="n">
+        <v>-0.006191950464396268</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -20597,6 +22919,12 @@
       <c r="P387" s="3" t="n">
         <v>0.0005060728744940309</v>
       </c>
+      <c r="Q387" s="1" t="n">
+        <v>0.0005917</v>
+      </c>
+      <c r="R387" s="2" t="n">
+        <v>-0.002360478839993313</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -20649,6 +22977,12 @@
       <c r="P388" s="3" t="n">
         <v>0.01244444444444455</v>
       </c>
+      <c r="Q388" s="1" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="R388" s="3" t="n">
+        <v>0.004389815627743608</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -20701,6 +23035,12 @@
       <c r="P389" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q389" s="1" t="n">
+        <v>0.00908</v>
+      </c>
+      <c r="R389" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -20753,6 +23093,12 @@
       <c r="P390" s="3" t="n">
         <v>0.004961832061068721</v>
       </c>
+      <c r="Q390" s="1" t="n">
+        <v>0.07890999999999999</v>
+      </c>
+      <c r="R390" s="2" t="n">
+        <v>-0.00101278642866199</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -20805,6 +23151,12 @@
       <c r="P391" s="3" t="n">
         <v>0.01095033242080573</v>
       </c>
+      <c r="Q391" s="1" t="n">
+        <v>0.05151</v>
+      </c>
+      <c r="R391" s="2" t="n">
+        <v>-0.003675048355899471</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -20857,6 +23209,12 @@
       <c r="P392" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q392" s="1" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="R392" s="2" t="n">
+        <v>-0.008368200836820106</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -20909,6 +23267,12 @@
       <c r="P393" s="2" t="n">
         <v>-0.001406469760900083</v>
       </c>
+      <c r="Q393" s="1" t="n">
+        <v>0.02141</v>
+      </c>
+      <c r="R393" s="3" t="n">
+        <v>0.005164319248826244</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -20961,6 +23325,12 @@
       <c r="P394" s="3" t="n">
         <v>0.000973236009732388</v>
       </c>
+      <c r="Q394" s="1" t="n">
+        <v>0.2052</v>
+      </c>
+      <c r="R394" s="2" t="n">
+        <v>-0.002430724355858048</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -21013,6 +23383,12 @@
       <c r="P395" s="3" t="n">
         <v>0.003089598352214157</v>
       </c>
+      <c r="Q395" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="R395" s="2" t="n">
+        <v>-0.001026694045174567</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -21065,6 +23441,12 @@
       <c r="P396" s="3" t="n">
         <v>0.004429678848283504</v>
       </c>
+      <c r="Q396" s="1" t="n">
+        <v>2.718</v>
+      </c>
+      <c r="R396" s="2" t="n">
+        <v>-0.001102535832414595</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -21117,6 +23499,12 @@
       <c r="P397" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q397" s="1" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="R397" s="2" t="n">
+        <v>-0.004750593824228033</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -21169,6 +23557,12 @@
       <c r="P398" s="3" t="n">
         <v>0.011908020804818</v>
       </c>
+      <c r="Q398" s="1" t="n">
+        <v>0.00737</v>
+      </c>
+      <c r="R398" s="2" t="n">
+        <v>-0.003111050994183748</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -21221,6 +23615,12 @@
       <c r="P399" s="3" t="n">
         <v>0.002301495972382008</v>
       </c>
+      <c r="Q399" s="1" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="R399" s="2" t="n">
+        <v>-0.004209720627631037</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -21273,6 +23673,12 @@
       <c r="P400" s="3" t="n">
         <v>0.004107424960505603</v>
       </c>
+      <c r="Q400" s="1" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="R400" s="2" t="n">
+        <v>-0.003146633102580242</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -21325,6 +23731,12 @@
       <c r="P401" s="3" t="n">
         <v>0.0006859651529702011</v>
       </c>
+      <c r="Q401" s="1" t="n">
+        <v>0.007251</v>
+      </c>
+      <c r="R401" s="2" t="n">
+        <v>-0.005895256375102893</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -21377,6 +23789,12 @@
       <c r="P402" s="3" t="n">
         <v>0.004596191726854932</v>
       </c>
+      <c r="Q402" s="1" t="n">
+        <v>0.004581</v>
+      </c>
+      <c r="R402" s="2" t="n">
+        <v>-0.001960784313725561</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -21429,6 +23847,12 @@
       <c r="P403" s="3" t="n">
         <v>0.001890359168241968</v>
       </c>
+      <c r="Q403" s="1" t="n">
+        <v>0.2646</v>
+      </c>
+      <c r="R403" s="2" t="n">
+        <v>-0.001509433962264194</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -21481,6 +23905,12 @@
       <c r="P404" s="3" t="n">
         <v>0.003754693366708435</v>
       </c>
+      <c r="Q404" s="1" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="R404" s="2" t="n">
+        <v>-0.002493765586034984</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -21533,6 +23963,12 @@
       <c r="P405" s="3" t="n">
         <v>0.008077544426494292</v>
       </c>
+      <c r="Q405" s="1" t="n">
+        <v>0.0008803</v>
+      </c>
+      <c r="R405" s="3" t="n">
+        <v>0.00766941391941392</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -21585,6 +24021,12 @@
       <c r="P406" s="3" t="n">
         <v>0.002172624925933358</v>
       </c>
+      <c r="Q406" s="1" t="n">
+        <v>0.005071</v>
+      </c>
+      <c r="R406" s="2" t="n">
+        <v>-0.0005912495072921557</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -21637,6 +24079,12 @@
       <c r="P407" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q407" s="1" t="n">
+        <v>0.01208</v>
+      </c>
+      <c r="R407" s="2" t="n">
+        <v>-0.003300330033003309</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -21689,6 +24137,12 @@
       <c r="P408" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q408" s="1" t="n">
+        <v>0.001447</v>
+      </c>
+      <c r="R408" s="3" t="n">
+        <v>0.0006915629322267745</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -21741,6 +24195,12 @@
       <c r="P409" s="2" t="n">
         <v>-0.002137894174238473</v>
       </c>
+      <c r="Q409" s="1" t="n">
+        <v>0.03715</v>
+      </c>
+      <c r="R409" s="2" t="n">
+        <v>-0.005088377075522114</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -21793,6 +24253,12 @@
       <c r="P410" s="3" t="n">
         <v>0.0006127450980391906</v>
       </c>
+      <c r="Q410" s="1" t="n">
+        <v>0.01628</v>
+      </c>
+      <c r="R410" s="2" t="n">
+        <v>-0.003061849357011722</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -21845,6 +24311,12 @@
       <c r="P411" s="3" t="n">
         <v>0.004219409282700543</v>
       </c>
+      <c r="Q411" s="1" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="R411" s="3" t="n">
+        <v>0.0005252100840335555</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -21897,6 +24369,12 @@
       <c r="P412" s="3" t="n">
         <v>0.002236802863107833</v>
       </c>
+      <c r="Q412" s="1" t="n">
+        <v>0.06727</v>
+      </c>
+      <c r="R412" s="3" t="n">
+        <v>0.0008927242969794764</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -21949,6 +24427,12 @@
       <c r="P413" s="3" t="n">
         <v>0.003155818540433925</v>
       </c>
+      <c r="Q413" s="1" t="n">
+        <v>2539</v>
+      </c>
+      <c r="R413" s="2" t="n">
+        <v>-0.00157294534014943</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -22001,6 +24485,12 @@
       <c r="P414" s="3" t="n">
         <v>0.0007655502392345514</v>
       </c>
+      <c r="Q414" s="1" t="n">
+        <v>0.05241</v>
+      </c>
+      <c r="R414" s="3" t="n">
+        <v>0.002294893861158828</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -22053,6 +24543,12 @@
       <c r="P415" s="3" t="n">
         <v>0.0017152658662092</v>
       </c>
+      <c r="Q415" s="1" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R415" s="2" t="n">
+        <v>-0.001141552511415526</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -22105,6 +24601,12 @@
       <c r="P416" s="3" t="n">
         <v>0.001595821848251835</v>
       </c>
+      <c r="Q416" s="1" t="n">
+        <v>0.06911</v>
+      </c>
+      <c r="R416" s="3" t="n">
+        <v>0.001013904982618781</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -22157,6 +24659,12 @@
       <c r="P417" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q417" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="R417" s="2" t="n">
+        <v>-0.02666666666666669</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -22209,6 +24717,12 @@
       <c r="P418" s="3" t="n">
         <v>0.00458415193189264</v>
       </c>
+      <c r="Q418" s="1" t="n">
+        <v>0.1535</v>
+      </c>
+      <c r="R418" s="3" t="n">
+        <v>0.0006518904823988852</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -22261,6 +24775,12 @@
       <c r="P419" s="2" t="n">
         <v>-0.008064516129032209</v>
       </c>
+      <c r="Q419" s="1" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="R419" s="3" t="n">
+        <v>0.008130081300812959</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -22313,6 +24833,12 @@
       <c r="P420" s="3" t="n">
         <v>0.01045478306325137</v>
       </c>
+      <c r="Q420" s="1" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="R420" s="2" t="n">
+        <v>-0.006725297465080271</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -22365,6 +24891,12 @@
       <c r="P421" s="3" t="n">
         <v>0.00378179557581713</v>
       </c>
+      <c r="Q421" s="1" t="n">
+        <v>0.19325</v>
+      </c>
+      <c r="R421" s="2" t="n">
+        <v>-0.00263212221304698</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -22417,6 +24949,12 @@
       <c r="P422" s="2" t="n">
         <v>-0.0005841121495326865</v>
       </c>
+      <c r="Q422" s="1" t="n">
+        <v>0.03415</v>
+      </c>
+      <c r="R422" s="2" t="n">
+        <v>-0.002045587375803641</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -22469,6 +25007,12 @@
       <c r="P423" s="3" t="n">
         <v>0.00282885431400291</v>
       </c>
+      <c r="Q423" s="1" t="n">
+        <v>0.1416</v>
+      </c>
+      <c r="R423" s="2" t="n">
+        <v>-0.001410437235543059</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -22521,6 +25065,12 @@
       <c r="P424" s="3" t="n">
         <v>0.003802281368821303</v>
       </c>
+      <c r="Q424" s="1" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="R424" s="2" t="n">
+        <v>-0.001893939393939317</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -22573,6 +25123,12 @@
       <c r="P425" s="3" t="n">
         <v>0.001908396946564808</v>
       </c>
+      <c r="Q425" s="1" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="R425" s="2" t="n">
+        <v>-0.0009523809523809797</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -22625,6 +25181,12 @@
       <c r="P426" s="2" t="n">
         <v>-0.002412031782065785</v>
       </c>
+      <c r="Q426" s="1" t="n">
+        <v>0.007047</v>
+      </c>
+      <c r="R426" s="3" t="n">
+        <v>0.00227563646707444</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -22677,6 +25239,12 @@
       <c r="P427" s="3" t="n">
         <v>0.00117739403453698</v>
       </c>
+      <c r="Q427" s="1" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="R427" s="3" t="n">
+        <v>0.0003920031360250722</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -22729,6 +25297,12 @@
       <c r="P428" s="3" t="n">
         <v>0.002362302623399219</v>
       </c>
+      <c r="Q428" s="1" t="n">
+        <v>0.008064</v>
+      </c>
+      <c r="R428" s="3" t="n">
+        <v>0.0002480774001488794</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -22781,6 +25355,12 @@
       <c r="P429" s="3" t="n">
         <v>0.006509357200976421</v>
       </c>
+      <c r="Q429" s="1" t="n">
+        <v>0.01238</v>
+      </c>
+      <c r="R429" s="3" t="n">
+        <v>0.0008084074373483906</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -22833,6 +25413,12 @@
       <c r="P430" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q430" s="1" t="n">
+        <v>0.06694</v>
+      </c>
+      <c r="R430" s="2" t="n">
+        <v>-0.0004479617739286583</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -22885,6 +25471,12 @@
       <c r="P431" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q431" s="1" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="R431" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -22937,6 +25529,12 @@
       <c r="P432" s="3" t="n">
         <v>0.0008243173621843717</v>
       </c>
+      <c r="Q432" s="1" t="n">
+        <v>0.009704000000000001</v>
+      </c>
+      <c r="R432" s="2" t="n">
+        <v>-0.0009265932255738281</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -22989,6 +25587,12 @@
       <c r="P433" s="3" t="n">
         <v>0.001450326323422879</v>
       </c>
+      <c r="Q433" s="1" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="R433" s="3" t="n">
+        <v>0.001689596910451379</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -23041,6 +25645,12 @@
       <c r="P434" s="2" t="n">
         <v>-0.002627806975633038</v>
       </c>
+      <c r="Q434" s="1" t="n">
+        <v>0.04191</v>
+      </c>
+      <c r="R434" s="3" t="n">
+        <v>0.003832335329341327</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -23093,6 +25703,12 @@
       <c r="P435" s="3" t="n">
         <v>0.005218525766470957</v>
       </c>
+      <c r="Q435" s="1" t="n">
+        <v>0.00154</v>
+      </c>
+      <c r="R435" s="2" t="n">
+        <v>-0.0006489292667100148</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -23145,6 +25761,12 @@
       <c r="P436" s="3" t="n">
         <v>0.002916514764856005</v>
       </c>
+      <c r="Q436" s="1" t="n">
+        <v>0.02753</v>
+      </c>
+      <c r="R436" s="3" t="n">
+        <v>0.0007270083605961172</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -23197,6 +25819,12 @@
       <c r="P437" s="2" t="n">
         <v>-0.007637289368408191</v>
       </c>
+      <c r="Q437" s="1" t="n">
+        <v>0.08207</v>
+      </c>
+      <c r="R437" s="3" t="n">
+        <v>0.002565355484974369</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -23249,6 +25877,12 @@
       <c r="P438" s="3" t="n">
         <v>0.006974716652136086</v>
       </c>
+      <c r="Q438" s="1" t="n">
+        <v>0.1151</v>
+      </c>
+      <c r="R438" s="2" t="n">
+        <v>-0.003463203463203562</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -23301,6 +25935,12 @@
       <c r="P439" s="3" t="n">
         <v>0.001296176279974078</v>
       </c>
+      <c r="Q439" s="1" t="n">
+        <v>1.544</v>
+      </c>
+      <c r="R439" s="2" t="n">
+        <v>-0.0006472491909384401</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -23353,6 +25993,12 @@
       <c r="P440" s="3" t="n">
         <v>0.008389261744966344</v>
       </c>
+      <c r="Q440" s="1" t="n">
+        <v>0.001801</v>
+      </c>
+      <c r="R440" s="2" t="n">
+        <v>-0.001109262340543445</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -23405,6 +26051,12 @@
       <c r="P441" s="2" t="n">
         <v>-0.0008152173913044089</v>
       </c>
+      <c r="Q441" s="1" t="n">
+        <v>0.03677</v>
+      </c>
+      <c r="R441" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -23457,6 +26109,12 @@
       <c r="P442" s="3" t="n">
         <v>0.001618122977346212</v>
       </c>
+      <c r="Q442" s="1" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="R442" s="2" t="n">
+        <v>-0.003769520732364061</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -23509,6 +26167,12 @@
       <c r="P443" s="3" t="n">
         <v>0.001799546201392537</v>
       </c>
+      <c r="Q443" s="1" t="n">
+        <v>0.12777</v>
+      </c>
+      <c r="R443" s="2" t="n">
+        <v>-0.002108716026241741</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -23561,6 +26225,12 @@
       <c r="P444" s="3" t="n">
         <v>0.002804557405784468</v>
       </c>
+      <c r="Q444" s="1" t="n">
+        <v>0.011535</v>
+      </c>
+      <c r="R444" s="3" t="n">
+        <v>0.00812794965915044</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -23613,6 +26283,12 @@
       <c r="P445" s="3" t="n">
         <v>0.004470938897168396</v>
       </c>
+      <c r="Q445" s="1" t="n">
+        <v>0.08087999999999999</v>
+      </c>
+      <c r="R445" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -23665,6 +26341,12 @@
       <c r="P446" s="3" t="n">
         <v>0.002844950213371207</v>
       </c>
+      <c r="Q446" s="1" t="n">
+        <v>0.0002117</v>
+      </c>
+      <c r="R446" s="3" t="n">
+        <v>0.0009456264775413942</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -23717,6 +26399,12 @@
       <c r="P447" s="3" t="n">
         <v>0.004615384615384695</v>
       </c>
+      <c r="Q447" s="1" t="n">
+        <v>0.00663</v>
+      </c>
+      <c r="R447" s="3" t="n">
+        <v>0.01531393568147004</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -23769,6 +26457,12 @@
       <c r="P448" s="2" t="n">
         <v>-0.005791161796151209</v>
       </c>
+      <c r="Q448" s="1" t="n">
+        <v>0.11082</v>
+      </c>
+      <c r="R448" s="2" t="n">
+        <v>-0.006900259879917492</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -23821,6 +26515,12 @@
       <c r="P449" s="3" t="n">
         <v>0.001188354129530629</v>
       </c>
+      <c r="Q449" s="1" t="n">
+        <v>0.001684</v>
+      </c>
+      <c r="R449" s="2" t="n">
+        <v>-0.0005934718100890995</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -23873,6 +26573,12 @@
       <c r="P450" s="3" t="n">
         <v>0.000968523002421331</v>
       </c>
+      <c r="Q450" s="1" t="n">
+        <v>0.0002067</v>
+      </c>
+      <c r="R450" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -23925,6 +26631,12 @@
       <c r="P451" s="3" t="n">
         <v>0.005686125852918959</v>
       </c>
+      <c r="Q451" s="1" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="R451" s="2" t="n">
+        <v>-0.008292499057670653</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -23977,6 +26689,12 @@
       <c r="P452" s="3" t="n">
         <v>0.004474272930648691</v>
       </c>
+      <c r="Q452" s="1" t="n">
+        <v>0.1344</v>
+      </c>
+      <c r="R452" s="2" t="n">
+        <v>-0.002227171492204861</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -24029,6 +26747,12 @@
       <c r="P453" s="3" t="n">
         <v>0.004589787722317799</v>
       </c>
+      <c r="Q453" s="1" t="n">
+        <v>0.000175</v>
+      </c>
+      <c r="R453" s="2" t="n">
+        <v>-0.0005711022272987004</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -24081,6 +26805,12 @@
       <c r="P454" s="3" t="n">
         <v>0.008943389267932866</v>
       </c>
+      <c r="Q454" s="1" t="n">
+        <v>0.1093</v>
+      </c>
+      <c r="R454" s="2" t="n">
+        <v>-0.001187974047336243</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -24133,6 +26863,12 @@
       <c r="P455" s="3" t="n">
         <v>0.0009984025559104332</v>
       </c>
+      <c r="Q455" s="1" t="n">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="R455" s="3" t="n">
+        <v>0.002393776181926948</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -24185,6 +26921,12 @@
       <c r="P456" s="2" t="n">
         <v>-0.0006881881881882252</v>
       </c>
+      <c r="Q456" s="1" t="n">
+        <v>0.015969</v>
+      </c>
+      <c r="R456" s="2" t="n">
+        <v>-0.0002504225881174814</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -24237,6 +26979,12 @@
       <c r="P457" s="3" t="n">
         <v>0.003290949887808574</v>
       </c>
+      <c r="Q457" s="1" t="n">
+        <v>0.006691</v>
+      </c>
+      <c r="R457" s="2" t="n">
+        <v>-0.002385567317727805</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -24289,6 +27037,12 @@
       <c r="P458" s="3" t="n">
         <v>0.001872269606823292</v>
       </c>
+      <c r="Q458" s="1" t="n">
+        <v>0.4811</v>
+      </c>
+      <c r="R458" s="2" t="n">
+        <v>-0.001038205980066331</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -24341,6 +27095,12 @@
       <c r="P459" s="3" t="n">
         <v>0.0003138239447668913</v>
       </c>
+      <c r="Q459" s="1" t="n">
+        <v>0.006366</v>
+      </c>
+      <c r="R459" s="2" t="n">
+        <v>-0.001411764705882268</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -24393,6 +27153,12 @@
       <c r="P460" s="3" t="n">
         <v>0.002175489485134117</v>
       </c>
+      <c r="Q460" s="1" t="n">
+        <v>0.1383</v>
+      </c>
+      <c r="R460" s="3" t="n">
+        <v>0.0007235890014472992</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -24445,6 +27211,12 @@
       <c r="P461" s="3" t="n">
         <v>0.003471833351999157</v>
       </c>
+      <c r="Q461" s="1" t="n">
+        <v>0.08987000000000001</v>
+      </c>
+      <c r="R461" s="3" t="n">
+        <v>0.003013392857142928</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -24497,6 +27269,12 @@
       <c r="P462" s="3" t="n">
         <v>0.002400698384984701</v>
       </c>
+      <c r="Q462" s="1" t="n">
+        <v>0.04613</v>
+      </c>
+      <c r="R462" s="3" t="n">
+        <v>0.004354452427607202</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -24549,6 +27327,12 @@
       <c r="P463" s="3" t="n">
         <v>0.002869440459110481</v>
       </c>
+      <c r="Q463" s="1" t="n">
+        <v>0.00698</v>
+      </c>
+      <c r="R463" s="2" t="n">
+        <v>-0.001430615164520686</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -24601,6 +27385,12 @@
       <c r="P464" s="3" t="n">
         <v>0.002291825821237673</v>
       </c>
+      <c r="Q464" s="1" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="R464" s="3" t="n">
+        <v>0.0007621951219511355</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -24653,6 +27443,12 @@
       <c r="P465" s="3" t="n">
         <v>0.006043370067543474</v>
       </c>
+      <c r="Q465" s="1" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="R465" s="2" t="n">
+        <v>-0.001766784452296821</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -24705,6 +27501,12 @@
       <c r="P466" s="3" t="n">
         <v>0.002820874471086039</v>
       </c>
+      <c r="Q466" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R466" s="2" t="n">
+        <v>-0.001406469760900142</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -24757,6 +27559,12 @@
       <c r="P467" s="3" t="n">
         <v>0.002619172341540148</v>
       </c>
+      <c r="Q467" s="1" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="R467" s="2" t="n">
+        <v>-0.00261233019853717</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -24809,6 +27617,12 @@
       <c r="P468" s="3" t="n">
         <v>0.01012145748987848</v>
       </c>
+      <c r="Q468" s="1" t="n">
+        <v>0.009979999999999999</v>
+      </c>
+      <c r="R468" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -24861,6 +27675,12 @@
       <c r="P469" s="3" t="n">
         <v>0.002490660024906602</v>
       </c>
+      <c r="Q469" s="1" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="R469" s="2" t="n">
+        <v>-0.001739130434782693</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -24913,6 +27733,12 @@
       <c r="P470" s="3" t="n">
         <v>0.002270147559591376</v>
       </c>
+      <c r="Q470" s="1" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="R470" s="2" t="n">
+        <v>-0.001132502831257079</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -24965,6 +27791,12 @@
       <c r="P471" s="3" t="n">
         <v>0.003101736972704649</v>
       </c>
+      <c r="Q471" s="1" t="n">
+        <v>3.231</v>
+      </c>
+      <c r="R471" s="2" t="n">
+        <v>-0.0009276437847866771</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -25017,6 +27849,12 @@
       <c r="P472" s="3" t="n">
         <v>0.009514515735545291</v>
       </c>
+      <c r="Q472" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="R472" s="3" t="n">
+        <v>0.005316578057032333</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -25069,6 +27907,12 @@
       <c r="P473" s="3" t="n">
         <v>0.008051529790660233</v>
       </c>
+      <c r="Q473" s="1" t="n">
+        <v>1.253</v>
+      </c>
+      <c r="R473" s="3" t="n">
+        <v>0.0007987220447283465</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -25121,6 +27965,12 @@
       <c r="P474" s="3" t="n">
         <v>0.004351405386334302</v>
       </c>
+      <c r="Q474" s="1" t="n">
+        <v>0.008538</v>
+      </c>
+      <c r="R474" s="2" t="n">
+        <v>-0.0002341920374707571</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -25173,6 +28023,12 @@
       <c r="P475" s="3" t="n">
         <v>0.00215982721382289</v>
       </c>
+      <c r="Q475" s="1" t="n">
+        <v>0.04162</v>
+      </c>
+      <c r="R475" s="2" t="n">
+        <v>-0.003352490421455968</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -25225,6 +28081,12 @@
       <c r="P476" s="3" t="n">
         <v>0.003434677521943854</v>
       </c>
+      <c r="Q476" s="1" t="n">
+        <v>0.07894</v>
+      </c>
+      <c r="R476" s="3" t="n">
+        <v>0.0007606490872209763</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -25277,6 +28139,12 @@
       <c r="P477" s="2" t="n">
         <v>-0.002844846451236425</v>
       </c>
+      <c r="Q477" s="1" t="n">
+        <v>0.13694</v>
+      </c>
+      <c r="R477" s="3" t="n">
+        <v>0.001755669348939415</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -25329,6 +28197,12 @@
       <c r="P478" s="3" t="n">
         <v>0.002530044275774869</v>
       </c>
+      <c r="Q478" s="1" t="n">
+        <v>0.04749</v>
+      </c>
+      <c r="R478" s="2" t="n">
+        <v>-0.00126182965299694</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -25381,6 +28255,12 @@
       <c r="P479" s="3" t="n">
         <v>0.003782863627766229</v>
       </c>
+      <c r="Q479" s="1" t="n">
+        <v>0.005294</v>
+      </c>
+      <c r="R479" s="2" t="n">
+        <v>-0.002449594874693799</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -25433,6 +28313,12 @@
       <c r="P480" s="3" t="n">
         <v>0.001077973409989301</v>
       </c>
+      <c r="Q480" s="1" t="n">
+        <v>0.2789</v>
+      </c>
+      <c r="R480" s="3" t="n">
+        <v>0.001076812634601461</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -25485,6 +28371,12 @@
       <c r="P481" s="3" t="n">
         <v>0.00171662485144581</v>
       </c>
+      <c r="Q481" s="1" t="n">
+        <v>0.07588</v>
+      </c>
+      <c r="R481" s="3" t="n">
+        <v>0.0002636435539151875</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -25537,6 +28429,12 @@
       <c r="P482" s="3" t="n">
         <v>0.0006756756756756481</v>
       </c>
+      <c r="Q482" s="1" t="n">
+        <v>0.01483</v>
+      </c>
+      <c r="R482" s="3" t="n">
+        <v>0.001350438892640053</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -25589,6 +28487,12 @@
       <c r="P483" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q483" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="R483" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -25641,6 +28545,12 @@
       <c r="P484" s="3" t="n">
         <v>0.002319109461966671</v>
       </c>
+      <c r="Q484" s="1" t="n">
+        <v>0.02155</v>
+      </c>
+      <c r="R484" s="2" t="n">
+        <v>-0.002776492364646044</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -25693,6 +28603,12 @@
       <c r="P485" s="3" t="n">
         <v>0.001565133638333838</v>
       </c>
+      <c r="Q485" s="1" t="n">
+        <v>0.00822</v>
+      </c>
+      <c r="R485" s="2" t="n">
+        <v>-0.01190046880634693</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -25745,6 +28661,12 @@
       <c r="P486" s="3" t="n">
         <v>0.002822580645161199</v>
       </c>
+      <c r="Q486" s="1" t="n">
+        <v>0.007465</v>
+      </c>
+      <c r="R486" s="3" t="n">
+        <v>0.0005361211633829957</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -25797,6 +28719,12 @@
       <c r="P487" s="3" t="n">
         <v>0.005415162454873676</v>
       </c>
+      <c r="Q487" s="1" t="n">
+        <v>0.1117</v>
+      </c>
+      <c r="R487" s="3" t="n">
+        <v>0.002692998204667816</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -25849,6 +28777,12 @@
       <c r="P488" s="3" t="n">
         <v>0.0002136067499733275</v>
       </c>
+      <c r="Q488" s="1" t="n">
+        <v>0.009351999999999999</v>
+      </c>
+      <c r="R488" s="2" t="n">
+        <v>-0.001388147357181085</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -25901,6 +28835,12 @@
       <c r="P489" s="3" t="n">
         <v>0.001559251559251496</v>
       </c>
+      <c r="Q489" s="1" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="R489" s="3" t="n">
+        <v>0.001556824078879203</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -25953,6 +28893,12 @@
       <c r="P490" s="3" t="n">
         <v>0.0001706484641638748</v>
       </c>
+      <c r="Q490" s="1" t="n">
+        <v>0.05867</v>
+      </c>
+      <c r="R490" s="3" t="n">
+        <v>0.001023716089404497</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -26005,6 +28951,12 @@
       <c r="P491" s="3" t="n">
         <v>0.002081165452653401</v>
       </c>
+      <c r="Q491" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="R491" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -26057,6 +29009,12 @@
       <c r="P492" s="3" t="n">
         <v>0.002260738507912671</v>
       </c>
+      <c r="Q492" s="1" t="n">
+        <v>1.329</v>
+      </c>
+      <c r="R492" s="2" t="n">
+        <v>-0.0007518796992482044</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -26109,6 +29067,12 @@
       <c r="P493" s="3" t="n">
         <v>0.001702127659574596</v>
       </c>
+      <c r="Q493" s="1" t="n">
+        <v>0.03523</v>
+      </c>
+      <c r="R493" s="2" t="n">
+        <v>-0.002265647125460314</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -26161,6 +29125,12 @@
       <c r="P494" s="3" t="n">
         <v>0.00645161290322595</v>
       </c>
+      <c r="Q494" s="1" t="n">
+        <v>0.01716</v>
+      </c>
+      <c r="R494" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -26213,6 +29183,12 @@
       <c r="P495" s="3" t="n">
         <v>0.0008444162972345022</v>
       </c>
+      <c r="Q495" s="1" t="n">
+        <v>0.04724</v>
+      </c>
+      <c r="R495" s="2" t="n">
+        <v>-0.003585741404767</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -26265,6 +29241,12 @@
       <c r="P496" s="3" t="n">
         <v>0.002074688796680557</v>
       </c>
+      <c r="Q496" s="1" t="n">
+        <v>0.04837</v>
+      </c>
+      <c r="R496" s="3" t="n">
+        <v>0.001449275362318853</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -26317,6 +29299,12 @@
       <c r="P497" s="3" t="n">
         <v>0.001208702659145941</v>
       </c>
+      <c r="Q497" s="1" t="n">
+        <v>0.04966</v>
+      </c>
+      <c r="R497" s="2" t="n">
+        <v>-0.0008048289738430256</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -26369,6 +29357,12 @@
       <c r="P498" s="3" t="n">
         <v>0.003820771101076728</v>
       </c>
+      <c r="Q498" s="1" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="R498" s="2" t="n">
+        <v>-0.001384083044982547</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -26421,6 +29415,12 @@
       <c r="P499" s="3" t="n">
         <v>0.002570694087403724</v>
       </c>
+      <c r="Q499" s="1" t="n">
+        <v>0.2725</v>
+      </c>
+      <c r="R499" s="2" t="n">
+        <v>-0.001831501831501833</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -26473,6 +29473,12 @@
       <c r="P500" s="3" t="n">
         <v>0.003759398496240611</v>
       </c>
+      <c r="Q500" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="R500" s="2" t="n">
+        <v>-0.003745318352059935</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -26525,6 +29531,12 @@
       <c r="P501" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q501" s="1" t="n">
+        <v>0.03575</v>
+      </c>
+      <c r="R501" s="2" t="n">
+        <v>-0.004732739420935509</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -26577,6 +29589,12 @@
       <c r="P502" s="3" t="n">
         <v>0.001256676091737522</v>
       </c>
+      <c r="Q502" s="1" t="n">
+        <v>0.03191</v>
+      </c>
+      <c r="R502" s="3" t="n">
+        <v>0.001255098839033523</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -26629,6 +29647,12 @@
       <c r="P503" s="3" t="n">
         <v>0.001035062750679285</v>
       </c>
+      <c r="Q503" s="1" t="n">
+        <v>0.007713</v>
+      </c>
+      <c r="R503" s="2" t="n">
+        <v>-0.003101977510663011</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -26681,6 +29705,12 @@
       <c r="P504" s="3" t="n">
         <v>0.007189542483660064</v>
       </c>
+      <c r="Q504" s="1" t="n">
+        <v>3.081</v>
+      </c>
+      <c r="R504" s="2" t="n">
+        <v>-0.0003244646333549286</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -26733,6 +29763,12 @@
       <c r="P505" s="3" t="n">
         <v>0.0008101539292465766</v>
       </c>
+      <c r="Q505" s="1" t="n">
+        <v>0.0007424</v>
+      </c>
+      <c r="R505" s="3" t="n">
+        <v>0.001618996222342187</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -26785,6 +29821,12 @@
       <c r="P506" s="3" t="n">
         <v>0.002704530087897118</v>
       </c>
+      <c r="Q506" s="1" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="R506" s="2" t="n">
+        <v>-0.003371544167228594</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -26837,6 +29879,12 @@
       <c r="P507" s="3" t="n">
         <v>0.002460456942003537</v>
       </c>
+      <c r="Q507" s="1" t="n">
+        <v>0.002847</v>
+      </c>
+      <c r="R507" s="2" t="n">
+        <v>-0.001753155680224333</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -26889,6 +29937,12 @@
       <c r="P508" s="3" t="n">
         <v>0.0003156067539846319</v>
       </c>
+      <c r="Q508" s="1" t="n">
+        <v>0.06340999999999999</v>
+      </c>
+      <c r="R508" s="3" t="n">
+        <v>0.0003155071777881723</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -26941,6 +29995,12 @@
       <c r="P509" s="3" t="n">
         <v>0.001781737193763921</v>
       </c>
+      <c r="Q509" s="1" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="R509" s="3" t="n">
+        <v>0.0008892841262782479</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -26993,6 +30053,12 @@
       <c r="P510" s="3" t="n">
         <v>0.006041466428669502</v>
       </c>
+      <c r="Q510" s="1" t="n">
+        <v>0.0007323</v>
+      </c>
+      <c r="R510" s="2" t="n">
+        <v>-0.0005459260270233516</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -27045,6 +30111,12 @@
       <c r="P511" s="3" t="n">
         <v>0.001811594202898552</v>
       </c>
+      <c r="Q511" s="1" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="R511" s="2" t="n">
+        <v>-0.0003616636528030542</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -27097,6 +30169,12 @@
       <c r="P512" s="3" t="n">
         <v>0.00666389004581418</v>
       </c>
+      <c r="Q512" s="1" t="n">
+        <v>0.0004852</v>
+      </c>
+      <c r="R512" s="3" t="n">
+        <v>0.003723624327678919</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -27149,6 +30227,12 @@
       <c r="P513" s="3" t="n">
         <v>0.003258508327299052</v>
       </c>
+      <c r="Q513" s="1" t="n">
+        <v>0.05546</v>
+      </c>
+      <c r="R513" s="3" t="n">
+        <v>0.0007217610970769633</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -27201,6 +30285,12 @@
       <c r="P514" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q514" s="1" t="n">
+        <v>0.03036</v>
+      </c>
+      <c r="R514" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -27253,6 +30343,12 @@
       <c r="P515" s="3" t="n">
         <v>0.002629272567922844</v>
       </c>
+      <c r="Q515" s="1" t="n">
+        <v>0.001142</v>
+      </c>
+      <c r="R515" s="2" t="n">
+        <v>-0.001748251748251791</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -27305,6 +30401,12 @@
       <c r="P516" s="2" t="n">
         <v>-0.0013558300692979</v>
       </c>
+      <c r="Q516" s="1" t="n">
+        <v>0.00662</v>
+      </c>
+      <c r="R516" s="2" t="n">
+        <v>-0.001357670840247447</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -27357,6 +30459,12 @@
       <c r="P517" s="3" t="n">
         <v>0.001758352172820915</v>
       </c>
+      <c r="Q517" s="1" t="n">
+        <v>0.03987</v>
+      </c>
+      <c r="R517" s="2" t="n">
+        <v>-0.0002507522567702137</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -27409,6 +30517,12 @@
       <c r="P518" s="3" t="n">
         <v>0.001947419668938712</v>
       </c>
+      <c r="Q518" s="1" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="R518" s="2" t="n">
+        <v>-0.0009718172983479384</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -27461,6 +30575,12 @@
       <c r="P519" s="2" t="n">
         <v>-0.001140250855188095</v>
       </c>
+      <c r="Q519" s="1" t="n">
+        <v>0.00876</v>
+      </c>
+      <c r="R519" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -27513,6 +30633,12 @@
       <c r="P520" s="3" t="n">
         <v>0.003132832080200504</v>
       </c>
+      <c r="Q520" s="1" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="R520" s="3" t="n">
+        <v>0.001249219237976301</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -27565,6 +30691,12 @@
       <c r="P521" s="2" t="n">
         <v>-0.003901895206243066</v>
       </c>
+      <c r="Q521" s="1" t="n">
+        <v>0.01788</v>
+      </c>
+      <c r="R521" s="3" t="n">
+        <v>0.0005595970900951087</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -27617,6 +30749,12 @@
       <c r="P522" s="3" t="n">
         <v>0.0006082725060827002</v>
       </c>
+      <c r="Q522" s="1" t="n">
+        <v>0.01638</v>
+      </c>
+      <c r="R522" s="2" t="n">
+        <v>-0.004255319148936208</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -27669,6 +30807,12 @@
       <c r="P523" s="2" t="n">
         <v>-0.0004778972520908639</v>
       </c>
+      <c r="Q523" s="1" t="n">
+        <v>0.004179</v>
+      </c>
+      <c r="R523" s="2" t="n">
+        <v>-0.0009562514941428792</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -27721,6 +30865,12 @@
       <c r="P524" s="3" t="n">
         <v>0.004933051444679396</v>
       </c>
+      <c r="Q524" s="1" t="n">
+        <v>0.01423</v>
+      </c>
+      <c r="R524" s="2" t="n">
+        <v>-0.002103786816269321</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -27773,6 +30923,12 @@
       <c r="P525" s="3" t="n">
         <v>0.001207243460764538</v>
       </c>
+      <c r="Q525" s="1" t="n">
+        <v>0.02487</v>
+      </c>
+      <c r="R525" s="2" t="n">
+        <v>-0.0004019292604501444</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -27825,6 +30981,12 @@
       <c r="P526" s="3" t="n">
         <v>0.001662510390689874</v>
       </c>
+      <c r="Q526" s="1" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="R526" s="2" t="n">
+        <v>-0.000829875518672223</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -27877,6 +31039,12 @@
       <c r="P527" s="3" t="n">
         <v>0.0006988120195666595</v>
       </c>
+      <c r="Q527" s="1" t="n">
+        <v>0.07198</v>
+      </c>
+      <c r="R527" s="3" t="n">
+        <v>0.005307262569832477</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -27929,6 +31097,12 @@
       <c r="P528" s="3" t="n">
         <v>0.002542177027963924</v>
       </c>
+      <c r="Q528" s="1" t="n">
+        <v>0.04331</v>
+      </c>
+      <c r="R528" s="2" t="n">
+        <v>-0.001613646841862624</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -27981,6 +31155,12 @@
       <c r="P529" s="3" t="n">
         <v>0.001111640463712889</v>
       </c>
+      <c r="Q529" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="R529" s="2" t="n">
+        <v>-0.0006345177664974361</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -28033,6 +31213,12 @@
       <c r="P530" s="3" t="n">
         <v>0.002591189954155868</v>
       </c>
+      <c r="Q530" s="1" t="n">
+        <v>0.005017</v>
+      </c>
+      <c r="R530" s="2" t="n">
+        <v>-0.002584493041749501</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -28085,6 +31271,12 @@
       <c r="P531" s="2" t="n">
         <v>-0.0007662835249043428</v>
       </c>
+      <c r="Q531" s="1" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="R531" s="2" t="n">
+        <v>-0.00460122699386495</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -28137,6 +31329,12 @@
       <c r="P532" s="3" t="n">
         <v>0.003001313074469958</v>
       </c>
+      <c r="Q532" s="1" t="n">
+        <v>0.05342</v>
+      </c>
+      <c r="R532" s="2" t="n">
+        <v>-0.000935103796521311</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -28189,6 +31387,12 @@
       <c r="P533" s="3" t="n">
         <v>0.00508021390374341</v>
       </c>
+      <c r="Q533" s="1" t="n">
+        <v>0.003726</v>
+      </c>
+      <c r="R533" s="2" t="n">
+        <v>-0.008778930566640074</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -28241,6 +31445,12 @@
       <c r="P534" s="3" t="n">
         <v>0.0005824111822947975</v>
       </c>
+      <c r="Q534" s="1" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="R534" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -28293,6 +31503,12 @@
       <c r="P535" s="3" t="n">
         <v>0.008928571428571494</v>
       </c>
+      <c r="Q535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="R535" s="2" t="n">
+        <v>-0.00884955752212396</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -28345,6 +31561,12 @@
       <c r="P536" s="3" t="n">
         <v>0.000673703121491146</v>
       </c>
+      <c r="Q536" s="1" t="n">
+        <v>0.0004437</v>
+      </c>
+      <c r="R536" s="2" t="n">
+        <v>-0.004263913824057433</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -28397,6 +31619,12 @@
       <c r="P537" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Q537" s="1" t="n">
+        <v>0.009679999999999999</v>
+      </c>
+      <c r="R537" s="2" t="n">
+        <v>-0.002061855670103187</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -28449,6 +31677,12 @@
       <c r="P538" s="3" t="n">
         <v>0.002563633034242835</v>
       </c>
+      <c r="Q538" s="1" t="n">
+        <v>0.05469</v>
+      </c>
+      <c r="R538" s="2" t="n">
+        <v>-0.001095890410958859</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -28501,6 +31735,12 @@
       <c r="P539" s="3" t="n">
         <v>0.000733568075117453</v>
       </c>
+      <c r="Q539" s="1" t="n">
+        <v>0.6824</v>
+      </c>
+      <c r="R539" s="3" t="n">
+        <v>0.0004398182084737824</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -28553,6 +31793,12 @@
       <c r="P540" s="3" t="n">
         <v>0.002645502645502721</v>
       </c>
+      <c r="Q540" s="1" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="R540" s="2" t="n">
+        <v>-0.002638522427440709</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -28605,6 +31851,12 @@
       <c r="P541" s="3" t="n">
         <v>0.002290076335877769</v>
       </c>
+      <c r="Q541" s="1" t="n">
+        <v>0.01309</v>
+      </c>
+      <c r="R541" s="2" t="n">
+        <v>-0.003046458492003055</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -28657,6 +31909,12 @@
       <c r="P542" s="2" t="n">
         <v>-0.01065340909090915</v>
       </c>
+      <c r="Q542" s="1" t="n">
+        <v>0.01401</v>
+      </c>
+      <c r="R542" s="3" t="n">
+        <v>0.005743000717875105</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -28708,6 +31966,12 @@
       </c>
       <c r="P543" s="3" t="n">
         <v>0.0005236515971374105</v>
+      </c>
+      <c r="Q543" s="1" t="n">
+        <v>0.05719</v>
+      </c>
+      <c r="R543" s="2" t="n">
+        <v>-0.002267969295185016</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T543"/>
+  <dimension ref="A1:V543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -446,6 +446,8 @@
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,6 +551,16 @@
           <t>change_02:15</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>price_02:30</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>change_02:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +625,12 @@
       <c r="T2" s="2" t="n">
         <v>-0.000169594910442403</v>
       </c>
+      <c r="U2" s="1" t="n">
+        <v>69970.7</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>-0.002631305118786547</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -677,6 +695,12 @@
       <c r="T3" s="2" t="n">
         <v>-0.0006319268909195641</v>
       </c>
+      <c r="U3" s="1" t="n">
+        <v>2051.69</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.002047764969113301</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -741,6 +765,12 @@
       <c r="T4" s="2" t="n">
         <v>-0.001039861351819797</v>
       </c>
+      <c r="U4" s="1" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.004279435577145389</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -805,6 +835,12 @@
       <c r="T5" s="2" t="n">
         <v>-0.03022460486181726</v>
       </c>
+      <c r="U5" s="1" t="n">
+        <v>0.010542</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>0.004765535646206605</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -869,6 +905,12 @@
       <c r="T6" s="2" t="n">
         <v>-0.001014860456687094</v>
       </c>
+      <c r="U6" s="1" t="n">
+        <v>1.3753</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.002031782889485622</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -933,6 +975,12 @@
       <c r="T7" s="2" t="n">
         <v>-0.0012723995334536</v>
       </c>
+      <c r="U7" s="1" t="n">
+        <v>0.09406</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.001380188979721746</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -997,6 +1045,12 @@
       <c r="T8" s="2" t="n">
         <v>-0.005888281788764557</v>
       </c>
+      <c r="U8" s="1" t="n">
+        <v>37.466</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.0003735325506935911</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1061,6 +1115,12 @@
       <c r="T9" s="3" t="n">
         <v>0.001830384380719947</v>
       </c>
+      <c r="U9" s="1" t="n">
+        <v>0.04958</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>0.00649614291514415</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1125,6 +1185,12 @@
       <c r="T10" s="2" t="n">
         <v>-0.005954912803062437</v>
       </c>
+      <c r="U10" s="1" t="n">
+        <v>18.668</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>-0.001497646555413042</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1189,6 +1255,12 @@
       <c r="T11" s="3" t="n">
         <v>0.0007992253661835172</v>
       </c>
+      <c r="U11" s="1" t="n">
+        <v>649.51</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>-0.002518620901481972</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1253,6 +1325,12 @@
       <c r="T12" s="3" t="n">
         <v>0.007016333103289619</v>
       </c>
+      <c r="U12" s="1" t="n">
+        <v>0.8683</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>-0.008223872073101067</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1317,6 +1395,12 @@
       <c r="T13" s="3" t="n">
         <v>0.0004273707203571082</v>
       </c>
+      <c r="U13" s="1" t="n">
+        <v>210.78</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>0.0004746535029428247</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1381,6 +1465,12 @@
       <c r="T14" s="3" t="n">
         <v>0.0009648144239756619</v>
       </c>
+      <c r="U14" s="1" t="n">
+        <v>0.0033221</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>0.0006626705623663197</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1445,6 +1535,12 @@
       <c r="T15" s="3" t="n">
         <v>0.02443756168952712</v>
       </c>
+      <c r="U15" s="1" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>0.04535034386524468</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1509,6 +1605,12 @@
       <c r="T16" s="2" t="n">
         <v>-0.000616016427104655</v>
       </c>
+      <c r="U16" s="1" t="n">
+        <v>0.9743000000000001</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>0.000924594205876322</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1573,6 +1675,12 @@
       <c r="T17" s="2" t="n">
         <v>-0.01067615658362995</v>
       </c>
+      <c r="U17" s="1" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>0.003597122302158377</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1637,6 +1745,12 @@
       <c r="T18" s="2" t="n">
         <v>-0.002433773284657915</v>
       </c>
+      <c r="U18" s="1" t="n">
+        <v>212.87</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>-0.001266773013042985</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1701,6 +1815,12 @@
       <c r="T19" s="2" t="n">
         <v>-0.0007627765064835163</v>
       </c>
+      <c r="U19" s="1" t="n">
+        <v>0.2615</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>-0.001908396946564887</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1765,6 +1885,12 @@
       <c r="T20" s="3" t="n">
         <v>0.002648616833431424</v>
       </c>
+      <c r="U20" s="1" t="n">
+        <v>0.017057</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>0.001291458761373508</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1829,6 +1955,12 @@
       <c r="T21" s="3" t="n">
         <v>0.002304388813239786</v>
       </c>
+      <c r="U21" s="1" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>0.0001045041279129946</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1893,6 +2025,12 @@
       <c r="T22" s="2" t="n">
         <v>-0.0005945303210463079</v>
       </c>
+      <c r="U22" s="1" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <v>0.005353955978584247</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1957,6 +2095,12 @@
       <c r="T23" s="3" t="n">
         <v>0.003301457194899802</v>
       </c>
+      <c r="U23" s="1" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>-0.007205264949506373</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2021,6 +2165,12 @@
       <c r="T24" s="2" t="n">
         <v>-0.006904487917146152</v>
       </c>
+      <c r="U24" s="1" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>0.002317497103128623</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2085,6 +2235,12 @@
       <c r="T25" s="3" t="n">
         <v>0.000111061750333321</v>
       </c>
+      <c r="U25" s="1" t="n">
+        <v>9.007999999999999</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>0.0003331482509714977</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2149,6 +2305,12 @@
       <c r="T26" s="3" t="n">
         <v>0.003734129947722267</v>
       </c>
+      <c r="U26" s="1" t="n">
+        <v>1.335</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>-0.00669642857142866</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2213,6 +2375,12 @@
       <c r="T27" s="3" t="n">
         <v>0.0002407968614185623</v>
       </c>
+      <c r="U27" s="1" t="n">
+        <v>5107.8</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>-0.0002877123346388534</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2277,6 +2445,12 @@
       <c r="T28" s="3" t="n">
         <v>0.004514672686230221</v>
       </c>
+      <c r="U28" s="1" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>0.001685393258426937</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2341,6 +2515,12 @@
       <c r="T29" s="2" t="n">
         <v>-0.003424657534246536</v>
       </c>
+      <c r="U29" s="1" t="n">
+        <v>2.616</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>-0.001145475372279539</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2405,6 +2585,12 @@
       <c r="T30" s="2" t="n">
         <v>-0.0060753129309894</v>
       </c>
+      <c r="U30" s="1" t="n">
+        <v>0.56887</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>-0.0008079672597615021</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2469,6 +2655,12 @@
       <c r="T31" s="2" t="n">
         <v>-0.001433349259436199</v>
       </c>
+      <c r="U31" s="1" t="n">
+        <v>0.002088</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>-0.0009569377990429818</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2533,6 +2725,12 @@
       <c r="T32" s="2" t="n">
         <v>-0.001619870410367163</v>
       </c>
+      <c r="U32" s="1" t="n">
+        <v>1.2902</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>-0.003167735455458543</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2597,6 +2795,12 @@
       <c r="T33" s="3" t="n">
         <v>0.01470137825421124</v>
       </c>
+      <c r="U33" s="1" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>0.02626018714156366</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2661,6 +2865,12 @@
       <c r="T34" s="2" t="n">
         <v>-0.001338688085676039</v>
       </c>
+      <c r="U34" s="1" t="n">
+        <v>1.496</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>0.002680965147453085</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2725,6 +2935,12 @@
       <c r="T35" s="2" t="n">
         <v>-0.000637951515684728</v>
       </c>
+      <c r="U35" s="1" t="n">
+        <v>454.87</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>0.001276717515243532</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2789,6 +3005,12 @@
       <c r="T36" s="2" t="n">
         <v>-0.004370447450572358</v>
       </c>
+      <c r="U36" s="1" t="n">
+        <v>0.04794</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>0.002090301003344541</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2853,6 +3075,12 @@
       <c r="T37" s="2" t="n">
         <v>-0.001131701796576634</v>
       </c>
+      <c r="U37" s="1" t="n">
+        <v>0.7057</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>-0.0005664919983004616</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2917,6 +3145,12 @@
       <c r="T38" s="3" t="n">
         <v>0.002849002849002799</v>
       </c>
+      <c r="U38" s="1" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>-0.001893939393939448</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2981,6 +3215,12 @@
       <c r="T39" s="2" t="n">
         <v>-0.003732702112163115</v>
       </c>
+      <c r="U39" s="1" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>0.00475189618934475</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3045,6 +3285,12 @@
       <c r="T40" s="3" t="n">
         <v>0.01147891083822744</v>
       </c>
+      <c r="U40" s="1" t="n">
+        <v>0.03765</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>-0.00633412509897063</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3109,6 +3355,12 @@
       <c r="T41" s="2" t="n">
         <v>-0.007235890014471861</v>
       </c>
+      <c r="U41" s="1" t="n">
+        <v>0.05495</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>0.001275510204081644</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3173,6 +3425,12 @@
       <c r="T42" s="2" t="n">
         <v>-0.001107419712070917</v>
       </c>
+      <c r="U42" s="1" t="n">
+        <v>54.18</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>0.001108647450110907</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3237,6 +3495,12 @@
       <c r="T43" s="3" t="n">
         <v>0.002283105022831221</v>
       </c>
+      <c r="U43" s="1" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>0.001518602885345315</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3301,6 +3565,12 @@
       <c r="T44" s="3" t="n">
         <v>0.001698369565217322</v>
       </c>
+      <c r="U44" s="1" t="n">
+        <v>0.005897</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>-0.0001695489996607775</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3365,6 +3635,12 @@
       <c r="T45" s="3" t="n">
         <v>0.0084042021010506</v>
       </c>
+      <c r="U45" s="1" t="n">
+        <v>0.10087</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>0.0007937295366603506</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3429,6 +3705,12 @@
       <c r="T46" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U46" s="1" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>0.001076426264800902</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3493,6 +3775,12 @@
       <c r="T47" s="2" t="n">
         <v>-0.0004498425551057787</v>
       </c>
+      <c r="U47" s="1" t="n">
+        <v>0.28886</v>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3557,6 +3845,12 @@
       <c r="T48" s="2" t="n">
         <v>-0.003734827264239006</v>
       </c>
+      <c r="U48" s="1" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="V48" s="3" t="n">
+        <v>0.004686035613870669</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3621,6 +3915,12 @@
       <c r="T49" s="2" t="n">
         <v>-0.004535882067066296</v>
       </c>
+      <c r="U49" s="1" t="n">
+        <v>0.24437</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>-0.005817737998372608</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3685,6 +3985,12 @@
       <c r="T50" s="3" t="n">
         <v>0.004028837998303704</v>
       </c>
+      <c r="U50" s="1" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="V50" s="3" t="n">
+        <v>0.005279831045406551</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3749,6 +4055,12 @@
       <c r="T51" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U51" s="1" t="n">
+        <v>3.902</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>0.001797175866495537</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3813,6 +4125,12 @@
       <c r="T52" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U52" s="1" t="n">
+        <v>0.00023</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>-0.004329004329004317</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3877,6 +4195,12 @@
       <c r="T53" s="3" t="n">
         <v>0.007228915662650475</v>
       </c>
+      <c r="U53" s="1" t="n">
+        <v>0.1674</v>
+      </c>
+      <c r="V53" s="3" t="n">
+        <v>0.001196172248803862</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3941,6 +4265,12 @@
       <c r="T54" s="2" t="n">
         <v>-0.002138783269961972</v>
       </c>
+      <c r="U54" s="1" t="n">
+        <v>0.04204</v>
+      </c>
+      <c r="V54" s="3" t="n">
+        <v>0.001190759704691627</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4005,6 +4335,12 @@
       <c r="T55" s="3" t="n">
         <v>0.006617706399806209</v>
       </c>
+      <c r="U55" s="1" t="n">
+        <v>0.12259</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>-0.01715705924797554</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4069,6 +4405,12 @@
       <c r="T56" s="2" t="n">
         <v>-0.002840012622278358</v>
       </c>
+      <c r="U56" s="1" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>-0.006645569620253135</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4133,6 +4475,12 @@
       <c r="T57" s="3" t="n">
         <v>0.004306632213608931</v>
       </c>
+      <c r="U57" s="1" t="n">
+        <v>0.01162</v>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>-0.003430531732418534</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4197,6 +4545,12 @@
       <c r="T58" s="2" t="n">
         <v>-0.002016129032257982</v>
       </c>
+      <c r="U58" s="1" t="n">
+        <v>0.09909999999999999</v>
+      </c>
+      <c r="V58" s="3" t="n">
+        <v>0.001010101010100899</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4261,6 +4615,12 @@
       <c r="T59" s="2" t="n">
         <v>-0.002994011976047912</v>
       </c>
+      <c r="U59" s="1" t="n">
+        <v>0.00333</v>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4325,6 +4685,12 @@
       <c r="T60" s="3" t="n">
         <v>0.001299545159194139</v>
       </c>
+      <c r="U60" s="1" t="n">
+        <v>0.1539</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>-0.001297858533419714</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4389,6 +4755,12 @@
       <c r="T61" s="3" t="n">
         <v>0.0001254311696456083</v>
       </c>
+      <c r="U61" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>-0.00294726280805166</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4453,6 +4825,12 @@
       <c r="T62" s="3" t="n">
         <v>0.003822738213223736</v>
       </c>
+      <c r="U62" s="1" t="n">
+        <v>0.7085</v>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>-0.0007052186177714315</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4517,6 +4895,12 @@
       <c r="T63" s="2" t="n">
         <v>-0.007159904534606174</v>
       </c>
+      <c r="U63" s="1" t="n">
+        <v>5.828</v>
+      </c>
+      <c r="V63" s="3" t="n">
+        <v>0.0006868131868132637</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4581,6 +4965,12 @@
       <c r="T64" s="3" t="n">
         <v>0.00435332116275813</v>
       </c>
+      <c r="U64" s="1" t="n">
+        <v>0.007136</v>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>-0.002237136465324439</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4645,6 +5035,12 @@
       <c r="T65" s="2" t="n">
         <v>-0.005372945638432474</v>
       </c>
+      <c r="U65" s="1" t="n">
+        <v>0.03198</v>
+      </c>
+      <c r="V65" s="3" t="n">
+        <v>0.01620591039084854</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4709,6 +5105,12 @@
       <c r="T66" s="3" t="n">
         <v>0.004273504273504159</v>
       </c>
+      <c r="U66" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>-0.004255319148936056</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4773,6 +5175,12 @@
       <c r="T67" s="3" t="n">
         <v>0.006215040397762591</v>
       </c>
+      <c r="U67" s="1" t="n">
+        <v>1.603</v>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>-0.009882643607164926</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4837,6 +5245,12 @@
       <c r="T68" s="2" t="n">
         <v>-4.990268975486149e-05</v>
       </c>
+      <c r="U68" s="1" t="n">
+        <v>2.0103</v>
+      </c>
+      <c r="V68" s="3" t="n">
+        <v>0.003243836710250499</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4901,6 +5315,12 @@
       <c r="T69" s="3" t="n">
         <v>0.001043115438108369</v>
       </c>
+      <c r="U69" s="1" t="n">
+        <v>0.5768</v>
+      </c>
+      <c r="V69" s="3" t="n">
+        <v>0.001736714136853076</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4965,6 +5385,12 @@
       <c r="T70" s="2" t="n">
         <v>-0.009523809523809533</v>
       </c>
+      <c r="U70" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="V70" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5029,6 +5455,12 @@
       <c r="T71" s="2" t="n">
         <v>-0.0023102310231023</v>
       </c>
+      <c r="U71" s="1" t="n">
+        <v>0.9082</v>
+      </c>
+      <c r="V71" s="3" t="n">
+        <v>0.001433454625647776</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5093,6 +5525,12 @@
       <c r="T72" s="3" t="n">
         <v>0.0002350728725904772</v>
       </c>
+      <c r="U72" s="1" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="V72" s="2" t="n">
+        <v>-0.0002350176263219483</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5157,6 +5595,12 @@
       <c r="T73" s="2" t="n">
         <v>-0.001275781416117467</v>
       </c>
+      <c r="U73" s="1" t="n">
+        <v>0.09385</v>
+      </c>
+      <c r="V73" s="2" t="n">
+        <v>-0.0009580583351074395</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5221,6 +5665,12 @@
       <c r="T74" s="2" t="n">
         <v>-0.003673576489110454</v>
       </c>
+      <c r="U74" s="1" t="n">
+        <v>1.1458</v>
+      </c>
+      <c r="V74" s="3" t="n">
+        <v>0.005881836537617354</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5285,6 +5735,12 @@
       <c r="T75" s="3" t="n">
         <v>0.002514142049025667</v>
       </c>
+      <c r="U75" s="1" t="n">
+        <v>0.01592</v>
+      </c>
+      <c r="V75" s="2" t="n">
+        <v>-0.001880877742946632</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5349,6 +5805,12 @@
       <c r="T76" s="3" t="n">
         <v>0.005316149818767683</v>
       </c>
+      <c r="U76" s="1" t="n">
+        <v>0.1256</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>0.006329621023956295</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5413,6 +5875,12 @@
       <c r="T77" s="2" t="n">
         <v>-0.0008554319931565685</v>
       </c>
+      <c r="U77" s="1" t="n">
+        <v>0.1171</v>
+      </c>
+      <c r="V77" s="3" t="n">
+        <v>0.002568493150684886</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5477,6 +5945,12 @@
       <c r="T78" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U78" s="1" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="V78" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5541,6 +6015,12 @@
       <c r="T79" s="3" t="n">
         <v>0.006022080963533029</v>
       </c>
+      <c r="U79" s="1" t="n">
+        <v>0.006003</v>
+      </c>
+      <c r="V79" s="2" t="n">
+        <v>-0.001829065513801229</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5605,6 +6085,12 @@
       <c r="T80" s="2" t="n">
         <v>-0.005381727158948857</v>
       </c>
+      <c r="U80" s="1" t="n">
+        <v>0.007918</v>
+      </c>
+      <c r="V80" s="2" t="n">
+        <v>-0.003649175789606079</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5669,6 +6155,12 @@
       <c r="T81" s="3" t="n">
         <v>0.001679731243001183</v>
       </c>
+      <c r="U81" s="1" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="V81" s="2" t="n">
+        <v>-0.002794857462269464</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5733,6 +6225,12 @@
       <c r="T82" s="3" t="n">
         <v>0.004326328800988913</v>
       </c>
+      <c r="U82" s="1" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="V82" s="2" t="n">
+        <v>-0.007384615384615425</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5797,6 +6295,12 @@
       <c r="T83" s="2" t="n">
         <v>-0.0001221448638084092</v>
       </c>
+      <c r="U83" s="1" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V83" s="3" t="n">
+        <v>0.001710236989982818</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5861,6 +6365,12 @@
       <c r="T84" s="3" t="n">
         <v>0.002215783194136781</v>
       </c>
+      <c r="U84" s="1" t="n">
+        <v>352.95</v>
+      </c>
+      <c r="V84" s="3" t="n">
+        <v>0.0004251700680271464</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5925,6 +6435,12 @@
       <c r="T85" s="2" t="n">
         <v>-0.003176930596285433</v>
       </c>
+      <c r="U85" s="1" t="n">
+        <v>0.004066</v>
+      </c>
+      <c r="V85" s="2" t="n">
+        <v>-0.003187055650894825</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5989,6 +6505,12 @@
       <c r="T86" s="2" t="n">
         <v>-0.008093797276853368</v>
       </c>
+      <c r="U86" s="1" t="n">
+        <v>0.13193</v>
+      </c>
+      <c r="V86" s="3" t="n">
+        <v>0.006100815984137841</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6053,6 +6575,12 @@
       <c r="T87" s="2" t="n">
         <v>-0.015223097112861</v>
       </c>
+      <c r="U87" s="1" t="n">
+        <v>0.01874</v>
+      </c>
+      <c r="V87" s="2" t="n">
+        <v>-0.001066098081023411</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6117,6 +6645,12 @@
       <c r="T88" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U88" s="1" t="n">
+        <v>1.132</v>
+      </c>
+      <c r="V88" s="3" t="n">
+        <v>0.002657218777679266</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6181,6 +6715,12 @@
       <c r="T89" s="2" t="n">
         <v>-0.001357773251866789</v>
       </c>
+      <c r="U89" s="1" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="V89" s="3" t="n">
+        <v>0.001019714479945503</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6245,6 +6785,12 @@
       <c r="T90" s="3" t="n">
         <v>0.0003894080996886468</v>
       </c>
+      <c r="U90" s="1" t="n">
+        <v>0.2569</v>
+      </c>
+      <c r="V90" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6309,6 +6855,12 @@
       <c r="T91" s="3" t="n">
         <v>0.0003551136363636219</v>
       </c>
+      <c r="U91" s="1" t="n">
+        <v>0.05686</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>0.009229676961306348</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6373,6 +6925,12 @@
       <c r="T92" s="3" t="n">
         <v>0.004074415744157505</v>
       </c>
+      <c r="U92" s="1" t="n">
+        <v>1.3082</v>
+      </c>
+      <c r="V92" s="3" t="n">
+        <v>0.001607840134752309</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6437,6 +6995,12 @@
       <c r="T93" s="3" t="n">
         <v>0.002541296060991002</v>
       </c>
+      <c r="U93" s="1" t="n">
+        <v>0.06304</v>
+      </c>
+      <c r="V93" s="2" t="n">
+        <v>-0.001267427122940379</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6501,6 +7065,12 @@
       <c r="T94" s="3" t="n">
         <v>0.002270147559591281</v>
       </c>
+      <c r="U94" s="1" t="n">
+        <v>0.00881</v>
+      </c>
+      <c r="V94" s="2" t="n">
+        <v>-0.002265005662514064</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6565,6 +7135,12 @@
       <c r="T95" s="3" t="n">
         <v>0.0006016847172082837</v>
       </c>
+      <c r="U95" s="1" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="V95" s="3" t="n">
+        <v>0.001202645820805807</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6629,6 +7205,12 @@
       <c r="T96" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U96" s="1" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="V96" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6693,6 +7275,12 @@
       <c r="T97" s="2" t="n">
         <v>-0.003977968176254668</v>
       </c>
+      <c r="U97" s="1" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="V97" s="3" t="n">
+        <v>0.002150537634408611</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6757,6 +7345,12 @@
       <c r="T98" s="3" t="n">
         <v>0.00452898550724628</v>
       </c>
+      <c r="U98" s="1" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="V98" s="2" t="n">
+        <v>-0.000901713255184752</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6821,6 +7415,12 @@
       <c r="T99" s="3" t="n">
         <v>0.001667778519012639</v>
       </c>
+      <c r="U99" s="1" t="n">
+        <v>3.004</v>
+      </c>
+      <c r="V99" s="3" t="n">
+        <v>0.0003330003330002963</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6885,6 +7485,12 @@
       <c r="T100" s="2" t="n">
         <v>-0.005815644082582111</v>
       </c>
+      <c r="U100" s="1" t="n">
+        <v>0.03426</v>
+      </c>
+      <c r="V100" s="3" t="n">
+        <v>0.002047382275519176</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6949,6 +7555,12 @@
       <c r="T101" s="2" t="n">
         <v>-0.0005512679162073384</v>
       </c>
+      <c r="U101" s="1" t="n">
+        <v>1.819</v>
+      </c>
+      <c r="V101" s="3" t="n">
+        <v>0.003309431880860455</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7013,6 +7625,12 @@
       <c r="T102" s="2" t="n">
         <v>-0.01453864977688216</v>
       </c>
+      <c r="U102" s="1" t="n">
+        <v>0.006866</v>
+      </c>
+      <c r="V102" s="3" t="n">
+        <v>0.002921413964358758</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7077,6 +7695,12 @@
       <c r="T103" s="3" t="n">
         <v>0.001789442290486266</v>
       </c>
+      <c r="U103" s="1" t="n">
+        <v>0.06630999999999999</v>
+      </c>
+      <c r="V103" s="2" t="n">
+        <v>-0.01295028282226868</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7141,6 +7765,12 @@
       <c r="T104" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U104" s="1" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="V104" s="3" t="n">
+        <v>0.0007304601899195689</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7205,6 +7835,12 @@
       <c r="T105" s="3" t="n">
         <v>0.0005608524957936691</v>
       </c>
+      <c r="U105" s="1" t="n">
+        <v>1.784</v>
+      </c>
+      <c r="V105" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7269,6 +7905,12 @@
       <c r="T106" s="3" t="n">
         <v>0.005654578979717382</v>
       </c>
+      <c r="U106" s="1" t="n">
+        <v>0.008265</v>
+      </c>
+      <c r="V106" s="3" t="n">
+        <v>0.01026769343601015</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7333,6 +7975,12 @@
       <c r="T107" s="3" t="n">
         <v>0.001103752759381853</v>
       </c>
+      <c r="U107" s="1" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="V107" s="3" t="n">
+        <v>0.001653803748621763</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7397,6 +8045,12 @@
       <c r="T108" s="3" t="n">
         <v>0.01316408086506812</v>
       </c>
+      <c r="U108" s="1" t="n">
+        <v>0.02148</v>
+      </c>
+      <c r="V108" s="2" t="n">
+        <v>-0.003248259860788892</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7461,6 +8115,12 @@
       <c r="T109" s="2" t="n">
         <v>-0.005550581915845977</v>
       </c>
+      <c r="U109" s="1" t="n">
+        <v>0.05553</v>
+      </c>
+      <c r="V109" s="2" t="n">
+        <v>-0.0001800504141158827</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7525,6 +8185,12 @@
       <c r="T110" s="3" t="n">
         <v>0.004220136077857122</v>
       </c>
+      <c r="U110" s="1" t="n">
+        <v>0.11611</v>
+      </c>
+      <c r="V110" s="2" t="n">
+        <v>-0.004202401372212611</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7589,6 +8255,12 @@
       <c r="T111" s="2" t="n">
         <v>-0.002951353551801329</v>
       </c>
+      <c r="U111" s="1" t="n">
+        <v>0.09783</v>
+      </c>
+      <c r="V111" s="2" t="n">
+        <v>-0.001429008880269483</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7653,6 +8325,12 @@
       <c r="T112" s="3" t="n">
         <v>0.002710027100270892</v>
       </c>
+      <c r="U112" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="V112" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7717,6 +8395,12 @@
       <c r="T113" s="3" t="n">
         <v>0.0001020512297174202</v>
       </c>
+      <c r="U113" s="1" t="n">
+        <v>0.09798999999999999</v>
+      </c>
+      <c r="V113" s="2" t="n">
+        <v>-0.0001020408163266327</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7781,6 +8465,12 @@
       <c r="T114" s="2" t="n">
         <v>-0.003484320557491248</v>
       </c>
+      <c r="U114" s="1" t="n">
+        <v>0.001711</v>
+      </c>
+      <c r="V114" s="2" t="n">
+        <v>-0.002913752913752921</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7845,6 +8535,12 @@
       <c r="T115" s="3" t="n">
         <v>0.002793965035523317</v>
       </c>
+      <c r="U115" s="1" t="n">
+        <v>1.2554</v>
+      </c>
+      <c r="V115" s="2" t="n">
+        <v>-0.0006368412673140518</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7909,6 +8605,12 @@
       <c r="T116" s="3" t="n">
         <v>0.002963590177815437</v>
       </c>
+      <c r="U116" s="1" t="n">
+        <v>0.2365</v>
+      </c>
+      <c r="V116" s="2" t="n">
+        <v>-0.001688476150274426</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7973,6 +8675,12 @@
       <c r="T117" s="3" t="n">
         <v>0.004422604422604413</v>
       </c>
+      <c r="U117" s="1" t="n">
+        <v>0.06142</v>
+      </c>
+      <c r="V117" s="3" t="n">
+        <v>0.001630789302022225</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8037,6 +8745,12 @@
       <c r="T118" s="3" t="n">
         <v>0.006165791276547143</v>
       </c>
+      <c r="U118" s="1" t="n">
+        <v>0.04401</v>
+      </c>
+      <c r="V118" s="2" t="n">
+        <v>-0.001134816159782148</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8101,6 +8815,12 @@
       <c r="T119" s="2" t="n">
         <v>-0.000805585392051548</v>
       </c>
+      <c r="U119" s="1" t="n">
+        <v>0.003727</v>
+      </c>
+      <c r="V119" s="3" t="n">
+        <v>0.001612469766191865</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8165,6 +8885,12 @@
       <c r="T120" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U120" s="1" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="V120" s="3" t="n">
+        <v>0.001270648030495554</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8229,6 +8955,12 @@
       <c r="T121" s="2" t="n">
         <v>-0.0006738544474394659</v>
       </c>
+      <c r="U121" s="1" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="V121" s="3" t="n">
+        <v>0.0006743088334458311</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8293,6 +9025,12 @@
       <c r="T122" s="2" t="n">
         <v>-0.001932876471622036</v>
       </c>
+      <c r="U122" s="1" t="n">
+        <v>0.5689</v>
+      </c>
+      <c r="V122" s="3" t="n">
+        <v>0.001584507042253542</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8357,6 +9095,12 @@
       <c r="T123" s="2" t="n">
         <v>-0.003264156129741662</v>
       </c>
+      <c r="U123" s="1" t="n">
+        <v>0.02912</v>
+      </c>
+      <c r="V123" s="3" t="n">
+        <v>0.003826398703850529</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8421,6 +9165,12 @@
       <c r="T124" s="2" t="n">
         <v>-0.0006407791874920975</v>
       </c>
+      <c r="U124" s="1" t="n">
+        <v>0.07852000000000001</v>
+      </c>
+      <c r="V124" s="3" t="n">
+        <v>0.006924852526288956</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8485,6 +9235,12 @@
       <c r="T125" s="3" t="n">
         <v>0.01202228521161172</v>
       </c>
+      <c r="U125" s="1" t="n">
+        <v>0.10334</v>
+      </c>
+      <c r="V125" s="2" t="n">
+        <v>-0.001931620629708247</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8549,6 +9305,12 @@
       <c r="T126" s="2" t="n">
         <v>-0.002249718785151764</v>
       </c>
+      <c r="U126" s="1" t="n">
+        <v>0.02674</v>
+      </c>
+      <c r="V126" s="3" t="n">
+        <v>0.004885381435550476</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8613,6 +9375,12 @@
       <c r="T127" s="3" t="n">
         <v>0.001822323462414504</v>
       </c>
+      <c r="U127" s="1" t="n">
+        <v>0.02193</v>
+      </c>
+      <c r="V127" s="2" t="n">
+        <v>-0.002728512960436451</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8677,6 +9445,12 @@
       <c r="T128" s="3" t="n">
         <v>0.001855287569573251</v>
       </c>
+      <c r="U128" s="1" t="n">
+        <v>0.1617</v>
+      </c>
+      <c r="V128" s="2" t="n">
+        <v>-0.001851851851851819</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8741,6 +9515,12 @@
       <c r="T129" s="3" t="n">
         <v>0.01878612716763</v>
       </c>
+      <c r="U129" s="1" t="n">
+        <v>0.14058</v>
+      </c>
+      <c r="V129" s="2" t="n">
+        <v>-0.002978723404255149</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8805,6 +9585,12 @@
       <c r="T130" s="2" t="n">
         <v>-0.007371830671283378</v>
       </c>
+      <c r="U130" s="1" t="n">
+        <v>0.053103</v>
+      </c>
+      <c r="V130" s="2" t="n">
+        <v>-0.004107122763587335</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8869,6 +9655,12 @@
       <c r="T131" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U131" s="1" t="n">
+        <v>0.08182</v>
+      </c>
+      <c r="V131" s="3" t="n">
+        <v>0.001101186834699703</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8933,6 +9725,12 @@
       <c r="T132" s="3" t="n">
         <v>0.002296211251435198</v>
       </c>
+      <c r="U132" s="1" t="n">
+        <v>0.0876</v>
+      </c>
+      <c r="V132" s="3" t="n">
+        <v>0.003436426116838427</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8997,6 +9795,12 @@
       <c r="T133" s="3" t="n">
         <v>0.002253032928942945</v>
       </c>
+      <c r="U133" s="1" t="n">
+        <v>0.5787</v>
+      </c>
+      <c r="V133" s="3" t="n">
+        <v>0.0006916825177242883</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9061,6 +9865,12 @@
       <c r="T134" s="2" t="n">
         <v>-0.003343363423604126</v>
       </c>
+      <c r="U134" s="1" t="n">
+        <v>0.02996</v>
+      </c>
+      <c r="V134" s="3" t="n">
+        <v>0.005031868500503214</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9125,6 +9935,12 @@
       <c r="T135" s="3" t="n">
         <v>0.003988603988604024</v>
       </c>
+      <c r="U135" s="1" t="n">
+        <v>0.01759</v>
+      </c>
+      <c r="V135" s="2" t="n">
+        <v>-0.001702610669693461</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9189,6 +10005,12 @@
       <c r="T136" s="3" t="n">
         <v>0.00241870464928782</v>
       </c>
+      <c r="U136" s="1" t="n">
+        <v>0.03723</v>
+      </c>
+      <c r="V136" s="2" t="n">
+        <v>-0.001876675603217175</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9253,6 +10075,12 @@
       <c r="T137" s="3" t="n">
         <v>0.001478196600147759</v>
       </c>
+      <c r="U137" s="1" t="n">
+        <v>0.02715</v>
+      </c>
+      <c r="V137" s="3" t="n">
+        <v>0.001845018450184555</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9317,6 +10145,12 @@
       <c r="T138" s="3" t="n">
         <v>0.002388535031847047</v>
       </c>
+      <c r="U138" s="1" t="n">
+        <v>2.518</v>
+      </c>
+      <c r="V138" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9381,6 +10215,12 @@
       <c r="T139" s="2" t="n">
         <v>-0.0008460236886633949</v>
       </c>
+      <c r="U139" s="1" t="n">
+        <v>0.01183</v>
+      </c>
+      <c r="V139" s="3" t="n">
+        <v>0.001693480101608884</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9445,6 +10285,12 @@
       <c r="T140" s="2" t="n">
         <v>-0.002668445630420287</v>
       </c>
+      <c r="U140" s="1" t="n">
+        <v>0.01492</v>
+      </c>
+      <c r="V140" s="2" t="n">
+        <v>-0.002006688963210737</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9509,6 +10355,12 @@
       <c r="T141" s="2" t="n">
         <v>-0.001920812937604486</v>
       </c>
+      <c r="U141" s="1" t="n">
+        <v>16.124</v>
+      </c>
+      <c r="V141" s="3" t="n">
+        <v>0.0009932952570150383</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9573,6 +10425,12 @@
       <c r="T142" s="3" t="n">
         <v>0.002417405318291742</v>
       </c>
+      <c r="U142" s="1" t="n">
+        <v>0.01249</v>
+      </c>
+      <c r="V142" s="3" t="n">
+        <v>0.004019292604501583</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9637,6 +10495,12 @@
       <c r="T143" s="3" t="n">
         <v>0.002630590003757878</v>
       </c>
+      <c r="U143" s="1" t="n">
+        <v>0.02661</v>
+      </c>
+      <c r="V143" s="2" t="n">
+        <v>-0.002623688155921932</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9701,6 +10565,12 @@
       <c r="T144" s="3" t="n">
         <v>0.04335449967155688</v>
       </c>
+      <c r="U144" s="1" t="n">
+        <v>0.004741</v>
+      </c>
+      <c r="V144" s="2" t="n">
+        <v>-0.005036726128016729</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9765,6 +10635,12 @@
       <c r="T145" s="3" t="n">
         <v>0.003210681887677083</v>
       </c>
+      <c r="U145" s="1" t="n">
+        <v>1.9777</v>
+      </c>
+      <c r="V145" s="3" t="n">
+        <v>0.004673609347218744</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9829,6 +10705,12 @@
       <c r="T146" s="2" t="n">
         <v>-0.001299826689774644</v>
       </c>
+      <c r="U146" s="1" t="n">
+        <v>0.02317</v>
+      </c>
+      <c r="V146" s="3" t="n">
+        <v>0.005206073752711435</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9893,6 +10775,12 @@
       <c r="T147" s="3" t="n">
         <v>0.003686327077747955</v>
       </c>
+      <c r="U147" s="1" t="n">
+        <v>0.08982999999999999</v>
+      </c>
+      <c r="V147" s="2" t="n">
+        <v>-0.0002225932109071355</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9957,6 +10845,12 @@
       <c r="T148" s="3" t="n">
         <v>0.002547365069256384</v>
       </c>
+      <c r="U148" s="1" t="n">
+        <v>0.06109</v>
+      </c>
+      <c r="V148" s="2" t="n">
+        <v>-0.02985548673971732</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10021,6 +10915,12 @@
       <c r="T149" s="3" t="n">
         <v>0.001515661839003028</v>
       </c>
+      <c r="U149" s="1" t="n">
+        <v>0.05939</v>
+      </c>
+      <c r="V149" s="2" t="n">
+        <v>-0.001345216075332162</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10085,6 +10985,12 @@
       <c r="T150" s="2" t="n">
         <v>-0.001380991064175495</v>
       </c>
+      <c r="U150" s="1" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="V150" s="3" t="n">
+        <v>0.0001626942162206632</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10149,6 +11055,12 @@
       <c r="T151" s="3" t="n">
         <v>0.008321167883211723</v>
       </c>
+      <c r="U151" s="1" t="n">
+        <v>6.889e-05</v>
+      </c>
+      <c r="V151" s="2" t="n">
+        <v>-0.002606051831475339</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10213,6 +11125,12 @@
       <c r="T152" s="3" t="n">
         <v>0.0002247191011235707</v>
       </c>
+      <c r="U152" s="1" t="n">
+        <v>0.4455</v>
+      </c>
+      <c r="V152" s="3" t="n">
+        <v>0.0008986744551786373</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10277,6 +11195,12 @@
       <c r="T153" s="3" t="n">
         <v>0.001637733377006225</v>
       </c>
+      <c r="U153" s="1" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="V153" s="3" t="n">
+        <v>0.002289077828646103</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10341,6 +11265,12 @@
       <c r="T154" s="2" t="n">
         <v>-0.008827586206896498</v>
       </c>
+      <c r="U154" s="1" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="V154" s="3" t="n">
+        <v>0.007792930698580488</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10405,6 +11335,12 @@
       <c r="T155" s="3" t="n">
         <v>0.003470715835140977</v>
       </c>
+      <c r="U155" s="1" t="n">
+        <v>0.2316</v>
+      </c>
+      <c r="V155" s="3" t="n">
+        <v>0.001297016861219173</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10469,6 +11405,12 @@
       <c r="T156" s="2" t="n">
         <v>-0.001235177865612684</v>
       </c>
+      <c r="U156" s="1" t="n">
+        <v>0.08051999999999999</v>
+      </c>
+      <c r="V156" s="2" t="n">
+        <v>-0.004204798417017153</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10533,6 +11475,12 @@
       <c r="T157" s="2" t="n">
         <v>-0.00714970790827449</v>
       </c>
+      <c r="U157" s="1" t="n">
+        <v>0.22726</v>
+      </c>
+      <c r="V157" s="2" t="n">
+        <v>-0.002107666637393555</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10597,6 +11545,12 @@
       <c r="T158" s="3" t="n">
         <v>0.005622489959839407</v>
       </c>
+      <c r="U158" s="1" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="V158" s="3" t="n">
+        <v>0.002396166134185261</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10661,6 +11615,12 @@
       <c r="T159" s="2" t="n">
         <v>-0.002385821404226352</v>
       </c>
+      <c r="U159" s="1" t="n">
+        <v>2.934</v>
+      </c>
+      <c r="V159" s="3" t="n">
+        <v>0.002391527160915653</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10725,6 +11685,12 @@
       <c r="T160" s="2" t="n">
         <v>-0.001000000000000029</v>
       </c>
+      <c r="U160" s="1" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="V160" s="2" t="n">
+        <v>-0.003003003003003089</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10789,6 +11755,12 @@
       <c r="T161" s="2" t="n">
         <v>-0.0002059166723863992</v>
       </c>
+      <c r="U161" s="1" t="n">
+        <v>0.14658</v>
+      </c>
+      <c r="V161" s="3" t="n">
+        <v>0.00631607853906341</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10853,6 +11825,12 @@
       <c r="T162" s="3" t="n">
         <v>0.003670847353930822</v>
       </c>
+      <c r="U162" s="1" t="n">
+        <v>0.003281</v>
+      </c>
+      <c r="V162" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10917,6 +11895,12 @@
       <c r="T163" s="2" t="n">
         <v>-0.003403403403403508</v>
       </c>
+      <c r="U163" s="1" t="n">
+        <v>0.004988</v>
+      </c>
+      <c r="V163" s="3" t="n">
+        <v>0.002008838891121024</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10981,6 +11965,12 @@
       <c r="T164" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U164" s="1" t="n">
+        <v>0.0954</v>
+      </c>
+      <c r="V164" s="3" t="n">
+        <v>0.003154574132492058</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11045,6 +12035,12 @@
       <c r="T165" s="3" t="n">
         <v>0.0006531678641410123</v>
       </c>
+      <c r="U165" s="1" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="V165" s="3" t="n">
+        <v>0.002610966057441147</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11109,6 +12105,12 @@
       <c r="T166" s="2" t="n">
         <v>-0.0007907411401050254</v>
       </c>
+      <c r="U166" s="1" t="n">
+        <v>1.3907</v>
+      </c>
+      <c r="V166" s="3" t="n">
+        <v>0.0005035971223022626</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11173,6 +12175,12 @@
       <c r="T167" s="3" t="n">
         <v>0.001084206722081758</v>
       </c>
+      <c r="U167" s="1" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="V167" s="2" t="n">
+        <v>-0.0003610108303250704</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11237,6 +12245,12 @@
       <c r="T168" s="2" t="n">
         <v>-0.003205128205128208</v>
       </c>
+      <c r="U168" s="1" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="V168" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11301,6 +12315,12 @@
       <c r="T169" s="3" t="n">
         <v>0.005385392123864033</v>
       </c>
+      <c r="U169" s="1" t="n">
+        <v>0.02984</v>
+      </c>
+      <c r="V169" s="2" t="n">
+        <v>-0.001004352192835696</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11365,6 +12385,12 @@
       <c r="T170" s="3" t="n">
         <v>0.0002302555836978154</v>
       </c>
+      <c r="U170" s="1" t="n">
+        <v>0.04358</v>
+      </c>
+      <c r="V170" s="3" t="n">
+        <v>0.003222836095764301</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11429,6 +12455,12 @@
       <c r="T171" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U171" s="1" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="V171" s="2" t="n">
+        <v>-0.006024096385542133</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11493,6 +12525,12 @@
       <c r="T172" s="2" t="n">
         <v>-0.02255639097744365</v>
       </c>
+      <c r="U172" s="1" t="n">
+        <v>1.32e-05</v>
+      </c>
+      <c r="V172" s="3" t="n">
+        <v>0.0153846153846155</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11557,6 +12595,12 @@
       <c r="T173" s="3" t="n">
         <v>0.001423149905123282</v>
       </c>
+      <c r="U173" s="1" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="V173" s="2" t="n">
+        <v>-0.0004737091425864326</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11621,6 +12665,12 @@
       <c r="T174" s="3" t="n">
         <v>0.003115958157133346</v>
       </c>
+      <c r="U174" s="1" t="n">
+        <v>0.09064</v>
+      </c>
+      <c r="V174" s="3" t="n">
+        <v>0.005546927002440653</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11685,6 +12735,12 @@
       <c r="T175" s="3" t="n">
         <v>0.004976499861763805</v>
       </c>
+      <c r="U175" s="1" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="V175" s="3" t="n">
+        <v>0.000825309491059209</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11749,6 +12805,12 @@
       <c r="T176" s="3" t="n">
         <v>0.002334267040149298</v>
       </c>
+      <c r="U176" s="1" t="n">
+        <v>0.02147</v>
+      </c>
+      <c r="V176" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11813,6 +12875,12 @@
       <c r="T177" s="2" t="n">
         <v>-0.003807106598984837</v>
       </c>
+      <c r="U177" s="1" t="n">
+        <v>0.007849999999999999</v>
+      </c>
+      <c r="V177" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11877,6 +12945,12 @@
       <c r="T178" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U178" s="1" t="n">
+        <v>0.000963</v>
+      </c>
+      <c r="V178" s="2" t="n">
+        <v>-0.001037344398340274</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11941,6 +13015,12 @@
       <c r="T179" s="3" t="n">
         <v>0.0002192693943778477</v>
       </c>
+      <c r="U179" s="1" t="n">
+        <v>0.022848</v>
+      </c>
+      <c r="V179" s="3" t="n">
+        <v>0.001753770606804711</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12005,6 +13085,12 @@
       <c r="T180" s="2" t="n">
         <v>-0.006038647342995041</v>
       </c>
+      <c r="U180" s="1" t="n">
+        <v>4.123</v>
+      </c>
+      <c r="V180" s="3" t="n">
+        <v>0.001944106925880925</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -12069,6 +13155,12 @@
       <c r="T181" s="3" t="n">
         <v>0.001737921445950645</v>
       </c>
+      <c r="U181" s="1" t="n">
+        <v>0.5851</v>
+      </c>
+      <c r="V181" s="3" t="n">
+        <v>0.01509368494101306</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12133,6 +13225,12 @@
       <c r="T182" s="3" t="n">
         <v>0.003602161296778059</v>
       </c>
+      <c r="U182" s="1" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="V182" s="3" t="n">
+        <v>0.0009970089730807863</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12197,6 +13295,12 @@
       <c r="T183" s="3" t="n">
         <v>0.00091374269005846</v>
       </c>
+      <c r="U183" s="1" t="n">
+        <v>5.482</v>
+      </c>
+      <c r="V183" s="3" t="n">
+        <v>0.0009129085265656186</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12261,6 +13365,12 @@
       <c r="T184" s="2" t="n">
         <v>-0.0006963788300835506</v>
       </c>
+      <c r="U184" s="1" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="V184" s="3" t="n">
+        <v>0.001742160278745669</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -12325,6 +13435,12 @@
       <c r="T185" s="3" t="n">
         <v>0.002141327623126437</v>
       </c>
+      <c r="U185" s="1" t="n">
+        <v>0.01895</v>
+      </c>
+      <c r="V185" s="3" t="n">
+        <v>0.01228632478632484</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12389,6 +13505,12 @@
       <c r="T186" s="2" t="n">
         <v>-0.00318471337579604</v>
       </c>
+      <c r="U186" s="1" t="n">
+        <v>3.14e-05</v>
+      </c>
+      <c r="V186" s="3" t="n">
+        <v>0.003194888178913599</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12453,6 +13575,12 @@
       <c r="T187" s="2" t="n">
         <v>-0.005000000000000013</v>
       </c>
+      <c r="U187" s="1" t="n">
+        <v>0.01593</v>
+      </c>
+      <c r="V187" s="3" t="n">
+        <v>0.0006281407035175624</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12517,6 +13645,12 @@
       <c r="T188" s="2" t="n">
         <v>-0.0004950495049504749</v>
       </c>
+      <c r="U188" s="1" t="n">
+        <v>0.04039</v>
+      </c>
+      <c r="V188" s="3" t="n">
+        <v>0.000247647350173429</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12581,6 +13715,12 @@
       <c r="T189" s="3" t="n">
         <v>0.003642987249544592</v>
       </c>
+      <c r="U189" s="1" t="n">
+        <v>0.0004409</v>
+      </c>
+      <c r="V189" s="3" t="n">
+        <v>0.0002268602540834901</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12645,6 +13785,12 @@
       <c r="T190" s="3" t="n">
         <v>0.005136986301369951</v>
       </c>
+      <c r="U190" s="1" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="V190" s="2" t="n">
+        <v>-0.0004258943781941904</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12709,6 +13855,12 @@
       <c r="T191" s="3" t="n">
         <v>0.0006333122229260964</v>
       </c>
+      <c r="U191" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="V191" s="2" t="n">
+        <v>-0.004430379746835481</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12773,6 +13925,12 @@
       <c r="T192" s="3" t="n">
         <v>0.001066287542207172</v>
       </c>
+      <c r="U192" s="1" t="n">
+        <v>0.05641</v>
+      </c>
+      <c r="V192" s="3" t="n">
+        <v>0.00142020237883905</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12837,6 +13995,12 @@
       <c r="T193" s="3" t="n">
         <v>0.0005344735435596833</v>
       </c>
+      <c r="U193" s="1" t="n">
+        <v>0.1873</v>
+      </c>
+      <c r="V193" s="3" t="n">
+        <v>0.0005341880341879754</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12901,6 +14065,12 @@
       <c r="T194" s="3" t="n">
         <v>0.001567398119122193</v>
       </c>
+      <c r="U194" s="1" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="V194" s="3" t="n">
+        <v>0.001564945226916994</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -12965,6 +14135,12 @@
       <c r="T195" s="3" t="n">
         <v>0.003039513677811475</v>
       </c>
+      <c r="U195" s="1" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="V195" s="2" t="n">
+        <v>-0.003729603729603707</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13029,6 +14205,12 @@
       <c r="T196" s="2" t="n">
         <v>-0.004012841091492892</v>
       </c>
+      <c r="U196" s="1" t="n">
+        <v>0.01237</v>
+      </c>
+      <c r="V196" s="2" t="n">
+        <v>-0.003223207091055469</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13093,6 +14275,12 @@
       <c r="T197" s="3" t="n">
         <v>0.005422993492407813</v>
       </c>
+      <c r="U197" s="1" t="n">
+        <v>0.04637</v>
+      </c>
+      <c r="V197" s="3" t="n">
+        <v>0.0004314994606256566</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -13157,6 +14345,12 @@
       <c r="T198" s="2" t="n">
         <v>-0.0001964250638381241</v>
       </c>
+      <c r="U198" s="1" t="n">
+        <v>0.5066000000000001</v>
+      </c>
+      <c r="V198" s="2" t="n">
+        <v>-0.004715127701375162</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13221,6 +14415,12 @@
       <c r="T199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U199" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="V199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13285,6 +14485,12 @@
       <c r="T200" s="2" t="n">
         <v>-0.00200400801603214</v>
       </c>
+      <c r="U200" s="1" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="V200" s="3" t="n">
+        <v>0.002008032128514132</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13349,6 +14555,12 @@
       <c r="T201" s="3" t="n">
         <v>0.0001749475157452996</v>
       </c>
+      <c r="U201" s="1" t="n">
+        <v>0.005755</v>
+      </c>
+      <c r="V201" s="3" t="n">
+        <v>0.006646842749693868</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13413,6 +14625,12 @@
       <c r="T202" s="3" t="n">
         <v>0.004847225828788952</v>
       </c>
+      <c r="U202" s="1" t="n">
+        <v>0.02321</v>
+      </c>
+      <c r="V202" s="2" t="n">
+        <v>-0.000344560254974485</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -13477,6 +14695,12 @@
       <c r="T203" s="2" t="n">
         <v>-0.01086956521739124</v>
       </c>
+      <c r="U203" s="1" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="V203" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -13541,6 +14765,12 @@
       <c r="T204" s="2" t="n">
         <v>-0.002366863905325348</v>
       </c>
+      <c r="U204" s="1" t="n">
+        <v>0.03374</v>
+      </c>
+      <c r="V204" s="3" t="n">
+        <v>0.0005931198102016366</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -13605,6 +14835,12 @@
       <c r="T205" s="3" t="n">
         <v>0.00474721101352945</v>
       </c>
+      <c r="U205" s="1" t="n">
+        <v>4.233</v>
+      </c>
+      <c r="V205" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -13669,6 +14905,12 @@
       <c r="T206" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U206" s="1" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="V206" s="2" t="n">
+        <v>-0.005540166204986155</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -13733,6 +14975,12 @@
       <c r="T207" s="3" t="n">
         <v>0.02558097640064857</v>
       </c>
+      <c r="U207" s="1" t="n">
+        <v>0.0011201</v>
+      </c>
+      <c r="V207" s="2" t="n">
+        <v>-0.01624802388898654</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13797,6 +15045,12 @@
       <c r="T208" s="2" t="n">
         <v>-0.003153276665752735</v>
       </c>
+      <c r="U208" s="1" t="n">
+        <v>0.007292</v>
+      </c>
+      <c r="V208" s="3" t="n">
+        <v>0.002888185944161764</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -13861,6 +15115,12 @@
       <c r="T209" s="2" t="n">
         <v>-0.001669449081803053</v>
       </c>
+      <c r="U209" s="1" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="V209" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13925,6 +15185,12 @@
       <c r="T210" s="3" t="n">
         <v>0.001543209876543254</v>
       </c>
+      <c r="U210" s="1" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="V210" s="2" t="n">
+        <v>-0.0007704160246532279</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13989,6 +15255,12 @@
       <c r="T211" s="3" t="n">
         <v>0.0008442380751373008</v>
       </c>
+      <c r="U211" s="1" t="n">
+        <v>0.007123</v>
+      </c>
+      <c r="V211" s="3" t="n">
+        <v>0.00140587656403762</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -14053,6 +15325,12 @@
       <c r="T212" s="3" t="n">
         <v>0.009386523633925475</v>
       </c>
+      <c r="U212" s="1" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="V212" s="2" t="n">
+        <v>-0.02125539687811346</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -14117,6 +15395,12 @@
       <c r="T213" s="3" t="n">
         <v>0.005148233623291294</v>
       </c>
+      <c r="U213" s="1" t="n">
+        <v>0.05653</v>
+      </c>
+      <c r="V213" s="2" t="n">
+        <v>-0.001589544330625217</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -14181,6 +15465,12 @@
       <c r="T214" s="3" t="n">
         <v>0.003186404673393612</v>
       </c>
+      <c r="U214" s="1" t="n">
+        <v>0.1891</v>
+      </c>
+      <c r="V214" s="3" t="n">
+        <v>0.001058761249338158</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -14245,6 +15535,12 @@
       <c r="T215" s="3" t="n">
         <v>0.004003049942813607</v>
       </c>
+      <c r="U215" s="1" t="n">
+        <v>0.05289</v>
+      </c>
+      <c r="V215" s="3" t="n">
+        <v>0.004176950825897057</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -14309,6 +15605,12 @@
       <c r="T216" s="2" t="n">
         <v>-0.0009596928982724721</v>
       </c>
+      <c r="U216" s="1" t="n">
+        <v>0.002088</v>
+      </c>
+      <c r="V216" s="3" t="n">
+        <v>0.002881844380403424</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -14373,6 +15675,12 @@
       <c r="T217" s="2" t="n">
         <v>-0.0006658897952388147</v>
       </c>
+      <c r="U217" s="1" t="n">
+        <v>6.007</v>
+      </c>
+      <c r="V217" s="3" t="n">
+        <v>0.000666333499916635</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -14437,6 +15745,12 @@
       <c r="T218" s="2" t="n">
         <v>-0.008154020385051071</v>
       </c>
+      <c r="U218" s="1" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="V218" s="3" t="n">
+        <v>0.007764329755652135</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -14501,6 +15815,12 @@
       <c r="T219" s="2" t="n">
         <v>-0.004832713754646836</v>
       </c>
+      <c r="U219" s="1" t="n">
+        <v>0.005346</v>
+      </c>
+      <c r="V219" s="2" t="n">
+        <v>-0.001494209936496114</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -14565,6 +15885,12 @@
       <c r="T220" s="3" t="n">
         <v>0.002669902912621334</v>
       </c>
+      <c r="U220" s="1" t="n">
+        <v>0.04137</v>
+      </c>
+      <c r="V220" s="3" t="n">
+        <v>0.001452432824981785</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -14629,6 +15955,12 @@
       <c r="T221" s="2" t="n">
         <v>-0.003631333218052946</v>
       </c>
+      <c r="U221" s="1" t="n">
+        <v>0.005741</v>
+      </c>
+      <c r="V221" s="2" t="n">
+        <v>-0.003644567858382538</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -14693,6 +16025,12 @@
       <c r="T222" s="3" t="n">
         <v>0.00110375275938193</v>
       </c>
+      <c r="U222" s="1" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="V222" s="3" t="n">
+        <v>0.001102535832414585</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -14757,6 +16095,12 @@
       <c r="T223" s="2" t="n">
         <v>-0.004761904761904898</v>
       </c>
+      <c r="U223" s="1" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="V223" s="3" t="n">
+        <v>0.0020933014354068</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -14821,6 +16165,12 @@
       <c r="T224" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U224" s="1" t="n">
+        <v>0.4313</v>
+      </c>
+      <c r="V224" s="2" t="n">
+        <v>-0.001851423281647691</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -14885,6 +16235,12 @@
       <c r="T225" s="2" t="n">
         <v>-0.002747909199522032</v>
       </c>
+      <c r="U225" s="1" t="n">
+        <v>0.08371000000000001</v>
+      </c>
+      <c r="V225" s="3" t="n">
+        <v>0.00287528453336533</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -14949,6 +16305,12 @@
       <c r="T226" s="3" t="n">
         <v>0.002656748140276378</v>
       </c>
+      <c r="U226" s="1" t="n">
+        <v>0.01889</v>
+      </c>
+      <c r="V226" s="3" t="n">
+        <v>0.001059883412824546</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -15013,6 +16375,12 @@
       <c r="T227" s="3" t="n">
         <v>0.001499892864795236</v>
       </c>
+      <c r="U227" s="1" t="n">
+        <v>0.04674</v>
+      </c>
+      <c r="V227" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -15077,6 +16445,12 @@
       <c r="T228" s="2" t="n">
         <v>-0.005603448275861991</v>
       </c>
+      <c r="U228" s="1" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="V228" s="3" t="n">
+        <v>0.001300390117035057</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -15141,6 +16515,12 @@
       <c r="T229" s="3" t="n">
         <v>0.001858736059479607</v>
       </c>
+      <c r="U229" s="1" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="V229" s="2" t="n">
+        <v>-0.001855287569573337</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -15205,6 +16585,12 @@
       <c r="T230" s="2" t="n">
         <v>-0.001203369434416233</v>
       </c>
+      <c r="U230" s="1" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="V230" s="2" t="n">
+        <v>-0.002409638554216936</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -15269,6 +16655,12 @@
       <c r="T231" s="3" t="n">
         <v>0.001639344262295129</v>
       </c>
+      <c r="U231" s="1" t="n">
+        <v>0.03042</v>
+      </c>
+      <c r="V231" s="2" t="n">
+        <v>-0.004255319148936224</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -15333,6 +16725,12 @@
       <c r="T232" s="2" t="n">
         <v>-0.003074220465524688</v>
       </c>
+      <c r="U232" s="1" t="n">
+        <v>0.02274</v>
+      </c>
+      <c r="V232" s="3" t="n">
+        <v>0.001762114537444862</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -15397,6 +16795,12 @@
       <c r="T233" s="2" t="n">
         <v>-0.03474484256243211</v>
       </c>
+      <c r="U233" s="1" t="n">
+        <v>0.11432</v>
+      </c>
+      <c r="V233" s="2" t="n">
+        <v>-0.01081595569784547</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -15461,6 +16865,12 @@
       <c r="T234" s="3" t="n">
         <v>0.002371541501976243</v>
       </c>
+      <c r="U234" s="1" t="n">
+        <v>0.2529</v>
+      </c>
+      <c r="V234" s="2" t="n">
+        <v>-0.002760252365930515</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -15525,6 +16935,12 @@
       <c r="T235" s="3" t="n">
         <v>0.0001443834825295426</v>
       </c>
+      <c r="U235" s="1" t="n">
+        <v>0.06929</v>
+      </c>
+      <c r="V235" s="3" t="n">
+        <v>0.0002887252778981684</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -15589,6 +17005,12 @@
       <c r="T236" s="2" t="n">
         <v>-0.001832231339122186</v>
       </c>
+      <c r="U236" s="1" t="n">
+        <v>0.12498</v>
+      </c>
+      <c r="V236" s="2" t="n">
+        <v>-0.002553870710295298</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -15653,6 +17075,12 @@
       <c r="T237" s="3" t="n">
         <v>0.004894384337970187</v>
       </c>
+      <c r="U237" s="1" t="n">
+        <v>0.03886</v>
+      </c>
+      <c r="V237" s="2" t="n">
+        <v>-0.003845167905665324</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -15717,6 +17145,12 @@
       <c r="T238" s="2" t="n">
         <v>-0.008333333333333342</v>
       </c>
+      <c r="U238" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="V238" s="3" t="n">
+        <v>0.008403361344537823</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -15781,6 +17215,12 @@
       <c r="T239" s="2" t="n">
         <v>-0.00375469336670845</v>
       </c>
+      <c r="U239" s="1" t="n">
+        <v>0.003964</v>
+      </c>
+      <c r="V239" s="2" t="n">
+        <v>-0.00402010050251266</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -15845,6 +17285,12 @@
       <c r="T240" s="2" t="n">
         <v>-0.002189781021897848</v>
       </c>
+      <c r="U240" s="1" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="V240" s="3" t="n">
+        <v>0.002194586686174141</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -15909,6 +17355,12 @@
       <c r="T241" s="3" t="n">
         <v>0.006397075622572595</v>
       </c>
+      <c r="U241" s="1" t="n">
+        <v>0.4391</v>
+      </c>
+      <c r="V241" s="2" t="n">
+        <v>-0.003178206583427951</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -15973,6 +17425,12 @@
       <c r="T242" s="3" t="n">
         <v>0.005369127516778538</v>
       </c>
+      <c r="U242" s="1" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="V242" s="3" t="n">
+        <v>0.004005340453938537</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -16037,6 +17495,12 @@
       <c r="T243" s="2" t="n">
         <v>-0.01561822125813461</v>
       </c>
+      <c r="U243" s="1" t="n">
+        <v>0.02284</v>
+      </c>
+      <c r="V243" s="3" t="n">
+        <v>0.00661084178052009</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -16101,6 +17565,12 @@
       <c r="T244" s="3" t="n">
         <v>0.00119474313022703</v>
       </c>
+      <c r="U244" s="1" t="n">
+        <v>0.001689</v>
+      </c>
+      <c r="V244" s="3" t="n">
+        <v>0.007756563245823384</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -16165,6 +17635,12 @@
       <c r="T245" s="2" t="n">
         <v>-0.004569687738004489</v>
       </c>
+      <c r="U245" s="1" t="n">
+        <v>0.1312</v>
+      </c>
+      <c r="V245" s="3" t="n">
+        <v>0.003825554705432291</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -16229,6 +17705,12 @@
       <c r="T246" s="3" t="n">
         <v>0.01407099456347947</v>
       </c>
+      <c r="U246" s="1" t="n">
+        <v>0.03196</v>
+      </c>
+      <c r="V246" s="3" t="n">
+        <v>0.007883948281299281</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -16293,6 +17775,12 @@
       <c r="T247" s="3" t="n">
         <v>0.001126760563380314</v>
       </c>
+      <c r="U247" s="1" t="n">
+        <v>0.1774</v>
+      </c>
+      <c r="V247" s="2" t="n">
+        <v>-0.001688238604389391</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -16357,6 +17845,12 @@
       <c r="T248" s="2" t="n">
         <v>-0.003593596863769977</v>
       </c>
+      <c r="U248" s="1" t="n">
+        <v>0.03068</v>
+      </c>
+      <c r="V248" s="3" t="n">
+        <v>0.005901639344262282</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -16421,6 +17915,12 @@
       <c r="T249" s="3" t="n">
         <v>0.0009470818041909627</v>
       </c>
+      <c r="U249" s="1" t="n">
+        <v>0.008461</v>
+      </c>
+      <c r="V249" s="3" t="n">
+        <v>0.0007096392667059801</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -16485,6 +17985,12 @@
       <c r="T250" s="2" t="n">
         <v>-0.0128015755785329</v>
       </c>
+      <c r="U250" s="1" t="n">
+        <v>0.02025</v>
+      </c>
+      <c r="V250" s="3" t="n">
+        <v>0.009975062344139765</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -16549,6 +18055,12 @@
       <c r="T251" s="2" t="n">
         <v>-0.00214915108532136</v>
       </c>
+      <c r="U251" s="1" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="V251" s="2" t="n">
+        <v>-0.0006461339651088143</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -16613,6 +18125,12 @@
       <c r="T252" s="3" t="n">
         <v>0.007096392667060826</v>
       </c>
+      <c r="U252" s="1" t="n">
+        <v>0.008487</v>
+      </c>
+      <c r="V252" s="2" t="n">
+        <v>-0.003288314738696447</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -16677,6 +18195,12 @@
       <c r="T253" s="3" t="n">
         <v>0.00647668393782384</v>
       </c>
+      <c r="U253" s="1" t="n">
+        <v>0.03908</v>
+      </c>
+      <c r="V253" s="3" t="n">
+        <v>0.005920205920205768</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -16741,6 +18265,12 @@
       <c r="T254" s="3" t="n">
         <v>0.0006531678641410576</v>
       </c>
+      <c r="U254" s="1" t="n">
+        <v>0.06165</v>
+      </c>
+      <c r="V254" s="3" t="n">
+        <v>0.006037859007832935</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -16805,6 +18335,12 @@
       <c r="T255" s="2" t="n">
         <v>-0.00252383623107132</v>
       </c>
+      <c r="U255" s="1" t="n">
+        <v>0.003546</v>
+      </c>
+      <c r="V255" s="2" t="n">
+        <v>-0.00309249367444468</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -16869,6 +18405,12 @@
       <c r="T256" s="3" t="n">
         <v>0.01321821515892417</v>
       </c>
+      <c r="U256" s="1" t="n">
+        <v>0.013264</v>
+      </c>
+      <c r="V256" s="3" t="n">
+        <v>0.0002262272830102957</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -16933,6 +18475,12 @@
       <c r="T257" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U257" s="1" t="n">
+        <v>0.999425</v>
+      </c>
+      <c r="V257" s="2" t="n">
+        <v>-1.000574329694e-06</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -16997,6 +18545,12 @@
       <c r="T258" s="2" t="n">
         <v>-0.001836758121914905</v>
       </c>
+      <c r="U258" s="1" t="n">
+        <v>0.08926000000000001</v>
+      </c>
+      <c r="V258" s="3" t="n">
+        <v>0.02656699252443941</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -17061,6 +18615,12 @@
       <c r="T259" s="3" t="n">
         <v>0.004642936104355557</v>
       </c>
+      <c r="U259" s="1" t="n">
+        <v>0.09181</v>
+      </c>
+      <c r="V259" s="3" t="n">
+        <v>0.01023327464788733</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -17125,6 +18685,12 @@
       <c r="T260" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U260" s="1" t="n">
+        <v>0.08203000000000001</v>
+      </c>
+      <c r="V260" s="3" t="n">
+        <v>0.006132711885195639</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -17189,6 +18755,12 @@
       <c r="T261" s="3" t="n">
         <v>0.008764241893076256</v>
       </c>
+      <c r="U261" s="1" t="n">
+        <v>1.149</v>
+      </c>
+      <c r="V261" s="2" t="n">
+        <v>-0.001737619461337968</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -17253,6 +18825,12 @@
       <c r="T262" s="2" t="n">
         <v>-0.005546751188589475</v>
       </c>
+      <c r="U262" s="1" t="n">
+        <v>0.003757</v>
+      </c>
+      <c r="V262" s="2" t="n">
+        <v>-0.002124833997344009</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -17317,6 +18895,12 @@
       <c r="T263" s="2" t="n">
         <v>-0.005115089514066524</v>
       </c>
+      <c r="U263" s="1" t="n">
+        <v>0.1164</v>
+      </c>
+      <c r="V263" s="2" t="n">
+        <v>-0.002570694087403554</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -17381,6 +18965,12 @@
       <c r="T264" s="3" t="n">
         <v>0.01653033401499672</v>
       </c>
+      <c r="U264" s="1" t="n">
+        <v>0.0006442</v>
+      </c>
+      <c r="V264" s="3" t="n">
+        <v>0.07996647108130767</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -17445,6 +19035,12 @@
       <c r="T265" s="2" t="n">
         <v>-0.004054054054054123</v>
       </c>
+      <c r="U265" s="1" t="n">
+        <v>0.01475</v>
+      </c>
+      <c r="V265" s="3" t="n">
+        <v>0.0006784260515603523</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -17509,6 +19105,12 @@
       <c r="T266" s="3" t="n">
         <v>0.003154574132492204</v>
       </c>
+      <c r="U266" s="1" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="V266" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -17573,6 +19175,12 @@
       <c r="T267" s="2" t="n">
         <v>-0.004299754299754338</v>
       </c>
+      <c r="U267" s="1" t="n">
+        <v>0.01624</v>
+      </c>
+      <c r="V267" s="3" t="n">
+        <v>0.001850709438618276</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -17637,6 +19245,12 @@
       <c r="T268" s="3" t="n">
         <v>0.002293052052281643</v>
       </c>
+      <c r="U268" s="1" t="n">
+        <v>0.0004319</v>
+      </c>
+      <c r="V268" s="2" t="n">
+        <v>-0.0118965911690689</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -17701,6 +19315,12 @@
       <c r="T269" s="2" t="n">
         <v>-0.002895752895752778</v>
       </c>
+      <c r="U269" s="1" t="n">
+        <v>0.02075</v>
+      </c>
+      <c r="V269" s="3" t="n">
+        <v>0.004356243949661171</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -17765,6 +19385,12 @@
       <c r="T270" s="3" t="n">
         <v>0.001108033240997262</v>
       </c>
+      <c r="U270" s="1" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="V270" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -17829,6 +19455,12 @@
       <c r="T271" s="3" t="n">
         <v>0.0013614703880191</v>
       </c>
+      <c r="U271" s="1" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="V271" s="2" t="n">
+        <v>-0.0006798096532971906</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -17893,6 +19525,12 @@
       <c r="T272" s="2" t="n">
         <v>-0.01080945198592257</v>
       </c>
+      <c r="U272" s="1" t="n">
+        <v>0.03945</v>
+      </c>
+      <c r="V272" s="3" t="n">
+        <v>0.002541296060991002</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -17957,6 +19595,12 @@
       <c r="T273" s="3" t="n">
         <v>0.002157497303128373</v>
       </c>
+      <c r="U273" s="1" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="V273" s="2" t="n">
+        <v>-0.001076426264800862</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -18021,6 +19665,12 @@
       <c r="T274" s="2" t="n">
         <v>-0.001425629653096838</v>
       </c>
+      <c r="U274" s="1" t="n">
+        <v>63.18</v>
+      </c>
+      <c r="V274" s="3" t="n">
+        <v>0.002220812182741126</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -18085,6 +19735,12 @@
       <c r="T275" s="2" t="n">
         <v>-0.005277044854881204</v>
       </c>
+      <c r="U275" s="1" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="V275" s="3" t="n">
+        <v>0.0008841732979663654</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -18149,6 +19805,12 @@
       <c r="T276" s="3" t="n">
         <v>0.001542020046260603</v>
       </c>
+      <c r="U276" s="1" t="n">
+        <v>2.603</v>
+      </c>
+      <c r="V276" s="3" t="n">
+        <v>0.001924557351809214</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -18213,6 +19875,12 @@
       <c r="T277" s="2" t="n">
         <v>-0.002142857142857138</v>
       </c>
+      <c r="U277" s="1" t="n">
+        <v>0.04193</v>
+      </c>
+      <c r="V277" s="3" t="n">
+        <v>0.000477213075638253</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -18277,6 +19945,12 @@
       <c r="T278" s="2" t="n">
         <v>-0.004563894523326562</v>
       </c>
+      <c r="U278" s="1" t="n">
+        <v>0.01952</v>
+      </c>
+      <c r="V278" s="2" t="n">
+        <v>-0.005603667855323609</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -18341,6 +20015,12 @@
       <c r="T279" s="2" t="n">
         <v>-0.006414825374198071</v>
       </c>
+      <c r="U279" s="1" t="n">
+        <v>0.00562</v>
+      </c>
+      <c r="V279" s="3" t="n">
+        <v>0.00789096126255376</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -18405,6 +20085,12 @@
       <c r="T280" s="3" t="n">
         <v>0.009854771784232504</v>
       </c>
+      <c r="U280" s="1" t="n">
+        <v>0.03919</v>
+      </c>
+      <c r="V280" s="3" t="n">
+        <v>0.006420133538777612</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -18469,6 +20155,12 @@
       <c r="T281" s="2" t="n">
         <v>-0.003325942350332597</v>
       </c>
+      <c r="U281" s="1" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="V281" s="3" t="n">
+        <v>0.002224694104560625</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -18533,6 +20225,12 @@
       <c r="T282" s="3" t="n">
         <v>0.002726822012890498</v>
       </c>
+      <c r="U282" s="1" t="n">
+        <v>0.0004049</v>
+      </c>
+      <c r="V282" s="3" t="n">
+        <v>0.0009888751545116328</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -18597,6 +20295,12 @@
       <c r="T283" s="2" t="n">
         <v>-0.0007509386733417333</v>
       </c>
+      <c r="U283" s="1" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="V283" s="3" t="n">
+        <v>0.02204408817635285</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -18661,6 +20365,12 @@
       <c r="T284" s="2" t="n">
         <v>-0.001434034416826111</v>
       </c>
+      <c r="U284" s="1" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="V284" s="3" t="n">
+        <v>0.0004786979415988317</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -18725,6 +20435,12 @@
       <c r="T285" s="2" t="n">
         <v>-0.00195149149707278</v>
       </c>
+      <c r="U285" s="1" t="n">
+        <v>0.10732</v>
+      </c>
+      <c r="V285" s="2" t="n">
+        <v>-0.0007448789571694297</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -18789,6 +20505,12 @@
       <c r="T286" s="3" t="n">
         <v>0.002392344497607766</v>
       </c>
+      <c r="U286" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="V286" s="2" t="n">
+        <v>-0.002386634844868845</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -18853,6 +20575,12 @@
       <c r="T287" s="3" t="n">
         <v>0.004531424443423025</v>
       </c>
+      <c r="U287" s="1" t="n">
+        <v>0.15312</v>
+      </c>
+      <c r="V287" s="3" t="n">
+        <v>0.001046025104602468</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -18917,6 +20645,12 @@
       <c r="T288" s="2" t="n">
         <v>-0.003313086692435214</v>
       </c>
+      <c r="U288" s="1" t="n">
+        <v>0.1804</v>
+      </c>
+      <c r="V288" s="2" t="n">
+        <v>-0.000554016620498554</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -18981,6 +20715,12 @@
       <c r="T289" s="3" t="n">
         <v>0.002175489485134238</v>
       </c>
+      <c r="U289" s="1" t="n">
+        <v>4.151</v>
+      </c>
+      <c r="V289" s="3" t="n">
+        <v>0.001205981669078604</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -19045,6 +20785,12 @@
       <c r="T290" s="3" t="n">
         <v>0.001292596944770846</v>
       </c>
+      <c r="U290" s="1" t="n">
+        <v>0.08577</v>
+      </c>
+      <c r="V290" s="3" t="n">
+        <v>0.006571998591714646</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -19109,6 +20855,12 @@
       <c r="T291" s="3" t="n">
         <v>0.002540937323546014</v>
       </c>
+      <c r="U291" s="1" t="n">
+        <v>0.03555</v>
+      </c>
+      <c r="V291" s="3" t="n">
+        <v>0.001126443255420962</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -19173,6 +20925,12 @@
       <c r="T292" s="3" t="n">
         <v>0.003900102634279875</v>
       </c>
+      <c r="U292" s="1" t="n">
+        <v>1.4702</v>
+      </c>
+      <c r="V292" s="3" t="n">
+        <v>0.002044711014176589</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -19237,6 +20995,12 @@
       <c r="T293" s="3" t="n">
         <v>0.003085361672951775</v>
       </c>
+      <c r="U293" s="1" t="n">
+        <v>0.005831</v>
+      </c>
+      <c r="V293" s="2" t="n">
+        <v>-0.003588516746411515</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -19301,6 +21065,12 @@
       <c r="T294" s="3" t="n">
         <v>0.0008779631255487165</v>
       </c>
+      <c r="U294" s="1" t="n">
+        <v>0.003432</v>
+      </c>
+      <c r="V294" s="3" t="n">
+        <v>0.003508771929824647</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -19365,6 +21135,12 @@
       <c r="T295" s="3" t="n">
         <v>0.0009293680297396746</v>
       </c>
+      <c r="U295" s="1" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="V295" s="3" t="n">
+        <v>0.0009285051067781913</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -19429,6 +21205,12 @@
       <c r="T296" s="2" t="n">
         <v>-0.001776988005330966</v>
       </c>
+      <c r="U296" s="1" t="n">
+        <v>2.249</v>
+      </c>
+      <c r="V296" s="3" t="n">
+        <v>0.0008900756564308962</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -19493,6 +21275,12 @@
       <c r="T297" s="2" t="n">
         <v>-0.001184132622853711</v>
       </c>
+      <c r="U297" s="1" t="n">
+        <v>0.01688</v>
+      </c>
+      <c r="V297" s="3" t="n">
+        <v>0.0005927682276229753</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -19557,6 +21345,12 @@
       <c r="T298" s="2" t="n">
         <v>-0.006640841173215311</v>
       </c>
+      <c r="U298" s="1" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="V298" s="3" t="n">
+        <v>0.001949860724234078</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -19621,6 +21415,12 @@
       <c r="T299" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U299" s="1" t="n">
+        <v>0.01108</v>
+      </c>
+      <c r="V299" s="3" t="n">
+        <v>0.001808318264014393</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -19685,6 +21485,12 @@
       <c r="T300" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U300" s="1" t="n">
+        <v>0.02064</v>
+      </c>
+      <c r="V300" s="2" t="n">
+        <v>-0.0009680542110359464</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -19749,6 +21555,12 @@
       <c r="T301" s="3" t="n">
         <v>0.0003266906239792372</v>
       </c>
+      <c r="U301" s="1" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="V301" s="3" t="n">
+        <v>0.004572175048987448</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -19813,6 +21625,12 @@
       <c r="T302" s="3" t="n">
         <v>0.008040935672514673</v>
       </c>
+      <c r="U302" s="1" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="V302" s="2" t="n">
+        <v>-0.003625815808556903</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -19877,6 +21695,12 @@
       <c r="T303" s="2" t="n">
         <v>-0.0002707459049682702</v>
       </c>
+      <c r="U303" s="1" t="n">
+        <v>0.07392</v>
+      </c>
+      <c r="V303" s="3" t="n">
+        <v>0.0009478672985782074</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -19941,6 +21765,12 @@
       <c r="T304" s="2" t="n">
         <v>-0.005653266331658279</v>
       </c>
+      <c r="U304" s="1" t="n">
+        <v>0.01588</v>
+      </c>
+      <c r="V304" s="3" t="n">
+        <v>0.00315855969677814</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -20005,6 +21835,12 @@
       <c r="T305" s="2" t="n">
         <v>-0.001853281853281778</v>
       </c>
+      <c r="U305" s="1" t="n">
+        <v>0.0645</v>
+      </c>
+      <c r="V305" s="2" t="n">
+        <v>-0.002011449791118754</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -20069,6 +21905,12 @@
       <c r="T306" s="2" t="n">
         <v>-0.005627009646302161</v>
       </c>
+      <c r="U306" s="1" t="n">
+        <v>0.04978</v>
+      </c>
+      <c r="V306" s="3" t="n">
+        <v>0.00606305578011307</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -20133,6 +21975,12 @@
       <c r="T307" s="2" t="n">
         <v>-0.006486486486486492</v>
       </c>
+      <c r="U307" s="1" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="V307" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -20197,6 +22045,12 @@
       <c r="T308" s="3" t="n">
         <v>0.003270440251572281</v>
       </c>
+      <c r="U308" s="1" t="n">
+        <v>0.03977</v>
+      </c>
+      <c r="V308" s="2" t="n">
+        <v>-0.002758274824473395</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -20261,6 +22115,12 @@
       <c r="T309" s="3" t="n">
         <v>0.002562459961563107</v>
       </c>
+      <c r="U309" s="1" t="n">
+        <v>0.01565</v>
+      </c>
+      <c r="V309" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -20325,6 +22185,12 @@
       <c r="T310" s="3" t="n">
         <v>0.0009228497600590888</v>
       </c>
+      <c r="U310" s="1" t="n">
+        <v>0.05431</v>
+      </c>
+      <c r="V310" s="3" t="n">
+        <v>0.001475198229762064</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -20389,6 +22255,12 @@
       <c r="T311" s="2" t="n">
         <v>-0.00268396331916794</v>
       </c>
+      <c r="U311" s="1" t="n">
+        <v>0.004459</v>
+      </c>
+      <c r="V311" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -20453,6 +22325,12 @@
       <c r="T312" s="3" t="n">
         <v>0.0008284023668639126</v>
       </c>
+      <c r="U312" s="1" t="n">
+        <v>0.08465</v>
+      </c>
+      <c r="V312" s="3" t="n">
+        <v>0.0009459619250324788</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -20517,6 +22395,12 @@
       <c r="T313" s="2" t="n">
         <v>-0.0008012820512821113</v>
       </c>
+      <c r="U313" s="1" t="n">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V313" s="3" t="n">
+        <v>0.001069232825447698</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -20581,6 +22465,12 @@
       <c r="T314" s="2" t="n">
         <v>-0.0006527415143602414</v>
       </c>
+      <c r="U314" s="1" t="n">
+        <v>0.1533</v>
+      </c>
+      <c r="V314" s="3" t="n">
+        <v>0.001306335728282025</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -20645,6 +22535,12 @@
       <c r="T315" s="3" t="n">
         <v>0.001879699248120268</v>
       </c>
+      <c r="U315" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V315" s="3" t="n">
+        <v>0.0006253908692934131</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -20709,6 +22605,12 @@
       <c r="T316" s="2" t="n">
         <v>-0.008728859792689527</v>
       </c>
+      <c r="U316" s="1" t="n">
+        <v>0.1817</v>
+      </c>
+      <c r="V316" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -20773,6 +22675,12 @@
       <c r="T317" s="2" t="n">
         <v>-0.0005335467520342178</v>
       </c>
+      <c r="U317" s="1" t="n">
+        <v>0.007489</v>
+      </c>
+      <c r="V317" s="2" t="n">
+        <v>-0.0005338315761376837</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -20837,6 +22745,12 @@
       <c r="T318" s="3" t="n">
         <v>0.002002803925495612</v>
       </c>
+      <c r="U318" s="1" t="n">
+        <v>0.05019</v>
+      </c>
+      <c r="V318" s="3" t="n">
+        <v>0.003198081151309223</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -20901,6 +22815,12 @@
       <c r="T319" s="3" t="n">
         <v>0.00392425115207366</v>
       </c>
+      <c r="U319" s="1" t="n">
+        <v>0.27785</v>
+      </c>
+      <c r="V319" s="2" t="n">
+        <v>-0.003586157432311282</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -20965,6 +22885,12 @@
       <c r="T320" s="2" t="n">
         <v>-0.0004542357483534714</v>
       </c>
+      <c r="U320" s="1" t="n">
+        <v>0.4403</v>
+      </c>
+      <c r="V320" s="3" t="n">
+        <v>0.0004544421722336594</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -21029,6 +22955,12 @@
       <c r="T321" s="2" t="n">
         <v>-0.001290655653071618</v>
       </c>
+      <c r="U321" s="1" t="n">
+        <v>0.07774</v>
+      </c>
+      <c r="V321" s="3" t="n">
+        <v>0.004652364952184017</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -21093,6 +23025,12 @@
       <c r="T322" s="3" t="n">
         <v>0.003071253071253074</v>
       </c>
+      <c r="U322" s="1" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="V322" s="3" t="n">
+        <v>0.001224739742804689</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -21157,6 +23095,12 @@
       <c r="T323" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U323" s="1" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="V323" s="3" t="n">
+        <v>0.0005045408678103491</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -21221,6 +23165,12 @@
       <c r="T324" s="2" t="n">
         <v>-0.0002628910504375281</v>
       </c>
+      <c r="U324" s="1" t="n">
+        <v>0.053319</v>
+      </c>
+      <c r="V324" s="3" t="n">
+        <v>0.001483846731780536</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -21285,6 +23235,12 @@
       <c r="T325" s="3" t="n">
         <v>0.006399373122632942</v>
       </c>
+      <c r="U325" s="1" t="n">
+        <v>0.15374</v>
+      </c>
+      <c r="V325" s="2" t="n">
+        <v>-0.002465611212042689</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -21349,6 +23305,12 @@
       <c r="T326" s="2" t="n">
         <v>-0.005389590391130189</v>
       </c>
+      <c r="U326" s="1" t="n">
+        <v>0.006457</v>
+      </c>
+      <c r="V326" s="2" t="n">
+        <v>-0.000309645455952975</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -21413,6 +23375,12 @@
       <c r="T327" s="3" t="n">
         <v>0.002107898030432829</v>
       </c>
+      <c r="U327" s="1" t="n">
+        <v>0.015201</v>
+      </c>
+      <c r="V327" s="2" t="n">
+        <v>-0.0007887990534412405</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -21477,6 +23445,12 @@
       <c r="T328" s="3" t="n">
         <v>0.005274261603375532</v>
       </c>
+      <c r="U328" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="V328" s="3" t="n">
+        <v>0.004197271773347299</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -21541,6 +23515,12 @@
       <c r="T329" s="2" t="n">
         <v>-0.0006784260515602738</v>
       </c>
+      <c r="U329" s="1" t="n">
+        <v>0.004411</v>
+      </c>
+      <c r="V329" s="2" t="n">
+        <v>-0.001810364335822628</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -21605,6 +23585,12 @@
       <c r="T330" s="3" t="n">
         <v>0.0001938735944163653</v>
       </c>
+      <c r="U330" s="1" t="n">
+        <v>0.05158</v>
+      </c>
+      <c r="V330" s="2" t="n">
+        <v>-0.000193836014731462</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -21669,6 +23655,12 @@
       <c r="T331" s="2" t="n">
         <v>-0.001929969671904982</v>
       </c>
+      <c r="U331" s="1" t="n">
+        <v>0.03631</v>
+      </c>
+      <c r="V331" s="3" t="n">
+        <v>0.003038674033149143</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -21733,6 +23725,12 @@
       <c r="T332" s="3" t="n">
         <v>0.00205338809034904</v>
       </c>
+      <c r="U332" s="1" t="n">
+        <v>0.1472</v>
+      </c>
+      <c r="V332" s="3" t="n">
+        <v>0.005464480874316907</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -21797,6 +23795,12 @@
       <c r="T333" s="3" t="n">
         <v>0.001037344398340279</v>
       </c>
+      <c r="U333" s="1" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="V333" s="3" t="n">
+        <v>0.001036269430051843</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -21861,6 +23865,12 @@
       <c r="T334" s="3" t="n">
         <v>0.003651300775901425</v>
       </c>
+      <c r="U334" s="1" t="n">
+        <v>0.04407</v>
+      </c>
+      <c r="V334" s="3" t="n">
+        <v>0.002046384720327417</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -21925,6 +23935,12 @@
       <c r="T335" s="2" t="n">
         <v>-0.0002467917077986935</v>
       </c>
+      <c r="U335" s="1" t="n">
+        <v>0.0813</v>
+      </c>
+      <c r="V335" s="3" t="n">
+        <v>0.003455936805727012</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -21989,6 +24005,12 @@
       <c r="T336" s="2" t="n">
         <v>-0.0004892367906065997</v>
       </c>
+      <c r="U336" s="1" t="n">
+        <v>0.2048</v>
+      </c>
+      <c r="V336" s="3" t="n">
+        <v>0.002447381302006855</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -22053,6 +24075,12 @@
       <c r="T337" s="2" t="n">
         <v>-0.002941176470588285</v>
       </c>
+      <c r="U337" s="1" t="n">
+        <v>0.01018</v>
+      </c>
+      <c r="V337" s="3" t="n">
+        <v>0.000983284169124837</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -22117,6 +24145,12 @@
       <c r="T338" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U338" s="1" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="V338" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -22181,6 +24215,12 @@
       <c r="T339" s="2" t="n">
         <v>-0.002729257641921286</v>
       </c>
+      <c r="U339" s="1" t="n">
+        <v>0.01835</v>
+      </c>
+      <c r="V339" s="3" t="n">
+        <v>0.004378762999452666</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -22245,6 +24285,12 @@
       <c r="T340" s="2" t="n">
         <v>-0.003792893691630606</v>
       </c>
+      <c r="U340" s="1" t="n">
+        <v>0.27477</v>
+      </c>
+      <c r="V340" s="2" t="n">
+        <v>-0.01307424302287984</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -22309,6 +24355,12 @@
       <c r="T341" s="2" t="n">
         <v>-0.003948896631823381</v>
       </c>
+      <c r="U341" s="1" t="n">
+        <v>0.04293</v>
+      </c>
+      <c r="V341" s="3" t="n">
+        <v>0.001166044776119436</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -22373,6 +24425,12 @@
       <c r="T342" s="3" t="n">
         <v>0.001170960187353718</v>
       </c>
+      <c r="U342" s="1" t="n">
+        <v>0.07718999999999999</v>
+      </c>
+      <c r="V342" s="3" t="n">
+        <v>0.00311890838206615</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -22437,6 +24495,12 @@
       <c r="T343" s="3" t="n">
         <v>0.001307702366941256</v>
       </c>
+      <c r="U343" s="1" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="V343" s="3" t="n">
+        <v>0.001697792869269936</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -22501,6 +24565,12 @@
       <c r="T344" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U344" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V344" s="2" t="n">
+        <v>-0.002493765586035007</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -22565,6 +24635,12 @@
       <c r="T345" s="3" t="n">
         <v>0.001074691026329886</v>
       </c>
+      <c r="U345" s="1" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="V345" s="3" t="n">
+        <v>0.00107353730542132</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -22629,6 +24705,12 @@
       <c r="T346" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U346" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="V346" s="3" t="n">
+        <v>0.004830917874396106</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -22693,6 +24775,12 @@
       <c r="T347" s="3" t="n">
         <v>0.001724137931034612</v>
       </c>
+      <c r="U347" s="1" t="n">
+        <v>0.1747</v>
+      </c>
+      <c r="V347" s="3" t="n">
+        <v>0.002294893861158828</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -22757,6 +24845,12 @@
       <c r="T348" s="3" t="n">
         <v>0.0005587776257732415</v>
       </c>
+      <c r="U348" s="1" t="n">
+        <v>5189.7</v>
+      </c>
+      <c r="V348" s="2" t="n">
+        <v>-0.0005969804344477668</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -22821,6 +24915,12 @@
       <c r="T349" s="2" t="n">
         <v>-0.01064584811923356</v>
       </c>
+      <c r="U349" s="1" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="V349" s="2" t="n">
+        <v>-0.00358680057388807</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -22885,6 +24985,12 @@
       <c r="T350" s="3" t="n">
         <v>0.004638833664678636</v>
       </c>
+      <c r="U350" s="1" t="n">
+        <v>0.01526</v>
+      </c>
+      <c r="V350" s="3" t="n">
+        <v>0.006596306068601543</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -22949,6 +25055,12 @@
       <c r="T351" s="2" t="n">
         <v>-0.0004917226684151147</v>
       </c>
+      <c r="U351" s="1" t="n">
+        <v>0.0006082</v>
+      </c>
+      <c r="V351" s="2" t="n">
+        <v>-0.002623811085601723</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -23013,6 +25125,12 @@
       <c r="T352" s="3" t="n">
         <v>0.006602336211274843</v>
       </c>
+      <c r="U352" s="1" t="n">
+        <v>0.01982</v>
+      </c>
+      <c r="V352" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -23077,6 +25195,12 @@
       <c r="T353" s="2" t="n">
         <v>-0.002676659528907925</v>
       </c>
+      <c r="U353" s="1" t="n">
+        <v>0.09314</v>
+      </c>
+      <c r="V353" s="2" t="n">
+        <v>-0.0001073537305420947</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -23141,6 +25265,12 @@
       <c r="T354" s="2" t="n">
         <v>-0.003303964757709346</v>
       </c>
+      <c r="U354" s="1" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="V354" s="3" t="n">
+        <v>0.001104972375690639</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -23205,6 +25335,12 @@
       <c r="T355" s="3" t="n">
         <v>0.01271322819439961</v>
       </c>
+      <c r="U355" s="1" t="n">
+        <v>0.0006311</v>
+      </c>
+      <c r="V355" s="3" t="n">
+        <v>0.002860320991578014</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -23269,6 +25405,12 @@
       <c r="T356" s="2" t="n">
         <v>-0.007801072647489036</v>
       </c>
+      <c r="U356" s="1" t="n">
+        <v>2.033</v>
+      </c>
+      <c r="V356" s="2" t="n">
+        <v>-0.0009828009828010927</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -23333,6 +25475,12 @@
       <c r="T357" s="3" t="n">
         <v>0.001316944688323037</v>
       </c>
+      <c r="U357" s="1" t="n">
+        <v>0.02282</v>
+      </c>
+      <c r="V357" s="3" t="n">
+        <v>0.0004384042086803855</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -23397,6 +25545,12 @@
       <c r="T358" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U358" s="1" t="n">
+        <v>0.000405</v>
+      </c>
+      <c r="V358" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -23461,6 +25615,12 @@
       <c r="T359" s="2" t="n">
         <v>-0.002721088435374157</v>
       </c>
+      <c r="U359" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="V359" s="3" t="n">
+        <v>0.002046384720327457</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -23525,6 +25685,12 @@
       <c r="T360" s="2" t="n">
         <v>-0.004486987735566932</v>
       </c>
+      <c r="U360" s="1" t="n">
+        <v>0.00333</v>
+      </c>
+      <c r="V360" s="3" t="n">
+        <v>0.0006009615384616183</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -23589,6 +25755,12 @@
       <c r="T361" s="3" t="n">
         <v>0.004067584480600824</v>
       </c>
+      <c r="U361" s="1" t="n">
+        <v>0.6429</v>
+      </c>
+      <c r="V361" s="3" t="n">
+        <v>0.001713929573075709</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -23653,6 +25825,12 @@
       <c r="T362" s="3" t="n">
         <v>0.0008583690987124113</v>
       </c>
+      <c r="U362" s="1" t="n">
+        <v>0.02342</v>
+      </c>
+      <c r="V362" s="3" t="n">
+        <v>0.00428816466552313</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -23717,6 +25895,12 @@
       <c r="T363" s="2" t="n">
         <v>-0.0007645259938837078</v>
       </c>
+      <c r="U363" s="1" t="n">
+        <v>0.06536</v>
+      </c>
+      <c r="V363" s="3" t="n">
+        <v>0.0001530221882172322</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -23781,6 +25965,12 @@
       <c r="T364" s="3" t="n">
         <v>0.001486830926083193</v>
       </c>
+      <c r="U364" s="1" t="n">
+        <v>4.705</v>
+      </c>
+      <c r="V364" s="2" t="n">
+        <v>-0.002120890774125087</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -23845,6 +26035,12 @@
       <c r="T365" s="3" t="n">
         <v>0.002243409983174528</v>
       </c>
+      <c r="U365" s="1" t="n">
+        <v>0.07174999999999999</v>
+      </c>
+      <c r="V365" s="3" t="n">
+        <v>0.003777280358142032</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -23909,6 +26105,12 @@
       <c r="T366" s="3" t="n">
         <v>0.006076854334226989</v>
       </c>
+      <c r="U366" s="1" t="n">
+        <v>0.05617</v>
+      </c>
+      <c r="V366" s="2" t="n">
+        <v>-0.002131817374311637</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -23973,6 +26175,12 @@
       <c r="T367" s="3" t="n">
         <v>0.001540832049306741</v>
       </c>
+      <c r="U367" s="1" t="n">
+        <v>0.05857</v>
+      </c>
+      <c r="V367" s="3" t="n">
+        <v>0.001196581196581088</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -24037,6 +26245,12 @@
       <c r="T368" s="2" t="n">
         <v>-0.0008719916288803877</v>
       </c>
+      <c r="U368" s="1" t="n">
+        <v>0.05732</v>
+      </c>
+      <c r="V368" s="3" t="n">
+        <v>0.0005236515971374105</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -24101,6 +26315,12 @@
       <c r="T369" s="3" t="n">
         <v>0.0003226847370119262</v>
       </c>
+      <c r="U369" s="1" t="n">
+        <v>0.03103</v>
+      </c>
+      <c r="V369" s="3" t="n">
+        <v>0.0009677419354838315</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -24165,6 +26385,12 @@
       <c r="T370" s="2" t="n">
         <v>-0.001231527093595922</v>
       </c>
+      <c r="U370" s="1" t="n">
+        <v>0.0001625</v>
+      </c>
+      <c r="V370" s="3" t="n">
+        <v>0.001849568434031937</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -24229,6 +26455,12 @@
       <c r="T371" s="2" t="n">
         <v>-0.002338497515346447</v>
       </c>
+      <c r="U371" s="1" t="n">
+        <v>0.006833</v>
+      </c>
+      <c r="V371" s="3" t="n">
+        <v>0.001025490770583074</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -24293,6 +26525,12 @@
       <c r="T372" s="3" t="n">
         <v>0.003586286042174702</v>
       </c>
+      <c r="U372" s="1" t="n">
+        <v>0.007018</v>
+      </c>
+      <c r="V372" s="3" t="n">
+        <v>0.00314465408805036</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -24357,6 +26595,12 @@
       <c r="T373" s="2" t="n">
         <v>-0.005784906652642597</v>
       </c>
+      <c r="U373" s="1" t="n">
+        <v>3.787</v>
+      </c>
+      <c r="V373" s="3" t="n">
+        <v>0.001586881777307533</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -24421,6 +26665,12 @@
       <c r="T374" s="2" t="n">
         <v>-0.003395105389729864</v>
       </c>
+      <c r="U374" s="1" t="n">
+        <v>0.07053</v>
+      </c>
+      <c r="V374" s="3" t="n">
+        <v>0.001135557132718194</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -24485,6 +26735,12 @@
       <c r="T375" s="3" t="n">
         <v>0.009189534141671963</v>
       </c>
+      <c r="U375" s="1" t="n">
+        <v>0.07953</v>
+      </c>
+      <c r="V375" s="3" t="n">
+        <v>0.005817629948147237</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -24549,6 +26805,12 @@
       <c r="T376" s="3" t="n">
         <v>0.001116783663050425</v>
       </c>
+      <c r="U376" s="1" t="n">
+        <v>0.06283999999999999</v>
+      </c>
+      <c r="V376" s="3" t="n">
+        <v>0.001434262948207058</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -24613,6 +26875,12 @@
       <c r="T377" s="3" t="n">
         <v>0.001572945340149548</v>
       </c>
+      <c r="U377" s="1" t="n">
+        <v>0.07659000000000001</v>
+      </c>
+      <c r="V377" s="3" t="n">
+        <v>0.002355712603062421</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -24677,6 +26945,12 @@
       <c r="T378" s="2" t="n">
         <v>-0.001739562624254515</v>
       </c>
+      <c r="U378" s="1" t="n">
+        <v>0.0004028</v>
+      </c>
+      <c r="V378" s="3" t="n">
+        <v>0.002738361961662864</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -24741,6 +27015,12 @@
       <c r="T379" s="3" t="n">
         <v>0.001075268817204444</v>
       </c>
+      <c r="U379" s="1" t="n">
+        <v>0.07443</v>
+      </c>
+      <c r="V379" s="2" t="n">
+        <v>-0.0006713211600430769</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -24805,6 +27085,12 @@
       <c r="T380" s="3" t="n">
         <v>0.003684598378776723</v>
       </c>
+      <c r="U380" s="1" t="n">
+        <v>0.001368</v>
+      </c>
+      <c r="V380" s="3" t="n">
+        <v>0.004405286343612442</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -24869,6 +27155,12 @@
       <c r="T381" s="3" t="n">
         <v>0.003132341425215421</v>
       </c>
+      <c r="U381" s="1" t="n">
+        <v>6.404</v>
+      </c>
+      <c r="V381" s="2" t="n">
+        <v>-0.0001561280249805361</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -24933,6 +27225,12 @@
       <c r="T382" s="3" t="n">
         <v>0.0007320644216690771</v>
       </c>
+      <c r="U382" s="1" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="V382" s="3" t="n">
+        <v>0.005120702267739621</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -24997,6 +27295,12 @@
       <c r="T383" s="3" t="n">
         <v>0.0005691519635742512</v>
       </c>
+      <c r="U383" s="1" t="n">
+        <v>0.01758</v>
+      </c>
+      <c r="V383" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -25061,6 +27365,12 @@
       <c r="T384" s="2" t="n">
         <v>-0.002944062806673293</v>
       </c>
+      <c r="U384" s="1" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="V384" s="3" t="n">
+        <v>0.0009842519685039652</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -25125,6 +27435,12 @@
       <c r="T385" s="3" t="n">
         <v>0.001563197856185923</v>
       </c>
+      <c r="U385" s="1" t="n">
+        <v>4.488</v>
+      </c>
+      <c r="V385" s="3" t="n">
+        <v>0.0006688963210702595</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -25189,6 +27505,12 @@
       <c r="T386" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U386" s="1" t="n">
+        <v>0.00128</v>
+      </c>
+      <c r="V386" s="2" t="n">
+        <v>-0.003115264797507695</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -25253,6 +27575,12 @@
       <c r="T387" s="3" t="n">
         <v>0.0008450228156159505</v>
       </c>
+      <c r="U387" s="1" t="n">
+        <v>0.0005939</v>
+      </c>
+      <c r="V387" s="3" t="n">
+        <v>0.002870651806821998</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -25317,6 +27645,12 @@
       <c r="T388" s="2" t="n">
         <v>-0.001748251748251828</v>
       </c>
+      <c r="U388" s="1" t="n">
+        <v>0.01143</v>
+      </c>
+      <c r="V388" s="3" t="n">
+        <v>0.000875656742556882</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -25381,6 +27715,12 @@
       <c r="T389" s="2" t="n">
         <v>-0.003303964757709117</v>
       </c>
+      <c r="U389" s="1" t="n">
+        <v>0.009050000000000001</v>
+      </c>
+      <c r="V389" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -25445,6 +27785,12 @@
       <c r="T390" s="3" t="n">
         <v>0.001267266506146279</v>
       </c>
+      <c r="U390" s="1" t="n">
+        <v>0.07906000000000001</v>
+      </c>
+      <c r="V390" s="3" t="n">
+        <v>0.0006328312871789441</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -25509,6 +27855,12 @@
       <c r="T391" s="3" t="n">
         <v>0.002717918850708624</v>
       </c>
+      <c r="U391" s="1" t="n">
+        <v>0.05153</v>
+      </c>
+      <c r="V391" s="2" t="n">
+        <v>-0.002323330106486003</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -25573,6 +27925,12 @@
       <c r="T392" s="3" t="n">
         <v>0.004219409282700433</v>
       </c>
+      <c r="U392" s="1" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="V392" s="2" t="n">
+        <v>-0.008403361344537837</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -25637,6 +27995,12 @@
       <c r="T393" s="3" t="n">
         <v>0.001868285847734789</v>
       </c>
+      <c r="U393" s="1" t="n">
+        <v>0.02139</v>
+      </c>
+      <c r="V393" s="2" t="n">
+        <v>-0.002797202797202845</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -25701,6 +28065,12 @@
       <c r="T394" s="2" t="n">
         <v>-0.004385964912280624</v>
       </c>
+      <c r="U394" s="1" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="V394" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -25765,6 +28135,12 @@
       <c r="T395" s="2" t="n">
         <v>-0.001027749229188108</v>
       </c>
+      <c r="U395" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="V395" s="3" t="n">
+        <v>0.001028806584362169</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -25829,6 +28205,12 @@
       <c r="T396" s="3" t="n">
         <v>0.000735835172921348</v>
       </c>
+      <c r="U396" s="1" t="n">
+        <v>2.728</v>
+      </c>
+      <c r="V396" s="3" t="n">
+        <v>0.002941176470588238</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -25893,6 +28275,12 @@
       <c r="T397" s="3" t="n">
         <v>0.002386634844868826</v>
       </c>
+      <c r="U397" s="1" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="V397" s="3" t="n">
+        <v>0.003968253968253884</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -25957,6 +28345,12 @@
       <c r="T398" s="3" t="n">
         <v>0.002985074626865715</v>
       </c>
+      <c r="U398" s="1" t="n">
+        <v>0.007373</v>
+      </c>
+      <c r="V398" s="2" t="n">
+        <v>-0.00257034632034631</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -26021,6 +28415,12 @@
       <c r="T399" s="2" t="n">
         <v>-0.004996156802459523</v>
       </c>
+      <c r="U399" s="1" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="V399" s="3" t="n">
+        <v>0.001158748551564183</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -26085,6 +28485,12 @@
       <c r="T400" s="3" t="n">
         <v>0.005997474747474612</v>
       </c>
+      <c r="U400" s="1" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="V400" s="3" t="n">
+        <v>0.0003137747097583589</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -26149,6 +28555,12 @@
       <c r="T401" s="2" t="n">
         <v>-0.004551096400496489</v>
       </c>
+      <c r="U401" s="1" t="n">
+        <v>0.007227</v>
+      </c>
+      <c r="V401" s="3" t="n">
+        <v>0.001246882793017502</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -26213,6 +28625,12 @@
       <c r="T402" s="3" t="n">
         <v>0.0004365858982755437</v>
       </c>
+      <c r="U402" s="1" t="n">
+        <v>0.00462</v>
+      </c>
+      <c r="V402" s="3" t="n">
+        <v>0.008073314422867054</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -26277,6 +28695,12 @@
       <c r="T403" s="3" t="n">
         <v>0.001511715797430126</v>
       </c>
+      <c r="U403" s="1" t="n">
+        <v>0.2656</v>
+      </c>
+      <c r="V403" s="3" t="n">
+        <v>0.002264150943396187</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -26341,6 +28765,12 @@
       <c r="T404" s="2" t="n">
         <v>-0.003333333333333313</v>
       </c>
+      <c r="U404" s="1" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="V404" s="3" t="n">
+        <v>0.003344481605351151</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -26405,6 +28835,12 @@
       <c r="T405" s="2" t="n">
         <v>-0.006020674769964747</v>
       </c>
+      <c r="U405" s="1" t="n">
+        <v>0.0008767</v>
+      </c>
+      <c r="V405" s="3" t="n">
+        <v>0.001942857142857128</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -26469,6 +28905,12 @@
       <c r="T406" s="2" t="n">
         <v>-0.0001971997633603101</v>
       </c>
+      <c r="U406" s="1" t="n">
+        <v>0.005074</v>
+      </c>
+      <c r="V406" s="3" t="n">
+        <v>0.000788954635108586</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -26533,6 +28975,12 @@
       <c r="T407" s="2" t="n">
         <v>-0.004139072847682094</v>
       </c>
+      <c r="U407" s="1" t="n">
+        <v>0.01203</v>
+      </c>
+      <c r="V407" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -26597,6 +29045,12 @@
       <c r="T408" s="3" t="n">
         <v>0.003455425017277134</v>
       </c>
+      <c r="U408" s="1" t="n">
+        <v>0.001454</v>
+      </c>
+      <c r="V408" s="3" t="n">
+        <v>0.001377410468319593</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -26661,6 +29115,12 @@
       <c r="T409" s="3" t="n">
         <v>0.009690444145356641</v>
       </c>
+      <c r="U409" s="1" t="n">
+        <v>0.03759</v>
+      </c>
+      <c r="V409" s="3" t="n">
+        <v>0.002132764596107618</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -26725,6 +29185,12 @@
       <c r="T410" s="2" t="n">
         <v>-0.001842751842751768</v>
       </c>
+      <c r="U410" s="1" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="V410" s="3" t="n">
+        <v>0.003076923076922952</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -26789,6 +29255,12 @@
       <c r="T411" s="2" t="n">
         <v>-0.00104986876640423</v>
       </c>
+      <c r="U411" s="1" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="V411" s="2" t="n">
+        <v>-0.001050972149238075</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -26853,6 +29325,12 @@
       <c r="T412" s="3" t="n">
         <v>0.0002973093503791605</v>
       </c>
+      <c r="U412" s="1" t="n">
+        <v>0.06762</v>
+      </c>
+      <c r="V412" s="3" t="n">
+        <v>0.004904146232723985</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -26917,6 +29395,12 @@
       <c r="T413" s="2" t="n">
         <v>-0.0003938558487593541</v>
       </c>
+      <c r="U413" s="1" t="n">
+        <v>2539</v>
+      </c>
+      <c r="V413" s="3" t="n">
+        <v>0.0003940110323089047</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -26981,6 +29465,12 @@
       <c r="T414" s="3" t="n">
         <v>0.005914901736309955</v>
       </c>
+      <c r="U414" s="1" t="n">
+        <v>0.05259</v>
+      </c>
+      <c r="V414" s="2" t="n">
+        <v>-0.002465857359635909</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -27045,6 +29535,12 @@
       <c r="T415" s="2" t="n">
         <v>-0.006857142857142863</v>
       </c>
+      <c r="U415" s="1" t="n">
+        <v>1.738</v>
+      </c>
+      <c r="V415" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -27109,6 +29605,12 @@
       <c r="T416" s="2" t="n">
         <v>-0.00347272464187533</v>
       </c>
+      <c r="U416" s="1" t="n">
+        <v>0.06901</v>
+      </c>
+      <c r="V416" s="3" t="n">
+        <v>0.002032815449397433</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -27173,6 +29675,12 @@
       <c r="T417" s="3" t="n">
         <v>0.02739726027397263</v>
       </c>
+      <c r="U417" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="V417" s="2" t="n">
+        <v>-0.01333333333333335</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -27237,6 +29745,12 @@
       <c r="T418" s="2" t="n">
         <v>-0.003257328990228016</v>
       </c>
+      <c r="U418" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="V418" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -27301,6 +29815,12 @@
       <c r="T419" s="2" t="n">
         <v>-0.008064516129032209</v>
       </c>
+      <c r="U419" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="V419" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -27365,6 +29885,12 @@
       <c r="T420" s="3" t="n">
         <v>0.004687500000000171</v>
       </c>
+      <c r="U420" s="1" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="V420" s="2" t="n">
+        <v>-0.002073613271125031</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -27429,6 +29955,12 @@
       <c r="T421" s="3" t="n">
         <v>0.0008796895213454255</v>
       </c>
+      <c r="U421" s="1" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="V421" s="3" t="n">
+        <v>0.005118395202150712</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -27493,6 +30025,12 @@
       <c r="T422" s="2" t="n">
         <v>-0.002049780380673517</v>
       </c>
+      <c r="U422" s="1" t="n">
+        <v>0.03407</v>
+      </c>
+      <c r="V422" s="2" t="n">
+        <v>-0.0002934272300468346</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -27557,6 +30095,12 @@
       <c r="T423" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U423" s="1" t="n">
+        <v>0.1416</v>
+      </c>
+      <c r="V423" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -27621,6 +30165,12 @@
       <c r="T424" s="3" t="n">
         <v>0.001897533206831042</v>
       </c>
+      <c r="U424" s="1" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="V424" s="2" t="n">
+        <v>-0.001893939393939317</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -27685,6 +30235,12 @@
       <c r="T425" s="2" t="n">
         <v>-0.0009532888465203907</v>
       </c>
+      <c r="U425" s="1" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="V425" s="2" t="n">
+        <v>-0.00095419847328247</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -27749,6 +30305,12 @@
       <c r="T426" s="2" t="n">
         <v>-0.001560947921101262</v>
       </c>
+      <c r="U426" s="1" t="n">
+        <v>0.007041</v>
+      </c>
+      <c r="V426" s="3" t="n">
+        <v>0.0007106310403639374</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -27813,6 +30375,12 @@
       <c r="T427" s="2" t="n">
         <v>-0.002742946708463974</v>
       </c>
+      <c r="U427" s="1" t="n">
+        <v>0.02547</v>
+      </c>
+      <c r="V427" s="3" t="n">
+        <v>0.0007858546168958422</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -27877,6 +30445,12 @@
       <c r="T428" s="2" t="n">
         <v>-0.003224206349206347</v>
       </c>
+      <c r="U428" s="1" t="n">
+        <v>0.00805</v>
+      </c>
+      <c r="V428" s="3" t="n">
+        <v>0.00149290868375216</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -27941,6 +30515,12 @@
       <c r="T429" s="3" t="n">
         <v>0.0008077544426494017</v>
       </c>
+      <c r="U429" s="1" t="n">
+        <v>0.01239</v>
+      </c>
+      <c r="V429" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -28005,6 +30585,12 @@
       <c r="T430" s="2" t="n">
         <v>-0.001195100089632458</v>
       </c>
+      <c r="U430" s="1" t="n">
+        <v>0.06677</v>
+      </c>
+      <c r="V430" s="2" t="n">
+        <v>-0.001346096320670158</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -28069,6 +30655,12 @@
       <c r="T431" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U431" s="1" t="n">
+        <v>0.00541</v>
+      </c>
+      <c r="V431" s="3" t="n">
+        <v>0.001851851851851776</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -28133,6 +30725,12 @@
       <c r="T432" s="2" t="n">
         <v>-0.002267106347897896</v>
       </c>
+      <c r="U432" s="1" t="n">
+        <v>0.009719999999999999</v>
+      </c>
+      <c r="V432" s="3" t="n">
+        <v>0.003924808923776063</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -28197,6 +30795,12 @@
       <c r="T433" s="2" t="n">
         <v>-0.003132530120482051</v>
       </c>
+      <c r="U433" s="1" t="n">
+        <v>0.04145</v>
+      </c>
+      <c r="V433" s="3" t="n">
+        <v>0.001933768431230449</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -28261,6 +30865,12 @@
       <c r="T434" s="2" t="n">
         <v>-0.004772130756382861</v>
       </c>
+      <c r="U434" s="1" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="V434" s="3" t="n">
+        <v>0.001918005274514593</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -28325,6 +30935,12 @@
       <c r="T435" s="3" t="n">
         <v>0.00129870129870133</v>
       </c>
+      <c r="U435" s="1" t="n">
+        <v>0.001543</v>
+      </c>
+      <c r="V435" s="3" t="n">
+        <v>0.000648508430609684</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -28389,6 +31005,12 @@
       <c r="T436" s="2" t="n">
         <v>-0.003995641118779477</v>
       </c>
+      <c r="U436" s="1" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V436" s="3" t="n">
+        <v>0.002917578409919774</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -28453,6 +31075,12 @@
       <c r="T437" s="2" t="n">
         <v>-0.002558791275740244</v>
       </c>
+      <c r="U437" s="1" t="n">
+        <v>0.08175</v>
+      </c>
+      <c r="V437" s="2" t="n">
+        <v>-0.00134375763498655</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -28517,6 +31145,12 @@
       <c r="T438" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U438" s="1" t="n">
+        <v>0.1151</v>
+      </c>
+      <c r="V438" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -28581,6 +31215,12 @@
       <c r="T439" s="3" t="n">
         <v>0.0006476683937823121</v>
       </c>
+      <c r="U439" s="1" t="n">
+        <v>1.544</v>
+      </c>
+      <c r="V439" s="2" t="n">
+        <v>-0.0006472491909384401</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -28645,6 +31285,12 @@
       <c r="T440" s="2" t="n">
         <v>-0.0005552470849528777</v>
       </c>
+      <c r="U440" s="1" t="n">
+        <v>0.001802</v>
+      </c>
+      <c r="V440" s="3" t="n">
+        <v>0.001111111111111138</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -28709,6 +31355,12 @@
       <c r="T441" s="3" t="n">
         <v>0.007070981778623968</v>
       </c>
+      <c r="U441" s="1" t="n">
+        <v>0.03698</v>
+      </c>
+      <c r="V441" s="2" t="n">
+        <v>-0.0013502565487443</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -28773,6 +31425,12 @@
       <c r="T442" s="2" t="n">
         <v>-0.002702702702702593</v>
       </c>
+      <c r="U442" s="1" t="n">
+        <v>0.01847</v>
+      </c>
+      <c r="V442" s="3" t="n">
+        <v>0.001084010840108357</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -28837,6 +31495,12 @@
       <c r="T443" s="3" t="n">
         <v>0.0001565312671205467</v>
       </c>
+      <c r="U443" s="1" t="n">
+        <v>0.12746</v>
+      </c>
+      <c r="V443" s="2" t="n">
+        <v>-0.002582361687142945</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -28901,6 +31565,12 @@
       <c r="T444" s="3" t="n">
         <v>0.0005201560468139629</v>
       </c>
+      <c r="U444" s="1" t="n">
+        <v>0.011514</v>
+      </c>
+      <c r="V444" s="2" t="n">
+        <v>-0.002339485313231024</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -28965,6 +31635,12 @@
       <c r="T445" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U445" s="1" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="V445" s="3" t="n">
+        <v>0.000247279920870501</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -29029,6 +31705,12 @@
       <c r="T446" s="2" t="n">
         <v>-0.000472366556447815</v>
       </c>
+      <c r="U446" s="1" t="n">
+        <v>0.000212</v>
+      </c>
+      <c r="V446" s="3" t="n">
+        <v>0.001890359168242012</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -29093,6 +31775,12 @@
       <c r="T447" s="2" t="n">
         <v>-0.001508295625942623</v>
       </c>
+      <c r="U447" s="1" t="n">
+        <v>0.00672</v>
+      </c>
+      <c r="V447" s="3" t="n">
+        <v>0.01510574018126892</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -29157,6 +31845,12 @@
       <c r="T448" s="2" t="n">
         <v>-0.092763039162606</v>
       </c>
+      <c r="U448" s="1" t="n">
+        <v>0.09936</v>
+      </c>
+      <c r="V448" s="2" t="n">
+        <v>-0.01173662223990452</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -29221,6 +31915,12 @@
       <c r="T449" s="2" t="n">
         <v>-0.001187648456057036</v>
       </c>
+      <c r="U449" s="1" t="n">
+        <v>0.001682</v>
+      </c>
+      <c r="V449" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -29285,6 +31985,12 @@
       <c r="T450" s="2" t="n">
         <v>-0.000483792936623137</v>
       </c>
+      <c r="U450" s="1" t="n">
+        <v>0.0002063</v>
+      </c>
+      <c r="V450" s="2" t="n">
+        <v>-0.001452081316553762</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -29349,6 +32055,12 @@
       <c r="T451" s="3" t="n">
         <v>0.001900418091980263</v>
       </c>
+      <c r="U451" s="1" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="V451" s="2" t="n">
+        <v>-0.0007587253414263875</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -29413,6 +32125,12 @@
       <c r="T452" s="2" t="n">
         <v>-0.0007440476190475371</v>
       </c>
+      <c r="U452" s="1" t="n">
+        <v>0.1345</v>
+      </c>
+      <c r="V452" s="3" t="n">
+        <v>0.00148920327624725</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -29477,6 +32195,12 @@
       <c r="T453" s="2" t="n">
         <v>-0.0005714285714285853</v>
       </c>
+      <c r="U453" s="1" t="n">
+        <v>0.0001751</v>
+      </c>
+      <c r="V453" s="3" t="n">
+        <v>0.001143510577472869</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -29541,6 +32265,12 @@
       <c r="T454" s="2" t="n">
         <v>-0.004025617566331162</v>
       </c>
+      <c r="U454" s="1" t="n">
+        <v>0.10959</v>
+      </c>
+      <c r="V454" s="3" t="n">
+        <v>0.006705860738563369</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -29605,6 +32335,12 @@
       <c r="T455" s="2" t="n">
         <v>-0.002587064676616852</v>
       </c>
+      <c r="U455" s="1" t="n">
+        <v>0.5031</v>
+      </c>
+      <c r="V455" s="3" t="n">
+        <v>0.003790901835594599</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -29669,6 +32405,12 @@
       <c r="T456" s="3" t="n">
         <v>0.0001878639864737636</v>
       </c>
+      <c r="U456" s="1" t="n">
+        <v>0.015979</v>
+      </c>
+      <c r="V456" s="3" t="n">
+        <v>0.0004382669671925909</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -29733,6 +32475,12 @@
       <c r="T457" s="3" t="n">
         <v>0.002241817366611905</v>
       </c>
+      <c r="U457" s="1" t="n">
+        <v>0.006717</v>
+      </c>
+      <c r="V457" s="3" t="n">
+        <v>0.001640322099612246</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -29797,6 +32545,12 @@
       <c r="T458" s="2" t="n">
         <v>-0.0004157139887757919</v>
       </c>
+      <c r="U458" s="1" t="n">
+        <v>0.4815</v>
+      </c>
+      <c r="V458" s="3" t="n">
+        <v>0.001247660636306903</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -29861,6 +32615,12 @@
       <c r="T459" s="3" t="n">
         <v>0.0003141690229343804</v>
       </c>
+      <c r="U459" s="1" t="n">
+        <v>0.006364</v>
+      </c>
+      <c r="V459" s="2" t="n">
+        <v>-0.0006281407035176713</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -29925,6 +32685,12 @@
       <c r="T460" s="2" t="n">
         <v>-0.001446131597975457</v>
       </c>
+      <c r="U460" s="1" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="V460" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -29989,6 +32755,12 @@
       <c r="T461" s="3" t="n">
         <v>0.01624568821631233</v>
       </c>
+      <c r="U461" s="1" t="n">
+        <v>0.09180000000000001</v>
+      </c>
+      <c r="V461" s="3" t="n">
+        <v>0.00514617321800079</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -30053,6 +32825,12 @@
       <c r="T462" s="2" t="n">
         <v>-0.002818122696726603</v>
       </c>
+      <c r="U462" s="1" t="n">
+        <v>0.04573</v>
+      </c>
+      <c r="V462" s="2" t="n">
+        <v>-0.005869565217391292</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -30117,6 +32895,12 @@
       <c r="T463" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U463" s="1" t="n">
+        <v>0.00697</v>
+      </c>
+      <c r="V463" s="2" t="n">
+        <v>-0.001432664756447057</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -30181,6 +32965,12 @@
       <c r="T464" s="2" t="n">
         <v>-0.001523229246001525</v>
       </c>
+      <c r="U464" s="1" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="V464" s="3" t="n">
+        <v>0.0007627765064836857</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -30245,6 +33035,12 @@
       <c r="T465" s="3" t="n">
         <v>0.0003539823008851133</v>
       </c>
+      <c r="U465" s="1" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="V465" s="3" t="n">
+        <v>0.0003538570417550919</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -30309,6 +33105,12 @@
       <c r="T466" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U466" s="1" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="V466" s="2" t="n">
+        <v>-0.0007042253521125986</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -30373,6 +33175,12 @@
       <c r="T467" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U467" s="1" t="n">
+        <v>0.01908</v>
+      </c>
+      <c r="V467" s="2" t="n">
+        <v>-0.0005238344683079933</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -30437,6 +33245,12 @@
       <c r="T468" s="3" t="n">
         <v>0.007014028056112287</v>
       </c>
+      <c r="U468" s="1" t="n">
+        <v>0.01001</v>
+      </c>
+      <c r="V468" s="2" t="n">
+        <v>-0.003980099502487572</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -30501,6 +33315,12 @@
       <c r="T469" s="2" t="n">
         <v>-0.002986560477849624</v>
       </c>
+      <c r="U469" s="1" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="V469" s="2" t="n">
+        <v>-0.00124812780828757</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -30565,6 +33385,12 @@
       <c r="T470" s="2" t="n">
         <v>-0.001133786848072563</v>
       </c>
+      <c r="U470" s="1" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="V470" s="3" t="n">
+        <v>0.001135073779795688</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -30629,6 +33455,12 @@
       <c r="T471" s="2" t="n">
         <v>-0.0006190034045186567</v>
       </c>
+      <c r="U471" s="1" t="n">
+        <v>3.231</v>
+      </c>
+      <c r="V471" s="3" t="n">
+        <v>0.0006193868070609414</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -30693,6 +33525,12 @@
       <c r="T472" s="3" t="n">
         <v>0.004326923076923068</v>
       </c>
+      <c r="U472" s="1" t="n">
+        <v>0.04183</v>
+      </c>
+      <c r="V472" s="3" t="n">
+        <v>0.001196744853997162</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -30757,6 +33595,12 @@
       <c r="T473" s="2" t="n">
         <v>-0.0007980845969671908</v>
       </c>
+      <c r="U473" s="1" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V473" s="2" t="n">
+        <v>-0.00159744408945687</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -30821,6 +33665,12 @@
       <c r="T474" s="3" t="n">
         <v>0.0003513703443428825</v>
       </c>
+      <c r="U474" s="1" t="n">
+        <v>0.008539</v>
+      </c>
+      <c r="V474" s="2" t="n">
+        <v>-0.0002341646177262926</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -30885,6 +33735,12 @@
       <c r="T475" s="3" t="n">
         <v>0.002642960115329311</v>
       </c>
+      <c r="U475" s="1" t="n">
+        <v>0.04175</v>
+      </c>
+      <c r="V475" s="3" t="n">
+        <v>0.0004792715073088709</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -30949,6 +33805,12 @@
       <c r="T476" s="2" t="n">
         <v>-0.00139346338991638</v>
       </c>
+      <c r="U476" s="1" t="n">
+        <v>0.07897999999999999</v>
+      </c>
+      <c r="V476" s="3" t="n">
+        <v>0.001902828872256722</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -31013,6 +33875,12 @@
       <c r="T477" s="2" t="n">
         <v>-0.002409814517306827</v>
       </c>
+      <c r="U477" s="1" t="n">
+        <v>0.13659</v>
+      </c>
+      <c r="V477" s="2" t="n">
+        <v>-0.0001464021667522143</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -31077,6 +33945,12 @@
       <c r="T478" s="2" t="n">
         <v>-0.0004211412929037521</v>
       </c>
+      <c r="U478" s="1" t="n">
+        <v>0.04743</v>
+      </c>
+      <c r="V478" s="2" t="n">
+        <v>-0.0008426374552348509</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -31141,6 +34015,12 @@
       <c r="T479" s="3" t="n">
         <v>0.003022289384208448</v>
       </c>
+      <c r="U479" s="1" t="n">
+        <v>0.005327</v>
+      </c>
+      <c r="V479" s="3" t="n">
+        <v>0.003201506591337198</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -31205,6 +34085,12 @@
       <c r="T480" s="3" t="n">
         <v>0.00250986016493379</v>
       </c>
+      <c r="U480" s="1" t="n">
+        <v>0.2794</v>
+      </c>
+      <c r="V480" s="2" t="n">
+        <v>-0.0007153075822604917</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -31269,6 +34155,12 @@
       <c r="T481" s="2" t="n">
         <v>-0.0001317870321559848</v>
       </c>
+      <c r="U481" s="1" t="n">
+        <v>0.07582</v>
+      </c>
+      <c r="V481" s="2" t="n">
+        <v>-0.0006590220113352888</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -31333,6 +34225,12 @@
       <c r="T482" s="3" t="n">
         <v>0.002022926500337189</v>
       </c>
+      <c r="U482" s="1" t="n">
+        <v>0.01493</v>
+      </c>
+      <c r="V482" s="3" t="n">
+        <v>0.00471063257065953</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -31397,6 +34295,12 @@
       <c r="T483" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U483" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="V483" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -31461,6 +34365,12 @@
       <c r="T484" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U484" s="1" t="n">
+        <v>0.02157</v>
+      </c>
+      <c r="V484" s="3" t="n">
+        <v>0.0009280742459396373</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -31525,6 +34435,12 @@
       <c r="T485" s="3" t="n">
         <v>0.009489051094890504</v>
       </c>
+      <c r="U485" s="1" t="n">
+        <v>0.008312</v>
+      </c>
+      <c r="V485" s="3" t="n">
+        <v>0.001687153530971333</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -31589,6 +34505,12 @@
       <c r="T486" s="3" t="n">
         <v>0.0002679169457467379</v>
       </c>
+      <c r="U486" s="1" t="n">
+        <v>0.007462</v>
+      </c>
+      <c r="V486" s="2" t="n">
+        <v>-0.0006696129637069502</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -31653,6 +34575,12 @@
       <c r="T487" s="2" t="n">
         <v>-0.0008952551477170008</v>
       </c>
+      <c r="U487" s="1" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="V487" s="2" t="n">
+        <v>-0.005376344086021534</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -31717,6 +34645,12 @@
       <c r="T488" s="3" t="n">
         <v>0.0008554319931566576</v>
       </c>
+      <c r="U488" s="1" t="n">
+        <v>0.009346999999999999</v>
+      </c>
+      <c r="V488" s="2" t="n">
+        <v>-0.00138888888888898</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -31781,6 +34715,12 @@
       <c r="T489" s="2" t="n">
         <v>-0.003626943005181379</v>
       </c>
+      <c r="U489" s="1" t="n">
+        <v>0.03845</v>
+      </c>
+      <c r="V489" s="2" t="n">
+        <v>-0.0002600104004160962</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -31845,6 +34785,12 @@
       <c r="T490" s="2" t="n">
         <v>-0.002386228055224156</v>
       </c>
+      <c r="U490" s="1" t="n">
+        <v>0.05862</v>
+      </c>
+      <c r="V490" s="3" t="n">
+        <v>0.00153767298821117</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -31909,6 +34855,12 @@
       <c r="T491" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U491" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="V491" s="3" t="n">
+        <v>0.001038421599169292</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -31973,6 +34925,12 @@
       <c r="T492" s="3" t="n">
         <v>0.0007524454477051256</v>
       </c>
+      <c r="U492" s="1" t="n">
+        <v>1.327</v>
+      </c>
+      <c r="V492" s="2" t="n">
+        <v>-0.002255639097744446</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -32037,6 +34995,12 @@
       <c r="T493" s="3" t="n">
         <v>0.001419244961680427</v>
       </c>
+      <c r="U493" s="1" t="n">
+        <v>0.03529</v>
+      </c>
+      <c r="V493" s="3" t="n">
+        <v>0.0002834467120182274</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -32101,6 +35065,12 @@
       <c r="T494" s="2" t="n">
         <v>-0.002913752913752997</v>
       </c>
+      <c r="U494" s="1" t="n">
+        <v>0.01702</v>
+      </c>
+      <c r="V494" s="2" t="n">
+        <v>-0.00526008182349502</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -32165,6 +35135,12 @@
       <c r="T495" s="3" t="n">
         <v>0.0002116850127011656</v>
       </c>
+      <c r="U495" s="1" t="n">
+        <v>0.04729</v>
+      </c>
+      <c r="V495" s="3" t="n">
+        <v>0.000846560846560812</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -32229,6 +35205,12 @@
       <c r="T496" s="2" t="n">
         <v>-0.004755013438081476</v>
       </c>
+      <c r="U496" s="1" t="n">
+        <v>0.04811</v>
+      </c>
+      <c r="V496" s="2" t="n">
+        <v>-0.0006231823847113055</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -32293,6 +35275,12 @@
       <c r="T497" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U497" s="1" t="n">
+        <v>0.04963</v>
+      </c>
+      <c r="V497" s="2" t="n">
+        <v>-0.0006041079339509111</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -32357,6 +35345,12 @@
       <c r="T498" s="3" t="n">
         <v>0.0006930006930006167</v>
       </c>
+      <c r="U498" s="1" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="V498" s="2" t="n">
+        <v>-0.002077562326869769</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -32421,6 +35415,12 @@
       <c r="T499" s="3" t="n">
         <v>0.0007339449541283595</v>
       </c>
+      <c r="U499" s="1" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="V499" s="3" t="n">
+        <v>0.001100110011001182</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -32485,6 +35485,12 @@
       <c r="T500" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U500" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="V500" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -32549,6 +35555,12 @@
       <c r="T501" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U501" s="1" t="n">
+        <v>0.03562</v>
+      </c>
+      <c r="V501" s="2" t="n">
+        <v>-0.003636363636363586</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -32613,6 +35625,12 @@
       <c r="T502" s="2" t="n">
         <v>-0.001253525540582838</v>
       </c>
+      <c r="U502" s="1" t="n">
+        <v>0.03187</v>
+      </c>
+      <c r="V502" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -32677,6 +35695,12 @@
       <c r="T503" s="3" t="n">
         <v>0.003630234668741006</v>
       </c>
+      <c r="U503" s="1" t="n">
+        <v>0.00774</v>
+      </c>
+      <c r="V503" s="2" t="n">
+        <v>-0.0001291822761916116</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -32741,6 +35765,12 @@
       <c r="T504" s="2" t="n">
         <v>-0.002271989613761804</v>
       </c>
+      <c r="U504" s="1" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="V504" s="2" t="n">
+        <v>-0.000325309043591376</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -32805,6 +35835,12 @@
       <c r="T505" s="2" t="n">
         <v>-0.006061422413793177</v>
       </c>
+      <c r="U505" s="1" t="n">
+        <v>0.000739</v>
+      </c>
+      <c r="V505" s="3" t="n">
+        <v>0.001490716899308812</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -32869,6 +35905,12 @@
       <c r="T506" s="2" t="n">
         <v>-0.001014884979702189</v>
       </c>
+      <c r="U506" s="1" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="V506" s="2" t="n">
+        <v>-0.0006772773450729207</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -32933,6 +35975,12 @@
       <c r="T507" s="2" t="n">
         <v>-0.003161222339304646</v>
       </c>
+      <c r="U507" s="1" t="n">
+        <v>0.002849</v>
+      </c>
+      <c r="V507" s="3" t="n">
+        <v>0.003875968992248118</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -32997,6 +36045,12 @@
       <c r="T508" s="2" t="n">
         <v>-0.0003154076644061228</v>
       </c>
+      <c r="U508" s="1" t="n">
+        <v>0.06333999999999999</v>
+      </c>
+      <c r="V508" s="2" t="n">
+        <v>-0.0007887679444708687</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -33061,6 +36115,12 @@
       <c r="T509" s="2" t="n">
         <v>-0.0008884940026653842</v>
       </c>
+      <c r="U509" s="1" t="n">
+        <v>2.244</v>
+      </c>
+      <c r="V509" s="2" t="n">
+        <v>-0.002223210315695817</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -33125,6 +36185,12 @@
       <c r="T510" s="3" t="n">
         <v>0.000546224225044394</v>
       </c>
+      <c r="U510" s="1" t="n">
+        <v>0.0007312</v>
+      </c>
+      <c r="V510" s="2" t="n">
+        <v>-0.002047222601337495</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -33189,6 +36255,12 @@
       <c r="T511" s="3" t="n">
         <v>0.001085383502170848</v>
       </c>
+      <c r="U511" s="1" t="n">
+        <v>0.2768</v>
+      </c>
+      <c r="V511" s="3" t="n">
+        <v>0.0003614022406938525</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -33253,6 +36325,12 @@
       <c r="T512" s="2" t="n">
         <v>-0.00288540807914258</v>
       </c>
+      <c r="U512" s="1" t="n">
+        <v>0.0004854</v>
+      </c>
+      <c r="V512" s="3" t="n">
+        <v>0.003307151715584921</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -33317,6 +36395,12 @@
       <c r="T513" s="3" t="n">
         <v>0.002163721601153897</v>
       </c>
+      <c r="U513" s="1" t="n">
+        <v>0.05566</v>
+      </c>
+      <c r="V513" s="3" t="n">
+        <v>0.001439366678661455</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -33381,6 +36465,12 @@
       <c r="T514" s="2" t="n">
         <v>-0.0009881422924901925</v>
       </c>
+      <c r="U514" s="1" t="n">
+        <v>0.03031</v>
+      </c>
+      <c r="V514" s="2" t="n">
+        <v>-0.0006594131223211073</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -33445,6 +36535,12 @@
       <c r="T515" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U515" s="1" t="n">
+        <v>0.00114</v>
+      </c>
+      <c r="V515" s="2" t="n">
+        <v>-0.001751313485113878</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -33509,6 +36605,12 @@
       <c r="T516" s="3" t="n">
         <v>0.0001510574018127089</v>
       </c>
+      <c r="U516" s="1" t="n">
+        <v>0.006634</v>
+      </c>
+      <c r="V516" s="3" t="n">
+        <v>0.00196344962996526</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -33573,6 +36675,12 @@
       <c r="T517" s="2" t="n">
         <v>-0.001003260596940188</v>
       </c>
+      <c r="U517" s="1" t="n">
+        <v>0.03984</v>
+      </c>
+      <c r="V517" s="3" t="n">
+        <v>0.0002510670348983947</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -33637,6 +36745,12 @@
       <c r="T518" s="3" t="n">
         <v>0.001945525291828714</v>
       </c>
+      <c r="U518" s="1" t="n">
+        <v>0.1029</v>
+      </c>
+      <c r="V518" s="2" t="n">
+        <v>-0.0009708737864076602</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -33701,6 +36815,12 @@
       <c r="T519" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U519" s="1" t="n">
+        <v>0.00876</v>
+      </c>
+      <c r="V519" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -33765,6 +36885,12 @@
       <c r="T520" s="2" t="n">
         <v>-0.004990642545227668</v>
       </c>
+      <c r="U520" s="1" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="V520" s="3" t="n">
+        <v>0.004388714733542358</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -33829,6 +36955,12 @@
       <c r="T521" s="3" t="n">
         <v>0.002237136465324294</v>
       </c>
+      <c r="U521" s="1" t="n">
+        <v>0.01793</v>
+      </c>
+      <c r="V521" s="3" t="n">
+        <v>0.0005580357142858852</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -33893,6 +37025,12 @@
       <c r="T522" s="3" t="n">
         <v>0.001221001221001383</v>
       </c>
+      <c r="U522" s="1" t="n">
+        <v>0.01635</v>
+      </c>
+      <c r="V522" s="2" t="n">
+        <v>-0.003048780487804965</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -33957,6 +37095,12 @@
       <c r="T523" s="3" t="n">
         <v>0.0004785833931561134</v>
       </c>
+      <c r="U523" s="1" t="n">
+        <v>0.004176</v>
+      </c>
+      <c r="V523" s="2" t="n">
+        <v>-0.001195886151638315</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -34021,6 +37165,12 @@
       <c r="T524" s="2" t="n">
         <v>-0.002810962754743507</v>
       </c>
+      <c r="U524" s="1" t="n">
+        <v>0.01421</v>
+      </c>
+      <c r="V524" s="3" t="n">
+        <v>0.001409443269908451</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -34085,6 +37235,12 @@
       <c r="T525" s="3" t="n">
         <v>0.0008041817450743541</v>
       </c>
+      <c r="U525" s="1" t="n">
+        <v>0.02487</v>
+      </c>
+      <c r="V525" s="2" t="n">
+        <v>-0.0008035355564483402</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -34149,6 +37305,12 @@
       <c r="T526" s="2" t="n">
         <v>-0.0008305647840530648</v>
       </c>
+      <c r="U526" s="1" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="V526" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -34213,6 +37375,12 @@
       <c r="T527" s="3" t="n">
         <v>0.00125034731869954</v>
       </c>
+      <c r="U527" s="1" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="V527" s="3" t="n">
+        <v>0.0004162619675315977</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -34277,6 +37445,12 @@
       <c r="T528" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U528" s="1" t="n">
+        <v>0.04329</v>
+      </c>
+      <c r="V528" s="2" t="n">
+        <v>-0.0004617871161394409</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -34341,6 +37515,12 @@
       <c r="T529" s="3" t="n">
         <v>0.001111111111111121</v>
       </c>
+      <c r="U529" s="1" t="n">
+        <v>0.06306</v>
+      </c>
+      <c r="V529" s="2" t="n">
+        <v>-0.0001585539876327275</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -34405,6 +37585,12 @@
       <c r="T530" s="3" t="n">
         <v>0.0003986446083317252</v>
       </c>
+      <c r="U530" s="1" t="n">
+        <v>0.005027</v>
+      </c>
+      <c r="V530" s="3" t="n">
+        <v>0.001593943016537198</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -34469,6 +37655,12 @@
       <c r="T531" s="2" t="n">
         <v>-0.003852080123266567</v>
       </c>
+      <c r="U531" s="1" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="V531" s="3" t="n">
+        <v>0.0007733952049496441</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -34533,6 +37725,12 @@
       <c r="T532" s="2" t="n">
         <v>-0.002059153874953182</v>
       </c>
+      <c r="U532" s="1" t="n">
+        <v>0.05327</v>
+      </c>
+      <c r="V532" s="2" t="n">
+        <v>-0.0007503282686176197</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -34597,6 +37795,12 @@
       <c r="T533" s="3" t="n">
         <v>0.004294149221685441</v>
       </c>
+      <c r="U533" s="1" t="n">
+        <v>0.003726</v>
+      </c>
+      <c r="V533" s="2" t="n">
+        <v>-0.004275788348476738</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -34661,6 +37865,12 @@
       <c r="T534" s="2" t="n">
         <v>-0.001164144353899917</v>
       </c>
+      <c r="U534" s="1" t="n">
+        <v>0.1715</v>
+      </c>
+      <c r="V534" s="2" t="n">
+        <v>-0.0005827505827505186</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -34725,6 +37935,12 @@
       <c r="T535" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="V535" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -34789,6 +38005,12 @@
       <c r="T536" s="2" t="n">
         <v>-0.0002253775073247745</v>
       </c>
+      <c r="U536" s="1" t="n">
+        <v>0.0004429</v>
+      </c>
+      <c r="V536" s="2" t="n">
+        <v>-0.001577998196573528</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -34853,6 +38075,12 @@
       <c r="T537" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U537" s="1" t="n">
+        <v>0.00967</v>
+      </c>
+      <c r="V537" s="2" t="n">
+        <v>-0.001033057851239627</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -34917,6 +38145,12 @@
       <c r="T538" s="2" t="n">
         <v>-0.001097092704333598</v>
       </c>
+      <c r="U538" s="1" t="n">
+        <v>0.05463</v>
+      </c>
+      <c r="V538" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -34981,6 +38215,12 @@
       <c r="T539" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="U539" s="1" t="n">
+        <v>0.6819</v>
+      </c>
+      <c r="V539" s="2" t="n">
+        <v>-0.0007327080890973856</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -35045,6 +38285,12 @@
       <c r="T540" s="3" t="n">
         <v>0.0006613756613755885</v>
       </c>
+      <c r="U540" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="V540" s="2" t="n">
+        <v>-0.001982815598149337</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -35109,6 +38355,12 @@
       <c r="T541" s="2" t="n">
         <v>-0.002291825821237493</v>
       </c>
+      <c r="U541" s="1" t="n">
+        <v>0.01303</v>
+      </c>
+      <c r="V541" s="2" t="n">
+        <v>-0.00229709035222056</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -35173,6 +38425,12 @@
       <c r="T542" s="2" t="n">
         <v>-0.004996431120628167</v>
       </c>
+      <c r="U542" s="1" t="n">
+        <v>0.01396</v>
+      </c>
+      <c r="V542" s="3" t="n">
+        <v>0.001434720229555303</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -35236,6 +38494,12 @@
       </c>
       <c r="T543" s="2" t="n">
         <v>-0.000174855744011123</v>
+      </c>
+      <c r="U543" s="1" t="n">
+        <v>0.05705</v>
+      </c>
+      <c r="V543" s="2" t="n">
+        <v>-0.002273522210563223</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X543"/>
+  <dimension ref="A1:Z543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -450,6 +450,8 @@
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -573,6 +575,16 @@
           <t>change_02:45</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>price_03:00</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>change_03:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -649,6 +661,12 @@
       <c r="X2" s="2" t="n">
         <v>-0.001151910728347598</v>
       </c>
+      <c r="Y2" s="1" t="n">
+        <v>69780.60000000001</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>-0.001566745504728137</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -725,6 +743,12 @@
       <c r="X3" s="3" t="n">
         <v>0.0005117732211005206</v>
       </c>
+      <c r="Y3" s="1" t="n">
+        <v>2047.78</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>-0.00241628262712268</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -801,6 +825,12 @@
       <c r="X4" s="2" t="n">
         <v>-0.0009292600766639365</v>
       </c>
+      <c r="Y4" s="1" t="n">
+        <v>85.81</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>-0.002325311010347667</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -877,6 +907,12 @@
       <c r="X5" s="3" t="n">
         <v>0.0005691519635743499</v>
       </c>
+      <c r="Y5" s="1" t="n">
+        <v>0.01046</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>-0.008342813803564613</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -953,6 +989,12 @@
       <c r="X6" s="2" t="n">
         <v>-0.001090671126299758</v>
       </c>
+      <c r="Y6" s="1" t="n">
+        <v>1.3714</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>-0.001746979181831386</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1029,6 +1071,12 @@
       <c r="X7" s="2" t="n">
         <v>-0.001488411652136947</v>
       </c>
+      <c r="Y7" s="1" t="n">
+        <v>0.09378</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>-0.001490630323679741</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1105,6 +1153,12 @@
       <c r="X8" s="2" t="n">
         <v>-0.008114023381199008</v>
       </c>
+      <c r="Y8" s="1" t="n">
+        <v>37.102</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>-0.001614552499865515</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1181,6 +1235,12 @@
       <c r="X9" s="2" t="n">
         <v>-0.002016942315449696</v>
       </c>
+      <c r="Y9" s="1" t="n">
+        <v>0.04988</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>0.008084074373484186</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1257,6 +1317,12 @@
       <c r="X10" s="2" t="n">
         <v>-0.01553460467109488</v>
       </c>
+      <c r="Y10" s="1" t="n">
+        <v>18.545</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>0.009086951790184003</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1333,6 +1399,12 @@
       <c r="X11" s="2" t="n">
         <v>-0.001077735523702553</v>
       </c>
+      <c r="Y11" s="1" t="n">
+        <v>648.02</v>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>-0.001217613785237533</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1409,6 +1481,12 @@
       <c r="X12" s="2" t="n">
         <v>-0.001842681101001883</v>
       </c>
+      <c r="Y12" s="1" t="n">
+        <v>0.8952</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>0.03288335064035995</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1563,12 @@
       <c r="X13" s="2" t="n">
         <v>-0.004601954644653188</v>
       </c>
+      <c r="Y13" s="1" t="n">
+        <v>208.97</v>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>-0.004003622324960695</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1561,6 +1645,12 @@
       <c r="X14" s="2" t="n">
         <v>-9.030432557718103e-05</v>
       </c>
+      <c r="Y14" s="1" t="n">
+        <v>0.0033195</v>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>-0.0006923956890842972</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1637,6 +1727,12 @@
       <c r="X15" s="2" t="n">
         <v>-0.003845664886854783</v>
       </c>
+      <c r="Y15" s="1" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>0.02667262227610642</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1713,6 +1809,12 @@
       <c r="X16" s="2" t="n">
         <v>-0.001436929077286326</v>
       </c>
+      <c r="Y16" s="1" t="n">
+        <v>0.9714</v>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>-0.001541782300339136</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1789,6 +1891,12 @@
       <c r="X17" s="3" t="n">
         <v>0.02150537634408602</v>
       </c>
+      <c r="Y17" s="1" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="Z17" s="2" t="n">
+        <v>-0.02105263157894736</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1865,6 +1973,12 @@
       <c r="X18" s="2" t="n">
         <v>-0.00831493399727538</v>
       </c>
+      <c r="Y18" s="1" t="n">
+        <v>210.92</v>
+      </c>
+      <c r="Z18" s="2" t="n">
+        <v>-0.0008526764566556458</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1941,6 +2055,12 @@
       <c r="X19" s="2" t="n">
         <v>-0.0007648183556406634</v>
       </c>
+      <c r="Y19" s="1" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="Z19" s="2" t="n">
+        <v>-0.002296211251435092</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2017,6 +2137,12 @@
       <c r="X20" s="3" t="n">
         <v>0.00281409392038456</v>
       </c>
+      <c r="Y20" s="1" t="n">
+        <v>0.017137</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>0.001870798012277157</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2093,6 +2219,12 @@
       <c r="X21" s="2" t="n">
         <v>-0.001671891327063742</v>
       </c>
+      <c r="Y21" s="1" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="Z21" s="2" t="n">
+        <v>-0.00146535482520422</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2169,6 +2301,12 @@
       <c r="X22" s="2" t="n">
         <v>-0.001183431952662756</v>
       </c>
+      <c r="Y22" s="1" t="n">
+        <v>0.1687</v>
+      </c>
+      <c r="Z22" s="2" t="n">
+        <v>-0.0005924170616114735</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2245,6 +2383,12 @@
       <c r="X23" s="2" t="n">
         <v>-0.006000342876735787</v>
       </c>
+      <c r="Y23" s="1" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="Z23" s="2" t="n">
+        <v>-0.009486029665401935</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2321,6 +2465,12 @@
       <c r="X24" s="3" t="n">
         <v>0.002312138728323701</v>
       </c>
+      <c r="Y24" s="1" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="Z24" s="2" t="n">
+        <v>-0.003460207612456751</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2397,6 +2547,12 @@
       <c r="X25" s="2" t="n">
         <v>-0.001998223801065598</v>
       </c>
+      <c r="Y25" s="1" t="n">
+        <v>8.973000000000001</v>
+      </c>
+      <c r="Z25" s="2" t="n">
+        <v>-0.001890989988876469</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2473,6 +2629,12 @@
       <c r="X26" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y26" s="1" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="Z26" s="2" t="n">
+        <v>-0.001498127340823971</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2549,6 +2711,12 @@
       <c r="X27" s="2" t="n">
         <v>-0.001035670934648961</v>
       </c>
+      <c r="Y27" s="1" t="n">
+        <v>5098.41</v>
+      </c>
+      <c r="Z27" s="2" t="n">
+        <v>-0.0008035261077392036</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2625,6 +2793,12 @@
       <c r="X28" s="2" t="n">
         <v>-0.002243409983174334</v>
       </c>
+      <c r="Y28" s="1" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>0.001967397414277624</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2701,6 +2875,12 @@
       <c r="X29" s="3" t="n">
         <v>0.001529051987767585</v>
       </c>
+      <c r="Y29" s="1" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>0.001908396946564845</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2777,6 +2957,12 @@
       <c r="X30" s="2" t="n">
         <v>-0.009861655562782365</v>
       </c>
+      <c r="Y30" s="1" t="n">
+        <v>0.56797</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>0.008362035294535369</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2853,6 +3039,12 @@
       <c r="X31" s="2" t="n">
         <v>-0.004310344827586156</v>
       </c>
+      <c r="Y31" s="1" t="n">
+        <v>0.002068</v>
+      </c>
+      <c r="Z31" s="2" t="n">
+        <v>-0.005291005291005367</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2929,6 +3121,12 @@
       <c r="X32" s="3" t="n">
         <v>0.004727949155169737</v>
       </c>
+      <c r="Y32" s="1" t="n">
+        <v>1.2927</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>-0.002777134922471687</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3005,6 +3203,12 @@
       <c r="X33" s="2" t="n">
         <v>-0.002352941176470655</v>
       </c>
+      <c r="Y33" s="1" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="Z33" s="2" t="n">
+        <v>-0.02122641509433958</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3081,6 +3285,12 @@
       <c r="X34" s="3" t="n">
         <v>0.002673796791443853</v>
       </c>
+      <c r="Y34" s="1" t="n">
+        <v>1.498</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>-0.001333333333333335</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3157,6 +3367,12 @@
       <c r="X35" s="3" t="n">
         <v>0.001121199463582982</v>
       </c>
+      <c r="Y35" s="1" t="n">
+        <v>454.96</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>-0.0009223066449998154</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3233,6 +3449,12 @@
       <c r="X36" s="3" t="n">
         <v>0.003337505214851762</v>
       </c>
+      <c r="Y36" s="1" t="n">
+        <v>0.04793</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>-0.003534303534303463</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3309,6 +3531,12 @@
       <c r="X37" s="2" t="n">
         <v>-0.0008502196400737494</v>
       </c>
+      <c r="Y37" s="1" t="n">
+        <v>0.7012</v>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>-0.005531130336122399</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3385,6 +3613,12 @@
       <c r="X38" s="2" t="n">
         <v>-0.002846299810246629</v>
       </c>
+      <c r="Y38" s="1" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="Z38" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3461,6 +3695,12 @@
       <c r="X39" s="2" t="n">
         <v>-0.001546157344247401</v>
       </c>
+      <c r="Y39" s="1" t="n">
+        <v>109.52</v>
+      </c>
+      <c r="Z39" s="2" t="n">
+        <v>-0.002368373109856122</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3537,6 +3777,12 @@
       <c r="X40" s="3" t="n">
         <v>0.001859229747675795</v>
       </c>
+      <c r="Y40" s="1" t="n">
+        <v>0.03688</v>
+      </c>
+      <c r="Z40" s="2" t="n">
+        <v>-0.02226935312831372</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3613,6 +3859,12 @@
       <c r="X41" s="2" t="n">
         <v>-0.001273885350318483</v>
       </c>
+      <c r="Y41" s="1" t="n">
+        <v>0.05508</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>0.003644314868804643</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3689,6 +3941,12 @@
       <c r="X42" s="3" t="n">
         <v>0.001661129568106375</v>
       </c>
+      <c r="Y42" s="1" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>-0.003501013451262296</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3765,6 +4023,12 @@
       <c r="X43" s="3" t="n">
         <v>0.001516300227445078</v>
       </c>
+      <c r="Y43" s="1" t="n">
+        <v>0.1322</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>0.0007570022710069398</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3841,6 +4105,12 @@
       <c r="X44" s="2" t="n">
         <v>-0.005256910293369619</v>
       </c>
+      <c r="Y44" s="1" t="n">
+        <v>0.00586</v>
+      </c>
+      <c r="Z44" s="2" t="n">
+        <v>-0.001022843504943732</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3917,6 +4187,12 @@
       <c r="X45" s="2" t="n">
         <v>-0.006047387726777034</v>
       </c>
+      <c r="Y45" s="1" t="n">
+        <v>0.10003</v>
+      </c>
+      <c r="Z45" s="2" t="n">
+        <v>-0.002294035507680111</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3993,6 +4269,12 @@
       <c r="X46" s="2" t="n">
         <v>-0.001433691756272403</v>
       </c>
+      <c r="Y46" s="1" t="n">
+        <v>2.779</v>
+      </c>
+      <c r="Z46" s="2" t="n">
+        <v>-0.002512562814070394</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4069,6 +4351,12 @@
       <c r="X47" s="3" t="n">
         <v>0.0004846638510003929</v>
       </c>
+      <c r="Y47" s="1" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="Z47" s="2" t="n">
+        <v>-0.001072664359861512</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4145,6 +4433,12 @@
       <c r="X48" s="3" t="n">
         <v>0.000932835820895549</v>
       </c>
+      <c r="Y48" s="1" t="n">
+        <v>0.1069</v>
+      </c>
+      <c r="Z48" s="2" t="n">
+        <v>-0.003727865796831421</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4221,6 +4515,12 @@
       <c r="X49" s="3" t="n">
         <v>0.006015468347178455</v>
       </c>
+      <c r="Y49" s="1" t="n">
+        <v>0.24558</v>
+      </c>
+      <c r="Z49" s="2" t="n">
+        <v>-0.001057598438008502</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4297,6 +4597,12 @@
       <c r="X50" s="3" t="n">
         <v>0.006722689075630123</v>
       </c>
+      <c r="Y50" s="1" t="n">
+        <v>0.04743</v>
+      </c>
+      <c r="Z50" s="2" t="n">
+        <v>-0.01022537562604335</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4373,6 +4679,12 @@
       <c r="X51" s="2" t="n">
         <v>-0.00307534597642235</v>
       </c>
+      <c r="Y51" s="1" t="n">
+        <v>3.889</v>
+      </c>
+      <c r="Z51" s="2" t="n">
+        <v>-0.0002570694087404457</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4449,6 +4761,12 @@
       <c r="X52" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y52" s="1" t="n">
+        <v>0.00023</v>
+      </c>
+      <c r="Z52" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4525,6 +4843,12 @@
       <c r="X53" s="2" t="n">
         <v>-0.00179211469534047</v>
       </c>
+      <c r="Y53" s="1" t="n">
+        <v>0.1674</v>
+      </c>
+      <c r="Z53" s="3" t="n">
+        <v>0.001795332136445211</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4601,6 +4925,12 @@
       <c r="X54" s="3" t="n">
         <v>0.007136060894386338</v>
       </c>
+      <c r="Y54" s="1" t="n">
+        <v>0.04197</v>
+      </c>
+      <c r="Z54" s="2" t="n">
+        <v>-0.008738781294284417</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4677,6 +5007,12 @@
       <c r="X55" s="2" t="n">
         <v>-0.009951872093971767</v>
       </c>
+      <c r="Y55" s="1" t="n">
+        <v>0.12136</v>
+      </c>
+      <c r="Z55" s="2" t="n">
+        <v>-8.239268352978496e-05</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4753,6 +5089,12 @@
       <c r="X56" s="3" t="n">
         <v>0.007645747053201699</v>
       </c>
+      <c r="Y56" s="1" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="Z56" s="2" t="n">
+        <v>-0.008852355358836625</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4829,6 +5171,12 @@
       <c r="X57" s="2" t="n">
         <v>-0.003442340791738391</v>
       </c>
+      <c r="Y57" s="1" t="n">
+        <v>0.01146</v>
+      </c>
+      <c r="Z57" s="2" t="n">
+        <v>-0.01036269430051816</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4905,6 +5253,12 @@
       <c r="X58" s="3" t="n">
         <v>0.001009081735620614</v>
       </c>
+      <c r="Y58" s="1" t="n">
+        <v>0.09909999999999999</v>
+      </c>
+      <c r="Z58" s="2" t="n">
+        <v>-0.001008064516129061</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4981,6 +5335,12 @@
       <c r="X59" s="2" t="n">
         <v>-0.003003003003003011</v>
       </c>
+      <c r="Y59" s="1" t="n">
+        <v>0.00332</v>
+      </c>
+      <c r="Z59" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5057,6 +5417,12 @@
       <c r="X60" s="2" t="n">
         <v>-0.001949317738791569</v>
       </c>
+      <c r="Y60" s="1" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="Z60" s="3" t="n">
+        <v>0.001302083333333371</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5133,6 +5499,12 @@
       <c r="X61" s="3" t="n">
         <v>0.0005031446540880298</v>
       </c>
+      <c r="Y61" s="1" t="n">
+        <v>0.15875</v>
+      </c>
+      <c r="Z61" s="2" t="n">
+        <v>-0.002074427960774434</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5209,6 +5581,12 @@
       <c r="X62" s="2" t="n">
         <v>-0.003952011291460868</v>
       </c>
+      <c r="Y62" s="1" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="Z62" s="3" t="n">
+        <v>0.0008502196400737494</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5285,6 +5663,12 @@
       <c r="X63" s="3" t="n">
         <v>0.01304049416609465</v>
       </c>
+      <c r="Y63" s="1" t="n">
+        <v>5.935</v>
+      </c>
+      <c r="Z63" s="3" t="n">
+        <v>0.005250677506775016</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5361,6 +5745,12 @@
       <c r="X64" s="2" t="n">
         <v>-0.002102017937219767</v>
       </c>
+      <c r="Y64" s="1" t="n">
+        <v>0.007144</v>
+      </c>
+      <c r="Z64" s="3" t="n">
+        <v>0.003229883443336674</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5437,6 +5827,12 @@
       <c r="X65" s="3" t="n">
         <v>0.0003126954346465329</v>
       </c>
+      <c r="Y65" s="1" t="n">
+        <v>0.03259</v>
+      </c>
+      <c r="Z65" s="3" t="n">
+        <v>0.01875586120662718</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5513,6 +5909,12 @@
       <c r="X66" s="2" t="n">
         <v>-0.004273504273504277</v>
       </c>
+      <c r="Y66" s="1" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="Z66" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5589,6 +5991,12 @@
       <c r="X67" s="2" t="n">
         <v>-0.003119151590767245</v>
       </c>
+      <c r="Y67" s="1" t="n">
+        <v>1.599</v>
+      </c>
+      <c r="Z67" s="3" t="n">
+        <v>0.000625782227784662</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5665,6 +6073,12 @@
       <c r="X68" s="2" t="n">
         <v>-0.00109436402526974</v>
       </c>
+      <c r="Y68" s="1" t="n">
+        <v>2.0096</v>
+      </c>
+      <c r="Z68" s="3" t="n">
+        <v>0.0007469747522531809</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5741,6 +6155,12 @@
       <c r="X69" s="3" t="n">
         <v>0.007281553398058221</v>
       </c>
+      <c r="Y69" s="1" t="n">
+        <v>0.5827</v>
+      </c>
+      <c r="Z69" s="3" t="n">
+        <v>0.002925989672977685</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5817,6 +6237,12 @@
       <c r="X70" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y70" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="Z70" s="2" t="n">
+        <v>-0.009615384615384625</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5893,6 +6319,12 @@
       <c r="X71" s="2" t="n">
         <v>-0.0004404316229904822</v>
       </c>
+      <c r="Y71" s="1" t="n">
+        <v>0.9051</v>
+      </c>
+      <c r="Z71" s="2" t="n">
+        <v>-0.002974223397224097</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5969,6 +6401,12 @@
       <c r="X72" s="2" t="n">
         <v>-0.003055947343676595</v>
       </c>
+      <c r="Y72" s="1" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="Z72" s="2" t="n">
+        <v>-0.002122141004479973</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6045,6 +6483,12 @@
       <c r="X73" s="3" t="n">
         <v>0.0002131060202449893</v>
       </c>
+      <c r="Y73" s="1" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="Z73" s="2" t="n">
+        <v>-0.001278363694471025</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6121,6 +6565,12 @@
       <c r="X74" s="3" t="n">
         <v>0.003141909582824269</v>
       </c>
+      <c r="Y74" s="1" t="n">
+        <v>1.1436</v>
+      </c>
+      <c r="Z74" s="2" t="n">
+        <v>-0.005046111014442341</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6197,6 +6647,12 @@
       <c r="X75" s="2" t="n">
         <v>-0.001884422110552687</v>
       </c>
+      <c r="Y75" s="1" t="n">
+        <v>0.01588</v>
+      </c>
+      <c r="Z75" s="2" t="n">
+        <v>-0.0006293266205162404</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6273,6 +6729,12 @@
       <c r="X76" s="3" t="n">
         <v>0.009235668789809094</v>
       </c>
+      <c r="Y76" s="1" t="n">
+        <v>0.12675</v>
+      </c>
+      <c r="Z76" s="2" t="n">
+        <v>-7.888923950781004e-05</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6349,6 +6811,12 @@
       <c r="X77" s="3" t="n">
         <v>0.0008539709649872149</v>
       </c>
+      <c r="Y77" s="1" t="n">
+        <v>0.1172</v>
+      </c>
+      <c r="Z77" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6425,6 +6893,12 @@
       <c r="X78" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y78" s="1" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="Z78" s="2" t="n">
+        <v>-0.002967359050445052</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6501,6 +6975,12 @@
       <c r="X79" s="2" t="n">
         <v>-0.001999000499750101</v>
       </c>
+      <c r="Y79" s="1" t="n">
+        <v>0.006004</v>
+      </c>
+      <c r="Z79" s="3" t="n">
+        <v>0.00216992154899015</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6577,6 +7057,12 @@
       <c r="X80" s="3" t="n">
         <v>0.005935842384440537</v>
       </c>
+      <c r="Y80" s="1" t="n">
+        <v>0.00801</v>
+      </c>
+      <c r="Z80" s="3" t="n">
+        <v>0.005649717514124282</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6653,6 +7139,12 @@
       <c r="X81" s="3" t="n">
         <v>0.001681614349775849</v>
       </c>
+      <c r="Y81" s="1" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="Z81" s="2" t="n">
+        <v>-0.0005595970900952189</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6729,6 +7221,12 @@
       <c r="X82" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y82" s="1" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="Z82" s="3" t="n">
+        <v>0.003719776813391131</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6805,6 +7303,12 @@
       <c r="X83" s="3" t="n">
         <v>0.000609756097561071</v>
       </c>
+      <c r="Y83" s="1" t="n">
+        <v>8.192</v>
+      </c>
+      <c r="Z83" s="2" t="n">
+        <v>-0.001584399756246179</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6881,6 +7385,12 @@
       <c r="X84" s="3" t="n">
         <v>0.003229919252018661</v>
       </c>
+      <c r="Y84" s="1" t="n">
+        <v>354.32</v>
+      </c>
+      <c r="Z84" s="3" t="n">
+        <v>0.0006495523736903562</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6957,6 +7467,12 @@
       <c r="X85" s="3" t="n">
         <v>0.001475651746187882</v>
       </c>
+      <c r="Y85" s="1" t="n">
+        <v>0.004066</v>
+      </c>
+      <c r="Z85" s="2" t="n">
+        <v>-0.001473477406679747</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7033,6 +7549,12 @@
       <c r="X86" s="2" t="n">
         <v>-0.006215417266732263</v>
       </c>
+      <c r="Y86" s="1" t="n">
+        <v>0.13077</v>
+      </c>
+      <c r="Z86" s="2" t="n">
+        <v>-0.002593242315612897</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7109,6 +7631,12 @@
       <c r="X87" s="3" t="n">
         <v>0.01280683030949843</v>
       </c>
+      <c r="Y87" s="1" t="n">
+        <v>0.01904</v>
+      </c>
+      <c r="Z87" s="3" t="n">
+        <v>0.003161222339304585</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7185,6 +7713,12 @@
       <c r="X88" s="3" t="n">
         <v>0.0008833922261485089</v>
       </c>
+      <c r="Y88" s="1" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="Z88" s="2" t="n">
+        <v>-0.001765225066195942</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7261,6 +7795,12 @@
       <c r="X89" s="3" t="n">
         <v>0.001018675721562046</v>
       </c>
+      <c r="Y89" s="1" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="Z89" s="2" t="n">
+        <v>-0.001356852103120799</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7337,6 +7877,12 @@
       <c r="X90" s="3" t="n">
         <v>0.0003892565200466679</v>
       </c>
+      <c r="Y90" s="1" t="n">
+        <v>0.2565</v>
+      </c>
+      <c r="Z90" s="2" t="n">
+        <v>-0.001945525291828796</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7413,6 +7959,12 @@
       <c r="X91" s="2" t="n">
         <v>-0.01248680970805491</v>
       </c>
+      <c r="Y91" s="1" t="n">
+        <v>0.05597</v>
+      </c>
+      <c r="Z91" s="2" t="n">
+        <v>-0.003205699020480848</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7489,6 +8041,12 @@
       <c r="X92" s="3" t="n">
         <v>0.006268154716404208</v>
       </c>
+      <c r="Y92" s="1" t="n">
+        <v>1.3127</v>
+      </c>
+      <c r="Z92" s="2" t="n">
+        <v>-0.002810695837131599</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7565,6 +8123,12 @@
       <c r="X93" s="3" t="n">
         <v>0.001110406091370568</v>
       </c>
+      <c r="Y93" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="Z93" s="3" t="n">
+        <v>0.001426081445095971</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7641,6 +8205,12 @@
       <c r="X94" s="3" t="n">
         <v>0.01362088535754828</v>
       </c>
+      <c r="Y94" s="1" t="n">
+        <v>0.008869999999999999</v>
+      </c>
+      <c r="Z94" s="2" t="n">
+        <v>-0.006718924972004593</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7717,6 +8287,12 @@
       <c r="X95" s="3" t="n">
         <v>0.001201201201201069</v>
       </c>
+      <c r="Y95" s="1" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="Z95" s="2" t="n">
+        <v>-0.0002999400119975675</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7793,6 +8369,12 @@
       <c r="X96" s="2" t="n">
         <v>-0.001769911504424707</v>
       </c>
+      <c r="Y96" s="1" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="Z96" s="2" t="n">
+        <v>-0.002659574468085152</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7869,6 +8451,12 @@
       <c r="X97" s="2" t="n">
         <v>-0.0003065603923972413</v>
       </c>
+      <c r="Y97" s="1" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="Z97" s="2" t="n">
+        <v>-0.000306654400490586</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7945,6 +8533,12 @@
       <c r="X98" s="3" t="n">
         <v>0.002707581227436725</v>
       </c>
+      <c r="Y98" s="1" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="Z98" s="2" t="n">
+        <v>-0.001800180018001802</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8021,6 +8615,12 @@
       <c r="X99" s="3" t="n">
         <v>0.001331557922769642</v>
       </c>
+      <c r="Y99" s="1" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Z99" s="3" t="n">
+        <v>0.0006648936170212034</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8097,6 +8697,12 @@
       <c r="X100" s="3" t="n">
         <v>0.0008756567425569833</v>
       </c>
+      <c r="Y100" s="1" t="n">
+        <v>0.03426</v>
+      </c>
+      <c r="Z100" s="2" t="n">
+        <v>-0.0008748906386702317</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8173,6 +8779,12 @@
       <c r="X101" s="3" t="n">
         <v>0.002748763056624583</v>
       </c>
+      <c r="Y101" s="1" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="Z101" s="2" t="n">
+        <v>-0.001644736842105326</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8249,6 +8861,12 @@
       <c r="X102" s="3" t="n">
         <v>0.01485581124381016</v>
       </c>
+      <c r="Y102" s="1" t="n">
+        <v>0.007048</v>
+      </c>
+      <c r="Z102" s="3" t="n">
+        <v>0.01148105625717557</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8325,6 +8943,12 @@
       <c r="X103" s="3" t="n">
         <v>0.001206454531744995</v>
       </c>
+      <c r="Y103" s="1" t="n">
+        <v>0.06652</v>
+      </c>
+      <c r="Z103" s="3" t="n">
+        <v>0.001958126223828758</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8401,6 +9025,12 @@
       <c r="X104" s="2" t="n">
         <v>-0.0009732360097322529</v>
       </c>
+      <c r="Y104" s="1" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="Z104" s="3" t="n">
+        <v>0.003653190452995619</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8477,6 +9107,12 @@
       <c r="X105" s="3" t="n">
         <v>0.00448430493273543</v>
       </c>
+      <c r="Y105" s="1" t="n">
+        <v>1.791</v>
+      </c>
+      <c r="Z105" s="2" t="n">
+        <v>-0.0005580357142857767</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8553,6 +9189,12 @@
       <c r="X106" s="2" t="n">
         <v>-0.002419842710223737</v>
       </c>
+      <c r="Y106" s="1" t="n">
+        <v>0.008215999999999999</v>
+      </c>
+      <c r="Z106" s="2" t="n">
+        <v>-0.003517283201940721</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8629,6 +9271,12 @@
       <c r="X107" s="2" t="n">
         <v>-0.002201430930104479</v>
       </c>
+      <c r="Y107" s="1" t="n">
+        <v>0.01819</v>
+      </c>
+      <c r="Z107" s="3" t="n">
+        <v>0.003309431880860509</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8705,6 +9353,12 @@
       <c r="X108" s="3" t="n">
         <v>0.002327746741154629</v>
       </c>
+      <c r="Y108" s="1" t="n">
+        <v>0.02149</v>
+      </c>
+      <c r="Z108" s="2" t="n">
+        <v>-0.001857872735717689</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8781,6 +9435,12 @@
       <c r="X109" s="2" t="n">
         <v>-0.0009004141905276685</v>
       </c>
+      <c r="Y109" s="1" t="n">
+        <v>0.05553</v>
+      </c>
+      <c r="Z109" s="3" t="n">
+        <v>0.0009012256669070193</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8857,6 +9517,12 @@
       <c r="X110" s="2" t="n">
         <v>-0.003272758590991347</v>
       </c>
+      <c r="Y110" s="1" t="n">
+        <v>0.11492</v>
+      </c>
+      <c r="Z110" s="2" t="n">
+        <v>-0.006999049511794739</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8933,6 +9599,12 @@
       <c r="X111" s="2" t="n">
         <v>-0.001328835735459523</v>
       </c>
+      <c r="Y111" s="1" t="n">
+        <v>0.09743</v>
+      </c>
+      <c r="Z111" s="2" t="n">
+        <v>-0.002763561924257855</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9009,6 +9681,12 @@
       <c r="X112" s="3" t="n">
         <v>0.005405405405405373</v>
       </c>
+      <c r="Y112" s="1" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="Z112" s="3" t="n">
+        <v>0.00268817204301083</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9085,6 +9763,12 @@
       <c r="X113" s="2" t="n">
         <v>-0.0001020512297172785</v>
       </c>
+      <c r="Y113" s="1" t="n">
+        <v>0.09791999999999999</v>
+      </c>
+      <c r="Z113" s="2" t="n">
+        <v>-0.0006123698714023729</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9161,6 +9845,12 @@
       <c r="X114" s="3" t="n">
         <v>0.01636469900642901</v>
       </c>
+      <c r="Y114" s="1" t="n">
+        <v>0.001737</v>
+      </c>
+      <c r="Z114" s="2" t="n">
+        <v>-0.001150086256469263</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9237,6 +9927,12 @@
       <c r="X115" s="2" t="n">
         <v>-0.002230364823960599</v>
       </c>
+      <c r="Y115" s="1" t="n">
+        <v>1.2523</v>
+      </c>
+      <c r="Z115" s="2" t="n">
+        <v>-0.0002395018361807177</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9313,6 +10009,12 @@
       <c r="X116" s="2" t="n">
         <v>-0.0008456659619449386</v>
       </c>
+      <c r="Y116" s="1" t="n">
+        <v>0.2358</v>
+      </c>
+      <c r="Z116" s="2" t="n">
+        <v>-0.002115954295387221</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9389,6 +10091,12 @@
       <c r="X117" s="3" t="n">
         <v>0.002279387821556403</v>
       </c>
+      <c r="Y117" s="1" t="n">
+        <v>0.06137</v>
+      </c>
+      <c r="Z117" s="2" t="n">
+        <v>-0.003086419753086351</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9465,6 +10173,12 @@
       <c r="X118" s="2" t="n">
         <v>-0.01226993865030672</v>
       </c>
+      <c r="Y118" s="1" t="n">
+        <v>0.04367</v>
+      </c>
+      <c r="Z118" s="3" t="n">
+        <v>0.004600874166091529</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9541,6 +10255,12 @@
       <c r="X119" s="2" t="n">
         <v>-0.006976120203917355</v>
       </c>
+      <c r="Y119" s="1" t="n">
+        <v>0.003729</v>
+      </c>
+      <c r="Z119" s="3" t="n">
+        <v>0.007565522831667184</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9617,6 +10337,12 @@
       <c r="X120" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y120" s="1" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="Z120" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -9693,6 +10419,12 @@
       <c r="X121" s="2" t="n">
         <v>-0.001010781671159105</v>
       </c>
+      <c r="Y121" s="1" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="Z121" s="2" t="n">
+        <v>-0.001011804384485555</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9769,6 +10501,12 @@
       <c r="X122" s="2" t="n">
         <v>-0.002988222886271619</v>
       </c>
+      <c r="Y122" s="1" t="n">
+        <v>0.5673</v>
+      </c>
+      <c r="Z122" s="3" t="n">
+        <v>0.0001763046544428579</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9845,6 +10583,12 @@
       <c r="X123" s="3" t="n">
         <v>0.0008241758241758144</v>
       </c>
+      <c r="Y123" s="1" t="n">
+        <v>0.028897</v>
+      </c>
+      <c r="Z123" s="2" t="n">
+        <v>-0.008475157836947595</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9921,6 +10665,12 @@
       <c r="X124" s="2" t="n">
         <v>-0.003948038716250697</v>
       </c>
+      <c r="Y124" s="1" t="n">
+        <v>0.07842</v>
+      </c>
+      <c r="Z124" s="3" t="n">
+        <v>0.002685078634445747</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9997,6 +10747,12 @@
       <c r="X125" s="3" t="n">
         <v>0.0005806077027288997</v>
       </c>
+      <c r="Y125" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="Z125" s="3" t="n">
+        <v>0.0009671179883944776</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10073,6 +10829,12 @@
       <c r="X126" s="3" t="n">
         <v>0.001121914734480134</v>
       </c>
+      <c r="Y126" s="1" t="n">
+        <v>0.02658</v>
+      </c>
+      <c r="Z126" s="2" t="n">
+        <v>-0.00709749719835634</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10149,6 +10911,12 @@
       <c r="X127" s="3" t="n">
         <v>0.0009119927040583303</v>
       </c>
+      <c r="Y127" s="1" t="n">
+        <v>0.02192</v>
+      </c>
+      <c r="Z127" s="2" t="n">
+        <v>-0.001366742596811036</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10225,6 +10993,12 @@
       <c r="X128" s="2" t="n">
         <v>-0.001236858379715558</v>
       </c>
+      <c r="Y128" s="1" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="Z128" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10301,6 +11075,12 @@
       <c r="X129" s="3" t="n">
         <v>0.01771233461374301</v>
       </c>
+      <c r="Y129" s="1" t="n">
+        <v>0.14347</v>
+      </c>
+      <c r="Z129" s="3" t="n">
+        <v>0.002795834207031409</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10377,6 +11157,12 @@
       <c r="X130" s="3" t="n">
         <v>0.0004519518671262111</v>
       </c>
+      <c r="Y130" s="1" t="n">
+        <v>0.052457</v>
+      </c>
+      <c r="Z130" s="2" t="n">
+        <v>-0.01261128992790867</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10453,6 +11239,12 @@
       <c r="X131" s="2" t="n">
         <v>-0.001099975556098836</v>
       </c>
+      <c r="Y131" s="1" t="n">
+        <v>0.08168</v>
+      </c>
+      <c r="Z131" s="2" t="n">
+        <v>-0.0006117704637219442</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10529,6 +11321,12 @@
       <c r="X132" s="2" t="n">
         <v>-0.001141552511415558</v>
       </c>
+      <c r="Y132" s="1" t="n">
+        <v>0.0876</v>
+      </c>
+      <c r="Z132" s="3" t="n">
+        <v>0.001142857142857176</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10605,6 +11403,12 @@
       <c r="X133" s="2" t="n">
         <v>-0.0008640055296352945</v>
       </c>
+      <c r="Y133" s="1" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="Z133" s="3" t="n">
+        <v>0.002075406433759908</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -10681,6 +11485,12 @@
       <c r="X134" s="2" t="n">
         <v>-0.004672897196261724</v>
       </c>
+      <c r="Y134" s="1" t="n">
+        <v>0.02968</v>
+      </c>
+      <c r="Z134" s="2" t="n">
+        <v>-0.004694835680751099</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10757,6 +11567,12 @@
       <c r="X135" s="3" t="n">
         <v>0.0005685048322910512</v>
       </c>
+      <c r="Y135" s="1" t="n">
+        <v>0.01761</v>
+      </c>
+      <c r="Z135" s="3" t="n">
+        <v>0.000568181818181795</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -10833,6 +11649,12 @@
       <c r="X136" s="2" t="n">
         <v>-0.00402900886381943</v>
       </c>
+      <c r="Y136" s="1" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="Z136" s="3" t="n">
+        <v>0.0005393743257820707</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10909,6 +11731,12 @@
       <c r="X137" s="2" t="n">
         <v>-0.003683241252302003</v>
       </c>
+      <c r="Y137" s="1" t="n">
+        <v>0.02718</v>
+      </c>
+      <c r="Z137" s="3" t="n">
+        <v>0.0048059149722735</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10985,6 +11813,12 @@
       <c r="X138" s="3" t="n">
         <v>0.00238284352660851</v>
       </c>
+      <c r="Y138" s="1" t="n">
+        <v>2.543</v>
+      </c>
+      <c r="Z138" s="3" t="n">
+        <v>0.007527733755942998</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11061,6 +11895,12 @@
       <c r="X139" s="3" t="n">
         <v>0.003381234150464929</v>
       </c>
+      <c r="Y139" s="1" t="n">
+        <v>0.01195</v>
+      </c>
+      <c r="Z139" s="3" t="n">
+        <v>0.006739679865206421</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11137,6 +11977,12 @@
       <c r="X140" s="2" t="n">
         <v>-0.004691689008042821</v>
       </c>
+      <c r="Y140" s="1" t="n">
+        <v>0.01493</v>
+      </c>
+      <c r="Z140" s="3" t="n">
+        <v>0.005387205387205401</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11213,6 +12059,12 @@
       <c r="X141" s="3" t="n">
         <v>0.0007442322004465676</v>
       </c>
+      <c r="Y141" s="1" t="n">
+        <v>16.144</v>
+      </c>
+      <c r="Z141" s="3" t="n">
+        <v>0.0004957858205254784</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11289,6 +12141,12 @@
       <c r="X142" s="3" t="n">
         <v>0.0008006405124100342</v>
       </c>
+      <c r="Y142" s="1" t="n">
+        <v>0.01251</v>
+      </c>
+      <c r="Z142" s="3" t="n">
+        <v>0.0007999999999999674</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11365,6 +12223,12 @@
       <c r="X143" s="2" t="n">
         <v>-0.0007515971439309528</v>
       </c>
+      <c r="Y143" s="1" t="n">
+        <v>0.02684</v>
+      </c>
+      <c r="Z143" s="3" t="n">
+        <v>0.00940203083866116</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -11441,6 +12305,12 @@
       <c r="X144" s="2" t="n">
         <v>-0.005484075089643714</v>
       </c>
+      <c r="Y144" s="1" t="n">
+        <v>0.004698</v>
+      </c>
+      <c r="Z144" s="2" t="n">
+        <v>-0.003605514316012652</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11517,6 +12387,12 @@
       <c r="X145" s="2" t="n">
         <v>-0.00369115639379081</v>
       </c>
+      <c r="Y145" s="1" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z145" s="2" t="n">
+        <v>-0.005278116118554591</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -11593,6 +12469,12 @@
       <c r="X146" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y146" s="1" t="n">
+        <v>0.02314</v>
+      </c>
+      <c r="Z146" s="2" t="n">
+        <v>-0.001294777729822994</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -11669,6 +12551,12 @@
       <c r="X147" s="2" t="n">
         <v>-0.002337749081598441</v>
       </c>
+      <c r="Y147" s="1" t="n">
+        <v>0.09014</v>
+      </c>
+      <c r="Z147" s="3" t="n">
+        <v>0.005802276277616521</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -11745,6 +12633,12 @@
       <c r="X148" s="3" t="n">
         <v>0.01391389752823709</v>
       </c>
+      <c r="Y148" s="1" t="n">
+        <v>0.06168</v>
+      </c>
+      <c r="Z148" s="2" t="n">
+        <v>-0.004197610590894467</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -11821,6 +12715,12 @@
       <c r="X149" s="3" t="n">
         <v>0.0001683785149015501</v>
       </c>
+      <c r="Y149" s="1" t="n">
+        <v>0.05928</v>
+      </c>
+      <c r="Z149" s="2" t="n">
+        <v>-0.002020202020202054</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -11897,6 +12797,12 @@
       <c r="X150" s="2" t="n">
         <v>-0.0002846685644571553</v>
       </c>
+      <c r="Y150" s="1" t="n">
+        <v>0.24397</v>
+      </c>
+      <c r="Z150" s="2" t="n">
+        <v>-0.007566204287515766</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -11973,6 +12879,12 @@
       <c r="X151" s="3" t="n">
         <v>0.002467702133836651</v>
       </c>
+      <c r="Y151" s="1" t="n">
+        <v>6.989e-05</v>
+      </c>
+      <c r="Z151" s="3" t="n">
+        <v>0.01201853460758746</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12049,6 +12961,12 @@
       <c r="X152" s="2" t="n">
         <v>-0.001571268237934981</v>
       </c>
+      <c r="Y152" s="1" t="n">
+        <v>0.4448</v>
+      </c>
+      <c r="Z152" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -12125,6 +13043,12 @@
       <c r="X153" s="3" t="n">
         <v>0.003262642740619905</v>
       </c>
+      <c r="Y153" s="1" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="Z153" s="2" t="n">
+        <v>-0.000975609756097634</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12201,6 +13125,12 @@
       <c r="X154" s="3" t="n">
         <v>0.001657000828500538</v>
       </c>
+      <c r="Y154" s="1" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="Z154" s="3" t="n">
+        <v>0.004962779156327456</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -12277,6 +13207,12 @@
       <c r="X155" s="2" t="n">
         <v>-0.001727115716753072</v>
       </c>
+      <c r="Y155" s="1" t="n">
+        <v>0.2307</v>
+      </c>
+      <c r="Z155" s="2" t="n">
+        <v>-0.002162629757785469</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -12353,6 +13289,12 @@
       <c r="X156" s="3" t="n">
         <v>0.003477396920019902</v>
       </c>
+      <c r="Y156" s="1" t="n">
+        <v>0.08054</v>
+      </c>
+      <c r="Z156" s="2" t="n">
+        <v>-0.003217821782178173</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12429,6 +13371,12 @@
       <c r="X157" s="3" t="n">
         <v>0.005764322802076941</v>
       </c>
+      <c r="Y157" s="1" t="n">
+        <v>0.22903</v>
+      </c>
+      <c r="Z157" s="3" t="n">
+        <v>0.002012512578203683</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -12505,6 +13453,12 @@
       <c r="X158" s="3" t="n">
         <v>0.003585657370517976</v>
       </c>
+      <c r="Y158" s="1" t="n">
+        <v>0.2518</v>
+      </c>
+      <c r="Z158" s="2" t="n">
+        <v>-0.0003969829297339777</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -12581,6 +13535,12 @@
       <c r="X159" s="3" t="n">
         <v>0.0006816632583502998</v>
       </c>
+      <c r="Y159" s="1" t="n">
+        <v>2.938</v>
+      </c>
+      <c r="Z159" s="3" t="n">
+        <v>0.0006811989100818201</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -12657,6 +13617,12 @@
       <c r="X160" s="3" t="n">
         <v>0.001004016064257057</v>
       </c>
+      <c r="Y160" s="1" t="n">
+        <v>0.09950000000000001</v>
+      </c>
+      <c r="Z160" s="2" t="n">
+        <v>-0.002006018054162406</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -12733,6 +13699,12 @@
       <c r="X161" s="3" t="n">
         <v>0.008050211488607004</v>
       </c>
+      <c r="Y161" s="1" t="n">
+        <v>0.14748</v>
+      </c>
+      <c r="Z161" s="2" t="n">
+        <v>-0.001894964807796443</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -12809,6 +13781,12 @@
       <c r="X162" s="2" t="n">
         <v>-0.002438281011886679</v>
       </c>
+      <c r="Y162" s="1" t="n">
+        <v>0.003273</v>
+      </c>
+      <c r="Z162" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -12885,6 +13863,12 @@
       <c r="X163" s="3" t="n">
         <v>0.001202886928628695</v>
       </c>
+      <c r="Y163" s="1" t="n">
+        <v>0.004993</v>
+      </c>
+      <c r="Z163" s="2" t="n">
+        <v>-0.0002002402883460418</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -12961,6 +13945,12 @@
       <c r="X164" s="2" t="n">
         <v>-0.001048218029350135</v>
       </c>
+      <c r="Y164" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="Z164" s="3" t="n">
+        <v>0.003147953830010583</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -13037,6 +14027,12 @@
       <c r="X165" s="2" t="n">
         <v>-0.0055338541666666</v>
       </c>
+      <c r="Y165" s="1" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="Z165" s="2" t="n">
+        <v>-0.0006546644844516464</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -13113,6 +14109,12 @@
       <c r="X166" s="2" t="n">
         <v>-0.002300999496656426</v>
       </c>
+      <c r="Y166" s="1" t="n">
+        <v>1.3865</v>
+      </c>
+      <c r="Z166" s="2" t="n">
+        <v>-0.0007207207207206414</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -13189,6 +14191,12 @@
       <c r="X167" s="3" t="n">
         <v>0.002889129649693113</v>
       </c>
+      <c r="Y167" s="1" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="Z167" s="3" t="n">
+        <v>0.001440403312927661</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -13265,6 +14273,12 @@
       <c r="X168" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y168" s="1" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="Z168" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -13341,6 +14355,12 @@
       <c r="X169" s="2" t="n">
         <v>-0.001675603217158109</v>
       </c>
+      <c r="Y169" s="1" t="n">
+        <v>0.02986</v>
+      </c>
+      <c r="Z169" s="3" t="n">
+        <v>0.00234978180597518</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -13417,6 +14437,12 @@
       <c r="X170" s="2" t="n">
         <v>-0.008031206975676986</v>
       </c>
+      <c r="Y170" s="1" t="n">
+        <v>0.04334</v>
+      </c>
+      <c r="Z170" s="3" t="n">
+        <v>0.002544529262086491</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -13493,6 +14519,12 @@
       <c r="X171" s="3" t="n">
         <v>0.006060606060606023</v>
       </c>
+      <c r="Y171" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="Z171" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -13569,6 +14601,12 @@
       <c r="X172" s="2" t="n">
         <v>-0.007575757575757631</v>
       </c>
+      <c r="Y172" s="1" t="n">
+        <v>1.32e-05</v>
+      </c>
+      <c r="Z172" s="3" t="n">
+        <v>0.007633587786259598</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -13645,6 +14683,12 @@
       <c r="X173" s="2" t="n">
         <v>-0.002369668246445565</v>
       </c>
+      <c r="Y173" s="1" t="n">
+        <v>0.02107</v>
+      </c>
+      <c r="Z173" s="3" t="n">
+        <v>0.000950118764845567</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -13721,6 +14765,12 @@
       <c r="X174" s="3" t="n">
         <v>0.003089143865842922</v>
       </c>
+      <c r="Y174" s="1" t="n">
+        <v>0.09086</v>
+      </c>
+      <c r="Z174" s="2" t="n">
+        <v>-0.0006599208095029091</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -13797,6 +14847,12 @@
       <c r="X175" s="2" t="n">
         <v>-0.0024738867509621</v>
       </c>
+      <c r="Y175" s="1" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="Z175" s="3" t="n">
+        <v>0.0005511160099200275</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -13873,6 +14929,12 @@
       <c r="X176" s="2" t="n">
         <v>-0.001863064741499691</v>
       </c>
+      <c r="Y176" s="1" t="n">
+        <v>0.02138</v>
+      </c>
+      <c r="Z176" s="2" t="n">
+        <v>-0.002333177788147523</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -13949,6 +15011,12 @@
       <c r="X177" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y177" s="1" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="Z177" s="3" t="n">
+        <v>0.00636942675159254</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -14025,6 +15093,12 @@
       <c r="X178" s="2" t="n">
         <v>-0.003115264797507751</v>
       </c>
+      <c r="Y178" s="1" t="n">
+        <v>0.000957</v>
+      </c>
+      <c r="Z178" s="2" t="n">
+        <v>-0.003125000000000076</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -14101,6 +15175,12 @@
       <c r="X179" s="2" t="n">
         <v>-0.005339635854341762</v>
       </c>
+      <c r="Y179" s="1" t="n">
+        <v>0.022725</v>
+      </c>
+      <c r="Z179" s="2" t="n">
+        <v>-4.400246413803573e-05</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -14177,6 +15257,12 @@
       <c r="X180" s="2" t="n">
         <v>-0.0004850836769342177</v>
       </c>
+      <c r="Y180" s="1" t="n">
+        <v>4.116</v>
+      </c>
+      <c r="Z180" s="2" t="n">
+        <v>-0.001213297743266387</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -14253,6 +15339,12 @@
       <c r="X181" s="2" t="n">
         <v>-0.004956417706374812</v>
       </c>
+      <c r="Y181" s="1" t="n">
+        <v>0.5793</v>
+      </c>
+      <c r="Z181" s="2" t="n">
+        <v>-0.004981106149089683</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -14329,6 +15421,12 @@
       <c r="X182" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y182" s="1" t="n">
+        <v>0.05087</v>
+      </c>
+      <c r="Z182" s="3" t="n">
+        <v>0.01334661354581667</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -14405,6 +15503,12 @@
       <c r="X183" s="2" t="n">
         <v>-0.00200656694636996</v>
       </c>
+      <c r="Y183" s="1" t="n">
+        <v>5.458</v>
+      </c>
+      <c r="Z183" s="2" t="n">
+        <v>-0.002376165234874776</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -14481,6 +15585,12 @@
       <c r="X184" s="2" t="n">
         <v>-0.0003478260869565761</v>
       </c>
+      <c r="Y184" s="1" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="Z184" s="3" t="n">
+        <v>0.0045233124565067</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -14557,6 +15667,12 @@
       <c r="X185" s="2" t="n">
         <v>-0.004221635883905024</v>
       </c>
+      <c r="Y185" s="1" t="n">
+        <v>0.01873</v>
+      </c>
+      <c r="Z185" s="2" t="n">
+        <v>-0.00741918388977219</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -14633,6 +15749,12 @@
       <c r="X186" s="2" t="n">
         <v>-0.009554140127388552</v>
       </c>
+      <c r="Y186" s="1" t="n">
+        <v>3.11e-05</v>
+      </c>
+      <c r="Z186" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -14709,6 +15831,12 @@
       <c r="X187" s="2" t="n">
         <v>-0.001255492780916459</v>
       </c>
+      <c r="Y187" s="1" t="n">
+        <v>0.01588</v>
+      </c>
+      <c r="Z187" s="2" t="n">
+        <v>-0.001885606536769469</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -14785,6 +15913,12 @@
       <c r="X188" s="3" t="n">
         <v>0.004208962614508456</v>
       </c>
+      <c r="Y188" s="1" t="n">
+        <v>0.04056</v>
+      </c>
+      <c r="Z188" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -14861,6 +15995,12 @@
       <c r="X189" s="2" t="n">
         <v>-0.0009072352007258103</v>
       </c>
+      <c r="Y189" s="1" t="n">
+        <v>0.0004421</v>
+      </c>
+      <c r="Z189" s="3" t="n">
+        <v>0.003632236095346286</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -14937,6 +16077,12 @@
       <c r="X190" s="2" t="n">
         <v>-0.000852151682999687</v>
       </c>
+      <c r="Y190" s="1" t="n">
+        <v>0.02323</v>
+      </c>
+      <c r="Z190" s="2" t="n">
+        <v>-0.009381663113006311</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -15013,6 +16159,12 @@
       <c r="X191" s="2" t="n">
         <v>-0.001271455816910531</v>
       </c>
+      <c r="Y191" s="1" t="n">
+        <v>0.01576</v>
+      </c>
+      <c r="Z191" s="3" t="n">
+        <v>0.003182686187142039</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -15089,6 +16241,12 @@
       <c r="X192" s="2" t="n">
         <v>-0.00850912958695269</v>
       </c>
+      <c r="Y192" s="1" t="n">
+        <v>0.05607</v>
+      </c>
+      <c r="Z192" s="3" t="n">
+        <v>0.002503128911138946</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -15165,6 +16323,12 @@
       <c r="X193" s="2" t="n">
         <v>-0.002135611318739902</v>
       </c>
+      <c r="Y193" s="1" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="Z193" s="3" t="n">
+        <v>0.0005350454788656447</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -15241,6 +16405,12 @@
       <c r="X194" s="3" t="n">
         <v>0.001041666666666805</v>
       </c>
+      <c r="Y194" s="1" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="Z194" s="3" t="n">
+        <v>0.001560874089490051</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -15317,6 +16487,12 @@
       <c r="X195" s="3" t="n">
         <v>0.001637810014038321</v>
       </c>
+      <c r="Y195" s="1" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="Z195" s="2" t="n">
+        <v>-0.001635131978509644</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -15393,6 +16569,12 @@
       <c r="X196" s="2" t="n">
         <v>-0.004042037186742234</v>
       </c>
+      <c r="Y196" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="Z196" s="2" t="n">
+        <v>-0.001623376623376557</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -15469,6 +16651,12 @@
       <c r="X197" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y197" s="1" t="n">
+        <v>0.04642</v>
+      </c>
+      <c r="Z197" s="3" t="n">
+        <v>0.001078283372870421</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -15545,6 +16733,12 @@
       <c r="X198" s="3" t="n">
         <v>0.009474930911961933</v>
       </c>
+      <c r="Y198" s="1" t="n">
+        <v>0.5117</v>
+      </c>
+      <c r="Z198" s="3" t="n">
+        <v>0.0005866249511147399</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -15621,6 +16815,12 @@
       <c r="X199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y199" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="Z199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -15697,6 +16897,12 @@
       <c r="X200" s="2" t="n">
         <v>-0.004676018704074835</v>
       </c>
+      <c r="Y200" s="1" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="Z200" s="2" t="n">
+        <v>-0.002684563758389324</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -15773,6 +16979,12 @@
       <c r="X201" s="2" t="n">
         <v>-0.005386620330147659</v>
       </c>
+      <c r="Y201" s="1" t="n">
+        <v>0.00573</v>
+      </c>
+      <c r="Z201" s="3" t="n">
+        <v>0.001048218029350093</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -15849,6 +17061,12 @@
       <c r="X202" s="2" t="n">
         <v>-0.004394657475226256</v>
       </c>
+      <c r="Y202" s="1" t="n">
+        <v>0.023033</v>
+      </c>
+      <c r="Z202" s="2" t="n">
+        <v>-0.003245629219317928</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -15925,6 +17143,12 @@
       <c r="X203" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y203" s="1" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="Z203" s="2" t="n">
+        <v>-0.003663003663003768</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -16001,6 +17225,12 @@
       <c r="X204" s="2" t="n">
         <v>-0.005334914048606983</v>
       </c>
+      <c r="Y204" s="1" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="Z204" s="2" t="n">
+        <v>-0.001787842669844981</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -16077,6 +17307,12 @@
       <c r="X205" s="2" t="n">
         <v>-0.009213323883770306</v>
       </c>
+      <c r="Y205" s="1" t="n">
+        <v>4.203</v>
+      </c>
+      <c r="Z205" s="3" t="n">
+        <v>0.002145922746781197</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -16153,6 +17389,12 @@
       <c r="X206" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y206" s="1" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="Z206" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -16229,6 +17471,12 @@
       <c r="X207" s="3" t="n">
         <v>0.02223015802160522</v>
       </c>
+      <c r="Y207" s="1" t="n">
+        <v>0.0011904</v>
+      </c>
+      <c r="Z207" s="3" t="n">
+        <v>0.03965065502183417</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -16305,6 +17553,12 @@
       <c r="X208" s="2" t="n">
         <v>-0.003154141524958802</v>
       </c>
+      <c r="Y208" s="1" t="n">
+        <v>0.007262</v>
+      </c>
+      <c r="Z208" s="2" t="n">
+        <v>-0.000962993534186279</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -16381,6 +17635,12 @@
       <c r="X209" s="2" t="n">
         <v>-0.003344481605351151</v>
       </c>
+      <c r="Y209" s="1" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="Z209" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -16457,6 +17717,12 @@
       <c r="X210" s="3" t="n">
         <v>0.001542020046260432</v>
       </c>
+      <c r="Y210" s="1" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="Z210" s="2" t="n">
+        <v>-0.001539645881447098</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -16533,6 +17799,12 @@
       <c r="X211" s="2" t="n">
         <v>-0.0004211708549768915</v>
       </c>
+      <c r="Y211" s="1" t="n">
+        <v>0.007118</v>
+      </c>
+      <c r="Z211" s="2" t="n">
+        <v>-0.0002808988764044098</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -16609,6 +17881,12 @@
       <c r="X212" s="2" t="n">
         <v>-0.008822531387852023</v>
       </c>
+      <c r="Y212" s="1" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="Z212" s="3" t="n">
+        <v>0.005477576172543616</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -16685,6 +17963,12 @@
       <c r="X213" s="2" t="n">
         <v>-0.01008314169467529</v>
       </c>
+      <c r="Y213" s="1" t="n">
+        <v>0.05613</v>
+      </c>
+      <c r="Z213" s="3" t="n">
+        <v>0.003037884203002082</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -16761,6 +18045,12 @@
       <c r="X214" s="2" t="n">
         <v>-0.002115282919090342</v>
       </c>
+      <c r="Y214" s="1" t="n">
+        <v>0.1882</v>
+      </c>
+      <c r="Z214" s="2" t="n">
+        <v>-0.002649708532061475</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -16837,6 +18127,12 @@
       <c r="X215" s="2" t="n">
         <v>-0.003025146530535081</v>
       </c>
+      <c r="Y215" s="1" t="n">
+        <v>0.05273</v>
+      </c>
+      <c r="Z215" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -16913,6 +18209,12 @@
       <c r="X216" s="2" t="n">
         <v>-0.0009578544061301876</v>
       </c>
+      <c r="Y216" s="1" t="n">
+        <v>0.00208</v>
+      </c>
+      <c r="Z216" s="2" t="n">
+        <v>-0.002876318312560097</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -16989,6 +18291,12 @@
       <c r="X217" s="2" t="n">
         <v>-0.0009988346928582221</v>
       </c>
+      <c r="Y217" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z217" s="2" t="n">
+        <v>-0.0001666388935178027</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -17065,6 +18373,12 @@
       <c r="X218" s="2" t="n">
         <v>-0.002945841830953977</v>
       </c>
+      <c r="Y218" s="1" t="n">
+        <v>4.399</v>
+      </c>
+      <c r="Z218" s="2" t="n">
+        <v>-0.0002272727272728032</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -17141,6 +18455,12 @@
       <c r="X219" s="2" t="n">
         <v>-0.003367003367003327</v>
       </c>
+      <c r="Y219" s="1" t="n">
+        <v>0.005336</v>
+      </c>
+      <c r="Z219" s="3" t="n">
+        <v>0.001501501501501375</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -17217,6 +18537,12 @@
       <c r="X220" s="2" t="n">
         <v>-0.002658931592941721</v>
       </c>
+      <c r="Y220" s="1" t="n">
+        <v>0.04126</v>
+      </c>
+      <c r="Z220" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -17293,6 +18619,12 @@
       <c r="X221" s="2" t="n">
         <v>-0.001567671137432409</v>
       </c>
+      <c r="Y221" s="1" t="n">
+        <v>0.005722</v>
+      </c>
+      <c r="Z221" s="2" t="n">
+        <v>-0.001744591765526947</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -17369,6 +18701,12 @@
       <c r="X222" s="3" t="n">
         <v>0.001101321585902962</v>
       </c>
+      <c r="Y222" s="1" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="Z222" s="2" t="n">
+        <v>-0.002200220022002111</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -17445,6 +18783,12 @@
       <c r="X223" s="2" t="n">
         <v>-0.002387347060579</v>
       </c>
+      <c r="Y223" s="1" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="Z223" s="2" t="n">
+        <v>-0.001495662578522287</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -17521,6 +18865,12 @@
       <c r="X224" s="2" t="n">
         <v>-0.001159285879897984</v>
       </c>
+      <c r="Y224" s="1" t="n">
+        <v>0.4301</v>
+      </c>
+      <c r="Z224" s="2" t="n">
+        <v>-0.001624883936861731</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -17597,6 +18947,12 @@
       <c r="X225" s="2" t="n">
         <v>-0.001433520487397073</v>
       </c>
+      <c r="Y225" s="1" t="n">
+        <v>0.08348</v>
+      </c>
+      <c r="Z225" s="2" t="n">
+        <v>-0.001315946883598504</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -17673,6 +19029,12 @@
       <c r="X226" s="2" t="n">
         <v>-0.002117522498676646</v>
       </c>
+      <c r="Y226" s="1" t="n">
+        <v>0.01884</v>
+      </c>
+      <c r="Z226" s="2" t="n">
+        <v>-0.0005305039787798192</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -17749,6 +19111,12 @@
       <c r="X227" s="2" t="n">
         <v>-0.001711596063328985</v>
       </c>
+      <c r="Y227" s="1" t="n">
+        <v>0.04667</v>
+      </c>
+      <c r="Z227" s="3" t="n">
+        <v>0.0002143163309044805</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -17825,6 +19193,12 @@
       <c r="X228" s="3" t="n">
         <v>0.001731601731601811</v>
       </c>
+      <c r="Y228" s="1" t="n">
+        <v>0.02307</v>
+      </c>
+      <c r="Z228" s="2" t="n">
+        <v>-0.003025064822817658</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -17901,6 +19275,12 @@
       <c r="X229" s="2" t="n">
         <v>-0.002788104089219282</v>
       </c>
+      <c r="Y229" s="1" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="Z229" s="3" t="n">
+        <v>0.002795899347623436</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -17977,6 +19357,12 @@
       <c r="X230" s="2" t="n">
         <v>-0.001207729468599068</v>
       </c>
+      <c r="Y230" s="1" t="n">
+        <v>0.1654</v>
+      </c>
+      <c r="Z230" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -18053,6 +19439,12 @@
       <c r="X231" s="2" t="n">
         <v>-0.001643655489809269</v>
       </c>
+      <c r="Y231" s="1" t="n">
+        <v>0.03033</v>
+      </c>
+      <c r="Z231" s="2" t="n">
+        <v>-0.001317089232795583</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -18129,6 +19521,12 @@
       <c r="X232" s="2" t="n">
         <v>-0.008355321020228637</v>
       </c>
+      <c r="Y232" s="1" t="n">
+        <v>0.02253</v>
+      </c>
+      <c r="Z232" s="2" t="n">
+        <v>-0.0008869179600886556</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -18205,6 +19603,12 @@
       <c r="X233" s="2" t="n">
         <v>-0.01662001399580125</v>
       </c>
+      <c r="Y233" s="1" t="n">
+        <v>0.10158</v>
+      </c>
+      <c r="Z233" s="2" t="n">
+        <v>-0.09642412382138411</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -18281,6 +19685,12 @@
       <c r="X234" s="2" t="n">
         <v>-0.001581652827204474</v>
       </c>
+      <c r="Y234" s="1" t="n">
+        <v>0.2527</v>
+      </c>
+      <c r="Z234" s="3" t="n">
+        <v>0.0007920792079207049</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -18357,6 +19767,12 @@
       <c r="X235" s="2" t="n">
         <v>-0.003608024245922936</v>
       </c>
+      <c r="Y235" s="1" t="n">
+        <v>0.06884</v>
+      </c>
+      <c r="Z235" s="2" t="n">
+        <v>-0.002896871378910859</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -18433,6 +19849,12 @@
       <c r="X236" s="3" t="n">
         <v>0.01352216354616747</v>
       </c>
+      <c r="Y236" s="1" t="n">
+        <v>0.12562</v>
+      </c>
+      <c r="Z236" s="2" t="n">
+        <v>-0.00828925554590665</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -18509,6 +19931,12 @@
       <c r="X237" s="2" t="n">
         <v>-0.008749356664951108</v>
       </c>
+      <c r="Y237" s="1" t="n">
+        <v>0.03862</v>
+      </c>
+      <c r="Z237" s="3" t="n">
+        <v>0.002596053997923231</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -18585,6 +20013,12 @@
       <c r="X238" s="2" t="n">
         <v>-0.008333333333333342</v>
       </c>
+      <c r="Y238" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z238" s="3" t="n">
+        <v>0.008403361344537823</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -18661,6 +20095,12 @@
       <c r="X239" s="3" t="n">
         <v>0.008324924318869839</v>
       </c>
+      <c r="Y239" s="1" t="n">
+        <v>0.003979</v>
+      </c>
+      <c r="Z239" s="2" t="n">
+        <v>-0.004503377533149809</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -18737,6 +20177,12 @@
       <c r="X240" s="2" t="n">
         <v>-0.002189781021897848</v>
       </c>
+      <c r="Y240" s="1" t="n">
+        <v>0.01368</v>
+      </c>
+      <c r="Z240" s="3" t="n">
+        <v>0.0007315288953913382</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -18813,6 +20259,12 @@
       <c r="X241" s="3" t="n">
         <v>0.006376679571851571</v>
       </c>
+      <c r="Y241" s="1" t="n">
+        <v>0.4381</v>
+      </c>
+      <c r="Z241" s="2" t="n">
+        <v>-0.008599230595157333</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -18889,6 +20341,12 @@
       <c r="X242" s="2" t="n">
         <v>-0.002659574468085113</v>
       </c>
+      <c r="Y242" s="1" t="n">
+        <v>0.00755</v>
+      </c>
+      <c r="Z242" s="3" t="n">
+        <v>0.006666666666666743</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -18965,6 +20423,12 @@
       <c r="X243" s="2" t="n">
         <v>-0.000437828371278441</v>
       </c>
+      <c r="Y243" s="1" t="n">
+        <v>0.02298</v>
+      </c>
+      <c r="Z243" s="3" t="n">
+        <v>0.006570302233902796</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -19041,6 +20505,12 @@
       <c r="X244" s="2" t="n">
         <v>-0.004144464179988195</v>
       </c>
+      <c r="Y244" s="1" t="n">
+        <v>0.001666</v>
+      </c>
+      <c r="Z244" s="2" t="n">
+        <v>-0.009512485136741947</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -19117,6 +20587,12 @@
       <c r="X245" s="2" t="n">
         <v>-0.003048780487804965</v>
       </c>
+      <c r="Y245" s="1" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="Z245" s="3" t="n">
+        <v>0.0007645259938837078</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -19193,6 +20669,12 @@
       <c r="X246" s="2" t="n">
         <v>-0.01939924906132674</v>
       </c>
+      <c r="Y246" s="1" t="n">
+        <v>0.03147</v>
+      </c>
+      <c r="Z246" s="3" t="n">
+        <v>0.004148053605615768</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -19269,6 +20751,12 @@
       <c r="X247" s="2" t="n">
         <v>-0.002818489289740701</v>
       </c>
+      <c r="Y247" s="1" t="n">
+        <v>0.1768</v>
+      </c>
+      <c r="Z247" s="2" t="n">
+        <v>-0.0005652911249292763</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -19345,6 +20833,12 @@
       <c r="X248" s="2" t="n">
         <v>-0.006192959582790065</v>
       </c>
+      <c r="Y248" s="1" t="n">
+        <v>0.03068</v>
+      </c>
+      <c r="Z248" s="3" t="n">
+        <v>0.006231551328304336</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -19421,6 +20915,12 @@
       <c r="X249" s="3" t="n">
         <v>0.006618603002009277</v>
       </c>
+      <c r="Y249" s="1" t="n">
+        <v>0.008519000000000001</v>
+      </c>
+      <c r="Z249" s="3" t="n">
+        <v>0.0002348244687096707</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -19497,6 +20997,12 @@
       <c r="X250" s="2" t="n">
         <v>-0.009876543209876654</v>
       </c>
+      <c r="Y250" s="1" t="n">
+        <v>0.02009</v>
+      </c>
+      <c r="Z250" s="3" t="n">
+        <v>0.001995012468828022</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -19573,6 +21079,12 @@
       <c r="X251" s="3" t="n">
         <v>0.001293103448275959</v>
       </c>
+      <c r="Y251" s="1" t="n">
+        <v>0.04652</v>
+      </c>
+      <c r="Z251" s="3" t="n">
+        <v>0.001291433491175152</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -19649,6 +21161,12 @@
       <c r="X252" s="3" t="n">
         <v>0.003770472487333661</v>
       </c>
+      <c r="Y252" s="1" t="n">
+        <v>0.008515</v>
+      </c>
+      <c r="Z252" s="2" t="n">
+        <v>-0.000469538678248683</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -19725,6 +21243,12 @@
       <c r="X253" s="2" t="n">
         <v>-0.004350051177072584</v>
       </c>
+      <c r="Y253" s="1" t="n">
+        <v>0.03865</v>
+      </c>
+      <c r="Z253" s="2" t="n">
+        <v>-0.006682086867129357</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -19801,6 +21325,12 @@
       <c r="X254" s="2" t="n">
         <v>-0.0035685320356854</v>
       </c>
+      <c r="Y254" s="1" t="n">
+        <v>0.06146</v>
+      </c>
+      <c r="Z254" s="3" t="n">
+        <v>0.0004883607357968786</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -19877,6 +21407,12 @@
       <c r="X255" s="2" t="n">
         <v>-0.003102086858432081</v>
       </c>
+      <c r="Y255" s="1" t="n">
+        <v>0.003537</v>
+      </c>
+      <c r="Z255" s="3" t="n">
+        <v>0.0005657708628006409</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -19953,6 +21489,12 @@
       <c r="X256" s="2" t="n">
         <v>-0.003392641737032562</v>
       </c>
+      <c r="Y256" s="1" t="n">
+        <v>0.013187</v>
+      </c>
+      <c r="Z256" s="2" t="n">
+        <v>-0.00242075799984863</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -20029,6 +21571,12 @@
       <c r="X257" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y257" s="1" t="n">
+        <v>0.999425</v>
+      </c>
+      <c r="Z257" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -20105,6 +21653,12 @@
       <c r="X258" s="3" t="n">
         <v>0.002352677571140353</v>
       </c>
+      <c r="Y258" s="1" t="n">
+        <v>0.08918</v>
+      </c>
+      <c r="Z258" s="2" t="n">
+        <v>-0.003241309936291479</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -20181,6 +21735,12 @@
       <c r="X259" s="2" t="n">
         <v>-0.007951203572595669</v>
       </c>
+      <c r="Y259" s="1" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="Z259" s="2" t="n">
+        <v>-0.003074220465524688</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -20257,6 +21817,12 @@
       <c r="X260" s="2" t="n">
         <v>-0.0003657198585883487</v>
       </c>
+      <c r="Y260" s="1" t="n">
+        <v>0.08194</v>
+      </c>
+      <c r="Z260" s="2" t="n">
+        <v>-0.0007317073170732255</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -20333,6 +21899,12 @@
       <c r="X261" s="2" t="n">
         <v>-0.00174064403829417</v>
       </c>
+      <c r="Y261" s="1" t="n">
+        <v>1.141</v>
+      </c>
+      <c r="Z261" s="2" t="n">
+        <v>-0.00523103748910201</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -20409,6 +21981,12 @@
       <c r="X262" s="3" t="n">
         <v>0.009582113388341765</v>
       </c>
+      <c r="Y262" s="1" t="n">
+        <v>0.00389</v>
+      </c>
+      <c r="Z262" s="3" t="n">
+        <v>0.02557342472976532</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -20485,6 +22063,12 @@
       <c r="X263" s="2" t="n">
         <v>-0.01202749140893469</v>
       </c>
+      <c r="Y263" s="1" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="Z263" s="3" t="n">
+        <v>0.001739130434782538</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -20561,6 +22145,12 @@
       <c r="X264" s="2" t="n">
         <v>-0.02918348339025151</v>
       </c>
+      <c r="Y264" s="1" t="n">
+        <v>0.0006142</v>
+      </c>
+      <c r="Z264" s="2" t="n">
+        <v>-0.01790853853533747</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -20637,6 +22227,12 @@
       <c r="X265" s="2" t="n">
         <v>-0.002711864406779551</v>
       </c>
+      <c r="Y265" s="1" t="n">
+        <v>0.01464</v>
+      </c>
+      <c r="Z265" s="2" t="n">
+        <v>-0.00475866757307958</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -20713,6 +22309,12 @@
       <c r="X266" s="2" t="n">
         <v>-0.001572327044025202</v>
       </c>
+      <c r="Y266" s="1" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="Z266" s="2" t="n">
+        <v>-0.001574803149606344</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -20789,6 +22391,12 @@
       <c r="X267" s="2" t="n">
         <v>-0.001231527093596222</v>
       </c>
+      <c r="Y267" s="1" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="Z267" s="3" t="n">
+        <v>0.0006165228113442086</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -20865,6 +22473,12 @@
       <c r="X268" s="2" t="n">
         <v>-0.004630701551285007</v>
       </c>
+      <c r="Y268" s="1" t="n">
+        <v>0.0004332</v>
+      </c>
+      <c r="Z268" s="3" t="n">
+        <v>0.007676203768318274</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -20941,6 +22555,12 @@
       <c r="X269" s="2" t="n">
         <v>-0.0009638554216868749</v>
       </c>
+      <c r="Y269" s="1" t="n">
+        <v>0.02073</v>
+      </c>
+      <c r="Z269" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -21017,6 +22637,12 @@
       <c r="X270" s="2" t="n">
         <v>-0.001660210293303789</v>
       </c>
+      <c r="Y270" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Z270" s="2" t="n">
+        <v>-0.002217294900221793</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -21093,6 +22719,12 @@
       <c r="X271" s="3" t="n">
         <v>0.002721088435374228</v>
       </c>
+      <c r="Y271" s="1" t="n">
+        <v>0.1472</v>
+      </c>
+      <c r="Z271" s="2" t="n">
+        <v>-0.001356852103120799</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -21169,6 +22801,12 @@
       <c r="X272" s="3" t="n">
         <v>0.003548795944233238</v>
       </c>
+      <c r="Y272" s="1" t="n">
+        <v>0.03954</v>
+      </c>
+      <c r="Z272" s="2" t="n">
+        <v>-0.001262945188178869</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -21245,6 +22883,12 @@
       <c r="X273" s="2" t="n">
         <v>-0.001077586206896553</v>
       </c>
+      <c r="Y273" s="1" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="Z273" s="2" t="n">
+        <v>-0.002157497303128373</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -21321,6 +22965,12 @@
       <c r="X274" s="2" t="n">
         <v>-0.001266223488445684</v>
       </c>
+      <c r="Y274" s="1" t="n">
+        <v>63.19</v>
+      </c>
+      <c r="Z274" s="3" t="n">
+        <v>0.001426307448494395</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -21397,6 +23047,12 @@
       <c r="X275" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y275" s="1" t="n">
+        <v>0.01116</v>
+      </c>
+      <c r="Z275" s="2" t="n">
+        <v>-0.01413427561837459</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -21473,6 +23129,12 @@
       <c r="X276" s="3" t="n">
         <v>0.001920860545524354</v>
       </c>
+      <c r="Y276" s="1" t="n">
+        <v>2.602</v>
+      </c>
+      <c r="Z276" s="2" t="n">
+        <v>-0.002300613496932602</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -21549,6 +23211,12 @@
       <c r="X277" s="3" t="n">
         <v>0.00166944908180302</v>
       </c>
+      <c r="Y277" s="1" t="n">
+        <v>0.04195</v>
+      </c>
+      <c r="Z277" s="2" t="n">
+        <v>-0.001190476190476224</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -21625,6 +23293,12 @@
       <c r="X278" s="3" t="n">
         <v>0.01639344262295086</v>
       </c>
+      <c r="Y278" s="1" t="n">
+        <v>0.01969</v>
+      </c>
+      <c r="Z278" s="2" t="n">
+        <v>-0.007560483870967784</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -21701,6 +23375,12 @@
       <c r="X279" s="2" t="n">
         <v>-0.005160142348754516</v>
       </c>
+      <c r="Y279" s="1" t="n">
+        <v>0.005598</v>
+      </c>
+      <c r="Z279" s="3" t="n">
+        <v>0.001252012162403874</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -21777,6 +23457,12 @@
       <c r="X280" s="2" t="n">
         <v>-0.001786169941311575</v>
       </c>
+      <c r="Y280" s="1" t="n">
+        <v>0.03945</v>
+      </c>
+      <c r="Z280" s="3" t="n">
+        <v>0.008435582822085811</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -21853,6 +23539,12 @@
       <c r="X281" s="3" t="n">
         <v>0.001109877913429524</v>
       </c>
+      <c r="Y281" s="1" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="Z281" s="3" t="n">
+        <v>0.002217294900221731</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -21929,6 +23621,12 @@
       <c r="X282" s="3" t="n">
         <v>0.008644109656705435</v>
       </c>
+      <c r="Y282" s="1" t="n">
+        <v>0.0004098</v>
+      </c>
+      <c r="Z282" s="3" t="n">
+        <v>0.003428011753183104</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -22005,6 +23703,12 @@
       <c r="X283" s="3" t="n">
         <v>0.004901960784313695</v>
       </c>
+      <c r="Y283" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="Z283" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -22081,6 +23785,12 @@
       <c r="X284" s="2" t="n">
         <v>-0.0009569377990430233</v>
       </c>
+      <c r="Y284" s="1" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="Z284" s="3" t="n">
+        <v>0.000718390804597755</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -22157,6 +23867,12 @@
       <c r="X285" s="2" t="n">
         <v>-0.000559075661572908</v>
       </c>
+      <c r="Y285" s="1" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="Z285" s="2" t="n">
+        <v>-0.0005593884020137108</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -22233,6 +23949,12 @@
       <c r="X286" s="3" t="n">
         <v>0.002392344497607766</v>
       </c>
+      <c r="Y286" s="1" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="Z286" s="3" t="n">
+        <v>0.002386634844868638</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -22309,6 +24031,12 @@
       <c r="X287" s="3" t="n">
         <v>0.002612330198536988</v>
       </c>
+      <c r="Y287" s="1" t="n">
+        <v>0.15526</v>
+      </c>
+      <c r="Z287" s="3" t="n">
+        <v>0.0113340281396562</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -22385,6 +24113,12 @@
       <c r="X288" s="2" t="n">
         <v>-0.002771618625277164</v>
       </c>
+      <c r="Y288" s="1" t="n">
+        <v>0.1803</v>
+      </c>
+      <c r="Z288" s="3" t="n">
+        <v>0.002223457476375674</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -22461,6 +24195,12 @@
       <c r="X289" s="2" t="n">
         <v>-0.001204529029149577</v>
       </c>
+      <c r="Y289" s="1" t="n">
+        <v>4.149</v>
+      </c>
+      <c r="Z289" s="3" t="n">
+        <v>0.0007235890014472055</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -22537,6 +24277,12 @@
       <c r="X290" s="2" t="n">
         <v>-0.002215226769266593</v>
       </c>
+      <c r="Y290" s="1" t="n">
+        <v>0.08545</v>
+      </c>
+      <c r="Z290" s="2" t="n">
+        <v>-0.001519046506193095</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -22613,6 +24359,12 @@
       <c r="X291" s="2" t="n">
         <v>-0.002812939521800167</v>
       </c>
+      <c r="Y291" s="1" t="n">
+        <v>0.03545</v>
+      </c>
+      <c r="Z291" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -22689,6 +24441,12 @@
       <c r="X292" s="3" t="n">
         <v>0.001360359134811592</v>
       </c>
+      <c r="Y292" s="1" t="n">
+        <v>1.4717</v>
+      </c>
+      <c r="Z292" s="2" t="n">
+        <v>-0.0003396277679662715</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -22765,6 +24523,12 @@
       <c r="X293" s="2" t="n">
         <v>-0.001543474532670267</v>
       </c>
+      <c r="Y293" s="1" t="n">
+        <v>0.005814</v>
+      </c>
+      <c r="Z293" s="2" t="n">
+        <v>-0.001374098248024767</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -22841,6 +24605,12 @@
       <c r="X294" s="3" t="n">
         <v>0.0008741258741258637</v>
       </c>
+      <c r="Y294" s="1" t="n">
+        <v>0.003431</v>
+      </c>
+      <c r="Z294" s="2" t="n">
+        <v>-0.001164483260553158</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -22917,6 +24687,12 @@
       <c r="X295" s="2" t="n">
         <v>-0.002597402597402723</v>
       </c>
+      <c r="Y295" s="1" t="n">
+        <v>0.5363</v>
+      </c>
+      <c r="Z295" s="2" t="n">
+        <v>-0.002418154761904702</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -22993,6 +24769,12 @@
       <c r="X296" s="2" t="n">
         <v>-0.003112494441974263</v>
       </c>
+      <c r="Y296" s="1" t="n">
+        <v>2.241</v>
+      </c>
+      <c r="Z296" s="2" t="n">
+        <v>-0.0004460303300623952</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -23069,6 +24851,12 @@
       <c r="X297" s="3" t="n">
         <v>0.0005924170616113503</v>
       </c>
+      <c r="Y297" s="1" t="n">
+        <v>0.01684</v>
+      </c>
+      <c r="Z297" s="2" t="n">
+        <v>-0.002960331557134278</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -23145,6 +24933,12 @@
       <c r="X298" s="3" t="n">
         <v>0.01918265221017504</v>
       </c>
+      <c r="Y298" s="1" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="Z298" s="2" t="n">
+        <v>-0.007364975450081779</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -23221,6 +25015,12 @@
       <c r="X299" s="3" t="n">
         <v>0.0009025270758122376</v>
       </c>
+      <c r="Y299" s="1" t="n">
+        <v>0.01109</v>
+      </c>
+      <c r="Z299" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -23297,6 +25097,12 @@
       <c r="X300" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y300" s="1" t="n">
+        <v>0.02065</v>
+      </c>
+      <c r="Z300" s="3" t="n">
+        <v>0.0004844961240311561</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -23373,6 +25179,12 @@
       <c r="X301" s="2" t="n">
         <v>-0.001950585175552632</v>
       </c>
+      <c r="Y301" s="1" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="Z301" s="2" t="n">
+        <v>-0.001628664495114008</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -23449,6 +25261,12 @@
       <c r="X302" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y302" s="1" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="Z302" s="3" t="n">
+        <v>0.004366812227074184</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -23525,6 +25343,12 @@
       <c r="X303" s="3" t="n">
         <v>0.001082251082251038</v>
       </c>
+      <c r="Y303" s="1" t="n">
+        <v>0.07391</v>
+      </c>
+      <c r="Z303" s="2" t="n">
+        <v>-0.00121621621621612</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -23601,6 +25425,12 @@
       <c r="X304" s="2" t="n">
         <v>-0.0006297229219143321</v>
       </c>
+      <c r="Y304" s="1" t="n">
+        <v>0.01588</v>
+      </c>
+      <c r="Z304" s="3" t="n">
+        <v>0.0006301197227472964</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -23677,6 +25507,12 @@
       <c r="X305" s="2" t="n">
         <v>-0.003100775193798538</v>
       </c>
+      <c r="Y305" s="1" t="n">
+        <v>0.06424000000000001</v>
+      </c>
+      <c r="Z305" s="2" t="n">
+        <v>-0.0009331259720060749</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -23753,6 +25589,12 @@
       <c r="X306" s="2" t="n">
         <v>-0.0008035355564483402</v>
       </c>
+      <c r="Y306" s="1" t="n">
+        <v>0.04953</v>
+      </c>
+      <c r="Z306" s="2" t="n">
+        <v>-0.004221954161640568</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -23829,6 +25671,12 @@
       <c r="X307" s="2" t="n">
         <v>-0.001088139281828075</v>
       </c>
+      <c r="Y307" s="1" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="Z307" s="3" t="n">
+        <v>0.002178649237472769</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -23905,6 +25753,12 @@
       <c r="X308" s="2" t="n">
         <v>-0.0002514458134272834</v>
       </c>
+      <c r="Y308" s="1" t="n">
+        <v>0.03987</v>
+      </c>
+      <c r="Z308" s="3" t="n">
+        <v>0.002766599597585662</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -23981,6 +25835,12 @@
       <c r="X309" s="2" t="n">
         <v>-0.005750798722044826</v>
       </c>
+      <c r="Y309" s="1" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="Z309" s="3" t="n">
+        <v>0.003856041131105464</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -24057,6 +25917,12 @@
       <c r="X310" s="2" t="n">
         <v>-0.0009206407659730159</v>
       </c>
+      <c r="Y310" s="1" t="n">
+        <v>0.05418</v>
+      </c>
+      <c r="Z310" s="2" t="n">
+        <v>-0.001474382602285361</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -24133,6 +25999,12 @@
       <c r="X311" s="3" t="n">
         <v>0.004485310607759599</v>
       </c>
+      <c r="Y311" s="1" t="n">
+        <v>0.00447</v>
+      </c>
+      <c r="Z311" s="2" t="n">
+        <v>-0.002009377093101211</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -24209,6 +26081,12 @@
       <c r="X312" s="3" t="n">
         <v>0.0002362669816892173</v>
       </c>
+      <c r="Y312" s="1" t="n">
+        <v>0.08466</v>
+      </c>
+      <c r="Z312" s="2" t="n">
+        <v>-0.0001181055863941907</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -24285,6 +26163,12 @@
       <c r="X313" s="2" t="n">
         <v>-0.001869158878504689</v>
       </c>
+      <c r="Y313" s="1" t="n">
+        <v>0.07481</v>
+      </c>
+      <c r="Z313" s="3" t="n">
+        <v>0.0006688068485822416</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -24361,6 +26245,12 @@
       <c r="X314" s="2" t="n">
         <v>-0.001304631441617599</v>
       </c>
+      <c r="Y314" s="1" t="n">
+        <v>0.1533</v>
+      </c>
+      <c r="Z314" s="3" t="n">
+        <v>0.001306335728282025</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -24437,6 +26327,12 @@
       <c r="X315" s="2" t="n">
         <v>-0.001874999999999967</v>
       </c>
+      <c r="Y315" s="1" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="Z315" s="2" t="n">
+        <v>-0.0006261740763933421</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -24513,6 +26409,12 @@
       <c r="X316" s="2" t="n">
         <v>-0.002751788662630712</v>
       </c>
+      <c r="Y316" s="1" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="Z316" s="2" t="n">
+        <v>-0.00110375275938193</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -24589,6 +26491,12 @@
       <c r="X317" s="2" t="n">
         <v>-0.000267058352250002</v>
       </c>
+      <c r="Y317" s="1" t="n">
+        <v>0.007493</v>
+      </c>
+      <c r="Z317" s="3" t="n">
+        <v>0.0008013890743956096</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -24665,6 +26573,12 @@
       <c r="X318" s="3" t="n">
         <v>0.002590157401872847</v>
       </c>
+      <c r="Y318" s="1" t="n">
+        <v>0.05007</v>
+      </c>
+      <c r="Z318" s="2" t="n">
+        <v>-0.004968203497615129</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -24741,6 +26655,12 @@
       <c r="X319" s="3" t="n">
         <v>0.0007198128486594691</v>
       </c>
+      <c r="Y319" s="1" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="Z319" s="3" t="n">
+        <v>0.002301744290595123</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -24817,6 +26737,12 @@
       <c r="X320" s="2" t="n">
         <v>-0.0004542357483534714</v>
       </c>
+      <c r="Y320" s="1" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Z320" s="2" t="n">
+        <v>-0.0002272210861167666</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -24893,6 +26819,12 @@
       <c r="X321" s="2" t="n">
         <v>-0.001286339078981256</v>
       </c>
+      <c r="Y321" s="1" t="n">
+        <v>0.07775</v>
+      </c>
+      <c r="Z321" s="3" t="n">
+        <v>0.001416795466254495</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -24969,6 +26901,12 @@
       <c r="X322" s="3" t="n">
         <v>0.001223241590214102</v>
       </c>
+      <c r="Y322" s="1" t="n">
+        <v>0.1633</v>
+      </c>
+      <c r="Z322" s="2" t="n">
+        <v>-0.002443494196701353</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -25045,6 +26983,12 @@
       <c r="X323" s="2" t="n">
         <v>-0.002521432173474592</v>
       </c>
+      <c r="Y323" s="1" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="Z323" s="2" t="n">
+        <v>-0.001516683518705709</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -25121,6 +27065,12 @@
       <c r="X324" s="2" t="n">
         <v>-0.001856749001294003</v>
       </c>
+      <c r="Y324" s="1" t="n">
+        <v>0.05311</v>
+      </c>
+      <c r="Z324" s="2" t="n">
+        <v>-0.002066892145809957</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -25197,6 +27147,12 @@
       <c r="X325" s="2" t="n">
         <v>-6.504488096775234e-05</v>
       </c>
+      <c r="Y325" s="1" t="n">
+        <v>0.15309</v>
+      </c>
+      <c r="Z325" s="2" t="n">
+        <v>-0.004163143173095698</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -25273,6 +27229,12 @@
       <c r="X326" s="3" t="n">
         <v>0.0001548706829797325</v>
       </c>
+      <c r="Y326" s="1" t="n">
+        <v>0.006472</v>
+      </c>
+      <c r="Z326" s="3" t="n">
+        <v>0.002167853824713553</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -25349,6 +27311,12 @@
       <c r="X327" s="2" t="n">
         <v>-0.0007894217485691638</v>
       </c>
+      <c r="Y327" s="1" t="n">
+        <v>0.015168</v>
+      </c>
+      <c r="Z327" s="2" t="n">
+        <v>-0.001382579498321166</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -25425,6 +27393,12 @@
       <c r="X328" s="2" t="n">
         <v>-0.001044932079414723</v>
       </c>
+      <c r="Y328" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="Z328" s="3" t="n">
+        <v>0.004184100418410016</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -25501,6 +27475,12 @@
       <c r="X329" s="2" t="n">
         <v>-0.002040353661301366</v>
       </c>
+      <c r="Y329" s="1" t="n">
+        <v>0.004401</v>
+      </c>
+      <c r="Z329" s="2" t="n">
+        <v>-0.000227169468423277</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -25577,6 +27557,12 @@
       <c r="X330" s="3" t="n">
         <v>0.0003877471888328652</v>
       </c>
+      <c r="Y330" s="1" t="n">
+        <v>0.05165</v>
+      </c>
+      <c r="Z330" s="3" t="n">
+        <v>0.0009689922480620432</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -25653,6 +27639,12 @@
       <c r="X331" s="2" t="n">
         <v>-0.005783530707794047</v>
       </c>
+      <c r="Y331" s="1" t="n">
+        <v>0.03591</v>
+      </c>
+      <c r="Z331" s="2" t="n">
+        <v>-0.005263157894736916</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -25729,6 +27721,12 @@
       <c r="X332" s="2" t="n">
         <v>-0.001358695652173952</v>
       </c>
+      <c r="Y332" s="1" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="Z332" s="2" t="n">
+        <v>-0.00340136054421769</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -25805,6 +27803,12 @@
       <c r="X333" s="2" t="n">
         <v>-0.00310559006211189</v>
       </c>
+      <c r="Y333" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="Z333" s="2" t="n">
+        <v>-0.004153686396677026</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -25881,6 +27885,12 @@
       <c r="X334" s="2" t="n">
         <v>-0.001588382119355585</v>
       </c>
+      <c r="Y334" s="1" t="n">
+        <v>0.04402</v>
+      </c>
+      <c r="Z334" s="3" t="n">
+        <v>0.0004545454545454361</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -25957,6 +27967,12 @@
       <c r="X335" s="3" t="n">
         <v>0.008733087330873338</v>
       </c>
+      <c r="Y335" s="1" t="n">
+        <v>0.08183</v>
+      </c>
+      <c r="Z335" s="2" t="n">
+        <v>-0.002194854286062671</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -26033,6 +28049,12 @@
       <c r="X336" s="2" t="n">
         <v>-0.0004882812500000817</v>
       </c>
+      <c r="Y336" s="1" t="n">
+        <v>0.2047</v>
+      </c>
+      <c r="Z336" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -26109,6 +28131,12 @@
       <c r="X337" s="2" t="n">
         <v>-0.002946954813359579</v>
       </c>
+      <c r="Y337" s="1" t="n">
+        <v>0.01013</v>
+      </c>
+      <c r="Z337" s="2" t="n">
+        <v>-0.001970443349753615</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -26185,6 +28213,12 @@
       <c r="X338" s="2" t="n">
         <v>-0.0008849557522124147</v>
       </c>
+      <c r="Y338" s="1" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="Z338" s="3" t="n">
+        <v>0.002657218777679315</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -26261,6 +28295,12 @@
       <c r="X339" s="2" t="n">
         <v>-0.0005449591280655619</v>
       </c>
+      <c r="Y339" s="1" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="Z339" s="2" t="n">
+        <v>-0.002181025081788352</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -26337,6 +28377,12 @@
       <c r="X340" s="2" t="n">
         <v>-0.001892491902318377</v>
       </c>
+      <c r="Y340" s="1" t="n">
+        <v>0.27611</v>
+      </c>
+      <c r="Z340" s="3" t="n">
+        <v>0.006782133090246229</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -26413,6 +28459,12 @@
       <c r="X341" s="2" t="n">
         <v>-0.003494060097833783</v>
       </c>
+      <c r="Y341" s="1" t="n">
+        <v>0.04284</v>
+      </c>
+      <c r="Z341" s="3" t="n">
+        <v>0.001402524544179628</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -26489,6 +28541,12 @@
       <c r="X342" s="2" t="n">
         <v>-0.00544111931597344</v>
       </c>
+      <c r="Y342" s="1" t="n">
+        <v>0.07718</v>
+      </c>
+      <c r="Z342" s="3" t="n">
+        <v>0.005340627849420264</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -26565,6 +28623,12 @@
       <c r="X343" s="2" t="n">
         <v>-0.002868318122555442</v>
       </c>
+      <c r="Y343" s="1" t="n">
+        <v>7.635</v>
+      </c>
+      <c r="Z343" s="2" t="n">
+        <v>-0.001699790794979067</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -26641,6 +28705,12 @@
       <c r="X344" s="2" t="n">
         <v>-0.0008333333333332416</v>
       </c>
+      <c r="Y344" s="1" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="Z344" s="2" t="n">
+        <v>-0.002502085070892505</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -26717,6 +28787,12 @@
       <c r="X345" s="3" t="n">
         <v>0.00107238605898119</v>
       </c>
+      <c r="Y345" s="1" t="n">
+        <v>0.03735</v>
+      </c>
+      <c r="Z345" s="3" t="n">
+        <v>0.0002678093197644098</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -26793,6 +28869,12 @@
       <c r="X346" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y346" s="1" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="Z346" s="3" t="n">
+        <v>0.002403846153846223</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -26869,6 +28951,12 @@
       <c r="X347" s="3" t="n">
         <v>0.001144819690898716</v>
       </c>
+      <c r="Y347" s="1" t="n">
+        <v>0.1743</v>
+      </c>
+      <c r="Z347" s="2" t="n">
+        <v>-0.003430531732418465</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -26945,6 +29033,12 @@
       <c r="X348" s="2" t="n">
         <v>-0.0002504961751161304</v>
       </c>
+      <c r="Y348" s="1" t="n">
+        <v>5187.1</v>
+      </c>
+      <c r="Z348" s="2" t="n">
+        <v>-0.0002505589391718588</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -27021,6 +29115,12 @@
       <c r="X349" s="2" t="n">
         <v>-0.0007199424046076021</v>
       </c>
+      <c r="Y349" s="1" t="n">
+        <v>0.01367</v>
+      </c>
+      <c r="Z349" s="2" t="n">
+        <v>-0.01512968299711816</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -27097,6 +29197,12 @@
       <c r="X350" s="3" t="n">
         <v>0.01572739187418091</v>
       </c>
+      <c r="Y350" s="1" t="n">
+        <v>0.01536</v>
+      </c>
+      <c r="Z350" s="2" t="n">
+        <v>-0.009032258064516097</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -27173,6 +29279,12 @@
       <c r="X351" s="3" t="n">
         <v>0.001150937191713191</v>
       </c>
+      <c r="Y351" s="1" t="n">
+        <v>0.0006112</v>
+      </c>
+      <c r="Z351" s="3" t="n">
+        <v>0.003777303333880771</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -27249,6 +29361,12 @@
       <c r="X352" s="2" t="n">
         <v>-0.006054490413723614</v>
       </c>
+      <c r="Y352" s="1" t="n">
+        <v>0.01979</v>
+      </c>
+      <c r="Z352" s="3" t="n">
+        <v>0.004568527918781716</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -27325,6 +29443,12 @@
       <c r="X353" s="3" t="n">
         <v>0.003220957698088841</v>
       </c>
+      <c r="Y353" s="1" t="n">
+        <v>0.09356</v>
+      </c>
+      <c r="Z353" s="3" t="n">
+        <v>0.001284246575342562</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -27401,6 +29525,12 @@
       <c r="X354" s="2" t="n">
         <v>-0.004415011037527567</v>
       </c>
+      <c r="Y354" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="Z354" s="2" t="n">
+        <v>-0.001108647450110896</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -27477,6 +29607,12 @@
       <c r="X355" s="2" t="n">
         <v>-0.01156710505466648</v>
       </c>
+      <c r="Y355" s="1" t="n">
+        <v>0.0006163</v>
+      </c>
+      <c r="Z355" s="2" t="n">
+        <v>-0.01202308432189808</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -27553,6 +29689,12 @@
       <c r="X356" s="3" t="n">
         <v>0.002951303492375911</v>
       </c>
+      <c r="Y356" s="1" t="n">
+        <v>2.034</v>
+      </c>
+      <c r="Z356" s="2" t="n">
+        <v>-0.002452182442373878</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -27629,6 +29771,12 @@
       <c r="X357" s="3" t="n">
         <v>0.006134969325153428</v>
       </c>
+      <c r="Y357" s="1" t="n">
+        <v>0.02298</v>
+      </c>
+      <c r="Z357" s="3" t="n">
+        <v>0.0008710801393727867</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -27705,6 +29853,12 @@
       <c r="X358" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y358" s="1" t="n">
+        <v>0.000405</v>
+      </c>
+      <c r="Z358" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -27781,6 +29935,12 @@
       <c r="X359" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y359" s="1" t="n">
+        <v>0.01465</v>
+      </c>
+      <c r="Z359" s="2" t="n">
+        <v>-0.002722940776038128</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -27857,6 +30017,12 @@
       <c r="X360" s="2" t="n">
         <v>-0.00120120120120123</v>
       </c>
+      <c r="Y360" s="1" t="n">
+        <v>0.003325</v>
+      </c>
+      <c r="Z360" s="2" t="n">
+        <v>-0.0003006614552014831</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -27933,6 +30099,12 @@
       <c r="X361" s="2" t="n">
         <v>-0.004044174832788998</v>
       </c>
+      <c r="Y361" s="1" t="n">
+        <v>0.6381</v>
+      </c>
+      <c r="Z361" s="2" t="n">
+        <v>-0.003435889426831141</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -28009,6 +30181,12 @@
       <c r="X362" s="3" t="n">
         <v>0.002134927412468037</v>
       </c>
+      <c r="Y362" s="1" t="n">
+        <v>0.02349</v>
+      </c>
+      <c r="Z362" s="3" t="n">
+        <v>0.0008521516829995392</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -28085,6 +30263,12 @@
       <c r="X363" s="2" t="n">
         <v>-0.001988984088127373</v>
       </c>
+      <c r="Y363" s="1" t="n">
+        <v>0.06512999999999999</v>
+      </c>
+      <c r="Z363" s="2" t="n">
+        <v>-0.001533036946190447</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -28161,6 +30345,12 @@
       <c r="X364" s="3" t="n">
         <v>0.0008501594048883229</v>
       </c>
+      <c r="Y364" s="1" t="n">
+        <v>4.701</v>
+      </c>
+      <c r="Z364" s="2" t="n">
+        <v>-0.001698874495646636</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -28237,6 +30427,12 @@
       <c r="X365" s="3" t="n">
         <v>0.002508710801393723</v>
       </c>
+      <c r="Y365" s="1" t="n">
+        <v>0.07195</v>
+      </c>
+      <c r="Z365" s="3" t="n">
+        <v>0.0002780481023217868</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -28313,6 +30509,12 @@
       <c r="X366" s="2" t="n">
         <v>-0.001424247819120469</v>
       </c>
+      <c r="Y366" s="1" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="Z366" s="3" t="n">
+        <v>0.0001782848992689628</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -28389,6 +30591,12 @@
       <c r="X367" s="2" t="n">
         <v>-0.001878094587672853</v>
       </c>
+      <c r="Y367" s="1" t="n">
+        <v>0.05839</v>
+      </c>
+      <c r="Z367" s="2" t="n">
+        <v>-0.001197399931577157</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -28465,6 +30673,12 @@
       <c r="X368" s="2" t="n">
         <v>-0.0005233775296580992</v>
       </c>
+      <c r="Y368" s="1" t="n">
+        <v>0.05734</v>
+      </c>
+      <c r="Z368" s="3" t="n">
+        <v>0.0008727526618956437</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -28541,6 +30755,12 @@
       <c r="X369" s="2" t="n">
         <v>-0.0009668063164678949</v>
       </c>
+      <c r="Y369" s="1" t="n">
+        <v>0.03099</v>
+      </c>
+      <c r="Z369" s="2" t="n">
+        <v>-0.0003225806451612772</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -28617,6 +30837,12 @@
       <c r="X370" s="2" t="n">
         <v>-0.001230769230769261</v>
       </c>
+      <c r="Y370" s="1" t="n">
+        <v>0.000162</v>
+      </c>
+      <c r="Z370" s="2" t="n">
+        <v>-0.001848428835489712</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -28693,6 +30919,12 @@
       <c r="X371" s="2" t="n">
         <v>-0.001024440216595941</v>
       </c>
+      <c r="Y371" s="1" t="n">
+        <v>0.006814</v>
+      </c>
+      <c r="Z371" s="2" t="n">
+        <v>-0.001757984178142376</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -28769,6 +31001,12 @@
       <c r="X372" s="2" t="n">
         <v>-0.00569962952408095</v>
       </c>
+      <c r="Y372" s="1" t="n">
+        <v>0.00696</v>
+      </c>
+      <c r="Z372" s="2" t="n">
+        <v>-0.002579535683576926</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -28845,6 +31083,12 @@
       <c r="X373" s="3" t="n">
         <v>0.001320306311064139</v>
       </c>
+      <c r="Y373" s="1" t="n">
+        <v>3.793</v>
+      </c>
+      <c r="Z373" s="3" t="n">
+        <v>0.0002637130801688644</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -28921,6 +31165,12 @@
       <c r="X374" s="2" t="n">
         <v>-0.003544590954203888</v>
       </c>
+      <c r="Y374" s="1" t="n">
+        <v>0.07029000000000001</v>
+      </c>
+      <c r="Z374" s="3" t="n">
+        <v>0.0001422879908937109</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -28997,6 +31247,12 @@
       <c r="X375" s="2" t="n">
         <v>-0.006538413177417409</v>
       </c>
+      <c r="Y375" s="1" t="n">
+        <v>0.07948</v>
+      </c>
+      <c r="Z375" s="3" t="n">
+        <v>0.005948614099481056</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -29073,6 +31329,12 @@
       <c r="X376" s="2" t="n">
         <v>-0.001432208784213763</v>
       </c>
+      <c r="Y376" s="1" t="n">
+        <v>0.06279999999999999</v>
+      </c>
+      <c r="Z376" s="3" t="n">
+        <v>0.0007968127490038963</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -29149,6 +31411,12 @@
       <c r="X377" s="2" t="n">
         <v>-0.0001305653479567829</v>
       </c>
+      <c r="Y377" s="1" t="n">
+        <v>0.07643</v>
+      </c>
+      <c r="Z377" s="2" t="n">
+        <v>-0.001958735962392235</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -29225,6 +31493,12 @@
       <c r="X378" s="2" t="n">
         <v>-0.003227408142998951</v>
       </c>
+      <c r="Y378" s="1" t="n">
+        <v>0.0004066</v>
+      </c>
+      <c r="Z378" s="3" t="n">
+        <v>0.0127023661270237</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -29301,6 +31575,12 @@
       <c r="X379" s="2" t="n">
         <v>-0.003493215101437543</v>
       </c>
+      <c r="Y379" s="1" t="n">
+        <v>0.07403999999999999</v>
+      </c>
+      <c r="Z379" s="2" t="n">
+        <v>-0.001752730214372457</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -29377,6 +31657,12 @@
       <c r="X380" s="2" t="n">
         <v>-0.0007309941520468806</v>
       </c>
+      <c r="Y380" s="1" t="n">
+        <v>0.001365</v>
+      </c>
+      <c r="Z380" s="2" t="n">
+        <v>-0.001463057790782772</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -29453,6 +31739,12 @@
       <c r="X381" s="2" t="n">
         <v>-0.001405371642723351</v>
       </c>
+      <c r="Y381" s="1" t="n">
+        <v>6.374</v>
+      </c>
+      <c r="Z381" s="2" t="n">
+        <v>-0.003283815480844395</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -29529,6 +31821,12 @@
       <c r="X382" s="3" t="n">
         <v>0.01455604075691403</v>
       </c>
+      <c r="Y382" s="1" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="Z382" s="2" t="n">
+        <v>-0.00358680057388807</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -29605,6 +31903,12 @@
       <c r="X383" s="3" t="n">
         <v>0.001706484641638353</v>
       </c>
+      <c r="Y383" s="1" t="n">
+        <v>0.01755</v>
+      </c>
+      <c r="Z383" s="2" t="n">
+        <v>-0.003407155025553721</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -29681,6 +31985,12 @@
       <c r="X384" s="2" t="n">
         <v>-0.0009832841691249053</v>
       </c>
+      <c r="Y384" s="1" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="Z384" s="2" t="n">
+        <v>-0.003937007874015725</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -29757,6 +32067,12 @@
       <c r="X385" s="3" t="n">
         <v>0.000222816399286864</v>
       </c>
+      <c r="Y385" s="1" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="Z385" s="3" t="n">
+        <v>0.0002227667631990051</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -29833,6 +32149,12 @@
       <c r="X386" s="3" t="n">
         <v>0.02031249999999998</v>
       </c>
+      <c r="Y386" s="1" t="n">
+        <v>0.001306</v>
+      </c>
+      <c r="Z386" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -29909,6 +32231,12 @@
       <c r="X387" s="3" t="n">
         <v>0.0008418925745076047</v>
       </c>
+      <c r="Y387" s="1" t="n">
+        <v>0.0005923</v>
+      </c>
+      <c r="Z387" s="2" t="n">
+        <v>-0.003532974427994611</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -29985,6 +32313,12 @@
       <c r="X388" s="3" t="n">
         <v>0.0008748906386702824</v>
       </c>
+      <c r="Y388" s="1" t="n">
+        <v>0.01148</v>
+      </c>
+      <c r="Z388" s="3" t="n">
+        <v>0.003496503496503506</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -30061,6 +32395,12 @@
       <c r="X389" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y389" s="1" t="n">
+        <v>0.00903</v>
+      </c>
+      <c r="Z389" s="2" t="n">
+        <v>-0.002209944751381317</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -30137,6 +32477,12 @@
       <c r="X390" s="2" t="n">
         <v>-0.00215026562104735</v>
       </c>
+      <c r="Y390" s="1" t="n">
+        <v>0.07871</v>
+      </c>
+      <c r="Z390" s="2" t="n">
+        <v>-0.002281658004816829</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -30213,6 +32559,12 @@
       <c r="X391" s="3" t="n">
         <v>0.0001940617116243559</v>
       </c>
+      <c r="Y391" s="1" t="n">
+        <v>0.05162</v>
+      </c>
+      <c r="Z391" s="3" t="n">
+        <v>0.001552192471866448</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -30289,6 +32641,12 @@
       <c r="X392" s="3" t="n">
         <v>0.004237288135593232</v>
       </c>
+      <c r="Y392" s="1" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="Z392" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -30365,6 +32723,12 @@
       <c r="X393" s="2" t="n">
         <v>-0.0004675081813931553</v>
       </c>
+      <c r="Y393" s="1" t="n">
+        <v>0.02131</v>
+      </c>
+      <c r="Z393" s="2" t="n">
+        <v>-0.003274087932647363</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -30441,6 +32805,12 @@
       <c r="X394" s="2" t="n">
         <v>-0.002936857562408307</v>
       </c>
+      <c r="Y394" s="1" t="n">
+        <v>0.2034</v>
+      </c>
+      <c r="Z394" s="2" t="n">
+        <v>-0.001472754050073612</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -30517,6 +32887,12 @@
       <c r="X395" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y395" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="Z395" s="2" t="n">
+        <v>-0.001027749229188108</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -30593,6 +32969,12 @@
       <c r="X396" s="3" t="n">
         <v>0.001099706744867914</v>
       </c>
+      <c r="Y396" s="1" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Z396" s="2" t="n">
+        <v>-0.0003661662394726803</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -30669,6 +33051,12 @@
       <c r="X397" s="2" t="n">
         <v>-0.007905138339920957</v>
       </c>
+      <c r="Y397" s="1" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="Z397" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -30745,6 +33133,12 @@
       <c r="X398" s="2" t="n">
         <v>-0.003255120032551279</v>
       </c>
+      <c r="Y398" s="1" t="n">
+        <v>0.007339</v>
+      </c>
+      <c r="Z398" s="2" t="n">
+        <v>-0.001360729350932044</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -30821,6 +33215,12 @@
       <c r="X399" s="3" t="n">
         <v>0.0007716049382717341</v>
       </c>
+      <c r="Y399" s="1" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="Z399" s="2" t="n">
+        <v>-0.001927525057825753</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -30897,6 +33297,12 @@
       <c r="X400" s="2" t="n">
         <v>-0.001254705144290954</v>
       </c>
+      <c r="Y400" s="1" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="Z400" s="2" t="n">
+        <v>-0.002198492462311664</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -30973,6 +33379,12 @@
       <c r="X401" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y401" s="1" t="n">
+        <v>0.007216</v>
+      </c>
+      <c r="Z401" s="2" t="n">
+        <v>-0.001522070015220662</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -31049,6 +33461,12 @@
       <c r="X402" s="2" t="n">
         <v>-0.006709956709956662</v>
       </c>
+      <c r="Y402" s="1" t="n">
+        <v>0.004581</v>
+      </c>
+      <c r="Z402" s="2" t="n">
+        <v>-0.001743299193724165</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -31125,6 +33543,12 @@
       <c r="X403" s="2" t="n">
         <v>-0.002635542168674618</v>
       </c>
+      <c r="Y403" s="1" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="Z403" s="3" t="n">
+        <v>0.001132502831256953</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -31201,6 +33625,12 @@
       <c r="X404" s="3" t="n">
         <v>0.001250000000000094</v>
       </c>
+      <c r="Y404" s="1" t="n">
+        <v>0.2394</v>
+      </c>
+      <c r="Z404" s="2" t="n">
+        <v>-0.003745318352059975</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -31277,6 +33707,12 @@
       <c r="X405" s="2" t="n">
         <v>-0.0001140641040265275</v>
       </c>
+      <c r="Y405" s="1" t="n">
+        <v>0.0008749</v>
+      </c>
+      <c r="Z405" s="2" t="n">
+        <v>-0.001939310974218557</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -31353,6 +33789,12 @@
       <c r="X406" s="2" t="n">
         <v>-0.001182499014584311</v>
       </c>
+      <c r="Y406" s="1" t="n">
+        <v>0.005065</v>
+      </c>
+      <c r="Z406" s="2" t="n">
+        <v>-0.0005919494869770187</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -31429,6 +33871,12 @@
       <c r="X407" s="2" t="n">
         <v>-0.0008312551953450812</v>
       </c>
+      <c r="Y407" s="1" t="n">
+        <v>0.01203</v>
+      </c>
+      <c r="Z407" s="3" t="n">
+        <v>0.0008319467554077644</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -31505,6 +33953,12 @@
       <c r="X408" s="3" t="n">
         <v>0.002751031636863891</v>
       </c>
+      <c r="Y408" s="1" t="n">
+        <v>0.00146</v>
+      </c>
+      <c r="Z408" s="3" t="n">
+        <v>0.001371742112482738</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -31581,6 +34035,12 @@
       <c r="X409" s="3" t="n">
         <v>0.007448789571694665</v>
       </c>
+      <c r="Y409" s="1" t="n">
+        <v>0.03795</v>
+      </c>
+      <c r="Z409" s="3" t="n">
+        <v>0.002112490097702581</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -31657,6 +34117,12 @@
       <c r="X410" s="3" t="n">
         <v>0.0006134969325155254</v>
       </c>
+      <c r="Y410" s="1" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="Z410" s="3" t="n">
+        <v>0.001226241569589159</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -31733,6 +34199,12 @@
       <c r="X411" s="2" t="n">
         <v>-0.003156233561283479</v>
       </c>
+      <c r="Y411" s="1" t="n">
+        <v>0.1894</v>
+      </c>
+      <c r="Z411" s="2" t="n">
+        <v>-0.0005277044854880685</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -31809,6 +34281,12 @@
       <c r="X412" s="3" t="n">
         <v>0.0034013605442176</v>
       </c>
+      <c r="Y412" s="1" t="n">
+        <v>0.06766999999999999</v>
+      </c>
+      <c r="Z412" s="2" t="n">
+        <v>-0.002652910832719228</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -31885,6 +34363,12 @@
       <c r="X413" s="2" t="n">
         <v>-0.001575423395037416</v>
       </c>
+      <c r="Y413" s="1" t="n">
+        <v>2527</v>
+      </c>
+      <c r="Z413" s="2" t="n">
+        <v>-0.003155818540433925</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -31961,6 +34445,12 @@
       <c r="X414" s="2" t="n">
         <v>-0.002281802624072925</v>
       </c>
+      <c r="Y414" s="1" t="n">
+        <v>0.05247</v>
+      </c>
+      <c r="Z414" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -32037,6 +34527,12 @@
       <c r="X415" s="2" t="n">
         <v>-0.0005753739930954488</v>
       </c>
+      <c r="Y415" s="1" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z415" s="3" t="n">
+        <v>0.00172711571675296</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -32113,6 +34609,12 @@
       <c r="X416" s="3" t="n">
         <v>0.001014345746993198</v>
       </c>
+      <c r="Y416" s="1" t="n">
+        <v>0.06889000000000001</v>
+      </c>
+      <c r="Z416" s="2" t="n">
+        <v>-0.002750434279096638</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -32189,6 +34691,12 @@
       <c r="X417" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y417" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="Z417" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -32265,6 +34773,12 @@
       <c r="X418" s="2" t="n">
         <v>-0.003267973856209153</v>
       </c>
+      <c r="Y418" s="1" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="Z418" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -32341,6 +34855,12 @@
       <c r="X419" s="3" t="n">
         <v>0.008130081300812959</v>
       </c>
+      <c r="Y419" s="1" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="Z419" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -32417,6 +34937,12 @@
       <c r="X420" s="2" t="n">
         <v>-0.007272727272727337</v>
       </c>
+      <c r="Y420" s="1" t="n">
+        <v>0.01915</v>
+      </c>
+      <c r="Z420" s="3" t="n">
+        <v>0.002093144950287904</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -32493,6 +35019,12 @@
       <c r="X421" s="3" t="n">
         <v>0.005400956740908366</v>
       </c>
+      <c r="Y421" s="1" t="n">
+        <v>0.19466</v>
+      </c>
+      <c r="Z421" s="2" t="n">
+        <v>-0.00409290903509667</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -32569,6 +35101,12 @@
       <c r="X422" s="3" t="n">
         <v>0.0008805400645728003</v>
       </c>
+      <c r="Y422" s="1" t="n">
+        <v>0.0342</v>
+      </c>
+      <c r="Z422" s="3" t="n">
+        <v>0.002932551319648178</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -32645,6 +35183,12 @@
       <c r="X423" s="3" t="n">
         <v>0.0007062146892654589</v>
       </c>
+      <c r="Y423" s="1" t="n">
+        <v>0.1417</v>
+      </c>
+      <c r="Z423" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -32721,6 +35265,12 @@
       <c r="X424" s="3" t="n">
         <v>0.003795066413662249</v>
       </c>
+      <c r="Y424" s="1" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="Z424" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -32797,6 +35347,12 @@
       <c r="X425" s="2" t="n">
         <v>-0.002865329512893932</v>
       </c>
+      <c r="Y425" s="1" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="Z425" s="2" t="n">
+        <v>-0.002873563218390887</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -32873,6 +35429,12 @@
       <c r="X426" s="3" t="n">
         <v>0.001278227524499284</v>
       </c>
+      <c r="Y426" s="1" t="n">
+        <v>0.007064</v>
+      </c>
+      <c r="Z426" s="3" t="n">
+        <v>0.001985815602836897</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -32949,6 +35511,12 @@
       <c r="X427" s="2" t="n">
         <v>-0.001177856301531165</v>
       </c>
+      <c r="Y427" s="1" t="n">
+        <v>0.02545</v>
+      </c>
+      <c r="Z427" s="3" t="n">
+        <v>0.0003930817610062733</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -33025,6 +35593,12 @@
       <c r="X428" s="3" t="n">
         <v>0.0002484472049689771</v>
       </c>
+      <c r="Y428" s="1" t="n">
+        <v>0.008055</v>
+      </c>
+      <c r="Z428" s="3" t="n">
+        <v>0.0003725782414306422</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -33101,6 +35675,12 @@
       <c r="X429" s="2" t="n">
         <v>-0.0008071025020177234</v>
       </c>
+      <c r="Y429" s="1" t="n">
+        <v>0.01235</v>
+      </c>
+      <c r="Z429" s="2" t="n">
+        <v>-0.002423263327948345</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -33177,6 +35757,12 @@
       <c r="X430" s="2" t="n">
         <v>-0.0001497678598172252</v>
       </c>
+      <c r="Y430" s="1" t="n">
+        <v>0.06683</v>
+      </c>
+      <c r="Z430" s="3" t="n">
+        <v>0.001048532055122837</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -33253,6 +35839,12 @@
       <c r="X431" s="2" t="n">
         <v>-0.001848428835489758</v>
       </c>
+      <c r="Y431" s="1" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="Z431" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -33329,6 +35921,12 @@
       <c r="X432" s="2" t="n">
         <v>-0.007098765432098727</v>
       </c>
+      <c r="Y432" s="1" t="n">
+        <v>0.009613</v>
+      </c>
+      <c r="Z432" s="2" t="n">
+        <v>-0.003937415811832954</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -33405,6 +36003,12 @@
       <c r="X433" s="2" t="n">
         <v>-0.0009650180940892248</v>
       </c>
+      <c r="Y433" s="1" t="n">
+        <v>0.04141</v>
+      </c>
+      <c r="Z433" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -33481,6 +36085,12 @@
       <c r="X434" s="3" t="n">
         <v>0.00311079205551563</v>
       </c>
+      <c r="Y434" s="1" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="Z434" s="3" t="n">
+        <v>0.004293893129770983</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -33557,6 +36167,12 @@
       <c r="X435" s="2" t="n">
         <v>-0.001296176279974108</v>
       </c>
+      <c r="Y435" s="1" t="n">
+        <v>0.001543</v>
+      </c>
+      <c r="Z435" s="3" t="n">
+        <v>0.001297858533419889</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -33633,6 +36249,12 @@
       <c r="X436" s="2" t="n">
         <v>-0.003272727272727266</v>
       </c>
+      <c r="Y436" s="1" t="n">
+        <v>0.02739</v>
+      </c>
+      <c r="Z436" s="2" t="n">
+        <v>-0.0007296607077708568</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -33709,6 +36331,12 @@
       <c r="X437" s="3" t="n">
         <v>0.001712538226299709</v>
       </c>
+      <c r="Y437" s="1" t="n">
+        <v>0.08212</v>
+      </c>
+      <c r="Z437" s="3" t="n">
+        <v>0.00280864574429105</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -33785,6 +36413,12 @@
       <c r="X438" s="2" t="n">
         <v>-0.0008688097306688878</v>
       </c>
+      <c r="Y438" s="1" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="Z438" s="2" t="n">
+        <v>-0.001739130434782658</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -33861,6 +36495,12 @@
       <c r="X439" s="3" t="n">
         <v>0.0006476683937823121</v>
       </c>
+      <c r="Y439" s="1" t="n">
+        <v>1.544</v>
+      </c>
+      <c r="Z439" s="2" t="n">
+        <v>-0.0006472491909384401</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -33937,6 +36577,12 @@
       <c r="X440" s="2" t="n">
         <v>-0.0005549389567147147</v>
       </c>
+      <c r="Y440" s="1" t="n">
+        <v>0.001803</v>
+      </c>
+      <c r="Z440" s="3" t="n">
+        <v>0.001110494169905515</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -34013,6 +36659,12 @@
       <c r="X441" s="2" t="n">
         <v>-0.001622498647917727</v>
       </c>
+      <c r="Y441" s="1" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="Z441" s="2" t="n">
+        <v>-0.003250270855904714</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -34089,6 +36741,12 @@
       <c r="X442" s="2" t="n">
         <v>-0.001624255549539728</v>
       </c>
+      <c r="Y442" s="1" t="n">
+        <v>0.01842</v>
+      </c>
+      <c r="Z442" s="2" t="n">
+        <v>-0.001084598698481706</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -34165,6 +36823,12 @@
       <c r="X443" s="2" t="n">
         <v>-0.002667503530519216</v>
       </c>
+      <c r="Y443" s="1" t="n">
+        <v>0.1268</v>
+      </c>
+      <c r="Z443" s="2" t="n">
+        <v>-0.002517306482064307</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -34241,6 +36905,12 @@
       <c r="X444" s="2" t="n">
         <v>-0.003821434775056508</v>
       </c>
+      <c r="Y444" s="1" t="n">
+        <v>0.011464</v>
+      </c>
+      <c r="Z444" s="2" t="n">
+        <v>-0.0005231037489101187</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -34317,6 +36987,12 @@
       <c r="X445" s="2" t="n">
         <v>-0.0007416563658838627</v>
       </c>
+      <c r="Y445" s="1" t="n">
+        <v>0.08053</v>
+      </c>
+      <c r="Z445" s="2" t="n">
+        <v>-0.003834735279564459</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -34393,6 +37069,12 @@
       <c r="X446" s="3" t="n">
         <v>0.005188679245283017</v>
       </c>
+      <c r="Y446" s="1" t="n">
+        <v>0.0002133</v>
+      </c>
+      <c r="Z446" s="3" t="n">
+        <v>0.0009385265133740257</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -34469,6 +37151,12 @@
       <c r="X447" s="2" t="n">
         <v>-0.002976190476190484</v>
       </c>
+      <c r="Y447" s="1" t="n">
+        <v>0.00661</v>
+      </c>
+      <c r="Z447" s="2" t="n">
+        <v>-0.01343283582089549</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -34545,6 +37233,12 @@
       <c r="X448" s="3" t="n">
         <v>0.009561191626408942</v>
       </c>
+      <c r="Y448" s="1" t="n">
+        <v>0.10101</v>
+      </c>
+      <c r="Z448" s="3" t="n">
+        <v>0.006978367062107528</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -34621,6 +37315,12 @@
       <c r="X449" s="2" t="n">
         <v>-0.002972651605231746</v>
       </c>
+      <c r="Y449" s="1" t="n">
+        <v>0.001671</v>
+      </c>
+      <c r="Z449" s="2" t="n">
+        <v>-0.00357781753130599</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -34697,6 +37397,12 @@
       <c r="X450" s="2" t="n">
         <v>-0.001938923897237081</v>
       </c>
+      <c r="Y450" s="1" t="n">
+        <v>0.0002063</v>
+      </c>
+      <c r="Z450" s="3" t="n">
+        <v>0.001942690626517774</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -34773,6 +37479,12 @@
       <c r="X451" s="3" t="n">
         <v>0.00379650721336376</v>
       </c>
+      <c r="Y451" s="1" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="Z451" s="2" t="n">
+        <v>-0.004160363086233093</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -34849,6 +37561,12 @@
       <c r="X452" s="2" t="n">
         <v>-0.000743494423791946</v>
       </c>
+      <c r="Y452" s="1" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="Z452" s="2" t="n">
+        <v>-0.0007440476190475371</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -34925,6 +37643,12 @@
       <c r="X453" s="2" t="n">
         <v>-0.002284408909194801</v>
       </c>
+      <c r="Y453" s="1" t="n">
+        <v>0.0001745</v>
+      </c>
+      <c r="Z453" s="2" t="n">
+        <v>-0.001144819690898556</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -35001,6 +37725,12 @@
       <c r="X454" s="3" t="n">
         <v>0.009581166164796016</v>
       </c>
+      <c r="Y454" s="1" t="n">
+        <v>0.11002</v>
+      </c>
+      <c r="Z454" s="2" t="n">
+        <v>-0.005603759942154696</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -35077,6 +37807,12 @@
       <c r="X455" s="2" t="n">
         <v>-0.001987676406281059</v>
       </c>
+      <c r="Y455" s="1" t="n">
+        <v>0.5021</v>
+      </c>
+      <c r="Z455" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -35153,6 +37889,12 @@
       <c r="X456" s="2" t="n">
         <v>-0.002252957006070549</v>
       </c>
+      <c r="Y456" s="1" t="n">
+        <v>0.015946</v>
+      </c>
+      <c r="Z456" s="3" t="n">
+        <v>0.0001881703568964142</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -35229,6 +37971,12 @@
       <c r="X457" s="2" t="n">
         <v>-0.002828643739764764</v>
       </c>
+      <c r="Y457" s="1" t="n">
+        <v>0.006697</v>
+      </c>
+      <c r="Z457" s="2" t="n">
+        <v>-0.0001492982979994226</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -35305,6 +38053,12 @@
       <c r="X458" s="2" t="n">
         <v>-0.0002076843198338297</v>
       </c>
+      <c r="Y458" s="1" t="n">
+        <v>0.4812</v>
+      </c>
+      <c r="Z458" s="2" t="n">
+        <v>-0.0004154549231407935</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -35381,6 +38135,12 @@
       <c r="X459" s="2" t="n">
         <v>-0.001257071024512916</v>
       </c>
+      <c r="Y459" s="1" t="n">
+        <v>0.006349</v>
+      </c>
+      <c r="Z459" s="2" t="n">
+        <v>-0.001101321585903094</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -35457,6 +38217,12 @@
       <c r="X460" s="2" t="n">
         <v>-0.005068790731354136</v>
       </c>
+      <c r="Y460" s="1" t="n">
+        <v>0.1374</v>
+      </c>
+      <c r="Z460" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -35533,6 +38299,12 @@
       <c r="X461" s="2" t="n">
         <v>-0.005228758169934729</v>
       </c>
+      <c r="Y461" s="1" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="Z461" s="2" t="n">
+        <v>-0.008979413053000452</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -35609,6 +38381,12 @@
       <c r="X462" s="2" t="n">
         <v>-0.005029521102121169</v>
       </c>
+      <c r="Y462" s="1" t="n">
+        <v>0.04553</v>
+      </c>
+      <c r="Z462" s="3" t="n">
+        <v>0.0006593406593407088</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -35685,6 +38463,12 @@
       <c r="X463" s="3" t="n">
         <v>0.001434720229555303</v>
       </c>
+      <c r="Y463" s="1" t="n">
+        <v>0.00697</v>
+      </c>
+      <c r="Z463" s="2" t="n">
+        <v>-0.001432664756447057</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -35761,6 +38545,12 @@
       <c r="X464" s="3" t="n">
         <v>0.0007621951219511355</v>
       </c>
+      <c r="Y464" s="1" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z464" s="2" t="n">
+        <v>-0.002284843869002203</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -35837,6 +38627,12 @@
       <c r="X465" s="2" t="n">
         <v>-0.009197028652281539</v>
       </c>
+      <c r="Y465" s="1" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="Z465" s="2" t="n">
+        <v>-0.005355230274901825</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -35913,6 +38709,12 @@
       <c r="X466" s="3" t="n">
         <v>0.0007047216349541155</v>
       </c>
+      <c r="Y466" s="1" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="Z466" s="2" t="n">
+        <v>-0.001408450704225353</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -35989,6 +38791,12 @@
       <c r="X467" s="3" t="n">
         <v>0.001048218029350062</v>
       </c>
+      <c r="Y467" s="1" t="n">
+        <v>0.01912</v>
+      </c>
+      <c r="Z467" s="3" t="n">
+        <v>0.001047120418848307</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -36065,6 +38873,12 @@
       <c r="X468" s="3" t="n">
         <v>0.003996003996004006</v>
       </c>
+      <c r="Y468" s="1" t="n">
+        <v>0.01013</v>
+      </c>
+      <c r="Z468" s="3" t="n">
+        <v>0.007960199004975145</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -36141,6 +38955,12 @@
       <c r="X469" s="2" t="n">
         <v>-0.004998750312421899</v>
       </c>
+      <c r="Y469" s="1" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="Z469" s="2" t="n">
+        <v>-0.00150715900527503</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -36217,6 +39037,12 @@
       <c r="X470" s="2" t="n">
         <v>-0.001133786848072563</v>
       </c>
+      <c r="Y470" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Z470" s="2" t="n">
+        <v>-0.001135073779795688</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -36293,6 +39119,12 @@
       <c r="X471" s="2" t="n">
         <v>-0.001547508511296779</v>
       </c>
+      <c r="Y471" s="1" t="n">
+        <v>3.222</v>
+      </c>
+      <c r="Z471" s="2" t="n">
+        <v>-0.001239925604463733</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -36369,6 +39201,12 @@
       <c r="X472" s="3" t="n">
         <v>0.008606263447286617</v>
       </c>
+      <c r="Y472" s="1" t="n">
+        <v>0.04201</v>
+      </c>
+      <c r="Z472" s="2" t="n">
+        <v>-0.004266413842142679</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -36445,6 +39283,12 @@
       <c r="X473" s="2" t="n">
         <v>-0.003200000000000003</v>
       </c>
+      <c r="Y473" s="1" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="Z473" s="2" t="n">
+        <v>-0.000802568218298467</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -36521,6 +39365,12 @@
       <c r="X474" s="3" t="n">
         <v>0.0009368778545498375</v>
       </c>
+      <c r="Y474" s="1" t="n">
+        <v>0.008536999999999999</v>
+      </c>
+      <c r="Z474" s="2" t="n">
+        <v>-0.001170001170001325</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -36597,6 +39447,12 @@
       <c r="X475" s="3" t="n">
         <v>0.002634730538922131</v>
       </c>
+      <c r="Y475" s="1" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="Z475" s="2" t="n">
+        <v>-0.0016722408026756</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -36673,6 +39529,12 @@
       <c r="X476" s="2" t="n">
         <v>-0.0002532286654848348</v>
       </c>
+      <c r="Y476" s="1" t="n">
+        <v>0.07876</v>
+      </c>
+      <c r="Z476" s="2" t="n">
+        <v>-0.002532928064843031</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -36749,6 +39611,12 @@
       <c r="X477" s="2" t="n">
         <v>-0.0005856944139395032</v>
       </c>
+      <c r="Y477" s="1" t="n">
+        <v>0.1365</v>
+      </c>
+      <c r="Z477" s="2" t="n">
+        <v>-7.325470661476995e-05</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -36825,6 +39693,12 @@
       <c r="X478" s="3" t="n">
         <v>0.0002108370229813001</v>
       </c>
+      <c r="Y478" s="1" t="n">
+        <v>0.04738</v>
+      </c>
+      <c r="Z478" s="2" t="n">
+        <v>-0.001264755480607177</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -36901,6 +39775,12 @@
       <c r="X479" s="3" t="n">
         <v>0.002064952130655101</v>
       </c>
+      <c r="Y479" s="1" t="n">
+        <v>0.005334</v>
+      </c>
+      <c r="Z479" s="2" t="n">
+        <v>-0.0007493443237166848</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -36977,6 +39857,12 @@
       <c r="X480" s="3" t="n">
         <v>0.002505368647101052</v>
       </c>
+      <c r="Y480" s="1" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="Z480" s="3" t="n">
+        <v>0.001071046054980246</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -37053,6 +39939,12 @@
       <c r="X481" s="3" t="n">
         <v>0.0005275652862041462</v>
       </c>
+      <c r="Y481" s="1" t="n">
+        <v>0.07575999999999999</v>
+      </c>
+      <c r="Z481" s="2" t="n">
+        <v>-0.001318217769575572</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -37129,6 +40021,12 @@
       <c r="X482" s="3" t="n">
         <v>0.0006697923643670189</v>
       </c>
+      <c r="Y482" s="1" t="n">
+        <v>0.01487</v>
+      </c>
+      <c r="Z482" s="2" t="n">
+        <v>-0.004685408299866172</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -37205,6 +40103,12 @@
       <c r="X483" s="2" t="n">
         <v>-0.007968127490039931</v>
       </c>
+      <c r="Y483" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="Z483" s="3" t="n">
+        <v>0.004016064257028227</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -37281,6 +40185,12 @@
       <c r="X484" s="2" t="n">
         <v>-0.001390820584144589</v>
       </c>
+      <c r="Y484" s="1" t="n">
+        <v>0.02154</v>
+      </c>
+      <c r="Z484" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -37357,6 +40267,12 @@
       <c r="X485" s="3" t="n">
         <v>0.0003609239653512429</v>
       </c>
+      <c r="Y485" s="1" t="n">
+        <v>0.008288</v>
+      </c>
+      <c r="Z485" s="2" t="n">
+        <v>-0.003247143716175496</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -37433,6 +40349,12 @@
       <c r="X486" s="2" t="n">
         <v>-0.0009380863039399707</v>
       </c>
+      <c r="Y486" s="1" t="n">
+        <v>0.007456</v>
+      </c>
+      <c r="Z486" s="3" t="n">
+        <v>0.0001341381623071942</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -37509,6 +40431,12 @@
       <c r="X487" s="2" t="n">
         <v>-0.001801801801801853</v>
       </c>
+      <c r="Y487" s="1" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="Z487" s="3" t="n">
+        <v>0.002707581227436901</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -37585,6 +40513,12 @@
       <c r="X488" s="2" t="n">
         <v>-0.0195784743768053</v>
       </c>
+      <c r="Y488" s="1" t="n">
+        <v>0.009272000000000001</v>
+      </c>
+      <c r="Z488" s="3" t="n">
+        <v>0.01178524661719778</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -37661,6 +40595,12 @@
       <c r="X489" s="3" t="n">
         <v>0.005201560468140411</v>
       </c>
+      <c r="Y489" s="1" t="n">
+        <v>0.03852</v>
+      </c>
+      <c r="Z489" s="2" t="n">
+        <v>-0.003363518758085335</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -37737,6 +40677,12 @@
       <c r="X490" s="2" t="n">
         <v>-0.001535312180143292</v>
       </c>
+      <c r="Y490" s="1" t="n">
+        <v>0.05854</v>
+      </c>
+      <c r="Z490" s="3" t="n">
+        <v>0.0001708525542457383</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -37813,6 +40759,12 @@
       <c r="X491" s="2" t="n">
         <v>-0.001037344398340279</v>
       </c>
+      <c r="Y491" s="1" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="Z491" s="3" t="n">
+        <v>0.002076843198338585</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -37889,6 +40841,12 @@
       <c r="X492" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y492" s="1" t="n">
+        <v>1.326</v>
+      </c>
+      <c r="Z492" s="2" t="n">
+        <v>-0.0007535795026374453</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -37965,6 +40923,12 @@
       <c r="X493" s="2" t="n">
         <v>-0.001133465570983432</v>
       </c>
+      <c r="Y493" s="1" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="Z493" s="2" t="n">
+        <v>-0.001418439716311901</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -38041,6 +41005,12 @@
       <c r="X494" s="2" t="n">
         <v>-0.001175088131609823</v>
       </c>
+      <c r="Y494" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="Z494" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -38117,6 +41087,12 @@
       <c r="X495" s="2" t="n">
         <v>-0.002960456756185266</v>
       </c>
+      <c r="Y495" s="1" t="n">
+        <v>0.04717</v>
+      </c>
+      <c r="Z495" s="3" t="n">
+        <v>0.0004241781548250092</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -38193,6 +41169,12 @@
       <c r="X496" s="3" t="n">
         <v>0.003325711910205787</v>
       </c>
+      <c r="Y496" s="1" t="n">
+        <v>0.04826</v>
+      </c>
+      <c r="Z496" s="2" t="n">
+        <v>-0.0002071680132588163</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -38269,6 +41251,12 @@
       <c r="X497" s="2" t="n">
         <v>-0.0008059641345959776</v>
       </c>
+      <c r="Y497" s="1" t="n">
+        <v>0.04951</v>
+      </c>
+      <c r="Z497" s="2" t="n">
+        <v>-0.001613228473482631</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -38345,6 +41333,12 @@
       <c r="X498" s="3" t="n">
         <v>0.002428868841082506</v>
       </c>
+      <c r="Y498" s="1" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="Z498" s="2" t="n">
+        <v>-0.0006922810661127656</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -38421,6 +41415,12 @@
       <c r="X499" s="3" t="n">
         <v>0.0007326007326006518</v>
       </c>
+      <c r="Y499" s="1" t="n">
+        <v>0.2728</v>
+      </c>
+      <c r="Z499" s="2" t="n">
+        <v>-0.001464128843338256</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -38497,6 +41497,12 @@
       <c r="X500" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y500" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="Z500" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -38573,6 +41579,12 @@
       <c r="X501" s="3" t="n">
         <v>0.003649635036496299</v>
       </c>
+      <c r="Y501" s="1" t="n">
+        <v>0.03576</v>
+      </c>
+      <c r="Z501" s="3" t="n">
+        <v>0.0002797202797203654</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -38649,6 +41661,12 @@
       <c r="X502" s="3" t="n">
         <v>0.001882648258550284</v>
       </c>
+      <c r="Y502" s="1" t="n">
+        <v>0.03196</v>
+      </c>
+      <c r="Z502" s="3" t="n">
+        <v>0.0009395552771688772</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -38725,6 +41743,12 @@
       <c r="X503" s="3" t="n">
         <v>0.001033591731266063</v>
       </c>
+      <c r="Y503" s="1" t="n">
+        <v>0.007743</v>
+      </c>
+      <c r="Z503" s="2" t="n">
+        <v>-0.000645327826535854</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -38801,6 +41825,12 @@
       <c r="X504" s="2" t="n">
         <v>-0.001301659616010414</v>
       </c>
+      <c r="Y504" s="1" t="n">
+        <v>3.062</v>
+      </c>
+      <c r="Z504" s="2" t="n">
+        <v>-0.002280873248615222</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -38877,6 +41907,12 @@
       <c r="X505" s="3" t="n">
         <v>0.003924221921515584</v>
       </c>
+      <c r="Y505" s="1" t="n">
+        <v>0.0007403000000000001</v>
+      </c>
+      <c r="Z505" s="2" t="n">
+        <v>-0.002156624882059483</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -38953,6 +41989,12 @@
       <c r="X506" s="2" t="n">
         <v>-0.005421890884445918</v>
       </c>
+      <c r="Y506" s="1" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="Z506" s="2" t="n">
+        <v>-0.001703577512776833</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -39029,6 +42071,12 @@
       <c r="X507" s="2" t="n">
         <v>-0.001755001755001684</v>
       </c>
+      <c r="Y507" s="1" t="n">
+        <v>0.002847</v>
+      </c>
+      <c r="Z507" s="3" t="n">
+        <v>0.001054852320675093</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -39105,6 +42153,12 @@
       <c r="X508" s="2" t="n">
         <v>-0.001263024944742607</v>
       </c>
+      <c r="Y508" s="1" t="n">
+        <v>0.06315</v>
+      </c>
+      <c r="Z508" s="2" t="n">
+        <v>-0.001738855516914306</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -39181,6 +42235,12 @@
       <c r="X509" s="2" t="n">
         <v>-0.003565062388591803</v>
       </c>
+      <c r="Y509" s="1" t="n">
+        <v>2.231</v>
+      </c>
+      <c r="Z509" s="2" t="n">
+        <v>-0.00223613595706634</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -39257,6 +42317,12 @@
       <c r="X510" s="2" t="n">
         <v>-0.0027352297592997</v>
       </c>
+      <c r="Y510" s="1" t="n">
+        <v>0.0007302</v>
+      </c>
+      <c r="Z510" s="3" t="n">
+        <v>0.00137136588041678</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -39333,6 +42399,12 @@
       <c r="X511" s="2" t="n">
         <v>-0.001083815028901615</v>
       </c>
+      <c r="Y511" s="1" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="Z511" s="2" t="n">
+        <v>-0.001808318264014468</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -39409,6 +42481,12 @@
       <c r="X512" s="2" t="n">
         <v>-0.002472187886279306</v>
       </c>
+      <c r="Y512" s="1" t="n">
+        <v>0.000483</v>
+      </c>
+      <c r="Z512" s="2" t="n">
+        <v>-0.002478314745972799</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -39485,6 +42563,12 @@
       <c r="X513" s="2" t="n">
         <v>-0.001257635644987435</v>
       </c>
+      <c r="Y513" s="1" t="n">
+        <v>0.05545</v>
+      </c>
+      <c r="Z513" s="2" t="n">
+        <v>-0.002518438568087808</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -39561,6 +42645,12 @@
       <c r="X514" s="3" t="n">
         <v>0.002969317057076866</v>
       </c>
+      <c r="Y514" s="1" t="n">
+        <v>0.03043</v>
+      </c>
+      <c r="Z514" s="3" t="n">
+        <v>0.0009868421052631176</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -39637,6 +42727,12 @@
       <c r="X515" s="2" t="n">
         <v>-0.001754385964912323</v>
       </c>
+      <c r="Y515" s="1" t="n">
+        <v>0.001138</v>
+      </c>
+      <c r="Z515" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -39713,6 +42809,12 @@
       <c r="X516" s="2" t="n">
         <v>-0.004522158577027512</v>
       </c>
+      <c r="Y516" s="1" t="n">
+        <v>0.006605</v>
+      </c>
+      <c r="Z516" s="3" t="n">
+        <v>0.0001514233797698566</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -39789,6 +42891,12 @@
       <c r="X517" s="2" t="n">
         <v>-0.0007530120481928275</v>
       </c>
+      <c r="Y517" s="1" t="n">
+        <v>0.03974</v>
+      </c>
+      <c r="Z517" s="2" t="n">
+        <v>-0.001758352172820915</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -39865,6 +42973,12 @@
       <c r="X518" s="3" t="n">
         <v>0.001943634596695742</v>
       </c>
+      <c r="Y518" s="1" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="Z518" s="2" t="n">
+        <v>-0.002909796314257951</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -39941,6 +43055,12 @@
       <c r="X519" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y519" s="1" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="Z519" s="2" t="n">
+        <v>-0.001141552511415479</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -40017,6 +43137,12 @@
       <c r="X520" s="2" t="n">
         <v>-0.005617977528089961</v>
       </c>
+      <c r="Y520" s="1" t="n">
+        <v>0.1594</v>
+      </c>
+      <c r="Z520" s="3" t="n">
+        <v>0.0006277463904581857</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -40093,6 +43219,12 @@
       <c r="X521" s="2" t="n">
         <v>-0.001115448968209852</v>
       </c>
+      <c r="Y521" s="1" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="Z521" s="2" t="n">
+        <v>-0.000558347292015611</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -40169,6 +43301,12 @@
       <c r="X522" s="2" t="n">
         <v>-0.001834862385321026</v>
       </c>
+      <c r="Y522" s="1" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="Z522" s="3" t="n">
+        <v>0.0006127450980391906</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -40245,6 +43383,12 @@
       <c r="X523" s="2" t="n">
         <v>-0.0002394636015325988</v>
       </c>
+      <c r="Y523" s="1" t="n">
+        <v>0.004171</v>
+      </c>
+      <c r="Z523" s="2" t="n">
+        <v>-0.0009580838323352488</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -40321,6 +43465,12 @@
       <c r="X524" s="3" t="n">
         <v>0.003518648838845862</v>
       </c>
+      <c r="Y524" s="1" t="n">
+        <v>0.01424</v>
+      </c>
+      <c r="Z524" s="2" t="n">
+        <v>-0.001402524544179588</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -40397,6 +43547,12 @@
       <c r="X525" s="2" t="n">
         <v>-0.003216726980297556</v>
       </c>
+      <c r="Y525" s="1" t="n">
+        <v>0.02465</v>
+      </c>
+      <c r="Z525" s="2" t="n">
+        <v>-0.005647438483259428</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -40473,6 +43629,12 @@
       <c r="X526" s="2" t="n">
         <v>-0.0008312551953449947</v>
       </c>
+      <c r="Y526" s="1" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="Z526" s="2" t="n">
+        <v>-0.003327787021630595</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -40549,6 +43711,12 @@
       <c r="X527" s="3" t="n">
         <v>0.0009708737864077756</v>
       </c>
+      <c r="Y527" s="1" t="n">
+        <v>0.07183</v>
+      </c>
+      <c r="Z527" s="2" t="n">
+        <v>-0.00471109879451286</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -40625,6 +43793,12 @@
       <c r="X528" s="2" t="n">
         <v>-0.0009240009240010466</v>
       </c>
+      <c r="Y528" s="1" t="n">
+        <v>0.04319</v>
+      </c>
+      <c r="Z528" s="2" t="n">
+        <v>-0.001387283236994163</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -40701,6 +43875,12 @@
       <c r="X529" s="3" t="n">
         <v>0.0006343165239454229</v>
       </c>
+      <c r="Y529" s="1" t="n">
+        <v>0.06304999999999999</v>
+      </c>
+      <c r="Z529" s="2" t="n">
+        <v>-0.0007923930269414955</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -40777,6 +43957,12 @@
       <c r="X530" s="3" t="n">
         <v>0.0003978516013525757</v>
       </c>
+      <c r="Y530" s="1" t="n">
+        <v>0.005017</v>
+      </c>
+      <c r="Z530" s="2" t="n">
+        <v>-0.002386160270431469</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -40853,6 +44039,12 @@
       <c r="X531" s="2" t="n">
         <v>-0.001545595054095657</v>
       </c>
+      <c r="Y531" s="1" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="Z531" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -40929,6 +44121,12 @@
       <c r="X532" s="2" t="n">
         <v>-0.001877229209686426</v>
       </c>
+      <c r="Y532" s="1" t="n">
+        <v>0.05313</v>
+      </c>
+      <c r="Z532" s="2" t="n">
+        <v>-0.0007523039307881381</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -41005,6 +44203,12 @@
       <c r="X533" s="3" t="n">
         <v>0.001878690284487403</v>
       </c>
+      <c r="Y533" s="1" t="n">
+        <v>0.003725</v>
+      </c>
+      <c r="Z533" s="2" t="n">
+        <v>-0.002143048486472058</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -41081,6 +44285,12 @@
       <c r="X534" s="3" t="n">
         <v>0.0005830903790086821</v>
       </c>
+      <c r="Y534" s="1" t="n">
+        <v>0.1715</v>
+      </c>
+      <c r="Z534" s="2" t="n">
+        <v>-0.0005827505827505186</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -41157,6 +44367,12 @@
       <c r="X535" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="Z535" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -41233,6 +44449,12 @@
       <c r="X536" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y536" s="1" t="n">
+        <v>0.000442</v>
+      </c>
+      <c r="Z536" s="2" t="n">
+        <v>-0.002032061413411532</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -41309,6 +44531,12 @@
       <c r="X537" s="2" t="n">
         <v>-0.004136504653567746</v>
       </c>
+      <c r="Y537" s="1" t="n">
+        <v>0.00962</v>
+      </c>
+      <c r="Z537" s="2" t="n">
+        <v>-0.00103842159916922</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -41385,6 +44613,12 @@
       <c r="X538" s="2" t="n">
         <v>-0.001281347245103434</v>
       </c>
+      <c r="Y538" s="1" t="n">
+        <v>0.05452</v>
+      </c>
+      <c r="Z538" s="2" t="n">
+        <v>-0.0007331378299119936</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -41461,6 +44695,12 @@
       <c r="X539" s="2" t="n">
         <v>-0.00219973603167612</v>
       </c>
+      <c r="Y539" s="1" t="n">
+        <v>0.6794</v>
+      </c>
+      <c r="Z539" s="2" t="n">
+        <v>-0.001469723691945916</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -41537,6 +44777,12 @@
       <c r="X540" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y540" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="Z540" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -41613,6 +44859,12 @@
       <c r="X541" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Y541" s="1" t="n">
+        <v>0.01304</v>
+      </c>
+      <c r="Z541" s="3" t="n">
+        <v>0.0007674597083652796</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -41689,6 +44941,12 @@
       <c r="X542" s="3" t="n">
         <v>0.001432664756446933</v>
       </c>
+      <c r="Y542" s="1" t="n">
+        <v>0.01399</v>
+      </c>
+      <c r="Z542" s="3" t="n">
+        <v>0.0007153075822604669</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -41764,6 +45022,12 @@
       </c>
       <c r="X543" s="2" t="n">
         <v>-0.000175284837861457</v>
+      </c>
+      <c r="Y543" s="1" t="n">
+        <v>0.05702</v>
+      </c>
+      <c r="Z543" s="2" t="n">
+        <v>-0.0003506311360448665</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z543"/>
+  <dimension ref="A1:AB543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -452,6 +452,8 @@
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -585,6 +587,16 @@
           <t>change_03:00</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>price_03:15</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>change_03:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -667,6 +679,12 @@
       <c r="Z2" s="2" t="n">
         <v>-0.001566745504728137</v>
       </c>
+      <c r="AA2" s="1" t="n">
+        <v>69896.60000000001</v>
+      </c>
+      <c r="AB2" s="3" t="n">
+        <v>0.001662353146863168</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -749,6 +767,12 @@
       <c r="Z3" s="2" t="n">
         <v>-0.00241628262712268</v>
       </c>
+      <c r="AA3" s="1" t="n">
+        <v>2048.49</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>0.0003467169324828883</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -831,6 +855,12 @@
       <c r="Z4" s="2" t="n">
         <v>-0.002325311010347667</v>
       </c>
+      <c r="AA4" s="1" t="n">
+        <v>85.79000000000001</v>
+      </c>
+      <c r="AB4" s="2" t="n">
+        <v>-0.0002330730684068992</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -913,6 +943,12 @@
       <c r="Z5" s="2" t="n">
         <v>-0.008342813803564613</v>
       </c>
+      <c r="AA5" s="1" t="n">
+        <v>0.010386</v>
+      </c>
+      <c r="AB5" s="2" t="n">
+        <v>-0.007074569789675062</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -995,6 +1031,12 @@
       <c r="Z6" s="2" t="n">
         <v>-0.001746979181831386</v>
       </c>
+      <c r="AA6" s="1" t="n">
+        <v>1.3718</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>0.0002916727431821175</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1077,6 +1119,12 @@
       <c r="Z7" s="2" t="n">
         <v>-0.001490630323679741</v>
       </c>
+      <c r="AA7" s="1" t="n">
+        <v>0.09397</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>0.002026018340797566</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1159,6 +1207,12 @@
       <c r="Z8" s="2" t="n">
         <v>-0.001614552499865515</v>
       </c>
+      <c r="AA8" s="1" t="n">
+        <v>37.039</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>-0.001698021669990709</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1241,6 +1295,12 @@
       <c r="Z9" s="3" t="n">
         <v>0.008084074373484186</v>
       </c>
+      <c r="AA9" s="1" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="AB9" s="3" t="n">
+        <v>0.01643945469125905</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1323,6 +1383,12 @@
       <c r="Z10" s="3" t="n">
         <v>0.009086951790184003</v>
       </c>
+      <c r="AA10" s="1" t="n">
+        <v>18.353</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>-0.01035319493124832</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1405,6 +1471,12 @@
       <c r="Z11" s="2" t="n">
         <v>-0.001217613785237533</v>
       </c>
+      <c r="AA11" s="1" t="n">
+        <v>647.8200000000001</v>
+      </c>
+      <c r="AB11" s="2" t="n">
+        <v>-0.0003086324496156473</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1487,6 +1559,12 @@
       <c r="Z12" s="3" t="n">
         <v>0.03288335064035995</v>
       </c>
+      <c r="AA12" s="1" t="n">
+        <v>0.8818</v>
+      </c>
+      <c r="AB12" s="2" t="n">
+        <v>-0.01496872207327968</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1569,6 +1647,12 @@
       <c r="Z13" s="2" t="n">
         <v>-0.004003622324960695</v>
       </c>
+      <c r="AA13" s="1" t="n">
+        <v>208.4</v>
+      </c>
+      <c r="AB13" s="2" t="n">
+        <v>-0.002727664258027435</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1651,6 +1735,12 @@
       <c r="Z14" s="2" t="n">
         <v>-0.0006923956890842972</v>
       </c>
+      <c r="AA14" s="1" t="n">
+        <v>0.0033219</v>
+      </c>
+      <c r="AB14" s="3" t="n">
+        <v>0.0007230004518753</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1733,6 +1823,12 @@
       <c r="Z15" s="3" t="n">
         <v>0.02667262227610642</v>
       </c>
+      <c r="AA15" s="1" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="AB15" s="2" t="n">
+        <v>-0.003449454613257092</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1815,6 +1911,12 @@
       <c r="Z16" s="2" t="n">
         <v>-0.001541782300339136</v>
       </c>
+      <c r="AA16" s="1" t="n">
+        <v>0.9721</v>
+      </c>
+      <c r="AB16" s="3" t="n">
+        <v>0.0007206094296890291</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1897,6 +1999,12 @@
       <c r="Z17" s="2" t="n">
         <v>-0.02105263157894736</v>
       </c>
+      <c r="AA17" s="1" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="AB17" s="2" t="n">
+        <v>-0.03942652329749105</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1979,6 +2087,12 @@
       <c r="Z18" s="2" t="n">
         <v>-0.0008526764566556458</v>
       </c>
+      <c r="AA18" s="1" t="n">
+        <v>211.04</v>
+      </c>
+      <c r="AB18" s="3" t="n">
+        <v>0.000568936089512633</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2061,6 +2175,12 @@
       <c r="Z19" s="2" t="n">
         <v>-0.002296211251435092</v>
       </c>
+      <c r="AA19" s="1" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="AB19" s="3" t="n">
+        <v>0.0003835826620636325</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2143,6 +2263,12 @@
       <c r="Z20" s="3" t="n">
         <v>0.001870798012277157</v>
       </c>
+      <c r="AA20" s="1" t="n">
+        <v>0.017058</v>
+      </c>
+      <c r="AB20" s="2" t="n">
+        <v>-0.004609908385364954</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2225,6 +2351,12 @@
       <c r="Z21" s="2" t="n">
         <v>-0.00146535482520422</v>
       </c>
+      <c r="AA21" s="1" t="n">
+        <v>9.548</v>
+      </c>
+      <c r="AB21" s="3" t="n">
+        <v>0.0008385744234801778</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2307,6 +2439,12 @@
       <c r="Z22" s="2" t="n">
         <v>-0.0005924170616114735</v>
       </c>
+      <c r="AA22" s="1" t="n">
+        <v>0.1682</v>
+      </c>
+      <c r="AB22" s="2" t="n">
+        <v>-0.002963841138115</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2389,6 +2527,12 @@
       <c r="Z23" s="2" t="n">
         <v>-0.009486029665401935</v>
       </c>
+      <c r="AA23" s="1" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="AB23" s="3" t="n">
+        <v>0.002815021185211058</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2471,6 +2615,12 @@
       <c r="Z24" s="2" t="n">
         <v>-0.003460207612456751</v>
       </c>
+      <c r="AA24" s="1" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="AB24" s="2" t="n">
+        <v>-0.001157407407407408</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2553,6 +2703,12 @@
       <c r="Z25" s="2" t="n">
         <v>-0.001890989988876469</v>
       </c>
+      <c r="AA25" s="1" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="AB25" s="3" t="n">
+        <v>0.0007801181321742642</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2635,6 +2791,12 @@
       <c r="Z26" s="2" t="n">
         <v>-0.001498127340823971</v>
       </c>
+      <c r="AA26" s="1" t="n">
+        <v>1.336</v>
+      </c>
+      <c r="AB26" s="3" t="n">
+        <v>0.00225056264066025</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2717,6 +2879,12 @@
       <c r="Z27" s="2" t="n">
         <v>-0.0008035261077392036</v>
       </c>
+      <c r="AA27" s="1" t="n">
+        <v>5090.34</v>
+      </c>
+      <c r="AB27" s="2" t="n">
+        <v>-0.001582846416824012</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2799,6 +2967,12 @@
       <c r="Z28" s="3" t="n">
         <v>0.001967397414277624</v>
       </c>
+      <c r="AA28" s="1" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AB28" s="3" t="n">
+        <v>0.002524544179523175</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2881,6 +3055,12 @@
       <c r="Z29" s="3" t="n">
         <v>0.001908396946564845</v>
       </c>
+      <c r="AA29" s="1" t="n">
+        <v>2.622</v>
+      </c>
+      <c r="AB29" s="2" t="n">
+        <v>-0.001142857142857186</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2963,6 +3143,12 @@
       <c r="Z30" s="3" t="n">
         <v>0.008362035294535369</v>
       </c>
+      <c r="AA30" s="1" t="n">
+        <v>0.57246</v>
+      </c>
+      <c r="AB30" s="3" t="n">
+        <v>0.007905347113403866</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3045,6 +3231,12 @@
       <c r="Z31" s="2" t="n">
         <v>-0.005291005291005367</v>
       </c>
+      <c r="AA31" s="1" t="n">
+        <v>0.002061</v>
+      </c>
+      <c r="AB31" s="2" t="n">
+        <v>-0.003384912959381074</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3127,6 +3319,12 @@
       <c r="Z32" s="2" t="n">
         <v>-0.002777134922471687</v>
       </c>
+      <c r="AA32" s="1" t="n">
+        <v>1.2985</v>
+      </c>
+      <c r="AB32" s="3" t="n">
+        <v>0.004486733194089911</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3209,6 +3407,12 @@
       <c r="Z33" s="2" t="n">
         <v>-0.02122641509433958</v>
       </c>
+      <c r="AA33" s="1" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="AB33" s="3" t="n">
+        <v>0.004819277108433706</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3291,6 +3495,12 @@
       <c r="Z34" s="2" t="n">
         <v>-0.001333333333333335</v>
       </c>
+      <c r="AA34" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB34" s="3" t="n">
+        <v>0.001335113484646196</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3373,6 +3583,12 @@
       <c r="Z35" s="2" t="n">
         <v>-0.0009223066449998154</v>
       </c>
+      <c r="AA35" s="1" t="n">
+        <v>455.07</v>
+      </c>
+      <c r="AB35" s="3" t="n">
+        <v>0.000241779497098676</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3455,6 +3671,12 @@
       <c r="Z36" s="2" t="n">
         <v>-0.003534303534303463</v>
       </c>
+      <c r="AA36" s="1" t="n">
+        <v>0.04782</v>
+      </c>
+      <c r="AB36" s="2" t="n">
+        <v>-0.002295013561443751</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3537,6 +3759,12 @@
       <c r="Z37" s="2" t="n">
         <v>-0.005531130336122399</v>
       </c>
+      <c r="AA37" s="1" t="n">
+        <v>0.7009</v>
+      </c>
+      <c r="AB37" s="2" t="n">
+        <v>-0.000427837992013802</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3619,6 +3847,12 @@
       <c r="Z38" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA38" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AB38" s="2" t="n">
+        <v>-0.0009514747859182004</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3701,6 +3935,12 @@
       <c r="Z39" s="2" t="n">
         <v>-0.002368373109856122</v>
       </c>
+      <c r="AA39" s="1" t="n">
+        <v>109.78</v>
+      </c>
+      <c r="AB39" s="3" t="n">
+        <v>0.002373995617238907</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3783,6 +4023,12 @@
       <c r="Z40" s="2" t="n">
         <v>-0.02226935312831372</v>
       </c>
+      <c r="AA40" s="1" t="n">
+        <v>0.03661</v>
+      </c>
+      <c r="AB40" s="2" t="n">
+        <v>-0.007321041214750714</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3865,6 +4111,12 @@
       <c r="Z41" s="3" t="n">
         <v>0.003644314868804643</v>
       </c>
+      <c r="AA41" s="1" t="n">
+        <v>0.05496</v>
+      </c>
+      <c r="AB41" s="2" t="n">
+        <v>-0.002178649237472678</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3947,6 +4199,12 @@
       <c r="Z42" s="2" t="n">
         <v>-0.003501013451262296</v>
       </c>
+      <c r="AA42" s="1" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="AB42" s="3" t="n">
+        <v>0.001109467455621344</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4029,6 +4287,12 @@
       <c r="Z43" s="3" t="n">
         <v>0.0007570022710069398</v>
       </c>
+      <c r="AA43" s="1" t="n">
+        <v>0.1325</v>
+      </c>
+      <c r="AB43" s="3" t="n">
+        <v>0.00226928895612704</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4111,6 +4375,12 @@
       <c r="Z44" s="2" t="n">
         <v>-0.001022843504943732</v>
       </c>
+      <c r="AA44" s="1" t="n">
+        <v>0.00586</v>
+      </c>
+      <c r="AB44" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4193,6 +4463,12 @@
       <c r="Z45" s="2" t="n">
         <v>-0.002294035507680111</v>
       </c>
+      <c r="AA45" s="1" t="n">
+        <v>0.0994</v>
+      </c>
+      <c r="AB45" s="2" t="n">
+        <v>-0.006298110566829869</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4275,6 +4551,12 @@
       <c r="Z46" s="2" t="n">
         <v>-0.002512562814070394</v>
       </c>
+      <c r="AA46" s="1" t="n">
+        <v>2.753</v>
+      </c>
+      <c r="AB46" s="2" t="n">
+        <v>-0.009355883411298957</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4357,6 +4639,12 @@
       <c r="Z47" s="2" t="n">
         <v>-0.001072664359861512</v>
       </c>
+      <c r="AA47" s="1" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="AB47" s="2" t="n">
+        <v>-0.0003117530915514184</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4439,6 +4727,12 @@
       <c r="Z48" s="2" t="n">
         <v>-0.003727865796831421</v>
       </c>
+      <c r="AA48" s="1" t="n">
+        <v>0.1065</v>
+      </c>
+      <c r="AB48" s="2" t="n">
+        <v>-0.003741814780168359</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4521,6 +4815,12 @@
       <c r="Z49" s="2" t="n">
         <v>-0.001057598438008502</v>
       </c>
+      <c r="AA49" s="1" t="n">
+        <v>0.24462</v>
+      </c>
+      <c r="AB49" s="2" t="n">
+        <v>-0.003909113119960863</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4603,6 +4903,12 @@
       <c r="Z50" s="2" t="n">
         <v>-0.01022537562604335</v>
       </c>
+      <c r="AA50" s="1" t="n">
+        <v>0.04766</v>
+      </c>
+      <c r="AB50" s="3" t="n">
+        <v>0.004849251528568439</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4685,6 +4991,12 @@
       <c r="Z51" s="2" t="n">
         <v>-0.0002570694087404457</v>
       </c>
+      <c r="AA51" s="1" t="n">
+        <v>3.887</v>
+      </c>
+      <c r="AB51" s="2" t="n">
+        <v>-0.0005142710208279197</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4767,6 +5079,12 @@
       <c r="Z52" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA52" s="1" t="n">
+        <v>0.000229</v>
+      </c>
+      <c r="AB52" s="2" t="n">
+        <v>-0.00434782608695651</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4849,6 +5167,12 @@
       <c r="Z53" s="3" t="n">
         <v>0.001795332136445211</v>
       </c>
+      <c r="AA53" s="1" t="n">
+        <v>0.1675</v>
+      </c>
+      <c r="AB53" s="3" t="n">
+        <v>0.0005973715651136006</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4931,6 +5255,12 @@
       <c r="Z54" s="2" t="n">
         <v>-0.008738781294284417</v>
       </c>
+      <c r="AA54" s="1" t="n">
+        <v>0.04203</v>
+      </c>
+      <c r="AB54" s="3" t="n">
+        <v>0.001429592566118598</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5013,6 +5343,12 @@
       <c r="Z55" s="2" t="n">
         <v>-8.239268352978496e-05</v>
       </c>
+      <c r="AA55" s="1" t="n">
+        <v>0.12301</v>
+      </c>
+      <c r="AB55" s="3" t="n">
+        <v>0.01359591298615688</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5095,6 +5431,12 @@
       <c r="Z56" s="2" t="n">
         <v>-0.008852355358836625</v>
       </c>
+      <c r="AA56" s="1" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="AB56" s="3" t="n">
+        <v>0.002870813397129225</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5177,6 +5519,12 @@
       <c r="Z57" s="2" t="n">
         <v>-0.01036269430051816</v>
       </c>
+      <c r="AA57" s="1" t="n">
+        <v>0.01151</v>
+      </c>
+      <c r="AB57" s="3" t="n">
+        <v>0.004363001745200672</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5259,6 +5607,12 @@
       <c r="Z58" s="2" t="n">
         <v>-0.001008064516129061</v>
       </c>
+      <c r="AA58" s="1" t="n">
+        <v>0.0993</v>
+      </c>
+      <c r="AB58" s="3" t="n">
+        <v>0.002018163471241229</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5341,6 +5695,12 @@
       <c r="Z59" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA59" s="1" t="n">
+        <v>0.00331</v>
+      </c>
+      <c r="AB59" s="2" t="n">
+        <v>-0.003012048192771092</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5423,6 +5783,12 @@
       <c r="Z60" s="3" t="n">
         <v>0.001302083333333371</v>
       </c>
+      <c r="AA60" s="1" t="n">
+        <v>0.1542</v>
+      </c>
+      <c r="AB60" s="3" t="n">
+        <v>0.002600780234070296</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5505,6 +5871,12 @@
       <c r="Z61" s="2" t="n">
         <v>-0.002074427960774434</v>
       </c>
+      <c r="AA61" s="1" t="n">
+        <v>0.15895</v>
+      </c>
+      <c r="AB61" s="3" t="n">
+        <v>0.001259842519685076</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5587,6 +5959,12 @@
       <c r="Z62" s="3" t="n">
         <v>0.0008502196400737494</v>
       </c>
+      <c r="AA62" s="1" t="n">
+        <v>0.7060999999999999</v>
+      </c>
+      <c r="AB62" s="2" t="n">
+        <v>-0.0002831657935722625</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5669,6 +6047,12 @@
       <c r="Z63" s="3" t="n">
         <v>0.005250677506775016</v>
       </c>
+      <c r="AA63" s="1" t="n">
+        <v>5.924</v>
+      </c>
+      <c r="AB63" s="2" t="n">
+        <v>-0.001853411962931631</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5751,6 +6135,12 @@
       <c r="Z64" s="3" t="n">
         <v>0.003229883443336674</v>
       </c>
+      <c r="AA64" s="1" t="n">
+        <v>0.007146</v>
+      </c>
+      <c r="AB64" s="3" t="n">
+        <v>0.0002799552071667691</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5833,6 +6223,12 @@
       <c r="Z65" s="3" t="n">
         <v>0.01875586120662718</v>
       </c>
+      <c r="AA65" s="1" t="n">
+        <v>0.03223</v>
+      </c>
+      <c r="AB65" s="2" t="n">
+        <v>-0.01104633323105244</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5915,6 +6311,12 @@
       <c r="Z66" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA66" s="1" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="AB66" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5997,6 +6399,12 @@
       <c r="Z67" s="3" t="n">
         <v>0.000625782227784662</v>
       </c>
+      <c r="AA67" s="1" t="n">
+        <v>1.615</v>
+      </c>
+      <c r="AB67" s="3" t="n">
+        <v>0.01000625390869294</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6079,6 +6487,12 @@
       <c r="Z68" s="3" t="n">
         <v>0.0007469747522531809</v>
       </c>
+      <c r="AA68" s="1" t="n">
+        <v>2.0178</v>
+      </c>
+      <c r="AB68" s="3" t="n">
+        <v>0.004080414012738847</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6161,6 +6575,12 @@
       <c r="Z69" s="3" t="n">
         <v>0.002925989672977685</v>
       </c>
+      <c r="AA69" s="1" t="n">
+        <v>0.5824</v>
+      </c>
+      <c r="AB69" s="2" t="n">
+        <v>-0.0005148446885189068</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6243,6 +6663,12 @@
       <c r="Z70" s="2" t="n">
         <v>-0.009615384615384625</v>
       </c>
+      <c r="AA70" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="AB70" s="2" t="n">
+        <v>-0.009708737864077679</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6325,6 +6751,12 @@
       <c r="Z71" s="2" t="n">
         <v>-0.002974223397224097</v>
       </c>
+      <c r="AA71" s="1" t="n">
+        <v>0.9083</v>
+      </c>
+      <c r="AB71" s="3" t="n">
+        <v>0.003535520936913027</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6407,6 +6839,12 @@
       <c r="Z72" s="2" t="n">
         <v>-0.002122141004479973</v>
       </c>
+      <c r="AA72" s="1" t="n">
+        <v>0.4233</v>
+      </c>
+      <c r="AB72" s="3" t="n">
+        <v>0.0002362948960302197</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6489,6 +6927,12 @@
       <c r="Z73" s="2" t="n">
         <v>-0.001278363694471025</v>
       </c>
+      <c r="AA73" s="1" t="n">
+        <v>0.09379</v>
+      </c>
+      <c r="AB73" s="3" t="n">
+        <v>0.0004266666666666493</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6571,6 +7015,12 @@
       <c r="Z74" s="2" t="n">
         <v>-0.005046111014442341</v>
       </c>
+      <c r="AA74" s="1" t="n">
+        <v>1.1441</v>
+      </c>
+      <c r="AB74" s="3" t="n">
+        <v>0.0004372158097236315</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6653,6 +7103,12 @@
       <c r="Z75" s="2" t="n">
         <v>-0.0006293266205162404</v>
       </c>
+      <c r="AA75" s="1" t="n">
+        <v>0.01592</v>
+      </c>
+      <c r="AB75" s="3" t="n">
+        <v>0.002518891687657547</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6735,6 +7191,12 @@
       <c r="Z76" s="2" t="n">
         <v>-7.888923950781004e-05</v>
       </c>
+      <c r="AA76" s="1" t="n">
+        <v>0.12256</v>
+      </c>
+      <c r="AB76" s="2" t="n">
+        <v>-0.03305719921104536</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6817,6 +7279,12 @@
       <c r="Z77" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA77" s="1" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="AB77" s="3" t="n">
+        <v>0.00341296928327643</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6899,6 +7367,12 @@
       <c r="Z78" s="2" t="n">
         <v>-0.002967359050445052</v>
       </c>
+      <c r="AA78" s="1" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="AB78" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6981,6 +7455,12 @@
       <c r="Z79" s="3" t="n">
         <v>0.00216992154899015</v>
       </c>
+      <c r="AA79" s="1" t="n">
+        <v>0.006021</v>
+      </c>
+      <c r="AB79" s="3" t="n">
+        <v>0.002831445702864844</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7063,6 +7543,12 @@
       <c r="Z80" s="3" t="n">
         <v>0.005649717514124282</v>
       </c>
+      <c r="AA80" s="1" t="n">
+        <v>0.007934</v>
+      </c>
+      <c r="AB80" s="2" t="n">
+        <v>-0.009488139825218437</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7145,6 +7631,12 @@
       <c r="Z81" s="2" t="n">
         <v>-0.0005595970900952189</v>
       </c>
+      <c r="AA81" s="1" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="AB81" s="3" t="n">
+        <v>0.003359462486002367</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7227,6 +7719,12 @@
       <c r="Z82" s="3" t="n">
         <v>0.003719776813391131</v>
       </c>
+      <c r="AA82" s="1" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="AB82" s="3" t="n">
+        <v>0.00370599135268695</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7309,6 +7807,12 @@
       <c r="Z83" s="2" t="n">
         <v>-0.001584399756246179</v>
       </c>
+      <c r="AA83" s="1" t="n">
+        <v>8.193</v>
+      </c>
+      <c r="AB83" s="3" t="n">
+        <v>0.0001220703124999323</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7391,6 +7895,12 @@
       <c r="Z84" s="3" t="n">
         <v>0.0006495523736903562</v>
       </c>
+      <c r="AA84" s="1" t="n">
+        <v>349.69</v>
+      </c>
+      <c r="AB84" s="2" t="n">
+        <v>-0.01306728381124406</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7473,6 +7983,12 @@
       <c r="Z85" s="2" t="n">
         <v>-0.001473477406679747</v>
       </c>
+      <c r="AA85" s="1" t="n">
+        <v>0.004069</v>
+      </c>
+      <c r="AB85" s="3" t="n">
+        <v>0.0007378258730938344</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7555,6 +8071,12 @@
       <c r="Z86" s="2" t="n">
         <v>-0.002593242315612897</v>
       </c>
+      <c r="AA86" s="1" t="n">
+        <v>0.13114</v>
+      </c>
+      <c r="AB86" s="3" t="n">
+        <v>0.00282939512120524</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7637,6 +8159,12 @@
       <c r="Z87" s="3" t="n">
         <v>0.003161222339304585</v>
       </c>
+      <c r="AA87" s="1" t="n">
+        <v>0.01841</v>
+      </c>
+      <c r="AB87" s="2" t="n">
+        <v>-0.03308823529411775</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7719,6 +8247,12 @@
       <c r="Z88" s="2" t="n">
         <v>-0.001765225066195942</v>
       </c>
+      <c r="AA88" s="1" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="AB88" s="2" t="n">
+        <v>-0.001768346595932804</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7801,6 +8335,12 @@
       <c r="Z89" s="2" t="n">
         <v>-0.001356852103120799</v>
       </c>
+      <c r="AA89" s="1" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="AB89" s="2" t="n">
+        <v>-0.003057065217391345</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7883,6 +8423,12 @@
       <c r="Z90" s="2" t="n">
         <v>-0.001945525291828796</v>
       </c>
+      <c r="AA90" s="1" t="n">
+        <v>0.2569</v>
+      </c>
+      <c r="AB90" s="3" t="n">
+        <v>0.001559454191033183</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7965,6 +8511,12 @@
       <c r="Z91" s="2" t="n">
         <v>-0.003205699020480848</v>
       </c>
+      <c r="AA91" s="1" t="n">
+        <v>0.05589</v>
+      </c>
+      <c r="AB91" s="2" t="n">
+        <v>-0.001429337144898995</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8047,6 +8599,12 @@
       <c r="Z92" s="2" t="n">
         <v>-0.002810695837131599</v>
       </c>
+      <c r="AA92" s="1" t="n">
+        <v>1.3134</v>
+      </c>
+      <c r="AB92" s="3" t="n">
+        <v>0.0005332520758740938</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8129,6 +8687,12 @@
       <c r="Z93" s="3" t="n">
         <v>0.001426081445095971</v>
       </c>
+      <c r="AA93" s="1" t="n">
+        <v>0.06319</v>
+      </c>
+      <c r="AB93" s="2" t="n">
+        <v>-0.000158227848101424</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8211,6 +8775,12 @@
       <c r="Z94" s="2" t="n">
         <v>-0.006718924972004593</v>
       </c>
+      <c r="AA94" s="1" t="n">
+        <v>0.008840000000000001</v>
+      </c>
+      <c r="AB94" s="2" t="n">
+        <v>-0.003382187147688701</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8293,6 +8863,12 @@
       <c r="Z95" s="2" t="n">
         <v>-0.0002999400119975675</v>
       </c>
+      <c r="AA95" s="1" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AB95" s="3" t="n">
+        <v>0.001200120012001234</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8375,6 +8951,12 @@
       <c r="Z96" s="2" t="n">
         <v>-0.002659574468085152</v>
       </c>
+      <c r="AA96" s="1" t="n">
+        <v>0.02248</v>
+      </c>
+      <c r="AB96" s="2" t="n">
+        <v>-0.0008888888888888527</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8457,6 +9039,12 @@
       <c r="Z97" s="2" t="n">
         <v>-0.000306654400490586</v>
       </c>
+      <c r="AA97" s="1" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="AB97" s="2" t="n">
+        <v>-0.0009202453987730409</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8539,6 +9127,12 @@
       <c r="Z98" s="2" t="n">
         <v>-0.001800180018001802</v>
       </c>
+      <c r="AA98" s="1" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="AB98" s="3" t="n">
+        <v>0.003606853020739408</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8621,6 +9215,12 @@
       <c r="Z99" s="3" t="n">
         <v>0.0006648936170212034</v>
       </c>
+      <c r="AA99" s="1" t="n">
+        <v>3.021</v>
+      </c>
+      <c r="AB99" s="3" t="n">
+        <v>0.003654485049833928</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8703,6 +9303,12 @@
       <c r="Z100" s="2" t="n">
         <v>-0.0008748906386702317</v>
       </c>
+      <c r="AA100" s="1" t="n">
+        <v>0.03422</v>
+      </c>
+      <c r="AB100" s="2" t="n">
+        <v>-0.001167542323409176</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8785,6 +9391,12 @@
       <c r="Z101" s="2" t="n">
         <v>-0.001644736842105326</v>
       </c>
+      <c r="AA101" s="1" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="AB101" s="3" t="n">
+        <v>0.002745744096650256</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8867,6 +9479,12 @@
       <c r="Z102" s="3" t="n">
         <v>0.01148105625717557</v>
       </c>
+      <c r="AA102" s="1" t="n">
+        <v>0.006944</v>
+      </c>
+      <c r="AB102" s="2" t="n">
+        <v>-0.01475595913734392</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8949,6 +9567,12 @@
       <c r="Z103" s="3" t="n">
         <v>0.001958126223828758</v>
       </c>
+      <c r="AA103" s="1" t="n">
+        <v>0.06585000000000001</v>
+      </c>
+      <c r="AB103" s="2" t="n">
+        <v>-0.0100721587492482</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9031,6 +9655,12 @@
       <c r="Z104" s="3" t="n">
         <v>0.003653190452995619</v>
       </c>
+      <c r="AA104" s="1" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="AB104" s="2" t="n">
+        <v>-0.004125212327105156</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9113,6 +9743,12 @@
       <c r="Z105" s="2" t="n">
         <v>-0.0005580357142857767</v>
       </c>
+      <c r="AA105" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB105" s="3" t="n">
+        <v>0.00502512562814077</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9195,6 +9831,12 @@
       <c r="Z106" s="2" t="n">
         <v>-0.003517283201940721</v>
       </c>
+      <c r="AA106" s="1" t="n">
+        <v>0.008122000000000001</v>
+      </c>
+      <c r="AB106" s="2" t="n">
+        <v>-0.01144109055501444</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9277,6 +9919,12 @@
       <c r="Z107" s="3" t="n">
         <v>0.003309431880860509</v>
       </c>
+      <c r="AA107" s="1" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="AB107" s="2" t="n">
+        <v>-0.002748763056624597</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9359,6 +10007,12 @@
       <c r="Z108" s="2" t="n">
         <v>-0.001857872735717689</v>
       </c>
+      <c r="AA108" s="1" t="n">
+        <v>0.02152</v>
+      </c>
+      <c r="AB108" s="3" t="n">
+        <v>0.001395998138669253</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9441,6 +10095,12 @@
       <c r="Z109" s="3" t="n">
         <v>0.0009012256669070193</v>
       </c>
+      <c r="AA109" s="1" t="n">
+        <v>0.05551</v>
+      </c>
+      <c r="AB109" s="2" t="n">
+        <v>-0.0003601656762111674</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9523,6 +10183,12 @@
       <c r="Z110" s="2" t="n">
         <v>-0.006999049511794739</v>
       </c>
+      <c r="AA110" s="1" t="n">
+        <v>0.11534</v>
+      </c>
+      <c r="AB110" s="3" t="n">
+        <v>0.003654716324399615</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9605,6 +10271,12 @@
       <c r="Z111" s="2" t="n">
         <v>-0.002763561924257855</v>
       </c>
+      <c r="AA111" s="1" t="n">
+        <v>0.09736</v>
+      </c>
+      <c r="AB111" s="2" t="n">
+        <v>-0.0007184645386431347</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9687,6 +10359,12 @@
       <c r="Z112" s="3" t="n">
         <v>0.00268817204301083</v>
       </c>
+      <c r="AA112" s="1" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="AB112" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9769,6 +10447,12 @@
       <c r="Z113" s="2" t="n">
         <v>-0.0006123698714023729</v>
       </c>
+      <c r="AA113" s="1" t="n">
+        <v>0.09769</v>
+      </c>
+      <c r="AB113" s="2" t="n">
+        <v>-0.002348856209150267</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9851,6 +10535,12 @@
       <c r="Z114" s="2" t="n">
         <v>-0.001150086256469263</v>
       </c>
+      <c r="AA114" s="1" t="n">
+        <v>0.001743</v>
+      </c>
+      <c r="AB114" s="3" t="n">
+        <v>0.003454231433506004</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9933,6 +10623,12 @@
       <c r="Z115" s="2" t="n">
         <v>-0.0002395018361807177</v>
       </c>
+      <c r="AA115" s="1" t="n">
+        <v>1.2501</v>
+      </c>
+      <c r="AB115" s="2" t="n">
+        <v>-0.001756767547712193</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10015,6 +10711,12 @@
       <c r="Z116" s="2" t="n">
         <v>-0.002115954295387221</v>
       </c>
+      <c r="AA116" s="1" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="AB116" s="3" t="n">
+        <v>0.0004240882103477056</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10097,6 +10799,12 @@
       <c r="Z117" s="2" t="n">
         <v>-0.003086419753086351</v>
       </c>
+      <c r="AA117" s="1" t="n">
+        <v>0.06122</v>
+      </c>
+      <c r="AB117" s="2" t="n">
+        <v>-0.002444190972788077</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10179,6 +10887,12 @@
       <c r="Z118" s="3" t="n">
         <v>0.004600874166091529</v>
       </c>
+      <c r="AA118" s="1" t="n">
+        <v>0.04389</v>
+      </c>
+      <c r="AB118" s="3" t="n">
+        <v>0.005037783375314815</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10261,6 +10975,12 @@
       <c r="Z119" s="3" t="n">
         <v>0.007565522831667184</v>
       </c>
+      <c r="AA119" s="1" t="n">
+        <v>0.003685</v>
+      </c>
+      <c r="AB119" s="2" t="n">
+        <v>-0.01179941002949858</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10343,6 +11063,12 @@
       <c r="Z120" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA120" s="1" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="AB120" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10425,6 +11151,12 @@
       <c r="Z121" s="2" t="n">
         <v>-0.001011804384485555</v>
       </c>
+      <c r="AA121" s="1" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AB121" s="3" t="n">
+        <v>0.002700877785280106</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10507,6 +11239,12 @@
       <c r="Z122" s="3" t="n">
         <v>0.0001763046544428579</v>
       </c>
+      <c r="AA122" s="1" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="AB122" s="3" t="n">
+        <v>0.0003525471531816992</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10589,6 +11327,12 @@
       <c r="Z123" s="2" t="n">
         <v>-0.008475157836947595</v>
       </c>
+      <c r="AA123" s="1" t="n">
+        <v>0.028706</v>
+      </c>
+      <c r="AB123" s="2" t="n">
+        <v>-0.006609682666020701</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10671,6 +11415,12 @@
       <c r="Z124" s="3" t="n">
         <v>0.002685078634445747</v>
       </c>
+      <c r="AA124" s="1" t="n">
+        <v>0.07883999999999999</v>
+      </c>
+      <c r="AB124" s="3" t="n">
+        <v>0.005355776587605073</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10753,6 +11503,12 @@
       <c r="Z125" s="3" t="n">
         <v>0.0009671179883944776</v>
       </c>
+      <c r="AA125" s="1" t="n">
+        <v>0.10351</v>
+      </c>
+      <c r="AB125" s="3" t="n">
+        <v>9.661835748801933e-05</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10835,6 +11591,12 @@
       <c r="Z126" s="2" t="n">
         <v>-0.00709749719835634</v>
       </c>
+      <c r="AA126" s="1" t="n">
+        <v>0.02648</v>
+      </c>
+      <c r="AB126" s="2" t="n">
+        <v>-0.003762227238525184</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10917,6 +11679,12 @@
       <c r="Z127" s="2" t="n">
         <v>-0.001366742596811036</v>
       </c>
+      <c r="AA127" s="1" t="n">
+        <v>0.02191</v>
+      </c>
+      <c r="AB127" s="2" t="n">
+        <v>-0.0004562043795620252</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10999,6 +11767,12 @@
       <c r="Z128" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA128" s="1" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="AB128" s="2" t="n">
+        <v>-0.0006191950464397322</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11081,6 +11855,12 @@
       <c r="Z129" s="3" t="n">
         <v>0.002795834207031409</v>
       </c>
+      <c r="AA129" s="1" t="n">
+        <v>0.14415</v>
+      </c>
+      <c r="AB129" s="3" t="n">
+        <v>0.004739666829302391</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11163,6 +11943,12 @@
       <c r="Z130" s="2" t="n">
         <v>-0.01261128992790867</v>
       </c>
+      <c r="AA130" s="1" t="n">
+        <v>0.052832</v>
+      </c>
+      <c r="AB130" s="3" t="n">
+        <v>0.007148712278628217</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11245,6 +12031,12 @@
       <c r="Z131" s="2" t="n">
         <v>-0.0006117704637219442</v>
       </c>
+      <c r="AA131" s="1" t="n">
+        <v>0.08155999999999999</v>
+      </c>
+      <c r="AB131" s="2" t="n">
+        <v>-0.001469147894221462</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11327,6 +12119,12 @@
       <c r="Z132" s="3" t="n">
         <v>0.001142857142857176</v>
       </c>
+      <c r="AA132" s="1" t="n">
+        <v>0.0877</v>
+      </c>
+      <c r="AB132" s="3" t="n">
+        <v>0.001141552511415558</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11409,6 +12207,12 @@
       <c r="Z133" s="3" t="n">
         <v>0.002075406433759908</v>
       </c>
+      <c r="AA133" s="1" t="n">
+        <v>0.5803</v>
+      </c>
+      <c r="AB133" s="3" t="n">
+        <v>0.001553331032102195</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11491,6 +12295,12 @@
       <c r="Z134" s="2" t="n">
         <v>-0.004694835680751099</v>
       </c>
+      <c r="AA134" s="1" t="n">
+        <v>0.02979</v>
+      </c>
+      <c r="AB134" s="3" t="n">
+        <v>0.003706199460916408</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11573,6 +12383,12 @@
       <c r="Z135" s="3" t="n">
         <v>0.000568181818181795</v>
       </c>
+      <c r="AA135" s="1" t="n">
+        <v>0.01756</v>
+      </c>
+      <c r="AB135" s="2" t="n">
+        <v>-0.002839295854628133</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11655,6 +12471,12 @@
       <c r="Z136" s="3" t="n">
         <v>0.0005393743257820707</v>
       </c>
+      <c r="AA136" s="1" t="n">
+        <v>0.03702</v>
+      </c>
+      <c r="AB136" s="2" t="n">
+        <v>-0.002156334231806029</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11737,6 +12559,12 @@
       <c r="Z137" s="3" t="n">
         <v>0.0048059149722735</v>
       </c>
+      <c r="AA137" s="1" t="n">
+        <v>0.02705</v>
+      </c>
+      <c r="AB137" s="2" t="n">
+        <v>-0.004782928623988159</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11819,6 +12647,12 @@
       <c r="Z138" s="3" t="n">
         <v>0.007527733755942998</v>
       </c>
+      <c r="AA138" s="1" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="AB138" s="3" t="n">
+        <v>0.0007864726700746282</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11901,6 +12735,12 @@
       <c r="Z139" s="3" t="n">
         <v>0.006739679865206421</v>
       </c>
+      <c r="AA139" s="1" t="n">
+        <v>0.01198</v>
+      </c>
+      <c r="AB139" s="3" t="n">
+        <v>0.002510460251045923</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11983,6 +12823,12 @@
       <c r="Z140" s="3" t="n">
         <v>0.005387205387205401</v>
       </c>
+      <c r="AA140" s="1" t="n">
+        <v>0.01486</v>
+      </c>
+      <c r="AB140" s="2" t="n">
+        <v>-0.004688546550569364</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12065,6 +12911,12 @@
       <c r="Z141" s="3" t="n">
         <v>0.0004957858205254784</v>
       </c>
+      <c r="AA141" s="1" t="n">
+        <v>16.115</v>
+      </c>
+      <c r="AB141" s="2" t="n">
+        <v>-0.001796333002973236</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12147,6 +12999,12 @@
       <c r="Z142" s="3" t="n">
         <v>0.0007999999999999674</v>
       </c>
+      <c r="AA142" s="1" t="n">
+        <v>0.01259</v>
+      </c>
+      <c r="AB142" s="3" t="n">
+        <v>0.006394884092725836</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12229,6 +13087,12 @@
       <c r="Z143" s="3" t="n">
         <v>0.00940203083866116</v>
       </c>
+      <c r="AA143" s="1" t="n">
+        <v>0.02701</v>
+      </c>
+      <c r="AB143" s="3" t="n">
+        <v>0.006333830104321908</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12311,6 +13175,12 @@
       <c r="Z144" s="2" t="n">
         <v>-0.003605514316012652</v>
       </c>
+      <c r="AA144" s="1" t="n">
+        <v>0.004735</v>
+      </c>
+      <c r="AB144" s="3" t="n">
+        <v>0.007875691783737699</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12393,6 +13263,12 @@
       <c r="Z145" s="2" t="n">
         <v>-0.005278116118554591</v>
       </c>
+      <c r="AA145" s="1" t="n">
+        <v>1.9589</v>
+      </c>
+      <c r="AB145" s="2" t="n">
+        <v>-0.0005612244897958566</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12475,6 +13351,12 @@
       <c r="Z146" s="2" t="n">
         <v>-0.001294777729822994</v>
       </c>
+      <c r="AA146" s="1" t="n">
+        <v>0.02319</v>
+      </c>
+      <c r="AB146" s="3" t="n">
+        <v>0.002160760587726792</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12557,6 +13439,12 @@
       <c r="Z147" s="3" t="n">
         <v>0.005802276277616521</v>
       </c>
+      <c r="AA147" s="1" t="n">
+        <v>0.09007</v>
+      </c>
+      <c r="AB147" s="2" t="n">
+        <v>-0.0007765697803416976</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12639,6 +13527,12 @@
       <c r="Z148" s="2" t="n">
         <v>-0.004197610590894467</v>
       </c>
+      <c r="AA148" s="1" t="n">
+        <v>0.06211</v>
+      </c>
+      <c r="AB148" s="3" t="n">
+        <v>0.006971465629053175</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -12721,6 +13615,12 @@
       <c r="Z149" s="2" t="n">
         <v>-0.002020202020202054</v>
       </c>
+      <c r="AA149" s="1" t="n">
+        <v>0.05931</v>
+      </c>
+      <c r="AB149" s="3" t="n">
+        <v>0.0005060728744939651</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -12803,6 +13703,12 @@
       <c r="Z150" s="2" t="n">
         <v>-0.007566204287515766</v>
       </c>
+      <c r="AA150" s="1" t="n">
+        <v>0.24481</v>
+      </c>
+      <c r="AB150" s="3" t="n">
+        <v>0.003443046276181528</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -12885,6 +13791,12 @@
       <c r="Z151" s="3" t="n">
         <v>0.01201853460758746</v>
       </c>
+      <c r="AA151" s="1" t="n">
+        <v>7.020999999999999e-05</v>
+      </c>
+      <c r="AB151" s="3" t="n">
+        <v>0.004578623551294849</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12967,6 +13879,12 @@
       <c r="Z152" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA152" s="1" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="AB152" s="3" t="n">
+        <v>0.0006744604316547268</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -13049,6 +13967,12 @@
       <c r="Z153" s="2" t="n">
         <v>-0.000975609756097634</v>
       </c>
+      <c r="AA153" s="1" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="AB153" s="3" t="n">
+        <v>0.001953125000000147</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -13131,6 +14055,12 @@
       <c r="Z154" s="3" t="n">
         <v>0.004962779156327456</v>
       </c>
+      <c r="AA154" s="1" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="AB154" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -13213,6 +14143,12 @@
       <c r="Z155" s="2" t="n">
         <v>-0.002162629757785469</v>
       </c>
+      <c r="AA155" s="1" t="n">
+        <v>0.2302</v>
+      </c>
+      <c r="AB155" s="2" t="n">
+        <v>-0.002167316861725186</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -13295,6 +14231,12 @@
       <c r="Z156" s="2" t="n">
         <v>-0.003217821782178173</v>
       </c>
+      <c r="AA156" s="1" t="n">
+        <v>0.08078</v>
+      </c>
+      <c r="AB156" s="3" t="n">
+        <v>0.002979885771045494</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -13377,6 +14319,12 @@
       <c r="Z157" s="3" t="n">
         <v>0.002012512578203683</v>
       </c>
+      <c r="AA157" s="1" t="n">
+        <v>0.22991</v>
+      </c>
+      <c r="AB157" s="3" t="n">
+        <v>0.003842291402872951</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -13459,6 +14407,12 @@
       <c r="Z158" s="2" t="n">
         <v>-0.0003969829297339777</v>
       </c>
+      <c r="AA158" s="1" t="n">
+        <v>0.2536</v>
+      </c>
+      <c r="AB158" s="3" t="n">
+        <v>0.007148530579825132</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -13541,6 +14495,12 @@
       <c r="Z159" s="3" t="n">
         <v>0.0006811989100818201</v>
       </c>
+      <c r="AA159" s="1" t="n">
+        <v>2.941</v>
+      </c>
+      <c r="AB159" s="3" t="n">
+        <v>0.001021102791014183</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -13623,6 +14583,12 @@
       <c r="Z160" s="2" t="n">
         <v>-0.002006018054162406</v>
       </c>
+      <c r="AA160" s="1" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="AB160" s="2" t="n">
+        <v>-0.005025125628140708</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13705,6 +14671,12 @@
       <c r="Z161" s="2" t="n">
         <v>-0.001894964807796443</v>
       </c>
+      <c r="AA161" s="1" t="n">
+        <v>0.14749</v>
+      </c>
+      <c r="AB161" s="3" t="n">
+        <v>6.780580417690534e-05</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -13787,6 +14759,12 @@
       <c r="Z162" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA162" s="1" t="n">
+        <v>0.003271</v>
+      </c>
+      <c r="AB162" s="2" t="n">
+        <v>-0.0006110601894286073</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -13869,6 +14847,12 @@
       <c r="Z163" s="2" t="n">
         <v>-0.0002002402883460418</v>
       </c>
+      <c r="AA163" s="1" t="n">
+        <v>0.00502</v>
+      </c>
+      <c r="AB163" s="3" t="n">
+        <v>0.005407570598838397</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -13951,6 +14935,12 @@
       <c r="Z164" s="3" t="n">
         <v>0.003147953830010583</v>
       </c>
+      <c r="AA164" s="1" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="AB164" s="2" t="n">
+        <v>-0.00104602510460254</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -14033,6 +15023,12 @@
       <c r="Z165" s="2" t="n">
         <v>-0.0006546644844516464</v>
       </c>
+      <c r="AA165" s="1" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="AB165" s="3" t="n">
+        <v>0.004585653455617284</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -14115,6 +15111,12 @@
       <c r="Z166" s="2" t="n">
         <v>-0.0007207207207206414</v>
       </c>
+      <c r="AA166" s="1" t="n">
+        <v>1.3873</v>
+      </c>
+      <c r="AB166" s="3" t="n">
+        <v>0.0005769924269743324</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -14197,6 +15199,12 @@
       <c r="Z167" s="3" t="n">
         <v>0.001440403312927661</v>
       </c>
+      <c r="AA167" s="1" t="n">
+        <v>0.2771</v>
+      </c>
+      <c r="AB167" s="2" t="n">
+        <v>-0.003595828838547288</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -14279,6 +15287,12 @@
       <c r="Z168" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA168" s="1" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AB168" s="3" t="n">
+        <v>0.003215434083601289</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -14361,6 +15375,12 @@
       <c r="Z169" s="3" t="n">
         <v>0.00234978180597518</v>
       </c>
+      <c r="AA169" s="1" t="n">
+        <v>0.02995</v>
+      </c>
+      <c r="AB169" s="3" t="n">
+        <v>0.003014065639651701</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -14443,6 +15463,12 @@
       <c r="Z170" s="3" t="n">
         <v>0.002544529262086491</v>
       </c>
+      <c r="AA170" s="1" t="n">
+        <v>0.04322</v>
+      </c>
+      <c r="AB170" s="2" t="n">
+        <v>-0.002768804799261539</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -14525,6 +15551,12 @@
       <c r="Z171" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA171" s="1" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="AB171" s="2" t="n">
+        <v>-0.006024096385542133</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -14607,6 +15639,12 @@
       <c r="Z172" s="3" t="n">
         <v>0.007633587786259598</v>
       </c>
+      <c r="AA172" s="1" t="n">
+        <v>1.34e-05</v>
+      </c>
+      <c r="AB172" s="3" t="n">
+        <v>0.01515151515151513</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -14689,6 +15727,12 @@
       <c r="Z173" s="3" t="n">
         <v>0.000950118764845567</v>
       </c>
+      <c r="AA173" s="1" t="n">
+        <v>0.02105</v>
+      </c>
+      <c r="AB173" s="2" t="n">
+        <v>-0.0009492168960607113</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -14771,6 +15815,12 @@
       <c r="Z174" s="2" t="n">
         <v>-0.0006599208095029091</v>
       </c>
+      <c r="AA174" s="1" t="n">
+        <v>0.09009</v>
+      </c>
+      <c r="AB174" s="2" t="n">
+        <v>-0.008474576271186363</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -14853,6 +15903,12 @@
       <c r="Z175" s="3" t="n">
         <v>0.0005511160099200275</v>
       </c>
+      <c r="AA175" s="1" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="AB175" s="2" t="n">
+        <v>-0.003580280914348576</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -14935,6 +15991,12 @@
       <c r="Z176" s="2" t="n">
         <v>-0.002333177788147523</v>
       </c>
+      <c r="AA176" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="AB176" s="2" t="n">
+        <v>-0.001403180542563086</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -15017,6 +16079,12 @@
       <c r="Z177" s="3" t="n">
         <v>0.00636942675159254</v>
       </c>
+      <c r="AA177" s="1" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="AB177" s="2" t="n">
+        <v>-0.01139240506329122</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -15099,6 +16167,12 @@
       <c r="Z178" s="2" t="n">
         <v>-0.003125000000000076</v>
       </c>
+      <c r="AA178" s="1" t="n">
+        <v>0.000958</v>
+      </c>
+      <c r="AB178" s="3" t="n">
+        <v>0.001044932079414864</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -15181,6 +16255,12 @@
       <c r="Z179" s="2" t="n">
         <v>-4.400246413803573e-05</v>
       </c>
+      <c r="AA179" s="1" t="n">
+        <v>0.022715</v>
+      </c>
+      <c r="AB179" s="2" t="n">
+        <v>-0.0004400440044004221</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -15263,6 +16343,12 @@
       <c r="Z180" s="2" t="n">
         <v>-0.001213297743266387</v>
       </c>
+      <c r="AA180" s="1" t="n">
+        <v>4.111</v>
+      </c>
+      <c r="AB180" s="2" t="n">
+        <v>-0.001214771622934862</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -15345,6 +16431,12 @@
       <c r="Z181" s="2" t="n">
         <v>-0.004981106149089683</v>
       </c>
+      <c r="AA181" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB181" s="2" t="n">
+        <v>-0.01605385810460916</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -15427,6 +16519,12 @@
       <c r="Z182" s="3" t="n">
         <v>0.01334661354581667</v>
       </c>
+      <c r="AA182" s="1" t="n">
+        <v>0.0506</v>
+      </c>
+      <c r="AB182" s="2" t="n">
+        <v>-0.005307646943188508</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -15509,6 +16607,12 @@
       <c r="Z183" s="2" t="n">
         <v>-0.002376165234874776</v>
       </c>
+      <c r="AA183" s="1" t="n">
+        <v>5.457</v>
+      </c>
+      <c r="AB183" s="2" t="n">
+        <v>-0.0001832172957127765</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -15591,6 +16695,12 @@
       <c r="Z184" s="3" t="n">
         <v>0.0045233124565067</v>
       </c>
+      <c r="AA184" s="1" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="AB184" s="2" t="n">
+        <v>-0.001039140976792557</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -15673,6 +16783,12 @@
       <c r="Z185" s="2" t="n">
         <v>-0.00741918388977219</v>
       </c>
+      <c r="AA185" s="1" t="n">
+        <v>0.01889</v>
+      </c>
+      <c r="AB185" s="3" t="n">
+        <v>0.008542445274959979</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -15755,6 +16871,12 @@
       <c r="Z186" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA186" s="1" t="n">
+        <v>3.09e-05</v>
+      </c>
+      <c r="AB186" s="2" t="n">
+        <v>-0.006430868167202512</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -15837,6 +16959,12 @@
       <c r="Z187" s="2" t="n">
         <v>-0.001885606536769469</v>
       </c>
+      <c r="AA187" s="1" t="n">
+        <v>0.01583</v>
+      </c>
+      <c r="AB187" s="2" t="n">
+        <v>-0.003148614609571661</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -15919,6 +17047,12 @@
       <c r="Z188" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA188" s="1" t="n">
+        <v>0.04061</v>
+      </c>
+      <c r="AB188" s="3" t="n">
+        <v>0.001232741617357037</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -16001,6 +17135,12 @@
       <c r="Z189" s="3" t="n">
         <v>0.003632236095346286</v>
       </c>
+      <c r="AA189" s="1" t="n">
+        <v>0.0004436</v>
+      </c>
+      <c r="AB189" s="3" t="n">
+        <v>0.003392897534494418</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -16083,6 +17223,12 @@
       <c r="Z190" s="2" t="n">
         <v>-0.009381663113006311</v>
       </c>
+      <c r="AA190" s="1" t="n">
+        <v>0.02325</v>
+      </c>
+      <c r="AB190" s="3" t="n">
+        <v>0.0008609556607834345</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -16165,6 +17311,12 @@
       <c r="Z191" s="3" t="n">
         <v>0.003182686187142039</v>
       </c>
+      <c r="AA191" s="1" t="n">
+        <v>0.01575</v>
+      </c>
+      <c r="AB191" s="2" t="n">
+        <v>-0.0006345177664974361</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -16247,6 +17399,12 @@
       <c r="Z192" s="3" t="n">
         <v>0.002503128911138946</v>
       </c>
+      <c r="AA192" s="1" t="n">
+        <v>0.05582</v>
+      </c>
+      <c r="AB192" s="2" t="n">
+        <v>-0.004458712323880867</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -16329,6 +17487,12 @@
       <c r="Z193" s="3" t="n">
         <v>0.0005350454788656447</v>
       </c>
+      <c r="AA193" s="1" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="AB193" s="3" t="n">
+        <v>0.002139037433155141</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -16411,6 +17575,12 @@
       <c r="Z194" s="3" t="n">
         <v>0.001560874089490051</v>
       </c>
+      <c r="AA194" s="1" t="n">
+        <v>0.01926</v>
+      </c>
+      <c r="AB194" s="3" t="n">
+        <v>0.0005194805194804983</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -16493,6 +17663,12 @@
       <c r="Z195" s="2" t="n">
         <v>-0.001635131978509644</v>
       </c>
+      <c r="AA195" s="1" t="n">
+        <v>0.4236</v>
+      </c>
+      <c r="AB195" s="2" t="n">
+        <v>-0.008890968647636934</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -16575,6 +17751,12 @@
       <c r="Z196" s="2" t="n">
         <v>-0.001623376623376557</v>
       </c>
+      <c r="AA196" s="1" t="n">
+        <v>0.01239</v>
+      </c>
+      <c r="AB196" s="3" t="n">
+        <v>0.007317073170731691</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -16657,6 +17839,12 @@
       <c r="Z197" s="3" t="n">
         <v>0.001078283372870421</v>
       </c>
+      <c r="AA197" s="1" t="n">
+        <v>0.04627</v>
+      </c>
+      <c r="AB197" s="2" t="n">
+        <v>-0.003231365790607589</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -16739,6 +17927,12 @@
       <c r="Z198" s="3" t="n">
         <v>0.0005866249511147399</v>
       </c>
+      <c r="AA198" s="1" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="AB198" s="2" t="n">
+        <v>-0.001367989056087617</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -16821,6 +18015,12 @@
       <c r="Z199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA199" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB199" s="2" t="n">
+        <v>-0.01136363636363637</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -16903,6 +18103,12 @@
       <c r="Z200" s="2" t="n">
         <v>-0.002684563758389324</v>
       </c>
+      <c r="AA200" s="1" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="AB200" s="3" t="n">
+        <v>0.0006729475100941983</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -16985,6 +18191,12 @@
       <c r="Z201" s="3" t="n">
         <v>0.001048218029350093</v>
       </c>
+      <c r="AA201" s="1" t="n">
+        <v>0.00572</v>
+      </c>
+      <c r="AB201" s="2" t="n">
+        <v>-0.001745200698080208</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -17067,6 +18279,12 @@
       <c r="Z202" s="2" t="n">
         <v>-0.003245629219317928</v>
       </c>
+      <c r="AA202" s="1" t="n">
+        <v>0.023102</v>
+      </c>
+      <c r="AB202" s="3" t="n">
+        <v>0.002995701819129059</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -17149,6 +18367,12 @@
       <c r="Z203" s="2" t="n">
         <v>-0.003663003663003768</v>
       </c>
+      <c r="AA203" s="1" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="AB203" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -17231,6 +18455,12 @@
       <c r="Z204" s="2" t="n">
         <v>-0.001787842669844981</v>
       </c>
+      <c r="AA204" s="1" t="n">
+        <v>0.03344</v>
+      </c>
+      <c r="AB204" s="2" t="n">
+        <v>-0.001791044776119537</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -17313,6 +18543,12 @@
       <c r="Z205" s="3" t="n">
         <v>0.002145922746781197</v>
       </c>
+      <c r="AA205" s="1" t="n">
+        <v>4.198</v>
+      </c>
+      <c r="AB205" s="2" t="n">
+        <v>-0.001189626457292385</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -17395,6 +18631,12 @@
       <c r="Z206" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA206" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB206" s="3" t="n">
+        <v>0.002785515320334264</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -17477,6 +18719,12 @@
       <c r="Z207" s="3" t="n">
         <v>0.03965065502183417</v>
       </c>
+      <c r="AA207" s="1" t="n">
+        <v>0.0012066</v>
+      </c>
+      <c r="AB207" s="3" t="n">
+        <v>0.01360887096774181</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -17559,6 +18807,12 @@
       <c r="Z208" s="2" t="n">
         <v>-0.000962993534186279</v>
       </c>
+      <c r="AA208" s="1" t="n">
+        <v>0.00717</v>
+      </c>
+      <c r="AB208" s="2" t="n">
+        <v>-0.01266868631231067</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -17641,6 +18895,12 @@
       <c r="Z209" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA209" s="1" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="AB209" s="3" t="n">
+        <v>0.003355704697986557</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -17723,6 +18983,12 @@
       <c r="Z210" s="2" t="n">
         <v>-0.001539645881447098</v>
       </c>
+      <c r="AA210" s="1" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="AB210" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -17805,6 +19071,12 @@
       <c r="Z211" s="2" t="n">
         <v>-0.0002808988764044098</v>
       </c>
+      <c r="AA211" s="1" t="n">
+        <v>0.007106</v>
+      </c>
+      <c r="AB211" s="2" t="n">
+        <v>-0.001685866816521475</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -17887,6 +19159,12 @@
       <c r="Z212" s="3" t="n">
         <v>0.005477576172543616</v>
       </c>
+      <c r="AA212" s="1" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="AB212" s="2" t="n">
+        <v>-0.003404834865509026</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -17969,6 +19247,12 @@
       <c r="Z213" s="3" t="n">
         <v>0.003037884203002082</v>
       </c>
+      <c r="AA213" s="1" t="n">
+        <v>0.05583</v>
+      </c>
+      <c r="AB213" s="2" t="n">
+        <v>-0.005344735435595968</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -18051,6 +19335,12 @@
       <c r="Z214" s="2" t="n">
         <v>-0.002649708532061475</v>
       </c>
+      <c r="AA214" s="1" t="n">
+        <v>0.1889</v>
+      </c>
+      <c r="AB214" s="3" t="n">
+        <v>0.003719447396386855</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -18133,6 +19423,12 @@
       <c r="Z215" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA215" s="1" t="n">
+        <v>0.05283</v>
+      </c>
+      <c r="AB215" s="3" t="n">
+        <v>0.001896453631708759</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -18215,6 +19511,12 @@
       <c r="Z216" s="2" t="n">
         <v>-0.002876318312560097</v>
       </c>
+      <c r="AA216" s="1" t="n">
+        <v>0.002074</v>
+      </c>
+      <c r="AB216" s="2" t="n">
+        <v>-0.002884615384615351</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -18297,6 +19599,12 @@
       <c r="Z217" s="2" t="n">
         <v>-0.0001666388935178027</v>
       </c>
+      <c r="AA217" s="1" t="n">
+        <v>6.001</v>
+      </c>
+      <c r="AB217" s="3" t="n">
+        <v>0.0001666666666667223</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -18379,6 +19687,12 @@
       <c r="Z218" s="2" t="n">
         <v>-0.0002272727272728032</v>
       </c>
+      <c r="AA218" s="1" t="n">
+        <v>4.244</v>
+      </c>
+      <c r="AB218" s="2" t="n">
+        <v>-0.03523528074562406</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -18461,6 +19775,12 @@
       <c r="Z219" s="3" t="n">
         <v>0.001501501501501375</v>
       </c>
+      <c r="AA219" s="1" t="n">
+        <v>0.005332</v>
+      </c>
+      <c r="AB219" s="2" t="n">
+        <v>-0.0007496251874062338</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -18543,6 +19863,12 @@
       <c r="Z220" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA220" s="1" t="n">
+        <v>0.04127</v>
+      </c>
+      <c r="AB220" s="3" t="n">
+        <v>0.0002423654871547034</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -18625,6 +19951,12 @@
       <c r="Z221" s="2" t="n">
         <v>-0.001744591765526947</v>
       </c>
+      <c r="AA221" s="1" t="n">
+        <v>0.005715</v>
+      </c>
+      <c r="AB221" s="2" t="n">
+        <v>-0.001223348479552615</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -18707,6 +20039,12 @@
       <c r="Z222" s="2" t="n">
         <v>-0.002200220022002111</v>
       </c>
+      <c r="AA222" s="1" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="AB222" s="2" t="n">
+        <v>-0.001102535832414585</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -18789,6 +20127,12 @@
       <c r="Z223" s="2" t="n">
         <v>-0.001495662578522287</v>
       </c>
+      <c r="AA223" s="1" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="AB223" s="3" t="n">
+        <v>0.00089874176153392</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -18871,6 +20215,12 @@
       <c r="Z224" s="2" t="n">
         <v>-0.001624883936861731</v>
       </c>
+      <c r="AA224" s="1" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="AB224" s="3" t="n">
+        <v>0.0006975122064636654</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -18953,6 +20303,12 @@
       <c r="Z225" s="2" t="n">
         <v>-0.001315946883598504</v>
       </c>
+      <c r="AA225" s="1" t="n">
+        <v>0.08323</v>
+      </c>
+      <c r="AB225" s="2" t="n">
+        <v>-0.002994729276473409</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -19035,6 +20391,12 @@
       <c r="Z226" s="2" t="n">
         <v>-0.0005305039787798192</v>
       </c>
+      <c r="AA226" s="1" t="n">
+        <v>0.01872</v>
+      </c>
+      <c r="AB226" s="2" t="n">
+        <v>-0.006369426751592282</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -19117,6 +20479,12 @@
       <c r="Z227" s="3" t="n">
         <v>0.0002143163309044805</v>
       </c>
+      <c r="AA227" s="1" t="n">
+        <v>0.04673</v>
+      </c>
+      <c r="AB227" s="3" t="n">
+        <v>0.001285622455538838</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -19199,6 +20567,12 @@
       <c r="Z228" s="2" t="n">
         <v>-0.003025064822817658</v>
       </c>
+      <c r="AA228" s="1" t="n">
+        <v>0.02304</v>
+      </c>
+      <c r="AB228" s="2" t="n">
+        <v>-0.001300390117035057</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -19281,6 +20655,12 @@
       <c r="Z229" s="3" t="n">
         <v>0.002795899347623436</v>
       </c>
+      <c r="AA229" s="1" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="AB229" s="3" t="n">
+        <v>0.001858736059479607</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -19363,6 +20743,12 @@
       <c r="Z230" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA230" s="1" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="AB230" s="3" t="n">
+        <v>0.0006045949214027615</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -19445,6 +20831,12 @@
       <c r="Z231" s="2" t="n">
         <v>-0.001317089232795583</v>
       </c>
+      <c r="AA231" s="1" t="n">
+        <v>0.03031</v>
+      </c>
+      <c r="AB231" s="2" t="n">
+        <v>-0.0006594131223211073</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -19527,6 +20919,12 @@
       <c r="Z232" s="2" t="n">
         <v>-0.0008869179600886556</v>
       </c>
+      <c r="AA232" s="1" t="n">
+        <v>0.02246</v>
+      </c>
+      <c r="AB232" s="2" t="n">
+        <v>-0.003106968486462522</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -19609,6 +21007,12 @@
       <c r="Z233" s="2" t="n">
         <v>-0.09642412382138411</v>
       </c>
+      <c r="AA233" s="1" t="n">
+        <v>0.09626</v>
+      </c>
+      <c r="AB233" s="2" t="n">
+        <v>-0.05237251427446353</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -19691,6 +21095,12 @@
       <c r="Z234" s="3" t="n">
         <v>0.0007920792079207049</v>
       </c>
+      <c r="AA234" s="1" t="n">
+        <v>0.2527</v>
+      </c>
+      <c r="AB234" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -19773,6 +21183,12 @@
       <c r="Z235" s="2" t="n">
         <v>-0.002896871378910859</v>
       </c>
+      <c r="AA235" s="1" t="n">
+        <v>0.06847</v>
+      </c>
+      <c r="AB235" s="2" t="n">
+        <v>-0.005374782103428172</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -19855,6 +21271,12 @@
       <c r="Z236" s="2" t="n">
         <v>-0.00828925554590665</v>
       </c>
+      <c r="AA236" s="1" t="n">
+        <v>0.12485</v>
+      </c>
+      <c r="AB236" s="2" t="n">
+        <v>-0.006129597197898478</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -19937,6 +21359,12 @@
       <c r="Z237" s="3" t="n">
         <v>0.002596053997923231</v>
       </c>
+      <c r="AA237" s="1" t="n">
+        <v>0.03874</v>
+      </c>
+      <c r="AB237" s="3" t="n">
+        <v>0.003107198342827424</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -20019,6 +21447,12 @@
       <c r="Z238" s="3" t="n">
         <v>0.008403361344537823</v>
       </c>
+      <c r="AA238" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AB238" s="2" t="n">
+        <v>-0.008333333333333342</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -20101,6 +21535,12 @@
       <c r="Z239" s="2" t="n">
         <v>-0.004503377533149809</v>
       </c>
+      <c r="AA239" s="1" t="n">
+        <v>0.003977</v>
+      </c>
+      <c r="AB239" s="2" t="n">
+        <v>-0.0005026388539834797</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -20183,6 +21623,12 @@
       <c r="Z240" s="3" t="n">
         <v>0.0007315288953913382</v>
       </c>
+      <c r="AA240" s="1" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="AB240" s="3" t="n">
+        <v>0.001461988304093635</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -20265,6 +21711,12 @@
       <c r="Z241" s="2" t="n">
         <v>-0.008599230595157333</v>
       </c>
+      <c r="AA241" s="1" t="n">
+        <v>0.4354</v>
+      </c>
+      <c r="AB241" s="2" t="n">
+        <v>-0.006162976489385939</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -20347,6 +21799,12 @@
       <c r="Z242" s="3" t="n">
         <v>0.006666666666666743</v>
       </c>
+      <c r="AA242" s="1" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="AB242" s="2" t="n">
+        <v>-0.002649006622516563</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -20429,6 +21887,12 @@
       <c r="Z243" s="3" t="n">
         <v>0.006570302233902796</v>
       </c>
+      <c r="AA243" s="1" t="n">
+        <v>0.02296</v>
+      </c>
+      <c r="AB243" s="2" t="n">
+        <v>-0.0008703220191470489</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -20511,6 +21975,12 @@
       <c r="Z244" s="2" t="n">
         <v>-0.009512485136741947</v>
       </c>
+      <c r="AA244" s="1" t="n">
+        <v>0.001661</v>
+      </c>
+      <c r="AB244" s="2" t="n">
+        <v>-0.003001200480192085</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -20593,6 +22063,12 @@
       <c r="Z245" s="3" t="n">
         <v>0.0007645259938837078</v>
       </c>
+      <c r="AA245" s="1" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="AB245" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -20675,6 +22151,12 @@
       <c r="Z246" s="3" t="n">
         <v>0.004148053605615768</v>
       </c>
+      <c r="AA246" s="1" t="n">
+        <v>0.03194</v>
+      </c>
+      <c r="AB246" s="3" t="n">
+        <v>0.01493485859548793</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -20757,6 +22239,12 @@
       <c r="Z247" s="2" t="n">
         <v>-0.0005652911249292763</v>
       </c>
+      <c r="AA247" s="1" t="n">
+        <v>0.1764</v>
+      </c>
+      <c r="AB247" s="2" t="n">
+        <v>-0.002262443438914092</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -20839,6 +22327,12 @@
       <c r="Z248" s="3" t="n">
         <v>0.006231551328304336</v>
       </c>
+      <c r="AA248" s="1" t="n">
+        <v>0.03063</v>
+      </c>
+      <c r="AB248" s="2" t="n">
+        <v>-0.001629726205997326</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -20921,6 +22415,12 @@
       <c r="Z249" s="3" t="n">
         <v>0.0002348244687096707</v>
       </c>
+      <c r="AA249" s="1" t="n">
+        <v>0.008531</v>
+      </c>
+      <c r="AB249" s="3" t="n">
+        <v>0.001408616034745845</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -21003,6 +22503,12 @@
       <c r="Z250" s="3" t="n">
         <v>0.001995012468828022</v>
       </c>
+      <c r="AA250" s="1" t="n">
+        <v>0.01995</v>
+      </c>
+      <c r="AB250" s="2" t="n">
+        <v>-0.00696864111498264</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -21085,6 +22591,12 @@
       <c r="Z251" s="3" t="n">
         <v>0.001291433491175152</v>
       </c>
+      <c r="AA251" s="1" t="n">
+        <v>0.04635</v>
+      </c>
+      <c r="AB251" s="2" t="n">
+        <v>-0.003654342218400614</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -21167,6 +22679,12 @@
       <c r="Z252" s="2" t="n">
         <v>-0.000469538678248683</v>
       </c>
+      <c r="AA252" s="1" t="n">
+        <v>0.008536</v>
+      </c>
+      <c r="AB252" s="3" t="n">
+        <v>0.002466236054022335</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -21249,6 +22767,12 @@
       <c r="Z253" s="2" t="n">
         <v>-0.006682086867129357</v>
       </c>
+      <c r="AA253" s="1" t="n">
+        <v>0.03864</v>
+      </c>
+      <c r="AB253" s="2" t="n">
+        <v>-0.0002587322121603137</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -21331,6 +22855,12 @@
       <c r="Z254" s="3" t="n">
         <v>0.0004883607357968786</v>
       </c>
+      <c r="AA254" s="1" t="n">
+        <v>0.06125</v>
+      </c>
+      <c r="AB254" s="2" t="n">
+        <v>-0.003416856492027365</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -21413,6 +22943,12 @@
       <c r="Z255" s="3" t="n">
         <v>0.0005657708628006409</v>
       </c>
+      <c r="AA255" s="1" t="n">
+        <v>0.003562</v>
+      </c>
+      <c r="AB255" s="3" t="n">
+        <v>0.007068136839129162</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -21495,6 +23031,12 @@
       <c r="Z256" s="2" t="n">
         <v>-0.00242075799984863</v>
       </c>
+      <c r="AA256" s="1" t="n">
+        <v>0.013321</v>
+      </c>
+      <c r="AB256" s="3" t="n">
+        <v>0.01016152271176148</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -21577,6 +23119,12 @@
       <c r="Z257" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA257" s="1" t="n">
+        <v>0.999426</v>
+      </c>
+      <c r="AB257" s="3" t="n">
+        <v>1.000575330843991e-06</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -21659,6 +23207,12 @@
       <c r="Z258" s="2" t="n">
         <v>-0.003241309936291479</v>
       </c>
+      <c r="AA258" s="1" t="n">
+        <v>0.08862</v>
+      </c>
+      <c r="AB258" s="2" t="n">
+        <v>-0.006279434850863322</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -21741,6 +23295,12 @@
       <c r="Z259" s="2" t="n">
         <v>-0.003074220465524688</v>
       </c>
+      <c r="AA259" s="1" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="AB259" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -21823,6 +23383,12 @@
       <c r="Z260" s="2" t="n">
         <v>-0.0007317073170732255</v>
       </c>
+      <c r="AA260" s="1" t="n">
+        <v>0.08191</v>
+      </c>
+      <c r="AB260" s="2" t="n">
+        <v>-0.0003661215523554094</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -21905,6 +23471,12 @@
       <c r="Z261" s="2" t="n">
         <v>-0.00523103748910201</v>
       </c>
+      <c r="AA261" s="1" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="AB261" s="2" t="n">
+        <v>-0.003505696757230503</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -21987,6 +23559,12 @@
       <c r="Z262" s="3" t="n">
         <v>0.02557342472976532</v>
       </c>
+      <c r="AA262" s="1" t="n">
+        <v>0.003871</v>
+      </c>
+      <c r="AB262" s="2" t="n">
+        <v>-0.004884318766066818</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -22069,6 +23647,12 @@
       <c r="Z263" s="3" t="n">
         <v>0.001739130434782538</v>
       </c>
+      <c r="AA263" s="1" t="n">
+        <v>0.1149</v>
+      </c>
+      <c r="AB263" s="2" t="n">
+        <v>-0.002604166666666621</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -22151,6 +23735,12 @@
       <c r="Z264" s="2" t="n">
         <v>-0.01790853853533747</v>
       </c>
+      <c r="AA264" s="1" t="n">
+        <v>0.0006283</v>
+      </c>
+      <c r="AB264" s="3" t="n">
+        <v>0.02295669163139055</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -22233,6 +23823,12 @@
       <c r="Z265" s="2" t="n">
         <v>-0.00475866757307958</v>
       </c>
+      <c r="AA265" s="1" t="n">
+        <v>0.01459</v>
+      </c>
+      <c r="AB265" s="2" t="n">
+        <v>-0.003415300546448067</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -22315,6 +23911,12 @@
       <c r="Z266" s="2" t="n">
         <v>-0.001574803149606344</v>
       </c>
+      <c r="AA266" s="1" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="AB266" s="3" t="n">
+        <v>0.001577287066246102</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -22397,6 +23999,12 @@
       <c r="Z267" s="3" t="n">
         <v>0.0006165228113442086</v>
       </c>
+      <c r="AA267" s="1" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="AB267" s="3" t="n">
+        <v>0.001232285890326506</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -22479,6 +24087,12 @@
       <c r="Z268" s="3" t="n">
         <v>0.007676203768318274</v>
       </c>
+      <c r="AA268" s="1" t="n">
+        <v>0.0004317</v>
+      </c>
+      <c r="AB268" s="2" t="n">
+        <v>-0.003462603878116428</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -22561,6 +24175,12 @@
       <c r="Z269" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA269" s="1" t="n">
+        <v>0.02076</v>
+      </c>
+      <c r="AB269" s="3" t="n">
+        <v>0.001447178002894465</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -22643,6 +24263,12 @@
       <c r="Z270" s="2" t="n">
         <v>-0.002217294900221793</v>
       </c>
+      <c r="AA270" s="1" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="AB270" s="3" t="n">
+        <v>0.003888888888888923</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -22725,6 +24351,12 @@
       <c r="Z271" s="2" t="n">
         <v>-0.001356852103120799</v>
       </c>
+      <c r="AA271" s="1" t="n">
+        <v>0.1476</v>
+      </c>
+      <c r="AB271" s="3" t="n">
+        <v>0.002717391304347904</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -22807,6 +24439,12 @@
       <c r="Z272" s="2" t="n">
         <v>-0.001262945188178869</v>
       </c>
+      <c r="AA272" s="1" t="n">
+        <v>0.03951</v>
+      </c>
+      <c r="AB272" s="2" t="n">
+        <v>-0.0007587253414262851</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -22889,6 +24527,12 @@
       <c r="Z273" s="2" t="n">
         <v>-0.002157497303128373</v>
       </c>
+      <c r="AA273" s="1" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="AB273" s="2" t="n">
+        <v>-0.003243243243243246</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -22971,6 +24615,12 @@
       <c r="Z274" s="3" t="n">
         <v>0.001426307448494395</v>
       </c>
+      <c r="AA274" s="1" t="n">
+        <v>63.12</v>
+      </c>
+      <c r="AB274" s="2" t="n">
+        <v>-0.001107770216806461</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -23053,6 +24703,12 @@
       <c r="Z275" s="2" t="n">
         <v>-0.01413427561837459</v>
       </c>
+      <c r="AA275" s="1" t="n">
+        <v>0.01123</v>
+      </c>
+      <c r="AB275" s="3" t="n">
+        <v>0.006272401433691812</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -23135,6 +24791,12 @@
       <c r="Z276" s="2" t="n">
         <v>-0.002300613496932602</v>
       </c>
+      <c r="AA276" s="1" t="n">
+        <v>2.602</v>
+      </c>
+      <c r="AB276" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -23217,6 +24879,12 @@
       <c r="Z277" s="2" t="n">
         <v>-0.001190476190476224</v>
       </c>
+      <c r="AA277" s="1" t="n">
+        <v>0.04197</v>
+      </c>
+      <c r="AB277" s="3" t="n">
+        <v>0.0004767580452919949</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -23299,6 +24967,12 @@
       <c r="Z278" s="2" t="n">
         <v>-0.007560483870967784</v>
       </c>
+      <c r="AA278" s="1" t="n">
+        <v>0.01976</v>
+      </c>
+      <c r="AB278" s="3" t="n">
+        <v>0.003555104113763363</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -23381,6 +25055,12 @@
       <c r="Z279" s="3" t="n">
         <v>0.001252012162403874</v>
       </c>
+      <c r="AA279" s="1" t="n">
+        <v>0.005596</v>
+      </c>
+      <c r="AB279" s="2" t="n">
+        <v>-0.0003572704537333687</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -23463,6 +25143,12 @@
       <c r="Z280" s="3" t="n">
         <v>0.008435582822085811</v>
       </c>
+      <c r="AA280" s="1" t="n">
+        <v>0.03984</v>
+      </c>
+      <c r="AB280" s="3" t="n">
+        <v>0.009885931558935399</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -23545,6 +25231,12 @@
       <c r="Z281" s="3" t="n">
         <v>0.002217294900221731</v>
       </c>
+      <c r="AA281" s="1" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="AB281" s="2" t="n">
+        <v>-0.001106194690265488</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -23627,6 +25319,12 @@
       <c r="Z282" s="3" t="n">
         <v>0.003428011753183104</v>
       </c>
+      <c r="AA282" s="1" t="n">
+        <v>0.0004096</v>
+      </c>
+      <c r="AB282" s="2" t="n">
+        <v>-0.0004880429477794165</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -23709,6 +25407,12 @@
       <c r="Z283" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA283" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AB283" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -23791,6 +25495,12 @@
       <c r="Z284" s="3" t="n">
         <v>0.000718390804597755</v>
       </c>
+      <c r="AA284" s="1" t="n">
+        <v>0.04203</v>
+      </c>
+      <c r="AB284" s="3" t="n">
+        <v>0.005743000717875021</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -23873,6 +25583,12 @@
       <c r="Z285" s="2" t="n">
         <v>-0.0005593884020137108</v>
       </c>
+      <c r="AA285" s="1" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="AB285" s="3" t="n">
+        <v>0.001865671641790969</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -23955,6 +25671,12 @@
       <c r="Z286" s="3" t="n">
         <v>0.002386634844868638</v>
       </c>
+      <c r="AA286" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="AB286" s="2" t="n">
+        <v>-0.002380952380952284</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -24037,6 +25759,12 @@
       <c r="Z287" s="3" t="n">
         <v>0.0113340281396562</v>
       </c>
+      <c r="AA287" s="1" t="n">
+        <v>0.15414</v>
+      </c>
+      <c r="AB287" s="2" t="n">
+        <v>-0.007213706041478873</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -24119,6 +25847,12 @@
       <c r="Z288" s="3" t="n">
         <v>0.002223457476375674</v>
       </c>
+      <c r="AA288" s="1" t="n">
+        <v>0.1801</v>
+      </c>
+      <c r="AB288" s="2" t="n">
+        <v>-0.001109262340543416</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -24201,6 +25935,12 @@
       <c r="Z289" s="3" t="n">
         <v>0.0007235890014472055</v>
       </c>
+      <c r="AA289" s="1" t="n">
+        <v>4.152</v>
+      </c>
+      <c r="AB289" s="3" t="n">
+        <v>0.0007230657989877353</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -24283,6 +26023,12 @@
       <c r="Z290" s="2" t="n">
         <v>-0.001519046506193095</v>
       </c>
+      <c r="AA290" s="1" t="n">
+        <v>0.08556999999999999</v>
+      </c>
+      <c r="AB290" s="3" t="n">
+        <v>0.001404330017554068</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -24365,6 +26111,12 @@
       <c r="Z291" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA291" s="1" t="n">
+        <v>0.03544</v>
+      </c>
+      <c r="AB291" s="2" t="n">
+        <v>-0.00028208744710869</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -24447,6 +26199,12 @@
       <c r="Z292" s="2" t="n">
         <v>-0.0003396277679662715</v>
       </c>
+      <c r="AA292" s="1" t="n">
+        <v>1.4625</v>
+      </c>
+      <c r="AB292" s="2" t="n">
+        <v>-0.006251274036828224</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -24529,6 +26287,12 @@
       <c r="Z293" s="2" t="n">
         <v>-0.001374098248024767</v>
       </c>
+      <c r="AA293" s="1" t="n">
+        <v>0.005834</v>
+      </c>
+      <c r="AB293" s="3" t="n">
+        <v>0.003439972480220167</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -24611,6 +26375,12 @@
       <c r="Z294" s="2" t="n">
         <v>-0.001164483260553158</v>
       </c>
+      <c r="AA294" s="1" t="n">
+        <v>0.003426</v>
+      </c>
+      <c r="AB294" s="2" t="n">
+        <v>-0.001457301078402865</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -24693,6 +26463,12 @@
       <c r="Z295" s="2" t="n">
         <v>-0.002418154761904702</v>
       </c>
+      <c r="AA295" s="1" t="n">
+        <v>0.5387</v>
+      </c>
+      <c r="AB295" s="3" t="n">
+        <v>0.004475107216110307</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -24775,6 +26551,12 @@
       <c r="Z296" s="2" t="n">
         <v>-0.0004460303300623952</v>
       </c>
+      <c r="AA296" s="1" t="n">
+        <v>2.241</v>
+      </c>
+      <c r="AB296" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -24857,6 +26639,12 @@
       <c r="Z297" s="2" t="n">
         <v>-0.002960331557134278</v>
       </c>
+      <c r="AA297" s="1" t="n">
+        <v>0.01681</v>
+      </c>
+      <c r="AB297" s="2" t="n">
+        <v>-0.001781472684085644</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -24939,6 +26727,12 @@
       <c r="Z298" s="2" t="n">
         <v>-0.007364975450081779</v>
       </c>
+      <c r="AA298" s="1" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="AB298" s="3" t="n">
+        <v>0.003297609233305795</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -25021,6 +26815,12 @@
       <c r="Z299" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA299" s="1" t="n">
+        <v>0.01109</v>
+      </c>
+      <c r="AB299" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -25103,6 +26903,12 @@
       <c r="Z300" s="3" t="n">
         <v>0.0004844961240311561</v>
       </c>
+      <c r="AA300" s="1" t="n">
+        <v>0.02068</v>
+      </c>
+      <c r="AB300" s="3" t="n">
+        <v>0.001452784503631902</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -25185,6 +26991,12 @@
       <c r="Z301" s="2" t="n">
         <v>-0.001628664495114008</v>
       </c>
+      <c r="AA301" s="1" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="AB301" s="3" t="n">
+        <v>0.001305057096247998</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -25267,6 +27079,12 @@
       <c r="Z302" s="3" t="n">
         <v>0.004366812227074184</v>
       </c>
+      <c r="AA302" s="1" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="AB302" s="2" t="n">
+        <v>-0.003623188405797079</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -25349,6 +27167,12 @@
       <c r="Z303" s="2" t="n">
         <v>-0.00121621621621612</v>
       </c>
+      <c r="AA303" s="1" t="n">
+        <v>0.07405</v>
+      </c>
+      <c r="AB303" s="3" t="n">
+        <v>0.001894195643350037</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -25431,6 +27255,12 @@
       <c r="Z304" s="3" t="n">
         <v>0.0006301197227472964</v>
       </c>
+      <c r="AA304" s="1" t="n">
+        <v>0.01587</v>
+      </c>
+      <c r="AB304" s="2" t="n">
+        <v>-0.0006297229219143321</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -25513,6 +27343,12 @@
       <c r="Z305" s="2" t="n">
         <v>-0.0009331259720060749</v>
       </c>
+      <c r="AA305" s="1" t="n">
+        <v>0.06408999999999999</v>
+      </c>
+      <c r="AB305" s="2" t="n">
+        <v>-0.002334993773350112</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -25595,6 +27431,12 @@
       <c r="Z306" s="2" t="n">
         <v>-0.004221954161640568</v>
       </c>
+      <c r="AA306" s="1" t="n">
+        <v>0.04955</v>
+      </c>
+      <c r="AB306" s="3" t="n">
+        <v>0.0004037956793862141</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -25677,6 +27519,12 @@
       <c r="Z307" s="3" t="n">
         <v>0.002178649237472769</v>
       </c>
+      <c r="AA307" s="1" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="AB307" s="3" t="n">
+        <v>0.003260869565217394</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -25759,6 +27607,12 @@
       <c r="Z308" s="3" t="n">
         <v>0.002766599597585662</v>
       </c>
+      <c r="AA308" s="1" t="n">
+        <v>0.03987</v>
+      </c>
+      <c r="AB308" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -25841,6 +27695,12 @@
       <c r="Z309" s="3" t="n">
         <v>0.003856041131105464</v>
       </c>
+      <c r="AA309" s="1" t="n">
+        <v>0.01558</v>
+      </c>
+      <c r="AB309" s="2" t="n">
+        <v>-0.00256081946222792</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -25923,6 +27783,12 @@
       <c r="Z310" s="2" t="n">
         <v>-0.001474382602285361</v>
       </c>
+      <c r="AA310" s="1" t="n">
+        <v>0.05433</v>
+      </c>
+      <c r="AB310" s="3" t="n">
+        <v>0.002768549280177266</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -26005,6 +27871,12 @@
       <c r="Z311" s="2" t="n">
         <v>-0.002009377093101211</v>
       </c>
+      <c r="AA311" s="1" t="n">
+        <v>0.004464</v>
+      </c>
+      <c r="AB311" s="2" t="n">
+        <v>-0.001342281879194615</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -26087,6 +27959,12 @@
       <c r="Z312" s="2" t="n">
         <v>-0.0001181055863941907</v>
       </c>
+      <c r="AA312" s="1" t="n">
+        <v>0.08482000000000001</v>
+      </c>
+      <c r="AB312" s="3" t="n">
+        <v>0.001889912591542728</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -26169,6 +28047,12 @@
       <c r="Z313" s="3" t="n">
         <v>0.0006688068485822416</v>
       </c>
+      <c r="AA313" s="1" t="n">
+        <v>0.07475999999999999</v>
+      </c>
+      <c r="AB313" s="2" t="n">
+        <v>-0.0006683598449406279</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -26251,6 +28135,12 @@
       <c r="Z314" s="3" t="n">
         <v>0.001306335728282025</v>
       </c>
+      <c r="AA314" s="1" t="n">
+        <v>0.1529</v>
+      </c>
+      <c r="AB314" s="2" t="n">
+        <v>-0.00260926288323538</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -26333,6 +28223,12 @@
       <c r="Z315" s="2" t="n">
         <v>-0.0006261740763933421</v>
       </c>
+      <c r="AA315" s="1" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="AB315" s="2" t="n">
+        <v>-0.0006265664160400313</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -26415,6 +28311,12 @@
       <c r="Z316" s="2" t="n">
         <v>-0.00110375275938193</v>
       </c>
+      <c r="AA316" s="1" t="n">
+        <v>0.1814</v>
+      </c>
+      <c r="AB316" s="3" t="n">
+        <v>0.002209944751381279</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -26497,6 +28399,12 @@
       <c r="Z317" s="3" t="n">
         <v>0.0008013890743956096</v>
       </c>
+      <c r="AA317" s="1" t="n">
+        <v>0.007483</v>
+      </c>
+      <c r="AB317" s="2" t="n">
+        <v>-0.001334578940344267</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -26579,6 +28487,12 @@
       <c r="Z318" s="2" t="n">
         <v>-0.004968203497615129</v>
       </c>
+      <c r="AA318" s="1" t="n">
+        <v>0.05007</v>
+      </c>
+      <c r="AB318" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -26661,6 +28575,12 @@
       <c r="Z319" s="3" t="n">
         <v>0.002301744290595123</v>
       </c>
+      <c r="AA319" s="1" t="n">
+        <v>0.27907</v>
+      </c>
+      <c r="AB319" s="3" t="n">
+        <v>0.001363522193117771</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -26743,6 +28663,12 @@
       <c r="Z320" s="2" t="n">
         <v>-0.0002272210861167666</v>
       </c>
+      <c r="AA320" s="1" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="AB320" s="2" t="n">
+        <v>-0.00181818181818187</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -26825,6 +28751,12 @@
       <c r="Z321" s="3" t="n">
         <v>0.001416795466254495</v>
       </c>
+      <c r="AA321" s="1" t="n">
+        <v>0.07759000000000001</v>
+      </c>
+      <c r="AB321" s="2" t="n">
+        <v>-0.002057877813504739</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -26907,6 +28839,12 @@
       <c r="Z322" s="2" t="n">
         <v>-0.002443494196701353</v>
       </c>
+      <c r="AA322" s="1" t="n">
+        <v>0.1638</v>
+      </c>
+      <c r="AB322" s="3" t="n">
+        <v>0.003061849357011638</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -26989,6 +28927,12 @@
       <c r="Z323" s="2" t="n">
         <v>-0.001516683518705709</v>
       </c>
+      <c r="AA323" s="1" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB323" s="2" t="n">
+        <v>-0.002531645569620311</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -27071,6 +29015,12 @@
       <c r="Z324" s="2" t="n">
         <v>-0.002066892145809957</v>
       </c>
+      <c r="AA324" s="1" t="n">
+        <v>0.053065</v>
+      </c>
+      <c r="AB324" s="2" t="n">
+        <v>-0.0008472980606288163</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -27153,6 +29103,12 @@
       <c r="Z325" s="2" t="n">
         <v>-0.004163143173095698</v>
       </c>
+      <c r="AA325" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="AB325" s="2" t="n">
+        <v>-0.0005878894767784097</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -27235,6 +29191,12 @@
       <c r="Z326" s="3" t="n">
         <v>0.002167853824713553</v>
       </c>
+      <c r="AA326" s="1" t="n">
+        <v>0.006466</v>
+      </c>
+      <c r="AB326" s="2" t="n">
+        <v>-0.0009270704573547479</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -27317,6 +29279,12 @@
       <c r="Z327" s="2" t="n">
         <v>-0.001382579498321166</v>
       </c>
+      <c r="AA327" s="1" t="n">
+        <v>0.015075</v>
+      </c>
+      <c r="AB327" s="2" t="n">
+        <v>-0.006131329113924007</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -27399,6 +29367,12 @@
       <c r="Z328" s="3" t="n">
         <v>0.004184100418410016</v>
       </c>
+      <c r="AA328" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="AB328" s="2" t="n">
+        <v>-0.00312500000000009</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -27481,6 +29455,12 @@
       <c r="Z329" s="2" t="n">
         <v>-0.000227169468423277</v>
       </c>
+      <c r="AA329" s="1" t="n">
+        <v>0.004402</v>
+      </c>
+      <c r="AB329" s="3" t="n">
+        <v>0.0002272210861166247</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -27563,6 +29543,12 @@
       <c r="Z330" s="3" t="n">
         <v>0.0009689922480620432</v>
       </c>
+      <c r="AA330" s="1" t="n">
+        <v>0.05176</v>
+      </c>
+      <c r="AB330" s="3" t="n">
+        <v>0.00212971926427878</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -27645,6 +29631,12 @@
       <c r="Z331" s="2" t="n">
         <v>-0.005263157894736916</v>
       </c>
+      <c r="AA331" s="1" t="n">
+        <v>0.03586</v>
+      </c>
+      <c r="AB331" s="2" t="n">
+        <v>-0.001392369813422292</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -27727,6 +29719,12 @@
       <c r="Z332" s="2" t="n">
         <v>-0.00340136054421769</v>
       </c>
+      <c r="AA332" s="1" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="AB332" s="2" t="n">
+        <v>-0.000682593856655215</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -27809,6 +29807,12 @@
       <c r="Z333" s="2" t="n">
         <v>-0.004153686396677026</v>
       </c>
+      <c r="AA333" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="AB333" s="3" t="n">
+        <v>0.002085505735140832</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -27891,6 +29895,12 @@
       <c r="Z334" s="3" t="n">
         <v>0.0004545454545454361</v>
       </c>
+      <c r="AA334" s="1" t="n">
+        <v>0.04409</v>
+      </c>
+      <c r="AB334" s="3" t="n">
+        <v>0.001590186278964121</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -27973,6 +29983,12 @@
       <c r="Z335" s="2" t="n">
         <v>-0.002194854286062671</v>
       </c>
+      <c r="AA335" s="1" t="n">
+        <v>0.08178000000000001</v>
+      </c>
+      <c r="AB335" s="2" t="n">
+        <v>-0.0006110228522546071</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -28055,6 +30071,12 @@
       <c r="Z336" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA336" s="1" t="n">
+        <v>0.2051</v>
+      </c>
+      <c r="AB336" s="3" t="n">
+        <v>0.001954079140205234</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -28137,6 +30159,12 @@
       <c r="Z337" s="2" t="n">
         <v>-0.001970443349753615</v>
       </c>
+      <c r="AA337" s="1" t="n">
+        <v>0.01013</v>
+      </c>
+      <c r="AB337" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -28219,6 +30247,12 @@
       <c r="Z338" s="3" t="n">
         <v>0.002657218777679315</v>
       </c>
+      <c r="AA338" s="1" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="AB338" s="3" t="n">
+        <v>0.001766784452296871</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -28301,6 +30335,12 @@
       <c r="Z339" s="2" t="n">
         <v>-0.002181025081788352</v>
       </c>
+      <c r="AA339" s="1" t="n">
+        <v>0.01826</v>
+      </c>
+      <c r="AB339" s="2" t="n">
+        <v>-0.002185792349726877</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -28383,6 +30423,12 @@
       <c r="Z340" s="3" t="n">
         <v>0.006782133090246229</v>
       </c>
+      <c r="AA340" s="1" t="n">
+        <v>0.27337</v>
+      </c>
+      <c r="AB340" s="2" t="n">
+        <v>-0.009923581181413278</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -28465,6 +30511,12 @@
       <c r="Z341" s="3" t="n">
         <v>0.001402524544179628</v>
       </c>
+      <c r="AA341" s="1" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="AB341" s="3" t="n">
+        <v>0.001400560224089579</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -28547,6 +30599,12 @@
       <c r="Z342" s="3" t="n">
         <v>0.005340627849420264</v>
       </c>
+      <c r="AA342" s="1" t="n">
+        <v>0.07915999999999999</v>
+      </c>
+      <c r="AB342" s="3" t="n">
+        <v>0.02565431458927177</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -28629,6 +30687,12 @@
       <c r="Z343" s="2" t="n">
         <v>-0.001699790794979067</v>
       </c>
+      <c r="AA343" s="1" t="n">
+        <v>7.619</v>
+      </c>
+      <c r="AB343" s="2" t="n">
+        <v>-0.002095612311722333</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -28711,6 +30775,12 @@
       <c r="Z344" s="2" t="n">
         <v>-0.002502085070892505</v>
       </c>
+      <c r="AA344" s="1" t="n">
+        <v>0.5985</v>
+      </c>
+      <c r="AB344" s="3" t="n">
+        <v>0.0008361204013378862</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -28793,6 +30863,12 @@
       <c r="Z345" s="3" t="n">
         <v>0.0002678093197644098</v>
       </c>
+      <c r="AA345" s="1" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="AB345" s="3" t="n">
+        <v>0.001338688085676076</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -28875,6 +30951,12 @@
       <c r="Z346" s="3" t="n">
         <v>0.002403846153846223</v>
       </c>
+      <c r="AA346" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="AB346" s="2" t="n">
+        <v>-0.002398081534772251</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -28957,6 +31039,12 @@
       <c r="Z347" s="2" t="n">
         <v>-0.003430531732418465</v>
       </c>
+      <c r="AA347" s="1" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="AB347" s="3" t="n">
+        <v>0.001147446930579334</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -29039,6 +31127,12 @@
       <c r="Z348" s="2" t="n">
         <v>-0.0002505589391718588</v>
       </c>
+      <c r="AA348" s="1" t="n">
+        <v>5194.1</v>
+      </c>
+      <c r="AB348" s="3" t="n">
+        <v>0.00134950164831987</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -29121,6 +31215,12 @@
       <c r="Z349" s="2" t="n">
         <v>-0.01512968299711816</v>
       </c>
+      <c r="AA349" s="1" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="AB349" s="2" t="n">
+        <v>-0.01243599122165326</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -29203,6 +31303,12 @@
       <c r="Z350" s="2" t="n">
         <v>-0.009032258064516097</v>
       </c>
+      <c r="AA350" s="1" t="n">
+        <v>0.01549</v>
+      </c>
+      <c r="AB350" s="3" t="n">
+        <v>0.008463541666666661</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -29285,6 +31391,12 @@
       <c r="Z351" s="3" t="n">
         <v>0.003777303333880771</v>
       </c>
+      <c r="AA351" s="1" t="n">
+        <v>0.0006122</v>
+      </c>
+      <c r="AB351" s="3" t="n">
+        <v>0.001636125654450301</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -29367,6 +31479,12 @@
       <c r="Z352" s="3" t="n">
         <v>0.004568527918781716</v>
       </c>
+      <c r="AA352" s="1" t="n">
+        <v>0.01975</v>
+      </c>
+      <c r="AB352" s="2" t="n">
+        <v>-0.002021222839818008</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -29449,6 +31567,12 @@
       <c r="Z353" s="3" t="n">
         <v>0.001284246575342562</v>
       </c>
+      <c r="AA353" s="1" t="n">
+        <v>0.09328</v>
+      </c>
+      <c r="AB353" s="2" t="n">
+        <v>-0.002992731936725123</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -29531,6 +31655,12 @@
       <c r="Z354" s="2" t="n">
         <v>-0.001108647450110896</v>
       </c>
+      <c r="AA354" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="AB354" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -29613,6 +31743,12 @@
       <c r="Z355" s="2" t="n">
         <v>-0.01202308432189808</v>
       </c>
+      <c r="AA355" s="1" t="n">
+        <v>0.0006125</v>
+      </c>
+      <c r="AB355" s="2" t="n">
+        <v>-0.006165828330358566</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -29695,6 +31831,12 @@
       <c r="Z356" s="2" t="n">
         <v>-0.002452182442373878</v>
       </c>
+      <c r="AA356" s="1" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="AB356" s="2" t="n">
+        <v>-0.004916420845624281</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -29777,6 +31919,12 @@
       <c r="Z357" s="3" t="n">
         <v>0.0008710801393727867</v>
       </c>
+      <c r="AA357" s="1" t="n">
+        <v>0.02282</v>
+      </c>
+      <c r="AB357" s="2" t="n">
+        <v>-0.006962576153176693</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -29859,6 +32007,12 @@
       <c r="Z358" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA358" s="1" t="n">
+        <v>0.000406</v>
+      </c>
+      <c r="AB358" s="3" t="n">
+        <v>0.002469135802469196</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -29941,6 +32095,12 @@
       <c r="Z359" s="2" t="n">
         <v>-0.002722940776038128</v>
       </c>
+      <c r="AA359" s="1" t="n">
+        <v>0.01468</v>
+      </c>
+      <c r="AB359" s="3" t="n">
+        <v>0.002047781569965905</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -30023,6 +32183,12 @@
       <c r="Z360" s="2" t="n">
         <v>-0.0003006614552014831</v>
       </c>
+      <c r="AA360" s="1" t="n">
+        <v>0.003314</v>
+      </c>
+      <c r="AB360" s="2" t="n">
+        <v>-0.003308270676691647</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -30105,6 +32271,12 @@
       <c r="Z361" s="2" t="n">
         <v>-0.003435889426831141</v>
       </c>
+      <c r="AA361" s="1" t="n">
+        <v>0.6363</v>
+      </c>
+      <c r="AB361" s="2" t="n">
+        <v>-0.002820874471086074</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -30187,6 +32359,12 @@
       <c r="Z362" s="3" t="n">
         <v>0.0008521516829995392</v>
       </c>
+      <c r="AA362" s="1" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="AB362" s="3" t="n">
+        <v>0.002128565346956065</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -30269,6 +32447,12 @@
       <c r="Z363" s="2" t="n">
         <v>-0.001533036946190447</v>
       </c>
+      <c r="AA363" s="1" t="n">
+        <v>0.06508</v>
+      </c>
+      <c r="AB363" s="2" t="n">
+        <v>-0.0007676953784737371</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -30351,6 +32535,12 @@
       <c r="Z364" s="2" t="n">
         <v>-0.001698874495646636</v>
       </c>
+      <c r="AA364" s="1" t="n">
+        <v>4.702</v>
+      </c>
+      <c r="AB364" s="3" t="n">
+        <v>0.0002127206977239596</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -30433,6 +32623,12 @@
       <c r="Z365" s="3" t="n">
         <v>0.0002780481023217868</v>
       </c>
+      <c r="AA365" s="1" t="n">
+        <v>0.07163</v>
+      </c>
+      <c r="AB365" s="2" t="n">
+        <v>-0.004447533009034063</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -30515,6 +32711,12 @@
       <c r="Z366" s="3" t="n">
         <v>0.0001782848992689628</v>
       </c>
+      <c r="AA366" s="1" t="n">
+        <v>0.05612</v>
+      </c>
+      <c r="AB366" s="3" t="n">
+        <v>0.0003565062388592892</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -30597,6 +32799,12 @@
       <c r="Z367" s="2" t="n">
         <v>-0.001197399931577157</v>
       </c>
+      <c r="AA367" s="1" t="n">
+        <v>0.05835</v>
+      </c>
+      <c r="AB367" s="2" t="n">
+        <v>-0.0006850488097276652</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -30679,6 +32887,12 @@
       <c r="Z368" s="3" t="n">
         <v>0.0008727526618956437</v>
       </c>
+      <c r="AA368" s="1" t="n">
+        <v>0.05718</v>
+      </c>
+      <c r="AB368" s="2" t="n">
+        <v>-0.002790373212417168</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -30761,6 +32975,12 @@
       <c r="Z369" s="2" t="n">
         <v>-0.0003225806451612772</v>
       </c>
+      <c r="AA369" s="1" t="n">
+        <v>0.03093</v>
+      </c>
+      <c r="AB369" s="2" t="n">
+        <v>-0.001936108422071669</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -30843,6 +33063,12 @@
       <c r="Z370" s="2" t="n">
         <v>-0.001848428835489712</v>
       </c>
+      <c r="AA370" s="1" t="n">
+        <v>0.0001621</v>
+      </c>
+      <c r="AB370" s="3" t="n">
+        <v>0.0006172839506172989</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -30925,6 +33151,12 @@
       <c r="Z371" s="2" t="n">
         <v>-0.001757984178142376</v>
       </c>
+      <c r="AA371" s="1" t="n">
+        <v>0.006771</v>
+      </c>
+      <c r="AB371" s="2" t="n">
+        <v>-0.006310537129439337</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -31007,6 +33239,12 @@
       <c r="Z372" s="2" t="n">
         <v>-0.002579535683576926</v>
       </c>
+      <c r="AA372" s="1" t="n">
+        <v>0.006971</v>
+      </c>
+      <c r="AB372" s="3" t="n">
+        <v>0.001580459770114903</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -31089,6 +33327,12 @@
       <c r="Z373" s="3" t="n">
         <v>0.0002637130801688644</v>
       </c>
+      <c r="AA373" s="1" t="n">
+        <v>3.772</v>
+      </c>
+      <c r="AB373" s="2" t="n">
+        <v>-0.005536514632217335</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -31171,6 +33415,12 @@
       <c r="Z374" s="3" t="n">
         <v>0.0001422879908937109</v>
       </c>
+      <c r="AA374" s="1" t="n">
+        <v>0.07028</v>
+      </c>
+      <c r="AB374" s="2" t="n">
+        <v>-0.000142267747901693</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -31253,6 +33503,12 @@
       <c r="Z375" s="3" t="n">
         <v>0.005948614099481056</v>
       </c>
+      <c r="AA375" s="1" t="n">
+        <v>0.07947</v>
+      </c>
+      <c r="AB375" s="2" t="n">
+        <v>-0.0001258178158026689</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -31335,6 +33591,12 @@
       <c r="Z376" s="3" t="n">
         <v>0.0007968127490038963</v>
       </c>
+      <c r="AA376" s="1" t="n">
+        <v>0.06285</v>
+      </c>
+      <c r="AB376" s="3" t="n">
+        <v>0.000796178343949178</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -31417,6 +33679,12 @@
       <c r="Z377" s="2" t="n">
         <v>-0.001958735962392235</v>
       </c>
+      <c r="AA377" s="1" t="n">
+        <v>0.07671</v>
+      </c>
+      <c r="AB377" s="3" t="n">
+        <v>0.003663482925552826</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -31499,6 +33767,12 @@
       <c r="Z378" s="3" t="n">
         <v>0.0127023661270237</v>
       </c>
+      <c r="AA378" s="1" t="n">
+        <v>0.0004043</v>
+      </c>
+      <c r="AB378" s="2" t="n">
+        <v>-0.005656665027053619</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -31581,6 +33855,12 @@
       <c r="Z379" s="2" t="n">
         <v>-0.001752730214372457</v>
       </c>
+      <c r="AA379" s="1" t="n">
+        <v>0.07371</v>
+      </c>
+      <c r="AB379" s="2" t="n">
+        <v>-0.004457050243111791</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -31663,6 +33943,12 @@
       <c r="Z380" s="2" t="n">
         <v>-0.001463057790782772</v>
       </c>
+      <c r="AA380" s="1" t="n">
+        <v>0.001365</v>
+      </c>
+      <c r="AB380" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -31745,6 +34031,12 @@
       <c r="Z381" s="2" t="n">
         <v>-0.003283815480844395</v>
       </c>
+      <c r="AA381" s="1" t="n">
+        <v>6.325</v>
+      </c>
+      <c r="AB381" s="2" t="n">
+        <v>-0.00768748038908056</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -31827,6 +34119,12 @@
       <c r="Z382" s="2" t="n">
         <v>-0.00358680057388807</v>
       </c>
+      <c r="AA382" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="AB382" s="3" t="n">
+        <v>0.005759539236861067</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -31909,6 +34207,12 @@
       <c r="Z383" s="2" t="n">
         <v>-0.003407155025553721</v>
       </c>
+      <c r="AA383" s="1" t="n">
+        <v>0.01757</v>
+      </c>
+      <c r="AB383" s="3" t="n">
+        <v>0.001139601139601093</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -31991,6 +34295,12 @@
       <c r="Z384" s="2" t="n">
         <v>-0.003937007874015725</v>
       </c>
+      <c r="AA384" s="1" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="AB384" s="3" t="n">
+        <v>0.0009881422924901469</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -32073,6 +34383,12 @@
       <c r="Z385" s="3" t="n">
         <v>0.0002227667631990051</v>
       </c>
+      <c r="AA385" s="1" t="n">
+        <v>4.481</v>
+      </c>
+      <c r="AB385" s="2" t="n">
+        <v>-0.002004454342984486</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -32155,6 +34471,12 @@
       <c r="Z386" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA386" s="1" t="n">
+        <v>0.001301</v>
+      </c>
+      <c r="AB386" s="2" t="n">
+        <v>-0.003828483920367544</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -32237,6 +34559,12 @@
       <c r="Z387" s="2" t="n">
         <v>-0.003532974427994611</v>
       </c>
+      <c r="AA387" s="1" t="n">
+        <v>0.000592</v>
+      </c>
+      <c r="AB387" s="2" t="n">
+        <v>-0.0005065000844167845</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -32319,6 +34647,12 @@
       <c r="Z388" s="3" t="n">
         <v>0.003496503496503506</v>
       </c>
+      <c r="AA388" s="1" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="AB388" s="2" t="n">
+        <v>-0.003484320557491298</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -32401,6 +34735,12 @@
       <c r="Z389" s="2" t="n">
         <v>-0.002209944751381317</v>
       </c>
+      <c r="AA389" s="1" t="n">
+        <v>0.009039999999999999</v>
+      </c>
+      <c r="AB389" s="3" t="n">
+        <v>0.00110741971207083</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -32483,6 +34823,12 @@
       <c r="Z390" s="2" t="n">
         <v>-0.002281658004816829</v>
       </c>
+      <c r="AA390" s="1" t="n">
+        <v>0.07868</v>
+      </c>
+      <c r="AB390" s="2" t="n">
+        <v>-0.000381145978909951</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -32565,6 +34911,12 @@
       <c r="Z391" s="3" t="n">
         <v>0.001552192471866448</v>
       </c>
+      <c r="AA391" s="1" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="AB391" s="3" t="n">
+        <v>0.001937233630375879</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -32647,6 +34999,12 @@
       <c r="Z392" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA392" s="1" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="AB392" s="2" t="n">
+        <v>-0.004219409282700433</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -32729,6 +35087,12 @@
       <c r="Z393" s="2" t="n">
         <v>-0.003274087932647363</v>
       </c>
+      <c r="AA393" s="1" t="n">
+        <v>0.02129</v>
+      </c>
+      <c r="AB393" s="2" t="n">
+        <v>-0.0009385265133739646</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -32811,6 +35175,12 @@
       <c r="Z394" s="2" t="n">
         <v>-0.001472754050073612</v>
       </c>
+      <c r="AA394" s="1" t="n">
+        <v>0.2033</v>
+      </c>
+      <c r="AB394" s="2" t="n">
+        <v>-0.0004916420845623844</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -32893,6 +35263,12 @@
       <c r="Z395" s="2" t="n">
         <v>-0.001027749229188108</v>
       </c>
+      <c r="AA395" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="AB395" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -32975,6 +35351,12 @@
       <c r="Z396" s="2" t="n">
         <v>-0.0003661662394726803</v>
       </c>
+      <c r="AA396" s="1" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AB396" s="3" t="n">
+        <v>0.01098901098901092</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -33057,6 +35439,12 @@
       <c r="Z397" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA397" s="1" t="n">
+        <v>1.262</v>
+      </c>
+      <c r="AB397" s="3" t="n">
+        <v>0.005577689243027983</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -33139,6 +35527,12 @@
       <c r="Z398" s="2" t="n">
         <v>-0.001360729350932044</v>
       </c>
+      <c r="AA398" s="1" t="n">
+        <v>0.007349</v>
+      </c>
+      <c r="AB398" s="3" t="n">
+        <v>0.001362583458236762</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -33221,6 +35615,12 @@
       <c r="Z399" s="2" t="n">
         <v>-0.001927525057825753</v>
       </c>
+      <c r="AA399" s="1" t="n">
+        <v>0.2591</v>
+      </c>
+      <c r="AB399" s="3" t="n">
+        <v>0.0007724990343761219</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -33303,6 +35703,12 @@
       <c r="Z400" s="2" t="n">
         <v>-0.002198492462311664</v>
       </c>
+      <c r="AA400" s="1" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="AB400" s="2" t="n">
+        <v>-0.0003147623544223764</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -33385,6 +35791,12 @@
       <c r="Z401" s="2" t="n">
         <v>-0.001522070015220662</v>
       </c>
+      <c r="AA401" s="1" t="n">
+        <v>0.007168</v>
+      </c>
+      <c r="AB401" s="2" t="n">
+        <v>-0.00665188470066523</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -33467,6 +35879,12 @@
       <c r="Z402" s="2" t="n">
         <v>-0.001743299193724165</v>
       </c>
+      <c r="AA402" s="1" t="n">
+        <v>0.004576</v>
+      </c>
+      <c r="AB402" s="2" t="n">
+        <v>-0.00109146474568867</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -33549,6 +35967,12 @@
       <c r="Z403" s="3" t="n">
         <v>0.001132502831256953</v>
       </c>
+      <c r="AA403" s="1" t="n">
+        <v>0.2657</v>
+      </c>
+      <c r="AB403" s="3" t="n">
+        <v>0.001885369532428358</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -33631,6 +36055,12 @@
       <c r="Z404" s="2" t="n">
         <v>-0.003745318352059975</v>
       </c>
+      <c r="AA404" s="1" t="n">
+        <v>0.2394</v>
+      </c>
+      <c r="AB404" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -33713,6 +36143,12 @@
       <c r="Z405" s="2" t="n">
         <v>-0.001939310974218557</v>
       </c>
+      <c r="AA405" s="1" t="n">
+        <v>0.0008768</v>
+      </c>
+      <c r="AB405" s="3" t="n">
+        <v>0.002171676763058626</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -33795,6 +36231,12 @@
       <c r="Z406" s="2" t="n">
         <v>-0.0005919494869770187</v>
       </c>
+      <c r="AA406" s="1" t="n">
+        <v>0.005062</v>
+      </c>
+      <c r="AB406" s="2" t="n">
+        <v>-0.0005923000987167617</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -33877,6 +36319,12 @@
       <c r="Z407" s="3" t="n">
         <v>0.0008319467554077644</v>
       </c>
+      <c r="AA407" s="1" t="n">
+        <v>0.01202</v>
+      </c>
+      <c r="AB407" s="2" t="n">
+        <v>-0.0008312551953450812</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -33959,6 +36407,12 @@
       <c r="Z408" s="3" t="n">
         <v>0.001371742112482738</v>
       </c>
+      <c r="AA408" s="1" t="n">
+        <v>0.001462</v>
+      </c>
+      <c r="AB408" s="3" t="n">
+        <v>0.001369863013698664</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -34041,6 +36495,12 @@
       <c r="Z409" s="3" t="n">
         <v>0.002112490097702581</v>
       </c>
+      <c r="AA409" s="1" t="n">
+        <v>0.03874</v>
+      </c>
+      <c r="AB409" s="3" t="n">
+        <v>0.02081686429512514</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -34123,6 +36583,12 @@
       <c r="Z410" s="3" t="n">
         <v>0.001226241569589159</v>
       </c>
+      <c r="AA410" s="1" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="AB410" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -34205,6 +36671,12 @@
       <c r="Z411" s="2" t="n">
         <v>-0.0005277044854880685</v>
       </c>
+      <c r="AA411" s="1" t="n">
+        <v>0.1887</v>
+      </c>
+      <c r="AB411" s="2" t="n">
+        <v>-0.003695881731784615</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -34287,6 +36759,12 @@
       <c r="Z412" s="2" t="n">
         <v>-0.002652910832719228</v>
       </c>
+      <c r="AA412" s="1" t="n">
+        <v>0.0674</v>
+      </c>
+      <c r="AB412" s="2" t="n">
+        <v>-0.003989951233929252</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -34369,6 +36847,12 @@
       <c r="Z413" s="2" t="n">
         <v>-0.003155818540433925</v>
       </c>
+      <c r="AA413" s="1" t="n">
+        <v>2526</v>
+      </c>
+      <c r="AB413" s="2" t="n">
+        <v>-0.0003957261574990107</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -34451,6 +36935,12 @@
       <c r="Z414" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA414" s="1" t="n">
+        <v>0.05243</v>
+      </c>
+      <c r="AB414" s="2" t="n">
+        <v>-0.0007623403849819955</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -34533,6 +37023,12 @@
       <c r="Z415" s="3" t="n">
         <v>0.00172711571675296</v>
       </c>
+      <c r="AA415" s="1" t="n">
+        <v>1.744</v>
+      </c>
+      <c r="AB415" s="3" t="n">
+        <v>0.002298850574712646</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -34615,6 +37111,12 @@
       <c r="Z416" s="2" t="n">
         <v>-0.002750434279096638</v>
       </c>
+      <c r="AA416" s="1" t="n">
+        <v>0.06901</v>
+      </c>
+      <c r="AB416" s="3" t="n">
+        <v>0.001741907388590435</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -34697,6 +37199,12 @@
       <c r="Z417" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA417" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AB417" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -34779,6 +37287,12 @@
       <c r="Z418" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA418" s="1" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="AB418" s="2" t="n">
+        <v>-0.003278688524590167</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -34861,6 +37375,12 @@
       <c r="Z419" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA419" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="AB419" s="2" t="n">
+        <v>-0.008064516129032209</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -34943,6 +37463,12 @@
       <c r="Z420" s="3" t="n">
         <v>0.002093144950287904</v>
       </c>
+      <c r="AA420" s="1" t="n">
+        <v>0.01908</v>
+      </c>
+      <c r="AB420" s="2" t="n">
+        <v>-0.003655352480417787</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -35025,6 +37551,12 @@
       <c r="Z421" s="2" t="n">
         <v>-0.00409290903509667</v>
       </c>
+      <c r="AA421" s="1" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="AB421" s="2" t="n">
+        <v>-0.00128429055789582</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -35107,6 +37639,12 @@
       <c r="Z422" s="3" t="n">
         <v>0.002932551319648178</v>
       </c>
+      <c r="AA422" s="1" t="n">
+        <v>0.03418</v>
+      </c>
+      <c r="AB422" s="2" t="n">
+        <v>-0.0005847953216374031</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -35189,6 +37727,12 @@
       <c r="Z423" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA423" s="1" t="n">
+        <v>0.1414</v>
+      </c>
+      <c r="AB423" s="2" t="n">
+        <v>-0.002117148906139695</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -35271,6 +37815,12 @@
       <c r="Z424" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA424" s="1" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="AB424" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -35353,6 +37903,12 @@
       <c r="Z425" s="2" t="n">
         <v>-0.002873563218390887</v>
       </c>
+      <c r="AA425" s="1" t="n">
+        <v>0.1042</v>
+      </c>
+      <c r="AB425" s="3" t="n">
+        <v>0.0009606147934678469</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -35435,6 +37991,12 @@
       <c r="Z426" s="3" t="n">
         <v>0.001985815602836897</v>
       </c>
+      <c r="AA426" s="1" t="n">
+        <v>0.007114</v>
+      </c>
+      <c r="AB426" s="3" t="n">
+        <v>0.007078142695356696</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -35517,6 +38079,12 @@
       <c r="Z427" s="3" t="n">
         <v>0.0003930817610062733</v>
       </c>
+      <c r="AA427" s="1" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="AB427" s="2" t="n">
+        <v>-0.001964636542239742</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -35599,6 +38167,12 @@
       <c r="Z428" s="3" t="n">
         <v>0.0003725782414306422</v>
       </c>
+      <c r="AA428" s="1" t="n">
+        <v>0.008073</v>
+      </c>
+      <c r="AB428" s="3" t="n">
+        <v>0.002234636871508461</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -35681,6 +38255,12 @@
       <c r="Z429" s="2" t="n">
         <v>-0.002423263327948345</v>
       </c>
+      <c r="AA429" s="1" t="n">
+        <v>0.01232</v>
+      </c>
+      <c r="AB429" s="2" t="n">
+        <v>-0.002429149797570892</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -35763,6 +38343,12 @@
       <c r="Z430" s="3" t="n">
         <v>0.001048532055122837</v>
       </c>
+      <c r="AA430" s="1" t="n">
+        <v>0.06675</v>
+      </c>
+      <c r="AB430" s="2" t="n">
+        <v>-0.001197067185395732</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -35845,6 +38431,12 @@
       <c r="Z431" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA431" s="1" t="n">
+        <v>0.00542</v>
+      </c>
+      <c r="AB431" s="3" t="n">
+        <v>0.003703703703703713</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -35927,6 +38519,12 @@
       <c r="Z432" s="2" t="n">
         <v>-0.003937415811832954</v>
       </c>
+      <c r="AA432" s="1" t="n">
+        <v>0.009572000000000001</v>
+      </c>
+      <c r="AB432" s="2" t="n">
+        <v>-0.004265057734318046</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -36009,6 +38607,12 @@
       <c r="Z433" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA433" s="1" t="n">
+        <v>0.04123</v>
+      </c>
+      <c r="AB433" s="2" t="n">
+        <v>-0.004346776141028727</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -36091,6 +38695,12 @@
       <c r="Z434" s="3" t="n">
         <v>0.004293893129770983</v>
       </c>
+      <c r="AA434" s="1" t="n">
+        <v>0.04239</v>
+      </c>
+      <c r="AB434" s="3" t="n">
+        <v>0.006888361045130608</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -36173,6 +38783,12 @@
       <c r="Z435" s="3" t="n">
         <v>0.001297858533419889</v>
       </c>
+      <c r="AA435" s="1" t="n">
+        <v>0.001543</v>
+      </c>
+      <c r="AB435" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -36255,6 +38871,12 @@
       <c r="Z436" s="2" t="n">
         <v>-0.0007296607077708568</v>
       </c>
+      <c r="AA436" s="1" t="n">
+        <v>0.02736</v>
+      </c>
+      <c r="AB436" s="2" t="n">
+        <v>-0.00109529025191684</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -36337,6 +38959,12 @@
       <c r="Z437" s="3" t="n">
         <v>0.00280864574429105</v>
       </c>
+      <c r="AA437" s="1" t="n">
+        <v>0.08155</v>
+      </c>
+      <c r="AB437" s="2" t="n">
+        <v>-0.006941061860691684</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -36419,6 +39047,12 @@
       <c r="Z438" s="2" t="n">
         <v>-0.001739130434782658</v>
       </c>
+      <c r="AA438" s="1" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="AB438" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -36501,6 +39135,12 @@
       <c r="Z439" s="2" t="n">
         <v>-0.0006472491909384401</v>
       </c>
+      <c r="AA439" s="1" t="n">
+        <v>1.543</v>
+      </c>
+      <c r="AB439" s="2" t="n">
+        <v>-0.0006476683937824559</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -36583,6 +39223,12 @@
       <c r="Z440" s="3" t="n">
         <v>0.001110494169905515</v>
       </c>
+      <c r="AA440" s="1" t="n">
+        <v>0.001815</v>
+      </c>
+      <c r="AB440" s="3" t="n">
+        <v>0.006655574043261273</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -36665,6 +39311,12 @@
       <c r="Z441" s="2" t="n">
         <v>-0.003250270855904714</v>
       </c>
+      <c r="AA441" s="1" t="n">
+        <v>0.03677</v>
+      </c>
+      <c r="AB441" s="2" t="n">
+        <v>-0.0008152173913044089</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -36747,6 +39399,12 @@
       <c r="Z442" s="2" t="n">
         <v>-0.001084598698481706</v>
       </c>
+      <c r="AA442" s="1" t="n">
+        <v>0.01828</v>
+      </c>
+      <c r="AB442" s="2" t="n">
+        <v>-0.00760043431053191</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -36829,6 +39487,12 @@
       <c r="Z443" s="2" t="n">
         <v>-0.002517306482064307</v>
       </c>
+      <c r="AA443" s="1" t="n">
+        <v>0.12678</v>
+      </c>
+      <c r="AB443" s="2" t="n">
+        <v>-0.0001577287066245445</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -36911,6 +39575,12 @@
       <c r="Z444" s="2" t="n">
         <v>-0.0005231037489101187</v>
       </c>
+      <c r="AA444" s="1" t="n">
+        <v>0.011438</v>
+      </c>
+      <c r="AB444" s="2" t="n">
+        <v>-0.002267969295184925</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -36993,6 +39663,12 @@
       <c r="Z445" s="2" t="n">
         <v>-0.003834735279564459</v>
       </c>
+      <c r="AA445" s="1" t="n">
+        <v>0.08053</v>
+      </c>
+      <c r="AB445" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -37075,6 +39751,12 @@
       <c r="Z446" s="3" t="n">
         <v>0.0009385265133740257</v>
       </c>
+      <c r="AA446" s="1" t="n">
+        <v>0.0002145</v>
+      </c>
+      <c r="AB446" s="3" t="n">
+        <v>0.005625879043600572</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -37157,6 +39839,12 @@
       <c r="Z447" s="2" t="n">
         <v>-0.01343283582089549</v>
       </c>
+      <c r="AA447" s="1" t="n">
+        <v>0.00664</v>
+      </c>
+      <c r="AB447" s="3" t="n">
+        <v>0.004538577912254107</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -37239,6 +39927,12 @@
       <c r="Z448" s="3" t="n">
         <v>0.006978367062107528</v>
       </c>
+      <c r="AA448" s="1" t="n">
+        <v>0.09916999999999999</v>
+      </c>
+      <c r="AB448" s="2" t="n">
+        <v>-0.0182160182160183</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -37321,6 +40015,12 @@
       <c r="Z449" s="2" t="n">
         <v>-0.00357781753130599</v>
       </c>
+      <c r="AA449" s="1" t="n">
+        <v>0.001674</v>
+      </c>
+      <c r="AB449" s="3" t="n">
+        <v>0.001795332136445221</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -37403,6 +40103,12 @@
       <c r="Z450" s="3" t="n">
         <v>0.001942690626517774</v>
       </c>
+      <c r="AA450" s="1" t="n">
+        <v>0.0002063</v>
+      </c>
+      <c r="AB450" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -37485,6 +40191,12 @@
       <c r="Z451" s="2" t="n">
         <v>-0.004160363086233093</v>
       </c>
+      <c r="AA451" s="1" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AB451" s="2" t="n">
+        <v>-0.003038359285985503</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -37567,6 +40279,12 @@
       <c r="Z452" s="2" t="n">
         <v>-0.0007440476190475371</v>
       </c>
+      <c r="AA452" s="1" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="AB452" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -37649,6 +40367,12 @@
       <c r="Z453" s="2" t="n">
         <v>-0.001144819690898556</v>
       </c>
+      <c r="AA453" s="1" t="n">
+        <v>0.0001744</v>
+      </c>
+      <c r="AB453" s="2" t="n">
+        <v>-0.0005730659025788104</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -37731,6 +40455,12 @@
       <c r="Z454" s="2" t="n">
         <v>-0.005603759942154696</v>
       </c>
+      <c r="AA454" s="1" t="n">
+        <v>0.11034</v>
+      </c>
+      <c r="AB454" s="3" t="n">
+        <v>0.002908562079621768</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -37813,6 +40543,12 @@
       <c r="Z455" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA455" s="1" t="n">
+        <v>0.5018</v>
+      </c>
+      <c r="AB455" s="2" t="n">
+        <v>-0.0005974905397330551</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -37895,6 +40631,12 @@
       <c r="Z456" s="3" t="n">
         <v>0.0001881703568964142</v>
       </c>
+      <c r="AA456" s="1" t="n">
+        <v>0.015932</v>
+      </c>
+      <c r="AB456" s="2" t="n">
+        <v>-0.0008779631255485172</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -37977,6 +40719,12 @@
       <c r="Z457" s="2" t="n">
         <v>-0.0001492982979994226</v>
       </c>
+      <c r="AA457" s="1" t="n">
+        <v>0.006682</v>
+      </c>
+      <c r="AB457" s="2" t="n">
+        <v>-0.002239808869643162</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -38059,6 +40807,12 @@
       <c r="Z458" s="2" t="n">
         <v>-0.0004154549231407935</v>
       </c>
+      <c r="AA458" s="1" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="AB458" s="2" t="n">
+        <v>-0.001454696591853769</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -38141,6 +40895,12 @@
       <c r="Z459" s="2" t="n">
         <v>-0.001101321585903094</v>
       </c>
+      <c r="AA459" s="1" t="n">
+        <v>0.006345</v>
+      </c>
+      <c r="AB459" s="2" t="n">
+        <v>-0.0006300204756654062</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -38223,6 +40983,12 @@
       <c r="Z460" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA460" s="1" t="n">
+        <v>0.1378</v>
+      </c>
+      <c r="AB460" s="3" t="n">
+        <v>0.002911208151382907</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -38305,6 +41071,12 @@
       <c r="Z461" s="2" t="n">
         <v>-0.008979413053000452</v>
       </c>
+      <c r="AA461" s="1" t="n">
+        <v>0.09003</v>
+      </c>
+      <c r="AB461" s="2" t="n">
+        <v>-0.005193370165745836</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -38387,6 +41159,12 @@
       <c r="Z462" s="3" t="n">
         <v>0.0006593406593407088</v>
       </c>
+      <c r="AA462" s="1" t="n">
+        <v>0.04538</v>
+      </c>
+      <c r="AB462" s="2" t="n">
+        <v>-0.003294531078409934</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -38469,6 +41247,12 @@
       <c r="Z463" s="2" t="n">
         <v>-0.001432664756447057</v>
       </c>
+      <c r="AA463" s="1" t="n">
+        <v>0.00698</v>
+      </c>
+      <c r="AB463" s="3" t="n">
+        <v>0.001434720229555303</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -38551,6 +41335,12 @@
       <c r="Z464" s="2" t="n">
         <v>-0.002284843869002203</v>
       </c>
+      <c r="AA464" s="1" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="AB464" s="2" t="n">
+        <v>-0.0007633587786260396</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -38633,6 +41423,12 @@
       <c r="Z465" s="2" t="n">
         <v>-0.005355230274901825</v>
       </c>
+      <c r="AA465" s="1" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="AB465" s="2" t="n">
+        <v>-0.0003589375448671535</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -38715,6 +41511,12 @@
       <c r="Z466" s="2" t="n">
         <v>-0.001408450704225353</v>
       </c>
+      <c r="AA466" s="1" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="AB466" s="2" t="n">
+        <v>-0.0007052186177714315</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -38797,6 +41599,12 @@
       <c r="Z467" s="3" t="n">
         <v>0.001047120418848307</v>
       </c>
+      <c r="AA467" s="1" t="n">
+        <v>0.01918</v>
+      </c>
+      <c r="AB467" s="3" t="n">
+        <v>0.003138075313807403</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -38879,6 +41687,12 @@
       <c r="Z468" s="3" t="n">
         <v>0.007960199004975145</v>
       </c>
+      <c r="AA468" s="1" t="n">
+        <v>0.01024</v>
+      </c>
+      <c r="AB468" s="3" t="n">
+        <v>0.01085883514313926</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -38961,6 +41775,12 @@
       <c r="Z469" s="2" t="n">
         <v>-0.00150715900527503</v>
       </c>
+      <c r="AA469" s="1" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="AB469" s="2" t="n">
+        <v>-0.0002515723270441371</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -39043,6 +41863,12 @@
       <c r="Z470" s="2" t="n">
         <v>-0.001135073779795688</v>
       </c>
+      <c r="AA470" s="1" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="AB470" s="2" t="n">
+        <v>-0.001136363636363637</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -39125,6 +41951,12 @@
       <c r="Z471" s="2" t="n">
         <v>-0.001239925604463733</v>
       </c>
+      <c r="AA471" s="1" t="n">
+        <v>3.213</v>
+      </c>
+      <c r="AB471" s="2" t="n">
+        <v>-0.002793296089385443</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -39207,6 +42039,12 @@
       <c r="Z472" s="2" t="n">
         <v>-0.004266413842142679</v>
       </c>
+      <c r="AA472" s="1" t="n">
+        <v>0.04217</v>
+      </c>
+      <c r="AB472" s="3" t="n">
+        <v>0.003808616995953354</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -39289,6 +42127,12 @@
       <c r="Z473" s="2" t="n">
         <v>-0.000802568218298467</v>
       </c>
+      <c r="AA473" s="1" t="n">
+        <v>1.248</v>
+      </c>
+      <c r="AB473" s="3" t="n">
+        <v>0.00240963855421678</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -39371,6 +42215,12 @@
       <c r="Z474" s="2" t="n">
         <v>-0.001170001170001325</v>
       </c>
+      <c r="AA474" s="1" t="n">
+        <v>0.008551</v>
+      </c>
+      <c r="AB474" s="3" t="n">
+        <v>0.001639920346726031</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -39453,6 +42303,12 @@
       <c r="Z475" s="2" t="n">
         <v>-0.0016722408026756</v>
       </c>
+      <c r="AA475" s="1" t="n">
+        <v>0.04157</v>
+      </c>
+      <c r="AB475" s="2" t="n">
+        <v>-0.005264417324718784</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -39535,6 +42391,12 @@
       <c r="Z476" s="2" t="n">
         <v>-0.002532928064843031</v>
       </c>
+      <c r="AA476" s="1" t="n">
+        <v>0.07881000000000001</v>
+      </c>
+      <c r="AB476" s="3" t="n">
+        <v>0.000634840020314987</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -39617,6 +42479,12 @@
       <c r="Z477" s="2" t="n">
         <v>-7.325470661476995e-05</v>
       </c>
+      <c r="AA477" s="1" t="n">
+        <v>0.13626</v>
+      </c>
+      <c r="AB477" s="2" t="n">
+        <v>-0.00175824175824189</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -39699,6 +42567,12 @@
       <c r="Z478" s="2" t="n">
         <v>-0.001264755480607177</v>
       </c>
+      <c r="AA478" s="1" t="n">
+        <v>0.04732</v>
+      </c>
+      <c r="AB478" s="2" t="n">
+        <v>-0.001266357112705732</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -39781,6 +42655,12 @@
       <c r="Z479" s="2" t="n">
         <v>-0.0007493443237166848</v>
       </c>
+      <c r="AA479" s="1" t="n">
+        <v>0.005337</v>
+      </c>
+      <c r="AB479" s="3" t="n">
+        <v>0.000562429696287876</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -39863,6 +42743,12 @@
       <c r="Z480" s="3" t="n">
         <v>0.001071046054980246</v>
       </c>
+      <c r="AA480" s="1" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="AB480" s="3" t="n">
+        <v>0.001426533523537844</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -39945,6 +42831,12 @@
       <c r="Z481" s="2" t="n">
         <v>-0.001318217769575572</v>
       </c>
+      <c r="AA481" s="1" t="n">
+        <v>0.07563</v>
+      </c>
+      <c r="AB481" s="2" t="n">
+        <v>-0.001715945089757012</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -40027,6 +42919,12 @@
       <c r="Z482" s="2" t="n">
         <v>-0.004685408299866172</v>
       </c>
+      <c r="AA482" s="1" t="n">
+        <v>0.01487</v>
+      </c>
+      <c r="AB482" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -40109,6 +43007,12 @@
       <c r="Z483" s="3" t="n">
         <v>0.004016064257028227</v>
       </c>
+      <c r="AA483" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB483" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -40191,6 +43095,12 @@
       <c r="Z484" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA484" s="1" t="n">
+        <v>0.02154</v>
+      </c>
+      <c r="AB484" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -40273,6 +43183,12 @@
       <c r="Z485" s="2" t="n">
         <v>-0.003247143716175496</v>
       </c>
+      <c r="AA485" s="1" t="n">
+        <v>0.008259000000000001</v>
+      </c>
+      <c r="AB485" s="2" t="n">
+        <v>-0.00349903474903469</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -40355,6 +43271,12 @@
       <c r="Z486" s="3" t="n">
         <v>0.0001341381623071942</v>
       </c>
+      <c r="AA486" s="1" t="n">
+        <v>0.007447</v>
+      </c>
+      <c r="AB486" s="2" t="n">
+        <v>-0.001207081545064422</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -40437,6 +43359,12 @@
       <c r="Z487" s="3" t="n">
         <v>0.002707581227436901</v>
       </c>
+      <c r="AA487" s="1" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="AB487" s="2" t="n">
+        <v>-0.002700270027002777</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -40519,6 +43447,12 @@
       <c r="Z488" s="3" t="n">
         <v>0.01178524661719778</v>
       </c>
+      <c r="AA488" s="1" t="n">
+        <v>0.009233999999999999</v>
+      </c>
+      <c r="AB488" s="2" t="n">
+        <v>-0.004098360655737874</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -40601,6 +43535,12 @@
       <c r="Z489" s="2" t="n">
         <v>-0.003363518758085335</v>
       </c>
+      <c r="AA489" s="1" t="n">
+        <v>0.03859</v>
+      </c>
+      <c r="AB489" s="3" t="n">
+        <v>0.001817237798546226</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -40683,6 +43623,12 @@
       <c r="Z490" s="3" t="n">
         <v>0.0001708525542457383</v>
       </c>
+      <c r="AA490" s="1" t="n">
+        <v>0.05815</v>
+      </c>
+      <c r="AB490" s="2" t="n">
+        <v>-0.006662111376836376</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -40765,6 +43711,12 @@
       <c r="Z491" s="3" t="n">
         <v>0.002076843198338585</v>
       </c>
+      <c r="AA491" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="AB491" s="3" t="n">
+        <v>0.006217616580310915</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -40847,6 +43799,12 @@
       <c r="Z492" s="2" t="n">
         <v>-0.0007535795026374453</v>
       </c>
+      <c r="AA492" s="1" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="AB492" s="3" t="n">
+        <v>0.001508295625942686</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -40929,6 +43887,12 @@
       <c r="Z493" s="2" t="n">
         <v>-0.001418439716311901</v>
       </c>
+      <c r="AA493" s="1" t="n">
+        <v>0.03524</v>
+      </c>
+      <c r="AB493" s="3" t="n">
+        <v>0.00113636363636359</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -41011,6 +43975,12 @@
       <c r="Z494" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA494" s="1" t="n">
+        <v>0.01699</v>
+      </c>
+      <c r="AB494" s="2" t="n">
+        <v>-0.000588235294117623</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -41093,6 +44063,12 @@
       <c r="Z495" s="3" t="n">
         <v>0.0004241781548250092</v>
       </c>
+      <c r="AA495" s="1" t="n">
+        <v>0.04705</v>
+      </c>
+      <c r="AB495" s="2" t="n">
+        <v>-0.0025439898240406</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -41175,6 +44151,12 @@
       <c r="Z496" s="2" t="n">
         <v>-0.0002071680132588163</v>
       </c>
+      <c r="AA496" s="1" t="n">
+        <v>0.04835</v>
+      </c>
+      <c r="AB496" s="3" t="n">
+        <v>0.001864898466639035</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -41257,6 +44239,12 @@
       <c r="Z497" s="2" t="n">
         <v>-0.001613228473482631</v>
       </c>
+      <c r="AA497" s="1" t="n">
+        <v>0.04955</v>
+      </c>
+      <c r="AB497" s="3" t="n">
+        <v>0.0008079175924055417</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -41339,6 +44327,12 @@
       <c r="Z498" s="2" t="n">
         <v>-0.0006922810661127656</v>
       </c>
+      <c r="AA498" s="1" t="n">
+        <v>0.2883</v>
+      </c>
+      <c r="AB498" s="2" t="n">
+        <v>-0.001385521302390064</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -41421,6 +44415,12 @@
       <c r="Z499" s="2" t="n">
         <v>-0.001464128843338256</v>
       </c>
+      <c r="AA499" s="1" t="n">
+        <v>0.2739</v>
+      </c>
+      <c r="AB499" s="3" t="n">
+        <v>0.004032258064516092</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -41503,6 +44503,12 @@
       <c r="Z500" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA500" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="AB500" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -41585,6 +44591,12 @@
       <c r="Z501" s="3" t="n">
         <v>0.0002797202797203654</v>
       </c>
+      <c r="AA501" s="1" t="n">
+        <v>0.03576</v>
+      </c>
+      <c r="AB501" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -41667,6 +44679,12 @@
       <c r="Z502" s="3" t="n">
         <v>0.0009395552771688772</v>
       </c>
+      <c r="AA502" s="1" t="n">
+        <v>0.03186</v>
+      </c>
+      <c r="AB502" s="2" t="n">
+        <v>-0.003128911138923744</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -41749,6 +44767,12 @@
       <c r="Z503" s="2" t="n">
         <v>-0.000645327826535854</v>
       </c>
+      <c r="AA503" s="1" t="n">
+        <v>0.007728</v>
+      </c>
+      <c r="AB503" s="2" t="n">
+        <v>-0.001937233630375856</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -41831,6 +44855,12 @@
       <c r="Z504" s="2" t="n">
         <v>-0.002280873248615222</v>
       </c>
+      <c r="AA504" s="1" t="n">
+        <v>3.042</v>
+      </c>
+      <c r="AB504" s="2" t="n">
+        <v>-0.006531678641410849</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -41913,6 +44943,12 @@
       <c r="Z505" s="2" t="n">
         <v>-0.002156624882059483</v>
       </c>
+      <c r="AA505" s="1" t="n">
+        <v>0.0007404999999999999</v>
+      </c>
+      <c r="AB505" s="3" t="n">
+        <v>0.0002701607456435181</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -41995,6 +45031,12 @@
       <c r="Z506" s="2" t="n">
         <v>-0.001703577512776833</v>
       </c>
+      <c r="AA506" s="1" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="AB506" s="2" t="n">
+        <v>-0.003071672354948657</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -42077,6 +45119,12 @@
       <c r="Z507" s="3" t="n">
         <v>0.001054852320675093</v>
       </c>
+      <c r="AA507" s="1" t="n">
+        <v>0.002842</v>
+      </c>
+      <c r="AB507" s="2" t="n">
+        <v>-0.001756234632947042</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -42159,6 +45207,12 @@
       <c r="Z508" s="2" t="n">
         <v>-0.001738855516914306</v>
       </c>
+      <c r="AA508" s="1" t="n">
+        <v>0.06304</v>
+      </c>
+      <c r="AB508" s="2" t="n">
+        <v>-0.001741884402216928</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -42241,6 +45295,12 @@
       <c r="Z509" s="2" t="n">
         <v>-0.00223613595706634</v>
       </c>
+      <c r="AA509" s="1" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="AB509" s="3" t="n">
+        <v>0.000448229493500822</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -42323,6 +45383,12 @@
       <c r="Z510" s="3" t="n">
         <v>0.00137136588041678</v>
       </c>
+      <c r="AA510" s="1" t="n">
+        <v>0.0007301</v>
+      </c>
+      <c r="AB510" s="2" t="n">
+        <v>-0.0001369487811557768</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -42405,6 +45471,12 @@
       <c r="Z511" s="2" t="n">
         <v>-0.001808318264014468</v>
       </c>
+      <c r="AA511" s="1" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="AB511" s="2" t="n">
+        <v>-0.002173913043478424</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -42487,6 +45559,12 @@
       <c r="Z512" s="2" t="n">
         <v>-0.002478314745972799</v>
       </c>
+      <c r="AA512" s="1" t="n">
+        <v>0.0004797</v>
+      </c>
+      <c r="AB512" s="2" t="n">
+        <v>-0.006832298136645904</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -42569,6 +45647,12 @@
       <c r="Z513" s="2" t="n">
         <v>-0.002518438568087808</v>
       </c>
+      <c r="AA513" s="1" t="n">
+        <v>0.05549</v>
+      </c>
+      <c r="AB513" s="3" t="n">
+        <v>0.0007213706041478516</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -42651,6 +45735,12 @@
       <c r="Z514" s="3" t="n">
         <v>0.0009868421052631176</v>
       </c>
+      <c r="AA514" s="1" t="n">
+        <v>0.03033</v>
+      </c>
+      <c r="AB514" s="2" t="n">
+        <v>-0.003286230693394657</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -42733,6 +45823,12 @@
       <c r="Z515" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA515" s="1" t="n">
+        <v>0.001137</v>
+      </c>
+      <c r="AB515" s="2" t="n">
+        <v>-0.0008787346221440386</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -42815,6 +45911,12 @@
       <c r="Z516" s="3" t="n">
         <v>0.0001514233797698566</v>
       </c>
+      <c r="AA516" s="1" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="AB516" s="2" t="n">
+        <v>-0.0007570022710067822</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -42897,6 +45999,12 @@
       <c r="Z517" s="2" t="n">
         <v>-0.001758352172820915</v>
       </c>
+      <c r="AA517" s="1" t="n">
+        <v>0.03974</v>
+      </c>
+      <c r="AB517" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -42979,6 +46087,12 @@
       <c r="Z518" s="2" t="n">
         <v>-0.002909796314257951</v>
       </c>
+      <c r="AA518" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AB518" s="3" t="n">
+        <v>0.001945525291828714</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -43061,6 +46175,12 @@
       <c r="Z519" s="2" t="n">
         <v>-0.001141552511415479</v>
       </c>
+      <c r="AA519" s="1" t="n">
+        <v>0.00872</v>
+      </c>
+      <c r="AB519" s="2" t="n">
+        <v>-0.003428571428571487</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -43143,6 +46263,12 @@
       <c r="Z520" s="3" t="n">
         <v>0.0006277463904581857</v>
       </c>
+      <c r="AA520" s="1" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="AB520" s="3" t="n">
+        <v>0.0006273525721456509</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -43225,6 +46351,12 @@
       <c r="Z521" s="2" t="n">
         <v>-0.000558347292015611</v>
       </c>
+      <c r="AA521" s="1" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AB521" s="2" t="n">
+        <v>-0.002234636871508289</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -43307,6 +46439,12 @@
       <c r="Z522" s="3" t="n">
         <v>0.0006127450980391906</v>
       </c>
+      <c r="AA522" s="1" t="n">
+        <v>0.01635</v>
+      </c>
+      <c r="AB522" s="3" t="n">
+        <v>0.001224739742804604</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -43389,6 +46527,12 @@
       <c r="Z523" s="2" t="n">
         <v>-0.0009580838323352488</v>
       </c>
+      <c r="AA523" s="1" t="n">
+        <v>0.004172</v>
+      </c>
+      <c r="AB523" s="3" t="n">
+        <v>0.0002397506593143449</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -43471,6 +46615,12 @@
       <c r="Z524" s="2" t="n">
         <v>-0.001402524544179588</v>
       </c>
+      <c r="AA524" s="1" t="n">
+        <v>0.01423</v>
+      </c>
+      <c r="AB524" s="2" t="n">
+        <v>-0.0007022471910112074</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -43553,6 +46703,12 @@
       <c r="Z525" s="2" t="n">
         <v>-0.005647438483259428</v>
       </c>
+      <c r="AA525" s="1" t="n">
+        <v>0.02461</v>
+      </c>
+      <c r="AB525" s="2" t="n">
+        <v>-0.001622718052738271</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -43635,6 +46791,12 @@
       <c r="Z526" s="2" t="n">
         <v>-0.003327787021630595</v>
       </c>
+      <c r="AA526" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB526" s="3" t="n">
+        <v>0.001669449081802937</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -43717,6 +46879,12 @@
       <c r="Z527" s="2" t="n">
         <v>-0.00471109879451286</v>
       </c>
+      <c r="AA527" s="1" t="n">
+        <v>0.07188</v>
+      </c>
+      <c r="AB527" s="3" t="n">
+        <v>0.0006960879855212932</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -43799,6 +46967,12 @@
       <c r="Z528" s="2" t="n">
         <v>-0.001387283236994163</v>
       </c>
+      <c r="AA528" s="1" t="n">
+        <v>0.04319</v>
+      </c>
+      <c r="AB528" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -43881,6 +47055,12 @@
       <c r="Z529" s="2" t="n">
         <v>-0.0007923930269414955</v>
       </c>
+      <c r="AA529" s="1" t="n">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="AB529" s="3" t="n">
+        <v>0.0006344171292624643</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -43963,6 +47143,12 @@
       <c r="Z530" s="2" t="n">
         <v>-0.002386160270431469</v>
       </c>
+      <c r="AA530" s="1" t="n">
+        <v>0.005027</v>
+      </c>
+      <c r="AB530" s="3" t="n">
+        <v>0.001993223041658453</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -44045,6 +47231,12 @@
       <c r="Z531" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA531" s="1" t="n">
+        <v>0.1296</v>
+      </c>
+      <c r="AB531" s="3" t="n">
+        <v>0.003095975232198016</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -44127,6 +47319,12 @@
       <c r="Z532" s="2" t="n">
         <v>-0.0007523039307881381</v>
       </c>
+      <c r="AA532" s="1" t="n">
+        <v>0.05315</v>
+      </c>
+      <c r="AB532" s="3" t="n">
+        <v>0.00037643515904397</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -44209,6 +47407,12 @@
       <c r="Z533" s="2" t="n">
         <v>-0.002143048486472058</v>
       </c>
+      <c r="AA533" s="1" t="n">
+        <v>0.003727</v>
+      </c>
+      <c r="AB533" s="3" t="n">
+        <v>0.0005369127516778072</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -44291,6 +47495,12 @@
       <c r="Z534" s="2" t="n">
         <v>-0.0005827505827505186</v>
       </c>
+      <c r="AA534" s="1" t="n">
+        <v>0.1714</v>
+      </c>
+      <c r="AB534" s="2" t="n">
+        <v>-0.0005830903790088439</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -44373,6 +47583,12 @@
       <c r="Z535" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA535" s="1" t="n">
+        <v>1.13e-05</v>
+      </c>
+      <c r="AB535" s="3" t="n">
+        <v>0.008928571428571494</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -44455,6 +47671,12 @@
       <c r="Z536" s="2" t="n">
         <v>-0.002032061413411532</v>
       </c>
+      <c r="AA536" s="1" t="n">
+        <v>0.0004417</v>
+      </c>
+      <c r="AB536" s="2" t="n">
+        <v>-0.0006787330316742246</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -44537,6 +47759,12 @@
       <c r="Z537" s="2" t="n">
         <v>-0.00103842159916922</v>
       </c>
+      <c r="AA537" s="1" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="AB537" s="2" t="n">
+        <v>-0.002079002079002175</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -44619,6 +47847,12 @@
       <c r="Z538" s="2" t="n">
         <v>-0.0007331378299119936</v>
       </c>
+      <c r="AA538" s="1" t="n">
+        <v>0.05455</v>
+      </c>
+      <c r="AB538" s="3" t="n">
+        <v>0.000550256786500408</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -44701,6 +47935,12 @@
       <c r="Z539" s="2" t="n">
         <v>-0.001469723691945916</v>
       </c>
+      <c r="AA539" s="1" t="n">
+        <v>0.6792</v>
+      </c>
+      <c r="AB539" s="2" t="n">
+        <v>-0.0002943773918162761</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -44783,6 +48023,12 @@
       <c r="Z540" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA540" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="AB540" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -44865,6 +48111,12 @@
       <c r="Z541" s="3" t="n">
         <v>0.0007674597083652796</v>
       </c>
+      <c r="AA541" s="1" t="n">
+        <v>0.01302</v>
+      </c>
+      <c r="AB541" s="2" t="n">
+        <v>-0.001533742331288281</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -44947,6 +48199,12 @@
       <c r="Z542" s="3" t="n">
         <v>0.0007153075822604669</v>
       </c>
+      <c r="AA542" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="AB542" s="3" t="n">
+        <v>0.0007147962830592989</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -45028,6 +48286,12 @@
       </c>
       <c r="Z543" s="2" t="n">
         <v>-0.0003506311360448665</v>
+      </c>
+      <c r="AA543" s="1" t="n">
+        <v>0.05701</v>
+      </c>
+      <c r="AB543" s="2" t="n">
+        <v>-0.0001753770606805167</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB543"/>
+  <dimension ref="A1:AD543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -454,6 +454,8 @@
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -597,6 +599,16 @@
           <t>change_03:15</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>price_03:30</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>change_03:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -685,6 +697,12 @@
       <c r="AB2" s="3" t="n">
         <v>0.001662353146863168</v>
       </c>
+      <c r="AC2" s="1" t="n">
+        <v>70160.8</v>
+      </c>
+      <c r="AD2" s="3" t="n">
+        <v>0.003779869120958632</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -773,6 +791,12 @@
       <c r="AB3" s="3" t="n">
         <v>0.0003467169324828883</v>
       </c>
+      <c r="AC3" s="1" t="n">
+        <v>2060.43</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>0.005828683566920051</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -861,6 +885,12 @@
       <c r="AB4" s="2" t="n">
         <v>-0.0002330730684068992</v>
       </c>
+      <c r="AC4" s="1" t="n">
+        <v>86.39</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>0.006993822123790585</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -949,6 +979,12 @@
       <c r="AB5" s="2" t="n">
         <v>-0.007074569789675062</v>
       </c>
+      <c r="AC5" s="1" t="n">
+        <v>0.010474</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>0.008472944348161109</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1037,6 +1073,12 @@
       <c r="AB6" s="3" t="n">
         <v>0.0002916727431821175</v>
       </c>
+      <c r="AC6" s="1" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>0.003790640034990592</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1125,6 +1167,12 @@
       <c r="AB7" s="3" t="n">
         <v>0.002026018340797566</v>
       </c>
+      <c r="AC7" s="1" t="n">
+        <v>0.09433999999999999</v>
+      </c>
+      <c r="AD7" s="3" t="n">
+        <v>0.003937426838352616</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1213,6 +1261,12 @@
       <c r="AB8" s="2" t="n">
         <v>-0.001698021669990709</v>
       </c>
+      <c r="AC8" s="1" t="n">
+        <v>37.234</v>
+      </c>
+      <c r="AD8" s="3" t="n">
+        <v>0.005264720969788608</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1301,6 +1355,12 @@
       <c r="AB9" s="3" t="n">
         <v>0.01643945469125905</v>
       </c>
+      <c r="AC9" s="1" t="n">
+        <v>0.04995</v>
+      </c>
+      <c r="AD9" s="2" t="n">
+        <v>-0.01479289940828404</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1389,6 +1449,12 @@
       <c r="AB10" s="2" t="n">
         <v>-0.01035319493124832</v>
       </c>
+      <c r="AC10" s="1" t="n">
+        <v>18.462</v>
+      </c>
+      <c r="AD10" s="3" t="n">
+        <v>0.005939083528578336</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1477,6 +1543,12 @@
       <c r="AB11" s="2" t="n">
         <v>-0.0003086324496156473</v>
       </c>
+      <c r="AC11" s="1" t="n">
+        <v>650.71</v>
+      </c>
+      <c r="AD11" s="3" t="n">
+        <v>0.004461115742027085</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1565,6 +1637,12 @@
       <c r="AB12" s="2" t="n">
         <v>-0.01496872207327968</v>
       </c>
+      <c r="AC12" s="1" t="n">
+        <v>0.8794</v>
+      </c>
+      <c r="AD12" s="2" t="n">
+        <v>-0.002721705602177443</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1653,6 +1731,12 @@
       <c r="AB13" s="2" t="n">
         <v>-0.002727664258027435</v>
       </c>
+      <c r="AC13" s="1" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="AD13" s="3" t="n">
+        <v>0.002399232245681382</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1741,6 +1825,12 @@
       <c r="AB14" s="3" t="n">
         <v>0.0007230004518753</v>
       </c>
+      <c r="AC14" s="1" t="n">
+        <v>0.0033448</v>
+      </c>
+      <c r="AD14" s="3" t="n">
+        <v>0.006893645203046503</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1829,6 +1919,12 @@
       <c r="AB15" s="2" t="n">
         <v>-0.003449454613257092</v>
       </c>
+      <c r="AC15" s="1" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="AD15" s="3" t="n">
+        <v>0.01393912935013089</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1917,6 +2013,12 @@
       <c r="AB16" s="3" t="n">
         <v>0.0007206094296890291</v>
       </c>
+      <c r="AC16" s="1" t="n">
+        <v>0.9804</v>
+      </c>
+      <c r="AD16" s="3" t="n">
+        <v>0.008538216232897938</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2005,6 +2107,12 @@
       <c r="AB17" s="2" t="n">
         <v>-0.03942652329749105</v>
       </c>
+      <c r="AC17" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AD17" s="3" t="n">
+        <v>0.007462686567164134</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2093,6 +2201,12 @@
       <c r="AB18" s="3" t="n">
         <v>0.000568936089512633</v>
       </c>
+      <c r="AC18" s="1" t="n">
+        <v>213.57</v>
+      </c>
+      <c r="AD18" s="3" t="n">
+        <v>0.01198824867323731</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2181,6 +2295,12 @@
       <c r="AB19" s="3" t="n">
         <v>0.0003835826620636325</v>
       </c>
+      <c r="AC19" s="1" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="AD19" s="3" t="n">
+        <v>0.005751533742331294</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2269,6 +2389,12 @@
       <c r="AB20" s="2" t="n">
         <v>-0.004609908385364954</v>
       </c>
+      <c r="AC20" s="1" t="n">
+        <v>0.016939</v>
+      </c>
+      <c r="AD20" s="2" t="n">
+        <v>-0.006976198850979074</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2357,6 +2483,12 @@
       <c r="AB21" s="3" t="n">
         <v>0.0008385744234801778</v>
       </c>
+      <c r="AC21" s="1" t="n">
+        <v>9.603</v>
+      </c>
+      <c r="AD21" s="3" t="n">
+        <v>0.00576036866359444</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2445,6 +2577,12 @@
       <c r="AB22" s="2" t="n">
         <v>-0.002963841138115</v>
       </c>
+      <c r="AC22" s="1" t="n">
+        <v>0.1673</v>
+      </c>
+      <c r="AD22" s="2" t="n">
+        <v>-0.005350772889417267</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2533,6 +2671,12 @@
       <c r="AB23" s="3" t="n">
         <v>0.002815021185211058</v>
       </c>
+      <c r="AC23" s="1" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="AD23" s="3" t="n">
+        <v>0.005990450007234729</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2621,6 +2765,12 @@
       <c r="AB24" s="2" t="n">
         <v>-0.001157407407407408</v>
       </c>
+      <c r="AC24" s="1" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AD24" s="3" t="n">
+        <v>0.008111239860950182</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2709,6 +2859,12 @@
       <c r="AB25" s="3" t="n">
         <v>0.0007801181321742642</v>
       </c>
+      <c r="AC25" s="1" t="n">
+        <v>9.026999999999999</v>
+      </c>
+      <c r="AD25" s="3" t="n">
+        <v>0.005233853006681383</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2797,6 +2953,12 @@
       <c r="AB26" s="3" t="n">
         <v>0.00225056264066025</v>
       </c>
+      <c r="AC26" s="1" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="AD26" s="3" t="n">
+        <v>0.006736526946107707</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2885,6 +3047,12 @@
       <c r="AB27" s="2" t="n">
         <v>-0.001582846416824012</v>
       </c>
+      <c r="AC27" s="1" t="n">
+        <v>5098.56</v>
+      </c>
+      <c r="AD27" s="3" t="n">
+        <v>0.001614823371326916</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2973,6 +3141,12 @@
       <c r="AB28" s="3" t="n">
         <v>0.002524544179523175</v>
       </c>
+      <c r="AC28" s="1" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="AD28" s="3" t="n">
+        <v>0.01119194180190264</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3061,6 +3235,12 @@
       <c r="AB29" s="2" t="n">
         <v>-0.001142857142857186</v>
       </c>
+      <c r="AC29" s="1" t="n">
+        <v>2.629</v>
+      </c>
+      <c r="AD29" s="3" t="n">
+        <v>0.002669717772692646</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3149,6 +3329,12 @@
       <c r="AB30" s="3" t="n">
         <v>0.007905347113403866</v>
       </c>
+      <c r="AC30" s="1" t="n">
+        <v>0.57347</v>
+      </c>
+      <c r="AD30" s="3" t="n">
+        <v>0.001764315410683832</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3237,6 +3423,12 @@
       <c r="AB31" s="2" t="n">
         <v>-0.003384912959381074</v>
       </c>
+      <c r="AC31" s="1" t="n">
+        <v>0.002087</v>
+      </c>
+      <c r="AD31" s="3" t="n">
+        <v>0.0126152353226589</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3325,6 +3517,12 @@
       <c r="AB32" s="3" t="n">
         <v>0.004486733194089911</v>
       </c>
+      <c r="AC32" s="1" t="n">
+        <v>1.3191</v>
+      </c>
+      <c r="AD32" s="3" t="n">
+        <v>0.01586445899114359</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3413,6 +3611,12 @@
       <c r="AB33" s="3" t="n">
         <v>0.004819277108433706</v>
       </c>
+      <c r="AC33" s="1" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AD33" s="2" t="n">
+        <v>-0.0008992805755396357</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3501,6 +3705,12 @@
       <c r="AB34" s="3" t="n">
         <v>0.001335113484646196</v>
       </c>
+      <c r="AC34" s="1" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD34" s="3" t="n">
+        <v>0.006666666666666672</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3589,6 +3799,12 @@
       <c r="AB35" s="3" t="n">
         <v>0.000241779497098676</v>
       </c>
+      <c r="AC35" s="1" t="n">
+        <v>456.21</v>
+      </c>
+      <c r="AD35" s="3" t="n">
+        <v>0.002505109104093846</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3677,6 +3893,12 @@
       <c r="AB36" s="2" t="n">
         <v>-0.002295013561443751</v>
       </c>
+      <c r="AC36" s="1" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="AD36" s="3" t="n">
+        <v>0.001672940192388054</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3765,6 +3987,12 @@
       <c r="AB37" s="2" t="n">
         <v>-0.000427837992013802</v>
       </c>
+      <c r="AC37" s="1" t="n">
+        <v>0.7018</v>
+      </c>
+      <c r="AD37" s="3" t="n">
+        <v>0.001284063347125142</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3853,6 +4081,12 @@
       <c r="AB38" s="2" t="n">
         <v>-0.0009514747859182004</v>
       </c>
+      <c r="AC38" s="1" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="AD38" s="3" t="n">
+        <v>0.01142857142857149</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3941,6 +4175,12 @@
       <c r="AB39" s="3" t="n">
         <v>0.002373995617238907</v>
       </c>
+      <c r="AC39" s="1" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="AD39" s="3" t="n">
+        <v>0.01202404809619232</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4029,6 +4269,12 @@
       <c r="AB40" s="2" t="n">
         <v>-0.007321041214750714</v>
       </c>
+      <c r="AC40" s="1" t="n">
+        <v>0.03685</v>
+      </c>
+      <c r="AD40" s="3" t="n">
+        <v>0.006555585905490415</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4117,6 +4363,12 @@
       <c r="AB41" s="2" t="n">
         <v>-0.002178649237472678</v>
       </c>
+      <c r="AC41" s="1" t="n">
+        <v>0.05492</v>
+      </c>
+      <c r="AD41" s="2" t="n">
+        <v>-0.0007278020378458025</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4205,6 +4457,12 @@
       <c r="AB42" s="3" t="n">
         <v>0.001109467455621344</v>
       </c>
+      <c r="AC42" s="1" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="AD42" s="3" t="n">
+        <v>0.002585888437384569</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4293,6 +4551,12 @@
       <c r="AB43" s="3" t="n">
         <v>0.00226928895612704</v>
       </c>
+      <c r="AC43" s="1" t="n">
+        <v>0.1341</v>
+      </c>
+      <c r="AD43" s="3" t="n">
+        <v>0.01207547169811313</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4381,6 +4645,12 @@
       <c r="AB44" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC44" s="1" t="n">
+        <v>0.005904</v>
+      </c>
+      <c r="AD44" s="3" t="n">
+        <v>0.0075085324232083</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4469,6 +4739,12 @@
       <c r="AB45" s="2" t="n">
         <v>-0.006298110566829869</v>
       </c>
+      <c r="AC45" s="1" t="n">
+        <v>0.09934999999999999</v>
+      </c>
+      <c r="AD45" s="2" t="n">
+        <v>-0.0005030181086519956</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4557,6 +4833,12 @@
       <c r="AB46" s="2" t="n">
         <v>-0.009355883411298957</v>
       </c>
+      <c r="AC46" s="1" t="n">
+        <v>3.026</v>
+      </c>
+      <c r="AD46" s="3" t="n">
+        <v>0.09916454776607325</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4645,6 +4927,12 @@
       <c r="AB47" s="2" t="n">
         <v>-0.0003117530915514184</v>
       </c>
+      <c r="AC47" s="1" t="n">
+        <v>0.28872</v>
+      </c>
+      <c r="AD47" s="3" t="n">
+        <v>0.0004158004158002545</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4733,6 +5021,12 @@
       <c r="AB48" s="2" t="n">
         <v>-0.003741814780168359</v>
       </c>
+      <c r="AC48" s="1" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="AD48" s="3" t="n">
+        <v>0.006572769953051701</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4821,6 +5115,12 @@
       <c r="AB49" s="2" t="n">
         <v>-0.003909113119960863</v>
       </c>
+      <c r="AC49" s="1" t="n">
+        <v>0.24434</v>
+      </c>
+      <c r="AD49" s="2" t="n">
+        <v>-0.001144632491210868</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4909,6 +5209,12 @@
       <c r="AB50" s="3" t="n">
         <v>0.004849251528568439</v>
       </c>
+      <c r="AC50" s="1" t="n">
+        <v>0.04767</v>
+      </c>
+      <c r="AD50" s="3" t="n">
+        <v>0.0002098195551824617</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4997,6 +5303,12 @@
       <c r="AB51" s="2" t="n">
         <v>-0.0005142710208279197</v>
       </c>
+      <c r="AC51" s="1" t="n">
+        <v>3.909</v>
+      </c>
+      <c r="AD51" s="3" t="n">
+        <v>0.005659891947517313</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5085,6 +5397,12 @@
       <c r="AB52" s="2" t="n">
         <v>-0.00434782608695651</v>
       </c>
+      <c r="AC52" s="1" t="n">
+        <v>0.000229</v>
+      </c>
+      <c r="AD52" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5173,6 +5491,12 @@
       <c r="AB53" s="3" t="n">
         <v>0.0005973715651136006</v>
       </c>
+      <c r="AC53" s="1" t="n">
+        <v>0.1694</v>
+      </c>
+      <c r="AD53" s="3" t="n">
+        <v>0.01134328358208946</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5261,6 +5585,12 @@
       <c r="AB54" s="3" t="n">
         <v>0.001429592566118598</v>
       </c>
+      <c r="AC54" s="1" t="n">
+        <v>0.04204</v>
+      </c>
+      <c r="AD54" s="3" t="n">
+        <v>0.0002379252914585549</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5349,6 +5679,12 @@
       <c r="AB55" s="3" t="n">
         <v>0.01359591298615688</v>
       </c>
+      <c r="AC55" s="1" t="n">
+        <v>0.12212</v>
+      </c>
+      <c r="AD55" s="2" t="n">
+        <v>-0.007235184131371336</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5437,6 +5773,12 @@
       <c r="AB56" s="3" t="n">
         <v>0.002870813397129225</v>
       </c>
+      <c r="AC56" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AD56" s="3" t="n">
+        <v>0.005089058524172997</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5525,6 +5867,12 @@
       <c r="AB57" s="3" t="n">
         <v>0.004363001745200672</v>
       </c>
+      <c r="AC57" s="1" t="n">
+        <v>0.01153</v>
+      </c>
+      <c r="AD57" s="3" t="n">
+        <v>0.001737619461338047</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5613,6 +5961,12 @@
       <c r="AB58" s="3" t="n">
         <v>0.002018163471241229</v>
       </c>
+      <c r="AC58" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="AD58" s="3" t="n">
+        <v>0.009063444108761309</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5701,6 +6055,12 @@
       <c r="AB59" s="2" t="n">
         <v>-0.003012048192771092</v>
       </c>
+      <c r="AC59" s="1" t="n">
+        <v>0.00334</v>
+      </c>
+      <c r="AD59" s="3" t="n">
+        <v>0.009063444108761353</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5789,6 +6149,12 @@
       <c r="AB60" s="3" t="n">
         <v>0.002600780234070296</v>
       </c>
+      <c r="AC60" s="1" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="AD60" s="3" t="n">
+        <v>0.01297016861219197</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5877,6 +6243,12 @@
       <c r="AB61" s="3" t="n">
         <v>0.001259842519685076</v>
       </c>
+      <c r="AC61" s="1" t="n">
+        <v>0.15983</v>
+      </c>
+      <c r="AD61" s="3" t="n">
+        <v>0.005536332179930744</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5965,6 +6337,12 @@
       <c r="AB62" s="2" t="n">
         <v>-0.0002831657935722625</v>
       </c>
+      <c r="AC62" s="1" t="n">
+        <v>0.7116</v>
+      </c>
+      <c r="AD62" s="3" t="n">
+        <v>0.007789264976632291</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6053,6 +6431,12 @@
       <c r="AB63" s="2" t="n">
         <v>-0.001853411962931631</v>
       </c>
+      <c r="AC63" s="1" t="n">
+        <v>6.101</v>
+      </c>
+      <c r="AD63" s="3" t="n">
+        <v>0.02987846049966232</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6141,6 +6525,12 @@
       <c r="AB64" s="3" t="n">
         <v>0.0002799552071667691</v>
       </c>
+      <c r="AC64" s="1" t="n">
+        <v>0.007222</v>
+      </c>
+      <c r="AD64" s="3" t="n">
+        <v>0.01063532045899812</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6229,6 +6619,12 @@
       <c r="AB65" s="2" t="n">
         <v>-0.01104633323105244</v>
       </c>
+      <c r="AC65" s="1" t="n">
+        <v>0.03203</v>
+      </c>
+      <c r="AD65" s="2" t="n">
+        <v>-0.006205398696866236</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6317,6 +6713,12 @@
       <c r="AB66" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC66" s="1" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AD66" s="3" t="n">
+        <v>0.008583690987124351</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6405,6 +6807,12 @@
       <c r="AB67" s="3" t="n">
         <v>0.01000625390869294</v>
       </c>
+      <c r="AC67" s="1" t="n">
+        <v>1.624</v>
+      </c>
+      <c r="AD67" s="3" t="n">
+        <v>0.00557275541795673</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6493,6 +6901,12 @@
       <c r="AB68" s="3" t="n">
         <v>0.004080414012738847</v>
       </c>
+      <c r="AC68" s="1" t="n">
+        <v>2.0318</v>
+      </c>
+      <c r="AD68" s="3" t="n">
+        <v>0.00693824957874925</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6581,6 +6995,12 @@
       <c r="AB69" s="2" t="n">
         <v>-0.0005148446885189068</v>
       </c>
+      <c r="AC69" s="1" t="n">
+        <v>0.5849</v>
+      </c>
+      <c r="AD69" s="3" t="n">
+        <v>0.004292582417582326</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6669,6 +7089,12 @@
       <c r="AB70" s="2" t="n">
         <v>-0.009708737864077679</v>
       </c>
+      <c r="AC70" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AD70" s="3" t="n">
+        <v>0.00980392156862746</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6757,6 +7183,12 @@
       <c r="AB71" s="3" t="n">
         <v>0.003535520936913027</v>
       </c>
+      <c r="AC71" s="1" t="n">
+        <v>0.9135</v>
+      </c>
+      <c r="AD71" s="3" t="n">
+        <v>0.005724980733237898</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6845,6 +7277,12 @@
       <c r="AB72" s="3" t="n">
         <v>0.0002362948960302197</v>
       </c>
+      <c r="AC72" s="1" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="AD72" s="2" t="n">
+        <v>-0.004488542404913803</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6933,6 +7371,12 @@
       <c r="AB73" s="3" t="n">
         <v>0.0004266666666666493</v>
       </c>
+      <c r="AC73" s="1" t="n">
+        <v>0.09435</v>
+      </c>
+      <c r="AD73" s="3" t="n">
+        <v>0.005970785798059547</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7021,6 +7465,12 @@
       <c r="AB74" s="3" t="n">
         <v>0.0004372158097236315</v>
       </c>
+      <c r="AC74" s="1" t="n">
+        <v>1.1454</v>
+      </c>
+      <c r="AD74" s="3" t="n">
+        <v>0.00113626431256016</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7109,6 +7559,12 @@
       <c r="AB75" s="3" t="n">
         <v>0.002518891687657547</v>
       </c>
+      <c r="AC75" s="1" t="n">
+        <v>0.01601</v>
+      </c>
+      <c r="AD75" s="3" t="n">
+        <v>0.005653266331658279</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7197,6 +7653,12 @@
       <c r="AB76" s="2" t="n">
         <v>-0.03305719921104536</v>
       </c>
+      <c r="AC76" s="1" t="n">
+        <v>0.12154</v>
+      </c>
+      <c r="AD76" s="2" t="n">
+        <v>-0.008322454308094052</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7285,6 +7747,12 @@
       <c r="AB77" s="3" t="n">
         <v>0.00341296928327643</v>
       </c>
+      <c r="AC77" s="1" t="n">
+        <v>0.1187</v>
+      </c>
+      <c r="AD77" s="3" t="n">
+        <v>0.009353741496598672</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7373,6 +7841,12 @@
       <c r="AB78" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC78" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="AD78" s="3" t="n">
+        <v>0.01190476190476183</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7461,6 +7935,12 @@
       <c r="AB79" s="3" t="n">
         <v>0.002831445702864844</v>
       </c>
+      <c r="AC79" s="1" t="n">
+        <v>0.006064</v>
+      </c>
+      <c r="AD79" s="3" t="n">
+        <v>0.007141670818800802</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7549,6 +8029,12 @@
       <c r="AB80" s="2" t="n">
         <v>-0.009488139825218437</v>
       </c>
+      <c r="AC80" s="1" t="n">
+        <v>0.007887999999999999</v>
+      </c>
+      <c r="AD80" s="2" t="n">
+        <v>-0.005797832114948437</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7637,6 +8123,12 @@
       <c r="AB81" s="3" t="n">
         <v>0.003359462486002367</v>
       </c>
+      <c r="AC81" s="1" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="AD81" s="3" t="n">
+        <v>0.002232142857142809</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7725,6 +8217,12 @@
       <c r="AB82" s="3" t="n">
         <v>0.00370599135268695</v>
       </c>
+      <c r="AC82" s="1" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="AD82" s="3" t="n">
+        <v>0.006769230769230707</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7813,6 +8311,12 @@
       <c r="AB83" s="3" t="n">
         <v>0.0001220703124999323</v>
       </c>
+      <c r="AC83" s="1" t="n">
+        <v>8.241</v>
+      </c>
+      <c r="AD83" s="3" t="n">
+        <v>0.005858659831563535</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7901,6 +8405,12 @@
       <c r="AB84" s="2" t="n">
         <v>-0.01306728381124406</v>
       </c>
+      <c r="AC84" s="1" t="n">
+        <v>351.07</v>
+      </c>
+      <c r="AD84" s="3" t="n">
+        <v>0.003946352483628343</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7989,6 +8499,12 @@
       <c r="AB85" s="3" t="n">
         <v>0.0007378258730938344</v>
       </c>
+      <c r="AC85" s="1" t="n">
+        <v>0.00409</v>
+      </c>
+      <c r="AD85" s="3" t="n">
+        <v>0.005160973212091469</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8077,6 +8593,12 @@
       <c r="AB86" s="3" t="n">
         <v>0.00282939512120524</v>
       </c>
+      <c r="AC86" s="1" t="n">
+        <v>0.13114</v>
+      </c>
+      <c r="AD86" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8165,6 +8687,12 @@
       <c r="AB87" s="2" t="n">
         <v>-0.03308823529411775</v>
       </c>
+      <c r="AC87" s="1" t="n">
+        <v>0.01803</v>
+      </c>
+      <c r="AD87" s="2" t="n">
+        <v>-0.02064095600217265</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8253,6 +8781,12 @@
       <c r="AB88" s="2" t="n">
         <v>-0.001768346595932804</v>
       </c>
+      <c r="AC88" s="1" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="AD88" s="3" t="n">
+        <v>0.005314437555358729</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8341,6 +8875,12 @@
       <c r="AB89" s="2" t="n">
         <v>-0.003057065217391345</v>
       </c>
+      <c r="AC89" s="1" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="AD89" s="3" t="n">
+        <v>0.003747870528108995</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8429,6 +8969,12 @@
       <c r="AB90" s="3" t="n">
         <v>0.001559454191033183</v>
       </c>
+      <c r="AC90" s="1" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="AD90" s="3" t="n">
+        <v>0.008952899961074226</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8517,6 +9063,12 @@
       <c r="AB91" s="2" t="n">
         <v>-0.001429337144898995</v>
       </c>
+      <c r="AC91" s="1" t="n">
+        <v>0.05493</v>
+      </c>
+      <c r="AD91" s="2" t="n">
+        <v>-0.01717659688674186</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8605,6 +9157,12 @@
       <c r="AB92" s="3" t="n">
         <v>0.0005332520758740938</v>
       </c>
+      <c r="AC92" s="1" t="n">
+        <v>1.3133</v>
+      </c>
+      <c r="AD92" s="2" t="n">
+        <v>-7.613826709303258e-05</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8693,6 +9251,12 @@
       <c r="AB93" s="2" t="n">
         <v>-0.000158227848101424</v>
       </c>
+      <c r="AC93" s="1" t="n">
+        <v>0.06371</v>
+      </c>
+      <c r="AD93" s="3" t="n">
+        <v>0.008229150181990925</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8781,6 +9345,12 @@
       <c r="AB94" s="2" t="n">
         <v>-0.003382187147688701</v>
       </c>
+      <c r="AC94" s="1" t="n">
+        <v>0.00885</v>
+      </c>
+      <c r="AD94" s="3" t="n">
+        <v>0.001131221719456967</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8869,6 +9439,12 @@
       <c r="AB95" s="3" t="n">
         <v>0.001200120012001234</v>
       </c>
+      <c r="AC95" s="1" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="AD95" s="3" t="n">
+        <v>0.01078813305364097</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8957,6 +9533,12 @@
       <c r="AB96" s="2" t="n">
         <v>-0.0008888888888888527</v>
       </c>
+      <c r="AC96" s="1" t="n">
+        <v>0.02254</v>
+      </c>
+      <c r="AD96" s="3" t="n">
+        <v>0.002669039145907519</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9045,6 +9627,12 @@
       <c r="AB97" s="2" t="n">
         <v>-0.0009202453987730409</v>
       </c>
+      <c r="AC97" s="1" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="AD97" s="3" t="n">
+        <v>0.004912496162112269</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9133,6 +9721,12 @@
       <c r="AB98" s="3" t="n">
         <v>0.003606853020739408</v>
       </c>
+      <c r="AC98" s="1" t="n">
+        <v>1.121</v>
+      </c>
+      <c r="AD98" s="3" t="n">
+        <v>0.00718778077268644</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9221,6 +9815,12 @@
       <c r="AB99" s="3" t="n">
         <v>0.003654485049833928</v>
       </c>
+      <c r="AC99" s="1" t="n">
+        <v>3.036</v>
+      </c>
+      <c r="AD99" s="3" t="n">
+        <v>0.004965243296921591</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9309,6 +9909,12 @@
       <c r="AB100" s="2" t="n">
         <v>-0.001167542323409176</v>
       </c>
+      <c r="AC100" s="1" t="n">
+        <v>0.03445</v>
+      </c>
+      <c r="AD100" s="3" t="n">
+        <v>0.006721215663354794</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9397,6 +10003,12 @@
       <c r="AB101" s="3" t="n">
         <v>0.002745744096650256</v>
       </c>
+      <c r="AC101" s="1" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="AD101" s="3" t="n">
+        <v>0.002738225629791836</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9485,6 +10097,12 @@
       <c r="AB102" s="2" t="n">
         <v>-0.01475595913734392</v>
       </c>
+      <c r="AC102" s="1" t="n">
+        <v>0.006938</v>
+      </c>
+      <c r="AD102" s="2" t="n">
+        <v>-0.0008640552995391604</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9573,6 +10191,12 @@
       <c r="AB103" s="2" t="n">
         <v>-0.0100721587492482</v>
       </c>
+      <c r="AC103" s="1" t="n">
+        <v>0.06605999999999999</v>
+      </c>
+      <c r="AD103" s="3" t="n">
+        <v>0.003189066059225329</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9661,6 +10285,12 @@
       <c r="AB104" s="2" t="n">
         <v>-0.004125212327105156</v>
       </c>
+      <c r="AC104" s="1" t="n">
+        <v>0.4109</v>
+      </c>
+      <c r="AD104" s="3" t="n">
+        <v>0.00121832358674464</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9749,6 +10379,12 @@
       <c r="AB105" s="3" t="n">
         <v>0.00502512562814077</v>
       </c>
+      <c r="AC105" s="1" t="n">
+        <v>1.823</v>
+      </c>
+      <c r="AD105" s="3" t="n">
+        <v>0.01277777777777773</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9837,6 +10473,12 @@
       <c r="AB106" s="2" t="n">
         <v>-0.01144109055501444</v>
       </c>
+      <c r="AC106" s="1" t="n">
+        <v>0.008178</v>
+      </c>
+      <c r="AD106" s="3" t="n">
+        <v>0.006894853484363304</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9925,6 +10567,12 @@
       <c r="AB107" s="2" t="n">
         <v>-0.002748763056624597</v>
       </c>
+      <c r="AC107" s="1" t="n">
+        <v>0.01841</v>
+      </c>
+      <c r="AD107" s="3" t="n">
+        <v>0.01488423373759644</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10013,6 +10661,12 @@
       <c r="AB108" s="3" t="n">
         <v>0.001395998138669253</v>
       </c>
+      <c r="AC108" s="1" t="n">
+        <v>0.02161</v>
+      </c>
+      <c r="AD108" s="3" t="n">
+        <v>0.004182156133828987</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10101,6 +10755,12 @@
       <c r="AB109" s="2" t="n">
         <v>-0.0003601656762111674</v>
       </c>
+      <c r="AC109" s="1" t="n">
+        <v>0.05549</v>
+      </c>
+      <c r="AD109" s="2" t="n">
+        <v>-0.0003602954422626407</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10189,6 +10849,12 @@
       <c r="AB110" s="3" t="n">
         <v>0.003654716324399615</v>
       </c>
+      <c r="AC110" s="1" t="n">
+        <v>0.11518</v>
+      </c>
+      <c r="AD110" s="2" t="n">
+        <v>-0.001387203051846658</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10277,6 +10943,12 @@
       <c r="AB111" s="2" t="n">
         <v>-0.0007184645386431347</v>
       </c>
+      <c r="AC111" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="AD111" s="3" t="n">
+        <v>0.001437962202136414</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10365,6 +11037,12 @@
       <c r="AB112" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC112" s="1" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="AD112" s="3" t="n">
+        <v>0.00268096514745316</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10453,6 +11131,12 @@
       <c r="AB113" s="2" t="n">
         <v>-0.002348856209150267</v>
       </c>
+      <c r="AC113" s="1" t="n">
+        <v>0.09847</v>
+      </c>
+      <c r="AD113" s="3" t="n">
+        <v>0.007984440577336502</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10541,6 +11225,12 @@
       <c r="AB114" s="3" t="n">
         <v>0.003454231433506004</v>
       </c>
+      <c r="AC114" s="1" t="n">
+        <v>0.001754</v>
+      </c>
+      <c r="AD114" s="3" t="n">
+        <v>0.006310958118187</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10629,6 +11319,12 @@
       <c r="AB115" s="2" t="n">
         <v>-0.001756767547712193</v>
       </c>
+      <c r="AC115" s="1" t="n">
+        <v>1.2632</v>
+      </c>
+      <c r="AD115" s="3" t="n">
+        <v>0.01047916166706672</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10717,6 +11413,12 @@
       <c r="AB116" s="3" t="n">
         <v>0.0004240882103477056</v>
       </c>
+      <c r="AC116" s="1" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="AD116" s="3" t="n">
+        <v>0.001695633743111536</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10805,6 +11507,12 @@
       <c r="AB117" s="2" t="n">
         <v>-0.002444190972788077</v>
       </c>
+      <c r="AC117" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AD117" s="2" t="n">
+        <v>-0.003593596863769977</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10893,6 +11601,12 @@
       <c r="AB118" s="3" t="n">
         <v>0.005037783375314815</v>
       </c>
+      <c r="AC118" s="1" t="n">
+        <v>0.04371</v>
+      </c>
+      <c r="AD118" s="2" t="n">
+        <v>-0.004101161995898829</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10981,6 +11695,12 @@
       <c r="AB119" s="2" t="n">
         <v>-0.01179941002949858</v>
       </c>
+      <c r="AC119" s="1" t="n">
+        <v>0.003697</v>
+      </c>
+      <c r="AD119" s="3" t="n">
+        <v>0.003256445047489903</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11069,6 +11789,12 @@
       <c r="AB120" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC120" s="1" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AD120" s="3" t="n">
+        <v>0.00253807106598985</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11157,6 +11883,12 @@
       <c r="AB121" s="3" t="n">
         <v>0.002700877785280106</v>
       </c>
+      <c r="AC121" s="1" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="AD121" s="3" t="n">
+        <v>0.008417508417508426</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11245,6 +11977,12 @@
       <c r="AB122" s="3" t="n">
         <v>0.0003525471531816992</v>
       </c>
+      <c r="AC122" s="1" t="n">
+        <v>0.5726</v>
+      </c>
+      <c r="AD122" s="3" t="n">
+        <v>0.008986784140969151</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11333,6 +12071,12 @@
       <c r="AB123" s="2" t="n">
         <v>-0.006609682666020701</v>
       </c>
+      <c r="AC123" s="1" t="n">
+        <v>0.028653</v>
+      </c>
+      <c r="AD123" s="2" t="n">
+        <v>-0.001846303908590451</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11421,6 +12165,12 @@
       <c r="AB124" s="3" t="n">
         <v>0.005355776587605073</v>
       </c>
+      <c r="AC124" s="1" t="n">
+        <v>0.07889</v>
+      </c>
+      <c r="AD124" s="3" t="n">
+        <v>0.0006341958396753979</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11509,6 +12259,12 @@
       <c r="AB125" s="3" t="n">
         <v>9.661835748801933e-05</v>
       </c>
+      <c r="AC125" s="1" t="n">
+        <v>0.10596</v>
+      </c>
+      <c r="AD125" s="3" t="n">
+        <v>0.02366921070427972</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11597,6 +12353,12 @@
       <c r="AB126" s="2" t="n">
         <v>-0.003762227238525184</v>
       </c>
+      <c r="AC126" s="1" t="n">
+        <v>0.02662</v>
+      </c>
+      <c r="AD126" s="3" t="n">
+        <v>0.005287009063444155</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11685,6 +12447,12 @@
       <c r="AB127" s="2" t="n">
         <v>-0.0004562043795620252</v>
       </c>
+      <c r="AC127" s="1" t="n">
+        <v>0.02193</v>
+      </c>
+      <c r="AD127" s="3" t="n">
+        <v>0.0009128251939754749</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11773,6 +12541,12 @@
       <c r="AB128" s="2" t="n">
         <v>-0.0006191950464397322</v>
       </c>
+      <c r="AC128" s="1" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="AD128" s="3" t="n">
+        <v>0.008674101610904662</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11861,6 +12635,12 @@
       <c r="AB129" s="3" t="n">
         <v>0.004739666829302391</v>
       </c>
+      <c r="AC129" s="1" t="n">
+        <v>0.14259</v>
+      </c>
+      <c r="AD129" s="2" t="n">
+        <v>-0.01082206035379817</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11949,6 +12729,12 @@
       <c r="AB130" s="3" t="n">
         <v>0.007148712278628217</v>
       </c>
+      <c r="AC130" s="1" t="n">
+        <v>0.052626</v>
+      </c>
+      <c r="AD130" s="2" t="n">
+        <v>-0.003899152029073248</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12037,6 +12823,12 @@
       <c r="AB131" s="2" t="n">
         <v>-0.001469147894221462</v>
       </c>
+      <c r="AC131" s="1" t="n">
+        <v>0.08229</v>
+      </c>
+      <c r="AD131" s="3" t="n">
+        <v>0.008950465914664155</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12125,6 +12917,12 @@
       <c r="AB132" s="3" t="n">
         <v>0.001141552511415558</v>
       </c>
+      <c r="AC132" s="1" t="n">
+        <v>0.0881</v>
+      </c>
+      <c r="AD132" s="3" t="n">
+        <v>0.004561003420752538</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12213,6 +13011,12 @@
       <c r="AB133" s="3" t="n">
         <v>0.001553331032102195</v>
       </c>
+      <c r="AC133" s="1" t="n">
+        <v>0.5824</v>
+      </c>
+      <c r="AD133" s="3" t="n">
+        <v>0.003618817852834725</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -12301,6 +13105,12 @@
       <c r="AB134" s="3" t="n">
         <v>0.003706199460916408</v>
       </c>
+      <c r="AC134" s="1" t="n">
+        <v>0.02995</v>
+      </c>
+      <c r="AD134" s="3" t="n">
+        <v>0.00537092984222895</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12389,6 +13199,12 @@
       <c r="AB135" s="2" t="n">
         <v>-0.002839295854628133</v>
       </c>
+      <c r="AC135" s="1" t="n">
+        <v>0.01758</v>
+      </c>
+      <c r="AD135" s="3" t="n">
+        <v>0.001138952164009065</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12477,6 +13293,12 @@
       <c r="AB136" s="2" t="n">
         <v>-0.002156334231806029</v>
       </c>
+      <c r="AC136" s="1" t="n">
+        <v>0.03722</v>
+      </c>
+      <c r="AD136" s="3" t="n">
+        <v>0.005402485143166011</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12565,6 +13387,12 @@
       <c r="AB137" s="2" t="n">
         <v>-0.004782928623988159</v>
       </c>
+      <c r="AC137" s="1" t="n">
+        <v>0.02725</v>
+      </c>
+      <c r="AD137" s="3" t="n">
+        <v>0.007393715341959289</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12653,6 +13481,12 @@
       <c r="AB138" s="3" t="n">
         <v>0.0007864726700746282</v>
       </c>
+      <c r="AC138" s="1" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD138" s="3" t="n">
+        <v>0.009823182711198393</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12741,6 +13575,12 @@
       <c r="AB139" s="3" t="n">
         <v>0.002510460251045923</v>
       </c>
+      <c r="AC139" s="1" t="n">
+        <v>0.01192</v>
+      </c>
+      <c r="AD139" s="2" t="n">
+        <v>-0.005008347245408956</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12829,6 +13669,12 @@
       <c r="AB140" s="2" t="n">
         <v>-0.004688546550569364</v>
       </c>
+      <c r="AC140" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="AD140" s="2" t="n">
+        <v>-0.002691790040376858</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12917,6 +13763,12 @@
       <c r="AB141" s="2" t="n">
         <v>-0.001796333002973236</v>
       </c>
+      <c r="AC141" s="1" t="n">
+        <v>16.265</v>
+      </c>
+      <c r="AD141" s="3" t="n">
+        <v>0.009308098045299544</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13005,6 +13857,12 @@
       <c r="AB142" s="3" t="n">
         <v>0.006394884092725836</v>
       </c>
+      <c r="AC142" s="1" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AD142" s="3" t="n">
+        <v>0.0007942811755361074</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13093,6 +13951,12 @@
       <c r="AB143" s="3" t="n">
         <v>0.006333830104321908</v>
       </c>
+      <c r="AC143" s="1" t="n">
+        <v>0.02737</v>
+      </c>
+      <c r="AD143" s="3" t="n">
+        <v>0.0133283968900407</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -13181,6 +14045,12 @@
       <c r="AB144" s="3" t="n">
         <v>0.007875691783737699</v>
       </c>
+      <c r="AC144" s="1" t="n">
+        <v>0.004761</v>
+      </c>
+      <c r="AD144" s="3" t="n">
+        <v>0.005491024287222805</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -13269,6 +14139,12 @@
       <c r="AB145" s="2" t="n">
         <v>-0.0005612244897958566</v>
       </c>
+      <c r="AC145" s="1" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="AD145" s="3" t="n">
+        <v>0.004645464291183769</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13357,6 +14233,12 @@
       <c r="AB146" s="3" t="n">
         <v>0.002160760587726792</v>
       </c>
+      <c r="AC146" s="1" t="n">
+        <v>0.02334</v>
+      </c>
+      <c r="AD146" s="3" t="n">
+        <v>0.006468305304010385</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -13445,6 +14327,12 @@
       <c r="AB147" s="2" t="n">
         <v>-0.0007765697803416976</v>
       </c>
+      <c r="AC147" s="1" t="n">
+        <v>0.08956</v>
+      </c>
+      <c r="AD147" s="2" t="n">
+        <v>-0.005662262684578623</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -13533,6 +14421,12 @@
       <c r="AB148" s="3" t="n">
         <v>0.006971465629053175</v>
       </c>
+      <c r="AC148" s="1" t="n">
+        <v>0.0623</v>
+      </c>
+      <c r="AD148" s="3" t="n">
+        <v>0.003059088713572737</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13621,6 +14515,12 @@
       <c r="AB149" s="3" t="n">
         <v>0.0005060728744939651</v>
       </c>
+      <c r="AC149" s="1" t="n">
+        <v>0.05946</v>
+      </c>
+      <c r="AD149" s="3" t="n">
+        <v>0.002529084471421301</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -13709,6 +14609,12 @@
       <c r="AB150" s="3" t="n">
         <v>0.003443046276181528</v>
       </c>
+      <c r="AC150" s="1" t="n">
+        <v>0.24536</v>
+      </c>
+      <c r="AD150" s="3" t="n">
+        <v>0.002246640251623687</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13797,6 +14703,12 @@
       <c r="AB151" s="3" t="n">
         <v>0.004578623551294849</v>
       </c>
+      <c r="AC151" s="1" t="n">
+        <v>7.053e-05</v>
+      </c>
+      <c r="AD151" s="3" t="n">
+        <v>0.004557755305512185</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13885,6 +14797,12 @@
       <c r="AB152" s="3" t="n">
         <v>0.0006744604316547268</v>
       </c>
+      <c r="AC152" s="1" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="AD152" s="2" t="n">
+        <v>-0.002022017524151903</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -13973,6 +14891,12 @@
       <c r="AB153" s="3" t="n">
         <v>0.001953125000000147</v>
       </c>
+      <c r="AC153" s="1" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="AD153" s="3" t="n">
+        <v>0.002923976608186993</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14061,6 +14985,12 @@
       <c r="AB154" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC154" s="1" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="AD154" s="3" t="n">
+        <v>0.0005486968449932331</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -14149,6 +15079,12 @@
       <c r="AB155" s="2" t="n">
         <v>-0.002167316861725186</v>
       </c>
+      <c r="AC155" s="1" t="n">
+        <v>0.2306</v>
+      </c>
+      <c r="AD155" s="3" t="n">
+        <v>0.001737619461338017</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14237,6 +15173,12 @@
       <c r="AB156" s="3" t="n">
         <v>0.002979885771045494</v>
       </c>
+      <c r="AC156" s="1" t="n">
+        <v>0.08076999999999999</v>
+      </c>
+      <c r="AD156" s="2" t="n">
+        <v>-0.0001237930180739044</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -14325,6 +15267,12 @@
       <c r="AB157" s="3" t="n">
         <v>0.003842291402872951</v>
       </c>
+      <c r="AC157" s="1" t="n">
+        <v>0.2294</v>
+      </c>
+      <c r="AD157" s="2" t="n">
+        <v>-0.002218259318863948</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -14413,6 +15361,12 @@
       <c r="AB158" s="3" t="n">
         <v>0.007148530579825132</v>
       </c>
+      <c r="AC158" s="1" t="n">
+        <v>0.2541</v>
+      </c>
+      <c r="AD158" s="3" t="n">
+        <v>0.001971608832807573</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -14501,6 +15455,12 @@
       <c r="AB159" s="3" t="n">
         <v>0.001021102791014183</v>
       </c>
+      <c r="AC159" s="1" t="n">
+        <v>2.917</v>
+      </c>
+      <c r="AD159" s="2" t="n">
+        <v>-0.00816048962937777</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14589,6 +15549,12 @@
       <c r="AB160" s="2" t="n">
         <v>-0.005025125628140708</v>
       </c>
+      <c r="AC160" s="1" t="n">
+        <v>0.0992</v>
+      </c>
+      <c r="AD160" s="3" t="n">
+        <v>0.002020202020201938</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -14677,6 +15643,12 @@
       <c r="AB161" s="3" t="n">
         <v>6.780580417690534e-05</v>
       </c>
+      <c r="AC161" s="1" t="n">
+        <v>0.14773</v>
+      </c>
+      <c r="AD161" s="3" t="n">
+        <v>0.001627228964675505</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -14765,6 +15737,12 @@
       <c r="AB162" s="2" t="n">
         <v>-0.0006110601894286073</v>
       </c>
+      <c r="AC162" s="1" t="n">
+        <v>0.003302</v>
+      </c>
+      <c r="AD162" s="3" t="n">
+        <v>0.009477224090492136</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -14853,6 +15831,12 @@
       <c r="AB163" s="3" t="n">
         <v>0.005407570598838397</v>
       </c>
+      <c r="AC163" s="1" t="n">
+        <v>0.005041</v>
+      </c>
+      <c r="AD163" s="3" t="n">
+        <v>0.004183266932270953</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -14941,6 +15925,12 @@
       <c r="AB164" s="2" t="n">
         <v>-0.00104602510460254</v>
       </c>
+      <c r="AC164" s="1" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="AD164" s="3" t="n">
+        <v>0.01151832460732988</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -15029,6 +16019,12 @@
       <c r="AB165" s="3" t="n">
         <v>0.004585653455617284</v>
       </c>
+      <c r="AC165" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AD165" s="3" t="n">
+        <v>0.01075970003260523</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -15117,6 +16113,12 @@
       <c r="AB166" s="3" t="n">
         <v>0.0005769924269743324</v>
       </c>
+      <c r="AC166" s="1" t="n">
+        <v>1.3933</v>
+      </c>
+      <c r="AD166" s="3" t="n">
+        <v>0.00432494774021481</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15205,6 +16207,12 @@
       <c r="AB167" s="2" t="n">
         <v>-0.003595828838547288</v>
       </c>
+      <c r="AC167" s="1" t="n">
+        <v>0.2789</v>
+      </c>
+      <c r="AD167" s="3" t="n">
+        <v>0.006495849873691693</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15293,6 +16301,12 @@
       <c r="AB168" s="3" t="n">
         <v>0.003215434083601289</v>
       </c>
+      <c r="AC168" s="1" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AD168" s="3" t="n">
+        <v>0.003205128205128208</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -15381,6 +16395,12 @@
       <c r="AB169" s="3" t="n">
         <v>0.003014065639651701</v>
       </c>
+      <c r="AC169" s="1" t="n">
+        <v>0.03015</v>
+      </c>
+      <c r="AD169" s="3" t="n">
+        <v>0.006677796327211979</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -15469,6 +16489,12 @@
       <c r="AB170" s="2" t="n">
         <v>-0.002768804799261539</v>
       </c>
+      <c r="AC170" s="1" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AD170" s="3" t="n">
+        <v>0.003239241092087025</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -15557,6 +16583,12 @@
       <c r="AB171" s="2" t="n">
         <v>-0.006024096385542133</v>
       </c>
+      <c r="AC171" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="AD171" s="3" t="n">
+        <v>0.006060606060606023</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -15645,6 +16677,12 @@
       <c r="AB172" s="3" t="n">
         <v>0.01515151515151513</v>
       </c>
+      <c r="AC172" s="1" t="n">
+        <v>1.32e-05</v>
+      </c>
+      <c r="AD172" s="2" t="n">
+        <v>-0.01492537313432834</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -15733,6 +16771,12 @@
       <c r="AB173" s="2" t="n">
         <v>-0.0009492168960607113</v>
       </c>
+      <c r="AC173" s="1" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="AD173" s="3" t="n">
+        <v>0.01187648456057008</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -15821,6 +16865,12 @@
       <c r="AB174" s="2" t="n">
         <v>-0.008474576271186363</v>
       </c>
+      <c r="AC174" s="1" t="n">
+        <v>0.09019000000000001</v>
+      </c>
+      <c r="AD174" s="3" t="n">
+        <v>0.001110001110001142</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -15909,6 +16959,12 @@
       <c r="AB175" s="2" t="n">
         <v>-0.003580280914348576</v>
       </c>
+      <c r="AC175" s="1" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="AD175" s="3" t="n">
+        <v>0.003593145384190072</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -15997,6 +17053,12 @@
       <c r="AB176" s="2" t="n">
         <v>-0.001403180542563086</v>
       </c>
+      <c r="AC176" s="1" t="n">
+        <v>0.02142</v>
+      </c>
+      <c r="AD176" s="3" t="n">
+        <v>0.003278688524590193</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -16085,6 +17147,12 @@
       <c r="AB177" s="2" t="n">
         <v>-0.01139240506329122</v>
       </c>
+      <c r="AC177" s="1" t="n">
+        <v>0.007860000000000001</v>
+      </c>
+      <c r="AD177" s="3" t="n">
+        <v>0.006402048655569855</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -16173,6 +17241,12 @@
       <c r="AB178" s="3" t="n">
         <v>0.001044932079414864</v>
       </c>
+      <c r="AC178" s="1" t="n">
+        <v>0.000961</v>
+      </c>
+      <c r="AD178" s="3" t="n">
+        <v>0.003131524008350807</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -16261,6 +17335,12 @@
       <c r="AB179" s="2" t="n">
         <v>-0.0004400440044004221</v>
       </c>
+      <c r="AC179" s="1" t="n">
+        <v>0.02283</v>
+      </c>
+      <c r="AD179" s="3" t="n">
+        <v>0.005062733876293221</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -16349,6 +17429,12 @@
       <c r="AB180" s="2" t="n">
         <v>-0.001214771622934862</v>
       </c>
+      <c r="AC180" s="1" t="n">
+        <v>4.128</v>
+      </c>
+      <c r="AD180" s="3" t="n">
+        <v>0.004135246898564911</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -16437,6 +17523,12 @@
       <c r="AB181" s="2" t="n">
         <v>-0.01605385810460916</v>
       </c>
+      <c r="AC181" s="1" t="n">
+        <v>0.5653</v>
+      </c>
+      <c r="AD181" s="2" t="n">
+        <v>-0.008245614035087591</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -16525,6 +17617,12 @@
       <c r="AB182" s="2" t="n">
         <v>-0.005307646943188508</v>
       </c>
+      <c r="AC182" s="1" t="n">
+        <v>0.05111</v>
+      </c>
+      <c r="AD182" s="3" t="n">
+        <v>0.01007905138339928</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -16613,6 +17711,12 @@
       <c r="AB183" s="2" t="n">
         <v>-0.0001832172957127765</v>
       </c>
+      <c r="AC183" s="1" t="n">
+        <v>5.477</v>
+      </c>
+      <c r="AD183" s="3" t="n">
+        <v>0.003665017408832777</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -16701,6 +17805,12 @@
       <c r="AB184" s="2" t="n">
         <v>-0.001039140976792557</v>
       </c>
+      <c r="AC184" s="1" t="n">
+        <v>28.96</v>
+      </c>
+      <c r="AD184" s="3" t="n">
+        <v>0.004160887656033322</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -16789,6 +17899,12 @@
       <c r="AB185" s="3" t="n">
         <v>0.008542445274959979</v>
       </c>
+      <c r="AC185" s="1" t="n">
+        <v>0.01902</v>
+      </c>
+      <c r="AD185" s="3" t="n">
+        <v>0.006881948120698685</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -16877,6 +17993,12 @@
       <c r="AB186" s="2" t="n">
         <v>-0.006430868167202512</v>
       </c>
+      <c r="AC186" s="1" t="n">
+        <v>3.08e-05</v>
+      </c>
+      <c r="AD186" s="2" t="n">
+        <v>-0.003236245954692416</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -16965,6 +18087,12 @@
       <c r="AB187" s="2" t="n">
         <v>-0.003148614609571661</v>
       </c>
+      <c r="AC187" s="1" t="n">
+        <v>0.01586</v>
+      </c>
+      <c r="AD187" s="3" t="n">
+        <v>0.001895135818066884</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -17053,6 +18181,12 @@
       <c r="AB188" s="3" t="n">
         <v>0.001232741617357037</v>
       </c>
+      <c r="AC188" s="1" t="n">
+        <v>0.04094</v>
+      </c>
+      <c r="AD188" s="3" t="n">
+        <v>0.008126077320856857</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -17141,6 +18275,12 @@
       <c r="AB189" s="3" t="n">
         <v>0.003392897534494418</v>
       </c>
+      <c r="AC189" s="1" t="n">
+        <v>0.0004517</v>
+      </c>
+      <c r="AD189" s="3" t="n">
+        <v>0.01825969341749319</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -17229,6 +18369,12 @@
       <c r="AB190" s="3" t="n">
         <v>0.0008609556607834345</v>
       </c>
+      <c r="AC190" s="1" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="AD190" s="2" t="n">
+        <v>-0.002150537634408664</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -17317,6 +18463,12 @@
       <c r="AB191" s="2" t="n">
         <v>-0.0006345177664974361</v>
       </c>
+      <c r="AC191" s="1" t="n">
+        <v>0.01579</v>
+      </c>
+      <c r="AD191" s="3" t="n">
+        <v>0.002539682539682436</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -17405,6 +18557,12 @@
       <c r="AB192" s="2" t="n">
         <v>-0.004458712323880867</v>
       </c>
+      <c r="AC192" s="1" t="n">
+        <v>0.05596</v>
+      </c>
+      <c r="AD192" s="3" t="n">
+        <v>0.002508061626657134</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -17493,6 +18651,12 @@
       <c r="AB193" s="3" t="n">
         <v>0.002139037433155141</v>
       </c>
+      <c r="AC193" s="1" t="n">
+        <v>0.1892</v>
+      </c>
+      <c r="AD193" s="3" t="n">
+        <v>0.009605122732123777</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -17581,6 +18745,12 @@
       <c r="AB194" s="3" t="n">
         <v>0.0005194805194804983</v>
       </c>
+      <c r="AC194" s="1" t="n">
+        <v>0.01931</v>
+      </c>
+      <c r="AD194" s="3" t="n">
+        <v>0.002596053997923231</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -17669,6 +18839,12 @@
       <c r="AB195" s="2" t="n">
         <v>-0.008890968647636934</v>
       </c>
+      <c r="AC195" s="1" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="AD195" s="3" t="n">
+        <v>0.009442870632672341</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -17757,6 +18933,12 @@
       <c r="AB196" s="3" t="n">
         <v>0.007317073170731691</v>
       </c>
+      <c r="AC196" s="1" t="n">
+        <v>0.01244</v>
+      </c>
+      <c r="AD196" s="3" t="n">
+        <v>0.004035512510088757</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -17845,6 +19027,12 @@
       <c r="AB197" s="2" t="n">
         <v>-0.003231365790607589</v>
       </c>
+      <c r="AC197" s="1" t="n">
+        <v>0.04709</v>
+      </c>
+      <c r="AD197" s="3" t="n">
+        <v>0.01772206613356389</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -17933,6 +19121,12 @@
       <c r="AB198" s="2" t="n">
         <v>-0.001367989056087617</v>
       </c>
+      <c r="AC198" s="1" t="n">
+        <v>0.5129</v>
+      </c>
+      <c r="AD198" s="3" t="n">
+        <v>0.003718199608610593</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -18021,6 +19215,12 @@
       <c r="AB199" s="2" t="n">
         <v>-0.01136363636363637</v>
       </c>
+      <c r="AC199" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AD199" s="3" t="n">
+        <v>0.02298850574712646</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -18109,6 +19309,12 @@
       <c r="AB200" s="3" t="n">
         <v>0.0006729475100941983</v>
       </c>
+      <c r="AC200" s="1" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="AD200" s="3" t="n">
+        <v>0.001344989912575747</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -18197,6 +19403,12 @@
       <c r="AB201" s="2" t="n">
         <v>-0.001745200698080208</v>
       </c>
+      <c r="AC201" s="1" t="n">
+        <v>0.005729</v>
+      </c>
+      <c r="AD201" s="3" t="n">
+        <v>0.001573426573426479</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -18285,6 +19497,12 @@
       <c r="AB202" s="3" t="n">
         <v>0.002995701819129059</v>
       </c>
+      <c r="AC202" s="1" t="n">
+        <v>0.023048</v>
+      </c>
+      <c r="AD202" s="2" t="n">
+        <v>-0.002337459960176693</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -18373,6 +19591,12 @@
       <c r="AB203" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC203" s="1" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="AD203" s="3" t="n">
+        <v>0.007352941176470671</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -18461,6 +19685,12 @@
       <c r="AB204" s="2" t="n">
         <v>-0.001791044776119537</v>
       </c>
+      <c r="AC204" s="1" t="n">
+        <v>0.03357</v>
+      </c>
+      <c r="AD204" s="3" t="n">
+        <v>0.003887559808612593</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -18549,6 +19779,12 @@
       <c r="AB205" s="2" t="n">
         <v>-0.001189626457292385</v>
       </c>
+      <c r="AC205" s="1" t="n">
+        <v>4.198</v>
+      </c>
+      <c r="AD205" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -18637,6 +19873,12 @@
       <c r="AB206" s="3" t="n">
         <v>0.002785515320334264</v>
       </c>
+      <c r="AC206" s="1" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="AD206" s="3" t="n">
+        <v>0.008333333333333342</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -18725,6 +19967,12 @@
       <c r="AB207" s="3" t="n">
         <v>0.01360887096774181</v>
       </c>
+      <c r="AC207" s="1" t="n">
+        <v>0.0012104</v>
+      </c>
+      <c r="AD207" s="3" t="n">
+        <v>0.003149345267694335</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -18813,6 +20061,12 @@
       <c r="AB208" s="2" t="n">
         <v>-0.01266868631231067</v>
       </c>
+      <c r="AC208" s="1" t="n">
+        <v>0.007225</v>
+      </c>
+      <c r="AD208" s="3" t="n">
+        <v>0.007670850767085006</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -18901,6 +20155,12 @@
       <c r="AB209" s="3" t="n">
         <v>0.003355704697986557</v>
       </c>
+      <c r="AC209" s="1" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AD209" s="3" t="n">
+        <v>0.001672240802675633</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -18989,6 +20249,12 @@
       <c r="AB210" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC210" s="1" t="n">
+        <v>0.1302</v>
+      </c>
+      <c r="AD210" s="3" t="n">
+        <v>0.003855050115651507</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -19077,6 +20343,12 @@
       <c r="AB211" s="2" t="n">
         <v>-0.001685866816521475</v>
       </c>
+      <c r="AC211" s="1" t="n">
+        <v>0.007157</v>
+      </c>
+      <c r="AD211" s="3" t="n">
+        <v>0.007177033492822942</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -19165,6 +20437,12 @@
       <c r="AB212" s="2" t="n">
         <v>-0.003404834865509026</v>
       </c>
+      <c r="AC212" s="1" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="AD212" s="2" t="n">
+        <v>-0.00512470105910489</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -19253,6 +20531,12 @@
       <c r="AB213" s="2" t="n">
         <v>-0.005344735435595968</v>
       </c>
+      <c r="AC213" s="1" t="n">
+        <v>0.05533</v>
+      </c>
+      <c r="AD213" s="2" t="n">
+        <v>-0.008955758552749426</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -19341,6 +20625,12 @@
       <c r="AB214" s="3" t="n">
         <v>0.003719447396386855</v>
       </c>
+      <c r="AC214" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AD214" s="3" t="n">
+        <v>0.005823186871360454</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -19429,6 +20719,12 @@
       <c r="AB215" s="3" t="n">
         <v>0.001896453631708759</v>
       </c>
+      <c r="AC215" s="1" t="n">
+        <v>0.05326</v>
+      </c>
+      <c r="AD215" s="3" t="n">
+        <v>0.00813931478326708</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -19517,6 +20813,12 @@
       <c r="AB216" s="2" t="n">
         <v>-0.002884615384615351</v>
       </c>
+      <c r="AC216" s="1" t="n">
+        <v>0.002089</v>
+      </c>
+      <c r="AD216" s="3" t="n">
+        <v>0.007232401157184309</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -19605,6 +20907,12 @@
       <c r="AB217" s="3" t="n">
         <v>0.0001666666666667223</v>
       </c>
+      <c r="AC217" s="1" t="n">
+        <v>6.045</v>
+      </c>
+      <c r="AD217" s="3" t="n">
+        <v>0.007332111314780802</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -19693,6 +21001,12 @@
       <c r="AB218" s="2" t="n">
         <v>-0.03523528074562406</v>
       </c>
+      <c r="AC218" s="1" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AD218" s="3" t="n">
+        <v>0.01083883129123475</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -19781,6 +21095,12 @@
       <c r="AB219" s="2" t="n">
         <v>-0.0007496251874062338</v>
       </c>
+      <c r="AC219" s="1" t="n">
+        <v>0.005348</v>
+      </c>
+      <c r="AD219" s="3" t="n">
+        <v>0.00300075018754696</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -19869,6 +21189,12 @@
       <c r="AB220" s="3" t="n">
         <v>0.0002423654871547034</v>
       </c>
+      <c r="AC220" s="1" t="n">
+        <v>0.04131</v>
+      </c>
+      <c r="AD220" s="3" t="n">
+        <v>0.0009692270414344165</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -19957,6 +21283,12 @@
       <c r="AB221" s="2" t="n">
         <v>-0.001223348479552615</v>
       </c>
+      <c r="AC221" s="1" t="n">
+        <v>0.00577</v>
+      </c>
+      <c r="AD221" s="3" t="n">
+        <v>0.009623797025371892</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -20045,6 +21377,12 @@
       <c r="AB222" s="2" t="n">
         <v>-0.001102535832414585</v>
       </c>
+      <c r="AC222" s="1" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="AD222" s="3" t="n">
+        <v>0.006622516556291427</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -20133,6 +21471,12 @@
       <c r="AB223" s="3" t="n">
         <v>0.00089874176153392</v>
       </c>
+      <c r="AC223" s="1" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AD223" s="3" t="n">
+        <v>0.01077521700089791</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -20221,6 +21565,12 @@
       <c r="AB224" s="3" t="n">
         <v>0.0006975122064636654</v>
       </c>
+      <c r="AC224" s="1" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AD224" s="3" t="n">
+        <v>0.00604089219330853</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -20309,6 +21659,12 @@
       <c r="AB225" s="2" t="n">
         <v>-0.002994729276473409</v>
       </c>
+      <c r="AC225" s="1" t="n">
+        <v>0.08348</v>
+      </c>
+      <c r="AD225" s="3" t="n">
+        <v>0.003003724618526976</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -20397,6 +21753,12 @@
       <c r="AB226" s="2" t="n">
         <v>-0.006369426751592282</v>
       </c>
+      <c r="AC226" s="1" t="n">
+        <v>0.01872</v>
+      </c>
+      <c r="AD226" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -20485,6 +21847,12 @@
       <c r="AB227" s="3" t="n">
         <v>0.001285622455538838</v>
       </c>
+      <c r="AC227" s="1" t="n">
+        <v>0.0472</v>
+      </c>
+      <c r="AD227" s="3" t="n">
+        <v>0.01005777872886793</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -20573,6 +21941,12 @@
       <c r="AB228" s="2" t="n">
         <v>-0.001300390117035057</v>
       </c>
+      <c r="AC228" s="1" t="n">
+        <v>0.02309</v>
+      </c>
+      <c r="AD228" s="3" t="n">
+        <v>0.002170138888888801</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -20661,6 +22035,12 @@
       <c r="AB229" s="3" t="n">
         <v>0.001858736059479607</v>
       </c>
+      <c r="AC229" s="1" t="n">
+        <v>0.1095</v>
+      </c>
+      <c r="AD229" s="3" t="n">
+        <v>0.01576994434137285</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -20749,6 +22129,12 @@
       <c r="AB230" s="3" t="n">
         <v>0.0006045949214027615</v>
       </c>
+      <c r="AC230" s="1" t="n">
+        <v>0.1671</v>
+      </c>
+      <c r="AD230" s="3" t="n">
+        <v>0.009667673716012026</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -20837,6 +22223,12 @@
       <c r="AB231" s="2" t="n">
         <v>-0.0006594131223211073</v>
       </c>
+      <c r="AC231" s="1" t="n">
+        <v>0.03049</v>
+      </c>
+      <c r="AD231" s="3" t="n">
+        <v>0.005938634114153732</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -20925,6 +22317,12 @@
       <c r="AB232" s="2" t="n">
         <v>-0.003106968486462522</v>
       </c>
+      <c r="AC232" s="1" t="n">
+        <v>0.02248</v>
+      </c>
+      <c r="AD232" s="3" t="n">
+        <v>0.0008904719501335345</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -21013,6 +22411,12 @@
       <c r="AB233" s="2" t="n">
         <v>-0.05237251427446353</v>
       </c>
+      <c r="AC233" s="1" t="n">
+        <v>0.10109</v>
+      </c>
+      <c r="AD233" s="3" t="n">
+        <v>0.05017660502804904</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -21101,6 +22505,12 @@
       <c r="AB234" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC234" s="1" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="AD234" s="3" t="n">
+        <v>0.00672734467748332</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -21189,6 +22599,12 @@
       <c r="AB235" s="2" t="n">
         <v>-0.005374782103428172</v>
       </c>
+      <c r="AC235" s="1" t="n">
+        <v>0.0687</v>
+      </c>
+      <c r="AD235" s="3" t="n">
+        <v>0.003359135387760977</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -21277,6 +22693,12 @@
       <c r="AB236" s="2" t="n">
         <v>-0.006129597197898478</v>
       </c>
+      <c r="AC236" s="1" t="n">
+        <v>0.1253</v>
+      </c>
+      <c r="AD236" s="3" t="n">
+        <v>0.00360432519022821</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -21365,6 +22787,12 @@
       <c r="AB237" s="3" t="n">
         <v>0.003107198342827424</v>
       </c>
+      <c r="AC237" s="1" t="n">
+        <v>0.03913</v>
+      </c>
+      <c r="AD237" s="3" t="n">
+        <v>0.01006711409395977</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -21453,6 +22881,12 @@
       <c r="AB238" s="2" t="n">
         <v>-0.008333333333333342</v>
       </c>
+      <c r="AC238" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AD238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -21541,6 +22975,12 @@
       <c r="AB239" s="2" t="n">
         <v>-0.0005026388539834797</v>
       </c>
+      <c r="AC239" s="1" t="n">
+        <v>0.00399</v>
+      </c>
+      <c r="AD239" s="3" t="n">
+        <v>0.003268795574553682</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -21629,6 +23069,12 @@
       <c r="AB240" s="3" t="n">
         <v>0.001461988304093635</v>
       </c>
+      <c r="AC240" s="1" t="n">
+        <v>0.01377</v>
+      </c>
+      <c r="AD240" s="3" t="n">
+        <v>0.005109489051094809</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -21717,6 +23163,12 @@
       <c r="AB241" s="2" t="n">
         <v>-0.006162976489385939</v>
       </c>
+      <c r="AC241" s="1" t="n">
+        <v>0.4381</v>
+      </c>
+      <c r="AD241" s="3" t="n">
+        <v>0.006201194304088149</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -21805,6 +23257,12 @@
       <c r="AB242" s="2" t="n">
         <v>-0.002649006622516563</v>
       </c>
+      <c r="AC242" s="1" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="AD242" s="3" t="n">
+        <v>0.006640106241699827</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -21893,6 +23351,12 @@
       <c r="AB243" s="2" t="n">
         <v>-0.0008703220191470489</v>
       </c>
+      <c r="AC243" s="1" t="n">
+        <v>0.02293</v>
+      </c>
+      <c r="AD243" s="2" t="n">
+        <v>-0.001306620209059331</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -21981,6 +23445,12 @@
       <c r="AB244" s="2" t="n">
         <v>-0.003001200480192085</v>
       </c>
+      <c r="AC244" s="1" t="n">
+        <v>0.001679</v>
+      </c>
+      <c r="AD244" s="3" t="n">
+        <v>0.01083684527393137</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -22069,6 +23539,12 @@
       <c r="AB245" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC245" s="1" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="AD245" s="3" t="n">
+        <v>0.007639419404125294</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -22157,6 +23633,12 @@
       <c r="AB246" s="3" t="n">
         <v>0.01493485859548793</v>
       </c>
+      <c r="AC246" s="1" t="n">
+        <v>0.0323</v>
+      </c>
+      <c r="AD246" s="3" t="n">
+        <v>0.01127113337507825</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -22245,6 +23727,12 @@
       <c r="AB247" s="2" t="n">
         <v>-0.002262443438914092</v>
       </c>
+      <c r="AC247" s="1" t="n">
+        <v>0.1779</v>
+      </c>
+      <c r="AD247" s="3" t="n">
+        <v>0.008503401360544225</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -22333,6 +23821,12 @@
       <c r="AB248" s="2" t="n">
         <v>-0.001629726205997326</v>
       </c>
+      <c r="AC248" s="1" t="n">
+        <v>0.03039</v>
+      </c>
+      <c r="AD248" s="2" t="n">
+        <v>-0.00783545543584723</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -22421,6 +23915,12 @@
       <c r="AB249" s="3" t="n">
         <v>0.001408616034745845</v>
       </c>
+      <c r="AC249" s="1" t="n">
+        <v>0.008482999999999999</v>
+      </c>
+      <c r="AD249" s="2" t="n">
+        <v>-0.005626538506623042</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -22509,6 +24009,12 @@
       <c r="AB250" s="2" t="n">
         <v>-0.00696864111498264</v>
       </c>
+      <c r="AC250" s="1" t="n">
+        <v>0.02015</v>
+      </c>
+      <c r="AD250" s="3" t="n">
+        <v>0.01002506265664172</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -22597,6 +24103,12 @@
       <c r="AB251" s="2" t="n">
         <v>-0.003654342218400614</v>
       </c>
+      <c r="AC251" s="1" t="n">
+        <v>0.04665</v>
+      </c>
+      <c r="AD251" s="3" t="n">
+        <v>0.006472491909384999</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -22685,6 +24197,12 @@
       <c r="AB252" s="3" t="n">
         <v>0.002466236054022335</v>
       </c>
+      <c r="AC252" s="1" t="n">
+        <v>0.008574999999999999</v>
+      </c>
+      <c r="AD252" s="3" t="n">
+        <v>0.004568884723523793</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -22773,6 +24291,12 @@
       <c r="AB253" s="2" t="n">
         <v>-0.0002587322121603137</v>
       </c>
+      <c r="AC253" s="1" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AD253" s="3" t="n">
+        <v>0.0005175983436852791</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -22861,6 +24385,12 @@
       <c r="AB254" s="2" t="n">
         <v>-0.003416856492027365</v>
       </c>
+      <c r="AC254" s="1" t="n">
+        <v>0.06157</v>
+      </c>
+      <c r="AD254" s="3" t="n">
+        <v>0.005224489795918381</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -22949,6 +24479,12 @@
       <c r="AB255" s="3" t="n">
         <v>0.007068136839129162</v>
       </c>
+      <c r="AC255" s="1" t="n">
+        <v>0.003594</v>
+      </c>
+      <c r="AD255" s="3" t="n">
+        <v>0.008983717012914068</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -23037,6 +24573,12 @@
       <c r="AB256" s="3" t="n">
         <v>0.01016152271176148</v>
       </c>
+      <c r="AC256" s="1" t="n">
+        <v>0.013425</v>
+      </c>
+      <c r="AD256" s="3" t="n">
+        <v>0.007807221680054045</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -23125,6 +24667,12 @@
       <c r="AB257" s="3" t="n">
         <v>1.000575330843991e-06</v>
       </c>
+      <c r="AC257" s="1" t="n">
+        <v>0.9994729999999999</v>
+      </c>
+      <c r="AD257" s="3" t="n">
+        <v>4.702699349417388e-05</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -23213,6 +24761,12 @@
       <c r="AB258" s="2" t="n">
         <v>-0.006279434850863322</v>
       </c>
+      <c r="AC258" s="1" t="n">
+        <v>0.08867</v>
+      </c>
+      <c r="AD258" s="3" t="n">
+        <v>0.0005642067253441039</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -23301,6 +24855,12 @@
       <c r="AB259" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC259" s="1" t="n">
+        <v>0.09088</v>
+      </c>
+      <c r="AD259" s="3" t="n">
+        <v>0.000881057268722431</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -23389,6 +24949,12 @@
       <c r="AB260" s="2" t="n">
         <v>-0.0003661215523554094</v>
       </c>
+      <c r="AC260" s="1" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="AD260" s="3" t="n">
+        <v>0.00109876693932373</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -23477,6 +25043,12 @@
       <c r="AB261" s="2" t="n">
         <v>-0.003505696757230503</v>
       </c>
+      <c r="AC261" s="1" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="AD261" s="2" t="n">
+        <v>-0.005277044854881272</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -23565,6 +25137,12 @@
       <c r="AB262" s="2" t="n">
         <v>-0.004884318766066818</v>
       </c>
+      <c r="AC262" s="1" t="n">
+        <v>0.003818</v>
+      </c>
+      <c r="AD262" s="2" t="n">
+        <v>-0.01369155257039516</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -23653,6 +25231,12 @@
       <c r="AB263" s="2" t="n">
         <v>-0.002604166666666621</v>
       </c>
+      <c r="AC263" s="1" t="n">
+        <v>0.1158</v>
+      </c>
+      <c r="AD263" s="3" t="n">
+        <v>0.007832898172323742</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -23741,6 +25325,12 @@
       <c r="AB264" s="3" t="n">
         <v>0.02295669163139055</v>
       </c>
+      <c r="AC264" s="1" t="n">
+        <v>0.0006214</v>
+      </c>
+      <c r="AD264" s="2" t="n">
+        <v>-0.0109820149610059</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -23829,6 +25419,12 @@
       <c r="AB265" s="2" t="n">
         <v>-0.003415300546448067</v>
       </c>
+      <c r="AC265" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="AD265" s="3" t="n">
+        <v>0.006854009595613392</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -23917,6 +25513,12 @@
       <c r="AB266" s="3" t="n">
         <v>0.001577287066246102</v>
       </c>
+      <c r="AC266" s="1" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="AD266" s="3" t="n">
+        <v>0.003149606299212689</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -24005,6 +25607,12 @@
       <c r="AB267" s="3" t="n">
         <v>0.001232285890326506</v>
       </c>
+      <c r="AC267" s="1" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="AD267" s="3" t="n">
+        <v>0.004307692307692346</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -24093,6 +25701,12 @@
       <c r="AB268" s="2" t="n">
         <v>-0.003462603878116428</v>
       </c>
+      <c r="AC268" s="1" t="n">
+        <v>0.0004339</v>
+      </c>
+      <c r="AD268" s="3" t="n">
+        <v>0.005096131572851516</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -24181,6 +25795,12 @@
       <c r="AB269" s="3" t="n">
         <v>0.001447178002894465</v>
       </c>
+      <c r="AC269" s="1" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="AD269" s="3" t="n">
+        <v>0.006743737957610682</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -24269,6 +25889,12 @@
       <c r="AB270" s="3" t="n">
         <v>0.003888888888888923</v>
       </c>
+      <c r="AC270" s="1" t="n">
+        <v>0.1819</v>
+      </c>
+      <c r="AD270" s="3" t="n">
+        <v>0.006640841173215311</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -24357,6 +25983,12 @@
       <c r="AB271" s="3" t="n">
         <v>0.002717391304347904</v>
       </c>
+      <c r="AC271" s="1" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="AD271" s="3" t="n">
+        <v>0.004065040650406433</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -24445,6 +26077,12 @@
       <c r="AB272" s="2" t="n">
         <v>-0.0007587253414262851</v>
       </c>
+      <c r="AC272" s="1" t="n">
+        <v>0.03953</v>
+      </c>
+      <c r="AD272" s="3" t="n">
+        <v>0.0005062009617818067</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -24533,6 +26171,12 @@
       <c r="AB273" s="2" t="n">
         <v>-0.003243243243243246</v>
       </c>
+      <c r="AC273" s="1" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="AD273" s="3" t="n">
+        <v>0.006507592190889377</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -24621,6 +26265,12 @@
       <c r="AB274" s="2" t="n">
         <v>-0.001107770216806461</v>
       </c>
+      <c r="AC274" s="1" t="n">
+        <v>63.48</v>
+      </c>
+      <c r="AD274" s="3" t="n">
+        <v>0.005703422053231931</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -24709,6 +26359,12 @@
       <c r="AB275" s="3" t="n">
         <v>0.006272401433691812</v>
       </c>
+      <c r="AC275" s="1" t="n">
+        <v>0.01126</v>
+      </c>
+      <c r="AD275" s="3" t="n">
+        <v>0.002671415850400604</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -24797,6 +26453,12 @@
       <c r="AB276" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC276" s="1" t="n">
+        <v>2.607</v>
+      </c>
+      <c r="AD276" s="3" t="n">
+        <v>0.001921598770176917</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -24885,6 +26547,12 @@
       <c r="AB277" s="3" t="n">
         <v>0.0004767580452919949</v>
       </c>
+      <c r="AC277" s="1" t="n">
+        <v>0.04207</v>
+      </c>
+      <c r="AD277" s="3" t="n">
+        <v>0.002382654276864495</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -24973,6 +26641,12 @@
       <c r="AB278" s="3" t="n">
         <v>0.003555104113763363</v>
       </c>
+      <c r="AC278" s="1" t="n">
+        <v>0.02005</v>
+      </c>
+      <c r="AD278" s="3" t="n">
+        <v>0.01467611336032382</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -25061,6 +26735,12 @@
       <c r="AB279" s="2" t="n">
         <v>-0.0003572704537333687</v>
       </c>
+      <c r="AC279" s="1" t="n">
+        <v>0.00557</v>
+      </c>
+      <c r="AD279" s="2" t="n">
+        <v>-0.004646175839885629</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -25149,6 +26829,12 @@
       <c r="AB280" s="3" t="n">
         <v>0.009885931558935399</v>
       </c>
+      <c r="AC280" s="1" t="n">
+        <v>0.03926</v>
+      </c>
+      <c r="AD280" s="2" t="n">
+        <v>-0.01455823293172684</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -25237,6 +26923,12 @@
       <c r="AB281" s="2" t="n">
         <v>-0.001106194690265488</v>
       </c>
+      <c r="AC281" s="1" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="AD281" s="3" t="n">
+        <v>0.004429678848283504</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -25325,6 +27017,12 @@
       <c r="AB282" s="2" t="n">
         <v>-0.0004880429477794165</v>
       </c>
+      <c r="AC282" s="1" t="n">
+        <v>0.0004141</v>
+      </c>
+      <c r="AD282" s="3" t="n">
+        <v>0.010986328125</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -25413,6 +27111,12 @@
       <c r="AB283" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC283" s="1" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="AD283" s="2" t="n">
+        <v>-0.002439024390243972</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -25501,6 +27205,12 @@
       <c r="AB284" s="3" t="n">
         <v>0.005743000717875021</v>
       </c>
+      <c r="AC284" s="1" t="n">
+        <v>0.04229</v>
+      </c>
+      <c r="AD284" s="3" t="n">
+        <v>0.006186057577920612</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -25589,6 +27299,12 @@
       <c r="AB285" s="3" t="n">
         <v>0.001865671641790969</v>
       </c>
+      <c r="AC285" s="1" t="n">
+        <v>0.10748</v>
+      </c>
+      <c r="AD285" s="3" t="n">
+        <v>0.0007448789571695588</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -25677,6 +27393,12 @@
       <c r="AB286" s="2" t="n">
         <v>-0.002380952380952284</v>
       </c>
+      <c r="AC286" s="1" t="n">
+        <v>0.00422</v>
+      </c>
+      <c r="AD286" s="3" t="n">
+        <v>0.007159904534606121</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -25765,6 +27487,12 @@
       <c r="AB287" s="2" t="n">
         <v>-0.007213706041478873</v>
       </c>
+      <c r="AC287" s="1" t="n">
+        <v>0.15521</v>
+      </c>
+      <c r="AD287" s="3" t="n">
+        <v>0.006941741274166262</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -25853,6 +27581,12 @@
       <c r="AB288" s="2" t="n">
         <v>-0.001109262340543416</v>
       </c>
+      <c r="AC288" s="1" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="AD288" s="3" t="n">
+        <v>0.003331482509716765</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -25941,6 +27675,12 @@
       <c r="AB289" s="3" t="n">
         <v>0.0007230657989877353</v>
       </c>
+      <c r="AC289" s="1" t="n">
+        <v>4.181</v>
+      </c>
+      <c r="AD289" s="3" t="n">
+        <v>0.006984585741811155</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -26029,6 +27769,12 @@
       <c r="AB290" s="3" t="n">
         <v>0.001404330017554068</v>
       </c>
+      <c r="AC290" s="1" t="n">
+        <v>0.08602</v>
+      </c>
+      <c r="AD290" s="3" t="n">
+        <v>0.005258852401542667</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -26117,6 +27863,12 @@
       <c r="AB291" s="2" t="n">
         <v>-0.00028208744710869</v>
       </c>
+      <c r="AC291" s="1" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="AD291" s="3" t="n">
+        <v>0.00451467268623026</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -26205,6 +27957,12 @@
       <c r="AB292" s="2" t="n">
         <v>-0.006251274036828224</v>
       </c>
+      <c r="AC292" s="1" t="n">
+        <v>1.4629</v>
+      </c>
+      <c r="AD292" s="3" t="n">
+        <v>0.0002735042735043952</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -26293,6 +28051,12 @@
       <c r="AB293" s="3" t="n">
         <v>0.003439972480220167</v>
       </c>
+      <c r="AC293" s="1" t="n">
+        <v>0.005864</v>
+      </c>
+      <c r="AD293" s="3" t="n">
+        <v>0.005142269454919526</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -26381,6 +28145,12 @@
       <c r="AB294" s="2" t="n">
         <v>-0.001457301078402865</v>
       </c>
+      <c r="AC294" s="1" t="n">
+        <v>0.003439</v>
+      </c>
+      <c r="AD294" s="3" t="n">
+        <v>0.003794512551080101</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -26469,6 +28239,12 @@
       <c r="AB295" s="3" t="n">
         <v>0.004475107216110307</v>
       </c>
+      <c r="AC295" s="1" t="n">
+        <v>0.5407999999999999</v>
+      </c>
+      <c r="AD295" s="3" t="n">
+        <v>0.00389827362168181</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -26557,6 +28333,12 @@
       <c r="AB296" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC296" s="1" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="AD296" s="3" t="n">
+        <v>0.007139669790272206</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -26645,6 +28427,12 @@
       <c r="AB297" s="2" t="n">
         <v>-0.001781472684085644</v>
       </c>
+      <c r="AC297" s="1" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="AD297" s="3" t="n">
+        <v>0.005353955978584165</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -26733,6 +28521,12 @@
       <c r="AB298" s="3" t="n">
         <v>0.003297609233305795</v>
       </c>
+      <c r="AC298" s="1" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="AD298" s="2" t="n">
+        <v>-0.007395234182415723</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -26821,6 +28615,12 @@
       <c r="AB299" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC299" s="1" t="n">
+        <v>0.01113</v>
+      </c>
+      <c r="AD299" s="3" t="n">
+        <v>0.003606853020739415</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -26909,6 +28709,12 @@
       <c r="AB300" s="3" t="n">
         <v>0.001452784503631902</v>
       </c>
+      <c r="AC300" s="1" t="n">
+        <v>0.02079</v>
+      </c>
+      <c r="AD300" s="3" t="n">
+        <v>0.005319148936170164</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -26997,6 +28803,12 @@
       <c r="AB301" s="3" t="n">
         <v>0.001305057096247998</v>
       </c>
+      <c r="AC301" s="1" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AD301" s="3" t="n">
+        <v>0.00391006842619739</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -27085,6 +28897,12 @@
       <c r="AB302" s="2" t="n">
         <v>-0.003623188405797079</v>
       </c>
+      <c r="AC302" s="1" t="n">
+        <v>0.01381</v>
+      </c>
+      <c r="AD302" s="3" t="n">
+        <v>0.004363636363636312</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -27173,6 +28991,12 @@
       <c r="AB303" s="3" t="n">
         <v>0.001894195643350037</v>
       </c>
+      <c r="AC303" s="1" t="n">
+        <v>0.07406</v>
+      </c>
+      <c r="AD303" s="3" t="n">
+        <v>0.0001350438892639585</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -27261,6 +29085,12 @@
       <c r="AB304" s="2" t="n">
         <v>-0.0006297229219143321</v>
       </c>
+      <c r="AC304" s="1" t="n">
+        <v>0.01596</v>
+      </c>
+      <c r="AD304" s="3" t="n">
+        <v>0.005671077504725886</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -27349,6 +29179,12 @@
       <c r="AB305" s="2" t="n">
         <v>-0.002334993773350112</v>
       </c>
+      <c r="AC305" s="1" t="n">
+        <v>0.06451999999999999</v>
+      </c>
+      <c r="AD305" s="3" t="n">
+        <v>0.006709315025745044</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -27437,6 +29273,12 @@
       <c r="AB306" s="3" t="n">
         <v>0.0004037956793862141</v>
       </c>
+      <c r="AC306" s="1" t="n">
+        <v>0.04977</v>
+      </c>
+      <c r="AD306" s="3" t="n">
+        <v>0.004439959636730675</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -27525,6 +29367,12 @@
       <c r="AB307" s="3" t="n">
         <v>0.003260869565217394</v>
       </c>
+      <c r="AC307" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="AD307" s="3" t="n">
+        <v>0.006500541711809323</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -27613,6 +29461,12 @@
       <c r="AB308" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC308" s="1" t="n">
+        <v>0.04002</v>
+      </c>
+      <c r="AD308" s="3" t="n">
+        <v>0.003762227238525141</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -27701,6 +29555,12 @@
       <c r="AB309" s="2" t="n">
         <v>-0.00256081946222792</v>
       </c>
+      <c r="AC309" s="1" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="AD309" s="3" t="n">
+        <v>0.001283697047496738</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -27789,6 +29649,12 @@
       <c r="AB310" s="3" t="n">
         <v>0.002768549280177266</v>
       </c>
+      <c r="AC310" s="1" t="n">
+        <v>0.05461</v>
+      </c>
+      <c r="AD310" s="3" t="n">
+        <v>0.005153690410454547</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -27877,6 +29743,12 @@
       <c r="AB311" s="2" t="n">
         <v>-0.001342281879194615</v>
       </c>
+      <c r="AC311" s="1" t="n">
+        <v>0.004472</v>
+      </c>
+      <c r="AD311" s="3" t="n">
+        <v>0.001792114695340545</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -27965,6 +29837,12 @@
       <c r="AB312" s="3" t="n">
         <v>0.001889912591542728</v>
       </c>
+      <c r="AC312" s="1" t="n">
+        <v>0.08501</v>
+      </c>
+      <c r="AD312" s="3" t="n">
+        <v>0.00224003772695114</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -28053,6 +29931,12 @@
       <c r="AB313" s="2" t="n">
         <v>-0.0006683598449406279</v>
       </c>
+      <c r="AC313" s="1" t="n">
+        <v>0.07499</v>
+      </c>
+      <c r="AD313" s="3" t="n">
+        <v>0.003076511503477903</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -28141,6 +30025,12 @@
       <c r="AB314" s="2" t="n">
         <v>-0.00260926288323538</v>
       </c>
+      <c r="AC314" s="1" t="n">
+        <v>0.1528</v>
+      </c>
+      <c r="AD314" s="2" t="n">
+        <v>-0.0006540222367561591</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -28229,6 +30119,12 @@
       <c r="AB315" s="2" t="n">
         <v>-0.0006265664160400313</v>
       </c>
+      <c r="AC315" s="1" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="AD315" s="3" t="n">
+        <v>0.004388714733542358</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -28317,6 +30213,12 @@
       <c r="AB316" s="3" t="n">
         <v>0.002209944751381279</v>
       </c>
+      <c r="AC316" s="1" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="AD316" s="3" t="n">
+        <v>0.003858875413450971</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -28405,6 +30307,12 @@
       <c r="AB317" s="2" t="n">
         <v>-0.001334578940344267</v>
       </c>
+      <c r="AC317" s="1" t="n">
+        <v>0.007523</v>
+      </c>
+      <c r="AD317" s="3" t="n">
+        <v>0.005345449685954845</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -28493,6 +30401,12 @@
       <c r="AB318" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC318" s="1" t="n">
+        <v>0.05031</v>
+      </c>
+      <c r="AD318" s="3" t="n">
+        <v>0.004793289394847157</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -28581,6 +30495,12 @@
       <c r="AB319" s="3" t="n">
         <v>0.001363522193117771</v>
       </c>
+      <c r="AC319" s="1" t="n">
+        <v>0.27884</v>
+      </c>
+      <c r="AD319" s="2" t="n">
+        <v>-0.000824165979861712</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -28669,6 +30589,12 @@
       <c r="AB320" s="2" t="n">
         <v>-0.00181818181818187</v>
       </c>
+      <c r="AC320" s="1" t="n">
+        <v>0.4416</v>
+      </c>
+      <c r="AD320" s="3" t="n">
+        <v>0.00546448087431697</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -28757,6 +30683,12 @@
       <c r="AB321" s="2" t="n">
         <v>-0.002057877813504739</v>
       </c>
+      <c r="AC321" s="1" t="n">
+        <v>0.07788</v>
+      </c>
+      <c r="AD321" s="3" t="n">
+        <v>0.003737595050908604</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -28845,6 +30777,12 @@
       <c r="AB322" s="3" t="n">
         <v>0.003061849357011638</v>
       </c>
+      <c r="AC322" s="1" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="AD322" s="2" t="n">
+        <v>-0.001831501831501799</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -28933,6 +30871,12 @@
       <c r="AB323" s="2" t="n">
         <v>-0.002531645569620311</v>
       </c>
+      <c r="AC323" s="1" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD323" s="3" t="n">
+        <v>0.0050761421319797</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -29021,6 +30965,12 @@
       <c r="AB324" s="2" t="n">
         <v>-0.0008472980606288163</v>
       </c>
+      <c r="AC324" s="1" t="n">
+        <v>0.053282</v>
+      </c>
+      <c r="AD324" s="3" t="n">
+        <v>0.004089324413455233</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -29109,6 +31059,12 @@
       <c r="AB325" s="2" t="n">
         <v>-0.0005878894767784097</v>
       </c>
+      <c r="AC325" s="1" t="n">
+        <v>0.15367</v>
+      </c>
+      <c r="AD325" s="3" t="n">
+        <v>0.004379084967320287</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -29197,6 +31153,12 @@
       <c r="AB326" s="2" t="n">
         <v>-0.0009270704573547479</v>
       </c>
+      <c r="AC326" s="1" t="n">
+        <v>0.006483</v>
+      </c>
+      <c r="AD326" s="3" t="n">
+        <v>0.002629137024435455</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -29285,6 +31247,12 @@
       <c r="AB327" s="2" t="n">
         <v>-0.006131329113924007</v>
       </c>
+      <c r="AC327" s="1" t="n">
+        <v>0.015223</v>
+      </c>
+      <c r="AD327" s="3" t="n">
+        <v>0.00981757877280269</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -29373,6 +31341,12 @@
       <c r="AB328" s="2" t="n">
         <v>-0.00312500000000009</v>
       </c>
+      <c r="AC328" s="1" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="AD328" s="3" t="n">
+        <v>0.009404388714733668</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -29461,6 +31435,12 @@
       <c r="AB329" s="3" t="n">
         <v>0.0002272210861166247</v>
       </c>
+      <c r="AC329" s="1" t="n">
+        <v>0.004413</v>
+      </c>
+      <c r="AD329" s="3" t="n">
+        <v>0.002498864152658018</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -29549,6 +31529,12 @@
       <c r="AB330" s="3" t="n">
         <v>0.00212971926427878</v>
       </c>
+      <c r="AC330" s="1" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="AD330" s="3" t="n">
+        <v>0.002704791344667721</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -29637,6 +31623,12 @@
       <c r="AB331" s="2" t="n">
         <v>-0.001392369813422292</v>
       </c>
+      <c r="AC331" s="1" t="n">
+        <v>0.03599</v>
+      </c>
+      <c r="AD331" s="3" t="n">
+        <v>0.003625209146681488</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -29725,6 +31717,12 @@
       <c r="AB332" s="2" t="n">
         <v>-0.000682593856655215</v>
       </c>
+      <c r="AC332" s="1" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="AD332" s="3" t="n">
+        <v>0.01161202185792354</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -29813,6 +31811,12 @@
       <c r="AB333" s="3" t="n">
         <v>0.002085505735140832</v>
       </c>
+      <c r="AC333" s="1" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="AD333" s="3" t="n">
+        <v>0.00728407908428712</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -29901,6 +31905,12 @@
       <c r="AB334" s="3" t="n">
         <v>0.001590186278964121</v>
       </c>
+      <c r="AC334" s="1" t="n">
+        <v>0.04403</v>
+      </c>
+      <c r="AD334" s="2" t="n">
+        <v>-0.001360852801088627</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -29989,6 +31999,12 @@
       <c r="AB335" s="2" t="n">
         <v>-0.0006110228522546071</v>
       </c>
+      <c r="AC335" s="1" t="n">
+        <v>0.08205999999999999</v>
+      </c>
+      <c r="AD335" s="3" t="n">
+        <v>0.003423820004891032</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -30077,6 +32093,12 @@
       <c r="AB336" s="3" t="n">
         <v>0.001954079140205234</v>
       </c>
+      <c r="AC336" s="1" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="AD336" s="3" t="n">
+        <v>0.00926377376889315</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -30165,6 +32187,12 @@
       <c r="AB337" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC337" s="1" t="n">
+        <v>0.01008</v>
+      </c>
+      <c r="AD337" s="2" t="n">
+        <v>-0.00493583415597233</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -30253,6 +32281,12 @@
       <c r="AB338" s="3" t="n">
         <v>0.001766784452296871</v>
       </c>
+      <c r="AC338" s="1" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="AD338" s="3" t="n">
+        <v>0.009700176366843066</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -30341,6 +32375,12 @@
       <c r="AB339" s="2" t="n">
         <v>-0.002185792349726877</v>
       </c>
+      <c r="AC339" s="1" t="n">
+        <v>0.01836</v>
+      </c>
+      <c r="AD339" s="3" t="n">
+        <v>0.005476451259583947</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -30429,6 +32469,12 @@
       <c r="AB340" s="2" t="n">
         <v>-0.009923581181413278</v>
       </c>
+      <c r="AC340" s="1" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="AD340" s="2" t="n">
+        <v>-0.005011522844496405</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -30517,6 +32563,12 @@
       <c r="AB341" s="3" t="n">
         <v>0.001400560224089579</v>
       </c>
+      <c r="AC341" s="1" t="n">
+        <v>0.04307</v>
+      </c>
+      <c r="AD341" s="3" t="n">
+        <v>0.003962703962703882</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -30605,6 +32657,12 @@
       <c r="AB342" s="3" t="n">
         <v>0.02565431458927177</v>
       </c>
+      <c r="AC342" s="1" t="n">
+        <v>0.07964</v>
+      </c>
+      <c r="AD342" s="3" t="n">
+        <v>0.006063668519454374</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -30693,6 +32751,12 @@
       <c r="AB343" s="2" t="n">
         <v>-0.002095612311722333</v>
       </c>
+      <c r="AC343" s="1" t="n">
+        <v>7.645</v>
+      </c>
+      <c r="AD343" s="3" t="n">
+        <v>0.003412521328258276</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -30781,6 +32845,12 @@
       <c r="AB344" s="3" t="n">
         <v>0.0008361204013378862</v>
       </c>
+      <c r="AC344" s="1" t="n">
+        <v>0.6022</v>
+      </c>
+      <c r="AD344" s="3" t="n">
+        <v>0.006182121971595531</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -30869,6 +32939,12 @@
       <c r="AB345" s="3" t="n">
         <v>0.001338688085676076</v>
       </c>
+      <c r="AC345" s="1" t="n">
+        <v>0.03757</v>
+      </c>
+      <c r="AD345" s="3" t="n">
+        <v>0.004545454545454452</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -30957,6 +33033,12 @@
       <c r="AB346" s="2" t="n">
         <v>-0.002398081534772251</v>
       </c>
+      <c r="AC346" s="1" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="AD346" s="3" t="n">
+        <v>0.002403846153846223</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -31045,6 +33127,12 @@
       <c r="AB347" s="3" t="n">
         <v>0.001147446930579334</v>
       </c>
+      <c r="AC347" s="1" t="n">
+        <v>0.1751</v>
+      </c>
+      <c r="AD347" s="3" t="n">
+        <v>0.003438395415472878</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -31133,6 +33221,12 @@
       <c r="AB348" s="3" t="n">
         <v>0.00134950164831987</v>
       </c>
+      <c r="AC348" s="1" t="n">
+        <v>5191.5</v>
+      </c>
+      <c r="AD348" s="2" t="n">
+        <v>-0.0005005679520995675</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -31221,6 +33315,12 @@
       <c r="AB349" s="2" t="n">
         <v>-0.01243599122165326</v>
       </c>
+      <c r="AC349" s="1" t="n">
+        <v>0.01356</v>
+      </c>
+      <c r="AD349" s="3" t="n">
+        <v>0.004444444444444392</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -31309,6 +33409,12 @@
       <c r="AB350" s="3" t="n">
         <v>0.008463541666666661</v>
       </c>
+      <c r="AC350" s="1" t="n">
+        <v>0.01563</v>
+      </c>
+      <c r="AD350" s="3" t="n">
+        <v>0.009038089089735392</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -31397,6 +33503,12 @@
       <c r="AB351" s="3" t="n">
         <v>0.001636125654450301</v>
       </c>
+      <c r="AC351" s="1" t="n">
+        <v>0.0006173</v>
+      </c>
+      <c r="AD351" s="3" t="n">
+        <v>0.008330610911466777</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -31485,6 +33597,12 @@
       <c r="AB352" s="2" t="n">
         <v>-0.002021222839818008</v>
       </c>
+      <c r="AC352" s="1" t="n">
+        <v>0.01983</v>
+      </c>
+      <c r="AD352" s="3" t="n">
+        <v>0.004050632911392416</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -31573,6 +33691,12 @@
       <c r="AB353" s="2" t="n">
         <v>-0.002992731936725123</v>
       </c>
+      <c r="AC353" s="1" t="n">
+        <v>0.09319</v>
+      </c>
+      <c r="AD353" s="2" t="n">
+        <v>-0.0009648370497427823</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -31661,6 +33785,12 @@
       <c r="AB354" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC354" s="1" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="AD354" s="3" t="n">
+        <v>0.005549389567147619</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -31749,6 +33879,12 @@
       <c r="AB355" s="2" t="n">
         <v>-0.006165828330358566</v>
       </c>
+      <c r="AC355" s="1" t="n">
+        <v>0.000612</v>
+      </c>
+      <c r="AD355" s="2" t="n">
+        <v>-0.0008163265306121763</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -31837,6 +33973,12 @@
       <c r="AB356" s="2" t="n">
         <v>-0.004916420845624281</v>
       </c>
+      <c r="AC356" s="1" t="n">
+        <v>2.034</v>
+      </c>
+      <c r="AD356" s="3" t="n">
+        <v>0.004940711462450487</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -31925,6 +34067,12 @@
       <c r="AB357" s="2" t="n">
         <v>-0.006962576153176693</v>
       </c>
+      <c r="AC357" s="1" t="n">
+        <v>0.02289</v>
+      </c>
+      <c r="AD357" s="3" t="n">
+        <v>0.003067484662576714</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -32013,6 +34161,12 @@
       <c r="AB358" s="3" t="n">
         <v>0.002469135802469196</v>
       </c>
+      <c r="AC358" s="1" t="n">
+        <v>0.000408</v>
+      </c>
+      <c r="AD358" s="3" t="n">
+        <v>0.004926108374384223</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -32101,6 +34255,12 @@
       <c r="AB359" s="3" t="n">
         <v>0.002047781569965905</v>
       </c>
+      <c r="AC359" s="1" t="n">
+        <v>0.01473</v>
+      </c>
+      <c r="AD359" s="3" t="n">
+        <v>0.003405994550408699</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -32189,6 +34349,12 @@
       <c r="AB360" s="2" t="n">
         <v>-0.003308270676691647</v>
       </c>
+      <c r="AC360" s="1" t="n">
+        <v>0.00334</v>
+      </c>
+      <c r="AD360" s="3" t="n">
+        <v>0.007845503922751955</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -32277,6 +34443,12 @@
       <c r="AB361" s="2" t="n">
         <v>-0.002820874471086074</v>
       </c>
+      <c r="AC361" s="1" t="n">
+        <v>0.6382</v>
+      </c>
+      <c r="AD361" s="3" t="n">
+        <v>0.002986012887003006</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -32365,6 +34537,12 @@
       <c r="AB362" s="3" t="n">
         <v>0.002128565346956065</v>
       </c>
+      <c r="AC362" s="1" t="n">
+        <v>0.02364</v>
+      </c>
+      <c r="AD362" s="3" t="n">
+        <v>0.004248088360238015</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -32453,6 +34631,12 @@
       <c r="AB363" s="2" t="n">
         <v>-0.0007676953784737371</v>
       </c>
+      <c r="AC363" s="1" t="n">
+        <v>0.06542000000000001</v>
+      </c>
+      <c r="AD363" s="3" t="n">
+        <v>0.00522433927473889</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -32541,6 +34725,12 @@
       <c r="AB364" s="3" t="n">
         <v>0.0002127206977239596</v>
       </c>
+      <c r="AC364" s="1" t="n">
+        <v>4.724</v>
+      </c>
+      <c r="AD364" s="3" t="n">
+        <v>0.00467886005954918</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -32629,6 +34819,12 @@
       <c r="AB365" s="2" t="n">
         <v>-0.004447533009034063</v>
       </c>
+      <c r="AC365" s="1" t="n">
+        <v>0.07196</v>
+      </c>
+      <c r="AD365" s="3" t="n">
+        <v>0.00460700823677226</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -32717,6 +34913,12 @@
       <c r="AB366" s="3" t="n">
         <v>0.0003565062388592892</v>
       </c>
+      <c r="AC366" s="1" t="n">
+        <v>0.05641</v>
+      </c>
+      <c r="AD366" s="3" t="n">
+        <v>0.005167498218104037</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -32805,6 +35007,12 @@
       <c r="AB367" s="2" t="n">
         <v>-0.0006850488097276652</v>
       </c>
+      <c r="AC367" s="1" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="AD367" s="3" t="n">
+        <v>0.002570694087403673</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -32893,6 +35101,12 @@
       <c r="AB368" s="2" t="n">
         <v>-0.002790373212417168</v>
       </c>
+      <c r="AC368" s="1" t="n">
+        <v>0.05712</v>
+      </c>
+      <c r="AD368" s="2" t="n">
+        <v>-0.00104931794333691</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -32981,6 +35195,12 @@
       <c r="AB369" s="2" t="n">
         <v>-0.001936108422071669</v>
       </c>
+      <c r="AC369" s="1" t="n">
+        <v>0.03106</v>
+      </c>
+      <c r="AD369" s="3" t="n">
+        <v>0.004203039120594945</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -33069,6 +35289,12 @@
       <c r="AB370" s="3" t="n">
         <v>0.0006172839506172989</v>
       </c>
+      <c r="AC370" s="1" t="n">
+        <v>0.0001627</v>
+      </c>
+      <c r="AD370" s="3" t="n">
+        <v>0.003701418877236197</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -33157,6 +35383,12 @@
       <c r="AB371" s="2" t="n">
         <v>-0.006310537129439337</v>
       </c>
+      <c r="AC371" s="1" t="n">
+        <v>0.006788</v>
+      </c>
+      <c r="AD371" s="3" t="n">
+        <v>0.002510707428740165</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -33245,6 +35477,12 @@
       <c r="AB372" s="3" t="n">
         <v>0.001580459770114903</v>
       </c>
+      <c r="AC372" s="1" t="n">
+        <v>0.006975</v>
+      </c>
+      <c r="AD372" s="3" t="n">
+        <v>0.000573805766748032</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -33333,6 +35571,12 @@
       <c r="AB373" s="2" t="n">
         <v>-0.005536514632217335</v>
       </c>
+      <c r="AC373" s="1" t="n">
+        <v>3.785</v>
+      </c>
+      <c r="AD373" s="3" t="n">
+        <v>0.003446447507953432</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -33421,6 +35665,12 @@
       <c r="AB374" s="2" t="n">
         <v>-0.000142267747901693</v>
       </c>
+      <c r="AC374" s="1" t="n">
+        <v>0.07031</v>
+      </c>
+      <c r="AD374" s="3" t="n">
+        <v>0.0004268639726807377</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -33509,6 +35759,12 @@
       <c r="AB375" s="2" t="n">
         <v>-0.0001258178158026689</v>
       </c>
+      <c r="AC375" s="1" t="n">
+        <v>0.07972</v>
+      </c>
+      <c r="AD375" s="3" t="n">
+        <v>0.003145841197936331</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -33597,6 +35853,12 @@
       <c r="AB376" s="3" t="n">
         <v>0.000796178343949178</v>
       </c>
+      <c r="AC376" s="1" t="n">
+        <v>0.06292</v>
+      </c>
+      <c r="AD376" s="3" t="n">
+        <v>0.001113762927605419</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -33685,6 +35947,12 @@
       <c r="AB377" s="3" t="n">
         <v>0.003663482925552826</v>
       </c>
+      <c r="AC377" s="1" t="n">
+        <v>0.07691000000000001</v>
+      </c>
+      <c r="AD377" s="3" t="n">
+        <v>0.002607222004953797</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -33773,6 +36041,12 @@
       <c r="AB378" s="2" t="n">
         <v>-0.005656665027053619</v>
       </c>
+      <c r="AC378" s="1" t="n">
+        <v>0.0004044</v>
+      </c>
+      <c r="AD378" s="3" t="n">
+        <v>0.0002473410833539511</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -33861,6 +36135,12 @@
       <c r="AB379" s="2" t="n">
         <v>-0.004457050243111791</v>
       </c>
+      <c r="AC379" s="1" t="n">
+        <v>0.0738</v>
+      </c>
+      <c r="AD379" s="3" t="n">
+        <v>0.001221001221001313</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -33949,6 +36229,12 @@
       <c r="AB380" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC380" s="1" t="n">
+        <v>0.001371</v>
+      </c>
+      <c r="AD380" s="3" t="n">
+        <v>0.004395604395604503</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -34037,6 +36323,12 @@
       <c r="AB381" s="2" t="n">
         <v>-0.00768748038908056</v>
       </c>
+      <c r="AC381" s="1" t="n">
+        <v>6.359</v>
+      </c>
+      <c r="AD381" s="3" t="n">
+        <v>0.005375494071146215</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -34125,6 +36417,12 @@
       <c r="AB382" s="3" t="n">
         <v>0.005759539236861067</v>
       </c>
+      <c r="AC382" s="1" t="n">
+        <v>0.01411</v>
+      </c>
+      <c r="AD382" s="3" t="n">
+        <v>0.01002147458840369</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -34213,6 +36511,12 @@
       <c r="AB383" s="3" t="n">
         <v>0.001139601139601093</v>
       </c>
+      <c r="AC383" s="1" t="n">
+        <v>0.01763</v>
+      </c>
+      <c r="AD383" s="3" t="n">
+        <v>0.003414911781445705</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -34301,6 +36605,12 @@
       <c r="AB384" s="3" t="n">
         <v>0.0009881422924901469</v>
       </c>
+      <c r="AC384" s="1" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="AD384" s="3" t="n">
+        <v>0.002961500493583364</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -34389,6 +36699,12 @@
       <c r="AB385" s="2" t="n">
         <v>-0.002004454342984486</v>
       </c>
+      <c r="AC385" s="1" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="AD385" s="3" t="n">
+        <v>0.00557911180540066</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -34477,6 +36793,12 @@
       <c r="AB386" s="2" t="n">
         <v>-0.003828483920367544</v>
       </c>
+      <c r="AC386" s="1" t="n">
+        <v>0.001302</v>
+      </c>
+      <c r="AD386" s="3" t="n">
+        <v>0.0007686395080706501</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -34565,6 +36887,12 @@
       <c r="AB387" s="2" t="n">
         <v>-0.0005065000844167845</v>
       </c>
+      <c r="AC387" s="1" t="n">
+        <v>0.0005935</v>
+      </c>
+      <c r="AD387" s="3" t="n">
+        <v>0.002533783783783754</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -34653,6 +36981,12 @@
       <c r="AB388" s="2" t="n">
         <v>-0.003484320557491298</v>
       </c>
+      <c r="AC388" s="1" t="n">
+        <v>0.01148</v>
+      </c>
+      <c r="AD388" s="3" t="n">
+        <v>0.003496503496503506</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -34741,6 +37075,12 @@
       <c r="AB389" s="3" t="n">
         <v>0.00110741971207083</v>
       </c>
+      <c r="AC389" s="1" t="n">
+        <v>0.00908</v>
+      </c>
+      <c r="AD389" s="3" t="n">
+        <v>0.004424778761061959</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -34829,6 +37169,12 @@
       <c r="AB390" s="2" t="n">
         <v>-0.000381145978909951</v>
       </c>
+      <c r="AC390" s="1" t="n">
+        <v>0.07918</v>
+      </c>
+      <c r="AD390" s="3" t="n">
+        <v>0.006354855109303514</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -34917,6 +37263,12 @@
       <c r="AB391" s="3" t="n">
         <v>0.001937233630375879</v>
       </c>
+      <c r="AC391" s="1" t="n">
+        <v>0.05225</v>
+      </c>
+      <c r="AD391" s="3" t="n">
+        <v>0.01024748646558383</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -35005,6 +37357,12 @@
       <c r="AB392" s="2" t="n">
         <v>-0.004219409282700433</v>
       </c>
+      <c r="AC392" s="1" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="AD392" s="3" t="n">
+        <v>0.008474576271186463</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -35093,6 +37451,12 @@
       <c r="AB393" s="2" t="n">
         <v>-0.0009385265133739646</v>
       </c>
+      <c r="AC393" s="1" t="n">
+        <v>0.02144</v>
+      </c>
+      <c r="AD393" s="3" t="n">
+        <v>0.007045561296383318</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -35181,6 +37545,12 @@
       <c r="AB394" s="2" t="n">
         <v>-0.0004916420845623844</v>
       </c>
+      <c r="AC394" s="1" t="n">
+        <v>0.2033</v>
+      </c>
+      <c r="AD394" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -35269,6 +37639,12 @@
       <c r="AB395" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC395" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="AD395" s="3" t="n">
+        <v>0.005144032921810705</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -35357,6 +37733,12 @@
       <c r="AB396" s="3" t="n">
         <v>0.01098901098901092</v>
       </c>
+      <c r="AC396" s="1" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="AD396" s="3" t="n">
+        <v>0.009057971014492882</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -35445,6 +37827,12 @@
       <c r="AB397" s="3" t="n">
         <v>0.005577689243027983</v>
       </c>
+      <c r="AC397" s="1" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="AD397" s="3" t="n">
+        <v>0.00396196513470673</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -35533,6 +37921,12 @@
       <c r="AB398" s="3" t="n">
         <v>0.001362583458236762</v>
       </c>
+      <c r="AC398" s="1" t="n">
+        <v>0.007434</v>
+      </c>
+      <c r="AD398" s="3" t="n">
+        <v>0.01156619948292285</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -35621,6 +38015,12 @@
       <c r="AB399" s="3" t="n">
         <v>0.0007724990343761219</v>
       </c>
+      <c r="AC399" s="1" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="AD399" s="3" t="n">
+        <v>0.002701659590891465</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -35709,6 +38109,12 @@
       <c r="AB400" s="2" t="n">
         <v>-0.0003147623544223764</v>
       </c>
+      <c r="AC400" s="1" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="AD400" s="3" t="n">
+        <v>0.002833753148614647</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -35797,6 +38203,12 @@
       <c r="AB401" s="2" t="n">
         <v>-0.00665188470066523</v>
       </c>
+      <c r="AC401" s="1" t="n">
+        <v>0.007198</v>
+      </c>
+      <c r="AD401" s="3" t="n">
+        <v>0.004185267857142929</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -35885,6 +38297,12 @@
       <c r="AB402" s="2" t="n">
         <v>-0.00109146474568867</v>
       </c>
+      <c r="AC402" s="1" t="n">
+        <v>0.004588</v>
+      </c>
+      <c r="AD402" s="3" t="n">
+        <v>0.002622377622377591</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -35973,6 +38391,12 @@
       <c r="AB403" s="3" t="n">
         <v>0.001885369532428358</v>
       </c>
+      <c r="AC403" s="1" t="n">
+        <v>0.2669</v>
+      </c>
+      <c r="AD403" s="3" t="n">
+        <v>0.004516371847948944</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -36061,6 +38485,12 @@
       <c r="AB404" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC404" s="1" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="AD404" s="3" t="n">
+        <v>0.0004177109440266875</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -36149,6 +38579,12 @@
       <c r="AB405" s="3" t="n">
         <v>0.002171676763058626</v>
       </c>
+      <c r="AC405" s="1" t="n">
+        <v>0.0008799</v>
+      </c>
+      <c r="AD405" s="3" t="n">
+        <v>0.003535583941605864</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -36237,6 +38673,12 @@
       <c r="AB406" s="2" t="n">
         <v>-0.0005923000987167617</v>
       </c>
+      <c r="AC406" s="1" t="n">
+        <v>0.005082</v>
+      </c>
+      <c r="AD406" s="3" t="n">
+        <v>0.003951007506914274</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -36325,6 +38767,12 @@
       <c r="AB407" s="2" t="n">
         <v>-0.0008312551953450812</v>
       </c>
+      <c r="AC407" s="1" t="n">
+        <v>0.01208</v>
+      </c>
+      <c r="AD407" s="3" t="n">
+        <v>0.004991680532446009</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -36413,6 +38861,12 @@
       <c r="AB408" s="3" t="n">
         <v>0.001369863013698664</v>
       </c>
+      <c r="AC408" s="1" t="n">
+        <v>0.001459</v>
+      </c>
+      <c r="AD408" s="2" t="n">
+        <v>-0.002051983584131303</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -36501,6 +38955,12 @@
       <c r="AB409" s="3" t="n">
         <v>0.02081686429512514</v>
       </c>
+      <c r="AC409" s="1" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="AD409" s="2" t="n">
+        <v>-0.003613835828600782</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -36589,6 +39049,12 @@
       <c r="AB410" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC410" s="1" t="n">
+        <v>0.01637</v>
+      </c>
+      <c r="AD410" s="3" t="n">
+        <v>0.002449479485609208</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -36677,6 +39143,12 @@
       <c r="AB411" s="2" t="n">
         <v>-0.003695881731784615</v>
       </c>
+      <c r="AC411" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AD411" s="3" t="n">
+        <v>0.006889242183359807</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -36765,6 +39237,12 @@
       <c r="AB412" s="2" t="n">
         <v>-0.003989951233929252</v>
       </c>
+      <c r="AC412" s="1" t="n">
+        <v>0.06759</v>
+      </c>
+      <c r="AD412" s="3" t="n">
+        <v>0.002818991097922785</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -36853,6 +39331,12 @@
       <c r="AB413" s="2" t="n">
         <v>-0.0003957261574990107</v>
       </c>
+      <c r="AC413" s="1" t="n">
+        <v>2537</v>
+      </c>
+      <c r="AD413" s="3" t="n">
+        <v>0.00435471100554236</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -36941,6 +39425,12 @@
       <c r="AB414" s="2" t="n">
         <v>-0.0007623403849819955</v>
       </c>
+      <c r="AC414" s="1" t="n">
+        <v>0.05252</v>
+      </c>
+      <c r="AD414" s="3" t="n">
+        <v>0.00171657448025939</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -37029,6 +39519,12 @@
       <c r="AB415" s="3" t="n">
         <v>0.002298850574712646</v>
       </c>
+      <c r="AC415" s="1" t="n">
+        <v>1.747</v>
+      </c>
+      <c r="AD415" s="3" t="n">
+        <v>0.001720183486238597</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -37117,6 +39613,12 @@
       <c r="AB416" s="3" t="n">
         <v>0.001741907388590435</v>
       </c>
+      <c r="AC416" s="1" t="n">
+        <v>0.06936</v>
+      </c>
+      <c r="AD416" s="3" t="n">
+        <v>0.005071728734965992</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -37205,6 +39707,12 @@
       <c r="AB417" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC417" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AD417" s="3" t="n">
+        <v>0.01351351351351353</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -37293,6 +39801,12 @@
       <c r="AB418" s="2" t="n">
         <v>-0.003278688524590167</v>
       </c>
+      <c r="AC418" s="1" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="AD418" s="3" t="n">
+        <v>0.003289473684210529</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -37381,6 +39895,12 @@
       <c r="AB419" s="2" t="n">
         <v>-0.008064516129032209</v>
       </c>
+      <c r="AC419" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="AD419" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -37469,6 +39989,12 @@
       <c r="AB420" s="2" t="n">
         <v>-0.003655352480417787</v>
       </c>
+      <c r="AC420" s="1" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="AD420" s="3" t="n">
+        <v>0.008909853249475892</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -37557,6 +40083,12 @@
       <c r="AB421" s="2" t="n">
         <v>-0.00128429055789582</v>
       </c>
+      <c r="AC421" s="1" t="n">
+        <v>0.19396</v>
+      </c>
+      <c r="AD421" s="2" t="n">
+        <v>-0.002314695746103626</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -37645,6 +40177,12 @@
       <c r="AB422" s="2" t="n">
         <v>-0.0005847953216374031</v>
       </c>
+      <c r="AC422" s="1" t="n">
+        <v>0.03434</v>
+      </c>
+      <c r="AD422" s="3" t="n">
+        <v>0.004681100058513763</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -37733,6 +40271,12 @@
       <c r="AB423" s="2" t="n">
         <v>-0.002117148906139695</v>
       </c>
+      <c r="AC423" s="1" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="AD423" s="3" t="n">
+        <v>0.006364922206506449</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -37821,6 +40365,12 @@
       <c r="AB424" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC424" s="1" t="n">
+        <v>0.00532</v>
+      </c>
+      <c r="AD424" s="3" t="n">
+        <v>0.005671077504725831</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -37909,6 +40459,12 @@
       <c r="AB425" s="3" t="n">
         <v>0.0009606147934678469</v>
       </c>
+      <c r="AC425" s="1" t="n">
+        <v>0.1044</v>
+      </c>
+      <c r="AD425" s="3" t="n">
+        <v>0.001919385796545161</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -37997,6 +40553,12 @@
       <c r="AB426" s="3" t="n">
         <v>0.007078142695356696</v>
       </c>
+      <c r="AC426" s="1" t="n">
+        <v>0.007134</v>
+      </c>
+      <c r="AD426" s="3" t="n">
+        <v>0.002811357885858877</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -38085,6 +40647,12 @@
       <c r="AB427" s="2" t="n">
         <v>-0.001964636542239742</v>
       </c>
+      <c r="AC427" s="1" t="n">
+        <v>0.02549</v>
+      </c>
+      <c r="AD427" s="3" t="n">
+        <v>0.003543307086614166</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -38173,6 +40741,12 @@
       <c r="AB428" s="3" t="n">
         <v>0.002234636871508461</v>
       </c>
+      <c r="AC428" s="1" t="n">
+        <v>0.008147</v>
+      </c>
+      <c r="AD428" s="3" t="n">
+        <v>0.009166356992443876</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -38261,6 +40835,12 @@
       <c r="AB429" s="2" t="n">
         <v>-0.002429149797570892</v>
       </c>
+      <c r="AC429" s="1" t="n">
+        <v>0.01237</v>
+      </c>
+      <c r="AD429" s="3" t="n">
+        <v>0.004058441558441675</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -38349,6 +40929,12 @@
       <c r="AB430" s="2" t="n">
         <v>-0.001197067185395732</v>
       </c>
+      <c r="AC430" s="1" t="n">
+        <v>0.06703000000000001</v>
+      </c>
+      <c r="AD430" s="3" t="n">
+        <v>0.004194756554307153</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -38437,6 +41023,12 @@
       <c r="AB431" s="3" t="n">
         <v>0.003703703703703713</v>
       </c>
+      <c r="AC431" s="1" t="n">
+        <v>0.00544</v>
+      </c>
+      <c r="AD431" s="3" t="n">
+        <v>0.003690036900369013</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -38525,6 +41117,12 @@
       <c r="AB432" s="2" t="n">
         <v>-0.004265057734318046</v>
       </c>
+      <c r="AC432" s="1" t="n">
+        <v>0.009625</v>
+      </c>
+      <c r="AD432" s="3" t="n">
+        <v>0.005536982866694445</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -38613,6 +41211,12 @@
       <c r="AB433" s="2" t="n">
         <v>-0.004346776141028727</v>
       </c>
+      <c r="AC433" s="1" t="n">
+        <v>0.04139</v>
+      </c>
+      <c r="AD433" s="3" t="n">
+        <v>0.003880669415474179</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -38701,6 +41305,12 @@
       <c r="AB434" s="3" t="n">
         <v>0.006888361045130608</v>
       </c>
+      <c r="AC434" s="1" t="n">
+        <v>0.04241</v>
+      </c>
+      <c r="AD434" s="3" t="n">
+        <v>0.0004718093890069858</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -38789,6 +41399,12 @@
       <c r="AB435" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC435" s="1" t="n">
+        <v>0.001555</v>
+      </c>
+      <c r="AD435" s="3" t="n">
+        <v>0.007777057679844366</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -38877,6 +41493,12 @@
       <c r="AB436" s="2" t="n">
         <v>-0.00109529025191684</v>
       </c>
+      <c r="AC436" s="1" t="n">
+        <v>0.02752</v>
+      </c>
+      <c r="AD436" s="3" t="n">
+        <v>0.005847953216374284</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -38965,6 +41587,12 @@
       <c r="AB437" s="2" t="n">
         <v>-0.006941061860691684</v>
       </c>
+      <c r="AC437" s="1" t="n">
+        <v>0.08173</v>
+      </c>
+      <c r="AD437" s="3" t="n">
+        <v>0.002207234825260571</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -39053,6 +41681,12 @@
       <c r="AB438" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC438" s="1" t="n">
+        <v>0.1153</v>
+      </c>
+      <c r="AD438" s="3" t="n">
+        <v>0.004355400696864116</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -39141,6 +41775,12 @@
       <c r="AB439" s="2" t="n">
         <v>-0.0006476683937824559</v>
       </c>
+      <c r="AC439" s="1" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="AD439" s="3" t="n">
+        <v>0.006480881399870389</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -39229,6 +41869,12 @@
       <c r="AB440" s="3" t="n">
         <v>0.006655574043261273</v>
       </c>
+      <c r="AC440" s="1" t="n">
+        <v>0.001825</v>
+      </c>
+      <c r="AD440" s="3" t="n">
+        <v>0.005509641873278252</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -39317,6 +41963,12 @@
       <c r="AB441" s="2" t="n">
         <v>-0.0008152173913044089</v>
       </c>
+      <c r="AC441" s="1" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="AD441" s="3" t="n">
+        <v>0.0008158825129182009</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -39405,6 +42057,12 @@
       <c r="AB442" s="2" t="n">
         <v>-0.00760043431053191</v>
       </c>
+      <c r="AC442" s="1" t="n">
+        <v>0.01838</v>
+      </c>
+      <c r="AD442" s="3" t="n">
+        <v>0.005470459518599529</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -39493,6 +42151,12 @@
       <c r="AB443" s="2" t="n">
         <v>-0.0001577287066245445</v>
       </c>
+      <c r="AC443" s="1" t="n">
+        <v>0.12738</v>
+      </c>
+      <c r="AD443" s="3" t="n">
+        <v>0.004732607666824337</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -39581,6 +42245,12 @@
       <c r="AB444" s="2" t="n">
         <v>-0.002267969295184925</v>
       </c>
+      <c r="AC444" s="1" t="n">
+        <v>0.011463</v>
+      </c>
+      <c r="AD444" s="3" t="n">
+        <v>0.002185696800139796</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -39669,6 +42339,12 @@
       <c r="AB445" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC445" s="1" t="n">
+        <v>0.08105</v>
+      </c>
+      <c r="AD445" s="3" t="n">
+        <v>0.006457220911461476</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -39757,6 +42433,12 @@
       <c r="AB446" s="3" t="n">
         <v>0.005625879043600572</v>
       </c>
+      <c r="AC446" s="1" t="n">
+        <v>0.0002147</v>
+      </c>
+      <c r="AD446" s="3" t="n">
+        <v>0.0009324009324008286</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -39845,6 +42527,12 @@
       <c r="AB447" s="3" t="n">
         <v>0.004538577912254107</v>
       </c>
+      <c r="AC447" s="1" t="n">
+        <v>0.00669</v>
+      </c>
+      <c r="AD447" s="3" t="n">
+        <v>0.007530120481927665</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -39933,6 +42621,12 @@
       <c r="AB448" s="2" t="n">
         <v>-0.0182160182160183</v>
       </c>
+      <c r="AC448" s="1" t="n">
+        <v>0.09906</v>
+      </c>
+      <c r="AD448" s="2" t="n">
+        <v>-0.001109206413229797</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -40021,6 +42715,12 @@
       <c r="AB449" s="3" t="n">
         <v>0.001795332136445221</v>
       </c>
+      <c r="AC449" s="1" t="n">
+        <v>0.001681</v>
+      </c>
+      <c r="AD449" s="3" t="n">
+        <v>0.004181600955794541</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -40109,6 +42809,12 @@
       <c r="AB450" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC450" s="1" t="n">
+        <v>0.0002074</v>
+      </c>
+      <c r="AD450" s="3" t="n">
+        <v>0.00533204071740184</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -40197,6 +42903,12 @@
       <c r="AB451" s="2" t="n">
         <v>-0.003038359285985503</v>
       </c>
+      <c r="AC451" s="1" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AD451" s="3" t="n">
+        <v>0.005714285714285661</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -40285,6 +42997,12 @@
       <c r="AB452" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC452" s="1" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AD452" s="3" t="n">
+        <v>0.005212211466865273</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -40373,6 +43091,12 @@
       <c r="AB453" s="2" t="n">
         <v>-0.0005730659025788104</v>
       </c>
+      <c r="AC453" s="1" t="n">
+        <v>0.0001748</v>
+      </c>
+      <c r="AD453" s="3" t="n">
+        <v>0.002293577981651277</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -40461,6 +43185,12 @@
       <c r="AB454" s="3" t="n">
         <v>0.002908562079621768</v>
       </c>
+      <c r="AC454" s="1" t="n">
+        <v>0.11028</v>
+      </c>
+      <c r="AD454" s="2" t="n">
+        <v>-0.000543773790103232</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -40549,6 +43279,12 @@
       <c r="AB455" s="2" t="n">
         <v>-0.0005974905397330551</v>
       </c>
+      <c r="AC455" s="1" t="n">
+        <v>0.5033</v>
+      </c>
+      <c r="AD455" s="3" t="n">
+        <v>0.002989238740533969</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -40637,6 +43373,12 @@
       <c r="AB456" s="2" t="n">
         <v>-0.0008779631255485172</v>
       </c>
+      <c r="AC456" s="1" t="n">
+        <v>0.015979</v>
+      </c>
+      <c r="AD456" s="3" t="n">
+        <v>0.002950037660055136</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -40725,6 +43467,12 @@
       <c r="AB457" s="2" t="n">
         <v>-0.002239808869643162</v>
       </c>
+      <c r="AC457" s="1" t="n">
+        <v>0.006692</v>
+      </c>
+      <c r="AD457" s="3" t="n">
+        <v>0.001496557916791449</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -40813,6 +43561,12 @@
       <c r="AB458" s="2" t="n">
         <v>-0.001454696591853769</v>
       </c>
+      <c r="AC458" s="1" t="n">
+        <v>0.4825</v>
+      </c>
+      <c r="AD458" s="3" t="n">
+        <v>0.004162330905306976</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -40901,6 +43655,12 @@
       <c r="AB459" s="2" t="n">
         <v>-0.0006300204756654062</v>
       </c>
+      <c r="AC459" s="1" t="n">
+        <v>0.006371</v>
+      </c>
+      <c r="AD459" s="3" t="n">
+        <v>0.004097714736012606</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -40989,6 +43749,12 @@
       <c r="AB460" s="3" t="n">
         <v>0.002911208151382907</v>
       </c>
+      <c r="AC460" s="1" t="n">
+        <v>0.1385</v>
+      </c>
+      <c r="AD460" s="3" t="n">
+        <v>0.005079825834542861</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -41077,6 +43843,12 @@
       <c r="AB461" s="2" t="n">
         <v>-0.005193370165745836</v>
       </c>
+      <c r="AC461" s="1" t="n">
+        <v>0.08981</v>
+      </c>
+      <c r="AD461" s="2" t="n">
+        <v>-0.002443629901144041</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -41165,6 +43937,12 @@
       <c r="AB462" s="2" t="n">
         <v>-0.003294531078409934</v>
       </c>
+      <c r="AC462" s="1" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="AD462" s="2" t="n">
+        <v>-0.001762891141471942</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -41253,6 +44031,12 @@
       <c r="AB463" s="3" t="n">
         <v>0.001434720229555303</v>
       </c>
+      <c r="AC463" s="1" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="AD463" s="3" t="n">
+        <v>0.001432664756446933</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -41341,6 +44125,12 @@
       <c r="AB464" s="2" t="n">
         <v>-0.0007633587786260396</v>
       </c>
+      <c r="AC464" s="1" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AD464" s="3" t="n">
+        <v>0.002291825821237673</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -41429,6 +44219,12 @@
       <c r="AB465" s="2" t="n">
         <v>-0.0003589375448671535</v>
       </c>
+      <c r="AC465" s="1" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="AD465" s="3" t="n">
+        <v>0.002513464991023262</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -41517,6 +44313,12 @@
       <c r="AB466" s="2" t="n">
         <v>-0.0007052186177714315</v>
       </c>
+      <c r="AC466" s="1" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="AD466" s="3" t="n">
+        <v>0.005645730416372623</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -41605,6 +44407,12 @@
       <c r="AB467" s="3" t="n">
         <v>0.003138075313807403</v>
       </c>
+      <c r="AC467" s="1" t="n">
+        <v>0.01928</v>
+      </c>
+      <c r="AD467" s="3" t="n">
+        <v>0.005213764337851898</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -41693,6 +44501,12 @@
       <c r="AB468" s="3" t="n">
         <v>0.01085883514313926</v>
       </c>
+      <c r="AC468" s="1" t="n">
+        <v>0.01028</v>
+      </c>
+      <c r="AD468" s="3" t="n">
+        <v>0.00390624999999984</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -41781,6 +44595,12 @@
       <c r="AB469" s="2" t="n">
         <v>-0.0002515723270441371</v>
       </c>
+      <c r="AC469" s="1" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="AD469" s="3" t="n">
+        <v>0.003774534474081534</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -41869,6 +44689,12 @@
       <c r="AB470" s="2" t="n">
         <v>-0.001136363636363637</v>
       </c>
+      <c r="AC470" s="1" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="AD470" s="3" t="n">
+        <v>0.003412969283276454</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -41957,6 +44783,12 @@
       <c r="AB471" s="2" t="n">
         <v>-0.002793296089385443</v>
       </c>
+      <c r="AC471" s="1" t="n">
+        <v>3.245</v>
+      </c>
+      <c r="AD471" s="3" t="n">
+        <v>0.009959539371304086</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -42045,6 +44877,12 @@
       <c r="AB472" s="3" t="n">
         <v>0.003808616995953354</v>
       </c>
+      <c r="AC472" s="1" t="n">
+        <v>0.04231</v>
+      </c>
+      <c r="AD472" s="3" t="n">
+        <v>0.00331989566042213</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -42133,6 +44971,12 @@
       <c r="AB473" s="3" t="n">
         <v>0.00240963855421678</v>
       </c>
+      <c r="AC473" s="1" t="n">
+        <v>1.258</v>
+      </c>
+      <c r="AD473" s="3" t="n">
+        <v>0.008012820512820521</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -42221,6 +45065,12 @@
       <c r="AB474" s="3" t="n">
         <v>0.001639920346726031</v>
       </c>
+      <c r="AC474" s="1" t="n">
+        <v>0.008569</v>
+      </c>
+      <c r="AD474" s="3" t="n">
+        <v>0.00210501695708112</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -42309,6 +45159,12 @@
       <c r="AB475" s="2" t="n">
         <v>-0.005264417324718784</v>
       </c>
+      <c r="AC475" s="1" t="n">
+        <v>0.04183</v>
+      </c>
+      <c r="AD475" s="3" t="n">
+        <v>0.006254510464277035</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -42397,6 +45253,12 @@
       <c r="AB476" s="3" t="n">
         <v>0.000634840020314987</v>
       </c>
+      <c r="AC476" s="1" t="n">
+        <v>0.07935</v>
+      </c>
+      <c r="AD476" s="3" t="n">
+        <v>0.006851922344880076</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -42485,6 +45347,12 @@
       <c r="AB477" s="2" t="n">
         <v>-0.00175824175824189</v>
       </c>
+      <c r="AC477" s="1" t="n">
+        <v>0.13626</v>
+      </c>
+      <c r="AD477" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -42573,6 +45441,12 @@
       <c r="AB478" s="2" t="n">
         <v>-0.001266357112705732</v>
       </c>
+      <c r="AC478" s="1" t="n">
+        <v>0.04744</v>
+      </c>
+      <c r="AD478" s="3" t="n">
+        <v>0.002535925612848733</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -42661,6 +45535,12 @@
       <c r="AB479" s="3" t="n">
         <v>0.000562429696287876</v>
       </c>
+      <c r="AC479" s="1" t="n">
+        <v>0.005347</v>
+      </c>
+      <c r="AD479" s="3" t="n">
+        <v>0.00187371182312169</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -42749,6 +45629,12 @@
       <c r="AB480" s="3" t="n">
         <v>0.001426533523537844</v>
       </c>
+      <c r="AC480" s="1" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="AD480" s="3" t="n">
+        <v>0.003205128205128248</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -42837,6 +45723,12 @@
       <c r="AB481" s="2" t="n">
         <v>-0.001715945089757012</v>
       </c>
+      <c r="AC481" s="1" t="n">
+        <v>0.07597</v>
+      </c>
+      <c r="AD481" s="3" t="n">
+        <v>0.0044955705407906</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -42925,6 +45817,12 @@
       <c r="AB482" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC482" s="1" t="n">
+        <v>0.01491</v>
+      </c>
+      <c r="AD482" s="3" t="n">
+        <v>0.002689979825151319</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -43013,6 +45911,12 @@
       <c r="AB483" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC483" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="AD483" s="3" t="n">
+        <v>0.003999999999999976</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -43101,6 +46005,12 @@
       <c r="AB484" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC484" s="1" t="n">
+        <v>0.02163</v>
+      </c>
+      <c r="AD484" s="3" t="n">
+        <v>0.004178272980501383</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -43189,6 +46099,12 @@
       <c r="AB485" s="2" t="n">
         <v>-0.00349903474903469</v>
       </c>
+      <c r="AC485" s="1" t="n">
+        <v>0.008366999999999999</v>
+      </c>
+      <c r="AD485" s="3" t="n">
+        <v>0.01307664366146007</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -43277,6 +46193,12 @@
       <c r="AB486" s="2" t="n">
         <v>-0.001207081545064422</v>
       </c>
+      <c r="AC486" s="1" t="n">
+        <v>0.007498</v>
+      </c>
+      <c r="AD486" s="3" t="n">
+        <v>0.0068483953269774</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -43365,6 +46287,12 @@
       <c r="AB487" s="2" t="n">
         <v>-0.002700270027002777</v>
       </c>
+      <c r="AC487" s="1" t="n">
+        <v>0.1159</v>
+      </c>
+      <c r="AD487" s="3" t="n">
+        <v>0.04602888086642606</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -43453,6 +46381,12 @@
       <c r="AB488" s="2" t="n">
         <v>-0.004098360655737874</v>
       </c>
+      <c r="AC488" s="1" t="n">
+        <v>0.00923</v>
+      </c>
+      <c r="AD488" s="2" t="n">
+        <v>-0.000433181719731297</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -43541,6 +46475,12 @@
       <c r="AB489" s="3" t="n">
         <v>0.001817237798546226</v>
       </c>
+      <c r="AC489" s="1" t="n">
+        <v>0.03893</v>
+      </c>
+      <c r="AD489" s="3" t="n">
+        <v>0.00881057268722467</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -43629,6 +46569,12 @@
       <c r="AB490" s="2" t="n">
         <v>-0.006662111376836376</v>
       </c>
+      <c r="AC490" s="1" t="n">
+        <v>0.05792</v>
+      </c>
+      <c r="AD490" s="2" t="n">
+        <v>-0.00395528804815135</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -43717,6 +46663,12 @@
       <c r="AB491" s="3" t="n">
         <v>0.006217616580310915</v>
       </c>
+      <c r="AC491" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="AD491" s="3" t="n">
+        <v>0.003089598352214157</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -43805,6 +46757,12 @@
       <c r="AB492" s="3" t="n">
         <v>0.001508295625942686</v>
       </c>
+      <c r="AC492" s="1" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="AD492" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -43893,6 +46851,12 @@
       <c r="AB493" s="3" t="n">
         <v>0.00113636363636359</v>
       </c>
+      <c r="AC493" s="1" t="n">
+        <v>0.03528</v>
+      </c>
+      <c r="AD493" s="3" t="n">
+        <v>0.001135073779795641</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -43981,6 +46945,12 @@
       <c r="AB494" s="2" t="n">
         <v>-0.000588235294117623</v>
       </c>
+      <c r="AC494" s="1" t="n">
+        <v>0.01705</v>
+      </c>
+      <c r="AD494" s="3" t="n">
+        <v>0.003531489111241763</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -44069,6 +47039,12 @@
       <c r="AB495" s="2" t="n">
         <v>-0.0025439898240406</v>
       </c>
+      <c r="AC495" s="1" t="n">
+        <v>0.04727</v>
+      </c>
+      <c r="AD495" s="3" t="n">
+        <v>0.004675876726886248</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -44157,6 +47133,12 @@
       <c r="AB496" s="3" t="n">
         <v>0.001864898466639035</v>
       </c>
+      <c r="AC496" s="1" t="n">
+        <v>0.04847</v>
+      </c>
+      <c r="AD496" s="3" t="n">
+        <v>0.002481902792140684</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -44245,6 +47227,12 @@
       <c r="AB497" s="3" t="n">
         <v>0.0008079175924055417</v>
       </c>
+      <c r="AC497" s="1" t="n">
+        <v>0.04982</v>
+      </c>
+      <c r="AD497" s="3" t="n">
+        <v>0.005449041372351289</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -44333,6 +47321,12 @@
       <c r="AB498" s="2" t="n">
         <v>-0.001385521302390064</v>
       </c>
+      <c r="AC498" s="1" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="AD498" s="3" t="n">
+        <v>0.004509191814082634</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -44421,6 +47415,12 @@
       <c r="AB499" s="3" t="n">
         <v>0.004032258064516092</v>
       </c>
+      <c r="AC499" s="1" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="AD499" s="3" t="n">
+        <v>0.002555677254472559</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -44509,6 +47509,12 @@
       <c r="AB500" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC500" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="AD500" s="3" t="n">
+        <v>0.003759398496240611</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -44597,6 +47603,12 @@
       <c r="AB501" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC501" s="1" t="n">
+        <v>0.03583</v>
+      </c>
+      <c r="AD501" s="3" t="n">
+        <v>0.001957494407158854</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -44685,6 +47697,12 @@
       <c r="AB502" s="2" t="n">
         <v>-0.003128911138923744</v>
       </c>
+      <c r="AC502" s="1" t="n">
+        <v>0.03187</v>
+      </c>
+      <c r="AD502" s="3" t="n">
+        <v>0.0003138731952292236</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -44773,6 +47791,12 @@
       <c r="AB503" s="2" t="n">
         <v>-0.001937233630375856</v>
       </c>
+      <c r="AC503" s="1" t="n">
+        <v>0.007784</v>
+      </c>
+      <c r="AD503" s="3" t="n">
+        <v>0.007246376811594267</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -44861,6 +47885,12 @@
       <c r="AB504" s="2" t="n">
         <v>-0.006531678641410849</v>
       </c>
+      <c r="AC504" s="1" t="n">
+        <v>3.043</v>
+      </c>
+      <c r="AD504" s="3" t="n">
+        <v>0.000328731097961977</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -44949,6 +47979,12 @@
       <c r="AB505" s="3" t="n">
         <v>0.0002701607456435181</v>
       </c>
+      <c r="AC505" s="1" t="n">
+        <v>0.0007437</v>
+      </c>
+      <c r="AD505" s="3" t="n">
+        <v>0.004321404456448451</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -45037,6 +48073,12 @@
       <c r="AB506" s="2" t="n">
         <v>-0.003071672354948657</v>
       </c>
+      <c r="AC506" s="1" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AD506" s="2" t="n">
+        <v>-0.0003423485107841304</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -45125,6 +48167,12 @@
       <c r="AB507" s="2" t="n">
         <v>-0.001756234632947042</v>
       </c>
+      <c r="AC507" s="1" t="n">
+        <v>0.002869</v>
+      </c>
+      <c r="AD507" s="3" t="n">
+        <v>0.009500351864883926</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -45213,6 +48261,12 @@
       <c r="AB508" s="2" t="n">
         <v>-0.001741884402216928</v>
       </c>
+      <c r="AC508" s="1" t="n">
+        <v>0.06336</v>
+      </c>
+      <c r="AD508" s="3" t="n">
+        <v>0.005076142131979709</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -45301,6 +48355,12 @@
       <c r="AB509" s="3" t="n">
         <v>0.000448229493500822</v>
       </c>
+      <c r="AC509" s="1" t="n">
+        <v>2.242</v>
+      </c>
+      <c r="AD509" s="3" t="n">
+        <v>0.004480286738351159</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -45389,6 +48449,12 @@
       <c r="AB510" s="2" t="n">
         <v>-0.0001369487811557768</v>
       </c>
+      <c r="AC510" s="1" t="n">
+        <v>0.0007355</v>
+      </c>
+      <c r="AD510" s="3" t="n">
+        <v>0.007396247089439834</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -45477,6 +48543,12 @@
       <c r="AB511" s="2" t="n">
         <v>-0.002173913043478424</v>
       </c>
+      <c r="AC511" s="1" t="n">
+        <v>0.2763</v>
+      </c>
+      <c r="AD511" s="3" t="n">
+        <v>0.003267973856209194</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -45565,6 +48637,12 @@
       <c r="AB512" s="2" t="n">
         <v>-0.006832298136645904</v>
       </c>
+      <c r="AC512" s="1" t="n">
+        <v>0.0004828</v>
+      </c>
+      <c r="AD512" s="3" t="n">
+        <v>0.006462372316030897</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -45653,6 +48731,12 @@
       <c r="AB513" s="3" t="n">
         <v>0.0007213706041478516</v>
       </c>
+      <c r="AC513" s="1" t="n">
+        <v>0.05544</v>
+      </c>
+      <c r="AD513" s="2" t="n">
+        <v>-0.0009010632546403765</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -45741,6 +48825,12 @@
       <c r="AB514" s="2" t="n">
         <v>-0.003286230693394657</v>
       </c>
+      <c r="AC514" s="1" t="n">
+        <v>0.03039</v>
+      </c>
+      <c r="AD514" s="3" t="n">
+        <v>0.001978239366963436</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -45829,6 +48919,12 @@
       <c r="AB515" s="2" t="n">
         <v>-0.0008787346221440386</v>
       </c>
+      <c r="AC515" s="1" t="n">
+        <v>0.00114</v>
+      </c>
+      <c r="AD515" s="3" t="n">
+        <v>0.002638522427440602</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -45917,6 +49013,12 @@
       <c r="AB516" s="2" t="n">
         <v>-0.0007570022710067822</v>
       </c>
+      <c r="AC516" s="1" t="n">
+        <v>0.006646</v>
+      </c>
+      <c r="AD516" s="3" t="n">
+        <v>0.006969696969696975</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -46005,6 +49107,12 @@
       <c r="AB517" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC517" s="1" t="n">
+        <v>0.03988</v>
+      </c>
+      <c r="AD517" s="3" t="n">
+        <v>0.003522898842476126</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -46093,6 +49201,12 @@
       <c r="AB518" s="3" t="n">
         <v>0.001945525291828714</v>
       </c>
+      <c r="AC518" s="1" t="n">
+        <v>0.1036</v>
+      </c>
+      <c r="AD518" s="3" t="n">
+        <v>0.005825242718446634</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -46181,6 +49295,12 @@
       <c r="AB519" s="2" t="n">
         <v>-0.003428571428571487</v>
       </c>
+      <c r="AC519" s="1" t="n">
+        <v>0.00877</v>
+      </c>
+      <c r="AD519" s="3" t="n">
+        <v>0.005733944954128405</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -46269,6 +49389,12 @@
       <c r="AB520" s="3" t="n">
         <v>0.0006273525721456509</v>
       </c>
+      <c r="AC520" s="1" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="AD520" s="3" t="n">
+        <v>0.005642633228840026</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -46357,6 +49483,12 @@
       <c r="AB521" s="2" t="n">
         <v>-0.002234636871508289</v>
       </c>
+      <c r="AC521" s="1" t="n">
+        <v>0.01789</v>
+      </c>
+      <c r="AD521" s="3" t="n">
+        <v>0.001679731243001051</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -46445,6 +49577,12 @@
       <c r="AB522" s="3" t="n">
         <v>0.001224739742804604</v>
       </c>
+      <c r="AC522" s="1" t="n">
+        <v>0.01646</v>
+      </c>
+      <c r="AD522" s="3" t="n">
+        <v>0.006727828746177308</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -46533,6 +49671,12 @@
       <c r="AB523" s="3" t="n">
         <v>0.0002397506593143449</v>
       </c>
+      <c r="AC523" s="1" t="n">
+        <v>0.004165</v>
+      </c>
+      <c r="AD523" s="2" t="n">
+        <v>-0.001677852348993303</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -46621,6 +49765,12 @@
       <c r="AB524" s="2" t="n">
         <v>-0.0007022471910112074</v>
       </c>
+      <c r="AC524" s="1" t="n">
+        <v>0.01428</v>
+      </c>
+      <c r="AD524" s="3" t="n">
+        <v>0.003513703443429354</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -46709,6 +49859,12 @@
       <c r="AB525" s="2" t="n">
         <v>-0.001622718052738271</v>
       </c>
+      <c r="AC525" s="1" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="AD525" s="3" t="n">
+        <v>0.003657049979683048</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -46797,6 +49953,12 @@
       <c r="AB526" s="3" t="n">
         <v>0.001669449081802937</v>
       </c>
+      <c r="AC526" s="1" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="AD526" s="3" t="n">
+        <v>0.004166666666666671</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -46885,6 +50047,12 @@
       <c r="AB527" s="3" t="n">
         <v>0.0006960879855212932</v>
       </c>
+      <c r="AC527" s="1" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="AD527" s="3" t="n">
+        <v>0.001669449081802937</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -46973,6 +50141,12 @@
       <c r="AB528" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC528" s="1" t="n">
+        <v>0.04335</v>
+      </c>
+      <c r="AD528" s="3" t="n">
+        <v>0.003704561241028026</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -47061,6 +50235,12 @@
       <c r="AB529" s="3" t="n">
         <v>0.0006344171292624643</v>
       </c>
+      <c r="AC529" s="1" t="n">
+        <v>0.06315999999999999</v>
+      </c>
+      <c r="AD529" s="3" t="n">
+        <v>0.001109526073862746</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -47149,6 +50329,12 @@
       <c r="AB530" s="3" t="n">
         <v>0.001993223041658453</v>
       </c>
+      <c r="AC530" s="1" t="n">
+        <v>0.005036</v>
+      </c>
+      <c r="AD530" s="3" t="n">
+        <v>0.001790332206087022</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -47237,6 +50423,12 @@
       <c r="AB531" s="3" t="n">
         <v>0.003095975232198016</v>
       </c>
+      <c r="AC531" s="1" t="n">
+        <v>0.1302</v>
+      </c>
+      <c r="AD531" s="3" t="n">
+        <v>0.004629629629629762</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -47325,6 +50517,12 @@
       <c r="AB532" s="3" t="n">
         <v>0.00037643515904397</v>
       </c>
+      <c r="AC532" s="1" t="n">
+        <v>0.05316</v>
+      </c>
+      <c r="AD532" s="3" t="n">
+        <v>0.0001881467544684125</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -47413,6 +50611,12 @@
       <c r="AB533" s="3" t="n">
         <v>0.0005369127516778072</v>
       </c>
+      <c r="AC533" s="1" t="n">
+        <v>0.003734</v>
+      </c>
+      <c r="AD533" s="3" t="n">
+        <v>0.001878186208746998</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -47501,6 +50705,12 @@
       <c r="AB534" s="2" t="n">
         <v>-0.0005830903790088439</v>
       </c>
+      <c r="AC534" s="1" t="n">
+        <v>0.1721</v>
+      </c>
+      <c r="AD534" s="3" t="n">
+        <v>0.004084014002333759</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -47589,6 +50799,12 @@
       <c r="AB535" s="3" t="n">
         <v>0.008928571428571494</v>
       </c>
+      <c r="AC535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="AD535" s="2" t="n">
+        <v>-0.00884955752212396</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -47677,6 +50893,12 @@
       <c r="AB536" s="2" t="n">
         <v>-0.0006787330316742246</v>
       </c>
+      <c r="AC536" s="1" t="n">
+        <v>0.0004412</v>
+      </c>
+      <c r="AD536" s="2" t="n">
+        <v>-0.001131990038487689</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -47765,6 +50987,12 @@
       <c r="AB537" s="2" t="n">
         <v>-0.002079002079002175</v>
       </c>
+      <c r="AC537" s="1" t="n">
+        <v>0.009679999999999999</v>
+      </c>
+      <c r="AD537" s="3" t="n">
+        <v>0.008333333333333356</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -47853,6 +51081,12 @@
       <c r="AB538" s="3" t="n">
         <v>0.000550256786500408</v>
       </c>
+      <c r="AC538" s="1" t="n">
+        <v>0.05455</v>
+      </c>
+      <c r="AD538" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -47941,6 +51175,12 @@
       <c r="AB539" s="2" t="n">
         <v>-0.0002943773918162761</v>
       </c>
+      <c r="AC539" s="1" t="n">
+        <v>0.6818</v>
+      </c>
+      <c r="AD539" s="3" t="n">
+        <v>0.003828032979976348</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -48029,6 +51269,12 @@
       <c r="AB540" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AC540" s="1" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="AD540" s="3" t="n">
+        <v>0.001986754966887382</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -48117,6 +51363,12 @@
       <c r="AB541" s="2" t="n">
         <v>-0.001533742331288281</v>
       </c>
+      <c r="AC541" s="1" t="n">
+        <v>0.01306</v>
+      </c>
+      <c r="AD541" s="3" t="n">
+        <v>0.003072196620583725</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -48205,6 +51457,12 @@
       <c r="AB542" s="3" t="n">
         <v>0.0007147962830592989</v>
       </c>
+      <c r="AC542" s="1" t="n">
+        <v>0.01388</v>
+      </c>
+      <c r="AD542" s="2" t="n">
+        <v>-0.008571428571428594</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -48292,6 +51550,12 @@
       </c>
       <c r="AB543" s="2" t="n">
         <v>-0.0001753770606805167</v>
+      </c>
+      <c r="AC543" s="1" t="n">
+        <v>0.05706</v>
+      </c>
+      <c r="AD543" s="3" t="n">
+        <v>0.0008770391159445963</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF543"/>
+  <dimension ref="A1:AH543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -458,6 +458,8 @@
     <col width="18" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="18" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -621,6 +623,16 @@
           <t>change_03:45</t>
         </is>
       </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>price_04:00</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>change_04:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -721,6 +733,12 @@
       <c r="AF2" s="3" t="n">
         <v>0.001496562182871347</v>
       </c>
+      <c r="AG2" s="1" t="n">
+        <v>70398.3</v>
+      </c>
+      <c r="AH2" s="3" t="n">
+        <v>0.001885696882409365</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -821,6 +839,12 @@
       <c r="AF3" s="3" t="n">
         <v>0.003285721912416332</v>
       </c>
+      <c r="AG3" s="1" t="n">
+        <v>2069.16</v>
+      </c>
+      <c r="AH3" s="3" t="n">
+        <v>0.0009481424148606988</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -921,6 +945,12 @@
       <c r="AF4" s="3" t="n">
         <v>0.003125361731681861</v>
       </c>
+      <c r="AG4" s="1" t="n">
+        <v>86.78</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>0.001384721901684798</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1021,6 +1051,12 @@
       <c r="AF5" s="3" t="n">
         <v>9.547450830621208e-05</v>
       </c>
+      <c r="AG5" s="1" t="n">
+        <v>0.010498</v>
+      </c>
+      <c r="AH5" s="3" t="n">
+        <v>0.002195704057279279</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1121,6 +1157,12 @@
       <c r="AF6" s="3" t="n">
         <v>0.0009440813362382562</v>
       </c>
+      <c r="AG6" s="1" t="n">
+        <v>1.3782</v>
+      </c>
+      <c r="AH6" s="2" t="n">
+        <v>-7.255314517883551e-05</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1221,6 +1263,12 @@
       <c r="AF7" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG7" s="1" t="n">
+        <v>0.0944</v>
+      </c>
+      <c r="AH7" s="3" t="n">
+        <v>0.0006359974560102236</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1321,6 +1369,12 @@
       <c r="AF8" s="2" t="n">
         <v>-0.001316001504001705</v>
       </c>
+      <c r="AG8" s="1" t="n">
+        <v>37.082</v>
+      </c>
+      <c r="AH8" s="2" t="n">
+        <v>-0.002769934113217736</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1421,6 +1475,12 @@
       <c r="AF9" s="3" t="n">
         <v>0.00300300300300295</v>
       </c>
+      <c r="AG9" s="1" t="n">
+        <v>0.04998</v>
+      </c>
+      <c r="AH9" s="2" t="n">
+        <v>-0.002395209580838365</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1521,6 +1581,12 @@
       <c r="AF10" s="3" t="n">
         <v>0.005687357816054622</v>
       </c>
+      <c r="AG10" s="1" t="n">
+        <v>18.462</v>
+      </c>
+      <c r="AH10" s="2" t="n">
+        <v>-0.005655194700274704</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1621,6 +1687,12 @@
       <c r="AF11" s="3" t="n">
         <v>0.0002151496058151655</v>
       </c>
+      <c r="AG11" s="1" t="n">
+        <v>651.36</v>
+      </c>
+      <c r="AH11" s="3" t="n">
+        <v>0.0007835906890988567</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1721,6 +1793,12 @@
       <c r="AF12" s="3" t="n">
         <v>0.01159881737548327</v>
       </c>
+      <c r="AG12" s="1" t="n">
+        <v>0.8915</v>
+      </c>
+      <c r="AH12" s="3" t="n">
+        <v>0.002135791366906489</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1821,6 +1899,12 @@
       <c r="AF13" s="3" t="n">
         <v>0.0009573958831976478</v>
       </c>
+      <c r="AG13" s="1" t="n">
+        <v>208.85</v>
+      </c>
+      <c r="AH13" s="2" t="n">
+        <v>-0.001195600191296031</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1921,6 +2005,12 @@
       <c r="AF14" s="2" t="n">
         <v>-0.000448457306864446</v>
       </c>
+      <c r="AG14" s="1" t="n">
+        <v>0.0033524</v>
+      </c>
+      <c r="AH14" s="3" t="n">
+        <v>0.002721861633715242</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2021,6 +2111,12 @@
       <c r="AF15" s="2" t="n">
         <v>-0.0001230201445486221</v>
       </c>
+      <c r="AG15" s="1" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="AH15" s="2" t="n">
+        <v>-0.008673987265848448</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2121,6 +2217,12 @@
       <c r="AF16" s="2" t="n">
         <v>-0.00142798857609146</v>
       </c>
+      <c r="AG16" s="1" t="n">
+        <v>0.9791</v>
+      </c>
+      <c r="AH16" s="3" t="n">
+        <v>0.0001021450459652594</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2221,6 +2323,12 @@
       <c r="AF17" s="2" t="n">
         <v>-0.01111111111111104</v>
       </c>
+      <c r="AG17" s="1" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="AH17" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2321,6 +2429,12 @@
       <c r="AF18" s="2" t="n">
         <v>-0.0008896380577796401</v>
       </c>
+      <c r="AG18" s="1" t="n">
+        <v>213.49</v>
+      </c>
+      <c r="AH18" s="3" t="n">
+        <v>0.0005155122316993797</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2421,6 +2535,12 @@
       <c r="AF19" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG19" s="1" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AH19" s="3" t="n">
+        <v>0.002668699961875844</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2521,6 +2641,12 @@
       <c r="AF20" s="2" t="n">
         <v>-0.0002361414487278193</v>
       </c>
+      <c r="AG20" s="1" t="n">
+        <v>0.016942</v>
+      </c>
+      <c r="AH20" s="3" t="n">
+        <v>0.0004133451431945711</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2621,6 +2747,12 @@
       <c r="AF21" s="2" t="n">
         <v>-0.001041341247526792</v>
       </c>
+      <c r="AG21" s="1" t="n">
+        <v>9.601000000000001</v>
+      </c>
+      <c r="AH21" s="3" t="n">
+        <v>0.0008339414156156463</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2721,6 +2853,12 @@
       <c r="AF22" s="3" t="n">
         <v>0.005379557680812816</v>
       </c>
+      <c r="AG22" s="1" t="n">
+        <v>0.1682</v>
+      </c>
+      <c r="AH22" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2821,6 +2959,12 @@
       <c r="AF23" s="2" t="n">
         <v>-0.002445198780277205</v>
       </c>
+      <c r="AG23" s="1" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AH23" s="2" t="n">
+        <v>-0.0038930703348041</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2921,6 +3065,12 @@
       <c r="AF24" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG24" s="1" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AH24" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3021,6 +3171,12 @@
       <c r="AF25" s="2" t="n">
         <v>-0.0008862301982939093</v>
       </c>
+      <c r="AG25" s="1" t="n">
+        <v>9.031000000000001</v>
+      </c>
+      <c r="AH25" s="3" t="n">
+        <v>0.00133052444838679</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3121,6 +3277,12 @@
       <c r="AF26" s="3" t="n">
         <v>0.0007434944237919048</v>
       </c>
+      <c r="AG26" s="1" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>-0.005200594353640503</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3221,6 +3383,12 @@
       <c r="AF27" s="2" t="n">
         <v>-0.0003569635348021046</v>
       </c>
+      <c r="AG27" s="1" t="n">
+        <v>5091.47</v>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>-0.001033994278695701</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3321,6 +3489,12 @@
       <c r="AF28" s="3" t="n">
         <v>0.001936912008854395</v>
       </c>
+      <c r="AG28" s="1" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <v>-0.005523336095001386</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3421,6 +3595,12 @@
       <c r="AF29" s="3" t="n">
         <v>0.001901863826549979</v>
       </c>
+      <c r="AG29" s="1" t="n">
+        <v>2.632</v>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <v>-0.0007593014426726575</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3521,6 +3701,12 @@
       <c r="AF30" s="3" t="n">
         <v>0.003138786684569224</v>
       </c>
+      <c r="AG30" s="1" t="n">
+        <v>0.57565</v>
+      </c>
+      <c r="AH30" s="3" t="n">
+        <v>0.0006605593895041407</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3621,6 +3807,12 @@
       <c r="AF31" s="3" t="n">
         <v>0.003833253473886054</v>
       </c>
+      <c r="AG31" s="1" t="n">
+        <v>0.002093</v>
+      </c>
+      <c r="AH31" s="2" t="n">
+        <v>-0.0009546539379476207</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3721,6 +3913,12 @@
       <c r="AF32" s="2" t="n">
         <v>-0.003032370555681907</v>
       </c>
+      <c r="AG32" s="1" t="n">
+        <v>1.3074</v>
+      </c>
+      <c r="AH32" s="2" t="n">
+        <v>-0.005855068055661198</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3821,6 +4019,12 @@
       <c r="AF33" s="2" t="n">
         <v>-0.008700870087008575</v>
       </c>
+      <c r="AG33" s="1" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="AH33" s="3" t="n">
+        <v>0.007566585956416303</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3921,6 +4125,12 @@
       <c r="AF34" s="2" t="n">
         <v>-0.001324503311258279</v>
       </c>
+      <c r="AG34" s="1" t="n">
+        <v>1.506</v>
+      </c>
+      <c r="AH34" s="2" t="n">
+        <v>-0.001326259946949603</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4021,6 +4231,12 @@
       <c r="AF35" s="2" t="n">
         <v>-0.0002191972994891955</v>
       </c>
+      <c r="AG35" s="1" t="n">
+        <v>456.02</v>
+      </c>
+      <c r="AH35" s="2" t="n">
+        <v>-0.0001973208217316696</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4121,6 +4337,12 @@
       <c r="AF36" s="2" t="n">
         <v>-0.001252609603340241</v>
       </c>
+      <c r="AG36" s="1" t="n">
+        <v>0.04778</v>
+      </c>
+      <c r="AH36" s="2" t="n">
+        <v>-0.001254180602006638</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4221,6 +4443,12 @@
       <c r="AF37" s="3" t="n">
         <v>0.001424907381020235</v>
       </c>
+      <c r="AG37" s="1" t="n">
+        <v>0.7020999999999999</v>
+      </c>
+      <c r="AH37" s="2" t="n">
+        <v>-0.0009960159362550284</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4321,6 +4549,12 @@
       <c r="AF38" s="2" t="n">
         <v>-0.001883239171374819</v>
       </c>
+      <c r="AG38" s="1" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="AH38" s="3" t="n">
+        <v>0.0009433962264151213</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4421,6 +4655,12 @@
       <c r="AF39" s="3" t="n">
         <v>0.002520252025202531</v>
       </c>
+      <c r="AG39" s="1" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="AH39" s="3" t="n">
+        <v>0.001975219967678209</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4521,6 +4761,12 @@
       <c r="AF40" s="2" t="n">
         <v>-0.005970149253731288</v>
       </c>
+      <c r="AG40" s="1" t="n">
+        <v>0.03649</v>
+      </c>
+      <c r="AH40" s="2" t="n">
+        <v>-0.003822003822003855</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4621,6 +4867,12 @@
       <c r="AF41" s="2" t="n">
         <v>-0.001456664238892876</v>
       </c>
+      <c r="AG41" s="1" t="n">
+        <v>0.05479</v>
+      </c>
+      <c r="AH41" s="2" t="n">
+        <v>-0.0009117432530999532</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4721,6 +4973,12 @@
       <c r="AF42" s="3" t="n">
         <v>0.000184229918938799</v>
       </c>
+      <c r="AG42" s="1" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="AH42" s="2" t="n">
+        <v>-0.0003683919690550013</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4821,6 +5079,12 @@
       <c r="AF43" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG43" s="1" t="n">
+        <v>0.1328</v>
+      </c>
+      <c r="AH43" s="2" t="n">
+        <v>-0.009694258016405635</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4921,6 +5185,12 @@
       <c r="AF44" s="3" t="n">
         <v>0.003726287262872535</v>
       </c>
+      <c r="AG44" s="1" t="n">
+        <v>0.005933</v>
+      </c>
+      <c r="AH44" s="3" t="n">
+        <v>0.001181235234559578</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5021,6 +5291,12 @@
       <c r="AF45" s="3" t="n">
         <v>0.002717664821338766</v>
       </c>
+      <c r="AG45" s="1" t="n">
+        <v>0.10021</v>
+      </c>
+      <c r="AH45" s="3" t="n">
+        <v>0.005922505520979656</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5121,6 +5397,12 @@
       <c r="AF46" s="3" t="n">
         <v>0.01685393258426971</v>
       </c>
+      <c r="AG46" s="1" t="n">
+        <v>2.926</v>
+      </c>
+      <c r="AH46" s="2" t="n">
+        <v>-0.04907377315567105</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5221,6 +5503,12 @@
       <c r="AF47" s="2" t="n">
         <v>-3.463563313921616e-05</v>
       </c>
+      <c r="AG47" s="1" t="n">
+        <v>0.28864</v>
+      </c>
+      <c r="AH47" s="2" t="n">
+        <v>-0.0002424578296561064</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5321,6 +5609,12 @@
       <c r="AF48" s="2" t="n">
         <v>-0.001865671641791098</v>
       </c>
+      <c r="AG48" s="1" t="n">
+        <v>0.1065</v>
+      </c>
+      <c r="AH48" s="2" t="n">
+        <v>-0.004672897196261686</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5421,6 +5715,12 @@
       <c r="AF49" s="3" t="n">
         <v>0.00396987803879839</v>
       </c>
+      <c r="AG49" s="1" t="n">
+        <v>0.24513</v>
+      </c>
+      <c r="AH49" s="2" t="n">
+        <v>-0.0007337654396478476</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5521,6 +5821,12 @@
       <c r="AF50" s="3" t="n">
         <v>0.009859450388084858</v>
       </c>
+      <c r="AG50" s="1" t="n">
+        <v>0.04825</v>
+      </c>
+      <c r="AH50" s="3" t="n">
+        <v>0.002285002077274595</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5621,6 +5927,12 @@
       <c r="AF51" s="2" t="n">
         <v>-0.001023279611153749</v>
       </c>
+      <c r="AG51" s="1" t="n">
+        <v>3.909</v>
+      </c>
+      <c r="AH51" s="3" t="n">
+        <v>0.001024327784891166</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5721,6 +6033,12 @@
       <c r="AF52" s="2" t="n">
         <v>-0.008733624454148565</v>
       </c>
+      <c r="AG52" s="1" t="n">
+        <v>0.000229</v>
+      </c>
+      <c r="AH52" s="3" t="n">
+        <v>0.008810572687224764</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5821,6 +6139,12 @@
       <c r="AF53" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG53" s="1" t="n">
+        <v>0.1695</v>
+      </c>
+      <c r="AH53" s="3" t="n">
+        <v>0.0005903187721370528</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5921,6 +6245,12 @@
       <c r="AF54" s="3" t="n">
         <v>0.003805899143672702</v>
       </c>
+      <c r="AG54" s="1" t="n">
+        <v>0.04198</v>
+      </c>
+      <c r="AH54" s="2" t="n">
+        <v>-0.005213270142180046</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6021,6 +6351,12 @@
       <c r="AF55" s="3" t="n">
         <v>0.004995086799868977</v>
       </c>
+      <c r="AG55" s="1" t="n">
+        <v>0.12226</v>
+      </c>
+      <c r="AH55" s="2" t="n">
+        <v>-0.003829544528640203</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6121,6 +6457,12 @@
       <c r="AF56" s="2" t="n">
         <v>-0.001898734177215156</v>
       </c>
+      <c r="AG56" s="1" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AH56" s="2" t="n">
+        <v>-0.0009511731135067294</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6221,6 +6563,12 @@
       <c r="AF57" s="3" t="n">
         <v>0.0008673026886382994</v>
       </c>
+      <c r="AG57" s="1" t="n">
+        <v>0.01148</v>
+      </c>
+      <c r="AH57" s="2" t="n">
+        <v>-0.005199306759098726</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6321,6 +6669,12 @@
       <c r="AF58" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG58" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="AH58" s="3" t="n">
+        <v>0.0009980039920159966</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6421,6 +6775,12 @@
       <c r="AF59" s="2" t="n">
         <v>-0.002994011976047912</v>
       </c>
+      <c r="AG59" s="1" t="n">
+        <v>0.00334</v>
+      </c>
+      <c r="AH59" s="3" t="n">
+        <v>0.003003003003003011</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6521,6 +6881,12 @@
       <c r="AF60" s="2" t="n">
         <v>-0.001280409731113993</v>
       </c>
+      <c r="AG60" s="1" t="n">
+        <v>0.1558</v>
+      </c>
+      <c r="AH60" s="2" t="n">
+        <v>-0.001282051282051319</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6621,6 +6987,12 @@
       <c r="AF61" s="2" t="n">
         <v>-0.000500531815053474</v>
       </c>
+      <c r="AG61" s="1" t="n">
+        <v>0.15995</v>
+      </c>
+      <c r="AH61" s="3" t="n">
+        <v>0.001251956181533682</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6721,6 +7093,12 @@
       <c r="AF62" s="3" t="n">
         <v>0.002107925801011728</v>
       </c>
+      <c r="AG62" s="1" t="n">
+        <v>0.7127</v>
+      </c>
+      <c r="AH62" s="2" t="n">
+        <v>-0.0005609311457018034</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6821,6 +7199,12 @@
       <c r="AF63" s="2" t="n">
         <v>-0.007867562694640231</v>
       </c>
+      <c r="AG63" s="1" t="n">
+        <v>6.061</v>
+      </c>
+      <c r="AH63" s="3" t="n">
+        <v>0.001321658681645466</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6921,6 +7305,12 @@
       <c r="AF64" s="2" t="n">
         <v>-0.001800055386319578</v>
       </c>
+      <c r="AG64" s="1" t="n">
+        <v>0.007225</v>
+      </c>
+      <c r="AH64" s="3" t="n">
+        <v>0.002219447912331741</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7021,6 +7411,12 @@
       <c r="AF65" s="3" t="n">
         <v>0.005307524196066079</v>
       </c>
+      <c r="AG65" s="1" t="n">
+        <v>0.03259</v>
+      </c>
+      <c r="AH65" s="3" t="n">
+        <v>0.01211180124223607</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7121,6 +7517,12 @@
       <c r="AF66" s="2" t="n">
         <v>-0.004255319148936056</v>
       </c>
+      <c r="AG66" s="1" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AH66" s="3" t="n">
+        <v>0.004273504273504159</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7221,6 +7623,12 @@
       <c r="AF67" s="2" t="n">
         <v>-0.00369458128078818</v>
       </c>
+      <c r="AG67" s="1" t="n">
+        <v>1.618</v>
+      </c>
+      <c r="AH67" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7321,6 +7729,12 @@
       <c r="AF68" s="3" t="n">
         <v>0.001722610493158695</v>
       </c>
+      <c r="AG68" s="1" t="n">
+        <v>2.0346</v>
+      </c>
+      <c r="AH68" s="2" t="n">
+        <v>-0.0003439296418216975</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7421,6 +7835,12 @@
       <c r="AF69" s="3" t="n">
         <v>0.002906479740126577</v>
       </c>
+      <c r="AG69" s="1" t="n">
+        <v>0.5858</v>
+      </c>
+      <c r="AH69" s="2" t="n">
+        <v>-0.00136379133992503</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7521,6 +7941,12 @@
       <c r="AF70" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG70" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="AH70" s="2" t="n">
+        <v>-0.009708737864077679</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7621,6 +8047,12 @@
       <c r="AF71" s="2" t="n">
         <v>-0.001860974274767295</v>
       </c>
+      <c r="AG71" s="1" t="n">
+        <v>0.9109</v>
+      </c>
+      <c r="AH71" s="2" t="n">
+        <v>-0.0009870585654748979</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7721,6 +8153,12 @@
       <c r="AF72" s="3" t="n">
         <v>0.002135738016136716</v>
       </c>
+      <c r="AG72" s="1" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="AH72" s="3" t="n">
+        <v>0.0009471939379588241</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7821,6 +8259,12 @@
       <c r="AF73" s="2" t="n">
         <v>-0.001165871754107037</v>
       </c>
+      <c r="AG73" s="1" t="n">
+        <v>0.09437</v>
+      </c>
+      <c r="AH73" s="3" t="n">
+        <v>0.001379456706281741</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7921,6 +8365,12 @@
       <c r="AF74" s="3" t="n">
         <v>0.001658809149642058</v>
       </c>
+      <c r="AG74" s="1" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="AH74" s="3" t="n">
+        <v>0.00409657456637316</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8021,6 +8471,12 @@
       <c r="AF75" s="3" t="n">
         <v>0.000624609618988107</v>
       </c>
+      <c r="AG75" s="1" t="n">
+        <v>0.01602</v>
+      </c>
+      <c r="AH75" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8121,6 +8577,12 @@
       <c r="AF76" s="3" t="n">
         <v>0.006993582359716995</v>
       </c>
+      <c r="AG76" s="1" t="n">
+        <v>0.12217</v>
+      </c>
+      <c r="AH76" s="2" t="n">
+        <v>-0.001797532478143623</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8221,6 +8683,12 @@
       <c r="AF77" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG77" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AH77" s="3" t="n">
+        <v>0.002527379949452356</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8321,6 +8789,12 @@
       <c r="AF78" s="3" t="n">
         <v>0.001960784313725547</v>
       </c>
+      <c r="AG78" s="1" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="AH78" s="2" t="n">
+        <v>-0.00489236790606654</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8421,6 +8895,12 @@
       <c r="AF79" s="2" t="n">
         <v>-0.0009894459102902258</v>
       </c>
+      <c r="AG79" s="1" t="n">
+        <v>0.006077</v>
+      </c>
+      <c r="AH79" s="3" t="n">
+        <v>0.003136348629910848</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8521,6 +9001,12 @@
       <c r="AF80" s="2" t="n">
         <v>-0.003676470588235232</v>
       </c>
+      <c r="AG80" s="1" t="n">
+        <v>0.007842</v>
+      </c>
+      <c r="AH80" s="2" t="n">
+        <v>-0.002163125079526613</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8621,6 +9107,12 @@
       <c r="AF81" s="3" t="n">
         <v>0.0005567928730511141</v>
       </c>
+      <c r="AG81" s="1" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="AH81" s="2" t="n">
+        <v>-0.002225932109070626</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8721,6 +9213,12 @@
       <c r="AF82" s="3" t="n">
         <v>0.0006112469437653835</v>
       </c>
+      <c r="AG82" s="1" t="n">
+        <v>0.1633</v>
+      </c>
+      <c r="AH82" s="2" t="n">
+        <v>-0.002443494196701353</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8821,6 +9319,12 @@
       <c r="AF83" s="3" t="n">
         <v>0.0007280669821623866</v>
       </c>
+      <c r="AG83" s="1" t="n">
+        <v>8.249000000000001</v>
+      </c>
+      <c r="AH83" s="3" t="n">
+        <v>0.000242512428762055</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8921,6 +9425,12 @@
       <c r="AF84" s="2" t="n">
         <v>-0.002506622610875311</v>
       </c>
+      <c r="AG84" s="1" t="n">
+        <v>351.83</v>
+      </c>
+      <c r="AH84" s="3" t="n">
+        <v>0.004683171992346973</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9021,6 +9531,12 @@
       <c r="AF85" s="3" t="n">
         <v>0.00268948655256717</v>
       </c>
+      <c r="AG85" s="1" t="n">
+        <v>0.004092</v>
+      </c>
+      <c r="AH85" s="2" t="n">
+        <v>-0.002194586686173972</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9121,6 +9637,12 @@
       <c r="AF86" s="2" t="n">
         <v>-0.008540491078237074</v>
       </c>
+      <c r="AG86" s="1" t="n">
+        <v>0.13084</v>
+      </c>
+      <c r="AH86" s="3" t="n">
+        <v>0.006306722042762769</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9221,6 +9743,12 @@
       <c r="AF87" s="2" t="n">
         <v>-0.001663893510815432</v>
       </c>
+      <c r="AG87" s="1" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="AH87" s="3" t="n">
+        <v>0.005555555555555715</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9321,6 +9849,12 @@
       <c r="AF88" s="2" t="n">
         <v>-0.0008810572687225656</v>
       </c>
+      <c r="AG88" s="1" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="AH88" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9421,6 +9955,12 @@
       <c r="AF89" s="3" t="n">
         <v>0.00101832993890028</v>
       </c>
+      <c r="AG89" s="1" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AH89" s="2" t="n">
+        <v>-0.00271278399457451</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9521,6 +10061,12 @@
       <c r="AF90" s="2" t="n">
         <v>-0.003086419753086294</v>
       </c>
+      <c r="AG90" s="1" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="AH90" s="3" t="n">
+        <v>0.001547987616098901</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9621,6 +10167,12 @@
       <c r="AF91" s="3" t="n">
         <v>0.003640997633351516</v>
       </c>
+      <c r="AG91" s="1" t="n">
+        <v>0.05554</v>
+      </c>
+      <c r="AH91" s="3" t="n">
+        <v>0.007436967168510804</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9721,6 +10273,12 @@
       <c r="AF92" s="3" t="n">
         <v>0.001599025355973495</v>
       </c>
+      <c r="AG92" s="1" t="n">
+        <v>1.3117</v>
+      </c>
+      <c r="AH92" s="2" t="n">
+        <v>-0.002812832598449</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9821,6 +10379,12 @@
       <c r="AF93" s="3" t="n">
         <v>0.001412651075184317</v>
       </c>
+      <c r="AG93" s="1" t="n">
+        <v>0.06398</v>
+      </c>
+      <c r="AH93" s="3" t="n">
+        <v>0.002821316614420057</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9921,6 +10485,12 @@
       <c r="AF94" s="2" t="n">
         <v>-0.002259887005649821</v>
       </c>
+      <c r="AG94" s="1" t="n">
+        <v>0.008789999999999999</v>
+      </c>
+      <c r="AH94" s="2" t="n">
+        <v>-0.004530011325028325</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10021,6 +10591,12 @@
       <c r="AF95" s="2" t="n">
         <v>-0.0008894159501926089</v>
       </c>
+      <c r="AG95" s="1" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="AH95" s="3" t="n">
+        <v>0.002373887240355986</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10121,6 +10697,12 @@
       <c r="AF96" s="3" t="n">
         <v>0.002661934338952864</v>
       </c>
+      <c r="AG96" s="1" t="n">
+        <v>0.02266</v>
+      </c>
+      <c r="AH96" s="3" t="n">
+        <v>0.002654867256637214</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10221,6 +10803,12 @@
       <c r="AF97" s="2" t="n">
         <v>-0.0003055300947142686</v>
       </c>
+      <c r="AG97" s="1" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="AH97" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10321,6 +10909,12 @@
       <c r="AF98" s="3" t="n">
         <v>0.002676181980374767</v>
       </c>
+      <c r="AG98" s="1" t="n">
+        <v>1.126</v>
+      </c>
+      <c r="AH98" s="3" t="n">
+        <v>0.001779359430604786</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10421,6 +11015,12 @@
       <c r="AF99" s="2" t="n">
         <v>-0.001976284584980312</v>
       </c>
+      <c r="AG99" s="1" t="n">
+        <v>3.033</v>
+      </c>
+      <c r="AH99" s="3" t="n">
+        <v>0.0009900990099010276</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10521,6 +11121,12 @@
       <c r="AF100" s="2" t="n">
         <v>-0.003773584905660324</v>
       </c>
+      <c r="AG100" s="1" t="n">
+        <v>0.03446</v>
+      </c>
+      <c r="AH100" s="3" t="n">
+        <v>0.004079254079253913</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10621,6 +11227,12 @@
       <c r="AF101" s="3" t="n">
         <v>0.0005461496450027919</v>
       </c>
+      <c r="AG101" s="1" t="n">
+        <v>1.829</v>
+      </c>
+      <c r="AH101" s="2" t="n">
+        <v>-0.0016375545851529</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10721,6 +11333,12 @@
       <c r="AF102" s="2" t="n">
         <v>-0.0002882675122512826</v>
       </c>
+      <c r="AG102" s="1" t="n">
+        <v>0.006995</v>
+      </c>
+      <c r="AH102" s="3" t="n">
+        <v>0.008506343713956173</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10821,6 +11439,12 @@
       <c r="AF103" s="2" t="n">
         <v>-0.001513775355737042</v>
       </c>
+      <c r="AG103" s="1" t="n">
+        <v>0.06576</v>
+      </c>
+      <c r="AH103" s="2" t="n">
+        <v>-0.003032140691328164</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10921,6 +11545,12 @@
       <c r="AF104" s="3" t="n">
         <v>0.005354100754441556</v>
       </c>
+      <c r="AG104" s="1" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="AH104" s="2" t="n">
+        <v>-0.0009682885499879241</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11021,6 +11651,12 @@
       <c r="AF105" s="2" t="n">
         <v>-0.001097092704333517</v>
       </c>
+      <c r="AG105" s="1" t="n">
+        <v>1.822</v>
+      </c>
+      <c r="AH105" s="3" t="n">
+        <v>0.0005491488193300999</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11121,6 +11757,12 @@
       <c r="AF106" s="3" t="n">
         <v>0.008681829298116886</v>
       </c>
+      <c r="AG106" s="1" t="n">
+        <v>0.008227999999999999</v>
+      </c>
+      <c r="AH106" s="2" t="n">
+        <v>-0.002545763122802787</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11221,6 +11863,12 @@
       <c r="AF107" s="2" t="n">
         <v>-0.00271591526344367</v>
       </c>
+      <c r="AG107" s="1" t="n">
+        <v>0.01836</v>
+      </c>
+      <c r="AH107" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11321,6 +11969,12 @@
       <c r="AF108" s="3" t="n">
         <v>0.003701989819528006</v>
       </c>
+      <c r="AG108" s="1" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="AH108" s="3" t="n">
+        <v>0.0004610419548178696</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11421,6 +12075,12 @@
       <c r="AF109" s="3" t="n">
         <v>0.00288340241484953</v>
       </c>
+      <c r="AG109" s="1" t="n">
+        <v>0.05568</v>
+      </c>
+      <c r="AH109" s="3" t="n">
+        <v>0.0005390835579515229</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11521,6 +12181,12 @@
       <c r="AF110" s="3" t="n">
         <v>0.001128668171557486</v>
       </c>
+      <c r="AG110" s="1" t="n">
+        <v>0.11545</v>
+      </c>
+      <c r="AH110" s="3" t="n">
+        <v>0.001214118463272927</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11621,6 +12287,12 @@
       <c r="AF111" s="3" t="n">
         <v>0.003282051282051291</v>
       </c>
+      <c r="AG111" s="1" t="n">
+        <v>0.09755999999999999</v>
+      </c>
+      <c r="AH111" s="2" t="n">
+        <v>-0.002657943160907894</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11721,6 +12393,12 @@
       <c r="AF112" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG112" s="1" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="AH112" s="2" t="n">
+        <v>-0.002673796791443927</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11821,6 +12499,12 @@
       <c r="AF113" s="3" t="n">
         <v>0.002335736772621043</v>
       </c>
+      <c r="AG113" s="1" t="n">
+        <v>0.09863</v>
+      </c>
+      <c r="AH113" s="2" t="n">
+        <v>-0.0007092198581560347</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11921,6 +12605,12 @@
       <c r="AF114" s="3" t="n">
         <v>0.005701254275940722</v>
       </c>
+      <c r="AG114" s="1" t="n">
+        <v>0.001776</v>
+      </c>
+      <c r="AH114" s="3" t="n">
+        <v>0.006802721088435416</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -12021,6 +12711,12 @@
       <c r="AF115" s="2" t="n">
         <v>-0.0003166561114630921</v>
       </c>
+      <c r="AG115" s="1" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="AH115" s="2" t="n">
+        <v>-0.001425403864428274</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -12121,6 +12817,12 @@
       <c r="AF116" s="3" t="n">
         <v>0.01015658061785859</v>
       </c>
+      <c r="AG116" s="1" t="n">
+        <v>0.2373</v>
+      </c>
+      <c r="AH116" s="2" t="n">
+        <v>-0.005865102639296123</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12221,6 +12923,12 @@
       <c r="AF117" s="2" t="n">
         <v>-0.002622950819672138</v>
       </c>
+      <c r="AG117" s="1" t="n">
+        <v>0.06085</v>
+      </c>
+      <c r="AH117" s="3" t="n">
+        <v>0.0001643655489809839</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -12321,6 +13029,12 @@
       <c r="AF118" s="2" t="n">
         <v>-0.001601464195836207</v>
       </c>
+      <c r="AG118" s="1" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="AH118" s="2" t="n">
+        <v>-0.003208065994500487</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -12421,6 +13135,12 @@
       <c r="AF119" s="3" t="n">
         <v>0.002704895861509222</v>
       </c>
+      <c r="AG119" s="1" t="n">
+        <v>0.003714</v>
+      </c>
+      <c r="AH119" s="3" t="n">
+        <v>0.00188831939573781</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -12521,6 +13241,12 @@
       <c r="AF120" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG120" s="1" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AH120" s="3" t="n">
+        <v>0.001265822784810128</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12621,6 +13347,12 @@
       <c r="AF121" s="2" t="n">
         <v>-0.0003338898163605642</v>
       </c>
+      <c r="AG121" s="1" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="AH121" s="3" t="n">
+        <v>0.0003340013360053072</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12721,6 +13453,12 @@
       <c r="AF122" s="2" t="n">
         <v>-0.00139713587146354</v>
       </c>
+      <c r="AG122" s="1" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AH122" s="2" t="n">
+        <v>-0.001399090591115815</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12821,6 +13559,12 @@
       <c r="AF123" s="2" t="n">
         <v>-0.007363975848951343</v>
       </c>
+      <c r="AG123" s="1" t="n">
+        <v>0.028437</v>
+      </c>
+      <c r="AH123" s="2" t="n">
+        <v>-0.0001757963574994045</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12921,6 +13665,12 @@
       <c r="AF124" s="2" t="n">
         <v>-0.001014070224362996</v>
       </c>
+      <c r="AG124" s="1" t="n">
+        <v>0.07862</v>
+      </c>
+      <c r="AH124" s="2" t="n">
+        <v>-0.002410861565791265</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -13021,6 +13771,12 @@
       <c r="AF125" s="2" t="n">
         <v>-0.003020007550018883</v>
       </c>
+      <c r="AG125" s="1" t="n">
+        <v>0.10575</v>
+      </c>
+      <c r="AH125" s="3" t="n">
+        <v>0.001041272245361596</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -13121,6 +13877,12 @@
       <c r="AF126" s="3" t="n">
         <v>0.003005259203606319</v>
       </c>
+      <c r="AG126" s="1" t="n">
+        <v>0.02652</v>
+      </c>
+      <c r="AH126" s="2" t="n">
+        <v>-0.00674157303370798</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -13221,6 +13983,12 @@
       <c r="AF127" s="2" t="n">
         <v>-0.001367989056087654</v>
       </c>
+      <c r="AG127" s="1" t="n">
+        <v>0.02186</v>
+      </c>
+      <c r="AH127" s="2" t="n">
+        <v>-0.001826484018264766</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -13321,6 +14089,12 @@
       <c r="AF128" s="3" t="n">
         <v>0.001228501228501264</v>
       </c>
+      <c r="AG128" s="1" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="AH128" s="2" t="n">
+        <v>-0.00122699386503071</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13421,6 +14195,12 @@
       <c r="AF129" s="3" t="n">
         <v>0.003716950697804914</v>
       </c>
+      <c r="AG129" s="1" t="n">
+        <v>0.14382</v>
+      </c>
+      <c r="AH129" s="3" t="n">
+        <v>0.004891000558971536</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -13521,6 +14301,12 @@
       <c r="AF130" s="2" t="n">
         <v>-0.004864515638657684</v>
       </c>
+      <c r="AG130" s="1" t="n">
+        <v>0.052389</v>
+      </c>
+      <c r="AH130" s="3" t="n">
+        <v>0.0003628031315638378</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13621,6 +14407,12 @@
       <c r="AF131" s="2" t="n">
         <v>-0.0009721715882852927</v>
       </c>
+      <c r="AG131" s="1" t="n">
+        <v>0.08226</v>
+      </c>
+      <c r="AH131" s="3" t="n">
+        <v>0.0006081985159955539</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13721,6 +14513,12 @@
       <c r="AF132" s="2" t="n">
         <v>-0.002270147559591281</v>
       </c>
+      <c r="AG132" s="1" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="AH132" s="3" t="n">
+        <v>0.004550625711035239</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13821,6 +14619,12 @@
       <c r="AF133" s="3" t="n">
         <v>0.002747252747252635</v>
       </c>
+      <c r="AG133" s="1" t="n">
+        <v>0.5823</v>
+      </c>
+      <c r="AH133" s="2" t="n">
+        <v>-0.002910958904109459</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13921,6 +14725,12 @@
       <c r="AF134" s="2" t="n">
         <v>-0.005676126878130217</v>
       </c>
+      <c r="AG134" s="1" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="AH134" s="3" t="n">
+        <v>0.0006715916722632365</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -14021,6 +14831,12 @@
       <c r="AF135" s="2" t="n">
         <v>-0.002275312855517541</v>
       </c>
+      <c r="AG135" s="1" t="n">
+        <v>0.01751</v>
+      </c>
+      <c r="AH135" s="2" t="n">
+        <v>-0.001710376282782142</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -14121,6 +14937,12 @@
       <c r="AF136" s="3" t="n">
         <v>0.0008060182697473215</v>
       </c>
+      <c r="AG136" s="1" t="n">
+        <v>0.03728</v>
+      </c>
+      <c r="AH136" s="3" t="n">
+        <v>0.0008053691275168389</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14221,6 +15043,12 @@
       <c r="AF137" s="2" t="n">
         <v>-0.003669724770642179</v>
       </c>
+      <c r="AG137" s="1" t="n">
+        <v>0.02713</v>
+      </c>
+      <c r="AH137" s="2" t="n">
+        <v>-0.0007366482504603751</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14321,6 +15149,12 @@
       <c r="AF138" s="2" t="n">
         <v>-0.001945525291828752</v>
       </c>
+      <c r="AG138" s="1" t="n">
+        <v>2.559</v>
+      </c>
+      <c r="AH138" s="2" t="n">
+        <v>-0.002339181286549623</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14421,6 +15255,12 @@
       <c r="AF139" s="2" t="n">
         <v>-0.002516778523489976</v>
       </c>
+      <c r="AG139" s="1" t="n">
+        <v>0.01189</v>
+      </c>
+      <c r="AH139" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -14521,6 +15361,12 @@
       <c r="AF140" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG140" s="1" t="n">
+        <v>0.01474</v>
+      </c>
+      <c r="AH140" s="2" t="n">
+        <v>-0.005398110661268571</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -14621,6 +15467,12 @@
       <c r="AF141" s="2" t="n">
         <v>-0.0001229634183829629</v>
       </c>
+      <c r="AG141" s="1" t="n">
+        <v>16.261</v>
+      </c>
+      <c r="AH141" s="2" t="n">
+        <v>-0.0001229785402448776</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -14721,6 +15573,12 @@
       <c r="AF142" s="2" t="n">
         <v>-0.0007936507936507613</v>
       </c>
+      <c r="AG142" s="1" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AH142" s="3" t="n">
+        <v>0.0007942811755361074</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14821,6 +15679,12 @@
       <c r="AF143" s="2" t="n">
         <v>-0.002922908293752291</v>
       </c>
+      <c r="AG143" s="1" t="n">
+        <v>0.02755</v>
+      </c>
+      <c r="AH143" s="3" t="n">
+        <v>0.009527299377061316</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14921,6 +15785,12 @@
       <c r="AF144" s="2" t="n">
         <v>-0.0006301197227472235</v>
       </c>
+      <c r="AG144" s="1" t="n">
+        <v>0.004765</v>
+      </c>
+      <c r="AH144" s="3" t="n">
+        <v>0.001471206389239189</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -15021,6 +15891,12 @@
       <c r="AF145" s="2" t="n">
         <v>-5.08130081300757e-05</v>
       </c>
+      <c r="AG145" s="1" t="n">
+        <v>1.9705</v>
+      </c>
+      <c r="AH145" s="3" t="n">
+        <v>0.001321205345800059</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -15121,6 +15997,12 @@
       <c r="AF146" s="3" t="n">
         <v>0.002999143101970892</v>
       </c>
+      <c r="AG146" s="1" t="n">
+        <v>0.02337</v>
+      </c>
+      <c r="AH146" s="2" t="n">
+        <v>-0.001708671507902684</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -15221,6 +16103,12 @@
       <c r="AF147" s="3" t="n">
         <v>0.004131308619919555</v>
       </c>
+      <c r="AG147" s="1" t="n">
+        <v>0.09011</v>
+      </c>
+      <c r="AH147" s="3" t="n">
+        <v>0.002001556766373842</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15321,6 +16209,12 @@
       <c r="AF148" s="3" t="n">
         <v>0.002407704654895624</v>
       </c>
+      <c r="AG148" s="1" t="n">
+        <v>0.06263000000000001</v>
+      </c>
+      <c r="AH148" s="3" t="n">
+        <v>0.002882305844675845</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15421,6 +16315,12 @@
       <c r="AF149" s="2" t="n">
         <v>-0.002354524049781386</v>
       </c>
+      <c r="AG149" s="1" t="n">
+        <v>0.05942</v>
+      </c>
+      <c r="AH149" s="3" t="n">
+        <v>0.001685772083614344</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -15521,6 +16421,12 @@
       <c r="AF150" s="2" t="n">
         <v>-0.004034887512226895</v>
       </c>
+      <c r="AG150" s="1" t="n">
+        <v>0.24459</v>
+      </c>
+      <c r="AH150" s="3" t="n">
+        <v>0.0009002741744076522</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -15621,6 +16527,12 @@
       <c r="AF151" s="2" t="n">
         <v>-0.005245994612221723</v>
       </c>
+      <c r="AG151" s="1" t="n">
+        <v>7.043e-05</v>
+      </c>
+      <c r="AH151" s="3" t="n">
+        <v>0.003848346636259916</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -15721,6 +16633,12 @@
       <c r="AF152" s="3" t="n">
         <v>0.00585321927059881</v>
       </c>
+      <c r="AG152" s="1" t="n">
+        <v>0.4463</v>
+      </c>
+      <c r="AH152" s="2" t="n">
+        <v>-0.001119068934646375</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -15821,6 +16739,12 @@
       <c r="AF153" s="3" t="n">
         <v>0.004211208292841022</v>
       </c>
+      <c r="AG153" s="1" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AH153" s="2" t="n">
+        <v>-0.005483870967741868</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -15921,6 +16845,12 @@
       <c r="AF154" s="3" t="n">
         <v>0.0008225939128049546</v>
       </c>
+      <c r="AG154" s="1" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="AH154" s="2" t="n">
+        <v>-0.001643835616438327</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -16021,6 +16951,12 @@
       <c r="AF155" s="2" t="n">
         <v>-0.0004336513443191196</v>
       </c>
+      <c r="AG155" s="1" t="n">
+        <v>0.2303</v>
+      </c>
+      <c r="AH155" s="2" t="n">
+        <v>-0.0008676789587852742</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -16121,6 +17057,12 @@
       <c r="AF156" s="2" t="n">
         <v>-0.001114275102141796</v>
       </c>
+      <c r="AG156" s="1" t="n">
+        <v>0.08069999999999999</v>
+      </c>
+      <c r="AH156" s="3" t="n">
+        <v>0.0002478929102626704</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -16221,6 +17163,12 @@
       <c r="AF157" s="3" t="n">
         <v>0.01211857018308633</v>
       </c>
+      <c r="AG157" s="1" t="n">
+        <v>0.23421</v>
+      </c>
+      <c r="AH157" s="3" t="n">
+        <v>0.008743216469980206</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -16321,6 +17269,12 @@
       <c r="AF158" s="3" t="n">
         <v>0.00393545848091303</v>
       </c>
+      <c r="AG158" s="1" t="n">
+        <v>0.2539</v>
+      </c>
+      <c r="AH158" s="2" t="n">
+        <v>-0.004704037632300976</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -16421,6 +17375,12 @@
       <c r="AF159" s="3" t="n">
         <v>0.00274254370929037</v>
       </c>
+      <c r="AG159" s="1" t="n">
+        <v>2.913</v>
+      </c>
+      <c r="AH159" s="2" t="n">
+        <v>-0.004102564102564106</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -16521,6 +17481,12 @@
       <c r="AF160" s="2" t="n">
         <v>-0.003024193548387044</v>
       </c>
+      <c r="AG160" s="1" t="n">
+        <v>0.09909999999999999</v>
+      </c>
+      <c r="AH160" s="3" t="n">
+        <v>0.002022244691607602</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -16621,6 +17587,12 @@
       <c r="AF161" s="3" t="n">
         <v>0.003181479726528113</v>
       </c>
+      <c r="AG161" s="1" t="n">
+        <v>0.14828</v>
+      </c>
+      <c r="AH161" s="3" t="n">
+        <v>0.0005398110661268336</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -16721,6 +17693,12 @@
       <c r="AF162" s="3" t="n">
         <v>0.006056935190793475</v>
       </c>
+      <c r="AG162" s="1" t="n">
+        <v>0.003322</v>
+      </c>
+      <c r="AH162" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -16821,6 +17799,12 @@
       <c r="AF163" s="2" t="n">
         <v>-0.0003967466772466307</v>
       </c>
+      <c r="AG163" s="1" t="n">
+        <v>0.005045</v>
+      </c>
+      <c r="AH163" s="3" t="n">
+        <v>0.001190712442945015</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -16921,6 +17905,12 @@
       <c r="AF164" s="2" t="n">
         <v>-0.00414078674948252</v>
       </c>
+      <c r="AG164" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="AH164" s="3" t="n">
+        <v>0.002079002079002139</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -17021,6 +18011,12 @@
       <c r="AF165" s="3" t="n">
         <v>0.001935483870967708</v>
       </c>
+      <c r="AG165" s="1" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AH165" s="3" t="n">
+        <v>0.001287830006439187</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -17121,6 +18117,12 @@
       <c r="AF166" s="3" t="n">
         <v>0.001004808727481567</v>
       </c>
+      <c r="AG166" s="1" t="n">
+        <v>1.3968</v>
+      </c>
+      <c r="AH166" s="3" t="n">
+        <v>0.001505700150570008</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -17221,6 +18223,12 @@
       <c r="AF167" s="3" t="n">
         <v>0.002868411617067131</v>
       </c>
+      <c r="AG167" s="1" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="AH167" s="3" t="n">
+        <v>0.00178762960314623</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -17321,6 +18329,12 @@
       <c r="AF168" s="3" t="n">
         <v>0.003194888178913741</v>
       </c>
+      <c r="AG168" s="1" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AH168" s="2" t="n">
+        <v>-0.006369426751592362</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -17421,6 +18435,12 @@
       <c r="AF169" s="2" t="n">
         <v>-0.003316749585406282</v>
       </c>
+      <c r="AG169" s="1" t="n">
+        <v>0.03018</v>
+      </c>
+      <c r="AH169" s="3" t="n">
+        <v>0.004326123128119739</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -17521,6 +18541,12 @@
       <c r="AF170" s="2" t="n">
         <v>-0.001614391143911453</v>
       </c>
+      <c r="AG170" s="1" t="n">
+        <v>0.04333</v>
+      </c>
+      <c r="AH170" s="3" t="n">
+        <v>0.0009240009240008863</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -17621,6 +18647,12 @@
       <c r="AF171" s="3" t="n">
         <v>0.01204819277108427</v>
       </c>
+      <c r="AG171" s="1" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="AH171" s="2" t="n">
+        <v>-0.005952380952380916</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -17721,6 +18753,12 @@
       <c r="AF172" s="2" t="n">
         <v>-0.0303030303030304</v>
       </c>
+      <c r="AG172" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="AH172" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -17821,6 +18859,12 @@
       <c r="AF173" s="2" t="n">
         <v>-0.001877934272300393</v>
       </c>
+      <c r="AG173" s="1" t="n">
+        <v>0.02122</v>
+      </c>
+      <c r="AH173" s="2" t="n">
+        <v>-0.001881467544684941</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -17921,6 +18965,12 @@
       <c r="AF174" s="2" t="n">
         <v>-0.003769819270429171</v>
       </c>
+      <c r="AG174" s="1" t="n">
+        <v>0.09043</v>
+      </c>
+      <c r="AH174" s="3" t="n">
+        <v>0.006455203116304921</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -18021,6 +19071,12 @@
       <c r="AF175" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG175" s="1" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="AH175" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -18121,6 +19177,12 @@
       <c r="AF176" s="2" t="n">
         <v>-0.0009337068160598811</v>
       </c>
+      <c r="AG176" s="1" t="n">
+        <v>0.02134</v>
+      </c>
+      <c r="AH176" s="2" t="n">
+        <v>-0.002803738317756895</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -18221,6 +19283,12 @@
       <c r="AF177" s="3" t="n">
         <v>0.001272264631043205</v>
       </c>
+      <c r="AG177" s="1" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="AH177" s="2" t="n">
+        <v>-0.003811944091486723</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -18321,6 +19389,12 @@
       <c r="AF178" s="2" t="n">
         <v>-0.006243496357960497</v>
       </c>
+      <c r="AG178" s="1" t="n">
+        <v>0.000954</v>
+      </c>
+      <c r="AH178" s="2" t="n">
+        <v>-0.001047120418848193</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -18421,6 +19495,12 @@
       <c r="AF179" s="3" t="n">
         <v>0.001489268506351262</v>
       </c>
+      <c r="AG179" s="1" t="n">
+        <v>0.022857</v>
+      </c>
+      <c r="AH179" s="2" t="n">
+        <v>-0.0003061581525542364</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -18521,6 +19601,12 @@
       <c r="AF180" s="3" t="n">
         <v>0.0004844961240309544</v>
       </c>
+      <c r="AG180" s="1" t="n">
+        <v>4.122</v>
+      </c>
+      <c r="AH180" s="2" t="n">
+        <v>-0.001937046004842617</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -18621,6 +19707,12 @@
       <c r="AF181" s="3" t="n">
         <v>0.007606580576684893</v>
       </c>
+      <c r="AG181" s="1" t="n">
+        <v>0.5716</v>
+      </c>
+      <c r="AH181" s="3" t="n">
+        <v>0.003511235955056183</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -18721,6 +19813,12 @@
       <c r="AF182" s="2" t="n">
         <v>-0.006456662101350106</v>
       </c>
+      <c r="AG182" s="1" t="n">
+        <v>0.05103</v>
+      </c>
+      <c r="AH182" s="3" t="n">
+        <v>0.00492319810949193</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -18821,6 +19919,12 @@
       <c r="AF183" s="3" t="n">
         <v>0.001643235347818049</v>
       </c>
+      <c r="AG183" s="1" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AH183" s="2" t="n">
+        <v>-0.001093693036820879</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -18921,6 +20025,12 @@
       <c r="AF184" s="3" t="n">
         <v>0.002071823204419845</v>
       </c>
+      <c r="AG184" s="1" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="AH184" s="2" t="n">
+        <v>-0.003101309441764296</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -19021,6 +20131,12 @@
       <c r="AF185" s="2" t="n">
         <v>-0.01104100946372231</v>
       </c>
+      <c r="AG185" s="1" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="AH185" s="2" t="n">
+        <v>-0.003189792663476928</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -19121,6 +20237,12 @@
       <c r="AF186" s="3" t="n">
         <v>0.003246753246753105</v>
       </c>
+      <c r="AG186" s="1" t="n">
+        <v>3.09e-05</v>
+      </c>
+      <c r="AH186" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -19221,6 +20343,12 @@
       <c r="AF187" s="2" t="n">
         <v>-0.004413619167717568</v>
       </c>
+      <c r="AG187" s="1" t="n">
+        <v>0.01569</v>
+      </c>
+      <c r="AH187" s="2" t="n">
+        <v>-0.006333122229258987</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -19321,6 +20449,12 @@
       <c r="AF188" s="2" t="n">
         <v>-0.002198339032730821</v>
       </c>
+      <c r="AG188" s="1" t="n">
+        <v>0.04084</v>
+      </c>
+      <c r="AH188" s="2" t="n">
+        <v>-0.0002447980416155722</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -19421,6 +20555,12 @@
       <c r="AF189" s="2" t="n">
         <v>-0.007969891520920919</v>
       </c>
+      <c r="AG189" s="1" t="n">
+        <v>0.0004479</v>
+      </c>
+      <c r="AH189" s="2" t="n">
+        <v>-0.0004463289444320573</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -19521,6 +20661,12 @@
       <c r="AF190" s="2" t="n">
         <v>-0.002586206896551619</v>
       </c>
+      <c r="AG190" s="1" t="n">
+        <v>0.02315</v>
+      </c>
+      <c r="AH190" s="3" t="n">
+        <v>0.0004321521175453584</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -19621,6 +20767,12 @@
       <c r="AF191" s="3" t="n">
         <v>0.0006333122229260964</v>
       </c>
+      <c r="AG191" s="1" t="n">
+        <v>0.01577</v>
+      </c>
+      <c r="AH191" s="2" t="n">
+        <v>-0.001898734177215332</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -19721,6 +20873,12 @@
       <c r="AF192" s="2" t="n">
         <v>-0.001965689778413258</v>
       </c>
+      <c r="AG192" s="1" t="n">
+        <v>0.05592</v>
+      </c>
+      <c r="AH192" s="3" t="n">
+        <v>0.00125335720680395</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -19821,6 +20979,12 @@
       <c r="AF193" s="2" t="n">
         <v>-0.003171247357293959</v>
       </c>
+      <c r="AG193" s="1" t="n">
+        <v>0.1887</v>
+      </c>
+      <c r="AH193" s="3" t="n">
+        <v>0.000530222693531372</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -19921,6 +21085,12 @@
       <c r="AF194" s="2" t="n">
         <v>-0.003107198342827603</v>
       </c>
+      <c r="AG194" s="1" t="n">
+        <v>0.01934</v>
+      </c>
+      <c r="AH194" s="3" t="n">
+        <v>0.004675324675324665</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -20021,6 +21191,12 @@
       <c r="AF195" s="2" t="n">
         <v>-0.001403180542563119</v>
       </c>
+      <c r="AG195" s="1" t="n">
+        <v>0.4268</v>
+      </c>
+      <c r="AH195" s="2" t="n">
+        <v>-0.0004683840749414004</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -20121,6 +21297,12 @@
       <c r="AF196" s="2" t="n">
         <v>-0.005627009646302161</v>
       </c>
+      <c r="AG196" s="1" t="n">
+        <v>0.01231</v>
+      </c>
+      <c r="AH196" s="2" t="n">
+        <v>-0.004850444624090624</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -20221,6 +21403,12 @@
       <c r="AF197" s="2" t="n">
         <v>-0.00424718623911656</v>
       </c>
+      <c r="AG197" s="1" t="n">
+        <v>0.04681</v>
+      </c>
+      <c r="AH197" s="2" t="n">
+        <v>-0.001706120708040172</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -20321,6 +21509,12 @@
       <c r="AF198" s="2" t="n">
         <v>-0.002729576915578217</v>
       </c>
+      <c r="AG198" s="1" t="n">
+        <v>0.5152</v>
+      </c>
+      <c r="AH198" s="3" t="n">
+        <v>0.00723362658846537</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -20421,6 +21615,12 @@
       <c r="AF199" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG199" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AH199" s="2" t="n">
+        <v>-0.01123595505617979</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -20521,6 +21721,12 @@
       <c r="AF200" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG200" s="1" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="AH200" s="3" t="n">
+        <v>0.001343183344526499</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -20621,6 +21827,12 @@
       <c r="AF201" s="2" t="n">
         <v>-0.006807470762785822</v>
       </c>
+      <c r="AG201" s="1" t="n">
+        <v>0.005678</v>
+      </c>
+      <c r="AH201" s="2" t="n">
+        <v>-0.002108963093145845</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -20721,6 +21933,12 @@
       <c r="AF202" s="3" t="n">
         <v>0.001345019090593534</v>
       </c>
+      <c r="AG202" s="1" t="n">
+        <v>0.023023</v>
+      </c>
+      <c r="AH202" s="2" t="n">
+        <v>-0.002426448286320919</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -20821,6 +22039,12 @@
       <c r="AF203" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG203" s="1" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="AH203" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -20921,6 +22145,12 @@
       <c r="AF204" s="3" t="n">
         <v>0.001787310098301983</v>
       </c>
+      <c r="AG204" s="1" t="n">
+        <v>0.03361</v>
+      </c>
+      <c r="AH204" s="2" t="n">
+        <v>-0.0005947071067499014</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -21021,6 +22251,12 @@
       <c r="AF205" s="2" t="n">
         <v>-0.002143878037160634</v>
       </c>
+      <c r="AG205" s="1" t="n">
+        <v>4.193</v>
+      </c>
+      <c r="AH205" s="3" t="n">
+        <v>0.0009548818333730149</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -21121,6 +22357,12 @@
       <c r="AF206" s="3" t="n">
         <v>0.002754820936639121</v>
       </c>
+      <c r="AG206" s="1" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="AH206" s="2" t="n">
+        <v>-0.00274725274725275</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -21221,6 +22463,12 @@
       <c r="AF207" s="2" t="n">
         <v>-0.005370125578321213</v>
       </c>
+      <c r="AG207" s="1" t="n">
+        <v>0.0012598</v>
+      </c>
+      <c r="AH207" s="3" t="n">
+        <v>0.04643242794252015</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -21321,6 +22569,12 @@
       <c r="AF208" s="2" t="n">
         <v>-0.0101038062283736</v>
       </c>
+      <c r="AG208" s="1" t="n">
+        <v>0.007167</v>
+      </c>
+      <c r="AH208" s="3" t="n">
+        <v>0.002097315436241525</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -21421,6 +22675,12 @@
       <c r="AF209" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG209" s="1" t="n">
+        <v>0.0601</v>
+      </c>
+      <c r="AH209" s="3" t="n">
+        <v>0.00333889816360599</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -21521,6 +22781,12 @@
       <c r="AF210" s="2" t="n">
         <v>-0.0007680491551460578</v>
       </c>
+      <c r="AG210" s="1" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="AH210" s="2" t="n">
+        <v>-0.001537279016141474</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -21621,6 +22887,12 @@
       <c r="AF211" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG211" s="1" t="n">
+        <v>0.007148</v>
+      </c>
+      <c r="AH211" s="2" t="n">
+        <v>-0.001257510129942759</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -21721,6 +22993,12 @@
       <c r="AF212" s="2" t="n">
         <v>-0.008585164835164843</v>
       </c>
+      <c r="AG212" s="1" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="AH212" s="3" t="n">
+        <v>0.005195704883962596</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -21821,6 +23099,12 @@
       <c r="AF213" s="2" t="n">
         <v>-0.002891740466293158</v>
       </c>
+      <c r="AG213" s="1" t="n">
+        <v>0.05483</v>
+      </c>
+      <c r="AH213" s="2" t="n">
+        <v>-0.006162769621170927</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -21921,6 +23205,12 @@
       <c r="AF214" s="2" t="n">
         <v>-0.001052631578947399</v>
       </c>
+      <c r="AG214" s="1" t="n">
+        <v>0.1899</v>
+      </c>
+      <c r="AH214" s="3" t="n">
+        <v>0.0005268703898841767</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -22021,6 +23311,12 @@
       <c r="AF215" s="3" t="n">
         <v>0.005257228689447907</v>
       </c>
+      <c r="AG215" s="1" t="n">
+        <v>0.05357</v>
+      </c>
+      <c r="AH215" s="3" t="n">
+        <v>0.0005603287261860711</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -22121,6 +23417,12 @@
       <c r="AF216" s="2" t="n">
         <v>-0.001436093824796536</v>
       </c>
+      <c r="AG216" s="1" t="n">
+        <v>0.002086</v>
+      </c>
+      <c r="AH216" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -22221,6 +23523,12 @@
       <c r="AF217" s="3" t="n">
         <v>0.00016542597187764</v>
       </c>
+      <c r="AG217" s="1" t="n">
+        <v>6.046</v>
+      </c>
+      <c r="AH217" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -22321,6 +23629,12 @@
       <c r="AF218" s="3" t="n">
         <v>0.002097902097902177</v>
       </c>
+      <c r="AG218" s="1" t="n">
+        <v>4.301</v>
+      </c>
+      <c r="AH218" s="3" t="n">
+        <v>0.0004652244708071132</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -22421,6 +23735,12 @@
       <c r="AF219" s="3" t="n">
         <v>0.000560957367240002</v>
       </c>
+      <c r="AG219" s="1" t="n">
+        <v>0.005323</v>
+      </c>
+      <c r="AH219" s="2" t="n">
+        <v>-0.005232666791254018</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -22521,6 +23841,12 @@
       <c r="AF220" s="3" t="n">
         <v>0.0004841442749939285</v>
       </c>
+      <c r="AG220" s="1" t="n">
+        <v>0.04123</v>
+      </c>
+      <c r="AH220" s="2" t="n">
+        <v>-0.002419549963706652</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -22621,6 +23947,12 @@
       <c r="AF221" s="2" t="n">
         <v>-0.001213171577123061</v>
       </c>
+      <c r="AG221" s="1" t="n">
+        <v>0.005771</v>
+      </c>
+      <c r="AH221" s="3" t="n">
+        <v>0.00138816588582339</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -22721,6 +24053,12 @@
       <c r="AF222" s="3" t="n">
         <v>0.001096491228070207</v>
       </c>
+      <c r="AG222" s="1" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="AH222" s="3" t="n">
+        <v>0.004381161007667005</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -22821,6 +24159,12 @@
       <c r="AF223" s="2" t="n">
         <v>-0.0005922416345868463</v>
       </c>
+      <c r="AG223" s="1" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="AH223" s="3" t="n">
+        <v>0.001185185185185055</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -22921,6 +24265,12 @@
       <c r="AF224" s="3" t="n">
         <v>0.0004618937644341293</v>
       </c>
+      <c r="AG224" s="1" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="AH224" s="3" t="n">
+        <v>0.0002308402585411923</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -23021,6 +24371,12 @@
       <c r="AF225" s="2" t="n">
         <v>-0.002755150934355464</v>
       </c>
+      <c r="AG225" s="1" t="n">
+        <v>0.08323999999999999</v>
+      </c>
+      <c r="AH225" s="2" t="n">
+        <v>-0.0001201201201202402</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -23121,6 +24477,12 @@
       <c r="AF226" s="3" t="n">
         <v>0.0005341880341880124</v>
       </c>
+      <c r="AG226" s="1" t="n">
+        <v>0.01871</v>
+      </c>
+      <c r="AH226" s="2" t="n">
+        <v>-0.001067805659369951</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -23221,6 +24583,12 @@
       <c r="AF227" s="2" t="n">
         <v>-0.0008474576271186096</v>
       </c>
+      <c r="AG227" s="1" t="n">
+        <v>0.04717</v>
+      </c>
+      <c r="AH227" s="3" t="n">
+        <v>0.000212044105173794</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -23321,6 +24689,12 @@
       <c r="AF228" s="3" t="n">
         <v>0.002598527501082764</v>
       </c>
+      <c r="AG228" s="1" t="n">
+        <v>0.02307</v>
+      </c>
+      <c r="AH228" s="2" t="n">
+        <v>-0.00345572354211664</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -23421,6 +24795,12 @@
       <c r="AF229" s="2" t="n">
         <v>-0.002739726027397212</v>
       </c>
+      <c r="AG229" s="1" t="n">
+        <v>0.1093</v>
+      </c>
+      <c r="AH229" s="3" t="n">
+        <v>0.0009157509157508148</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -23521,6 +24901,12 @@
       <c r="AF230" s="2" t="n">
         <v>-0.002393776181927058</v>
       </c>
+      <c r="AG230" s="1" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="AH230" s="3" t="n">
+        <v>0.0005998800239953014</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -23621,6 +25007,12 @@
       <c r="AF231" s="2" t="n">
         <v>-0.001967858314201411</v>
       </c>
+      <c r="AG231" s="1" t="n">
+        <v>0.03038</v>
+      </c>
+      <c r="AH231" s="2" t="n">
+        <v>-0.001643115346697271</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -23721,6 +25113,12 @@
       <c r="AF232" s="2" t="n">
         <v>-0.00177935943060491</v>
       </c>
+      <c r="AG232" s="1" t="n">
+        <v>0.02235</v>
+      </c>
+      <c r="AH232" s="2" t="n">
+        <v>-0.004010695187165921</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -23821,6 +25219,12 @@
       <c r="AF233" s="3" t="n">
         <v>0.05747353843110096</v>
       </c>
+      <c r="AG233" s="1" t="n">
+        <v>0.10566</v>
+      </c>
+      <c r="AH233" s="2" t="n">
+        <v>-0.0115996258185219</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -23921,6 +25325,12 @@
       <c r="AF234" s="2" t="n">
         <v>-0.000393081761006246</v>
       </c>
+      <c r="AG234" s="1" t="n">
+        <v>0.2541</v>
+      </c>
+      <c r="AH234" s="2" t="n">
+        <v>-0.0007864726700748465</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -24021,6 +25431,12 @@
       <c r="AF235" s="3" t="n">
         <v>0.002765647743813823</v>
       </c>
+      <c r="AG235" s="1" t="n">
+        <v>0.06891</v>
+      </c>
+      <c r="AH235" s="3" t="n">
+        <v>0.0002903178980983052</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -24121,6 +25537,12 @@
       <c r="AF236" s="3" t="n">
         <v>0.003990422984836396</v>
       </c>
+      <c r="AG236" s="1" t="n">
+        <v>0.12562</v>
+      </c>
+      <c r="AH236" s="2" t="n">
+        <v>-0.001430842607313082</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -24221,6 +25643,12 @@
       <c r="AF237" s="2" t="n">
         <v>-0.003066700741119221</v>
       </c>
+      <c r="AG237" s="1" t="n">
+        <v>0.03886</v>
+      </c>
+      <c r="AH237" s="2" t="n">
+        <v>-0.003845167905665324</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -24321,6 +25749,12 @@
       <c r="AF238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG238" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AH238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -24421,6 +25855,12 @@
       <c r="AF239" s="2" t="n">
         <v>-0.003508771929824375</v>
       </c>
+      <c r="AG239" s="1" t="n">
+        <v>0.003983</v>
+      </c>
+      <c r="AH239" s="3" t="n">
+        <v>0.001760563380281706</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -24521,6 +25961,12 @@
       <c r="AF240" s="3" t="n">
         <v>0.002904865649963697</v>
       </c>
+      <c r="AG240" s="1" t="n">
+        <v>0.01379</v>
+      </c>
+      <c r="AH240" s="2" t="n">
+        <v>-0.001448225923243967</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -24621,6 +26067,12 @@
       <c r="AF241" s="3" t="n">
         <v>0.007532526820360706</v>
       </c>
+      <c r="AG241" s="1" t="n">
+        <v>0.4463</v>
+      </c>
+      <c r="AH241" s="3" t="n">
+        <v>0.01110104213864966</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -24721,6 +26173,12 @@
       <c r="AF242" s="2" t="n">
         <v>-0.00263852242744064</v>
       </c>
+      <c r="AG242" s="1" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="AH242" s="2" t="n">
+        <v>-0.003968253968253921</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -24821,6 +26279,12 @@
       <c r="AF243" s="3" t="n">
         <v>0.000872219799389562</v>
       </c>
+      <c r="AG243" s="1" t="n">
+        <v>0.02275</v>
+      </c>
+      <c r="AH243" s="2" t="n">
+        <v>-0.008714596949891166</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -24921,6 +26385,12 @@
       <c r="AF244" s="3" t="n">
         <v>0.01727218582489587</v>
       </c>
+      <c r="AG244" s="1" t="n">
+        <v>0.001703</v>
+      </c>
+      <c r="AH244" s="2" t="n">
+        <v>-0.002927400468384083</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -25021,6 +26491,12 @@
       <c r="AF245" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG245" s="1" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="AH245" s="3" t="n">
+        <v>0.000758150113722644</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -25121,6 +26597,12 @@
       <c r="AF246" s="2" t="n">
         <v>-0.01609907120743033</v>
       </c>
+      <c r="AG246" s="1" t="n">
+        <v>0.03203</v>
+      </c>
+      <c r="AH246" s="3" t="n">
+        <v>0.007866582756450604</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -25221,6 +26703,12 @@
       <c r="AF247" s="3" t="n">
         <v>0.002248454187745833</v>
       </c>
+      <c r="AG247" s="1" t="n">
+        <v>0.1781</v>
+      </c>
+      <c r="AH247" s="2" t="n">
+        <v>-0.001121704991587089</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -25321,6 +26809,12 @@
       <c r="AF248" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG248" s="1" t="n">
+        <v>0.03047</v>
+      </c>
+      <c r="AH248" s="3" t="n">
+        <v>0.002632444883185265</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -25421,6 +26915,12 @@
       <c r="AF249" s="2" t="n">
         <v>-0.007544500766238338</v>
       </c>
+      <c r="AG249" s="1" t="n">
+        <v>0.008298</v>
+      </c>
+      <c r="AH249" s="2" t="n">
+        <v>-0.0143722532367264</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -25521,6 +27021,12 @@
       <c r="AF250" s="2" t="n">
         <v>-0.01042183622828793</v>
       </c>
+      <c r="AG250" s="1" t="n">
+        <v>0.01994</v>
+      </c>
+      <c r="AH250" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -25621,6 +27127,12 @@
       <c r="AF251" s="2" t="n">
         <v>-0.0008574490889603081</v>
       </c>
+      <c r="AG251" s="1" t="n">
+        <v>0.04647</v>
+      </c>
+      <c r="AH251" s="2" t="n">
+        <v>-0.003003647285990157</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -25721,6 +27233,12 @@
       <c r="AF252" s="3" t="n">
         <v>0.006530612244898018</v>
       </c>
+      <c r="AG252" s="1" t="n">
+        <v>0.008636</v>
+      </c>
+      <c r="AH252" s="3" t="n">
+        <v>0.0005793071486501907</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -25821,6 +27339,12 @@
       <c r="AF253" s="3" t="n">
         <v>0.001034661148473833</v>
       </c>
+      <c r="AG253" s="1" t="n">
+        <v>0.03863</v>
+      </c>
+      <c r="AH253" s="2" t="n">
+        <v>-0.001808785529715778</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -25921,6 +27445,12 @@
       <c r="AF254" s="2" t="n">
         <v>-0.003735585512424899</v>
       </c>
+      <c r="AG254" s="1" t="n">
+        <v>0.0613</v>
+      </c>
+      <c r="AH254" s="2" t="n">
+        <v>-0.0006521030322790735</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -26021,6 +27551,12 @@
       <c r="AF255" s="2" t="n">
         <v>-0.005843071786310569</v>
       </c>
+      <c r="AG255" s="1" t="n">
+        <v>0.003561</v>
+      </c>
+      <c r="AH255" s="2" t="n">
+        <v>-0.003358522250209868</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -26121,6 +27657,12 @@
       <c r="AF256" s="2" t="n">
         <v>-0.001489757914338859</v>
       </c>
+      <c r="AG256" s="1" t="n">
+        <v>0.013387</v>
+      </c>
+      <c r="AH256" s="2" t="n">
+        <v>-0.001342782543826979</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -26221,6 +27763,12 @@
       <c r="AF257" s="2" t="n">
         <v>-1.00052727779313e-06</v>
       </c>
+      <c r="AG257" s="1" t="n">
+        <v>0.999499</v>
+      </c>
+      <c r="AH257" s="3" t="n">
+        <v>2.701426353114369e-05</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -26321,6 +27869,12 @@
       <c r="AF258" s="2" t="n">
         <v>-0.001804443441975792</v>
       </c>
+      <c r="AG258" s="1" t="n">
+        <v>0.08842999999999999</v>
+      </c>
+      <c r="AH258" s="2" t="n">
+        <v>-0.0009038526720145816</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -26421,6 +27975,12 @@
       <c r="AF259" s="2" t="n">
         <v>-0.009132922535211238</v>
       </c>
+      <c r="AG259" s="1" t="n">
+        <v>0.09017</v>
+      </c>
+      <c r="AH259" s="3" t="n">
+        <v>0.001332593003886675</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -26521,6 +28081,12 @@
       <c r="AF260" s="2" t="n">
         <v>-0.004878048780487775</v>
       </c>
+      <c r="AG260" s="1" t="n">
+        <v>0.08178000000000001</v>
+      </c>
+      <c r="AH260" s="3" t="n">
+        <v>0.002205882352941172</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -26621,6 +28187,12 @@
       <c r="AF261" s="2" t="n">
         <v>-0.002652519893899305</v>
       </c>
+      <c r="AG261" s="1" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="AH261" s="3" t="n">
+        <v>0.0008865248226951348</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -26721,6 +28293,12 @@
       <c r="AF262" s="3" t="n">
         <v>0.0005238344683079706</v>
       </c>
+      <c r="AG262" s="1" t="n">
+        <v>0.00383</v>
+      </c>
+      <c r="AH262" s="3" t="n">
+        <v>0.002617801047120426</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -26821,6 +28399,12 @@
       <c r="AF263" s="2" t="n">
         <v>-0.000863557858376536</v>
       </c>
+      <c r="AG263" s="1" t="n">
+        <v>0.1153</v>
+      </c>
+      <c r="AH263" s="2" t="n">
+        <v>-0.003457216940362987</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -26921,6 +28505,12 @@
       <c r="AF264" s="3" t="n">
         <v>0.004184100418409969</v>
       </c>
+      <c r="AG264" s="1" t="n">
+        <v>0.0006208</v>
+      </c>
+      <c r="AH264" s="2" t="n">
+        <v>-0.00512820512820508</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -27021,6 +28611,12 @@
       <c r="AF265" s="3" t="n">
         <v>0.0006807351940095026</v>
       </c>
+      <c r="AG265" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="AH265" s="2" t="n">
+        <v>-0.0006802721088435097</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -27121,6 +28717,12 @@
       <c r="AF266" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG266" s="1" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="AH266" s="2" t="n">
+        <v>-0.003139717425431801</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -27221,6 +28823,12 @@
       <c r="AF267" s="2" t="n">
         <v>-0.001225490196078594</v>
       </c>
+      <c r="AG267" s="1" t="n">
+        <v>0.01629</v>
+      </c>
+      <c r="AH267" s="2" t="n">
+        <v>-0.0006134969325153125</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -27321,6 +28929,12 @@
       <c r="AF268" s="2" t="n">
         <v>-0.002304678497349551</v>
       </c>
+      <c r="AG268" s="1" t="n">
+        <v>0.0004347</v>
+      </c>
+      <c r="AH268" s="3" t="n">
+        <v>0.004158004158004134</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -27421,6 +29035,12 @@
       <c r="AF269" s="2" t="n">
         <v>-0.001435406698564535</v>
       </c>
+      <c r="AG269" s="1" t="n">
+        <v>0.02084</v>
+      </c>
+      <c r="AH269" s="2" t="n">
+        <v>-0.001437470052707177</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -27521,6 +29141,12 @@
       <c r="AF270" s="3" t="n">
         <v>0.002748763056624521</v>
       </c>
+      <c r="AG270" s="1" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="AH270" s="2" t="n">
+        <v>-0.001644736842105234</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -27621,6 +29247,12 @@
       <c r="AF271" s="2" t="n">
         <v>-0.0006747638326584952</v>
       </c>
+      <c r="AG271" s="1" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="AH271" s="2" t="n">
+        <v>-0.00405131667792044</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -27721,6 +29353,12 @@
       <c r="AF272" s="3" t="n">
         <v>0.002782696686061193</v>
       </c>
+      <c r="AG272" s="1" t="n">
+        <v>0.03966</v>
+      </c>
+      <c r="AH272" s="3" t="n">
+        <v>0.000504540867810272</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -27821,6 +29459,12 @@
       <c r="AF273" s="2" t="n">
         <v>-0.001077586206896553</v>
       </c>
+      <c r="AG273" s="1" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="AH273" s="3" t="n">
+        <v>0.001078748651564187</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -27921,6 +29565,12 @@
       <c r="AF274" s="3" t="n">
         <v>0.0007876496534342197</v>
       </c>
+      <c r="AG274" s="1" t="n">
+        <v>63.44</v>
+      </c>
+      <c r="AH274" s="2" t="n">
+        <v>-0.001416653549504225</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -28021,6 +29671,12 @@
       <c r="AF275" s="3" t="n">
         <v>0.003552397868561289</v>
       </c>
+      <c r="AG275" s="1" t="n">
+        <v>0.01131</v>
+      </c>
+      <c r="AH275" s="3" t="n">
+        <v>0.0008849557522125069</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -28121,6 +29777,12 @@
       <c r="AF276" s="2" t="n">
         <v>-0.0003835826620638028</v>
       </c>
+      <c r="AG276" s="1" t="n">
+        <v>2.609</v>
+      </c>
+      <c r="AH276" s="3" t="n">
+        <v>0.00115118956254801</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -28221,6 +29883,12 @@
       <c r="AF277" s="2" t="n">
         <v>-0.001901592583789011</v>
       </c>
+      <c r="AG277" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AH277" s="3" t="n">
+        <v>0.0002381519409383916</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -28321,6 +29989,12 @@
       <c r="AF278" s="2" t="n">
         <v>-0.01546134663341635</v>
       </c>
+      <c r="AG278" s="1" t="n">
+        <v>0.01959</v>
+      </c>
+      <c r="AH278" s="2" t="n">
+        <v>-0.007598784194528917</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -28421,6 +30095,12 @@
       <c r="AF279" s="3" t="n">
         <v>0.01005385996409329</v>
       </c>
+      <c r="AG279" s="1" t="n">
+        <v>0.005747</v>
+      </c>
+      <c r="AH279" s="3" t="n">
+        <v>0.02150728759331682</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -28521,6 +30201,12 @@
       <c r="AF280" s="2" t="n">
         <v>-0.002037697401935906</v>
       </c>
+      <c r="AG280" s="1" t="n">
+        <v>0.03895</v>
+      </c>
+      <c r="AH280" s="2" t="n">
+        <v>-0.005870342011230246</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -28621,6 +30307,12 @@
       <c r="AF281" s="3" t="n">
         <v>0.002205071664829109</v>
       </c>
+      <c r="AG281" s="1" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="AH281" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -28721,6 +30413,12 @@
       <c r="AF282" s="3" t="n">
         <v>0.002173388070514422</v>
       </c>
+      <c r="AG282" s="1" t="n">
+        <v>0.0004147</v>
+      </c>
+      <c r="AH282" s="2" t="n">
+        <v>-0.0007228915662650778</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -28821,6 +30519,12 @@
       <c r="AF283" s="3" t="n">
         <v>0.00195599022004899</v>
       </c>
+      <c r="AG283" s="1" t="n">
+        <v>0.04095</v>
+      </c>
+      <c r="AH283" s="2" t="n">
+        <v>-0.0007320644216691617</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -28921,6 +30625,12 @@
       <c r="AF284" s="2" t="n">
         <v>-0.000236462520690543</v>
       </c>
+      <c r="AG284" s="1" t="n">
+        <v>0.04233</v>
+      </c>
+      <c r="AH284" s="3" t="n">
+        <v>0.001182592242194925</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -29021,6 +30731,12 @@
       <c r="AF285" s="3" t="n">
         <v>0.0005582433941197489</v>
       </c>
+      <c r="AG285" s="1" t="n">
+        <v>0.10812</v>
+      </c>
+      <c r="AH285" s="3" t="n">
+        <v>0.005393342012274476</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -29121,6 +30837,12 @@
       <c r="AF286" s="2" t="n">
         <v>-0.002369668246445401</v>
       </c>
+      <c r="AG286" s="1" t="n">
+        <v>0.00421</v>
+      </c>
+      <c r="AH286" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -29221,6 +30943,12 @@
       <c r="AF287" s="3" t="n">
         <v>0.003285870755750341</v>
       </c>
+      <c r="AG287" s="1" t="n">
+        <v>0.15619</v>
+      </c>
+      <c r="AH287" s="3" t="n">
+        <v>0.00301823786283071</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -29321,6 +31049,12 @@
       <c r="AF288" s="2" t="n">
         <v>-0.001660210293303789</v>
       </c>
+      <c r="AG288" s="1" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="AH288" s="3" t="n">
+        <v>0.001662971175166268</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -29421,6 +31155,12 @@
       <c r="AF289" s="2" t="n">
         <v>-0.002152595072949137</v>
       </c>
+      <c r="AG289" s="1" t="n">
+        <v>4.169</v>
+      </c>
+      <c r="AH289" s="2" t="n">
+        <v>-0.0007190795781400082</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -29521,6 +31261,12 @@
       <c r="AF290" s="2" t="n">
         <v>-0.0003487561032318327</v>
       </c>
+      <c r="AG290" s="1" t="n">
+        <v>0.08570999999999999</v>
+      </c>
+      <c r="AH290" s="2" t="n">
+        <v>-0.003256192580532649</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -29621,6 +31367,12 @@
       <c r="AF291" s="2" t="n">
         <v>-0.001685393258426898</v>
       </c>
+      <c r="AG291" s="1" t="n">
+        <v>0.03543</v>
+      </c>
+      <c r="AH291" s="2" t="n">
+        <v>-0.003095104108047242</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -29721,6 +31473,12 @@
       <c r="AF292" s="2" t="n">
         <v>-0.001845649053250493</v>
       </c>
+      <c r="AG292" s="1" t="n">
+        <v>1.4636</v>
+      </c>
+      <c r="AH292" s="3" t="n">
+        <v>0.002328448157786653</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -29821,6 +31579,12 @@
       <c r="AF293" s="3" t="n">
         <v>0.003922237380627486</v>
       </c>
+      <c r="AG293" s="1" t="n">
+        <v>0.005879</v>
+      </c>
+      <c r="AH293" s="2" t="n">
+        <v>-0.001358926448106029</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -29921,6 +31685,12 @@
       <c r="AF294" s="3" t="n">
         <v>0.002326257633032788</v>
       </c>
+      <c r="AG294" s="1" t="n">
+        <v>0.003445</v>
+      </c>
+      <c r="AH294" s="2" t="n">
+        <v>-0.0005802146794313408</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -30021,6 +31791,12 @@
       <c r="AF295" s="2" t="n">
         <v>-0.001479289940828239</v>
       </c>
+      <c r="AG295" s="1" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AH295" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -30121,6 +31897,12 @@
       <c r="AF296" s="3" t="n">
         <v>0.001772264067346036</v>
       </c>
+      <c r="AG296" s="1" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="AH296" s="2" t="n">
+        <v>-0.001769128704113226</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -30221,6 +32003,12 @@
       <c r="AF297" s="2" t="n">
         <v>-0.004142011834319359</v>
       </c>
+      <c r="AG297" s="1" t="n">
+        <v>0.01681</v>
+      </c>
+      <c r="AH297" s="2" t="n">
+        <v>-0.001188354129530758</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -30321,6 +32109,12 @@
       <c r="AF298" s="3" t="n">
         <v>0.008554083885209691</v>
       </c>
+      <c r="AG298" s="1" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AH298" s="3" t="n">
+        <v>0.004103967168262657</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -30421,6 +32215,12 @@
       <c r="AF299" s="2" t="n">
         <v>-0.0008984725965857675</v>
       </c>
+      <c r="AG299" s="1" t="n">
+        <v>0.01112</v>
+      </c>
+      <c r="AH299" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -30521,6 +32321,12 @@
       <c r="AF300" s="2" t="n">
         <v>-0.0004810004810004614</v>
       </c>
+      <c r="AG300" s="1" t="n">
+        <v>0.02081</v>
+      </c>
+      <c r="AH300" s="3" t="n">
+        <v>0.001443695861405138</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -30621,6 +32427,12 @@
       <c r="AF301" s="2" t="n">
         <v>-0.001298279779292475</v>
       </c>
+      <c r="AG301" s="1" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AH301" s="2" t="n">
+        <v>-0.01267468313292154</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -30721,6 +32533,12 @@
       <c r="AF302" s="3" t="n">
         <v>0.0007241129616221092</v>
       </c>
+      <c r="AG302" s="1" t="n">
+        <v>0.01383</v>
+      </c>
+      <c r="AH302" s="3" t="n">
+        <v>0.0007235890014471485</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -30821,6 +32639,12 @@
       <c r="AF303" s="3" t="n">
         <v>0.0005401026194976825</v>
       </c>
+      <c r="AG303" s="1" t="n">
+        <v>0.07403999999999999</v>
+      </c>
+      <c r="AH303" s="2" t="n">
+        <v>-0.0008097165991903441</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -30921,6 +32745,12 @@
       <c r="AF304" s="2" t="n">
         <v>-0.001879699248120224</v>
       </c>
+      <c r="AG304" s="1" t="n">
+        <v>0.01594</v>
+      </c>
+      <c r="AH304" s="3" t="n">
+        <v>0.0006277463904582293</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -31021,6 +32851,12 @@
       <c r="AF305" s="3" t="n">
         <v>0.0001549907005581215</v>
       </c>
+      <c r="AG305" s="1" t="n">
+        <v>0.06444</v>
+      </c>
+      <c r="AH305" s="2" t="n">
+        <v>-0.001394700139470118</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -31121,6 +32957,12 @@
       <c r="AF306" s="2" t="n">
         <v>-0.002210166767128772</v>
       </c>
+      <c r="AG306" s="1" t="n">
+        <v>0.04957</v>
+      </c>
+      <c r="AH306" s="2" t="n">
+        <v>-0.001812323801852594</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -31221,6 +33063,12 @@
       <c r="AF307" s="3" t="n">
         <v>0.001076426264800862</v>
       </c>
+      <c r="AG307" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="AH307" s="2" t="n">
+        <v>-0.001075268817204302</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -31321,6 +33169,12 @@
       <c r="AF308" s="2" t="n">
         <v>-0.004247876061969103</v>
       </c>
+      <c r="AG308" s="1" t="n">
+        <v>0.03985</v>
+      </c>
+      <c r="AH308" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -31421,6 +33275,12 @@
       <c r="AF309" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG309" s="1" t="n">
+        <v>0.01556</v>
+      </c>
+      <c r="AH309" s="2" t="n">
+        <v>-0.002564102564102571</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -31521,6 +33381,12 @@
       <c r="AF310" s="3" t="n">
         <v>0.002929866324848937</v>
       </c>
+      <c r="AG310" s="1" t="n">
+        <v>0.05472</v>
+      </c>
+      <c r="AH310" s="2" t="n">
+        <v>-0.0009129085265656643</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -31621,6 +33487,12 @@
       <c r="AF311" s="3" t="n">
         <v>0.001118067978533049</v>
       </c>
+      <c r="AG311" s="1" t="n">
+        <v>0.004472</v>
+      </c>
+      <c r="AH311" s="2" t="n">
+        <v>-0.001116819298637435</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -31721,6 +33593,12 @@
       <c r="AF312" s="2" t="n">
         <v>-0.001646865074697109</v>
       </c>
+      <c r="AG312" s="1" t="n">
+        <v>0.08488999999999999</v>
+      </c>
+      <c r="AH312" s="3" t="n">
+        <v>0.0002356545304582567</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -31821,6 +33699,12 @@
       <c r="AF313" s="2" t="n">
         <v>-0.001333511134818014</v>
       </c>
+      <c r="AG313" s="1" t="n">
+        <v>0.07482</v>
+      </c>
+      <c r="AH313" s="2" t="n">
+        <v>-0.0009347042328748914</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -31921,6 +33805,12 @@
       <c r="AF314" s="3" t="n">
         <v>0.003272251308900527</v>
       </c>
+      <c r="AG314" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="AH314" s="2" t="n">
+        <v>-0.00195694716242658</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -32021,6 +33911,12 @@
       <c r="AF315" s="2" t="n">
         <v>-0.001872659176030103</v>
       </c>
+      <c r="AG315" s="1" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="AH315" s="2" t="n">
+        <v>-0.0006253908692932395</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -32121,6 +34017,12 @@
       <c r="AF316" s="2" t="n">
         <v>-0.00604063701263052</v>
       </c>
+      <c r="AG316" s="1" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="AH316" s="2" t="n">
+        <v>-0.001657458563535883</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -32221,6 +34123,12 @@
       <c r="AF317" s="2" t="n">
         <v>-0.002658513890735086</v>
       </c>
+      <c r="AG317" s="1" t="n">
+        <v>0.007515</v>
+      </c>
+      <c r="AH317" s="3" t="n">
+        <v>0.001599360255897622</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -32321,6 +34229,12 @@
       <c r="AF318" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG318" s="1" t="n">
+        <v>0.05092</v>
+      </c>
+      <c r="AH318" s="3" t="n">
+        <v>0.01212482607831444</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -32421,6 +34335,12 @@
       <c r="AF319" s="3" t="n">
         <v>0.001291062975182997</v>
       </c>
+      <c r="AG319" s="1" t="n">
+        <v>0.27953</v>
+      </c>
+      <c r="AH319" s="3" t="n">
+        <v>0.001181948424068757</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -32521,6 +34441,12 @@
       <c r="AF320" s="2" t="n">
         <v>-0.001585144927536183</v>
       </c>
+      <c r="AG320" s="1" t="n">
+        <v>0.4409</v>
+      </c>
+      <c r="AH320" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -32621,6 +34547,12 @@
       <c r="AF321" s="3" t="n">
         <v>0.0007704160246531923</v>
       </c>
+      <c r="AG321" s="1" t="n">
+        <v>0.07772</v>
+      </c>
+      <c r="AH321" s="2" t="n">
+        <v>-0.002822684115986631</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -32721,6 +34653,12 @@
       <c r="AF322" s="2" t="n">
         <v>-0.001223241590214102</v>
       </c>
+      <c r="AG322" s="1" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="AH322" s="2" t="n">
+        <v>-0.01224739742804655</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -32821,6 +34759,12 @@
       <c r="AF323" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG323" s="1" t="n">
+        <v>1.982</v>
+      </c>
+      <c r="AH323" s="3" t="n">
+        <v>0.001010101010101011</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -32921,6 +34865,12 @@
       <c r="AF324" s="3" t="n">
         <v>0.0006756503134265674</v>
       </c>
+      <c r="AG324" s="1" t="n">
+        <v>0.053345</v>
+      </c>
+      <c r="AH324" s="3" t="n">
+        <v>0.0005063955887317463</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -33021,6 +34971,12 @@
       <c r="AF325" s="2" t="n">
         <v>-0.004555215722001732</v>
       </c>
+      <c r="AG325" s="1" t="n">
+        <v>0.15337</v>
+      </c>
+      <c r="AH325" s="3" t="n">
+        <v>0.002614891808851484</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -33121,6 +35077,12 @@
       <c r="AF326" s="2" t="n">
         <v>-0.004164738546969014</v>
       </c>
+      <c r="AG326" s="1" t="n">
+        <v>0.006468</v>
+      </c>
+      <c r="AH326" s="3" t="n">
+        <v>0.001858736059479532</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -33221,6 +35183,12 @@
       <c r="AF327" s="2" t="n">
         <v>-0.001839322078433965</v>
       </c>
+      <c r="AG327" s="1" t="n">
+        <v>0.01524</v>
+      </c>
+      <c r="AH327" s="3" t="n">
+        <v>0.002961500493583409</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -33321,6 +35289,12 @@
       <c r="AF328" s="2" t="n">
         <v>-0.00310559006211189</v>
       </c>
+      <c r="AG328" s="1" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="AH328" s="3" t="n">
+        <v>0.002076843198338585</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -33421,6 +35395,12 @@
       <c r="AF329" s="2" t="n">
         <v>-0.00317244504871972</v>
       </c>
+      <c r="AG329" s="1" t="n">
+        <v>0.004394</v>
+      </c>
+      <c r="AH329" s="2" t="n">
+        <v>-0.001136621959536212</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -33521,6 +35501,12 @@
       <c r="AF330" s="3" t="n">
         <v>0.002119460500963372</v>
       </c>
+      <c r="AG330" s="1" t="n">
+        <v>0.05205</v>
+      </c>
+      <c r="AH330" s="3" t="n">
+        <v>0.0007690828686790688</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -33621,6 +35607,12 @@
       <c r="AF331" s="2" t="n">
         <v>-0.003334259516532427</v>
       </c>
+      <c r="AG331" s="1" t="n">
+        <v>0.03584</v>
+      </c>
+      <c r="AH331" s="2" t="n">
+        <v>-0.0008363534987455325</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -33721,6 +35713,12 @@
       <c r="AF332" s="3" t="n">
         <v>0.004726536124240232</v>
       </c>
+      <c r="AG332" s="1" t="n">
+        <v>0.1488</v>
+      </c>
+      <c r="AH332" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -33821,6 +35819,12 @@
       <c r="AF333" s="2" t="n">
         <v>-0.003099173553718954</v>
       </c>
+      <c r="AG333" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="AH333" s="2" t="n">
+        <v>-0.001036269430051843</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -33921,6 +35925,12 @@
       <c r="AF334" s="2" t="n">
         <v>-0.0004542357483533769</v>
       </c>
+      <c r="AG334" s="1" t="n">
+        <v>0.04399</v>
+      </c>
+      <c r="AH334" s="2" t="n">
+        <v>-0.0004544421722335648</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -34021,6 +36031,12 @@
       <c r="AF335" s="2" t="n">
         <v>-0.002193516938825245</v>
       </c>
+      <c r="AG335" s="1" t="n">
+        <v>0.08187999999999999</v>
+      </c>
+      <c r="AH335" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -34121,6 +36137,12 @@
       <c r="AF336" s="2" t="n">
         <v>-0.00241545893719807</v>
       </c>
+      <c r="AG336" s="1" t="n">
+        <v>0.2066</v>
+      </c>
+      <c r="AH336" s="3" t="n">
+        <v>0.0004842615012107349</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -34221,6 +36243,12 @@
       <c r="AF337" s="3" t="n">
         <v>0.00496031746031743</v>
       </c>
+      <c r="AG337" s="1" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="AH337" s="2" t="n">
+        <v>-0.0009871668311944317</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -34321,6 +36349,12 @@
       <c r="AF338" s="2" t="n">
         <v>-0.00436681222707424</v>
       </c>
+      <c r="AG338" s="1" t="n">
+        <v>0.1139</v>
+      </c>
+      <c r="AH338" s="2" t="n">
+        <v>-0.0008771929824561654</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -34421,6 +36455,12 @@
       <c r="AF339" s="2" t="n">
         <v>-0.002178649237472867</v>
       </c>
+      <c r="AG339" s="1" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="AH339" s="2" t="n">
+        <v>-0.001091703056768514</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -34521,6 +36561,12 @@
       <c r="AF340" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG340" s="1" t="n">
+        <v>0.27192</v>
+      </c>
+      <c r="AH340" s="2" t="n">
+        <v>-0.0002941176470589135</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -34621,6 +36667,12 @@
       <c r="AF341" s="2" t="n">
         <v>-0.002553981889946575</v>
       </c>
+      <c r="AG341" s="1" t="n">
+        <v>0.04292</v>
+      </c>
+      <c r="AH341" s="2" t="n">
+        <v>-0.0009310986964617871</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -34721,6 +36773,12 @@
       <c r="AF342" s="2" t="n">
         <v>-0.001381215469613247</v>
       </c>
+      <c r="AG342" s="1" t="n">
+        <v>0.07899</v>
+      </c>
+      <c r="AH342" s="2" t="n">
+        <v>-0.006789890607317978</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -34821,6 +36879,12 @@
       <c r="AF343" s="3" t="n">
         <v>0.00183126226291697</v>
       </c>
+      <c r="AG343" s="1" t="n">
+        <v>7.652</v>
+      </c>
+      <c r="AH343" s="2" t="n">
+        <v>-0.0009139574356965235</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -34921,6 +36985,12 @@
       <c r="AF344" s="3" t="n">
         <v>0.001826635669212869</v>
       </c>
+      <c r="AG344" s="1" t="n">
+        <v>0.6039</v>
+      </c>
+      <c r="AH344" s="3" t="n">
+        <v>0.0009945300845351317</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -35021,6 +37091,12 @@
       <c r="AF345" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG345" s="1" t="n">
+        <v>0.03754</v>
+      </c>
+      <c r="AH345" s="2" t="n">
+        <v>-0.00079850944902854</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -35121,6 +37197,12 @@
       <c r="AF346" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG346" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="AH346" s="2" t="n">
+        <v>-0.002398081534772251</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -35221,6 +37303,12 @@
       <c r="AF347" s="3" t="n">
         <v>0.001713306681896029</v>
       </c>
+      <c r="AG347" s="1" t="n">
+        <v>0.1754</v>
+      </c>
+      <c r="AH347" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -35321,6 +37409,12 @@
       <c r="AF348" s="2" t="n">
         <v>-0.0005778676683039584</v>
       </c>
+      <c r="AG348" s="1" t="n">
+        <v>5197.5</v>
+      </c>
+      <c r="AH348" s="3" t="n">
+        <v>0.001734605377276669</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -35421,6 +37515,12 @@
       <c r="AF349" s="3" t="n">
         <v>0.009587020648967673</v>
       </c>
+      <c r="AG349" s="1" t="n">
+        <v>0.01368</v>
+      </c>
+      <c r="AH349" s="2" t="n">
+        <v>-0.0007304601899197463</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -35521,6 +37621,12 @@
       <c r="AF350" s="2" t="n">
         <v>-0.002559181062060258</v>
       </c>
+      <c r="AG350" s="1" t="n">
+        <v>0.01557</v>
+      </c>
+      <c r="AH350" s="2" t="n">
+        <v>-0.001282873636946708</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -35621,6 +37727,12 @@
       <c r="AF351" s="3" t="n">
         <v>0.001943949457314157</v>
       </c>
+      <c r="AG351" s="1" t="n">
+        <v>0.0006188</v>
+      </c>
+      <c r="AH351" s="3" t="n">
+        <v>0.0004850444624089783</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -35721,6 +37833,12 @@
       <c r="AF352" s="3" t="n">
         <v>0.001008572869389772</v>
       </c>
+      <c r="AG352" s="1" t="n">
+        <v>0.01984</v>
+      </c>
+      <c r="AH352" s="2" t="n">
+        <v>-0.0005037783375314656</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -35821,6 +37939,12 @@
       <c r="AF353" s="2" t="n">
         <v>-0.0002146153020709545</v>
       </c>
+      <c r="AG353" s="1" t="n">
+        <v>0.09338</v>
+      </c>
+      <c r="AH353" s="3" t="n">
+        <v>0.002253944402704753</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -35921,6 +38045,12 @@
       <c r="AF354" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG354" s="1" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="AH354" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -36021,6 +38151,12 @@
       <c r="AF355" s="2" t="n">
         <v>-0.005882352941176436</v>
       </c>
+      <c r="AG355" s="1" t="n">
+        <v>0.0006093</v>
+      </c>
+      <c r="AH355" s="3" t="n">
+        <v>0.001479289940828349</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -36121,6 +38257,12 @@
       <c r="AF356" s="2" t="n">
         <v>-0.004916420845624281</v>
       </c>
+      <c r="AG356" s="1" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="AH356" s="2" t="n">
+        <v>-0.001482213438735234</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -36221,6 +38363,12 @@
       <c r="AF357" s="3" t="n">
         <v>0.004368719965050213</v>
       </c>
+      <c r="AG357" s="1" t="n">
+        <v>0.02293</v>
+      </c>
+      <c r="AH357" s="2" t="n">
+        <v>-0.002609830361026578</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -36321,6 +38469,12 @@
       <c r="AF358" s="3" t="n">
         <v>0.004901960784313712</v>
       </c>
+      <c r="AG358" s="1" t="n">
+        <v>0.000408</v>
+      </c>
+      <c r="AH358" s="2" t="n">
+        <v>-0.004878048780487791</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -36421,6 +38575,12 @@
       <c r="AF359" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG359" s="1" t="n">
+        <v>0.01475</v>
+      </c>
+      <c r="AH359" s="3" t="n">
+        <v>0.001357773251866883</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -36521,6 +38681,12 @@
       <c r="AF360" s="3" t="n">
         <v>0.004790419161676633</v>
       </c>
+      <c r="AG360" s="1" t="n">
+        <v>0.003345</v>
+      </c>
+      <c r="AH360" s="2" t="n">
+        <v>-0.003277711561382646</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -36621,6 +38787,12 @@
       <c r="AF361" s="3" t="n">
         <v>0.0009401441554372375</v>
       </c>
+      <c r="AG361" s="1" t="n">
+        <v>0.6394</v>
+      </c>
+      <c r="AH361" s="3" t="n">
+        <v>0.0009392611145897524</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -36721,6 +38893,12 @@
       <c r="AF362" s="2" t="n">
         <v>-0.001692047377326643</v>
       </c>
+      <c r="AG362" s="1" t="n">
+        <v>0.02364</v>
+      </c>
+      <c r="AH362" s="3" t="n">
+        <v>0.001694915254237366</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -36821,6 +38999,12 @@
       <c r="AF363" s="3" t="n">
         <v>0.0004585753592171869</v>
       </c>
+      <c r="AG363" s="1" t="n">
+        <v>0.06536</v>
+      </c>
+      <c r="AH363" s="2" t="n">
+        <v>-0.001375095492742443</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -36921,6 +39105,12 @@
       <c r="AF364" s="2" t="n">
         <v>-0.0008467400508044978</v>
       </c>
+      <c r="AG364" s="1" t="n">
+        <v>4.717</v>
+      </c>
+      <c r="AH364" s="2" t="n">
+        <v>-0.0006355932203390072</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -37021,6 +39211,12 @@
       <c r="AF365" s="2" t="n">
         <v>-0.001945525291828811</v>
       </c>
+      <c r="AG365" s="1" t="n">
+        <v>0.07188</v>
+      </c>
+      <c r="AH365" s="3" t="n">
+        <v>0.0008354218880535296</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -37121,6 +39317,12 @@
       <c r="AF366" s="2" t="n">
         <v>-0.005850026591030028</v>
       </c>
+      <c r="AG366" s="1" t="n">
+        <v>0.05612</v>
+      </c>
+      <c r="AH366" s="3" t="n">
+        <v>0.0007132667617689962</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -37221,6 +39423,12 @@
       <c r="AF367" s="2" t="n">
         <v>-0.0006837606837607745</v>
       </c>
+      <c r="AG367" s="1" t="n">
+        <v>0.05841</v>
+      </c>
+      <c r="AH367" s="2" t="n">
+        <v>-0.0008552856654122722</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -37321,6 +39529,12 @@
       <c r="AF368" s="3" t="n">
         <v>0.001925770308123353</v>
       </c>
+      <c r="AG368" s="1" t="n">
+        <v>0.05723</v>
+      </c>
+      <c r="AH368" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -37421,6 +39635,12 @@
       <c r="AF369" s="3" t="n">
         <v>0.001287830006439098</v>
       </c>
+      <c r="AG369" s="1" t="n">
+        <v>0.03112</v>
+      </c>
+      <c r="AH369" s="3" t="n">
+        <v>0.000643086816720231</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -37521,6 +39741,12 @@
       <c r="AF370" s="2" t="n">
         <v>-0.0006146281499692835</v>
       </c>
+      <c r="AG370" s="1" t="n">
+        <v>0.0001619</v>
+      </c>
+      <c r="AH370" s="2" t="n">
+        <v>-0.004305043050430443</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -37621,6 +39847,12 @@
       <c r="AF371" s="3" t="n">
         <v>0.006776664702416033</v>
       </c>
+      <c r="AG371" s="1" t="n">
+        <v>0.006817</v>
+      </c>
+      <c r="AH371" s="2" t="n">
+        <v>-0.002487562189054676</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -37721,6 +39953,12 @@
       <c r="AF372" s="3" t="n">
         <v>0.001433691756272343</v>
       </c>
+      <c r="AG372" s="1" t="n">
+        <v>0.006963</v>
+      </c>
+      <c r="AH372" s="2" t="n">
+        <v>-0.003149606299212644</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -37821,6 +40059,12 @@
       <c r="AF373" s="3" t="n">
         <v>0.004755614266842746</v>
       </c>
+      <c r="AG373" s="1" t="n">
+        <v>3.841</v>
+      </c>
+      <c r="AH373" s="3" t="n">
+        <v>0.009992111490928282</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -37921,6 +40165,12 @@
       <c r="AF374" s="3" t="n">
         <v>0.0008533636751529583</v>
       </c>
+      <c r="AG374" s="1" t="n">
+        <v>0.07036000000000001</v>
+      </c>
+      <c r="AH374" s="2" t="n">
+        <v>-0.0001421060110842138</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -38021,6 +40271,12 @@
       <c r="AF375" s="3" t="n">
         <v>0.0008780732563973986</v>
       </c>
+      <c r="AG375" s="1" t="n">
+        <v>0.07987</v>
+      </c>
+      <c r="AH375" s="3" t="n">
+        <v>0.001002631908760455</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -38121,6 +40377,12 @@
       <c r="AF376" s="3" t="n">
         <v>0.0001589319771137337</v>
       </c>
+      <c r="AG376" s="1" t="n">
+        <v>0.06297999999999999</v>
+      </c>
+      <c r="AH376" s="3" t="n">
+        <v>0.0007945336087715636</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -38221,6 +40483,12 @@
       <c r="AF377" s="2" t="n">
         <v>-0.0006501105187883028</v>
       </c>
+      <c r="AG377" s="1" t="n">
+        <v>0.07678</v>
+      </c>
+      <c r="AH377" s="2" t="n">
+        <v>-0.001040853499869851</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -38321,6 +40589,12 @@
       <c r="AF378" s="3" t="n">
         <v>0.000741839762611294</v>
       </c>
+      <c r="AG378" s="1" t="n">
+        <v>0.000408</v>
+      </c>
+      <c r="AH378" s="3" t="n">
+        <v>0.008154188287620389</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -38421,6 +40695,12 @@
       <c r="AF379" s="3" t="n">
         <v>0.000677506775067676</v>
       </c>
+      <c r="AG379" s="1" t="n">
+        <v>0.07378</v>
+      </c>
+      <c r="AH379" s="2" t="n">
+        <v>-0.0009478672985782074</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -38521,6 +40801,12 @@
       <c r="AF380" s="3" t="n">
         <v>0.008752735229759195</v>
       </c>
+      <c r="AG380" s="1" t="n">
+        <v>0.001382</v>
+      </c>
+      <c r="AH380" s="2" t="n">
+        <v>-0.0007230657989876472</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -38621,6 +40907,12 @@
       <c r="AF381" s="3" t="n">
         <v>0.002044346595376616</v>
       </c>
+      <c r="AG381" s="1" t="n">
+        <v>6.368</v>
+      </c>
+      <c r="AH381" s="2" t="n">
+        <v>-0.0006277463904581857</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -38721,6 +41013,12 @@
       <c r="AF382" s="2" t="n">
         <v>-0.009922041105598831</v>
       </c>
+      <c r="AG382" s="1" t="n">
+        <v>0.01401</v>
+      </c>
+      <c r="AH382" s="3" t="n">
+        <v>0.002863278453829643</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -38821,6 +41119,12 @@
       <c r="AF383" s="2" t="n">
         <v>-0.003970504821327318</v>
       </c>
+      <c r="AG383" s="1" t="n">
+        <v>0.01752</v>
+      </c>
+      <c r="AH383" s="2" t="n">
+        <v>-0.00227790432801813</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -38921,6 +41225,12 @@
       <c r="AF384" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG384" s="1" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="AH384" s="3" t="n">
+        <v>0.00196850393700793</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -39021,6 +41331,12 @@
       <c r="AF385" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG385" s="1" t="n">
+        <v>4.504</v>
+      </c>
+      <c r="AH385" s="2" t="n">
+        <v>-0.0004438526409233617</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -39121,6 +41437,12 @@
       <c r="AF386" s="3" t="n">
         <v>0.003072196620583792</v>
       </c>
+      <c r="AG386" s="1" t="n">
+        <v>0.001308</v>
+      </c>
+      <c r="AH386" s="3" t="n">
+        <v>0.001531393568146885</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -39221,6 +41543,12 @@
       <c r="AF387" s="2" t="n">
         <v>-0.001684919966301459</v>
       </c>
+      <c r="AG387" s="1" t="n">
+        <v>0.0005922</v>
+      </c>
+      <c r="AH387" s="2" t="n">
+        <v>-0.0005063291139241544</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -39321,6 +41649,12 @@
       <c r="AF388" s="2" t="n">
         <v>-0.004355400696864236</v>
       </c>
+      <c r="AG388" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="AH388" s="2" t="n">
+        <v>-0.002624671916010392</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -39421,6 +41755,12 @@
       <c r="AF389" s="2" t="n">
         <v>-0.001101321585903039</v>
       </c>
+      <c r="AG389" s="1" t="n">
+        <v>0.009090000000000001</v>
+      </c>
+      <c r="AH389" s="3" t="n">
+        <v>0.002205071664829208</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -39521,6 +41861,12 @@
       <c r="AF390" s="2" t="n">
         <v>-0.0006314725940893469</v>
       </c>
+      <c r="AG390" s="1" t="n">
+        <v>0.07905</v>
+      </c>
+      <c r="AH390" s="2" t="n">
+        <v>-0.001010994565904342</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -39621,6 +41967,12 @@
       <c r="AF391" s="2" t="n">
         <v>-0.003636363636363555</v>
       </c>
+      <c r="AG391" s="1" t="n">
+        <v>0.05202</v>
+      </c>
+      <c r="AH391" s="2" t="n">
+        <v>-0.0007683442182098599</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -39721,6 +42073,12 @@
       <c r="AF392" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG392" s="1" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="AH392" s="2" t="n">
+        <v>-0.004201680672268919</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -39821,6 +42179,12 @@
       <c r="AF393" s="2" t="n">
         <v>-0.008395522388059682</v>
       </c>
+      <c r="AG393" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="AH393" s="3" t="n">
+        <v>0.004233301975540912</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -39921,6 +42285,12 @@
       <c r="AF394" s="2" t="n">
         <v>-0.0009837678307919612</v>
       </c>
+      <c r="AG394" s="1" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="AH394" s="2" t="n">
+        <v>-0.002954209748892119</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -40021,6 +42391,12 @@
       <c r="AF395" s="3" t="n">
         <v>0.001023541453428893</v>
       </c>
+      <c r="AG395" s="1" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="AH395" s="2" t="n">
+        <v>-0.002044989775051042</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -40121,6 +42497,12 @@
       <c r="AF396" s="2" t="n">
         <v>-0.001795332136445363</v>
       </c>
+      <c r="AG396" s="1" t="n">
+        <v>2.764</v>
+      </c>
+      <c r="AH396" s="2" t="n">
+        <v>-0.005755395683453243</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -40221,6 +42603,12 @@
       <c r="AF397" s="3" t="n">
         <v>0.002367797947908535</v>
       </c>
+      <c r="AG397" s="1" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="AH397" s="2" t="n">
+        <v>-0.003149606299212601</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -40321,6 +42709,12 @@
       <c r="AF398" s="3" t="n">
         <v>0.00914716168953462</v>
       </c>
+      <c r="AG398" s="1" t="n">
+        <v>0.007505</v>
+      </c>
+      <c r="AH398" s="3" t="n">
+        <v>0.0003998933617702477</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -40421,6 +42815,12 @@
       <c r="AF399" s="2" t="n">
         <v>-0.001154734411085323</v>
       </c>
+      <c r="AG399" s="1" t="n">
+        <v>0.2585</v>
+      </c>
+      <c r="AH399" s="2" t="n">
+        <v>-0.003853564547206169</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -40521,6 +42921,12 @@
       <c r="AF400" s="3" t="n">
         <v>0.002825745682888577</v>
       </c>
+      <c r="AG400" s="1" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AH400" s="2" t="n">
+        <v>-0.001878522229179852</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -40621,6 +43027,12 @@
       <c r="AF401" s="3" t="n">
         <v>0.006668519033064661</v>
       </c>
+      <c r="AG401" s="1" t="n">
+        <v>0.007305</v>
+      </c>
+      <c r="AH401" s="3" t="n">
+        <v>0.008142423406017117</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -40721,6 +43133,12 @@
       <c r="AF402" s="3" t="n">
         <v>0.004141238012205737</v>
       </c>
+      <c r="AG402" s="1" t="n">
+        <v>0.004595</v>
+      </c>
+      <c r="AH402" s="2" t="n">
+        <v>-0.002604731929672207</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -40821,6 +43239,12 @@
       <c r="AF403" s="2" t="n">
         <v>-0.001124016485575206</v>
       </c>
+      <c r="AG403" s="1" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="AH403" s="3" t="n">
+        <v>0.0003750937734433195</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -40921,6 +43345,12 @@
       <c r="AF404" s="3" t="n">
         <v>0.002087682672233822</v>
       </c>
+      <c r="AG404" s="1" t="n">
+        <v>0.2401</v>
+      </c>
+      <c r="AH404" s="3" t="n">
+        <v>0.0004166666666667365</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -41021,6 +43451,12 @@
       <c r="AF405" s="3" t="n">
         <v>0.001704739174906219</v>
       </c>
+      <c r="AG405" s="1" t="n">
+        <v>0.0008617</v>
+      </c>
+      <c r="AH405" s="2" t="n">
+        <v>-0.02235080553664624</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -41121,6 +43557,12 @@
       <c r="AF406" s="2" t="n">
         <v>-0.001377410468319571</v>
       </c>
+      <c r="AG406" s="1" t="n">
+        <v>0.00507</v>
+      </c>
+      <c r="AH406" s="2" t="n">
+        <v>-0.0009852216748768073</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -41221,6 +43663,12 @@
       <c r="AF407" s="2" t="n">
         <v>-0.0008278145695363901</v>
       </c>
+      <c r="AG407" s="1" t="n">
+        <v>0.01206</v>
+      </c>
+      <c r="AH407" s="2" t="n">
+        <v>-0.000828500414250317</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -41321,6 +43769,12 @@
       <c r="AF408" s="3" t="n">
         <v>0.005483207676490732</v>
       </c>
+      <c r="AG408" s="1" t="n">
+        <v>0.00148</v>
+      </c>
+      <c r="AH408" s="3" t="n">
+        <v>0.008861622358554868</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -41421,6 +43875,12 @@
       <c r="AF409" s="3" t="n">
         <v>0.006217616580310807</v>
       </c>
+      <c r="AG409" s="1" t="n">
+        <v>0.03884</v>
+      </c>
+      <c r="AH409" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -41521,6 +43981,12 @@
       <c r="AF410" s="2" t="n">
         <v>-0.002443494196701184</v>
       </c>
+      <c r="AG410" s="1" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="AH410" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -41621,6 +44087,12 @@
       <c r="AF411" s="3" t="n">
         <v>0.002631578947368423</v>
       </c>
+      <c r="AG411" s="1" t="n">
+        <v>0.1908</v>
+      </c>
+      <c r="AH411" s="3" t="n">
+        <v>0.001574803149606271</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -41721,6 +44193,12 @@
       <c r="AF412" s="2" t="n">
         <v>-0.0008877052818462882</v>
       </c>
+      <c r="AG412" s="1" t="n">
+        <v>0.06748999999999999</v>
+      </c>
+      <c r="AH412" s="2" t="n">
+        <v>-0.0005923293351105027</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -41821,6 +44299,12 @@
       <c r="AF413" s="2" t="n">
         <v>-0.0003941663381947182</v>
       </c>
+      <c r="AG413" s="1" t="n">
+        <v>2535</v>
+      </c>
+      <c r="AH413" s="2" t="n">
+        <v>-0.0003943217665615142</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -41921,6 +44405,12 @@
       <c r="AF414" s="3" t="n">
         <v>0.0007616146230008628</v>
       </c>
+      <c r="AG414" s="1" t="n">
+        <v>0.05256</v>
+      </c>
+      <c r="AH414" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -42021,6 +44511,12 @@
       <c r="AF415" s="3" t="n">
         <v>0.0005724098454492787</v>
       </c>
+      <c r="AG415" s="1" t="n">
+        <v>1.747</v>
+      </c>
+      <c r="AH415" s="2" t="n">
+        <v>-0.0005720823798626372</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -42121,6 +44617,12 @@
       <c r="AF416" s="2" t="n">
         <v>-0.001297577854671377</v>
       </c>
+      <c r="AG416" s="1" t="n">
+        <v>0.06905</v>
+      </c>
+      <c r="AH416" s="2" t="n">
+        <v>-0.00317597805687885</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -42221,6 +44723,12 @@
       <c r="AF417" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG417" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AH417" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -42321,6 +44829,12 @@
       <c r="AF418" s="2" t="n">
         <v>-0.003934426229508127</v>
       </c>
+      <c r="AG418" s="1" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="AH418" s="2" t="n">
+        <v>-0.0006583278472680497</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -42421,6 +44935,12 @@
       <c r="AF419" s="3" t="n">
         <v>0.008130081300812959</v>
       </c>
+      <c r="AG419" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="AH419" s="2" t="n">
+        <v>-0.008064516129032209</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -42521,6 +45041,12 @@
       <c r="AF420" s="2" t="n">
         <v>-0.001558441558441495</v>
       </c>
+      <c r="AG420" s="1" t="n">
+        <v>0.01928</v>
+      </c>
+      <c r="AH420" s="3" t="n">
+        <v>0.003121748178980102</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -42621,6 +45147,12 @@
       <c r="AF421" s="3" t="n">
         <v>0.001907609816457049</v>
       </c>
+      <c r="AG421" s="1" t="n">
+        <v>0.19456</v>
+      </c>
+      <c r="AH421" s="3" t="n">
+        <v>0.001183553748777893</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -42721,6 +45253,12 @@
       <c r="AF422" s="3" t="n">
         <v>0.0002912055911472371</v>
       </c>
+      <c r="AG422" s="1" t="n">
+        <v>0.03429</v>
+      </c>
+      <c r="AH422" s="2" t="n">
+        <v>-0.001746724890829623</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -42821,6 +45359,12 @@
       <c r="AF423" s="2" t="n">
         <v>-0.0007027406886859925</v>
       </c>
+      <c r="AG423" s="1" t="n">
+        <v>0.1417</v>
+      </c>
+      <c r="AH423" s="2" t="n">
+        <v>-0.003516174402250355</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -42921,6 +45465,12 @@
       <c r="AF424" s="2" t="n">
         <v>-0.003759398496240611</v>
       </c>
+      <c r="AG424" s="1" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="AH424" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -43021,6 +45571,12 @@
       <c r="AF425" s="3" t="n">
         <v>0.0009578544061301627</v>
       </c>
+      <c r="AG425" s="1" t="n">
+        <v>0.1044</v>
+      </c>
+      <c r="AH425" s="2" t="n">
+        <v>-0.0009569377990429568</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -43121,6 +45677,12 @@
       <c r="AF426" s="2" t="n">
         <v>-0.003364171572750171</v>
       </c>
+      <c r="AG426" s="1" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="AH426" s="2" t="n">
+        <v>-0.001406469760900083</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -43221,6 +45783,12 @@
       <c r="AF427" s="3" t="n">
         <v>0.0007846214201648747</v>
       </c>
+      <c r="AG427" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="AH427" s="2" t="n">
+        <v>-0.0003920031360252082</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -43321,6 +45889,12 @@
       <c r="AF428" s="2" t="n">
         <v>-0.002945869645268162</v>
       </c>
+      <c r="AG428" s="1" t="n">
+        <v>0.008078999999999999</v>
+      </c>
+      <c r="AH428" s="2" t="n">
+        <v>-0.005416717961344409</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -43421,6 +45995,12 @@
       <c r="AF429" s="2" t="n">
         <v>-0.001616814874696922</v>
       </c>
+      <c r="AG429" s="1" t="n">
+        <v>0.01234</v>
+      </c>
+      <c r="AH429" s="2" t="n">
+        <v>-0.0008097165991902504</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -43521,6 +46101,12 @@
       <c r="AF430" s="2" t="n">
         <v>-0.00179024317469803</v>
       </c>
+      <c r="AG430" s="1" t="n">
+        <v>0.06673999999999999</v>
+      </c>
+      <c r="AH430" s="2" t="n">
+        <v>-0.002540726348826834</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -43621,6 +46207,12 @@
       <c r="AF431" s="3" t="n">
         <v>0.001838235294117572</v>
       </c>
+      <c r="AG431" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="AH431" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -43721,6 +46313,12 @@
       <c r="AF432" s="2" t="n">
         <v>-0.002909090909090935</v>
       </c>
+      <c r="AG432" s="1" t="n">
+        <v>0.009561999999999999</v>
+      </c>
+      <c r="AH432" s="2" t="n">
+        <v>-0.00364697301239974</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -43821,6 +46419,12 @@
       <c r="AF433" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG433" s="1" t="n">
+        <v>0.04127</v>
+      </c>
+      <c r="AH433" s="2" t="n">
+        <v>-0.002899251026818121</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -43921,6 +46525,12 @@
       <c r="AF434" s="3" t="n">
         <v>0.008252770572977981</v>
       </c>
+      <c r="AG434" s="1" t="n">
+        <v>0.04252</v>
+      </c>
+      <c r="AH434" s="2" t="n">
+        <v>-0.005612722170252506</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -44021,6 +46631,12 @@
       <c r="AF435" s="3" t="n">
         <v>0.0006430868167203426</v>
       </c>
+      <c r="AG435" s="1" t="n">
+        <v>0.001555</v>
+      </c>
+      <c r="AH435" s="2" t="n">
+        <v>-0.000642673521850985</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -44121,6 +46737,12 @@
       <c r="AF436" s="3" t="n">
         <v>0.000363372093023241</v>
       </c>
+      <c r="AG436" s="1" t="n">
+        <v>0.02754</v>
+      </c>
+      <c r="AH436" s="3" t="n">
+        <v>0.0003632401017072137</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -44221,6 +46843,12 @@
       <c r="AF437" s="3" t="n">
         <v>0.007341245564664179</v>
       </c>
+      <c r="AG437" s="1" t="n">
+        <v>0.08260000000000001</v>
+      </c>
+      <c r="AH437" s="3" t="n">
+        <v>0.003279484999392765</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -44321,6 +46949,12 @@
       <c r="AF438" s="2" t="n">
         <v>-0.0008673026886383596</v>
       </c>
+      <c r="AG438" s="1" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="AH438" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -44421,6 +47055,12 @@
       <c r="AF439" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG439" s="1" t="n">
+        <v>1.555</v>
+      </c>
+      <c r="AH439" s="3" t="n">
+        <v>0.001287830006439151</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -44521,6 +47161,12 @@
       <c r="AF440" s="2" t="n">
         <v>-0.002191780821917861</v>
       </c>
+      <c r="AG440" s="1" t="n">
+        <v>0.001823</v>
+      </c>
+      <c r="AH440" s="3" t="n">
+        <v>0.001098297638660104</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -44621,6 +47267,12 @@
       <c r="AF441" s="2" t="n">
         <v>-0.002989130434782581</v>
       </c>
+      <c r="AG441" s="1" t="n">
+        <v>0.03675</v>
+      </c>
+      <c r="AH441" s="3" t="n">
+        <v>0.00163532297628775</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -44721,6 +47373,12 @@
       <c r="AF442" s="2" t="n">
         <v>-0.002720348204570263</v>
       </c>
+      <c r="AG442" s="1" t="n">
+        <v>0.01836</v>
+      </c>
+      <c r="AH442" s="3" t="n">
+        <v>0.001636661211129419</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -44821,6 +47479,12 @@
       <c r="AF443" s="2" t="n">
         <v>-0.001177578897786022</v>
       </c>
+      <c r="AG443" s="1" t="n">
+        <v>0.12703</v>
+      </c>
+      <c r="AH443" s="2" t="n">
+        <v>-0.001571956299614916</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -44921,6 +47585,12 @@
       <c r="AF444" s="3" t="n">
         <v>0.002791590334118536</v>
       </c>
+      <c r="AG444" s="1" t="n">
+        <v>0.011535</v>
+      </c>
+      <c r="AH444" s="3" t="n">
+        <v>0.003479773814702053</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -45021,6 +47691,12 @@
       <c r="AF445" s="2" t="n">
         <v>-0.003207896360271393</v>
       </c>
+      <c r="AG445" s="1" t="n">
+        <v>0.08076999999999999</v>
+      </c>
+      <c r="AH445" s="2" t="n">
+        <v>-0.0002475553905187043</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -45121,6 +47797,12 @@
       <c r="AF446" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG446" s="1" t="n">
+        <v>0.0002149</v>
+      </c>
+      <c r="AH446" s="3" t="n">
+        <v>0.0009315323707499063</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -45221,6 +47903,12 @@
       <c r="AF447" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG447" s="1" t="n">
+        <v>0.00664</v>
+      </c>
+      <c r="AH447" s="2" t="n">
+        <v>-0.007473841554558999</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -45321,6 +48009,12 @@
       <c r="AF448" s="3" t="n">
         <v>0.0009085402786190869</v>
       </c>
+      <c r="AG448" s="1" t="n">
+        <v>0.09775</v>
+      </c>
+      <c r="AH448" s="2" t="n">
+        <v>-0.01412002017145737</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -45421,6 +48115,12 @@
       <c r="AF449" s="2" t="n">
         <v>-0.002379535990481785</v>
       </c>
+      <c r="AG449" s="1" t="n">
+        <v>0.001676</v>
+      </c>
+      <c r="AH449" s="2" t="n">
+        <v>-0.0005963029218843963</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -45521,6 +48221,12 @@
       <c r="AF450" s="3" t="n">
         <v>0.00241080038572812</v>
       </c>
+      <c r="AG450" s="1" t="n">
+        <v>0.0002084</v>
+      </c>
+      <c r="AH450" s="3" t="n">
+        <v>0.002405002405002333</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -45621,6 +48327,12 @@
       <c r="AF451" s="3" t="n">
         <v>0.001893939393939421</v>
       </c>
+      <c r="AG451" s="1" t="n">
+        <v>26.44</v>
+      </c>
+      <c r="AH451" s="2" t="n">
+        <v>-0.000378071833648318</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -45721,6 +48433,12 @@
       <c r="AF452" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG452" s="1" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AH452" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -45821,6 +48539,12 @@
       <c r="AF453" s="2" t="n">
         <v>-0.0005720823798627141</v>
       </c>
+      <c r="AG453" s="1" t="n">
+        <v>0.0001745</v>
+      </c>
+      <c r="AH453" s="2" t="n">
+        <v>-0.001144819690898556</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -45921,6 +48645,12 @@
       <c r="AF454" s="3" t="n">
         <v>0.000725426187885353</v>
       </c>
+      <c r="AG454" s="1" t="n">
+        <v>0.11053</v>
+      </c>
+      <c r="AH454" s="3" t="n">
+        <v>0.001540413193185969</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -46021,6 +48751,12 @@
       <c r="AF455" s="3" t="n">
         <v>0.0001986886548777846</v>
       </c>
+      <c r="AG455" s="1" t="n">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="AH455" s="2" t="n">
+        <v>-0.001787842669845077</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -46121,6 +48857,12 @@
       <c r="AF456" s="2" t="n">
         <v>-0.0002503285562300852</v>
       </c>
+      <c r="AG456" s="1" t="n">
+        <v>0.015974</v>
+      </c>
+      <c r="AH456" s="2" t="n">
+        <v>-6.259780907674492e-05</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -46221,6 +48963,12 @@
       <c r="AF457" s="2" t="n">
         <v>-0.001195457262402898</v>
       </c>
+      <c r="AG457" s="1" t="n">
+        <v>0.00668</v>
+      </c>
+      <c r="AH457" s="2" t="n">
+        <v>-0.0005984440454816971</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -46321,6 +49069,12 @@
       <c r="AF458" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG458" s="1" t="n">
+        <v>0.4827</v>
+      </c>
+      <c r="AH458" s="3" t="n">
+        <v>0.0004145077720207948</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -46421,6 +49175,12 @@
       <c r="AF459" s="2" t="n">
         <v>-0.001098728614032344</v>
       </c>
+      <c r="AG459" s="1" t="n">
+        <v>0.006357</v>
+      </c>
+      <c r="AH459" s="2" t="n">
+        <v>-0.001099937146448784</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -46521,6 +49281,12 @@
       <c r="AF460" s="2" t="n">
         <v>-0.002166064981949621</v>
       </c>
+      <c r="AG460" s="1" t="n">
+        <v>0.1377</v>
+      </c>
+      <c r="AH460" s="2" t="n">
+        <v>-0.003617945007235893</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -46621,6 +49387,12 @@
       <c r="AF461" s="3" t="n">
         <v>0.005455962587685161</v>
       </c>
+      <c r="AG461" s="1" t="n">
+        <v>0.09009</v>
+      </c>
+      <c r="AH461" s="2" t="n">
+        <v>-0.002325581395348858</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -46721,6 +49493,12 @@
       <c r="AF462" s="2" t="n">
         <v>-0.003973509933774826</v>
       </c>
+      <c r="AG462" s="1" t="n">
+        <v>0.04509</v>
+      </c>
+      <c r="AH462" s="2" t="n">
+        <v>-0.0006648936170213263</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -46821,6 +49599,12 @@
       <c r="AF463" s="3" t="n">
         <v>0.00143061516452081</v>
       </c>
+      <c r="AG463" s="1" t="n">
+        <v>0.00701</v>
+      </c>
+      <c r="AH463" s="3" t="n">
+        <v>0.00142857142857137</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -46921,6 +49705,12 @@
       <c r="AF464" s="2" t="n">
         <v>-0.0007621951219513048</v>
       </c>
+      <c r="AG464" s="1" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="AH464" s="2" t="n">
+        <v>-0.00381388253241792</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -47021,6 +49811,12 @@
       <c r="AF465" s="2" t="n">
         <v>-0.0007163323782234168</v>
       </c>
+      <c r="AG465" s="1" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="AH465" s="2" t="n">
+        <v>-0.001433691756272442</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -47121,6 +49917,12 @@
       <c r="AF466" s="2" t="n">
         <v>-0.002807017543859652</v>
       </c>
+      <c r="AG466" s="1" t="n">
+        <v>1.422</v>
+      </c>
+      <c r="AH466" s="3" t="n">
+        <v>0.0007037297677690991</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -47221,6 +50023,12 @@
       <c r="AF467" s="2" t="n">
         <v>-0.002074688796680413</v>
       </c>
+      <c r="AG467" s="1" t="n">
+        <v>0.01922</v>
+      </c>
+      <c r="AH467" s="2" t="n">
+        <v>-0.001039501039500997</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -47321,6 +50129,12 @@
       <c r="AF468" s="2" t="n">
         <v>-0.01070038910505827</v>
       </c>
+      <c r="AG468" s="1" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="AH468" s="2" t="n">
+        <v>-0.006882989183874201</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -47421,6 +50235,12 @@
       <c r="AF469" s="2" t="n">
         <v>-0.001253446979192781</v>
       </c>
+      <c r="AG469" s="1" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="AH469" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -47521,6 +50341,12 @@
       <c r="AF470" s="2" t="n">
         <v>-0.001133786848072563</v>
       </c>
+      <c r="AG470" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AH470" s="2" t="n">
+        <v>-0.001135073779795688</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -47621,6 +50447,12 @@
       <c r="AF471" s="2" t="n">
         <v>-0.0006163328197227192</v>
       </c>
+      <c r="AG471" s="1" t="n">
+        <v>3.234</v>
+      </c>
+      <c r="AH471" s="2" t="n">
+        <v>-0.002775208140610514</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -47721,6 +50553,12 @@
       <c r="AF472" s="2" t="n">
         <v>-0.007090522335145395</v>
       </c>
+      <c r="AG472" s="1" t="n">
+        <v>0.04189</v>
+      </c>
+      <c r="AH472" s="2" t="n">
+        <v>-0.002856462746965057</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -47821,6 +50659,12 @@
       <c r="AF473" s="2" t="n">
         <v>-0.0007949125596185309</v>
       </c>
+      <c r="AG473" s="1" t="n">
+        <v>1.254</v>
+      </c>
+      <c r="AH473" s="2" t="n">
+        <v>-0.002386634844868649</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -47921,6 +50765,12 @@
       <c r="AF474" s="3" t="n">
         <v>0.0002333994631812657</v>
       </c>
+      <c r="AG474" s="1" t="n">
+        <v>0.008562</v>
+      </c>
+      <c r="AH474" s="2" t="n">
+        <v>-0.001050052502625169</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -48021,6 +50871,12 @@
       <c r="AF475" s="3" t="n">
         <v>0.002629691608893115</v>
       </c>
+      <c r="AG475" s="1" t="n">
+        <v>0.04178</v>
+      </c>
+      <c r="AH475" s="2" t="n">
+        <v>-0.003814973772055327</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -48121,6 +50977,12 @@
       <c r="AF476" s="2" t="n">
         <v>-0.001134215500945264</v>
       </c>
+      <c r="AG476" s="1" t="n">
+        <v>0.07922</v>
+      </c>
+      <c r="AH476" s="2" t="n">
+        <v>-0.0005046681806711882</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -48221,6 +51083,12 @@
       <c r="AF477" s="2" t="n">
         <v>-0.0002935564362247504</v>
       </c>
+      <c r="AG477" s="1" t="n">
+        <v>0.13635</v>
+      </c>
+      <c r="AH477" s="3" t="n">
+        <v>0.0009543385699602938</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -48321,6 +51189,12 @@
       <c r="AF478" s="3" t="n">
         <v>0.0006323777403034424</v>
       </c>
+      <c r="AG478" s="1" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="AH478" s="3" t="n">
+        <v>0.0006319780914262113</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -48421,6 +51295,12 @@
       <c r="AF479" s="2" t="n">
         <v>-0.0003740415186086152</v>
       </c>
+      <c r="AG479" s="1" t="n">
+        <v>0.005344</v>
+      </c>
+      <c r="AH479" s="2" t="n">
+        <v>-0.0001870907390084439</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -48521,6 +51401,12 @@
       <c r="AF480" s="2" t="n">
         <v>-0.00141995030173948</v>
       </c>
+      <c r="AG480" s="1" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="AH480" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -48621,6 +51507,12 @@
       <c r="AF481" s="2" t="n">
         <v>-0.0001316309069368978</v>
       </c>
+      <c r="AG481" s="1" t="n">
+        <v>0.07599</v>
+      </c>
+      <c r="AH481" s="3" t="n">
+        <v>0.0003949447077409459</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -48721,6 +51613,12 @@
       <c r="AF482" s="2" t="n">
         <v>-0.001341381623071709</v>
       </c>
+      <c r="AG482" s="1" t="n">
+        <v>0.01492</v>
+      </c>
+      <c r="AH482" s="3" t="n">
+        <v>0.00201477501678971</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -48821,6 +51719,12 @@
       <c r="AF483" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG483" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="AH483" s="3" t="n">
+        <v>0.003984063745019896</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -48921,6 +51825,12 @@
       <c r="AF484" s="2" t="n">
         <v>-0.001849283402681386</v>
       </c>
+      <c r="AG484" s="1" t="n">
+        <v>0.02158</v>
+      </c>
+      <c r="AH484" s="2" t="n">
+        <v>-0.000463177396943171</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -49021,6 +51931,12 @@
       <c r="AF485" s="3" t="n">
         <v>0.001075654356400183</v>
       </c>
+      <c r="AG485" s="1" t="n">
+        <v>0.008343</v>
+      </c>
+      <c r="AH485" s="2" t="n">
+        <v>-0.003939828080229231</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -49121,6 +52037,12 @@
       <c r="AF486" s="2" t="n">
         <v>-0.001333688983729056</v>
       </c>
+      <c r="AG486" s="1" t="n">
+        <v>0.007493</v>
+      </c>
+      <c r="AH486" s="3" t="n">
+        <v>0.0006677350427350155</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -49221,6 +52143,12 @@
       <c r="AF487" s="3" t="n">
         <v>0.007765314926660897</v>
       </c>
+      <c r="AG487" s="1" t="n">
+        <v>0.1136</v>
+      </c>
+      <c r="AH487" s="2" t="n">
+        <v>-0.02739726027397256</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -49321,6 +52249,12 @@
       <c r="AF488" s="2" t="n">
         <v>-0.002816901408450702</v>
       </c>
+      <c r="AG488" s="1" t="n">
+        <v>0.009221999999999999</v>
+      </c>
+      <c r="AH488" s="3" t="n">
+        <v>0.001955671447196754</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -49421,6 +52355,12 @@
       <c r="AF489" s="3" t="n">
         <v>0.005908040071923993</v>
       </c>
+      <c r="AG489" s="1" t="n">
+        <v>0.03929</v>
+      </c>
+      <c r="AH489" s="3" t="n">
+        <v>0.003319713993871251</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -49521,6 +52461,12 @@
       <c r="AF490" s="3" t="n">
         <v>0.006560773480662955</v>
       </c>
+      <c r="AG490" s="1" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="AH490" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -49621,6 +52567,12 @@
       <c r="AF491" s="3" t="n">
         <v>0.004106776180698127</v>
       </c>
+      <c r="AG491" s="1" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="AH491" s="2" t="n">
+        <v>-0.002044989775051042</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -49721,6 +52673,12 @@
       <c r="AF492" s="3" t="n">
         <v>0.003012048192771087</v>
       </c>
+      <c r="AG492" s="1" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="AH492" s="2" t="n">
+        <v>-0.005255255255255343</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -49821,6 +52779,12 @@
       <c r="AF493" s="3" t="n">
         <v>0.0005668934240362581</v>
       </c>
+      <c r="AG493" s="1" t="n">
+        <v>0.03527</v>
+      </c>
+      <c r="AH493" s="2" t="n">
+        <v>-0.0008498583569403771</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -49921,6 +52885,12 @@
       <c r="AF494" s="2" t="n">
         <v>-0.004105571847507368</v>
       </c>
+      <c r="AG494" s="1" t="n">
+        <v>0.01695</v>
+      </c>
+      <c r="AH494" s="2" t="n">
+        <v>-0.001766784452296748</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -50021,6 +52991,12 @@
       <c r="AF495" s="3" t="n">
         <v>0.0002115506663846639</v>
       </c>
+      <c r="AG495" s="1" t="n">
+        <v>0.04722</v>
+      </c>
+      <c r="AH495" s="2" t="n">
+        <v>-0.001269035532995019</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -50121,6 +53097,12 @@
       <c r="AF496" s="2" t="n">
         <v>-0.0006189395502373066</v>
       </c>
+      <c r="AG496" s="1" t="n">
+        <v>0.04843</v>
+      </c>
+      <c r="AH496" s="2" t="n">
+        <v>-0.0002064409578859646</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -50221,6 +53203,12 @@
       <c r="AF497" s="2" t="n">
         <v>-0.0006021678040947861</v>
       </c>
+      <c r="AG497" s="1" t="n">
+        <v>0.04979</v>
+      </c>
+      <c r="AH497" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -50321,6 +53309,12 @@
       <c r="AF498" s="2" t="n">
         <v>-0.0003453038674034685</v>
       </c>
+      <c r="AG498" s="1" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="AH498" s="2" t="n">
+        <v>-0.001727115716753024</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -50421,6 +53415,12 @@
       <c r="AF499" s="3" t="n">
         <v>0.0003641660597231937</v>
       </c>
+      <c r="AG499" s="1" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="AH499" s="2" t="n">
+        <v>-0.002184200946487038</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -50521,6 +53521,12 @@
       <c r="AF500" s="3" t="n">
         <v>0.003745318352059935</v>
       </c>
+      <c r="AG500" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="AH500" s="2" t="n">
+        <v>-0.003731343283582099</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -50621,6 +53627,12 @@
       <c r="AF501" s="3" t="n">
         <v>0.0008372871895060632</v>
       </c>
+      <c r="AG501" s="1" t="n">
+        <v>0.03581</v>
+      </c>
+      <c r="AH501" s="2" t="n">
+        <v>-0.00139431121026217</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -50721,6 +53733,12 @@
       <c r="AF502" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG502" s="1" t="n">
+        <v>0.03187</v>
+      </c>
+      <c r="AH502" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -50821,6 +53839,12 @@
       <c r="AF503" s="3" t="n">
         <v>0.004367934224049354</v>
       </c>
+      <c r="AG503" s="1" t="n">
+        <v>0.007792</v>
+      </c>
+      <c r="AH503" s="2" t="n">
+        <v>-0.003325658736249678</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -50921,6 +53945,12 @@
       <c r="AF504" s="2" t="n">
         <v>-0.003943476832073614</v>
       </c>
+      <c r="AG504" s="1" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AH504" s="2" t="n">
+        <v>-0.000329924117453096</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -51021,6 +54051,12 @@
       <c r="AF505" s="3" t="n">
         <v>0.001210165389269823</v>
       </c>
+      <c r="AG505" s="1" t="n">
+        <v>0.0007443</v>
+      </c>
+      <c r="AH505" s="2" t="n">
+        <v>-0.000402900886381887</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -51121,6 +54157,12 @@
       <c r="AF506" s="2" t="n">
         <v>-0.001369863013698479</v>
       </c>
+      <c r="AG506" s="1" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="AH506" s="3" t="n">
+        <v>0.000685871056241351</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -51221,6 +54263,12 @@
       <c r="AF507" s="2" t="n">
         <v>-0.002091321017776204</v>
       </c>
+      <c r="AG507" s="1" t="n">
+        <v>0.00287</v>
+      </c>
+      <c r="AH507" s="3" t="n">
+        <v>0.002444987775061146</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -51321,6 +54369,12 @@
       <c r="AF508" s="2" t="n">
         <v>-0.000473484848484884</v>
       </c>
+      <c r="AG508" s="1" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="AH508" s="3" t="n">
+        <v>0.001105321332701731</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -51421,6 +54475,12 @@
       <c r="AF509" s="2" t="n">
         <v>-0.003568242640499557</v>
       </c>
+      <c r="AG509" s="1" t="n">
+        <v>2.228</v>
+      </c>
+      <c r="AH509" s="2" t="n">
+        <v>-0.002685765443151201</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -51521,6 +54581,12 @@
       <c r="AF510" s="2" t="n">
         <v>-0.0005438477226376746</v>
       </c>
+      <c r="AG510" s="1" t="n">
+        <v>0.0007359000000000001</v>
+      </c>
+      <c r="AH510" s="3" t="n">
+        <v>0.001088287307849299</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -51621,6 +54687,12 @@
       <c r="AF511" s="2" t="n">
         <v>-0.002895403546869227</v>
       </c>
+      <c r="AG511" s="1" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="AH511" s="3" t="n">
+        <v>0.0003629764065335353</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -51721,6 +54793,12 @@
       <c r="AF512" s="3" t="n">
         <v>0.0002071251035624445</v>
       </c>
+      <c r="AG512" s="1" t="n">
+        <v>0.0004833</v>
+      </c>
+      <c r="AH512" s="3" t="n">
+        <v>0.0008283288465521013</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -51821,6 +54899,12 @@
       <c r="AF513" s="2" t="n">
         <v>-0.0003607503607504712</v>
       </c>
+      <c r="AG513" s="1" t="n">
+        <v>0.05537</v>
+      </c>
+      <c r="AH513" s="2" t="n">
+        <v>-0.0009022013713459851</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -51921,6 +55005,12 @@
       <c r="AF514" s="2" t="n">
         <v>-0.0009871668311944317</v>
       </c>
+      <c r="AG514" s="1" t="n">
+        <v>0.03027</v>
+      </c>
+      <c r="AH514" s="2" t="n">
+        <v>-0.002964426877470464</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -52021,6 +55111,12 @@
       <c r="AF515" s="2" t="n">
         <v>-0.0008771929824560666</v>
       </c>
+      <c r="AG515" s="1" t="n">
+        <v>0.001139</v>
+      </c>
+      <c r="AH515" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -52121,6 +55217,12 @@
       <c r="AF516" s="3" t="n">
         <v>0.0009027986758952647</v>
       </c>
+      <c r="AG516" s="1" t="n">
+        <v>0.006626</v>
+      </c>
+      <c r="AH516" s="2" t="n">
+        <v>-0.003908598917618759</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -52221,6 +55323,12 @@
       <c r="AF517" s="2" t="n">
         <v>-0.0002507522567702137</v>
       </c>
+      <c r="AG517" s="1" t="n">
+        <v>0.03988</v>
+      </c>
+      <c r="AH517" s="3" t="n">
+        <v>0.0002508151492349165</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -52321,6 +55429,12 @@
       <c r="AF518" s="2" t="n">
         <v>-0.0009652509652509929</v>
       </c>
+      <c r="AG518" s="1" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="AH518" s="3" t="n">
+        <v>0.00193236714975851</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -52421,6 +55535,12 @@
       <c r="AF519" s="2" t="n">
         <v>-0.004561003420752578</v>
       </c>
+      <c r="AG519" s="1" t="n">
+        <v>0.00873</v>
+      </c>
+      <c r="AH519" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -52521,6 +55641,12 @@
       <c r="AF520" s="3" t="n">
         <v>0.0006234413965088326</v>
       </c>
+      <c r="AG520" s="1" t="n">
+        <v>0.1607</v>
+      </c>
+      <c r="AH520" s="3" t="n">
+        <v>0.001246105919003151</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -52621,6 +55747,12 @@
       <c r="AF521" s="2" t="n">
         <v>-0.002235885969815448</v>
       </c>
+      <c r="AG521" s="1" t="n">
+        <v>0.01793</v>
+      </c>
+      <c r="AH521" s="3" t="n">
+        <v>0.004481792717086847</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -52721,6 +55853,12 @@
       <c r="AF522" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG522" s="1" t="n">
+        <v>0.01643</v>
+      </c>
+      <c r="AH522" s="2" t="n">
+        <v>-0.001822600243013292</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -52821,6 +55959,12 @@
       <c r="AF523" s="2" t="n">
         <v>-0.000720288115246194</v>
       </c>
+      <c r="AG523" s="1" t="n">
+        <v>0.004146</v>
+      </c>
+      <c r="AH523" s="2" t="n">
+        <v>-0.003844305622296858</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -52921,6 +56065,12 @@
       <c r="AF524" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG524" s="1" t="n">
+        <v>0.01428</v>
+      </c>
+      <c r="AH524" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -53021,6 +56171,12 @@
       <c r="AF525" s="3" t="n">
         <v>0.003238866396761142</v>
       </c>
+      <c r="AG525" s="1" t="n">
+        <v>0.02483</v>
+      </c>
+      <c r="AH525" s="3" t="n">
+        <v>0.002017756255044449</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -53121,6 +56277,12 @@
       <c r="AF526" s="2" t="n">
         <v>-0.000829875518672223</v>
       </c>
+      <c r="AG526" s="1" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="AH526" s="2" t="n">
+        <v>-0.0008305647840530648</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -53221,6 +56383,12 @@
       <c r="AF527" s="3" t="n">
         <v>0.001111111111111259</v>
       </c>
+      <c r="AG527" s="1" t="n">
+        <v>0.07192</v>
+      </c>
+      <c r="AH527" s="2" t="n">
+        <v>-0.002219755826859147</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -53321,6 +56489,12 @@
       <c r="AF528" s="3" t="n">
         <v>0.0002306805074971871</v>
       </c>
+      <c r="AG528" s="1" t="n">
+        <v>0.04335</v>
+      </c>
+      <c r="AH528" s="2" t="n">
+        <v>-0.0002306273062731333</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -53421,6 +56595,12 @@
       <c r="AF529" s="2" t="n">
         <v>-0.001108296390120339</v>
       </c>
+      <c r="AG529" s="1" t="n">
+        <v>0.06319</v>
+      </c>
+      <c r="AH529" s="3" t="n">
+        <v>0.001585037248375382</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -53521,6 +56701,12 @@
       <c r="AF530" s="2" t="n">
         <v>-0.001389992057188257</v>
       </c>
+      <c r="AG530" s="1" t="n">
+        <v>0.005019</v>
+      </c>
+      <c r="AH530" s="2" t="n">
+        <v>-0.001988466892026167</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -53621,6 +56807,12 @@
       <c r="AF531" s="2" t="n">
         <v>-0.001536098310291902</v>
       </c>
+      <c r="AG531" s="1" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="AH531" s="3" t="n">
+        <v>0.0007692307692306844</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -53721,6 +56913,12 @@
       <c r="AF532" s="3" t="n">
         <v>0.007900677200903004</v>
       </c>
+      <c r="AG532" s="1" t="n">
+        <v>0.05357</v>
+      </c>
+      <c r="AH532" s="2" t="n">
+        <v>-0.0001866368047779593</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -53821,6 +57019,12 @@
       <c r="AF533" s="3" t="n">
         <v>0.003213711837172012</v>
       </c>
+      <c r="AG533" s="1" t="n">
+        <v>0.00377</v>
+      </c>
+      <c r="AH533" s="3" t="n">
+        <v>0.006406833956219892</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -53921,6 +57125,12 @@
       <c r="AF534" s="2" t="n">
         <v>-0.001743172574084804</v>
       </c>
+      <c r="AG534" s="1" t="n">
+        <v>0.1721</v>
+      </c>
+      <c r="AH534" s="3" t="n">
+        <v>0.001746216530849795</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -54021,6 +57231,12 @@
       <c r="AF535" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="AH535" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -54121,6 +57337,12 @@
       <c r="AF536" s="3" t="n">
         <v>0.0002266545784224896</v>
       </c>
+      <c r="AG536" s="1" t="n">
+        <v>0.0004409</v>
+      </c>
+      <c r="AH536" s="2" t="n">
+        <v>-0.0009064128710627911</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -54221,6 +57443,12 @@
       <c r="AF537" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AG537" s="1" t="n">
+        <v>0.00967</v>
+      </c>
+      <c r="AH537" s="2" t="n">
+        <v>-0.001033057851239627</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -54321,6 +57549,12 @@
       <c r="AF538" s="3" t="n">
         <v>0.0003666361136571803</v>
       </c>
+      <c r="AG538" s="1" t="n">
+        <v>0.05461</v>
+      </c>
+      <c r="AH538" s="3" t="n">
+        <v>0.0007330034817665085</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -54421,6 +57655,12 @@
       <c r="AF539" s="2" t="n">
         <v>-0.0001466705778820607</v>
       </c>
+      <c r="AG539" s="1" t="n">
+        <v>0.6814</v>
+      </c>
+      <c r="AH539" s="2" t="n">
+        <v>-0.0004400762798884656</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -54521,6 +57761,12 @@
       <c r="AF540" s="2" t="n">
         <v>-0.001982815598149337</v>
       </c>
+      <c r="AG540" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="AH540" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -54621,6 +57867,12 @@
       <c r="AF541" s="2" t="n">
         <v>-0.00229709035222056</v>
       </c>
+      <c r="AG541" s="1" t="n">
+        <v>0.01298</v>
+      </c>
+      <c r="AH541" s="2" t="n">
+        <v>-0.003837298541826531</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -54721,6 +57973,12 @@
       <c r="AF542" s="3" t="n">
         <v>0.002881844380403466</v>
       </c>
+      <c r="AG542" s="1" t="n">
+        <v>0.01382</v>
+      </c>
+      <c r="AH542" s="2" t="n">
+        <v>-0.007183908045976968</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -54821,6 +58079,12 @@
       <c r="AF543" s="3" t="n">
         <v>0.001577287066246053</v>
       </c>
+      <c r="AG543" s="1" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="AH543" s="3" t="n">
+        <v>0.0008748906386701913</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH543"/>
+  <dimension ref="A1:AJ543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -460,6 +460,8 @@
     <col width="18" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,6 +635,16 @@
           <t>change_04:00</t>
         </is>
       </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>price_04:15</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>change_04:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -739,6 +751,12 @@
       <c r="AH2" s="3" t="n">
         <v>0.001885696882409365</v>
       </c>
+      <c r="AI2" s="1" t="n">
+        <v>70347.2</v>
+      </c>
+      <c r="AJ2" s="2" t="n">
+        <v>-0.0007258698008333415</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -845,6 +863,12 @@
       <c r="AH3" s="3" t="n">
         <v>0.0009481424148606988</v>
       </c>
+      <c r="AI3" s="1" t="n">
+        <v>2066</v>
+      </c>
+      <c r="AJ3" s="2" t="n">
+        <v>-0.001527189777494179</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -951,6 +975,12 @@
       <c r="AH4" s="3" t="n">
         <v>0.001384721901684798</v>
       </c>
+      <c r="AI4" s="1" t="n">
+        <v>86.65000000000001</v>
+      </c>
+      <c r="AJ4" s="2" t="n">
+        <v>-0.0014980410232772</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1057,6 +1087,12 @@
       <c r="AH5" s="3" t="n">
         <v>0.002195704057279279</v>
       </c>
+      <c r="AI5" s="1" t="n">
+        <v>0.010643</v>
+      </c>
+      <c r="AJ5" s="3" t="n">
+        <v>0.01381215469613253</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1163,6 +1199,12 @@
       <c r="AH6" s="2" t="n">
         <v>-7.255314517883551e-05</v>
       </c>
+      <c r="AI6" s="1" t="n">
+        <v>1.3743</v>
+      </c>
+      <c r="AJ6" s="2" t="n">
+        <v>-0.00282977797126688</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1269,6 +1311,12 @@
       <c r="AH7" s="3" t="n">
         <v>0.0006359974560102236</v>
       </c>
+      <c r="AI7" s="1" t="n">
+        <v>0.09435</v>
+      </c>
+      <c r="AJ7" s="2" t="n">
+        <v>-0.0005296610169490942</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1375,6 +1423,12 @@
       <c r="AH8" s="2" t="n">
         <v>-0.002769934113217736</v>
       </c>
+      <c r="AI8" s="1" t="n">
+        <v>36.931</v>
+      </c>
+      <c r="AJ8" s="2" t="n">
+        <v>-0.004072056523380706</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1481,6 +1535,12 @@
       <c r="AH9" s="2" t="n">
         <v>-0.002395209580838365</v>
       </c>
+      <c r="AI9" s="1" t="n">
+        <v>0.04934</v>
+      </c>
+      <c r="AJ9" s="2" t="n">
+        <v>-0.01280512204881942</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1587,6 +1647,12 @@
       <c r="AH10" s="2" t="n">
         <v>-0.005655194700274704</v>
       </c>
+      <c r="AI10" s="1" t="n">
+        <v>18.335</v>
+      </c>
+      <c r="AJ10" s="2" t="n">
+        <v>-0.006878994691799312</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1693,6 +1759,12 @@
       <c r="AH11" s="3" t="n">
         <v>0.0007835906890988567</v>
       </c>
+      <c r="AI11" s="1" t="n">
+        <v>650.62</v>
+      </c>
+      <c r="AJ11" s="2" t="n">
+        <v>-0.001136084500122834</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1799,6 +1871,12 @@
       <c r="AH12" s="3" t="n">
         <v>0.002135791366906489</v>
       </c>
+      <c r="AI12" s="1" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="AJ12" s="2" t="n">
+        <v>-0.0006730229949522534</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1905,6 +1983,12 @@
       <c r="AH13" s="2" t="n">
         <v>-0.001195600191296031</v>
       </c>
+      <c r="AI13" s="1" t="n">
+        <v>208.02</v>
+      </c>
+      <c r="AJ13" s="2" t="n">
+        <v>-0.003974144122575935</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2011,6 +2095,12 @@
       <c r="AH14" s="3" t="n">
         <v>0.002721861633715242</v>
       </c>
+      <c r="AI14" s="1" t="n">
+        <v>0.0033453</v>
+      </c>
+      <c r="AJ14" s="2" t="n">
+        <v>-0.002117885693831385</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2117,6 +2207,12 @@
       <c r="AH15" s="2" t="n">
         <v>-0.008673987265848448</v>
       </c>
+      <c r="AI15" s="1" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AJ15" s="2" t="n">
+        <v>-0.003351019268360872</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2223,6 +2319,12 @@
       <c r="AH16" s="3" t="n">
         <v>0.0001021450459652594</v>
       </c>
+      <c r="AI16" s="1" t="n">
+        <v>0.9758</v>
+      </c>
+      <c r="AJ16" s="2" t="n">
+        <v>-0.00337044224287608</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2329,6 +2431,12 @@
       <c r="AH17" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI17" s="1" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="AJ17" s="2" t="n">
+        <v>-0.01498127340823974</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2435,6 +2543,12 @@
       <c r="AH18" s="3" t="n">
         <v>0.0005155122316993797</v>
       </c>
+      <c r="AI18" s="1" t="n">
+        <v>213.75</v>
+      </c>
+      <c r="AJ18" s="3" t="n">
+        <v>0.00121785563726634</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2541,6 +2655,12 @@
       <c r="AH19" s="3" t="n">
         <v>0.002668699961875844</v>
       </c>
+      <c r="AI19" s="1" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="AJ19" s="2" t="n">
+        <v>-0.001901140684410648</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2647,6 +2767,12 @@
       <c r="AH20" s="3" t="n">
         <v>0.0004133451431945711</v>
       </c>
+      <c r="AI20" s="1" t="n">
+        <v>0.017001</v>
+      </c>
+      <c r="AJ20" s="3" t="n">
+        <v>0.003482469602172118</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2753,6 +2879,12 @@
       <c r="AH21" s="3" t="n">
         <v>0.0008339414156156463</v>
       </c>
+      <c r="AI21" s="1" t="n">
+        <v>9.598000000000001</v>
+      </c>
+      <c r="AJ21" s="2" t="n">
+        <v>-0.0003124674513071673</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2859,6 +2991,12 @@
       <c r="AH22" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI22" s="1" t="n">
+        <v>0.1669</v>
+      </c>
+      <c r="AJ22" s="2" t="n">
+        <v>-0.007728894173602828</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2965,6 +3103,12 @@
       <c r="AH23" s="2" t="n">
         <v>-0.0038930703348041</v>
       </c>
+      <c r="AI23" s="1" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="AJ23" s="3" t="n">
+        <v>0.005008395576399772</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3071,6 +3215,12 @@
       <c r="AH24" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI24" s="1" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="AJ24" s="2" t="n">
+        <v>-0.005747126436781614</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3177,6 +3327,12 @@
       <c r="AH25" s="3" t="n">
         <v>0.00133052444838679</v>
       </c>
+      <c r="AI25" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ25" s="2" t="n">
+        <v>-0.003432620972206907</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3283,6 +3439,12 @@
       <c r="AH26" s="2" t="n">
         <v>-0.005200594353640503</v>
       </c>
+      <c r="AI26" s="1" t="n">
+        <v>1.329</v>
+      </c>
+      <c r="AJ26" s="2" t="n">
+        <v>-0.007468259895444368</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3389,6 +3551,12 @@
       <c r="AH27" s="2" t="n">
         <v>-0.001033994278695701</v>
       </c>
+      <c r="AI27" s="1" t="n">
+        <v>5093.27</v>
+      </c>
+      <c r="AJ27" s="3" t="n">
+        <v>0.0003535324768682094</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3495,6 +3663,12 @@
       <c r="AH28" s="2" t="n">
         <v>-0.005523336095001386</v>
       </c>
+      <c r="AI28" s="1" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="AJ28" s="2" t="n">
+        <v>-0.003610108303249008</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3601,6 +3775,12 @@
       <c r="AH29" s="2" t="n">
         <v>-0.0007593014426726575</v>
       </c>
+      <c r="AI29" s="1" t="n">
+        <v>2.636</v>
+      </c>
+      <c r="AJ29" s="3" t="n">
+        <v>0.001519756838905776</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3707,6 +3887,12 @@
       <c r="AH30" s="3" t="n">
         <v>0.0006605593895041407</v>
       </c>
+      <c r="AI30" s="1" t="n">
+        <v>0.57436</v>
+      </c>
+      <c r="AJ30" s="2" t="n">
+        <v>-0.002240945018674565</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3813,6 +3999,12 @@
       <c r="AH31" s="2" t="n">
         <v>-0.0009546539379476207</v>
       </c>
+      <c r="AI31" s="1" t="n">
+        <v>0.002082</v>
+      </c>
+      <c r="AJ31" s="2" t="n">
+        <v>-0.005255613951265994</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3919,6 +4111,12 @@
       <c r="AH32" s="2" t="n">
         <v>-0.005855068055661198</v>
       </c>
+      <c r="AI32" s="1" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="AJ32" s="2" t="n">
+        <v>-0.01407373412880524</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4025,6 +4223,12 @@
       <c r="AH33" s="3" t="n">
         <v>0.007566585956416303</v>
       </c>
+      <c r="AI33" s="1" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="AJ33" s="3" t="n">
+        <v>0.008711324722138822</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4131,6 +4335,12 @@
       <c r="AH34" s="2" t="n">
         <v>-0.001326259946949603</v>
       </c>
+      <c r="AI34" s="1" t="n">
+        <v>1.507</v>
+      </c>
+      <c r="AJ34" s="3" t="n">
+        <v>0.0006640106241699136</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4237,6 +4447,12 @@
       <c r="AH35" s="2" t="n">
         <v>-0.0001973208217316696</v>
       </c>
+      <c r="AI35" s="1" t="n">
+        <v>454.56</v>
+      </c>
+      <c r="AJ35" s="2" t="n">
+        <v>-0.003201613964299767</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4343,6 +4559,12 @@
       <c r="AH36" s="2" t="n">
         <v>-0.001254180602006638</v>
       </c>
+      <c r="AI36" s="1" t="n">
+        <v>0.04757</v>
+      </c>
+      <c r="AJ36" s="2" t="n">
+        <v>-0.004395144411887857</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4449,6 +4671,12 @@
       <c r="AH37" s="2" t="n">
         <v>-0.0009960159362550284</v>
       </c>
+      <c r="AI37" s="1" t="n">
+        <v>0.7004</v>
+      </c>
+      <c r="AJ37" s="2" t="n">
+        <v>-0.00242130750605316</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4555,6 +4783,12 @@
       <c r="AH38" s="3" t="n">
         <v>0.0009433962264151213</v>
       </c>
+      <c r="AI38" s="1" t="n">
+        <v>0.1058</v>
+      </c>
+      <c r="AJ38" s="2" t="n">
+        <v>-0.002827521206408998</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4661,6 +4895,12 @@
       <c r="AH39" s="3" t="n">
         <v>0.001975219967678209</v>
       </c>
+      <c r="AI39" s="1" t="n">
+        <v>111.31</v>
+      </c>
+      <c r="AJ39" s="2" t="n">
+        <v>-0.002598566308243656</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4767,6 +5007,12 @@
       <c r="AH40" s="2" t="n">
         <v>-0.003822003822003855</v>
       </c>
+      <c r="AI40" s="1" t="n">
+        <v>0.03647</v>
+      </c>
+      <c r="AJ40" s="2" t="n">
+        <v>-0.000548095368594113</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4873,6 +5119,12 @@
       <c r="AH41" s="2" t="n">
         <v>-0.0009117432530999532</v>
       </c>
+      <c r="AI41" s="1" t="n">
+        <v>0.05473</v>
+      </c>
+      <c r="AJ41" s="2" t="n">
+        <v>-0.001095090344953414</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4979,6 +5231,12 @@
       <c r="AH42" s="2" t="n">
         <v>-0.0003683919690550013</v>
       </c>
+      <c r="AI42" s="1" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="AJ42" s="2" t="n">
+        <v>-0.001842638658559083</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5085,6 +5343,12 @@
       <c r="AH43" s="2" t="n">
         <v>-0.009694258016405635</v>
       </c>
+      <c r="AI43" s="1" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="AJ43" s="2" t="n">
+        <v>-0.009036144578313303</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5191,6 +5455,12 @@
       <c r="AH44" s="3" t="n">
         <v>0.001181235234559578</v>
       </c>
+      <c r="AI44" s="1" t="n">
+        <v>0.005915</v>
+      </c>
+      <c r="AJ44" s="2" t="n">
+        <v>-0.003033878307770064</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5297,6 +5567,12 @@
       <c r="AH45" s="3" t="n">
         <v>0.005922505520979656</v>
       </c>
+      <c r="AI45" s="1" t="n">
+        <v>0.09972</v>
+      </c>
+      <c r="AJ45" s="2" t="n">
+        <v>-0.004889731563716101</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5403,6 +5679,12 @@
       <c r="AH46" s="2" t="n">
         <v>-0.04907377315567105</v>
       </c>
+      <c r="AI46" s="1" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AJ46" s="3" t="n">
+        <v>0.008202323991797683</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5509,6 +5791,12 @@
       <c r="AH47" s="2" t="n">
         <v>-0.0002424578296561064</v>
       </c>
+      <c r="AI47" s="1" t="n">
+        <v>0.28867</v>
+      </c>
+      <c r="AJ47" s="3" t="n">
+        <v>0.0001039356984478052</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5615,6 +5903,12 @@
       <c r="AH48" s="2" t="n">
         <v>-0.004672897196261686</v>
       </c>
+      <c r="AI48" s="1" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="AJ48" s="2" t="n">
+        <v>-0.01220657276995301</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5721,6 +6015,12 @@
       <c r="AH49" s="2" t="n">
         <v>-0.0007337654396478476</v>
       </c>
+      <c r="AI49" s="1" t="n">
+        <v>0.24414</v>
+      </c>
+      <c r="AJ49" s="2" t="n">
+        <v>-0.004038673356994211</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5827,6 +6127,12 @@
       <c r="AH50" s="3" t="n">
         <v>0.002285002077274595</v>
       </c>
+      <c r="AI50" s="1" t="n">
+        <v>0.04813</v>
+      </c>
+      <c r="AJ50" s="2" t="n">
+        <v>-0.002487046632124395</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5933,6 +6239,12 @@
       <c r="AH51" s="3" t="n">
         <v>0.001024327784891166</v>
       </c>
+      <c r="AI51" s="1" t="n">
+        <v>3.901</v>
+      </c>
+      <c r="AJ51" s="2" t="n">
+        <v>-0.002046559222307497</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6039,6 +6351,12 @@
       <c r="AH52" s="3" t="n">
         <v>0.008810572687224764</v>
       </c>
+      <c r="AI52" s="1" t="n">
+        <v>0.000227</v>
+      </c>
+      <c r="AJ52" s="2" t="n">
+        <v>-0.008733624454148565</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6145,6 +6463,12 @@
       <c r="AH53" s="3" t="n">
         <v>0.0005903187721370528</v>
       </c>
+      <c r="AI53" s="1" t="n">
+        <v>0.1688</v>
+      </c>
+      <c r="AJ53" s="2" t="n">
+        <v>-0.00412979351032452</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6251,6 +6575,12 @@
       <c r="AH54" s="2" t="n">
         <v>-0.005213270142180046</v>
       </c>
+      <c r="AI54" s="1" t="n">
+        <v>0.04169</v>
+      </c>
+      <c r="AJ54" s="2" t="n">
+        <v>-0.006908051453073023</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6357,6 +6687,12 @@
       <c r="AH55" s="2" t="n">
         <v>-0.003829544528640203</v>
       </c>
+      <c r="AI55" s="1" t="n">
+        <v>0.12358</v>
+      </c>
+      <c r="AJ55" s="3" t="n">
+        <v>0.01079666284966466</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6463,6 +6799,12 @@
       <c r="AH56" s="2" t="n">
         <v>-0.0009511731135067294</v>
       </c>
+      <c r="AI56" s="1" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="AJ56" s="2" t="n">
+        <v>-0.001904157410345888</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6569,6 +6911,12 @@
       <c r="AH57" s="2" t="n">
         <v>-0.005199306759098726</v>
       </c>
+      <c r="AI57" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="AJ57" s="3" t="n">
+        <v>0.001742160278745573</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6675,6 +7023,12 @@
       <c r="AH58" s="3" t="n">
         <v>0.0009980039920159966</v>
       </c>
+      <c r="AI58" s="1" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="AJ58" s="2" t="n">
+        <v>-0.004985044865403793</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6781,6 +7135,12 @@
       <c r="AH59" s="3" t="n">
         <v>0.003003003003003011</v>
       </c>
+      <c r="AI59" s="1" t="n">
+        <v>0.00332</v>
+      </c>
+      <c r="AJ59" s="2" t="n">
+        <v>-0.005988023952095824</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6887,6 +7247,12 @@
       <c r="AH60" s="2" t="n">
         <v>-0.001282051282051319</v>
       </c>
+      <c r="AI60" s="1" t="n">
+        <v>0.1551</v>
+      </c>
+      <c r="AJ60" s="2" t="n">
+        <v>-0.004492939666238808</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6993,6 +7359,12 @@
       <c r="AH61" s="3" t="n">
         <v>0.001251956181533682</v>
       </c>
+      <c r="AI61" s="1" t="n">
+        <v>0.15968</v>
+      </c>
+      <c r="AJ61" s="2" t="n">
+        <v>-0.001688027508596563</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7099,6 +7471,12 @@
       <c r="AH62" s="2" t="n">
         <v>-0.0005609311457018034</v>
       </c>
+      <c r="AI62" s="1" t="n">
+        <v>0.7086</v>
+      </c>
+      <c r="AJ62" s="2" t="n">
+        <v>-0.005752771151957335</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7205,6 +7583,12 @@
       <c r="AH63" s="3" t="n">
         <v>0.001321658681645466</v>
       </c>
+      <c r="AI63" s="1" t="n">
+        <v>6.068</v>
+      </c>
+      <c r="AJ63" s="3" t="n">
+        <v>0.001154924929879504</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7311,6 +7695,12 @@
       <c r="AH64" s="3" t="n">
         <v>0.002219447912331741</v>
       </c>
+      <c r="AI64" s="1" t="n">
+        <v>0.007193</v>
+      </c>
+      <c r="AJ64" s="2" t="n">
+        <v>-0.004429065743944625</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7417,6 +7807,12 @@
       <c r="AH65" s="3" t="n">
         <v>0.01211180124223607</v>
       </c>
+      <c r="AI65" s="1" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="AJ65" s="2" t="n">
+        <v>-0.01503528689782155</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7523,6 +7919,12 @@
       <c r="AH66" s="3" t="n">
         <v>0.004273504273504159</v>
       </c>
+      <c r="AI66" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="AJ66" s="2" t="n">
+        <v>-0.004255319148936056</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7629,6 +8031,12 @@
       <c r="AH67" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI67" s="1" t="n">
+        <v>1.629</v>
+      </c>
+      <c r="AJ67" s="3" t="n">
+        <v>0.00679851668726817</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7735,6 +8143,12 @@
       <c r="AH68" s="2" t="n">
         <v>-0.0003439296418216975</v>
       </c>
+      <c r="AI68" s="1" t="n">
+        <v>2.0232</v>
+      </c>
+      <c r="AJ68" s="2" t="n">
+        <v>-0.00560306694190508</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7841,6 +8255,12 @@
       <c r="AH69" s="2" t="n">
         <v>-0.00136379133992503</v>
       </c>
+      <c r="AI69" s="1" t="n">
+        <v>0.5885</v>
+      </c>
+      <c r="AJ69" s="3" t="n">
+        <v>0.004609081597815015</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7947,6 +8367,12 @@
       <c r="AH70" s="2" t="n">
         <v>-0.009708737864077679</v>
       </c>
+      <c r="AI70" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AJ70" s="3" t="n">
+        <v>0.00980392156862746</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8053,6 +8479,12 @@
       <c r="AH71" s="2" t="n">
         <v>-0.0009870585654748979</v>
       </c>
+      <c r="AI71" s="1" t="n">
+        <v>0.9079</v>
+      </c>
+      <c r="AJ71" s="2" t="n">
+        <v>-0.003293446042375675</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8159,6 +8591,12 @@
       <c r="AH72" s="3" t="n">
         <v>0.0009471939379588241</v>
       </c>
+      <c r="AI72" s="1" t="n">
+        <v>0.4262</v>
+      </c>
+      <c r="AJ72" s="3" t="n">
+        <v>0.008280104092737172</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8265,6 +8703,12 @@
       <c r="AH73" s="3" t="n">
         <v>0.001379456706281741</v>
       </c>
+      <c r="AI73" s="1" t="n">
+        <v>0.09420000000000001</v>
+      </c>
+      <c r="AJ73" s="2" t="n">
+        <v>-0.001801419942778315</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8371,6 +8815,12 @@
       <c r="AH74" s="3" t="n">
         <v>0.00409657456637316</v>
       </c>
+      <c r="AI74" s="1" t="n">
+        <v>1.1448</v>
+      </c>
+      <c r="AJ74" s="2" t="n">
+        <v>-0.00624999999999989</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8477,6 +8927,12 @@
       <c r="AH75" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI75" s="1" t="n">
+        <v>0.01598</v>
+      </c>
+      <c r="AJ75" s="2" t="n">
+        <v>-0.002496878901373182</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8583,6 +9039,12 @@
       <c r="AH76" s="2" t="n">
         <v>-0.001797532478143623</v>
       </c>
+      <c r="AI76" s="1" t="n">
+        <v>0.12097</v>
+      </c>
+      <c r="AJ76" s="2" t="n">
+        <v>-0.009822378652697115</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8689,6 +9151,12 @@
       <c r="AH77" s="3" t="n">
         <v>0.002527379949452356</v>
       </c>
+      <c r="AI77" s="1" t="n">
+        <v>0.1187</v>
+      </c>
+      <c r="AJ77" s="2" t="n">
+        <v>-0.0025210084033613</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8795,6 +9263,12 @@
       <c r="AH78" s="2" t="n">
         <v>-0.00489236790606654</v>
       </c>
+      <c r="AI78" s="1" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="AJ78" s="2" t="n">
+        <v>-0.001966568338249674</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8901,6 +9375,12 @@
       <c r="AH79" s="3" t="n">
         <v>0.003136348629910848</v>
       </c>
+      <c r="AI79" s="1" t="n">
+        <v>0.006045</v>
+      </c>
+      <c r="AJ79" s="2" t="n">
+        <v>-0.00526575612966923</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9007,6 +9487,12 @@
       <c r="AH80" s="2" t="n">
         <v>-0.002163125079526613</v>
       </c>
+      <c r="AI80" s="1" t="n">
+        <v>0.007837999999999999</v>
+      </c>
+      <c r="AJ80" s="2" t="n">
+        <v>-0.0005100739607243728</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9113,6 +9599,12 @@
       <c r="AH81" s="2" t="n">
         <v>-0.002225932109070626</v>
       </c>
+      <c r="AI81" s="1" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="AJ81" s="2" t="n">
+        <v>-0.00167317345231462</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9219,6 +9711,12 @@
       <c r="AH82" s="2" t="n">
         <v>-0.002443494196701353</v>
       </c>
+      <c r="AI82" s="1" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="AJ82" s="3" t="n">
+        <v>0.004286589099816327</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9325,6 +9823,12 @@
       <c r="AH83" s="3" t="n">
         <v>0.000242512428762055</v>
       </c>
+      <c r="AI83" s="1" t="n">
+        <v>8.228999999999999</v>
+      </c>
+      <c r="AJ83" s="2" t="n">
+        <v>-0.002424536307431367</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9431,6 +9935,12 @@
       <c r="AH84" s="3" t="n">
         <v>0.004683171992346973</v>
       </c>
+      <c r="AI84" s="1" t="n">
+        <v>352.31</v>
+      </c>
+      <c r="AJ84" s="3" t="n">
+        <v>0.001364295256231755</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9537,6 +10047,12 @@
       <c r="AH85" s="2" t="n">
         <v>-0.002194586686173972</v>
       </c>
+      <c r="AI85" s="1" t="n">
+        <v>0.004069</v>
+      </c>
+      <c r="AJ85" s="2" t="n">
+        <v>-0.005620723362658956</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9643,6 +10159,12 @@
       <c r="AH86" s="3" t="n">
         <v>0.006306722042762769</v>
       </c>
+      <c r="AI86" s="1" t="n">
+        <v>0.13092</v>
+      </c>
+      <c r="AJ86" s="3" t="n">
+        <v>0.0006114338122897947</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9749,6 +10271,12 @@
       <c r="AH87" s="3" t="n">
         <v>0.005555555555555715</v>
       </c>
+      <c r="AI87" s="1" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="AJ87" s="3" t="n">
+        <v>0.003867403314916969</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9855,6 +10383,12 @@
       <c r="AH88" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI88" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AJ88" s="2" t="n">
+        <v>-0.003527336860670197</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9961,6 +10495,12 @@
       <c r="AH89" s="2" t="n">
         <v>-0.00271278399457451</v>
       </c>
+      <c r="AI89" s="1" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="AJ89" s="2" t="n">
+        <v>-0.004760285617136882</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10067,6 +10607,12 @@
       <c r="AH90" s="3" t="n">
         <v>0.001547987616098901</v>
       </c>
+      <c r="AI90" s="1" t="n">
+        <v>0.2582</v>
+      </c>
+      <c r="AJ90" s="2" t="n">
+        <v>-0.0023183925811437</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10173,6 +10719,12 @@
       <c r="AH91" s="3" t="n">
         <v>0.007436967168510804</v>
       </c>
+      <c r="AI91" s="1" t="n">
+        <v>0.05574</v>
+      </c>
+      <c r="AJ91" s="3" t="n">
+        <v>0.003601008282319028</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10279,6 +10831,12 @@
       <c r="AH92" s="2" t="n">
         <v>-0.002812832598449</v>
       </c>
+      <c r="AI92" s="1" t="n">
+        <v>1.3102</v>
+      </c>
+      <c r="AJ92" s="2" t="n">
+        <v>-0.001143554166349056</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10385,6 +10943,12 @@
       <c r="AH93" s="3" t="n">
         <v>0.002821316614420057</v>
       </c>
+      <c r="AI93" s="1" t="n">
+        <v>0.06408</v>
+      </c>
+      <c r="AJ93" s="3" t="n">
+        <v>0.001562988433885634</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10491,6 +11055,12 @@
       <c r="AH94" s="2" t="n">
         <v>-0.004530011325028325</v>
       </c>
+      <c r="AI94" s="1" t="n">
+        <v>0.00878</v>
+      </c>
+      <c r="AJ94" s="2" t="n">
+        <v>-0.001137656427758771</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10597,6 +11167,12 @@
       <c r="AH95" s="3" t="n">
         <v>0.002373887240355986</v>
       </c>
+      <c r="AI95" s="1" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="AJ95" s="2" t="n">
+        <v>-0.001184132622853794</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10703,6 +11279,12 @@
       <c r="AH96" s="3" t="n">
         <v>0.002654867256637214</v>
       </c>
+      <c r="AI96" s="1" t="n">
+        <v>0.02257</v>
+      </c>
+      <c r="AJ96" s="2" t="n">
+        <v>-0.003971756398940856</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10809,6 +11391,12 @@
       <c r="AH97" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI97" s="1" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="AJ97" s="2" t="n">
+        <v>-0.001833740831295913</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10915,6 +11503,12 @@
       <c r="AH98" s="3" t="n">
         <v>0.001779359430604786</v>
       </c>
+      <c r="AI98" s="1" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="AJ98" s="3" t="n">
+        <v>0.001776198934280641</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11021,6 +11615,12 @@
       <c r="AH99" s="3" t="n">
         <v>0.0009900990099010276</v>
       </c>
+      <c r="AI99" s="1" t="n">
+        <v>3.031</v>
+      </c>
+      <c r="AJ99" s="2" t="n">
+        <v>-0.0006594131223210616</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11127,6 +11727,12 @@
       <c r="AH100" s="3" t="n">
         <v>0.004079254079253913</v>
       </c>
+      <c r="AI100" s="1" t="n">
+        <v>0.03412</v>
+      </c>
+      <c r="AJ100" s="2" t="n">
+        <v>-0.009866511897852584</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11233,6 +11839,12 @@
       <c r="AH101" s="2" t="n">
         <v>-0.0016375545851529</v>
       </c>
+      <c r="AI101" s="1" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="AJ101" s="2" t="n">
+        <v>-0.002186987424822309</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11339,6 +11951,12 @@
       <c r="AH102" s="3" t="n">
         <v>0.008506343713956173</v>
       </c>
+      <c r="AI102" s="1" t="n">
+        <v>0.007044</v>
+      </c>
+      <c r="AJ102" s="3" t="n">
+        <v>0.007005003573981353</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -11445,6 +12063,12 @@
       <c r="AH103" s="2" t="n">
         <v>-0.003032140691328164</v>
       </c>
+      <c r="AI103" s="1" t="n">
+        <v>0.06544999999999999</v>
+      </c>
+      <c r="AJ103" s="2" t="n">
+        <v>-0.004714111922141191</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11551,6 +12175,12 @@
       <c r="AH104" s="2" t="n">
         <v>-0.0009682885499879241</v>
       </c>
+      <c r="AI104" s="1" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="AJ104" s="2" t="n">
+        <v>-0.005573055488248181</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11657,6 +12287,12 @@
       <c r="AH105" s="3" t="n">
         <v>0.0005491488193300999</v>
       </c>
+      <c r="AI105" s="1" t="n">
+        <v>1.814</v>
+      </c>
+      <c r="AJ105" s="2" t="n">
+        <v>-0.004390779363336996</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11763,6 +12399,12 @@
       <c r="AH106" s="2" t="n">
         <v>-0.002545763122802787</v>
       </c>
+      <c r="AI106" s="1" t="n">
+        <v>0.008248</v>
+      </c>
+      <c r="AJ106" s="3" t="n">
+        <v>0.002430724355858158</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11869,6 +12511,12 @@
       <c r="AH107" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI107" s="1" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="AJ107" s="2" t="n">
+        <v>-0.001633986928104698</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11975,6 +12623,12 @@
       <c r="AH108" s="3" t="n">
         <v>0.0004610419548178696</v>
       </c>
+      <c r="AI108" s="1" t="n">
+        <v>0.02175</v>
+      </c>
+      <c r="AJ108" s="3" t="n">
+        <v>0.002304147465437694</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -12081,6 +12735,12 @@
       <c r="AH109" s="3" t="n">
         <v>0.0005390835579515229</v>
       </c>
+      <c r="AI109" s="1" t="n">
+        <v>0.05557</v>
+      </c>
+      <c r="AJ109" s="2" t="n">
+        <v>-0.00197557471264366</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -12187,6 +12847,12 @@
       <c r="AH110" s="3" t="n">
         <v>0.001214118463272927</v>
       </c>
+      <c r="AI110" s="1" t="n">
+        <v>0.1153</v>
+      </c>
+      <c r="AJ110" s="2" t="n">
+        <v>-0.001299263750541337</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -12293,6 +12959,12 @@
       <c r="AH111" s="2" t="n">
         <v>-0.002657943160907894</v>
       </c>
+      <c r="AI111" s="1" t="n">
+        <v>0.09649000000000001</v>
+      </c>
+      <c r="AJ111" s="2" t="n">
+        <v>-0.01096760967609663</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -12399,6 +13071,12 @@
       <c r="AH112" s="2" t="n">
         <v>-0.002673796791443927</v>
       </c>
+      <c r="AI112" s="1" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="AJ112" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -12505,6 +13183,12 @@
       <c r="AH113" s="2" t="n">
         <v>-0.0007092198581560347</v>
       </c>
+      <c r="AI113" s="1" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="AJ113" s="2" t="n">
+        <v>-0.004359728277400384</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -12611,6 +13295,12 @@
       <c r="AH114" s="3" t="n">
         <v>0.006802721088435416</v>
       </c>
+      <c r="AI114" s="1" t="n">
+        <v>0.001768</v>
+      </c>
+      <c r="AJ114" s="2" t="n">
+        <v>-0.004504504504504491</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -12717,6 +13407,12 @@
       <c r="AH115" s="2" t="n">
         <v>-0.001425403864428274</v>
       </c>
+      <c r="AI115" s="1" t="n">
+        <v>1.2597</v>
+      </c>
+      <c r="AJ115" s="2" t="n">
+        <v>-0.001030927835051433</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -12823,6 +13519,12 @@
       <c r="AH116" s="2" t="n">
         <v>-0.005865102639296123</v>
       </c>
+      <c r="AI116" s="1" t="n">
+        <v>0.2366</v>
+      </c>
+      <c r="AJ116" s="2" t="n">
+        <v>-0.002949852507374657</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12929,6 +13631,12 @@
       <c r="AH117" s="3" t="n">
         <v>0.0001643655489809839</v>
       </c>
+      <c r="AI117" s="1" t="n">
+        <v>0.06087</v>
+      </c>
+      <c r="AJ117" s="3" t="n">
+        <v>0.0003286770747740211</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -13035,6 +13743,12 @@
       <c r="AH118" s="2" t="n">
         <v>-0.003208065994500487</v>
       </c>
+      <c r="AI118" s="1" t="n">
+        <v>0.04365</v>
+      </c>
+      <c r="AJ118" s="3" t="n">
+        <v>0.003448275862069064</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -13141,6 +13855,12 @@
       <c r="AH119" s="3" t="n">
         <v>0.00188831939573781</v>
       </c>
+      <c r="AI119" s="1" t="n">
+        <v>0.003694</v>
+      </c>
+      <c r="AJ119" s="2" t="n">
+        <v>-0.005385029617662912</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -13247,6 +13967,12 @@
       <c r="AH120" s="3" t="n">
         <v>0.001265822784810128</v>
       </c>
+      <c r="AI120" s="1" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="AJ120" s="2" t="n">
+        <v>-0.002528445006321114</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -13353,6 +14079,12 @@
       <c r="AH121" s="3" t="n">
         <v>0.0003340013360053072</v>
       </c>
+      <c r="AI121" s="1" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="AJ121" s="2" t="n">
+        <v>-0.004340567612687706</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -13459,6 +14191,12 @@
       <c r="AH122" s="2" t="n">
         <v>-0.001399090591115815</v>
       </c>
+      <c r="AI122" s="1" t="n">
+        <v>0.5688</v>
+      </c>
+      <c r="AJ122" s="2" t="n">
+        <v>-0.003852889667250403</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -13565,6 +14303,12 @@
       <c r="AH123" s="2" t="n">
         <v>-0.0001757963574994045</v>
       </c>
+      <c r="AI123" s="1" t="n">
+        <v>0.028383</v>
+      </c>
+      <c r="AJ123" s="2" t="n">
+        <v>-0.001898934486760276</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -13671,6 +14415,12 @@
       <c r="AH124" s="2" t="n">
         <v>-0.002410861565791265</v>
       </c>
+      <c r="AI124" s="1" t="n">
+        <v>0.07896</v>
+      </c>
+      <c r="AJ124" s="3" t="n">
+        <v>0.004324599338590778</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -13777,6 +14527,12 @@
       <c r="AH125" s="3" t="n">
         <v>0.001041272245361596</v>
       </c>
+      <c r="AI125" s="1" t="n">
+        <v>0.10587</v>
+      </c>
+      <c r="AJ125" s="3" t="n">
+        <v>0.00113475177304973</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -13883,6 +14639,12 @@
       <c r="AH126" s="2" t="n">
         <v>-0.00674157303370798</v>
       </c>
+      <c r="AI126" s="1" t="n">
+        <v>0.02652</v>
+      </c>
+      <c r="AJ126" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -13989,6 +14751,12 @@
       <c r="AH127" s="2" t="n">
         <v>-0.001826484018264766</v>
       </c>
+      <c r="AI127" s="1" t="n">
+        <v>0.02184</v>
+      </c>
+      <c r="AJ127" s="2" t="n">
+        <v>-0.0009149130832572119</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -14095,6 +14863,12 @@
       <c r="AH128" s="2" t="n">
         <v>-0.00122699386503071</v>
       </c>
+      <c r="AI128" s="1" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="AJ128" s="2" t="n">
+        <v>-0.009213759213759222</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -14201,6 +14975,12 @@
       <c r="AH129" s="3" t="n">
         <v>0.004891000558971536</v>
       </c>
+      <c r="AI129" s="1" t="n">
+        <v>0.14367</v>
+      </c>
+      <c r="AJ129" s="2" t="n">
+        <v>-0.001042970379641296</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -14307,6 +15087,12 @@
       <c r="AH130" s="3" t="n">
         <v>0.0003628031315638378</v>
       </c>
+      <c r="AI130" s="1" t="n">
+        <v>0.051782</v>
+      </c>
+      <c r="AJ130" s="2" t="n">
+        <v>-0.01158640172555301</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -14413,6 +15199,12 @@
       <c r="AH131" s="3" t="n">
         <v>0.0006081985159955539</v>
       </c>
+      <c r="AI131" s="1" t="n">
+        <v>0.08198999999999999</v>
+      </c>
+      <c r="AJ131" s="2" t="n">
+        <v>-0.003282275711159814</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -14519,6 +15311,12 @@
       <c r="AH132" s="3" t="n">
         <v>0.004550625711035239</v>
       </c>
+      <c r="AI132" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AJ132" s="2" t="n">
+        <v>-0.003397508493771332</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -14625,6 +15423,12 @@
       <c r="AH133" s="2" t="n">
         <v>-0.002910958904109459</v>
       </c>
+      <c r="AI133" s="1" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="AJ133" s="2" t="n">
+        <v>-0.002232526189249663</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -14731,6 +15535,12 @@
       <c r="AH134" s="3" t="n">
         <v>0.0006715916722632365</v>
       </c>
+      <c r="AI134" s="1" t="n">
+        <v>0.02971</v>
+      </c>
+      <c r="AJ134" s="2" t="n">
+        <v>-0.003020134228187913</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -14837,6 +15647,12 @@
       <c r="AH135" s="2" t="n">
         <v>-0.001710376282782142</v>
       </c>
+      <c r="AI135" s="1" t="n">
+        <v>0.01745</v>
+      </c>
+      <c r="AJ135" s="2" t="n">
+        <v>-0.003426613363792177</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -14943,6 +15759,12 @@
       <c r="AH136" s="3" t="n">
         <v>0.0008053691275168389</v>
       </c>
+      <c r="AI136" s="1" t="n">
+        <v>0.03722</v>
+      </c>
+      <c r="AJ136" s="2" t="n">
+        <v>-0.001609442060085771</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -15049,6 +15871,12 @@
       <c r="AH137" s="2" t="n">
         <v>-0.0007366482504603751</v>
       </c>
+      <c r="AI137" s="1" t="n">
+        <v>0.02698</v>
+      </c>
+      <c r="AJ137" s="2" t="n">
+        <v>-0.005528934758569879</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -15155,6 +15983,12 @@
       <c r="AH138" s="2" t="n">
         <v>-0.002339181286549623</v>
       </c>
+      <c r="AI138" s="1" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AJ138" s="2" t="n">
+        <v>-0.00351699882766719</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -15261,6 +16095,12 @@
       <c r="AH139" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI139" s="1" t="n">
+        <v>0.01184</v>
+      </c>
+      <c r="AJ139" s="2" t="n">
+        <v>-0.004205214465937738</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -15367,6 +16207,12 @@
       <c r="AH140" s="2" t="n">
         <v>-0.005398110661268571</v>
       </c>
+      <c r="AI140" s="1" t="n">
+        <v>0.01476</v>
+      </c>
+      <c r="AJ140" s="3" t="n">
+        <v>0.001356852103120822</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -15473,6 +16319,12 @@
       <c r="AH141" s="2" t="n">
         <v>-0.0001229785402448776</v>
       </c>
+      <c r="AI141" s="1" t="n">
+        <v>16.215</v>
+      </c>
+      <c r="AJ141" s="2" t="n">
+        <v>-0.00282885431400279</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -15579,6 +16431,12 @@
       <c r="AH142" s="3" t="n">
         <v>0.0007942811755361074</v>
       </c>
+      <c r="AI142" s="1" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AJ142" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -15685,6 +16543,12 @@
       <c r="AH143" s="3" t="n">
         <v>0.009527299377061316</v>
       </c>
+      <c r="AI143" s="1" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="AJ143" s="3" t="n">
+        <v>0.0308529945553539</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -15791,6 +16655,12 @@
       <c r="AH144" s="3" t="n">
         <v>0.001471206389239189</v>
       </c>
+      <c r="AI144" s="1" t="n">
+        <v>0.004762</v>
+      </c>
+      <c r="AJ144" s="2" t="n">
+        <v>-0.0006295907660021822</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -15897,6 +16767,12 @@
       <c r="AH145" s="3" t="n">
         <v>0.001321205345800059</v>
       </c>
+      <c r="AI145" s="1" t="n">
+        <v>1.9737</v>
+      </c>
+      <c r="AJ145" s="3" t="n">
+        <v>0.001623953311342346</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -16003,6 +16879,12 @@
       <c r="AH146" s="2" t="n">
         <v>-0.001708671507902684</v>
       </c>
+      <c r="AI146" s="1" t="n">
+        <v>0.02342</v>
+      </c>
+      <c r="AJ146" s="3" t="n">
+        <v>0.002139495079161379</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -16109,6 +16991,12 @@
       <c r="AH147" s="3" t="n">
         <v>0.002001556766373842</v>
       </c>
+      <c r="AI147" s="1" t="n">
+        <v>0.09017</v>
+      </c>
+      <c r="AJ147" s="3" t="n">
+        <v>0.0006658528465209688</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -16215,6 +17103,12 @@
       <c r="AH148" s="3" t="n">
         <v>0.002882305844675845</v>
       </c>
+      <c r="AI148" s="1" t="n">
+        <v>0.06412</v>
+      </c>
+      <c r="AJ148" s="3" t="n">
+        <v>0.0237905157272871</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -16321,6 +17215,12 @@
       <c r="AH149" s="3" t="n">
         <v>0.001685772083614344</v>
       </c>
+      <c r="AI149" s="1" t="n">
+        <v>0.05918</v>
+      </c>
+      <c r="AJ149" s="2" t="n">
+        <v>-0.004039044092897967</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -16427,6 +17327,12 @@
       <c r="AH150" s="3" t="n">
         <v>0.0009002741744076522</v>
       </c>
+      <c r="AI150" s="1" t="n">
+        <v>0.24458</v>
+      </c>
+      <c r="AJ150" s="2" t="n">
+        <v>-4.088474590134511e-05</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -16533,6 +17439,12 @@
       <c r="AH151" s="3" t="n">
         <v>0.003848346636259916</v>
       </c>
+      <c r="AI151" s="1" t="n">
+        <v>7.037000000000001e-05</v>
+      </c>
+      <c r="AJ151" s="2" t="n">
+        <v>-0.0008519096975720011</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -16639,6 +17551,12 @@
       <c r="AH152" s="2" t="n">
         <v>-0.001119068934646375</v>
       </c>
+      <c r="AI152" s="1" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="AJ152" s="2" t="n">
+        <v>-0.004257226081111265</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -16745,6 +17663,12 @@
       <c r="AH153" s="2" t="n">
         <v>-0.005483870967741868</v>
       </c>
+      <c r="AI153" s="1" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AJ153" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -16851,6 +17775,12 @@
       <c r="AH154" s="2" t="n">
         <v>-0.001643835616438327</v>
       </c>
+      <c r="AI154" s="1" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="AJ154" s="2" t="n">
+        <v>-0.007683863885839804</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -16957,6 +17887,12 @@
       <c r="AH155" s="2" t="n">
         <v>-0.0008676789587852742</v>
       </c>
+      <c r="AI155" s="1" t="n">
+        <v>0.2298</v>
+      </c>
+      <c r="AJ155" s="2" t="n">
+        <v>-0.002171081198436823</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -17063,6 +17999,12 @@
       <c r="AH156" s="3" t="n">
         <v>0.0002478929102626704</v>
       </c>
+      <c r="AI156" s="1" t="n">
+        <v>0.08084</v>
+      </c>
+      <c r="AJ156" s="3" t="n">
+        <v>0.001734820322180932</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -17169,6 +18111,12 @@
       <c r="AH157" s="3" t="n">
         <v>0.008743216469980206</v>
       </c>
+      <c r="AI157" s="1" t="n">
+        <v>0.2321</v>
+      </c>
+      <c r="AJ157" s="2" t="n">
+        <v>-0.009009009009009012</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -17275,6 +18223,12 @@
       <c r="AH158" s="2" t="n">
         <v>-0.004704037632300976</v>
       </c>
+      <c r="AI158" s="1" t="n">
+        <v>0.2543</v>
+      </c>
+      <c r="AJ158" s="3" t="n">
+        <v>0.001575423395037461</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -17381,6 +18335,12 @@
       <c r="AH159" s="2" t="n">
         <v>-0.004102564102564106</v>
       </c>
+      <c r="AI159" s="1" t="n">
+        <v>2.916</v>
+      </c>
+      <c r="AJ159" s="3" t="n">
+        <v>0.001029866117404776</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -17487,6 +18447,12 @@
       <c r="AH160" s="3" t="n">
         <v>0.002022244691607602</v>
       </c>
+      <c r="AI160" s="1" t="n">
+        <v>0.09909999999999999</v>
+      </c>
+      <c r="AJ160" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -17593,6 +18559,12 @@
       <c r="AH161" s="3" t="n">
         <v>0.0005398110661268336</v>
       </c>
+      <c r="AI161" s="1" t="n">
+        <v>0.14773</v>
+      </c>
+      <c r="AJ161" s="2" t="n">
+        <v>-0.003709198813056346</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -17699,6 +18671,12 @@
       <c r="AH162" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI162" s="1" t="n">
+        <v>0.003293</v>
+      </c>
+      <c r="AJ162" s="2" t="n">
+        <v>-0.008729680915111364</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -17805,6 +18783,12 @@
       <c r="AH163" s="3" t="n">
         <v>0.001190712442945015</v>
       </c>
+      <c r="AI163" s="1" t="n">
+        <v>0.005002</v>
+      </c>
+      <c r="AJ163" s="2" t="n">
+        <v>-0.008523290386521236</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -17911,6 +18895,12 @@
       <c r="AH164" s="3" t="n">
         <v>0.002079002079002139</v>
       </c>
+      <c r="AI164" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="AJ164" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -18017,6 +19007,12 @@
       <c r="AH165" s="3" t="n">
         <v>0.001287830006439187</v>
       </c>
+      <c r="AI165" s="1" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="AJ165" s="2" t="n">
+        <v>-0.01028938906752405</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -18123,6 +19119,12 @@
       <c r="AH166" s="3" t="n">
         <v>0.001505700150570008</v>
       </c>
+      <c r="AI166" s="1" t="n">
+        <v>1.3966</v>
+      </c>
+      <c r="AJ166" s="2" t="n">
+        <v>-0.0001431844215349212</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -18229,6 +19231,12 @@
       <c r="AH167" s="3" t="n">
         <v>0.00178762960314623</v>
       </c>
+      <c r="AI167" s="1" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AJ167" s="2" t="n">
+        <v>-0.0007137758743753675</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -18335,6 +19343,12 @@
       <c r="AH168" s="2" t="n">
         <v>-0.006369426751592362</v>
       </c>
+      <c r="AI168" s="1" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AJ168" s="2" t="n">
+        <v>-0.003205128205128208</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -18441,6 +19455,12 @@
       <c r="AH169" s="3" t="n">
         <v>0.004326123128119739</v>
       </c>
+      <c r="AI169" s="1" t="n">
+        <v>0.03008</v>
+      </c>
+      <c r="AJ169" s="2" t="n">
+        <v>-0.003313452617627548</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -18547,6 +19567,12 @@
       <c r="AH170" s="3" t="n">
         <v>0.0009240009240008863</v>
       </c>
+      <c r="AI170" s="1" t="n">
+        <v>0.04322</v>
+      </c>
+      <c r="AJ170" s="2" t="n">
+        <v>-0.002538656819755342</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -18653,6 +19679,12 @@
       <c r="AH171" s="2" t="n">
         <v>-0.005952380952380916</v>
       </c>
+      <c r="AI171" s="1" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="AJ171" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -18759,6 +19791,12 @@
       <c r="AH172" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI172" s="1" t="n">
+        <v>1.3e-05</v>
+      </c>
+      <c r="AJ172" s="3" t="n">
+        <v>0.01562499999999998</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -18865,6 +19903,12 @@
       <c r="AH173" s="2" t="n">
         <v>-0.001881467544684941</v>
       </c>
+      <c r="AI173" s="1" t="n">
+        <v>0.02118</v>
+      </c>
+      <c r="AJ173" s="2" t="n">
+        <v>-0.001885014137605955</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -18971,6 +20015,12 @@
       <c r="AH174" s="3" t="n">
         <v>0.006455203116304921</v>
       </c>
+      <c r="AI174" s="1" t="n">
+        <v>0.08994000000000001</v>
+      </c>
+      <c r="AJ174" s="2" t="n">
+        <v>-0.005418555789007967</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -19077,6 +20127,12 @@
       <c r="AH175" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI175" s="1" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="AJ175" s="2" t="n">
+        <v>-0.003580280914348576</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -19183,6 +20239,12 @@
       <c r="AH176" s="2" t="n">
         <v>-0.002803738317756895</v>
       </c>
+      <c r="AI176" s="1" t="n">
+        <v>0.02131</v>
+      </c>
+      <c r="AJ176" s="2" t="n">
+        <v>-0.001405810684161305</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -19289,6 +20351,12 @@
       <c r="AH177" s="2" t="n">
         <v>-0.003811944091486723</v>
       </c>
+      <c r="AI177" s="1" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="AJ177" s="2" t="n">
+        <v>-0.003826530612244853</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -19395,6 +20463,12 @@
       <c r="AH178" s="2" t="n">
         <v>-0.001047120418848193</v>
       </c>
+      <c r="AI178" s="1" t="n">
+        <v>0.000953</v>
+      </c>
+      <c r="AJ178" s="2" t="n">
+        <v>-0.00104821802935013</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -19501,6 +20575,12 @@
       <c r="AH179" s="2" t="n">
         <v>-0.0003061581525542364</v>
       </c>
+      <c r="AI179" s="1" t="n">
+        <v>0.022825</v>
+      </c>
+      <c r="AJ179" s="2" t="n">
+        <v>-0.00140000875005457</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -19607,6 +20687,12 @@
       <c r="AH180" s="2" t="n">
         <v>-0.001937046004842617</v>
       </c>
+      <c r="AI180" s="1" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ180" s="2" t="n">
+        <v>-0.005337214944201902</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -19713,6 +20799,12 @@
       <c r="AH181" s="3" t="n">
         <v>0.003511235955056183</v>
       </c>
+      <c r="AI181" s="1" t="n">
+        <v>0.5701000000000001</v>
+      </c>
+      <c r="AJ181" s="2" t="n">
+        <v>-0.002624212736179052</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -19819,6 +20911,12 @@
       <c r="AH182" s="3" t="n">
         <v>0.00492319810949193</v>
       </c>
+      <c r="AI182" s="1" t="n">
+        <v>0.05075</v>
+      </c>
+      <c r="AJ182" s="2" t="n">
+        <v>-0.005486968449931326</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -19925,6 +21023,12 @@
       <c r="AH183" s="2" t="n">
         <v>-0.001093693036820879</v>
       </c>
+      <c r="AI183" s="1" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="AJ183" s="2" t="n">
+        <v>-0.003649635036496434</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -20031,6 +21135,12 @@
       <c r="AH184" s="2" t="n">
         <v>-0.003101309441764296</v>
       </c>
+      <c r="AI184" s="1" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="AJ184" s="2" t="n">
+        <v>-0.003456619426201224</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -20137,6 +21247,12 @@
       <c r="AH185" s="2" t="n">
         <v>-0.003189792663476928</v>
       </c>
+      <c r="AI185" s="1" t="n">
+        <v>0.01866</v>
+      </c>
+      <c r="AJ185" s="2" t="n">
+        <v>-0.00479999999999999</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -20243,6 +21359,12 @@
       <c r="AH186" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI186" s="1" t="n">
+        <v>3.08e-05</v>
+      </c>
+      <c r="AJ186" s="2" t="n">
+        <v>-0.003236245954692416</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -20349,6 +21471,12 @@
       <c r="AH187" s="2" t="n">
         <v>-0.006333122229258987</v>
       </c>
+      <c r="AI187" s="1" t="n">
+        <v>0.01567</v>
+      </c>
+      <c r="AJ187" s="2" t="n">
+        <v>-0.00127469725940084</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -20455,6 +21583,12 @@
       <c r="AH188" s="2" t="n">
         <v>-0.0002447980416155722</v>
       </c>
+      <c r="AI188" s="1" t="n">
+        <v>0.04073</v>
+      </c>
+      <c r="AJ188" s="2" t="n">
+        <v>-0.002693437806072453</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -20561,6 +21695,12 @@
       <c r="AH189" s="2" t="n">
         <v>-0.0004463289444320573</v>
       </c>
+      <c r="AI189" s="1" t="n">
+        <v>0.0004477</v>
+      </c>
+      <c r="AJ189" s="2" t="n">
+        <v>-0.000446528242911375</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -20667,6 +21807,12 @@
       <c r="AH190" s="3" t="n">
         <v>0.0004321521175453584</v>
       </c>
+      <c r="AI190" s="1" t="n">
+        <v>0.02307</v>
+      </c>
+      <c r="AJ190" s="2" t="n">
+        <v>-0.00345572354211664</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -20773,6 +21919,12 @@
       <c r="AH191" s="2" t="n">
         <v>-0.001898734177215332</v>
       </c>
+      <c r="AI191" s="1" t="n">
+        <v>0.01574</v>
+      </c>
+      <c r="AJ191" s="2" t="n">
+        <v>-0.001902346227013239</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -20879,6 +22031,12 @@
       <c r="AH192" s="3" t="n">
         <v>0.00125335720680395</v>
       </c>
+      <c r="AI192" s="1" t="n">
+        <v>0.05577</v>
+      </c>
+      <c r="AJ192" s="2" t="n">
+        <v>-0.002682403433476348</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -20985,6 +22143,12 @@
       <c r="AH193" s="3" t="n">
         <v>0.000530222693531372</v>
       </c>
+      <c r="AI193" s="1" t="n">
+        <v>0.1878</v>
+      </c>
+      <c r="AJ193" s="2" t="n">
+        <v>-0.004769475357710715</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -21091,6 +22255,12 @@
       <c r="AH194" s="3" t="n">
         <v>0.004675324675324665</v>
       </c>
+      <c r="AI194" s="1" t="n">
+        <v>0.01931</v>
+      </c>
+      <c r="AJ194" s="2" t="n">
+        <v>-0.001551189245087838</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -21197,6 +22367,12 @@
       <c r="AH195" s="2" t="n">
         <v>-0.0004683840749414004</v>
       </c>
+      <c r="AI195" s="1" t="n">
+        <v>0.4243</v>
+      </c>
+      <c r="AJ195" s="2" t="n">
+        <v>-0.005857544517338337</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -21303,6 +22479,12 @@
       <c r="AH196" s="2" t="n">
         <v>-0.004850444624090624</v>
       </c>
+      <c r="AI196" s="1" t="n">
+        <v>0.01229</v>
+      </c>
+      <c r="AJ196" s="2" t="n">
+        <v>-0.00162469536961813</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -21409,6 +22591,12 @@
       <c r="AH197" s="2" t="n">
         <v>-0.001706120708040172</v>
       </c>
+      <c r="AI197" s="1" t="n">
+        <v>0.04654</v>
+      </c>
+      <c r="AJ197" s="2" t="n">
+        <v>-0.005767998290963457</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -21515,6 +22703,12 @@
       <c r="AH198" s="3" t="n">
         <v>0.00723362658846537</v>
       </c>
+      <c r="AI198" s="1" t="n">
+        <v>0.5159</v>
+      </c>
+      <c r="AJ198" s="3" t="n">
+        <v>0.001358695652173979</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -21621,6 +22815,12 @@
       <c r="AH199" s="2" t="n">
         <v>-0.01123595505617979</v>
       </c>
+      <c r="AI199" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AJ199" s="3" t="n">
+        <v>0.01136363636363637</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -21727,6 +22927,12 @@
       <c r="AH200" s="3" t="n">
         <v>0.001343183344526499</v>
       </c>
+      <c r="AI200" s="1" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="AJ200" s="2" t="n">
+        <v>-0.004024144869215325</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -21833,6 +23039,12 @@
       <c r="AH201" s="2" t="n">
         <v>-0.002108963093145845</v>
       </c>
+      <c r="AI201" s="1" t="n">
+        <v>0.005663</v>
+      </c>
+      <c r="AJ201" s="2" t="n">
+        <v>-0.00264177527298349</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -21939,6 +23151,12 @@
       <c r="AH202" s="2" t="n">
         <v>-0.002426448286320919</v>
       </c>
+      <c r="AI202" s="1" t="n">
+        <v>0.023048</v>
+      </c>
+      <c r="AJ202" s="3" t="n">
+        <v>0.001085870651088073</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -22045,6 +23263,12 @@
       <c r="AH203" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI203" s="1" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="AJ203" s="2" t="n">
+        <v>-0.007299270072992783</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -22151,6 +23375,12 @@
       <c r="AH204" s="2" t="n">
         <v>-0.0005947071067499014</v>
       </c>
+      <c r="AI204" s="1" t="n">
+        <v>0.03337</v>
+      </c>
+      <c r="AJ204" s="2" t="n">
+        <v>-0.007140731925022436</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -22257,6 +23487,12 @@
       <c r="AH205" s="3" t="n">
         <v>0.0009548818333730149</v>
       </c>
+      <c r="AI205" s="1" t="n">
+        <v>4.191</v>
+      </c>
+      <c r="AJ205" s="2" t="n">
+        <v>-0.0004769854519436632</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -22363,6 +23599,12 @@
       <c r="AH206" s="2" t="n">
         <v>-0.00274725274725275</v>
       </c>
+      <c r="AI206" s="1" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AJ206" s="2" t="n">
+        <v>-0.002754820936639121</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -22469,6 +23711,12 @@
       <c r="AH207" s="3" t="n">
         <v>0.04643242794252015</v>
       </c>
+      <c r="AI207" s="1" t="n">
+        <v>0.0012873</v>
+      </c>
+      <c r="AJ207" s="3" t="n">
+        <v>0.02182886172408316</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -22575,6 +23823,12 @@
       <c r="AH208" s="3" t="n">
         <v>0.002097315436241525</v>
       </c>
+      <c r="AI208" s="1" t="n">
+        <v>0.007126</v>
+      </c>
+      <c r="AJ208" s="2" t="n">
+        <v>-0.005720664155155487</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -22681,6 +23935,12 @@
       <c r="AH209" s="3" t="n">
         <v>0.00333889816360599</v>
       </c>
+      <c r="AI209" s="1" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AJ209" s="2" t="n">
+        <v>-0.003327787021630595</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -22787,6 +24047,12 @@
       <c r="AH210" s="2" t="n">
         <v>-0.001537279016141474</v>
       </c>
+      <c r="AI210" s="1" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="AJ210" s="2" t="n">
+        <v>-0.003849114703618172</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -22893,6 +24159,12 @@
       <c r="AH211" s="2" t="n">
         <v>-0.001257510129942759</v>
       </c>
+      <c r="AI211" s="1" t="n">
+        <v>0.00713</v>
+      </c>
+      <c r="AJ211" s="2" t="n">
+        <v>-0.002518186905428062</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -22999,6 +24271,12 @@
       <c r="AH212" s="3" t="n">
         <v>0.005195704883962596</v>
       </c>
+      <c r="AI212" s="1" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="AJ212" s="3" t="n">
+        <v>0.0006891798759475464</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -23105,6 +24383,12 @@
       <c r="AH213" s="2" t="n">
         <v>-0.006162769621170927</v>
       </c>
+      <c r="AI213" s="1" t="n">
+        <v>0.05422</v>
+      </c>
+      <c r="AJ213" s="2" t="n">
+        <v>-0.01112529637060003</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -23211,6 +24495,12 @@
       <c r="AH214" s="3" t="n">
         <v>0.0005268703898841767</v>
       </c>
+      <c r="AI214" s="1" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="AJ214" s="2" t="n">
+        <v>-0.006845708267509338</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -23317,6 +24607,12 @@
       <c r="AH215" s="3" t="n">
         <v>0.0005603287261860711</v>
       </c>
+      <c r="AI215" s="1" t="n">
+        <v>0.05333</v>
+      </c>
+      <c r="AJ215" s="2" t="n">
+        <v>-0.004480119469852477</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -23423,6 +24719,12 @@
       <c r="AH216" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI216" s="1" t="n">
+        <v>0.002055</v>
+      </c>
+      <c r="AJ216" s="2" t="n">
+        <v>-0.01486097794822637</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -23529,6 +24831,12 @@
       <c r="AH217" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI217" s="1" t="n">
+        <v>6.026</v>
+      </c>
+      <c r="AJ217" s="2" t="n">
+        <v>-0.003307972213033487</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -23635,6 +24943,12 @@
       <c r="AH218" s="3" t="n">
         <v>0.0004652244708071132</v>
       </c>
+      <c r="AI218" s="1" t="n">
+        <v>4.254</v>
+      </c>
+      <c r="AJ218" s="2" t="n">
+        <v>-0.01092769123459674</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -23741,6 +25055,12 @@
       <c r="AH219" s="2" t="n">
         <v>-0.005232666791254018</v>
       </c>
+      <c r="AI219" s="1" t="n">
+        <v>0.005324</v>
+      </c>
+      <c r="AJ219" s="3" t="n">
+        <v>0.0001878639864738179</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -23847,6 +25167,12 @@
       <c r="AH220" s="2" t="n">
         <v>-0.002419549963706652</v>
       </c>
+      <c r="AI220" s="1" t="n">
+        <v>0.04108</v>
+      </c>
+      <c r="AJ220" s="2" t="n">
+        <v>-0.003638127577007137</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -23953,6 +25279,12 @@
       <c r="AH221" s="3" t="n">
         <v>0.00138816588582339</v>
       </c>
+      <c r="AI221" s="1" t="n">
+        <v>0.005759</v>
+      </c>
+      <c r="AJ221" s="2" t="n">
+        <v>-0.002079362328885784</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -24059,6 +25391,12 @@
       <c r="AH222" s="3" t="n">
         <v>0.004381161007667005</v>
       </c>
+      <c r="AI222" s="1" t="n">
+        <v>0.09130000000000001</v>
+      </c>
+      <c r="AJ222" s="2" t="n">
+        <v>-0.004362050163576854</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -24165,6 +25503,12 @@
       <c r="AH223" s="3" t="n">
         <v>0.001185185185185055</v>
       </c>
+      <c r="AI223" s="1" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AJ223" s="2" t="n">
+        <v>-0.004143237644273326</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -24271,6 +25615,12 @@
       <c r="AH224" s="3" t="n">
         <v>0.0002308402585411923</v>
       </c>
+      <c r="AI224" s="1" t="n">
+        <v>0.4328</v>
+      </c>
+      <c r="AJ224" s="2" t="n">
+        <v>-0.001153934918070622</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -24377,6 +25727,12 @@
       <c r="AH225" s="2" t="n">
         <v>-0.0001201201201202402</v>
       </c>
+      <c r="AI225" s="1" t="n">
+        <v>0.08309</v>
+      </c>
+      <c r="AJ225" s="2" t="n">
+        <v>-0.001802018260451674</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -24483,6 +25839,12 @@
       <c r="AH226" s="2" t="n">
         <v>-0.001067805659369951</v>
       </c>
+      <c r="AI226" s="1" t="n">
+        <v>0.01869</v>
+      </c>
+      <c r="AJ226" s="2" t="n">
+        <v>-0.001068947087119329</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -24589,6 +25951,12 @@
       <c r="AH227" s="3" t="n">
         <v>0.000212044105173794</v>
       </c>
+      <c r="AI227" s="1" t="n">
+        <v>0.04713</v>
+      </c>
+      <c r="AJ227" s="2" t="n">
+        <v>-0.0008479966080135335</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -24695,6 +26063,12 @@
       <c r="AH228" s="2" t="n">
         <v>-0.00345572354211664</v>
       </c>
+      <c r="AI228" s="1" t="n">
+        <v>0.02304</v>
+      </c>
+      <c r="AJ228" s="2" t="n">
+        <v>-0.001300390117035057</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -24801,6 +26175,12 @@
       <c r="AH229" s="3" t="n">
         <v>0.0009157509157508148</v>
       </c>
+      <c r="AI229" s="1" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="AJ229" s="2" t="n">
+        <v>-0.006404391582799564</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -24907,6 +26287,12 @@
       <c r="AH230" s="3" t="n">
         <v>0.0005998800239953014</v>
       </c>
+      <c r="AI230" s="1" t="n">
+        <v>0.1665</v>
+      </c>
+      <c r="AJ230" s="2" t="n">
+        <v>-0.001798561151079105</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -25013,6 +26399,12 @@
       <c r="AH231" s="2" t="n">
         <v>-0.001643115346697271</v>
       </c>
+      <c r="AI231" s="1" t="n">
+        <v>0.03035</v>
+      </c>
+      <c r="AJ231" s="2" t="n">
+        <v>-0.0009874917709019832</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -25119,6 +26511,12 @@
       <c r="AH232" s="2" t="n">
         <v>-0.004010695187165921</v>
       </c>
+      <c r="AI232" s="1" t="n">
+        <v>0.02231</v>
+      </c>
+      <c r="AJ232" s="2" t="n">
+        <v>-0.001789709172259435</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -25225,6 +26623,12 @@
       <c r="AH233" s="2" t="n">
         <v>-0.0115996258185219</v>
       </c>
+      <c r="AI233" s="1" t="n">
+        <v>0.10465</v>
+      </c>
+      <c r="AJ233" s="2" t="n">
+        <v>-0.009558962710581081</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -25331,6 +26735,12 @@
       <c r="AH234" s="2" t="n">
         <v>-0.0007864726700748465</v>
       </c>
+      <c r="AI234" s="1" t="n">
+        <v>0.2536</v>
+      </c>
+      <c r="AJ234" s="2" t="n">
+        <v>-0.001967729240456515</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -25437,6 +26847,12 @@
       <c r="AH235" s="3" t="n">
         <v>0.0002903178980983052</v>
       </c>
+      <c r="AI235" s="1" t="n">
+        <v>0.06872</v>
+      </c>
+      <c r="AJ235" s="2" t="n">
+        <v>-0.002757219561747144</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -25543,6 +26959,12 @@
       <c r="AH236" s="2" t="n">
         <v>-0.001430842607313082</v>
       </c>
+      <c r="AI236" s="1" t="n">
+        <v>0.12534</v>
+      </c>
+      <c r="AJ236" s="2" t="n">
+        <v>-0.002228944435599446</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -25649,6 +27071,12 @@
       <c r="AH237" s="2" t="n">
         <v>-0.003845167905665324</v>
       </c>
+      <c r="AI237" s="1" t="n">
+        <v>0.03868</v>
+      </c>
+      <c r="AJ237" s="2" t="n">
+        <v>-0.004632012352032928</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -25755,6 +27183,12 @@
       <c r="AH238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI238" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AJ238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -25861,6 +27295,12 @@
       <c r="AH239" s="3" t="n">
         <v>0.001760563380281706</v>
       </c>
+      <c r="AI239" s="1" t="n">
+        <v>0.003966</v>
+      </c>
+      <c r="AJ239" s="2" t="n">
+        <v>-0.004268139593271534</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -25967,6 +27407,12 @@
       <c r="AH240" s="2" t="n">
         <v>-0.001448225923243967</v>
       </c>
+      <c r="AI240" s="1" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="AJ240" s="2" t="n">
+        <v>-0.003625815808556903</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -26073,6 +27519,12 @@
       <c r="AH241" s="3" t="n">
         <v>0.01110104213864966</v>
       </c>
+      <c r="AI241" s="1" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="AJ241" s="2" t="n">
+        <v>-0.008066323101053086</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -26179,6 +27631,12 @@
       <c r="AH242" s="2" t="n">
         <v>-0.003968253968253921</v>
       </c>
+      <c r="AI242" s="1" t="n">
+        <v>0.00749</v>
+      </c>
+      <c r="AJ242" s="2" t="n">
+        <v>-0.005312084993359907</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -26285,6 +27743,12 @@
       <c r="AH243" s="2" t="n">
         <v>-0.008714596949891166</v>
       </c>
+      <c r="AI243" s="1" t="n">
+        <v>0.02265</v>
+      </c>
+      <c r="AJ243" s="2" t="n">
+        <v>-0.004395604395604369</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -26391,6 +27855,12 @@
       <c r="AH244" s="2" t="n">
         <v>-0.002927400468384083</v>
       </c>
+      <c r="AI244" s="1" t="n">
+        <v>0.001698</v>
+      </c>
+      <c r="AJ244" s="2" t="n">
+        <v>-0.002935995302407524</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -26497,6 +27967,12 @@
       <c r="AH245" s="3" t="n">
         <v>0.000758150113722644</v>
       </c>
+      <c r="AI245" s="1" t="n">
+        <v>0.1312</v>
+      </c>
+      <c r="AJ245" s="2" t="n">
+        <v>-0.006060606060606023</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -26603,6 +28079,12 @@
       <c r="AH246" s="3" t="n">
         <v>0.007866582756450604</v>
       </c>
+      <c r="AI246" s="1" t="n">
+        <v>0.03182</v>
+      </c>
+      <c r="AJ246" s="2" t="n">
+        <v>-0.006556353418670054</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -26709,6 +28191,12 @@
       <c r="AH247" s="2" t="n">
         <v>-0.001121704991587089</v>
       </c>
+      <c r="AI247" s="1" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="AJ247" s="2" t="n">
+        <v>-0.002245929253228588</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -26815,6 +28303,12 @@
       <c r="AH248" s="3" t="n">
         <v>0.002632444883185265</v>
       </c>
+      <c r="AI248" s="1" t="n">
+        <v>0.03036</v>
+      </c>
+      <c r="AJ248" s="2" t="n">
+        <v>-0.003610108303249064</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -26921,6 +28415,12 @@
       <c r="AH249" s="2" t="n">
         <v>-0.0143722532367264</v>
       </c>
+      <c r="AI249" s="1" t="n">
+        <v>0.008178</v>
+      </c>
+      <c r="AJ249" s="2" t="n">
+        <v>-0.0144613159797542</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -27027,6 +28527,12 @@
       <c r="AH250" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI250" s="1" t="n">
+        <v>0.01989</v>
+      </c>
+      <c r="AJ250" s="2" t="n">
+        <v>-0.002507522567703007</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -27133,6 +28639,12 @@
       <c r="AH251" s="2" t="n">
         <v>-0.003003647285990157</v>
       </c>
+      <c r="AI251" s="1" t="n">
+        <v>0.04641</v>
+      </c>
+      <c r="AJ251" s="2" t="n">
+        <v>-0.001291155584247849</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -27239,6 +28751,12 @@
       <c r="AH252" s="3" t="n">
         <v>0.0005793071486501907</v>
       </c>
+      <c r="AI252" s="1" t="n">
+        <v>0.00861</v>
+      </c>
+      <c r="AJ252" s="2" t="n">
+        <v>-0.003010653080129687</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -27345,6 +28863,12 @@
       <c r="AH253" s="2" t="n">
         <v>-0.001808785529715778</v>
       </c>
+      <c r="AI253" s="1" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="AJ253" s="2" t="n">
+        <v>-0.003365260160496976</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -27451,6 +28975,12 @@
       <c r="AH254" s="2" t="n">
         <v>-0.0006521030322790735</v>
       </c>
+      <c r="AI254" s="1" t="n">
+        <v>0.06111</v>
+      </c>
+      <c r="AJ254" s="2" t="n">
+        <v>-0.00309951060358895</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -27557,6 +29087,12 @@
       <c r="AH255" s="2" t="n">
         <v>-0.003358522250209868</v>
       </c>
+      <c r="AI255" s="1" t="n">
+        <v>0.003533</v>
+      </c>
+      <c r="AJ255" s="2" t="n">
+        <v>-0.007862959842740751</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -27663,6 +29199,12 @@
       <c r="AH256" s="2" t="n">
         <v>-0.001342782543826979</v>
       </c>
+      <c r="AI256" s="1" t="n">
+        <v>0.013396</v>
+      </c>
+      <c r="AJ256" s="3" t="n">
+        <v>0.0006722940165832769</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -27769,6 +29311,12 @@
       <c r="AH257" s="3" t="n">
         <v>2.701426353114369e-05</v>
       </c>
+      <c r="AI257" s="1" t="n">
+        <v>0.999444</v>
+      </c>
+      <c r="AJ257" s="2" t="n">
+        <v>-5.502756881200206e-05</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -27875,6 +29423,12 @@
       <c r="AH258" s="2" t="n">
         <v>-0.0009038526720145816</v>
       </c>
+      <c r="AI258" s="1" t="n">
+        <v>0.08838</v>
+      </c>
+      <c r="AJ258" s="2" t="n">
+        <v>-0.0005654189754607542</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -27981,6 +29535,12 @@
       <c r="AH259" s="3" t="n">
         <v>0.001332593003886675</v>
       </c>
+      <c r="AI259" s="1" t="n">
+        <v>0.08974</v>
+      </c>
+      <c r="AJ259" s="2" t="n">
+        <v>-0.004768770100920481</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -28087,6 +29647,12 @@
       <c r="AH260" s="3" t="n">
         <v>0.002205882352941172</v>
       </c>
+      <c r="AI260" s="1" t="n">
+        <v>0.08149000000000001</v>
+      </c>
+      <c r="AJ260" s="2" t="n">
+        <v>-0.003546099290780124</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -28193,6 +29759,12 @@
       <c r="AH261" s="3" t="n">
         <v>0.0008865248226951348</v>
       </c>
+      <c r="AI261" s="1" t="n">
+        <v>1.126</v>
+      </c>
+      <c r="AJ261" s="2" t="n">
+        <v>-0.002657218777679463</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -28299,6 +29871,12 @@
       <c r="AH262" s="3" t="n">
         <v>0.002617801047120426</v>
       </c>
+      <c r="AI262" s="1" t="n">
+        <v>0.003873</v>
+      </c>
+      <c r="AJ262" s="3" t="n">
+        <v>0.01122715404699741</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -28405,6 +29983,12 @@
       <c r="AH263" s="2" t="n">
         <v>-0.003457216940362987</v>
       </c>
+      <c r="AI263" s="1" t="n">
+        <v>0.1153</v>
+      </c>
+      <c r="AJ263" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -28511,6 +30095,12 @@
       <c r="AH264" s="2" t="n">
         <v>-0.00512820512820508</v>
       </c>
+      <c r="AI264" s="1" t="n">
+        <v>0.0006147</v>
+      </c>
+      <c r="AJ264" s="2" t="n">
+        <v>-0.009826030927835029</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -28617,6 +30207,12 @@
       <c r="AH265" s="2" t="n">
         <v>-0.0006802721088435097</v>
       </c>
+      <c r="AI265" s="1" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="AJ265" s="2" t="n">
+        <v>-0.006126616746085759</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -28723,6 +30319,12 @@
       <c r="AH266" s="2" t="n">
         <v>-0.003139717425431801</v>
       </c>
+      <c r="AI266" s="1" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="AJ266" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -28829,6 +30431,12 @@
       <c r="AH267" s="2" t="n">
         <v>-0.0006134969325153125</v>
       </c>
+      <c r="AI267" s="1" t="n">
+        <v>0.01624</v>
+      </c>
+      <c r="AJ267" s="2" t="n">
+        <v>-0.003069367710251563</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -28935,6 +30543,12 @@
       <c r="AH268" s="3" t="n">
         <v>0.004158004158004134</v>
       </c>
+      <c r="AI268" s="1" t="n">
+        <v>0.0004358</v>
+      </c>
+      <c r="AJ268" s="3" t="n">
+        <v>0.002530480791350418</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -29041,6 +30655,12 @@
       <c r="AH269" s="2" t="n">
         <v>-0.001437470052707177</v>
       </c>
+      <c r="AI269" s="1" t="n">
+        <v>0.02075</v>
+      </c>
+      <c r="AJ269" s="2" t="n">
+        <v>-0.004318618042226478</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -29147,6 +30767,12 @@
       <c r="AH270" s="2" t="n">
         <v>-0.001644736842105234</v>
       </c>
+      <c r="AI270" s="1" t="n">
+        <v>0.1814</v>
+      </c>
+      <c r="AJ270" s="2" t="n">
+        <v>-0.003844041735310303</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -29253,6 +30879,12 @@
       <c r="AH271" s="2" t="n">
         <v>-0.00405131667792044</v>
       </c>
+      <c r="AI271" s="1" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="AJ271" s="3" t="n">
+        <v>0.001355932203389869</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -29359,6 +30991,12 @@
       <c r="AH272" s="3" t="n">
         <v>0.000504540867810272</v>
       </c>
+      <c r="AI272" s="1" t="n">
+        <v>0.03955</v>
+      </c>
+      <c r="AJ272" s="2" t="n">
+        <v>-0.002773575390821962</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -29465,6 +31103,12 @@
       <c r="AH273" s="3" t="n">
         <v>0.001078748651564187</v>
       </c>
+      <c r="AI273" s="1" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="AJ273" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -29571,6 +31215,12 @@
       <c r="AH274" s="2" t="n">
         <v>-0.001416653549504225</v>
       </c>
+      <c r="AI274" s="1" t="n">
+        <v>63.38</v>
+      </c>
+      <c r="AJ274" s="2" t="n">
+        <v>-0.0009457755359393943</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -29677,6 +31327,12 @@
       <c r="AH275" s="3" t="n">
         <v>0.0008849557522125069</v>
       </c>
+      <c r="AI275" s="1" t="n">
+        <v>0.01134</v>
+      </c>
+      <c r="AJ275" s="3" t="n">
+        <v>0.002652519893899096</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -29783,6 +31439,12 @@
       <c r="AH276" s="3" t="n">
         <v>0.00115118956254801</v>
       </c>
+      <c r="AI276" s="1" t="n">
+        <v>2.614</v>
+      </c>
+      <c r="AJ276" s="3" t="n">
+        <v>0.001916443081640435</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -29889,6 +31551,12 @@
       <c r="AH277" s="3" t="n">
         <v>0.0002381519409383916</v>
       </c>
+      <c r="AI277" s="1" t="n">
+        <v>0.04187</v>
+      </c>
+      <c r="AJ277" s="2" t="n">
+        <v>-0.003095238095238217</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -29995,6 +31663,12 @@
       <c r="AH278" s="2" t="n">
         <v>-0.007598784194528917</v>
       </c>
+      <c r="AI278" s="1" t="n">
+        <v>0.01955</v>
+      </c>
+      <c r="AJ278" s="2" t="n">
+        <v>-0.002041858090862602</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -30101,6 +31775,12 @@
       <c r="AH279" s="3" t="n">
         <v>0.02150728759331682</v>
       </c>
+      <c r="AI279" s="1" t="n">
+        <v>0.005667</v>
+      </c>
+      <c r="AJ279" s="2" t="n">
+        <v>-0.01392030624673746</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -30207,6 +31887,12 @@
       <c r="AH280" s="2" t="n">
         <v>-0.005870342011230246</v>
       </c>
+      <c r="AI280" s="1" t="n">
+        <v>0.03888</v>
+      </c>
+      <c r="AJ280" s="2" t="n">
+        <v>-0.001797175866495523</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -30313,6 +31999,12 @@
       <c r="AH281" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI281" s="1" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="AJ281" s="2" t="n">
+        <v>-0.004400440044004405</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -30419,6 +32111,12 @@
       <c r="AH282" s="2" t="n">
         <v>-0.0007228915662650778</v>
       </c>
+      <c r="AI282" s="1" t="n">
+        <v>0.0004141</v>
+      </c>
+      <c r="AJ282" s="2" t="n">
+        <v>-0.001446829033035965</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -30525,6 +32223,12 @@
       <c r="AH283" s="2" t="n">
         <v>-0.0007320644216691617</v>
       </c>
+      <c r="AI283" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AJ283" s="3" t="n">
+        <v>0.001221001221001256</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -30631,6 +32335,12 @@
       <c r="AH284" s="3" t="n">
         <v>0.001182592242194925</v>
       </c>
+      <c r="AI284" s="1" t="n">
+        <v>0.04204</v>
+      </c>
+      <c r="AJ284" s="2" t="n">
+        <v>-0.006850933144342041</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -30737,6 +32447,12 @@
       <c r="AH285" s="3" t="n">
         <v>0.005393342012274476</v>
       </c>
+      <c r="AI285" s="1" t="n">
+        <v>0.10761</v>
+      </c>
+      <c r="AJ285" s="2" t="n">
+        <v>-0.00471698113207544</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -30843,6 +32559,12 @@
       <c r="AH286" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI286" s="1" t="n">
+        <v>0.00421</v>
+      </c>
+      <c r="AJ286" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -30949,6 +32671,12 @@
       <c r="AH287" s="3" t="n">
         <v>0.00301823786283071</v>
       </c>
+      <c r="AI287" s="1" t="n">
+        <v>0.15616</v>
+      </c>
+      <c r="AJ287" s="2" t="n">
+        <v>-0.0001920737563224422</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -31055,6 +32783,12 @@
       <c r="AH288" s="3" t="n">
         <v>0.001662971175166268</v>
       </c>
+      <c r="AI288" s="1" t="n">
+        <v>0.1798</v>
+      </c>
+      <c r="AJ288" s="2" t="n">
+        <v>-0.004980630879911521</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -31161,6 +32895,12 @@
       <c r="AH289" s="2" t="n">
         <v>-0.0007190795781400082</v>
       </c>
+      <c r="AI289" s="1" t="n">
+        <v>4.147</v>
+      </c>
+      <c r="AJ289" s="2" t="n">
+        <v>-0.005277044854881112</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -31267,6 +33007,12 @@
       <c r="AH290" s="2" t="n">
         <v>-0.003256192580532649</v>
       </c>
+      <c r="AI290" s="1" t="n">
+        <v>0.08556999999999999</v>
+      </c>
+      <c r="AJ290" s="2" t="n">
+        <v>-0.001633415004083552</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -31373,6 +33119,12 @@
       <c r="AH291" s="2" t="n">
         <v>-0.003095104108047242</v>
       </c>
+      <c r="AI291" s="1" t="n">
+        <v>0.03543</v>
+      </c>
+      <c r="AJ291" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -31479,6 +33231,12 @@
       <c r="AH292" s="3" t="n">
         <v>0.002328448157786653</v>
       </c>
+      <c r="AI292" s="1" t="n">
+        <v>1.4641</v>
+      </c>
+      <c r="AJ292" s="3" t="n">
+        <v>0.0003416233943700088</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -31585,6 +33343,12 @@
       <c r="AH293" s="2" t="n">
         <v>-0.001358926448106029</v>
       </c>
+      <c r="AI293" s="1" t="n">
+        <v>0.005872</v>
+      </c>
+      <c r="AJ293" s="2" t="n">
+        <v>-0.001190678686851516</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -31691,6 +33455,12 @@
       <c r="AH294" s="2" t="n">
         <v>-0.0005802146794313408</v>
       </c>
+      <c r="AI294" s="1" t="n">
+        <v>0.003427</v>
+      </c>
+      <c r="AJ294" s="2" t="n">
+        <v>-0.005224963715529817</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -31797,6 +33567,12 @@
       <c r="AH295" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI295" s="1" t="n">
+        <v>0.5387999999999999</v>
+      </c>
+      <c r="AJ295" s="2" t="n">
+        <v>-0.002222222222222388</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -31903,6 +33679,12 @@
       <c r="AH296" s="2" t="n">
         <v>-0.001769128704113226</v>
       </c>
+      <c r="AI296" s="1" t="n">
+        <v>2.249</v>
+      </c>
+      <c r="AJ296" s="2" t="n">
+        <v>-0.003544528134692072</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -32009,6 +33791,12 @@
       <c r="AH297" s="2" t="n">
         <v>-0.001188354129530758</v>
       </c>
+      <c r="AI297" s="1" t="n">
+        <v>0.01664</v>
+      </c>
+      <c r="AJ297" s="2" t="n">
+        <v>-0.01011302795954789</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -32115,6 +33903,12 @@
       <c r="AH298" s="3" t="n">
         <v>0.004103967168262657</v>
       </c>
+      <c r="AI298" s="1" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="AJ298" s="3" t="n">
+        <v>0.0008174386920981539</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -32221,6 +34015,12 @@
       <c r="AH299" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI299" s="1" t="n">
+        <v>0.01108</v>
+      </c>
+      <c r="AJ299" s="2" t="n">
+        <v>-0.003597122302158283</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -32327,6 +34127,12 @@
       <c r="AH300" s="3" t="n">
         <v>0.001443695861405138</v>
       </c>
+      <c r="AI300" s="1" t="n">
+        <v>0.02076</v>
+      </c>
+      <c r="AJ300" s="2" t="n">
+        <v>-0.00240269101393551</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -32433,6 +34239,12 @@
       <c r="AH301" s="2" t="n">
         <v>-0.01267468313292154</v>
       </c>
+      <c r="AI301" s="1" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="AJ301" s="2" t="n">
+        <v>-0.005266622778143483</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -32539,6 +34351,12 @@
       <c r="AH302" s="3" t="n">
         <v>0.0007235890014471485</v>
       </c>
+      <c r="AI302" s="1" t="n">
+        <v>0.01386</v>
+      </c>
+      <c r="AJ302" s="3" t="n">
+        <v>0.002169197396963161</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -32645,6 +34463,12 @@
       <c r="AH303" s="2" t="n">
         <v>-0.0008097165991903441</v>
       </c>
+      <c r="AI303" s="1" t="n">
+        <v>0.07389</v>
+      </c>
+      <c r="AJ303" s="2" t="n">
+        <v>-0.002025931928687161</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -32751,6 +34575,12 @@
       <c r="AH304" s="3" t="n">
         <v>0.0006277463904582293</v>
       </c>
+      <c r="AI304" s="1" t="n">
+        <v>0.01588</v>
+      </c>
+      <c r="AJ304" s="2" t="n">
+        <v>-0.003764115432873339</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -32857,6 +34687,12 @@
       <c r="AH305" s="2" t="n">
         <v>-0.001394700139470118</v>
       </c>
+      <c r="AI305" s="1" t="n">
+        <v>0.06413000000000001</v>
+      </c>
+      <c r="AJ305" s="2" t="n">
+        <v>-0.004810676598385953</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -32963,6 +34799,12 @@
       <c r="AH306" s="2" t="n">
         <v>-0.001812323801852594</v>
       </c>
+      <c r="AI306" s="1" t="n">
+        <v>0.04936</v>
+      </c>
+      <c r="AJ306" s="2" t="n">
+        <v>-0.004236433326608873</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -33069,6 +34911,12 @@
       <c r="AH307" s="2" t="n">
         <v>-0.001075268817204302</v>
       </c>
+      <c r="AI307" s="1" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="AJ307" s="2" t="n">
+        <v>-0.006458557588805172</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -33175,6 +35023,12 @@
       <c r="AH308" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI308" s="1" t="n">
+        <v>0.03973</v>
+      </c>
+      <c r="AJ308" s="2" t="n">
+        <v>-0.003011292346298497</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -33281,6 +35135,12 @@
       <c r="AH309" s="2" t="n">
         <v>-0.002564102564102571</v>
       </c>
+      <c r="AI309" s="1" t="n">
+        <v>0.01548</v>
+      </c>
+      <c r="AJ309" s="2" t="n">
+        <v>-0.0051413881748071</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -33387,6 +35247,12 @@
       <c r="AH310" s="2" t="n">
         <v>-0.0009129085265656643</v>
       </c>
+      <c r="AI310" s="1" t="n">
+        <v>0.05465</v>
+      </c>
+      <c r="AJ310" s="2" t="n">
+        <v>-0.001279239766081883</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -33493,6 +35359,12 @@
       <c r="AH311" s="2" t="n">
         <v>-0.001116819298637435</v>
       </c>
+      <c r="AI311" s="1" t="n">
+        <v>0.004491</v>
+      </c>
+      <c r="AJ311" s="3" t="n">
+        <v>0.004248658318425742</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -33599,6 +35471,12 @@
       <c r="AH312" s="3" t="n">
         <v>0.0002356545304582567</v>
       </c>
+      <c r="AI312" s="1" t="n">
+        <v>0.0847</v>
+      </c>
+      <c r="AJ312" s="2" t="n">
+        <v>-0.002238190599599431</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -33705,6 +35583,12 @@
       <c r="AH313" s="2" t="n">
         <v>-0.0009347042328748914</v>
       </c>
+      <c r="AI313" s="1" t="n">
+        <v>0.07459</v>
+      </c>
+      <c r="AJ313" s="2" t="n">
+        <v>-0.003074044373162177</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -33811,6 +35695,12 @@
       <c r="AH314" s="2" t="n">
         <v>-0.00195694716242658</v>
       </c>
+      <c r="AI314" s="1" t="n">
+        <v>0.1529</v>
+      </c>
+      <c r="AJ314" s="2" t="n">
+        <v>-0.0006535947712417581</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -33917,6 +35807,12 @@
       <c r="AH315" s="2" t="n">
         <v>-0.0006253908692932395</v>
       </c>
+      <c r="AI315" s="1" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="AJ315" s="2" t="n">
+        <v>-0.003128911138923658</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -34023,6 +35919,12 @@
       <c r="AH316" s="2" t="n">
         <v>-0.001657458563535883</v>
       </c>
+      <c r="AI316" s="1" t="n">
+        <v>0.1806</v>
+      </c>
+      <c r="AJ316" s="2" t="n">
+        <v>-0.0005534034311012119</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -34129,6 +36031,12 @@
       <c r="AH317" s="3" t="n">
         <v>0.001599360255897622</v>
       </c>
+      <c r="AI317" s="1" t="n">
+        <v>0.00749</v>
+      </c>
+      <c r="AJ317" s="2" t="n">
+        <v>-0.00332667997338654</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -34235,6 +36143,12 @@
       <c r="AH318" s="3" t="n">
         <v>0.01212482607831444</v>
       </c>
+      <c r="AI318" s="1" t="n">
+        <v>0.05074</v>
+      </c>
+      <c r="AJ318" s="2" t="n">
+        <v>-0.003534956794972498</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -34341,6 +36255,12 @@
       <c r="AH319" s="3" t="n">
         <v>0.001181948424068757</v>
       </c>
+      <c r="AI319" s="1" t="n">
+        <v>0.27985</v>
+      </c>
+      <c r="AJ319" s="3" t="n">
+        <v>0.001144778735734937</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -34447,6 +36367,12 @@
       <c r="AH320" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI320" s="1" t="n">
+        <v>0.4402</v>
+      </c>
+      <c r="AJ320" s="2" t="n">
+        <v>-0.001587661601270206</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -34553,6 +36479,12 @@
       <c r="AH321" s="2" t="n">
         <v>-0.002822684115986631</v>
       </c>
+      <c r="AI321" s="1" t="n">
+        <v>0.07746</v>
+      </c>
+      <c r="AJ321" s="2" t="n">
+        <v>-0.003345342254245964</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -34659,6 +36591,12 @@
       <c r="AH322" s="2" t="n">
         <v>-0.01224739742804655</v>
       </c>
+      <c r="AI322" s="1" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="AJ322" s="3" t="n">
+        <v>0.001859888406695566</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -34765,6 +36703,12 @@
       <c r="AH323" s="3" t="n">
         <v>0.001010101010101011</v>
       </c>
+      <c r="AI323" s="1" t="n">
+        <v>1.977</v>
+      </c>
+      <c r="AJ323" s="2" t="n">
+        <v>-0.00252270433905141</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -34871,6 +36815,12 @@
       <c r="AH324" s="3" t="n">
         <v>0.0005063955887317463</v>
       </c>
+      <c r="AI324" s="1" t="n">
+        <v>0.053213</v>
+      </c>
+      <c r="AJ324" s="2" t="n">
+        <v>-0.002474458712156589</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -34977,6 +36927,12 @@
       <c r="AH325" s="3" t="n">
         <v>0.002614891808851484</v>
       </c>
+      <c r="AI325" s="1" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="AJ325" s="2" t="n">
+        <v>-0.005020538566864399</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -35083,6 +37039,12 @@
       <c r="AH326" s="3" t="n">
         <v>0.001858736059479532</v>
       </c>
+      <c r="AI326" s="1" t="n">
+        <v>0.006451</v>
+      </c>
+      <c r="AJ326" s="2" t="n">
+        <v>-0.002628324056895432</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -35189,6 +37151,12 @@
       <c r="AH327" s="3" t="n">
         <v>0.002961500493583409</v>
       </c>
+      <c r="AI327" s="1" t="n">
+        <v>0.015162</v>
+      </c>
+      <c r="AJ327" s="2" t="n">
+        <v>-0.005118110236220469</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -35295,6 +37263,12 @@
       <c r="AH328" s="3" t="n">
         <v>0.002076843198338585</v>
       </c>
+      <c r="AI328" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="AJ328" s="2" t="n">
+        <v>-0.005181347150259072</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -35401,6 +37375,12 @@
       <c r="AH329" s="2" t="n">
         <v>-0.001136621959536212</v>
       </c>
+      <c r="AI329" s="1" t="n">
+        <v>0.004376</v>
+      </c>
+      <c r="AJ329" s="2" t="n">
+        <v>-0.004096495220755725</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -35507,6 +37487,12 @@
       <c r="AH330" s="3" t="n">
         <v>0.0007690828686790688</v>
       </c>
+      <c r="AI330" s="1" t="n">
+        <v>0.05202</v>
+      </c>
+      <c r="AJ330" s="2" t="n">
+        <v>-0.0005763688760807348</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -35613,6 +37599,12 @@
       <c r="AH331" s="2" t="n">
         <v>-0.0008363534987455325</v>
       </c>
+      <c r="AI331" s="1" t="n">
+        <v>0.03576</v>
+      </c>
+      <c r="AJ331" s="2" t="n">
+        <v>-0.002232142857142766</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -35719,6 +37711,12 @@
       <c r="AH332" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI332" s="1" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="AJ332" s="2" t="n">
+        <v>-0.004704301075268673</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -35825,6 +37823,12 @@
       <c r="AH333" s="2" t="n">
         <v>-0.001036269430051843</v>
       </c>
+      <c r="AI333" s="1" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="AJ333" s="2" t="n">
+        <v>-0.002074688796680557</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -35931,6 +37935,12 @@
       <c r="AH334" s="2" t="n">
         <v>-0.0004544421722335648</v>
       </c>
+      <c r="AI334" s="1" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="AJ334" s="3" t="n">
+        <v>0.002500568310979745</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -36037,6 +38047,12 @@
       <c r="AH335" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI335" s="1" t="n">
+        <v>0.08132</v>
+      </c>
+      <c r="AJ335" s="2" t="n">
+        <v>-0.006839276990718015</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -36143,6 +38159,12 @@
       <c r="AH336" s="3" t="n">
         <v>0.0004842615012107349</v>
       </c>
+      <c r="AI336" s="1" t="n">
+        <v>0.2064</v>
+      </c>
+      <c r="AJ336" s="2" t="n">
+        <v>-0.0009680542110358457</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -36249,6 +38271,12 @@
       <c r="AH337" s="2" t="n">
         <v>-0.0009871668311944317</v>
       </c>
+      <c r="AI337" s="1" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="AJ337" s="2" t="n">
+        <v>-0.001976284584980328</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -36355,6 +38383,12 @@
       <c r="AH338" s="2" t="n">
         <v>-0.0008771929824561654</v>
       </c>
+      <c r="AI338" s="1" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="AJ338" s="2" t="n">
+        <v>-0.001755926251097504</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -36461,6 +38495,12 @@
       <c r="AH339" s="2" t="n">
         <v>-0.001091703056768514</v>
       </c>
+      <c r="AI339" s="1" t="n">
+        <v>0.01823</v>
+      </c>
+      <c r="AJ339" s="2" t="n">
+        <v>-0.003825136612021892</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -36567,6 +38607,12 @@
       <c r="AH340" s="2" t="n">
         <v>-0.0002941176470589135</v>
       </c>
+      <c r="AI340" s="1" t="n">
+        <v>0.2742</v>
+      </c>
+      <c r="AJ340" s="3" t="n">
+        <v>0.008384819064430732</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -36673,6 +38719,12 @@
       <c r="AH341" s="2" t="n">
         <v>-0.0009310986964617871</v>
       </c>
+      <c r="AI341" s="1" t="n">
+        <v>0.04273</v>
+      </c>
+      <c r="AJ341" s="2" t="n">
+        <v>-0.004426840633737248</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -36779,6 +38831,12 @@
       <c r="AH342" s="2" t="n">
         <v>-0.006789890607317978</v>
       </c>
+      <c r="AI342" s="1" t="n">
+        <v>0.07856</v>
+      </c>
+      <c r="AJ342" s="2" t="n">
+        <v>-0.005443727054057474</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -36885,6 +38943,12 @@
       <c r="AH343" s="2" t="n">
         <v>-0.0009139574356965235</v>
       </c>
+      <c r="AI343" s="1" t="n">
+        <v>7.633</v>
+      </c>
+      <c r="AJ343" s="2" t="n">
+        <v>-0.002483010977522233</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -36991,6 +39055,12 @@
       <c r="AH344" s="3" t="n">
         <v>0.0009945300845351317</v>
       </c>
+      <c r="AI344" s="1" t="n">
+        <v>0.6028</v>
+      </c>
+      <c r="AJ344" s="2" t="n">
+        <v>-0.001821493624772297</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -37097,6 +39167,12 @@
       <c r="AH345" s="2" t="n">
         <v>-0.00079850944902854</v>
       </c>
+      <c r="AI345" s="1" t="n">
+        <v>0.03733</v>
+      </c>
+      <c r="AJ345" s="2" t="n">
+        <v>-0.005594033031433003</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -37203,6 +39279,12 @@
       <c r="AH346" s="2" t="n">
         <v>-0.002398081534772251</v>
       </c>
+      <c r="AI346" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="AJ346" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -37309,6 +39391,12 @@
       <c r="AH347" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI347" s="1" t="n">
+        <v>0.1751</v>
+      </c>
+      <c r="AJ347" s="2" t="n">
+        <v>-0.001710376282782182</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -37415,6 +39503,12 @@
       <c r="AH348" s="3" t="n">
         <v>0.001734605377276669</v>
       </c>
+      <c r="AI348" s="1" t="n">
+        <v>5198</v>
+      </c>
+      <c r="AJ348" s="3" t="n">
+        <v>9.62000962000962e-05</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -37521,6 +39615,12 @@
       <c r="AH349" s="2" t="n">
         <v>-0.0007304601899197463</v>
       </c>
+      <c r="AI349" s="1" t="n">
+        <v>0.01359</v>
+      </c>
+      <c r="AJ349" s="2" t="n">
+        <v>-0.006578947368421038</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -37627,6 +39727,12 @@
       <c r="AH350" s="2" t="n">
         <v>-0.001282873636946708</v>
       </c>
+      <c r="AI350" s="1" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AJ350" s="3" t="n">
+        <v>0.003211303789338452</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -37733,6 +39839,12 @@
       <c r="AH351" s="3" t="n">
         <v>0.0004850444624089783</v>
       </c>
+      <c r="AI351" s="1" t="n">
+        <v>0.0006174</v>
+      </c>
+      <c r="AJ351" s="2" t="n">
+        <v>-0.002262443438913907</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -37839,6 +39951,12 @@
       <c r="AH352" s="2" t="n">
         <v>-0.0005037783375314656</v>
       </c>
+      <c r="AI352" s="1" t="n">
+        <v>0.01981</v>
+      </c>
+      <c r="AJ352" s="2" t="n">
+        <v>-0.001512096774193487</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -37945,6 +40063,12 @@
       <c r="AH353" s="3" t="n">
         <v>0.002253944402704753</v>
       </c>
+      <c r="AI353" s="1" t="n">
+        <v>0.0931</v>
+      </c>
+      <c r="AJ353" s="2" t="n">
+        <v>-0.002998500749625214</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -38051,6 +40175,12 @@
       <c r="AH354" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI354" s="1" t="n">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="AJ354" s="2" t="n">
+        <v>-0.003311258278145637</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -38157,6 +40287,12 @@
       <c r="AH355" s="3" t="n">
         <v>0.001479289940828349</v>
       </c>
+      <c r="AI355" s="1" t="n">
+        <v>0.0006153</v>
+      </c>
+      <c r="AJ355" s="3" t="n">
+        <v>0.009847365829640633</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -38263,6 +40399,12 @@
       <c r="AH356" s="2" t="n">
         <v>-0.001482213438735234</v>
       </c>
+      <c r="AI356" s="1" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="AJ356" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -38369,6 +40511,12 @@
       <c r="AH357" s="2" t="n">
         <v>-0.002609830361026578</v>
       </c>
+      <c r="AI357" s="1" t="n">
+        <v>0.02292</v>
+      </c>
+      <c r="AJ357" s="2" t="n">
+        <v>-0.0004361098996947053</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -38475,6 +40623,12 @@
       <c r="AH358" s="2" t="n">
         <v>-0.004878048780487791</v>
       </c>
+      <c r="AI358" s="1" t="n">
+        <v>0.000409</v>
+      </c>
+      <c r="AJ358" s="3" t="n">
+        <v>0.002450980392156922</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -38581,6 +40735,12 @@
       <c r="AH359" s="3" t="n">
         <v>0.001357773251866883</v>
       </c>
+      <c r="AI359" s="1" t="n">
+        <v>0.01472</v>
+      </c>
+      <c r="AJ359" s="2" t="n">
+        <v>-0.002033898305084663</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -38687,6 +40847,12 @@
       <c r="AH360" s="2" t="n">
         <v>-0.003277711561382646</v>
       </c>
+      <c r="AI360" s="1" t="n">
+        <v>0.003331</v>
+      </c>
+      <c r="AJ360" s="2" t="n">
+        <v>-0.004185351270552972</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -38793,6 +40959,12 @@
       <c r="AH361" s="3" t="n">
         <v>0.0009392611145897524</v>
       </c>
+      <c r="AI361" s="1" t="n">
+        <v>0.6364</v>
+      </c>
+      <c r="AJ361" s="2" t="n">
+        <v>-0.004691898654989057</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -38899,6 +41071,12 @@
       <c r="AH362" s="3" t="n">
         <v>0.001694915254237366</v>
       </c>
+      <c r="AI362" s="1" t="n">
+        <v>0.02357</v>
+      </c>
+      <c r="AJ362" s="2" t="n">
+        <v>-0.002961082910321515</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -39005,6 +41183,12 @@
       <c r="AH363" s="2" t="n">
         <v>-0.001375095492742443</v>
       </c>
+      <c r="AI363" s="1" t="n">
+        <v>0.06526</v>
+      </c>
+      <c r="AJ363" s="2" t="n">
+        <v>-0.001529987760097963</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -39111,6 +41295,12 @@
       <c r="AH364" s="2" t="n">
         <v>-0.0006355932203390072</v>
       </c>
+      <c r="AI364" s="1" t="n">
+        <v>4.704</v>
+      </c>
+      <c r="AJ364" s="2" t="n">
+        <v>-0.002755988976044075</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -39217,6 +41407,12 @@
       <c r="AH365" s="3" t="n">
         <v>0.0008354218880535296</v>
       </c>
+      <c r="AI365" s="1" t="n">
+        <v>0.07189</v>
+      </c>
+      <c r="AJ365" s="3" t="n">
+        <v>0.0001391207568168631</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -39323,6 +41519,12 @@
       <c r="AH366" s="3" t="n">
         <v>0.0007132667617689962</v>
       </c>
+      <c r="AI366" s="1" t="n">
+        <v>0.05592</v>
+      </c>
+      <c r="AJ366" s="2" t="n">
+        <v>-0.003563791874554628</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -39429,6 +41631,12 @@
       <c r="AH367" s="2" t="n">
         <v>-0.0008552856654122722</v>
       </c>
+      <c r="AI367" s="1" t="n">
+        <v>0.05833</v>
+      </c>
+      <c r="AJ367" s="2" t="n">
+        <v>-0.0013696284882725</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -39535,6 +41743,12 @@
       <c r="AH368" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI368" s="1" t="n">
+        <v>0.05697</v>
+      </c>
+      <c r="AJ368" s="2" t="n">
+        <v>-0.004543071815481448</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -39641,6 +41855,12 @@
       <c r="AH369" s="3" t="n">
         <v>0.000643086816720231</v>
       </c>
+      <c r="AI369" s="1" t="n">
+        <v>0.03101</v>
+      </c>
+      <c r="AJ369" s="2" t="n">
+        <v>-0.003534704370179916</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -39747,6 +41967,12 @@
       <c r="AH370" s="2" t="n">
         <v>-0.004305043050430443</v>
       </c>
+      <c r="AI370" s="1" t="n">
+        <v>0.0001615</v>
+      </c>
+      <c r="AJ370" s="2" t="n">
+        <v>-0.002470660901791289</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -39853,6 +42079,12 @@
       <c r="AH371" s="2" t="n">
         <v>-0.002487562189054676</v>
       </c>
+      <c r="AI371" s="1" t="n">
+        <v>0.006816</v>
+      </c>
+      <c r="AJ371" s="2" t="n">
+        <v>-0.0001466920932961908</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -39959,6 +42191,12 @@
       <c r="AH372" s="2" t="n">
         <v>-0.003149606299212644</v>
       </c>
+      <c r="AI372" s="1" t="n">
+        <v>0.006955</v>
+      </c>
+      <c r="AJ372" s="2" t="n">
+        <v>-0.001148930058882569</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -40065,6 +42303,12 @@
       <c r="AH373" s="3" t="n">
         <v>0.009992111490928282</v>
       </c>
+      <c r="AI373" s="1" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AJ373" s="3" t="n">
+        <v>0.007550117156990345</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -40171,6 +42415,12 @@
       <c r="AH374" s="2" t="n">
         <v>-0.0001421060110842138</v>
       </c>
+      <c r="AI374" s="1" t="n">
+        <v>0.07008</v>
+      </c>
+      <c r="AJ374" s="2" t="n">
+        <v>-0.003979533826037556</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -40277,6 +42527,12 @@
       <c r="AH375" s="3" t="n">
         <v>0.001002631908760455</v>
       </c>
+      <c r="AI375" s="1" t="n">
+        <v>0.07951</v>
+      </c>
+      <c r="AJ375" s="2" t="n">
+        <v>-0.004507324402153489</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -40383,6 +42639,12 @@
       <c r="AH376" s="3" t="n">
         <v>0.0007945336087715636</v>
       </c>
+      <c r="AI376" s="1" t="n">
+        <v>0.06302000000000001</v>
+      </c>
+      <c r="AJ376" s="3" t="n">
+        <v>0.0006351222610354438</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -40489,6 +42751,12 @@
       <c r="AH377" s="2" t="n">
         <v>-0.001040853499869851</v>
       </c>
+      <c r="AI377" s="1" t="n">
+        <v>0.07691000000000001</v>
+      </c>
+      <c r="AJ377" s="3" t="n">
+        <v>0.001693149257619238</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -40595,6 +42863,12 @@
       <c r="AH378" s="3" t="n">
         <v>0.008154188287620389</v>
       </c>
+      <c r="AI378" s="1" t="n">
+        <v>0.0004058</v>
+      </c>
+      <c r="AJ378" s="2" t="n">
+        <v>-0.005392156862745096</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -40701,6 +42975,12 @@
       <c r="AH379" s="2" t="n">
         <v>-0.0009478672985782074</v>
       </c>
+      <c r="AI379" s="1" t="n">
+        <v>0.07373</v>
+      </c>
+      <c r="AJ379" s="2" t="n">
+        <v>-0.0006776904310110395</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -40807,6 +43087,12 @@
       <c r="AH380" s="2" t="n">
         <v>-0.0007230657989876472</v>
       </c>
+      <c r="AI380" s="1" t="n">
+        <v>0.001367</v>
+      </c>
+      <c r="AJ380" s="2" t="n">
+        <v>-0.0108538350217077</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -40913,6 +43199,12 @@
       <c r="AH381" s="2" t="n">
         <v>-0.0006277463904581857</v>
       </c>
+      <c r="AI381" s="1" t="n">
+        <v>6.353</v>
+      </c>
+      <c r="AJ381" s="2" t="n">
+        <v>-0.002355527638191044</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -41019,6 +43311,12 @@
       <c r="AH382" s="3" t="n">
         <v>0.002863278453829643</v>
       </c>
+      <c r="AI382" s="1" t="n">
+        <v>0.01419</v>
+      </c>
+      <c r="AJ382" s="3" t="n">
+        <v>0.012847965738758</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -41125,6 +43423,12 @@
       <c r="AH383" s="2" t="n">
         <v>-0.00227790432801813</v>
       </c>
+      <c r="AI383" s="1" t="n">
+        <v>0.01748</v>
+      </c>
+      <c r="AJ383" s="2" t="n">
+        <v>-0.002283105022831155</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -41231,6 +43535,12 @@
       <c r="AH384" s="3" t="n">
         <v>0.00196850393700793</v>
       </c>
+      <c r="AI384" s="1" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="AJ384" s="2" t="n">
+        <v>-0.0009823182711198709</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -41337,6 +43647,12 @@
       <c r="AH385" s="2" t="n">
         <v>-0.0004438526409233617</v>
       </c>
+      <c r="AI385" s="1" t="n">
+        <v>4.488</v>
+      </c>
+      <c r="AJ385" s="2" t="n">
+        <v>-0.003552397868561085</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -41443,6 +43759,12 @@
       <c r="AH386" s="3" t="n">
         <v>0.001531393568146885</v>
       </c>
+      <c r="AI386" s="1" t="n">
+        <v>0.001301</v>
+      </c>
+      <c r="AJ386" s="2" t="n">
+        <v>-0.005351681957186426</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -41549,6 +43871,12 @@
       <c r="AH387" s="2" t="n">
         <v>-0.0005063291139241544</v>
       </c>
+      <c r="AI387" s="1" t="n">
+        <v>0.0005903</v>
+      </c>
+      <c r="AJ387" s="2" t="n">
+        <v>-0.003208375548801067</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -41655,6 +43983,12 @@
       <c r="AH388" s="2" t="n">
         <v>-0.002624671916010392</v>
       </c>
+      <c r="AI388" s="1" t="n">
+        <v>0.01143</v>
+      </c>
+      <c r="AJ388" s="3" t="n">
+        <v>0.002631578947368314</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -41761,6 +44095,12 @@
       <c r="AH389" s="3" t="n">
         <v>0.002205071664829208</v>
       </c>
+      <c r="AI389" s="1" t="n">
+        <v>0.009050000000000001</v>
+      </c>
+      <c r="AJ389" s="2" t="n">
+        <v>-0.004400440044004411</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -41867,6 +44207,12 @@
       <c r="AH390" s="2" t="n">
         <v>-0.001010994565904342</v>
       </c>
+      <c r="AI390" s="1" t="n">
+        <v>0.07890999999999999</v>
+      </c>
+      <c r="AJ390" s="2" t="n">
+        <v>-0.001771030993042394</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -41973,6 +44319,12 @@
       <c r="AH391" s="2" t="n">
         <v>-0.0007683442182098599</v>
       </c>
+      <c r="AI391" s="1" t="n">
+        <v>0.05205</v>
+      </c>
+      <c r="AJ391" s="3" t="n">
+        <v>0.0005767012687428345</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -42079,6 +44431,12 @@
       <c r="AH392" s="2" t="n">
         <v>-0.004201680672268919</v>
       </c>
+      <c r="AI392" s="1" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="AJ392" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -42185,6 +44543,12 @@
       <c r="AH393" s="3" t="n">
         <v>0.004233301975540912</v>
       </c>
+      <c r="AI393" s="1" t="n">
+        <v>0.02113</v>
+      </c>
+      <c r="AJ393" s="2" t="n">
+        <v>-0.01030444964871201</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -42291,6 +44655,12 @@
       <c r="AH394" s="2" t="n">
         <v>-0.002954209748892119</v>
       </c>
+      <c r="AI394" s="1" t="n">
+        <v>0.2014</v>
+      </c>
+      <c r="AJ394" s="2" t="n">
+        <v>-0.005432098765432185</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -42397,6 +44767,12 @@
       <c r="AH395" s="2" t="n">
         <v>-0.002044989775051042</v>
       </c>
+      <c r="AI395" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="AJ395" s="3" t="n">
+        <v>0.001024590163934313</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -42503,6 +44879,12 @@
       <c r="AH396" s="2" t="n">
         <v>-0.005755395683453243</v>
       </c>
+      <c r="AI396" s="1" t="n">
+        <v>2.753</v>
+      </c>
+      <c r="AJ396" s="2" t="n">
+        <v>-0.003979739507959362</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -42609,6 +44991,12 @@
       <c r="AH397" s="2" t="n">
         <v>-0.003149606299212601</v>
       </c>
+      <c r="AI397" s="1" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="AJ397" s="2" t="n">
+        <v>-0.0007898894154819209</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -42715,6 +45103,12 @@
       <c r="AH398" s="3" t="n">
         <v>0.0003998933617702477</v>
       </c>
+      <c r="AI398" s="1" t="n">
+        <v>0.007509</v>
+      </c>
+      <c r="AJ398" s="3" t="n">
+        <v>0.0005329780146568505</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -42821,6 +45215,12 @@
       <c r="AH399" s="2" t="n">
         <v>-0.003853564547206169</v>
       </c>
+      <c r="AI399" s="1" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="AJ399" s="2" t="n">
+        <v>-0.002707930367504967</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -42927,6 +45327,12 @@
       <c r="AH400" s="2" t="n">
         <v>-0.001878522229179852</v>
       </c>
+      <c r="AI400" s="1" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AJ400" s="2" t="n">
+        <v>-0.0003136762860727384</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -43033,6 +45439,12 @@
       <c r="AH401" s="3" t="n">
         <v>0.008142423406017117</v>
       </c>
+      <c r="AI401" s="1" t="n">
+        <v>0.007246</v>
+      </c>
+      <c r="AJ401" s="2" t="n">
+        <v>-0.008076659822039702</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -43139,6 +45551,12 @@
       <c r="AH402" s="2" t="n">
         <v>-0.002604731929672207</v>
       </c>
+      <c r="AI402" s="1" t="n">
+        <v>0.004577</v>
+      </c>
+      <c r="AJ402" s="2" t="n">
+        <v>-0.00391730141458102</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -43245,6 +45663,12 @@
       <c r="AH403" s="3" t="n">
         <v>0.0003750937734433195</v>
       </c>
+      <c r="AI403" s="1" t="n">
+        <v>0.2654</v>
+      </c>
+      <c r="AJ403" s="2" t="n">
+        <v>-0.004874390701162234</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -43351,6 +45775,12 @@
       <c r="AH404" s="3" t="n">
         <v>0.0004166666666667365</v>
       </c>
+      <c r="AI404" s="1" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="AJ404" s="2" t="n">
+        <v>-0.002082465639316953</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -43457,6 +45887,12 @@
       <c r="AH405" s="2" t="n">
         <v>-0.02235080553664624</v>
       </c>
+      <c r="AI405" s="1" t="n">
+        <v>0.0008561</v>
+      </c>
+      <c r="AJ405" s="2" t="n">
+        <v>-0.006498781478472693</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -43563,6 +45999,12 @@
       <c r="AH406" s="2" t="n">
         <v>-0.0009852216748768073</v>
       </c>
+      <c r="AI406" s="1" t="n">
+        <v>0.005041</v>
+      </c>
+      <c r="AJ406" s="2" t="n">
+        <v>-0.005719921104536393</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -43669,6 +46111,12 @@
       <c r="AH407" s="2" t="n">
         <v>-0.000828500414250317</v>
       </c>
+      <c r="AI407" s="1" t="n">
+        <v>0.01199</v>
+      </c>
+      <c r="AJ407" s="2" t="n">
+        <v>-0.005804311774460936</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -43775,6 +46223,12 @@
       <c r="AH408" s="3" t="n">
         <v>0.008861622358554868</v>
       </c>
+      <c r="AI408" s="1" t="n">
+        <v>0.001483</v>
+      </c>
+      <c r="AJ408" s="3" t="n">
+        <v>0.002027027027027003</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -43881,6 +46335,12 @@
       <c r="AH409" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI409" s="1" t="n">
+        <v>0.03931</v>
+      </c>
+      <c r="AJ409" s="3" t="n">
+        <v>0.01210092687950562</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -43987,6 +46447,12 @@
       <c r="AH410" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI410" s="1" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="AJ410" s="2" t="n">
+        <v>-0.006123698714023232</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -44093,6 +46559,12 @@
       <c r="AH411" s="3" t="n">
         <v>0.001574803149606271</v>
       </c>
+      <c r="AI411" s="1" t="n">
+        <v>0.1902</v>
+      </c>
+      <c r="AJ411" s="2" t="n">
+        <v>-0.003144654088050259</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -44199,6 +46671,12 @@
       <c r="AH412" s="2" t="n">
         <v>-0.0005923293351105027</v>
       </c>
+      <c r="AI412" s="1" t="n">
+        <v>0.06739000000000001</v>
+      </c>
+      <c r="AJ412" s="2" t="n">
+        <v>-0.001481700992739502</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -44305,6 +46783,12 @@
       <c r="AH413" s="2" t="n">
         <v>-0.0003943217665615142</v>
       </c>
+      <c r="AI413" s="1" t="n">
+        <v>2531</v>
+      </c>
+      <c r="AJ413" s="2" t="n">
+        <v>-0.001577909270216962</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -44411,6 +46895,12 @@
       <c r="AH414" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI414" s="1" t="n">
+        <v>0.05256</v>
+      </c>
+      <c r="AJ414" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -44517,6 +47007,12 @@
       <c r="AH415" s="2" t="n">
         <v>-0.0005720823798626372</v>
       </c>
+      <c r="AI415" s="1" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ415" s="3" t="n">
+        <v>0.001717229536347963</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -44623,6 +47119,12 @@
       <c r="AH416" s="2" t="n">
         <v>-0.00317597805687885</v>
       </c>
+      <c r="AI416" s="1" t="n">
+        <v>0.06895</v>
+      </c>
+      <c r="AJ416" s="2" t="n">
+        <v>-0.001448225923244068</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -44729,6 +47231,12 @@
       <c r="AH417" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI417" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AJ417" s="2" t="n">
+        <v>-0.01333333333333335</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -44835,6 +47343,12 @@
       <c r="AH418" s="2" t="n">
         <v>-0.0006583278472680497</v>
       </c>
+      <c r="AI418" s="1" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="AJ418" s="2" t="n">
+        <v>-0.003952569169960405</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -44941,6 +47455,12 @@
       <c r="AH419" s="2" t="n">
         <v>-0.008064516129032209</v>
       </c>
+      <c r="AI419" s="1" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="AJ419" s="3" t="n">
+        <v>0.008130081300812959</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -45047,6 +47567,12 @@
       <c r="AH420" s="3" t="n">
         <v>0.003121748178980102</v>
       </c>
+      <c r="AI420" s="1" t="n">
+        <v>0.01916</v>
+      </c>
+      <c r="AJ420" s="2" t="n">
+        <v>-0.00622406639004142</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -45153,6 +47679,12 @@
       <c r="AH421" s="3" t="n">
         <v>0.001183553748777893</v>
       </c>
+      <c r="AI421" s="1" t="n">
+        <v>0.19413</v>
+      </c>
+      <c r="AJ421" s="2" t="n">
+        <v>-0.002210115131579018</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -45259,6 +47791,12 @@
       <c r="AH422" s="2" t="n">
         <v>-0.001746724890829623</v>
       </c>
+      <c r="AI422" s="1" t="n">
+        <v>0.03406</v>
+      </c>
+      <c r="AJ422" s="2" t="n">
+        <v>-0.006707494896471305</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -45365,6 +47903,12 @@
       <c r="AH423" s="2" t="n">
         <v>-0.003516174402250355</v>
       </c>
+      <c r="AI423" s="1" t="n">
+        <v>0.1415</v>
+      </c>
+      <c r="AJ423" s="2" t="n">
+        <v>-0.001411432604093195</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -45471,6 +48015,12 @@
       <c r="AH424" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI424" s="1" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="AJ424" s="2" t="n">
+        <v>-0.001886792452830112</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -45577,6 +48127,12 @@
       <c r="AH425" s="2" t="n">
         <v>-0.0009569377990429568</v>
       </c>
+      <c r="AI425" s="1" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="AJ425" s="3" t="n">
+        <v>0.001915708812260458</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -45683,6 +48239,12 @@
       <c r="AH426" s="2" t="n">
         <v>-0.001406469760900083</v>
       </c>
+      <c r="AI426" s="1" t="n">
+        <v>0.00708</v>
+      </c>
+      <c r="AJ426" s="2" t="n">
+        <v>-0.002816901408450711</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -45789,6 +48351,12 @@
       <c r="AH427" s="2" t="n">
         <v>-0.0003920031360252082</v>
       </c>
+      <c r="AI427" s="1" t="n">
+        <v>0.02549</v>
+      </c>
+      <c r="AJ427" s="2" t="n">
+        <v>-0.0003921568627450821</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -45895,6 +48463,12 @@
       <c r="AH428" s="2" t="n">
         <v>-0.005416717961344409</v>
       </c>
+      <c r="AI428" s="1" t="n">
+        <v>0.008033999999999999</v>
+      </c>
+      <c r="AJ428" s="2" t="n">
+        <v>-0.00556999628666913</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -46001,6 +48575,12 @@
       <c r="AH429" s="2" t="n">
         <v>-0.0008097165991902504</v>
       </c>
+      <c r="AI429" s="1" t="n">
+        <v>0.01233</v>
+      </c>
+      <c r="AJ429" s="2" t="n">
+        <v>-0.0008103727714748454</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -46107,6 +48687,12 @@
       <c r="AH430" s="2" t="n">
         <v>-0.002540726348826834</v>
       </c>
+      <c r="AI430" s="1" t="n">
+        <v>0.06655</v>
+      </c>
+      <c r="AJ430" s="2" t="n">
+        <v>-0.002846868444710755</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -46213,6 +48799,12 @@
       <c r="AH431" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI431" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="AJ431" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -46319,6 +48911,12 @@
       <c r="AH432" s="2" t="n">
         <v>-0.00364697301239974</v>
       </c>
+      <c r="AI432" s="1" t="n">
+        <v>0.009593000000000001</v>
+      </c>
+      <c r="AJ432" s="3" t="n">
+        <v>0.003241999581677632</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -46425,6 +49023,12 @@
       <c r="AH433" s="2" t="n">
         <v>-0.002899251026818121</v>
       </c>
+      <c r="AI433" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="AJ433" s="2" t="n">
+        <v>-0.001696147322510313</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -46531,6 +49135,12 @@
       <c r="AH434" s="2" t="n">
         <v>-0.005612722170252506</v>
       </c>
+      <c r="AI434" s="1" t="n">
+        <v>0.04252</v>
+      </c>
+      <c r="AJ434" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -46637,6 +49247,12 @@
       <c r="AH435" s="2" t="n">
         <v>-0.000642673521850985</v>
       </c>
+      <c r="AI435" s="1" t="n">
+        <v>0.00155</v>
+      </c>
+      <c r="AJ435" s="2" t="n">
+        <v>-0.003215434083601295</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -46743,6 +49359,12 @@
       <c r="AH436" s="3" t="n">
         <v>0.0003632401017072137</v>
       </c>
+      <c r="AI436" s="1" t="n">
+        <v>0.02744</v>
+      </c>
+      <c r="AJ436" s="2" t="n">
+        <v>-0.00363108206245459</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -46849,6 +49471,12 @@
       <c r="AH437" s="3" t="n">
         <v>0.003279484999392765</v>
       </c>
+      <c r="AI437" s="1" t="n">
+        <v>0.08185000000000001</v>
+      </c>
+      <c r="AJ437" s="2" t="n">
+        <v>-0.009079903147699766</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -46955,6 +49583,12 @@
       <c r="AH438" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI438" s="1" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="AJ438" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -47061,6 +49695,12 @@
       <c r="AH439" s="3" t="n">
         <v>0.001287830006439151</v>
       </c>
+      <c r="AI439" s="1" t="n">
+        <v>1.554</v>
+      </c>
+      <c r="AJ439" s="2" t="n">
+        <v>-0.0006430868167201865</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -47167,6 +49807,12 @@
       <c r="AH440" s="3" t="n">
         <v>0.001098297638660104</v>
       </c>
+      <c r="AI440" s="1" t="n">
+        <v>0.001821</v>
+      </c>
+      <c r="AJ440" s="2" t="n">
+        <v>-0.001097092704333543</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -47273,6 +49919,12 @@
       <c r="AH441" s="3" t="n">
         <v>0.00163532297628775</v>
       </c>
+      <c r="AI441" s="1" t="n">
+        <v>0.03659</v>
+      </c>
+      <c r="AJ441" s="2" t="n">
+        <v>-0.004353741496598651</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -47379,6 +50031,12 @@
       <c r="AH442" s="3" t="n">
         <v>0.001636661211129419</v>
       </c>
+      <c r="AI442" s="1" t="n">
+        <v>0.01828</v>
+      </c>
+      <c r="AJ442" s="2" t="n">
+        <v>-0.004357298474945545</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -47485,6 +50143,12 @@
       <c r="AH443" s="2" t="n">
         <v>-0.001571956299614916</v>
       </c>
+      <c r="AI443" s="1" t="n">
+        <v>0.12679</v>
+      </c>
+      <c r="AJ443" s="2" t="n">
+        <v>-0.001889317484058807</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -47591,6 +50255,12 @@
       <c r="AH444" s="3" t="n">
         <v>0.003479773814702053</v>
       </c>
+      <c r="AI444" s="1" t="n">
+        <v>0.011539</v>
+      </c>
+      <c r="AJ444" s="3" t="n">
+        <v>0.0003467706978760755</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -47697,6 +50367,12 @@
       <c r="AH445" s="2" t="n">
         <v>-0.0002475553905187043</v>
       </c>
+      <c r="AI445" s="1" t="n">
+        <v>0.08051</v>
+      </c>
+      <c r="AJ445" s="2" t="n">
+        <v>-0.003219016961743176</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -47803,6 +50479,12 @@
       <c r="AH446" s="3" t="n">
         <v>0.0009315323707499063</v>
       </c>
+      <c r="AI446" s="1" t="n">
+        <v>0.0002143</v>
+      </c>
+      <c r="AJ446" s="2" t="n">
+        <v>-0.002791996277338239</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -47909,6 +50591,12 @@
       <c r="AH447" s="2" t="n">
         <v>-0.007473841554558999</v>
       </c>
+      <c r="AI447" s="1" t="n">
+        <v>0.00665</v>
+      </c>
+      <c r="AJ447" s="3" t="n">
+        <v>0.001506024096385481</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -48015,6 +50703,12 @@
       <c r="AH448" s="2" t="n">
         <v>-0.01412002017145737</v>
       </c>
+      <c r="AI448" s="1" t="n">
+        <v>0.09819</v>
+      </c>
+      <c r="AJ448" s="3" t="n">
+        <v>0.004501278772378475</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -48121,6 +50815,12 @@
       <c r="AH449" s="2" t="n">
         <v>-0.0005963029218843963</v>
       </c>
+      <c r="AI449" s="1" t="n">
+        <v>0.001675</v>
+      </c>
+      <c r="AJ449" s="2" t="n">
+        <v>-0.0005966587112171336</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -48227,6 +50927,12 @@
       <c r="AH450" s="3" t="n">
         <v>0.002405002405002333</v>
       </c>
+      <c r="AI450" s="1" t="n">
+        <v>0.0002079</v>
+      </c>
+      <c r="AJ450" s="2" t="n">
+        <v>-0.00239923224568131</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -48333,6 +51039,12 @@
       <c r="AH451" s="2" t="n">
         <v>-0.000378071833648318</v>
       </c>
+      <c r="AI451" s="1" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="AJ451" s="2" t="n">
+        <v>-0.003403933434190615</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -48439,6 +51151,12 @@
       <c r="AH452" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI452" s="1" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="AJ452" s="2" t="n">
+        <v>-0.001481481481481524</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -48545,6 +51263,12 @@
       <c r="AH453" s="2" t="n">
         <v>-0.001144819690898556</v>
       </c>
+      <c r="AI453" s="1" t="n">
+        <v>0.0001741</v>
+      </c>
+      <c r="AJ453" s="2" t="n">
+        <v>-0.002292263610315242</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -48651,6 +51375,12 @@
       <c r="AH454" s="3" t="n">
         <v>0.001540413193185969</v>
       </c>
+      <c r="AI454" s="1" t="n">
+        <v>0.11026</v>
+      </c>
+      <c r="AJ454" s="2" t="n">
+        <v>-0.002442775716999967</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -48757,6 +51487,12 @@
       <c r="AH455" s="2" t="n">
         <v>-0.001787842669845077</v>
       </c>
+      <c r="AI455" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ455" s="2" t="n">
+        <v>-0.004975124378109347</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -48863,6 +51599,12 @@
       <c r="AH456" s="2" t="n">
         <v>-6.259780907674492e-05</v>
       </c>
+      <c r="AI456" s="1" t="n">
+        <v>0.015983</v>
+      </c>
+      <c r="AJ456" s="3" t="n">
+        <v>0.0005634155502693166</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -48969,6 +51711,12 @@
       <c r="AH457" s="2" t="n">
         <v>-0.0005984440454816971</v>
       </c>
+      <c r="AI457" s="1" t="n">
+        <v>0.006677</v>
+      </c>
+      <c r="AJ457" s="2" t="n">
+        <v>-0.0004491017964072452</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -49075,6 +51823,12 @@
       <c r="AH458" s="3" t="n">
         <v>0.0004145077720207948</v>
       </c>
+      <c r="AI458" s="1" t="n">
+        <v>0.4826</v>
+      </c>
+      <c r="AJ458" s="2" t="n">
+        <v>-0.000207168013258845</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -49181,6 +51935,12 @@
       <c r="AH459" s="2" t="n">
         <v>-0.001099937146448784</v>
       </c>
+      <c r="AI459" s="1" t="n">
+        <v>0.006342</v>
+      </c>
+      <c r="AJ459" s="2" t="n">
+        <v>-0.002359603586597355</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -49287,6 +52047,12 @@
       <c r="AH460" s="2" t="n">
         <v>-0.003617945007235893</v>
       </c>
+      <c r="AI460" s="1" t="n">
+        <v>0.1371</v>
+      </c>
+      <c r="AJ460" s="2" t="n">
+        <v>-0.004357298474945457</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -49393,6 +52159,12 @@
       <c r="AH461" s="2" t="n">
         <v>-0.002325581395348858</v>
       </c>
+      <c r="AI461" s="1" t="n">
+        <v>0.08996</v>
+      </c>
+      <c r="AJ461" s="2" t="n">
+        <v>-0.0014430014430015</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -49499,6 +52271,12 @@
       <c r="AH462" s="2" t="n">
         <v>-0.0006648936170213263</v>
       </c>
+      <c r="AI462" s="1" t="n">
+        <v>0.04504</v>
+      </c>
+      <c r="AJ462" s="2" t="n">
+        <v>-0.001108893324462218</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -49605,6 +52383,12 @@
       <c r="AH463" s="3" t="n">
         <v>0.00142857142857137</v>
       </c>
+      <c r="AI463" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="AJ463" s="2" t="n">
+        <v>-0.001426533523537745</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -49711,6 +52495,12 @@
       <c r="AH464" s="2" t="n">
         <v>-0.00381388253241792</v>
       </c>
+      <c r="AI464" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="AJ464" s="2" t="n">
+        <v>-0.003828483920367623</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -49817,6 +52607,12 @@
       <c r="AH465" s="2" t="n">
         <v>-0.001433691756272442</v>
       </c>
+      <c r="AI465" s="1" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="AJ465" s="2" t="n">
+        <v>-0.003230437903804781</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -49923,6 +52719,12 @@
       <c r="AH466" s="3" t="n">
         <v>0.0007037297677690991</v>
       </c>
+      <c r="AI466" s="1" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="AJ466" s="2" t="n">
+        <v>-0.002109704641350135</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -50029,6 +52831,12 @@
       <c r="AH467" s="2" t="n">
         <v>-0.001039501039500997</v>
       </c>
+      <c r="AI467" s="1" t="n">
+        <v>0.01915</v>
+      </c>
+      <c r="AJ467" s="2" t="n">
+        <v>-0.003642039542143632</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -50135,6 +52943,12 @@
       <c r="AH468" s="2" t="n">
         <v>-0.006882989183874201</v>
       </c>
+      <c r="AI468" s="1" t="n">
+        <v>0.01017</v>
+      </c>
+      <c r="AJ468" s="3" t="n">
+        <v>0.006930693069306992</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -50241,6 +53055,12 @@
       <c r="AH469" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI469" s="1" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="AJ469" s="2" t="n">
+        <v>-0.004016064257028089</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -50347,6 +53167,12 @@
       <c r="AH470" s="2" t="n">
         <v>-0.001135073779795688</v>
       </c>
+      <c r="AI470" s="1" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="AJ470" s="2" t="n">
+        <v>-0.002272727272727275</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -50453,6 +53279,12 @@
       <c r="AH471" s="2" t="n">
         <v>-0.002775208140610514</v>
       </c>
+      <c r="AI471" s="1" t="n">
+        <v>3.219</v>
+      </c>
+      <c r="AJ471" s="2" t="n">
+        <v>-0.004638218923933248</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -50559,6 +53391,12 @@
       <c r="AH472" s="2" t="n">
         <v>-0.002856462746965057</v>
       </c>
+      <c r="AI472" s="1" t="n">
+        <v>0.04191</v>
+      </c>
+      <c r="AJ472" s="3" t="n">
+        <v>0.0004774409166867063</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -50665,6 +53503,12 @@
       <c r="AH473" s="2" t="n">
         <v>-0.002386634844868649</v>
       </c>
+      <c r="AI473" s="1" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="AJ473" s="2" t="n">
+        <v>-0.001594896331738438</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -50771,6 +53615,12 @@
       <c r="AH474" s="2" t="n">
         <v>-0.001050052502625169</v>
       </c>
+      <c r="AI474" s="1" t="n">
+        <v>0.00855</v>
+      </c>
+      <c r="AJ474" s="2" t="n">
+        <v>-0.001401541695865435</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -50877,6 +53727,12 @@
       <c r="AH475" s="2" t="n">
         <v>-0.003814973772055327</v>
       </c>
+      <c r="AI475" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="AJ475" s="2" t="n">
+        <v>-0.004308281474389651</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -50983,6 +53839,12 @@
       <c r="AH476" s="2" t="n">
         <v>-0.0005046681806711882</v>
       </c>
+      <c r="AI476" s="1" t="n">
+        <v>0.07886</v>
+      </c>
+      <c r="AJ476" s="2" t="n">
+        <v>-0.00454430699318353</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -51089,6 +53951,12 @@
       <c r="AH477" s="3" t="n">
         <v>0.0009543385699602938</v>
       </c>
+      <c r="AI477" s="1" t="n">
+        <v>0.13622</v>
+      </c>
+      <c r="AJ477" s="2" t="n">
+        <v>-0.0009534286762008891</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -51195,6 +54063,12 @@
       <c r="AH478" s="3" t="n">
         <v>0.0006319780914262113</v>
       </c>
+      <c r="AI478" s="1" t="n">
+        <v>0.04747</v>
+      </c>
+      <c r="AJ478" s="2" t="n">
+        <v>-0.0006315789473684683</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -51301,6 +54175,12 @@
       <c r="AH479" s="2" t="n">
         <v>-0.0001870907390084439</v>
       </c>
+      <c r="AI479" s="1" t="n">
+        <v>0.00533</v>
+      </c>
+      <c r="AJ479" s="2" t="n">
+        <v>-0.002619760479041939</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -51407,6 +54287,12 @@
       <c r="AH480" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI480" s="1" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="AJ480" s="2" t="n">
+        <v>-0.005687877710629187</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -51513,6 +54399,12 @@
       <c r="AH481" s="3" t="n">
         <v>0.0003949447077409459</v>
       </c>
+      <c r="AI481" s="1" t="n">
+        <v>0.07589</v>
+      </c>
+      <c r="AJ481" s="2" t="n">
+        <v>-0.001315962626661441</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -51619,6 +54511,12 @@
       <c r="AH482" s="3" t="n">
         <v>0.00201477501678971</v>
       </c>
+      <c r="AI482" s="1" t="n">
+        <v>0.01492</v>
+      </c>
+      <c r="AJ482" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -51725,6 +54623,12 @@
       <c r="AH483" s="3" t="n">
         <v>0.003984063745019896</v>
       </c>
+      <c r="AI483" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="AJ483" s="2" t="n">
+        <v>-0.003968253968253945</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -51831,6 +54735,12 @@
       <c r="AH484" s="2" t="n">
         <v>-0.000463177396943171</v>
       </c>
+      <c r="AI484" s="1" t="n">
+        <v>0.02152</v>
+      </c>
+      <c r="AJ484" s="2" t="n">
+        <v>-0.002780352177942426</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -51937,6 +54847,12 @@
       <c r="AH485" s="2" t="n">
         <v>-0.003939828080229231</v>
       </c>
+      <c r="AI485" s="1" t="n">
+        <v>0.008370000000000001</v>
+      </c>
+      <c r="AJ485" s="3" t="n">
+        <v>0.003236245954692674</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -52043,6 +54959,12 @@
       <c r="AH486" s="3" t="n">
         <v>0.0006677350427350155</v>
       </c>
+      <c r="AI486" s="1" t="n">
+        <v>0.007466</v>
+      </c>
+      <c r="AJ486" s="2" t="n">
+        <v>-0.003603363138929567</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -52149,6 +55071,12 @@
       <c r="AH487" s="2" t="n">
         <v>-0.02739726027397256</v>
       </c>
+      <c r="AI487" s="1" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="AJ487" s="2" t="n">
+        <v>-0.00616197183098597</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -52255,6 +55183,12 @@
       <c r="AH488" s="3" t="n">
         <v>0.001955671447196754</v>
       </c>
+      <c r="AI488" s="1" t="n">
+        <v>0.009266</v>
+      </c>
+      <c r="AJ488" s="3" t="n">
+        <v>0.004771199306007443</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -52361,6 +55295,12 @@
       <c r="AH489" s="3" t="n">
         <v>0.003319713993871251</v>
       </c>
+      <c r="AI489" s="1" t="n">
+        <v>0.03895</v>
+      </c>
+      <c r="AJ489" s="2" t="n">
+        <v>-0.008653601425299058</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -52467,6 +55407,12 @@
       <c r="AH490" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI490" s="1" t="n">
+        <v>0.05808</v>
+      </c>
+      <c r="AJ490" s="2" t="n">
+        <v>-0.003773584905660343</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -52573,6 +55519,12 @@
       <c r="AH491" s="2" t="n">
         <v>-0.002044989775051042</v>
       </c>
+      <c r="AI491" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="AJ491" s="2" t="n">
+        <v>-0.001024590163934456</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -52679,6 +55631,12 @@
       <c r="AH492" s="2" t="n">
         <v>-0.005255255255255343</v>
       </c>
+      <c r="AI492" s="1" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="AJ492" s="2" t="n">
+        <v>-0.003018867924528305</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -52785,6 +55743,12 @@
       <c r="AH493" s="2" t="n">
         <v>-0.0008498583569403771</v>
       </c>
+      <c r="AI493" s="1" t="n">
+        <v>0.03515</v>
+      </c>
+      <c r="AJ493" s="2" t="n">
+        <v>-0.003402324922030112</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -52891,6 +55855,12 @@
       <c r="AH494" s="2" t="n">
         <v>-0.001766784452296748</v>
       </c>
+      <c r="AI494" s="1" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="AJ494" s="2" t="n">
+        <v>-0.002949852507374716</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -52997,6 +55967,12 @@
       <c r="AH495" s="2" t="n">
         <v>-0.001269035532995019</v>
       </c>
+      <c r="AI495" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="AJ495" s="2" t="n">
+        <v>-0.00465904277848365</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -53103,6 +56079,12 @@
       <c r="AH496" s="2" t="n">
         <v>-0.0002064409578859646</v>
       </c>
+      <c r="AI496" s="1" t="n">
+        <v>0.04813</v>
+      </c>
+      <c r="AJ496" s="2" t="n">
+        <v>-0.006194507536650871</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -53209,6 +56191,12 @@
       <c r="AH497" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI497" s="1" t="n">
+        <v>0.04964</v>
+      </c>
+      <c r="AJ497" s="2" t="n">
+        <v>-0.003012653143201532</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -53315,6 +56303,12 @@
       <c r="AH498" s="2" t="n">
         <v>-0.001727115716753024</v>
       </c>
+      <c r="AI498" s="1" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="AJ498" s="3" t="n">
+        <v>0.001730103806228375</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -53421,6 +56415,12 @@
       <c r="AH499" s="2" t="n">
         <v>-0.002184200946487038</v>
       </c>
+      <c r="AI499" s="1" t="n">
+        <v>0.2725</v>
+      </c>
+      <c r="AJ499" s="2" t="n">
+        <v>-0.005837285662167057</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -53527,6 +56527,12 @@
       <c r="AH500" s="2" t="n">
         <v>-0.003731343283582099</v>
       </c>
+      <c r="AI500" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="AJ500" s="2" t="n">
+        <v>-0.003745318352059935</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -53633,6 +56639,12 @@
       <c r="AH501" s="2" t="n">
         <v>-0.00139431121026217</v>
       </c>
+      <c r="AI501" s="1" t="n">
+        <v>0.03562</v>
+      </c>
+      <c r="AJ501" s="2" t="n">
+        <v>-0.005305780508237996</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -53739,6 +56751,12 @@
       <c r="AH502" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI502" s="1" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="AJ502" s="3" t="n">
+        <v>0.0009413241292750332</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -53845,6 +56863,12 @@
       <c r="AH503" s="2" t="n">
         <v>-0.003325658736249678</v>
       </c>
+      <c r="AI503" s="1" t="n">
+        <v>0.007794</v>
+      </c>
+      <c r="AJ503" s="3" t="n">
+        <v>0.0002566735112935573</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -53951,6 +56975,12 @@
       <c r="AH504" s="2" t="n">
         <v>-0.000329924117453096</v>
       </c>
+      <c r="AI504" s="1" t="n">
+        <v>3.028</v>
+      </c>
+      <c r="AJ504" s="2" t="n">
+        <v>-0.0006600660066005874</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -54057,6 +57087,12 @@
       <c r="AH505" s="2" t="n">
         <v>-0.000402900886381887</v>
       </c>
+      <c r="AI505" s="1" t="n">
+        <v>0.0007411</v>
+      </c>
+      <c r="AJ505" s="2" t="n">
+        <v>-0.00429934166330791</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -54163,6 +57199,12 @@
       <c r="AH506" s="3" t="n">
         <v>0.000685871056241351</v>
       </c>
+      <c r="AI506" s="1" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="AJ506" s="2" t="n">
+        <v>-0.002741603838245452</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -54269,6 +57311,12 @@
       <c r="AH507" s="3" t="n">
         <v>0.002444987775061146</v>
       </c>
+      <c r="AI507" s="1" t="n">
+        <v>0.002851</v>
+      </c>
+      <c r="AJ507" s="2" t="n">
+        <v>-0.006620209059233572</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -54375,6 +57423,12 @@
       <c r="AH508" s="3" t="n">
         <v>0.001105321332701731</v>
       </c>
+      <c r="AI508" s="1" t="n">
+        <v>0.06322999999999999</v>
+      </c>
+      <c r="AJ508" s="2" t="n">
+        <v>-0.002681388012618352</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -54481,6 +57535,12 @@
       <c r="AH509" s="2" t="n">
         <v>-0.002685765443151201</v>
       </c>
+      <c r="AI509" s="1" t="n">
+        <v>2.231</v>
+      </c>
+      <c r="AJ509" s="3" t="n">
+        <v>0.001346499102333783</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -54587,6 +57647,12 @@
       <c r="AH510" s="3" t="n">
         <v>0.001088287307849299</v>
       </c>
+      <c r="AI510" s="1" t="n">
+        <v>0.0007331</v>
+      </c>
+      <c r="AJ510" s="2" t="n">
+        <v>-0.003804864791411969</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -54693,6 +57759,12 @@
       <c r="AH511" s="3" t="n">
         <v>0.0003629764065335353</v>
       </c>
+      <c r="AI511" s="1" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="AJ511" s="2" t="n">
+        <v>-0.002902757619738835</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -54799,6 +57871,12 @@
       <c r="AH512" s="3" t="n">
         <v>0.0008283288465521013</v>
       </c>
+      <c r="AI512" s="1" t="n">
+        <v>0.000483</v>
+      </c>
+      <c r="AJ512" s="2" t="n">
+        <v>-0.0006207324643078984</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -54905,6 +57983,12 @@
       <c r="AH513" s="2" t="n">
         <v>-0.0009022013713459851</v>
       </c>
+      <c r="AI513" s="1" t="n">
+        <v>0.05522</v>
+      </c>
+      <c r="AJ513" s="2" t="n">
+        <v>-0.002709048221058412</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -55011,6 +58095,12 @@
       <c r="AH514" s="2" t="n">
         <v>-0.002964426877470464</v>
       </c>
+      <c r="AI514" s="1" t="n">
+        <v>0.03026</v>
+      </c>
+      <c r="AJ514" s="2" t="n">
+        <v>-0.0003303600925008124</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -55117,6 +58207,12 @@
       <c r="AH515" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI515" s="1" t="n">
+        <v>0.00114</v>
+      </c>
+      <c r="AJ515" s="3" t="n">
+        <v>0.0008779631255486531</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -55223,6 +58319,12 @@
       <c r="AH516" s="2" t="n">
         <v>-0.003908598917618759</v>
       </c>
+      <c r="AI516" s="1" t="n">
+        <v>0.006594</v>
+      </c>
+      <c r="AJ516" s="2" t="n">
+        <v>-0.00482945970419558</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -55329,6 +58431,12 @@
       <c r="AH517" s="3" t="n">
         <v>0.0002508151492349165</v>
       </c>
+      <c r="AI517" s="1" t="n">
+        <v>0.03984</v>
+      </c>
+      <c r="AJ517" s="2" t="n">
+        <v>-0.001003009027081203</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -55435,6 +58543,12 @@
       <c r="AH518" s="3" t="n">
         <v>0.00193236714975851</v>
       </c>
+      <c r="AI518" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="AJ518" s="2" t="n">
+        <v>-0.001928640308582505</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -55541,6 +58655,12 @@
       <c r="AH519" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI519" s="1" t="n">
+        <v>0.00869</v>
+      </c>
+      <c r="AJ519" s="2" t="n">
+        <v>-0.004581901489117996</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -55647,6 +58767,12 @@
       <c r="AH520" s="3" t="n">
         <v>0.001246105919003151</v>
       </c>
+      <c r="AI520" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="AJ520" s="2" t="n">
+        <v>-0.003733665214685856</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -55753,6 +58879,12 @@
       <c r="AH521" s="3" t="n">
         <v>0.004481792717086847</v>
       </c>
+      <c r="AI521" s="1" t="n">
+        <v>0.01788</v>
+      </c>
+      <c r="AJ521" s="2" t="n">
+        <v>-0.002788622420524341</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -55859,6 +58991,12 @@
       <c r="AH522" s="2" t="n">
         <v>-0.001822600243013292</v>
       </c>
+      <c r="AI522" s="1" t="n">
+        <v>0.01643</v>
+      </c>
+      <c r="AJ522" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -55965,6 +59103,12 @@
       <c r="AH523" s="2" t="n">
         <v>-0.003844305622296858</v>
       </c>
+      <c r="AI523" s="1" t="n">
+        <v>0.004149</v>
+      </c>
+      <c r="AJ523" s="3" t="n">
+        <v>0.0007235890014470648</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -56071,6 +59215,12 @@
       <c r="AH524" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI524" s="1" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="AJ524" s="2" t="n">
+        <v>-0.005602240896358437</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -56177,6 +59327,12 @@
       <c r="AH525" s="3" t="n">
         <v>0.002017756255044449</v>
       </c>
+      <c r="AI525" s="1" t="n">
+        <v>0.02476</v>
+      </c>
+      <c r="AJ525" s="2" t="n">
+        <v>-0.002819170358437399</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -56283,6 +59439,12 @@
       <c r="AH526" s="2" t="n">
         <v>-0.0008305647840530648</v>
       </c>
+      <c r="AI526" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AJ526" s="2" t="n">
+        <v>-0.002493765586034984</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -56389,6 +59551,12 @@
       <c r="AH527" s="2" t="n">
         <v>-0.002219755826859147</v>
       </c>
+      <c r="AI527" s="1" t="n">
+        <v>0.07181999999999999</v>
+      </c>
+      <c r="AJ527" s="2" t="n">
+        <v>-0.001390433815350429</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -56495,6 +59663,12 @@
       <c r="AH528" s="2" t="n">
         <v>-0.0002306273062731333</v>
       </c>
+      <c r="AI528" s="1" t="n">
+        <v>0.04315</v>
+      </c>
+      <c r="AJ528" s="2" t="n">
+        <v>-0.004613610149942302</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -56601,6 +59775,12 @@
       <c r="AH529" s="3" t="n">
         <v>0.001585037248375382</v>
       </c>
+      <c r="AI529" s="1" t="n">
+        <v>0.06297</v>
+      </c>
+      <c r="AJ529" s="2" t="n">
+        <v>-0.003481563538534546</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -56707,6 +59887,12 @@
       <c r="AH530" s="2" t="n">
         <v>-0.001988466892026167</v>
       </c>
+      <c r="AI530" s="1" t="n">
+        <v>0.00501</v>
+      </c>
+      <c r="AJ530" s="2" t="n">
+        <v>-0.001793185893604369</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -56813,6 +59999,12 @@
       <c r="AH531" s="3" t="n">
         <v>0.0007692307692306844</v>
       </c>
+      <c r="AI531" s="1" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AJ531" s="2" t="n">
+        <v>-0.0007686395080706303</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -56919,6 +60111,12 @@
       <c r="AH532" s="2" t="n">
         <v>-0.0001866368047779593</v>
       </c>
+      <c r="AI532" s="1" t="n">
+        <v>0.05352</v>
+      </c>
+      <c r="AJ532" s="2" t="n">
+        <v>-0.0009333582228859703</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -57025,6 +60223,12 @@
       <c r="AH533" s="3" t="n">
         <v>0.006406833956219892</v>
       </c>
+      <c r="AI533" s="1" t="n">
+        <v>0.003739</v>
+      </c>
+      <c r="AJ533" s="2" t="n">
+        <v>-0.008222811671087474</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -57131,6 +60335,12 @@
       <c r="AH534" s="3" t="n">
         <v>0.001746216530849795</v>
       </c>
+      <c r="AI534" s="1" t="n">
+        <v>0.1711</v>
+      </c>
+      <c r="AJ534" s="2" t="n">
+        <v>-0.005810575246949453</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -57237,6 +60447,12 @@
       <c r="AH535" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI535" s="1" t="n">
+        <v>1.13e-05</v>
+      </c>
+      <c r="AJ535" s="3" t="n">
+        <v>0.008928571428571494</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -57343,6 +60559,12 @@
       <c r="AH536" s="2" t="n">
         <v>-0.0009064128710627911</v>
       </c>
+      <c r="AI536" s="1" t="n">
+        <v>0.0004391</v>
+      </c>
+      <c r="AJ536" s="2" t="n">
+        <v>-0.004082558403266023</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -57449,6 +60671,12 @@
       <c r="AH537" s="2" t="n">
         <v>-0.001033057851239627</v>
       </c>
+      <c r="AI537" s="1" t="n">
+        <v>0.00963</v>
+      </c>
+      <c r="AJ537" s="2" t="n">
+        <v>-0.004136504653567746</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -57555,6 +60783,12 @@
       <c r="AH538" s="3" t="n">
         <v>0.0007330034817665085</v>
       </c>
+      <c r="AI538" s="1" t="n">
+        <v>0.05455</v>
+      </c>
+      <c r="AJ538" s="2" t="n">
+        <v>-0.001098699871818304</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -57661,6 +60895,12 @@
       <c r="AH539" s="2" t="n">
         <v>-0.0004400762798884656</v>
       </c>
+      <c r="AI539" s="1" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="AJ539" s="3" t="n">
+        <v>0.000880540064573004</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -57767,6 +61007,12 @@
       <c r="AH540" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AI540" s="1" t="n">
+        <v>0.1508</v>
+      </c>
+      <c r="AJ540" s="2" t="n">
+        <v>-0.001324503311258316</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -57873,6 +61119,12 @@
       <c r="AH541" s="2" t="n">
         <v>-0.003837298541826531</v>
       </c>
+      <c r="AI541" s="1" t="n">
+        <v>0.01301</v>
+      </c>
+      <c r="AJ541" s="3" t="n">
+        <v>0.002311248073959978</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -57979,6 +61231,12 @@
       <c r="AH542" s="2" t="n">
         <v>-0.007183908045976968</v>
       </c>
+      <c r="AI542" s="1" t="n">
+        <v>0.01388</v>
+      </c>
+      <c r="AJ542" s="3" t="n">
+        <v>0.004341534008683016</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -58085,6 +61343,12 @@
       <c r="AH543" s="3" t="n">
         <v>0.0008748906386701913</v>
       </c>
+      <c r="AI543" s="1" t="n">
+        <v>0.05702</v>
+      </c>
+      <c r="AJ543" s="2" t="n">
+        <v>-0.00314685314685314</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-13.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ543"/>
+  <dimension ref="A1:AL543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -462,6 +462,8 @@
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="18" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -645,6 +647,16 @@
           <t>change_04:15</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>price_04:30</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>change_04:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -757,6 +769,12 @@
       <c r="AJ2" s="2" t="n">
         <v>-0.0007258698008333415</v>
       </c>
+      <c r="AK2" s="1" t="n">
+        <v>70270.89999999999</v>
+      </c>
+      <c r="AL2" s="2" t="n">
+        <v>-0.001084620283394405</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -869,6 +887,12 @@
       <c r="AJ3" s="2" t="n">
         <v>-0.001527189777494179</v>
       </c>
+      <c r="AK3" s="1" t="n">
+        <v>2065.88</v>
+      </c>
+      <c r="AL3" s="2" t="n">
+        <v>-5.808325266209625e-05</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -981,6 +1005,12 @@
       <c r="AJ4" s="2" t="n">
         <v>-0.0014980410232772</v>
       </c>
+      <c r="AK4" s="1" t="n">
+        <v>86.64</v>
+      </c>
+      <c r="AL4" s="2" t="n">
+        <v>-0.0001154068090017901</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1093,6 +1123,12 @@
       <c r="AJ5" s="3" t="n">
         <v>0.01381215469613253</v>
       </c>
+      <c r="AK5" s="1" t="n">
+        <v>0.010768</v>
+      </c>
+      <c r="AL5" s="3" t="n">
+        <v>0.01174480879451284</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1205,6 +1241,12 @@
       <c r="AJ6" s="2" t="n">
         <v>-0.00282977797126688</v>
       </c>
+      <c r="AK6" s="1" t="n">
+        <v>1.3732</v>
+      </c>
+      <c r="AL6" s="2" t="n">
+        <v>-0.0008004074801717971</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1317,6 +1359,12 @@
       <c r="AJ7" s="2" t="n">
         <v>-0.0005296610169490942</v>
       </c>
+      <c r="AK7" s="1" t="n">
+        <v>0.0941</v>
+      </c>
+      <c r="AL7" s="2" t="n">
+        <v>-0.002649708532061475</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1429,6 +1477,12 @@
       <c r="AJ8" s="2" t="n">
         <v>-0.004072056523380706</v>
       </c>
+      <c r="AK8" s="1" t="n">
+        <v>36.926</v>
+      </c>
+      <c r="AL8" s="2" t="n">
+        <v>-0.0001353876147408804</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1541,6 +1595,12 @@
       <c r="AJ9" s="2" t="n">
         <v>-0.01280512204881942</v>
       </c>
+      <c r="AK9" s="1" t="n">
+        <v>0.04961</v>
+      </c>
+      <c r="AL9" s="3" t="n">
+        <v>0.005472233481961884</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1653,6 +1713,12 @@
       <c r="AJ10" s="2" t="n">
         <v>-0.006878994691799312</v>
       </c>
+      <c r="AK10" s="1" t="n">
+        <v>18.457</v>
+      </c>
+      <c r="AL10" s="3" t="n">
+        <v>0.006653940550859007</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1765,6 +1831,12 @@
       <c r="AJ11" s="2" t="n">
         <v>-0.001136084500122834</v>
       </c>
+      <c r="AK11" s="1" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="AL11" s="2" t="n">
+        <v>-0.000845347514678237</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1877,6 +1949,12 @@
       <c r="AJ12" s="2" t="n">
         <v>-0.0006730229949522534</v>
       </c>
+      <c r="AK12" s="1" t="n">
+        <v>0.8848</v>
+      </c>
+      <c r="AL12" s="2" t="n">
+        <v>-0.00684700864294533</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1989,6 +2067,12 @@
       <c r="AJ13" s="2" t="n">
         <v>-0.003974144122575935</v>
       </c>
+      <c r="AK13" s="1" t="n">
+        <v>207.5</v>
+      </c>
+      <c r="AL13" s="2" t="n">
+        <v>-0.002499759638496348</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2101,6 +2185,12 @@
       <c r="AJ14" s="2" t="n">
         <v>-0.002117885693831385</v>
       </c>
+      <c r="AK14" s="1" t="n">
+        <v>0.0033338</v>
+      </c>
+      <c r="AL14" s="2" t="n">
+        <v>-0.003437658804890381</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2213,6 +2303,12 @@
       <c r="AJ15" s="2" t="n">
         <v>-0.003351019268360872</v>
       </c>
+      <c r="AK15" s="1" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="AL15" s="3" t="n">
+        <v>0.01438311385075189</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2325,6 +2421,12 @@
       <c r="AJ16" s="2" t="n">
         <v>-0.00337044224287608</v>
       </c>
+      <c r="AK16" s="1" t="n">
+        <v>0.9743000000000001</v>
+      </c>
+      <c r="AL16" s="2" t="n">
+        <v>-0.001537200245951984</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2437,6 +2539,12 @@
       <c r="AJ17" s="2" t="n">
         <v>-0.01498127340823974</v>
       </c>
+      <c r="AK17" s="1" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="AL17" s="3" t="n">
+        <v>0.01140684410646381</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2549,6 +2657,12 @@
       <c r="AJ18" s="3" t="n">
         <v>0.00121785563726634</v>
       </c>
+      <c r="AK18" s="1" t="n">
+        <v>213.65</v>
+      </c>
+      <c r="AL18" s="2" t="n">
+        <v>-0.0004678362573099149</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2661,6 +2775,12 @@
       <c r="AJ19" s="2" t="n">
         <v>-0.001901140684410648</v>
       </c>
+      <c r="AK19" s="1" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="AL19" s="2" t="n">
+        <v>-0.001904761904761906</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2773,6 +2893,12 @@
       <c r="AJ20" s="3" t="n">
         <v>0.003482469602172118</v>
       </c>
+      <c r="AK20" s="1" t="n">
+        <v>0.016945</v>
+      </c>
+      <c r="AL20" s="2" t="n">
+        <v>-0.003293923886830012</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2885,6 +3011,12 @@
       <c r="AJ21" s="2" t="n">
         <v>-0.0003124674513071673</v>
       </c>
+      <c r="AK21" s="1" t="n">
+        <v>9.603999999999999</v>
+      </c>
+      <c r="AL21" s="3" t="n">
+        <v>0.0006251302354655606</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2997,6 +3129,12 @@
       <c r="AJ22" s="2" t="n">
         <v>-0.007728894173602828</v>
       </c>
+      <c r="AK22" s="1" t="n">
+        <v>0.1666</v>
+      </c>
+      <c r="AL22" s="2" t="n">
+        <v>-0.001797483523067674</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3109,6 +3247,12 @@
       <c r="AJ23" s="3" t="n">
         <v>0.005008395576399772</v>
       </c>
+      <c r="AK23" s="1" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="AL23" s="3" t="n">
+        <v>0.003831196888952896</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3221,6 +3365,12 @@
       <c r="AJ24" s="2" t="n">
         <v>-0.005747126436781614</v>
       </c>
+      <c r="AK24" s="1" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="AL24" s="2" t="n">
+        <v>-0.002312138728323701</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3333,6 +3483,12 @@
       <c r="AJ25" s="2" t="n">
         <v>-0.003432620972206907</v>
       </c>
+      <c r="AK25" s="1" t="n">
+        <v>8.988</v>
+      </c>
+      <c r="AL25" s="2" t="n">
+        <v>-0.001333333333333384</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3445,6 +3601,12 @@
       <c r="AJ26" s="2" t="n">
         <v>-0.007468259895444368</v>
       </c>
+      <c r="AK26" s="1" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="AL26" s="2" t="n">
+        <v>-0.003009781790820168</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3557,6 +3719,12 @@
       <c r="AJ27" s="3" t="n">
         <v>0.0003535324768682094</v>
       </c>
+      <c r="AK27" s="1" t="n">
+        <v>5082.79</v>
+      </c>
+      <c r="AL27" s="2" t="n">
+        <v>-0.002057617208591037</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3669,6 +3837,12 @@
       <c r="AJ28" s="2" t="n">
         <v>-0.003610108303249008</v>
       </c>
+      <c r="AK28" s="1" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="AL28" s="2" t="n">
+        <v>-0.006688963210702377</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3781,6 +3955,12 @@
       <c r="AJ29" s="3" t="n">
         <v>0.001519756838905776</v>
       </c>
+      <c r="AK29" s="1" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AL29" s="2" t="n">
+        <v>-0.0003793626707133285</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3893,6 +4073,12 @@
       <c r="AJ30" s="2" t="n">
         <v>-0.002240945018674565</v>
       </c>
+      <c r="AK30" s="1" t="n">
+        <v>0.57872</v>
+      </c>
+      <c r="AL30" s="3" t="n">
+        <v>0.007591057873110994</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4005,6 +4191,12 @@
       <c r="AJ31" s="2" t="n">
         <v>-0.005255613951265994</v>
       </c>
+      <c r="AK31" s="1" t="n">
+        <v>0.002075</v>
+      </c>
+      <c r="AL31" s="2" t="n">
+        <v>-0.003362151777137397</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4117,6 +4309,12 @@
       <c r="AJ32" s="2" t="n">
         <v>-0.01407373412880524</v>
       </c>
+      <c r="AK32" s="1" t="n">
+        <v>1.2903</v>
+      </c>
+      <c r="AL32" s="3" t="n">
+        <v>0.001008533747090829</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4229,6 +4427,12 @@
       <c r="AJ33" s="3" t="n">
         <v>0.008711324722138822</v>
       </c>
+      <c r="AK33" s="1" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AL33" s="2" t="n">
+        <v>-0.00208457415128046</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4341,6 +4545,12 @@
       <c r="AJ34" s="3" t="n">
         <v>0.0006640106241699136</v>
       </c>
+      <c r="AK34" s="1" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="AL34" s="2" t="n">
+        <v>-0.001327140013271401</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4453,6 +4663,12 @@
       <c r="AJ35" s="2" t="n">
         <v>-0.003201613964299767</v>
       </c>
+      <c r="AK35" s="1" t="n">
+        <v>454.06</v>
+      </c>
+      <c r="AL35" s="2" t="n">
+        <v>-0.001099964801126364</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4565,6 +4781,12 @@
       <c r="AJ36" s="2" t="n">
         <v>-0.004395144411887857</v>
       </c>
+      <c r="AK36" s="1" t="n">
+        <v>0.04741</v>
+      </c>
+      <c r="AL36" s="2" t="n">
+        <v>-0.003363464368299357</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4677,6 +4899,12 @@
       <c r="AJ37" s="2" t="n">
         <v>-0.00242130750605316</v>
       </c>
+      <c r="AK37" s="1" t="n">
+        <v>0.7008</v>
+      </c>
+      <c r="AL37" s="3" t="n">
+        <v>0.0005711022272986236</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4789,6 +5017,12 @@
       <c r="AJ38" s="2" t="n">
         <v>-0.002827521206408998</v>
       </c>
+      <c r="AK38" s="1" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="AL38" s="2" t="n">
+        <v>-0.00378071833648404</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4901,6 +5135,12 @@
       <c r="AJ39" s="2" t="n">
         <v>-0.002598566308243656</v>
       </c>
+      <c r="AK39" s="1" t="n">
+        <v>111.21</v>
+      </c>
+      <c r="AL39" s="2" t="n">
+        <v>-0.0008983918785374946</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5013,6 +5253,12 @@
       <c r="AJ40" s="2" t="n">
         <v>-0.000548095368594113</v>
       </c>
+      <c r="AK40" s="1" t="n">
+        <v>0.03656</v>
+      </c>
+      <c r="AL40" s="3" t="n">
+        <v>0.00246778173841513</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5125,6 +5371,12 @@
       <c r="AJ41" s="2" t="n">
         <v>-0.001095090344953414</v>
       </c>
+      <c r="AK41" s="1" t="n">
+        <v>0.05499</v>
+      </c>
+      <c r="AL41" s="3" t="n">
+        <v>0.004750593824227962</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5237,6 +5489,12 @@
       <c r="AJ42" s="2" t="n">
         <v>-0.001842638658559083</v>
       </c>
+      <c r="AK42" s="1" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="AL42" s="2" t="n">
+        <v>-0.002399852316780553</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5349,6 +5607,12 @@
       <c r="AJ43" s="2" t="n">
         <v>-0.009036144578313303</v>
       </c>
+      <c r="AK43" s="1" t="n">
+        <v>0.1322</v>
+      </c>
+      <c r="AL43" s="3" t="n">
+        <v>0.004559270516717456</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5461,6 +5725,12 @@
       <c r="AJ44" s="2" t="n">
         <v>-0.003033878307770064</v>
       </c>
+      <c r="AK44" s="1" t="n">
+        <v>0.005886</v>
+      </c>
+      <c r="AL44" s="2" t="n">
+        <v>-0.004902789518174197</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5573,6 +5843,12 @@
       <c r="AJ45" s="2" t="n">
         <v>-0.004889731563716101</v>
       </c>
+      <c r="AK45" s="1" t="n">
+        <v>0.09979</v>
+      </c>
+      <c r="AL45" s="3" t="n">
+        <v>0.0007019655034095529</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5685,6 +5961,12 @@
       <c r="AJ46" s="3" t="n">
         <v>0.008202323991797683</v>
       </c>
+      <c r="AK46" s="1" t="n">
+        <v>2.901</v>
+      </c>
+      <c r="AL46" s="2" t="n">
+        <v>-0.01661016949152555</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5797,6 +6079,12 @@
       <c r="AJ47" s="3" t="n">
         <v>0.0001039356984478052</v>
       </c>
+      <c r="AK47" s="1" t="n">
+        <v>0.28876</v>
+      </c>
+      <c r="AL47" s="3" t="n">
+        <v>0.0003117746908235511</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5909,6 +6197,12 @@
       <c r="AJ48" s="2" t="n">
         <v>-0.01220657276995301</v>
       </c>
+      <c r="AK48" s="1" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="AL48" s="3" t="n">
+        <v>0.00380228136882127</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6021,6 +6315,12 @@
       <c r="AJ49" s="2" t="n">
         <v>-0.004038673356994211</v>
       </c>
+      <c r="AK49" s="1" t="n">
+        <v>0.24365</v>
+      </c>
+      <c r="AL49" s="2" t="n">
+        <v>-0.002007045138035514</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6133,6 +6433,12 @@
       <c r="AJ50" s="2" t="n">
         <v>-0.002487046632124395</v>
       </c>
+      <c r="AK50" s="1" t="n">
+        <v>0.04825</v>
+      </c>
+      <c r="AL50" s="3" t="n">
+        <v>0.002493247454809932</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6245,6 +6551,12 @@
       <c r="AJ51" s="2" t="n">
         <v>-0.002046559222307497</v>
       </c>
+      <c r="AK51" s="1" t="n">
+        <v>3.895</v>
+      </c>
+      <c r="AL51" s="2" t="n">
+        <v>-0.00153806716226603</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6357,6 +6669,12 @@
       <c r="AJ52" s="2" t="n">
         <v>-0.008733624454148565</v>
       </c>
+      <c r="AK52" s="1" t="n">
+        <v>0.000227</v>
+      </c>
+      <c r="AL52" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6469,6 +6787,12 @@
       <c r="AJ53" s="2" t="n">
         <v>-0.00412979351032452</v>
       </c>
+      <c r="AK53" s="1" t="n">
+        <v>0.1681</v>
+      </c>
+      <c r="AL53" s="2" t="n">
+        <v>-0.004146919431279658</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6581,6 +6905,12 @@
       <c r="AJ54" s="2" t="n">
         <v>-0.006908051453073023</v>
       </c>
+      <c r="AK54" s="1" t="n">
+        <v>0.04154</v>
+      </c>
+      <c r="AL54" s="2" t="n">
+        <v>-0.003597985128328073</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6693,6 +7023,12 @@
       <c r="AJ55" s="3" t="n">
         <v>0.01079666284966466</v>
       </c>
+      <c r="AK55" s="1" t="n">
+        <v>0.1234</v>
+      </c>
+      <c r="AL55" s="2" t="n">
+        <v>-0.001456546366726004</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6805,6 +7141,12 @@
       <c r="AJ56" s="2" t="n">
         <v>-0.001904157410345888</v>
       </c>
+      <c r="AK56" s="1" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AL56" s="2" t="n">
+        <v>-0.006995230524642225</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6917,6 +7259,12 @@
       <c r="AJ57" s="3" t="n">
         <v>0.001742160278745573</v>
       </c>
+      <c r="AK57" s="1" t="n">
+        <v>0.01148</v>
+      </c>
+      <c r="AL57" s="2" t="n">
+        <v>-0.001739130434782538</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7029,6 +7377,12 @@
       <c r="AJ58" s="2" t="n">
         <v>-0.004985044865403793</v>
       </c>
+      <c r="AK58" s="1" t="n">
+        <v>0.09950000000000001</v>
+      </c>
+      <c r="AL58" s="2" t="n">
+        <v>-0.003006012024048043</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7141,6 +7495,12 @@
       <c r="AJ59" s="2" t="n">
         <v>-0.005988023952095824</v>
       </c>
+      <c r="AK59" s="1" t="n">
+        <v>0.00331</v>
+      </c>
+      <c r="AL59" s="2" t="n">
+        <v>-0.003012048192771092</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7253,6 +7613,12 @@
       <c r="AJ60" s="2" t="n">
         <v>-0.004492939666238808</v>
       </c>
+      <c r="AK60" s="1" t="n">
+        <v>0.1543</v>
+      </c>
+      <c r="AL60" s="2" t="n">
+        <v>-0.005157962604771084</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7365,6 +7731,12 @@
       <c r="AJ61" s="2" t="n">
         <v>-0.001688027508596563</v>
       </c>
+      <c r="AK61" s="1" t="n">
+        <v>0.15926</v>
+      </c>
+      <c r="AL61" s="2" t="n">
+        <v>-0.002630260521041934</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7477,6 +7849,12 @@
       <c r="AJ62" s="2" t="n">
         <v>-0.005752771151957335</v>
       </c>
+      <c r="AK62" s="1" t="n">
+        <v>0.7052</v>
+      </c>
+      <c r="AL62" s="2" t="n">
+        <v>-0.004798193621224892</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7589,6 +7967,12 @@
       <c r="AJ63" s="3" t="n">
         <v>0.001154924929879504</v>
       </c>
+      <c r="AK63" s="1" t="n">
+        <v>6.067</v>
+      </c>
+      <c r="AL63" s="2" t="n">
+        <v>-0.0001647989452866588</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7701,6 +8085,12 @@
       <c r="AJ64" s="2" t="n">
         <v>-0.004429065743944625</v>
       </c>
+      <c r="AK64" s="1" t="n">
+        <v>0.00716</v>
+      </c>
+      <c r="AL64" s="2" t="n">
+        <v>-0.004587793688308084</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7813,6 +8203,12 @@
       <c r="AJ65" s="2" t="n">
         <v>-0.01503528689782155</v>
       </c>
+      <c r="AK65" s="1" t="n">
+        <v>0.03232</v>
+      </c>
+      <c r="AL65" s="3" t="n">
+        <v>0.006853582554517288</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7925,6 +8321,12 @@
       <c r="AJ66" s="2" t="n">
         <v>-0.004255319148936056</v>
       </c>
+      <c r="AK66" s="1" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="AL66" s="2" t="n">
+        <v>-0.004273504273504277</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8037,6 +8439,12 @@
       <c r="AJ67" s="3" t="n">
         <v>0.00679851668726817</v>
       </c>
+      <c r="AK67" s="1" t="n">
+        <v>1.623</v>
+      </c>
+      <c r="AL67" s="2" t="n">
+        <v>-0.003683241252302029</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8149,6 +8557,12 @@
       <c r="AJ68" s="2" t="n">
         <v>-0.00560306694190508</v>
       </c>
+      <c r="AK68" s="1" t="n">
+        <v>2.0276</v>
+      </c>
+      <c r="AL68" s="3" t="n">
+        <v>0.002174772637406069</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8261,6 +8675,12 @@
       <c r="AJ69" s="3" t="n">
         <v>0.004609081597815015</v>
       </c>
+      <c r="AK69" s="1" t="n">
+        <v>0.5894</v>
+      </c>
+      <c r="AL69" s="3" t="n">
+        <v>0.001529311809685662</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8373,6 +8793,12 @@
       <c r="AJ70" s="3" t="n">
         <v>0.00980392156862746</v>
       </c>
+      <c r="AK70" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AL70" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8485,6 +8911,12 @@
       <c r="AJ71" s="2" t="n">
         <v>-0.003293446042375675</v>
       </c>
+      <c r="AK71" s="1" t="n">
+        <v>0.9053</v>
+      </c>
+      <c r="AL71" s="2" t="n">
+        <v>-0.002863751514484025</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8597,6 +9029,12 @@
       <c r="AJ72" s="3" t="n">
         <v>0.008280104092737172</v>
       </c>
+      <c r="AK72" s="1" t="n">
+        <v>0.4311</v>
+      </c>
+      <c r="AL72" s="3" t="n">
+        <v>0.01149694978883144</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8709,6 +9147,12 @@
       <c r="AJ73" s="2" t="n">
         <v>-0.001801419942778315</v>
       </c>
+      <c r="AK73" s="1" t="n">
+        <v>0.09397999999999999</v>
+      </c>
+      <c r="AL73" s="2" t="n">
+        <v>-0.00233545647558399</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8821,6 +9265,12 @@
       <c r="AJ74" s="2" t="n">
         <v>-0.00624999999999989</v>
       </c>
+      <c r="AK74" s="1" t="n">
+        <v>1.1493</v>
+      </c>
+      <c r="AL74" s="3" t="n">
+        <v>0.003930817610062848</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8933,6 +9383,12 @@
       <c r="AJ75" s="2" t="n">
         <v>-0.002496878901373182</v>
       </c>
+      <c r="AK75" s="1" t="n">
+        <v>0.01602</v>
+      </c>
+      <c r="AL75" s="3" t="n">
+        <v>0.002503128911138821</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9045,6 +9501,12 @@
       <c r="AJ76" s="2" t="n">
         <v>-0.009822378652697115</v>
       </c>
+      <c r="AK76" s="1" t="n">
+        <v>0.12058</v>
+      </c>
+      <c r="AL76" s="2" t="n">
+        <v>-0.003223939819789928</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9157,6 +9619,12 @@
       <c r="AJ77" s="2" t="n">
         <v>-0.0025210084033613</v>
       </c>
+      <c r="AK77" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AL77" s="2" t="n">
+        <v>-0.005897219882055655</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9269,6 +9737,12 @@
       <c r="AJ78" s="2" t="n">
         <v>-0.001966568338249674</v>
       </c>
+      <c r="AK78" s="1" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="AL78" s="2" t="n">
+        <v>-0.003940886699507502</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9381,6 +9855,12 @@
       <c r="AJ79" s="2" t="n">
         <v>-0.00526575612966923</v>
       </c>
+      <c r="AK79" s="1" t="n">
+        <v>0.006014</v>
+      </c>
+      <c r="AL79" s="2" t="n">
+        <v>-0.005128205128205092</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9493,6 +9973,12 @@
       <c r="AJ80" s="2" t="n">
         <v>-0.0005100739607243728</v>
       </c>
+      <c r="AK80" s="1" t="n">
+        <v>0.007816</v>
+      </c>
+      <c r="AL80" s="2" t="n">
+        <v>-0.002806838479203808</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9605,6 +10091,12 @@
       <c r="AJ81" s="2" t="n">
         <v>-0.00167317345231462</v>
       </c>
+      <c r="AK81" s="1" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="AL81" s="2" t="n">
+        <v>-0.003910614525139681</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9717,6 +10209,12 @@
       <c r="AJ82" s="3" t="n">
         <v>0.004286589099816327</v>
       </c>
+      <c r="AK82" s="1" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="AL82" s="3" t="n">
+        <v>0.006097560975609762</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9829,6 +10327,12 @@
       <c r="AJ83" s="2" t="n">
         <v>-0.002424536307431367</v>
       </c>
+      <c r="AK83" s="1" t="n">
+        <v>8.224</v>
+      </c>
+      <c r="AL83" s="2" t="n">
+        <v>-0.0006076072426782119</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9941,6 +10445,12 @@
       <c r="AJ84" s="3" t="n">
         <v>0.001364295256231755</v>
       </c>
+      <c r="AK84" s="1" t="n">
+        <v>352.55</v>
+      </c>
+      <c r="AL84" s="3" t="n">
+        <v>0.0006812182452953623</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10053,6 +10563,12 @@
       <c r="AJ85" s="2" t="n">
         <v>-0.005620723362658956</v>
       </c>
+      <c r="AK85" s="1" t="n">
+        <v>0.004061</v>
+      </c>
+      <c r="AL85" s="2" t="n">
+        <v>-0.00196608503317752</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10165,6 +10681,12 @@
       <c r="AJ86" s="3" t="n">
         <v>0.0006114338122897947</v>
       </c>
+      <c r="AK86" s="1" t="n">
+        <v>0.13117</v>
+      </c>
+      <c r="AL86" s="3" t="n">
+        <v>0.00190956309196456</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10277,6 +10799,12 @@
       <c r="AJ87" s="3" t="n">
         <v>0.003867403314916969</v>
       </c>
+      <c r="AK87" s="1" t="n">
+        <v>0.01815</v>
+      </c>
+      <c r="AL87" s="2" t="n">
+        <v>-0.001100715465052239</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10389,6 +10917,12 @@
       <c r="AJ88" s="2" t="n">
         <v>-0.003527336860670197</v>
       </c>
+      <c r="AK88" s="1" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="AL88" s="2" t="n">
+        <v>-0.002654867256637073</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10501,6 +11035,12 @@
       <c r="AJ89" s="2" t="n">
         <v>-0.004760285617136882</v>
       </c>
+      <c r="AK89" s="1" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="AL89" s="2" t="n">
+        <v>-0.001024940211821054</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10613,6 +11153,12 @@
       <c r="AJ90" s="2" t="n">
         <v>-0.0023183925811437</v>
       </c>
+      <c r="AK90" s="1" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="AL90" s="2" t="n">
+        <v>-0.002323780015491826</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10725,6 +11271,12 @@
       <c r="AJ91" s="3" t="n">
         <v>0.003601008282319028</v>
       </c>
+      <c r="AK91" s="1" t="n">
+        <v>0.05673</v>
+      </c>
+      <c r="AL91" s="3" t="n">
+        <v>0.01776103336921429</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10837,6 +11389,12 @@
       <c r="AJ92" s="2" t="n">
         <v>-0.001143554166349056</v>
       </c>
+      <c r="AK92" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL92" s="2" t="n">
+        <v>-0.007785070981529528</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10949,6 +11507,12 @@
       <c r="AJ93" s="3" t="n">
         <v>0.001562988433885634</v>
       </c>
+      <c r="AK93" s="1" t="n">
+        <v>0.06412</v>
+      </c>
+      <c r="AL93" s="3" t="n">
+        <v>0.0006242197253432955</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11061,6 +11625,12 @@
       <c r="AJ94" s="2" t="n">
         <v>-0.001137656427758771</v>
       </c>
+      <c r="AK94" s="1" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="AL94" s="3" t="n">
+        <v>0.002277904328018328</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11173,6 +11743,12 @@
       <c r="AJ95" s="2" t="n">
         <v>-0.001184132622853794</v>
       </c>
+      <c r="AK95" s="1" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AL95" s="2" t="n">
+        <v>-0.0044457617071725</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11285,6 +11861,12 @@
       <c r="AJ96" s="2" t="n">
         <v>-0.003971756398940856</v>
       </c>
+      <c r="AK96" s="1" t="n">
+        <v>0.02254</v>
+      </c>
+      <c r="AL96" s="2" t="n">
+        <v>-0.001329198050509472</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11397,6 +11979,12 @@
       <c r="AJ97" s="2" t="n">
         <v>-0.001833740831295913</v>
       </c>
+      <c r="AK97" s="1" t="n">
+        <v>32.59</v>
+      </c>
+      <c r="AL97" s="2" t="n">
+        <v>-0.002143294549907936</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -11509,6 +12097,12 @@
       <c r="AJ98" s="3" t="n">
         <v>0.001776198934280641</v>
       </c>
+      <c r="AK98" s="1" t="n">
+        <v>1.126</v>
+      </c>
+      <c r="AL98" s="2" t="n">
+        <v>-0.001773049645390073</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11621,6 +12215,12 @@
       <c r="AJ99" s="2" t="n">
         <v>-0.0006594131223210616</v>
       </c>
+      <c r="AK99" s="1" t="n">
+        <v>3.025</v>
+      </c>
+      <c r="AL99" s="2" t="n">
+        <v>-0.00197954470471799</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11733,6 +12333,12 @@
       <c r="AJ100" s="2" t="n">
         <v>-0.009866511897852584</v>
       </c>
+      <c r="AK100" s="1" t="n">
+        <v>0.03408</v>
+      </c>
+      <c r="AL100" s="2" t="n">
+        <v>-0.001172332942555638</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11845,6 +12451,12 @@
       <c r="AJ101" s="2" t="n">
         <v>-0.002186987424822309</v>
       </c>
+      <c r="AK101" s="1" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="AL101" s="2" t="n">
+        <v>-0.0005479452054793917</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11957,6 +12569,12 @@
       <c r="AJ102" s="3" t="n">
         <v>0.007005003573981353</v>
       </c>
+      <c r="AK102" s="1" t="n">
+        <v>0.007072</v>
+      </c>
+      <c r="AL102" s="3" t="n">
+        <v>0.003975014196479308</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -12069,6 +12687,12 @@
       <c r="AJ103" s="2" t="n">
         <v>-0.004714111922141191</v>
       </c>
+      <c r="AK103" s="1" t="n">
+        <v>0.06536</v>
+      </c>
+      <c r="AL103" s="2" t="n">
+        <v>-0.001375095492742443</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -12181,6 +12805,12 @@
       <c r="AJ104" s="2" t="n">
         <v>-0.005573055488248181</v>
       </c>
+      <c r="AK104" s="1" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="AL104" s="3" t="n">
+        <v>0.003654970760233921</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -12293,6 +12923,12 @@
       <c r="AJ105" s="2" t="n">
         <v>-0.004390779363336996</v>
       </c>
+      <c r="AK105" s="1" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="AL105" s="3" t="n">
+        <v>0.000551267916207216</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -12405,6 +13041,12 @@
       <c r="AJ106" s="3" t="n">
         <v>0.002430724355858158</v>
       </c>
+      <c r="AK106" s="1" t="n">
+        <v>0.008192</v>
+      </c>
+      <c r="AL106" s="2" t="n">
+        <v>-0.006789524733268731</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -12517,6 +13159,12 @@
       <c r="AJ107" s="2" t="n">
         <v>-0.001633986928104698</v>
       </c>
+      <c r="AK107" s="1" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="AL107" s="2" t="n">
+        <v>-0.00927441352973268</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -12629,6 +13277,12 @@
       <c r="AJ108" s="3" t="n">
         <v>0.002304147465437694</v>
       </c>
+      <c r="AK108" s="1" t="n">
+        <v>0.02155</v>
+      </c>
+      <c r="AL108" s="2" t="n">
+        <v>-0.009195402298850519</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -12741,6 +13395,12 @@
       <c r="AJ109" s="2" t="n">
         <v>-0.00197557471264366</v>
       </c>
+      <c r="AK109" s="1" t="n">
+        <v>0.05578</v>
+      </c>
+      <c r="AL109" s="3" t="n">
+        <v>0.003779017455461613</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -12853,6 +13513,12 @@
       <c r="AJ110" s="2" t="n">
         <v>-0.001299263750541337</v>
       </c>
+      <c r="AK110" s="1" t="n">
+        <v>0.11483</v>
+      </c>
+      <c r="AL110" s="2" t="n">
+        <v>-0.004076322636600157</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -12965,6 +13631,12 @@
       <c r="AJ111" s="2" t="n">
         <v>-0.01096760967609663</v>
       </c>
+      <c r="AK111" s="1" t="n">
+        <v>0.09644999999999999</v>
+      </c>
+      <c r="AL111" s="2" t="n">
+        <v>-0.0004145507306457897</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13077,6 +13749,12 @@
       <c r="AJ112" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK112" s="1" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="AL112" s="2" t="n">
+        <v>-0.005361930294906134</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -13189,6 +13867,12 @@
       <c r="AJ113" s="2" t="n">
         <v>-0.004359728277400384</v>
       </c>
+      <c r="AK113" s="1" t="n">
+        <v>0.09812</v>
+      </c>
+      <c r="AL113" s="2" t="n">
+        <v>-0.0008146639511201298</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -13301,6 +13985,12 @@
       <c r="AJ114" s="2" t="n">
         <v>-0.004504504504504491</v>
       </c>
+      <c r="AK114" s="1" t="n">
+        <v>0.001773</v>
+      </c>
+      <c r="AL114" s="3" t="n">
+        <v>0.002828054298642541</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -13413,6 +14103,12 @@
       <c r="AJ115" s="2" t="n">
         <v>-0.001030927835051433</v>
       </c>
+      <c r="AK115" s="1" t="n">
+        <v>1.258</v>
+      </c>
+      <c r="AL115" s="2" t="n">
+        <v>-0.001349527665317167</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -13525,6 +14221,12 @@
       <c r="AJ116" s="2" t="n">
         <v>-0.002949852507374657</v>
       </c>
+      <c r="AK116" s="1" t="n">
+        <v>0.2357</v>
+      </c>
+      <c r="AL116" s="2" t="n">
+        <v>-0.003803888419273085</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -13637,6 +14339,12 @@
       <c r="AJ117" s="3" t="n">
         <v>0.0003286770747740211</v>
       </c>
+      <c r="AK117" s="1" t="n">
+        <v>0.06069</v>
+      </c>
+      <c r="AL117" s="2" t="n">
+        <v>-0.002957121734844745</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -13749,6 +14457,12 @@
       <c r="AJ118" s="3" t="n">
         <v>0.003448275862069064</v>
       </c>
+      <c r="AK118" s="1" t="n">
+        <v>0.04405</v>
+      </c>
+      <c r="AL118" s="3" t="n">
+        <v>0.009163802978235913</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -13861,6 +14575,12 @@
       <c r="AJ119" s="2" t="n">
         <v>-0.005385029617662912</v>
       </c>
+      <c r="AK119" s="1" t="n">
+        <v>0.003683</v>
+      </c>
+      <c r="AL119" s="2" t="n">
+        <v>-0.002977801840822882</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -13973,6 +14693,12 @@
       <c r="AJ120" s="2" t="n">
         <v>-0.002528445006321114</v>
       </c>
+      <c r="AK120" s="1" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="AL120" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -14085,6 +14811,12 @@
       <c r="AJ121" s="2" t="n">
         <v>-0.004340567612687706</v>
       </c>
+      <c r="AK121" s="1" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="AL121" s="2" t="n">
+        <v>-0.002012072434607797</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -14197,6 +14929,12 @@
       <c r="AJ122" s="2" t="n">
         <v>-0.003852889667250403</v>
       </c>
+      <c r="AK122" s="1" t="n">
+        <v>0.5672</v>
+      </c>
+      <c r="AL122" s="2" t="n">
+        <v>-0.002812939521800167</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -14309,6 +15047,12 @@
       <c r="AJ123" s="2" t="n">
         <v>-0.001898934486760276</v>
       </c>
+      <c r="AK123" s="1" t="n">
+        <v>0.028429</v>
+      </c>
+      <c r="AL123" s="3" t="n">
+        <v>0.00162068844026357</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -14421,6 +15165,12 @@
       <c r="AJ124" s="3" t="n">
         <v>0.004324599338590778</v>
       </c>
+      <c r="AK124" s="1" t="n">
+        <v>0.07908</v>
+      </c>
+      <c r="AL124" s="3" t="n">
+        <v>0.001519756838905713</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -14533,6 +15283,12 @@
       <c r="AJ125" s="3" t="n">
         <v>0.00113475177304973</v>
       </c>
+      <c r="AK125" s="1" t="n">
+        <v>0.10585</v>
+      </c>
+      <c r="AL125" s="2" t="n">
+        <v>-0.0001889109284972714</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -14645,6 +15401,12 @@
       <c r="AJ126" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK126" s="1" t="n">
+        <v>0.02643</v>
+      </c>
+      <c r="AL126" s="2" t="n">
+        <v>-0.003393665158371033</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -14757,6 +15519,12 @@
       <c r="AJ127" s="2" t="n">
         <v>-0.0009149130832572119</v>
       </c>
+      <c r="AK127" s="1" t="n">
+        <v>0.02178</v>
+      </c>
+      <c r="AL127" s="2" t="n">
+        <v>-0.002747252747252636</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -14869,6 +15637,12 @@
       <c r="AJ128" s="2" t="n">
         <v>-0.009213759213759222</v>
       </c>
+      <c r="AK128" s="1" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="AL128" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -14981,6 +15755,12 @@
       <c r="AJ129" s="2" t="n">
         <v>-0.001042970379641296</v>
       </c>
+      <c r="AK129" s="1" t="n">
+        <v>0.14302</v>
+      </c>
+      <c r="AL129" s="2" t="n">
+        <v>-0.004524256977796228</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -15093,6 +15873,12 @@
       <c r="AJ130" s="2" t="n">
         <v>-0.01158640172555301</v>
       </c>
+      <c r="AK130" s="1" t="n">
+        <v>0.051393</v>
+      </c>
+      <c r="AL130" s="2" t="n">
+        <v>-0.007512262948514936</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -15205,6 +15991,12 @@
       <c r="AJ131" s="2" t="n">
         <v>-0.003282275711159814</v>
       </c>
+      <c r="AK131" s="1" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="AL131" s="2" t="n">
+        <v>-0.001097694840834161</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -15317,6 +16109,12 @@
       <c r="AJ132" s="2" t="n">
         <v>-0.003397508493771332</v>
       </c>
+      <c r="AK132" s="1" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="AL132" s="2" t="n">
+        <v>-0.001136363636363511</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -15429,6 +16227,12 @@
       <c r="AJ133" s="2" t="n">
         <v>-0.002232526189249663</v>
       </c>
+      <c r="AK133" s="1" t="n">
+        <v>0.5793</v>
+      </c>
+      <c r="AL133" s="2" t="n">
+        <v>-0.002925989672977494</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -15541,6 +16345,12 @@
       <c r="AJ134" s="2" t="n">
         <v>-0.003020134228187913</v>
       </c>
+      <c r="AK134" s="1" t="n">
+        <v>0.02969</v>
+      </c>
+      <c r="AL134" s="2" t="n">
+        <v>-0.0006731740154829749</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -15653,6 +16463,12 @@
       <c r="AJ135" s="2" t="n">
         <v>-0.003426613363792177</v>
       </c>
+      <c r="AK135" s="1" t="n">
+        <v>0.01739</v>
+      </c>
+      <c r="AL135" s="2" t="n">
+        <v>-0.003438395415472838</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -15765,6 +16581,12 @@
       <c r="AJ136" s="2" t="n">
         <v>-0.001609442060085771</v>
       </c>
+      <c r="AK136" s="1" t="n">
+        <v>0.03706</v>
+      </c>
+      <c r="AL136" s="2" t="n">
+        <v>-0.004298764105319731</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -15877,6 +16699,12 @@
       <c r="AJ137" s="2" t="n">
         <v>-0.005528934758569879</v>
       </c>
+      <c r="AK137" s="1" t="n">
+        <v>0.02697</v>
+      </c>
+      <c r="AL137" s="2" t="n">
+        <v>-0.0003706449221645513</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -15989,6 +16817,12 @@
       <c r="AJ138" s="2" t="n">
         <v>-0.00351699882766719</v>
       </c>
+      <c r="AK138" s="1" t="n">
+        <v>2.536</v>
+      </c>
+      <c r="AL138" s="2" t="n">
+        <v>-0.005490196078431291</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -16101,6 +16935,12 @@
       <c r="AJ139" s="2" t="n">
         <v>-0.004205214465937738</v>
       </c>
+      <c r="AK139" s="1" t="n">
+        <v>0.01186</v>
+      </c>
+      <c r="AL139" s="3" t="n">
+        <v>0.001689189189189267</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -16213,6 +17053,12 @@
       <c r="AJ140" s="3" t="n">
         <v>0.001356852103120822</v>
       </c>
+      <c r="AK140" s="1" t="n">
+        <v>0.01472</v>
+      </c>
+      <c r="AL140" s="2" t="n">
+        <v>-0.00271002710027101</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -16325,6 +17171,12 @@
       <c r="AJ141" s="2" t="n">
         <v>-0.00282885431400279</v>
       </c>
+      <c r="AK141" s="1" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="AL141" s="2" t="n">
+        <v>-0.005242059821153305</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -16437,6 +17289,12 @@
       <c r="AJ142" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK142" s="1" t="n">
+        <v>0.01245</v>
+      </c>
+      <c r="AL142" s="2" t="n">
+        <v>-0.01190476190476197</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -16549,6 +17407,12 @@
       <c r="AJ143" s="3" t="n">
         <v>0.0308529945553539</v>
       </c>
+      <c r="AK143" s="1" t="n">
+        <v>0.02802</v>
+      </c>
+      <c r="AL143" s="2" t="n">
+        <v>-0.01338028169014091</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -16661,6 +17525,12 @@
       <c r="AJ144" s="2" t="n">
         <v>-0.0006295907660021822</v>
       </c>
+      <c r="AK144" s="1" t="n">
+        <v>0.004751</v>
+      </c>
+      <c r="AL144" s="2" t="n">
+        <v>-0.002309953800923924</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -16773,6 +17643,12 @@
       <c r="AJ145" s="3" t="n">
         <v>0.001623953311342346</v>
       </c>
+      <c r="AK145" s="1" t="n">
+        <v>1.9777</v>
+      </c>
+      <c r="AL145" s="3" t="n">
+        <v>0.002026650453463041</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -16885,6 +17761,12 @@
       <c r="AJ146" s="3" t="n">
         <v>0.002139495079161379</v>
       </c>
+      <c r="AK146" s="1" t="n">
+        <v>0.02344</v>
+      </c>
+      <c r="AL146" s="3" t="n">
+        <v>0.0008539709649871556</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -16997,6 +17879,12 @@
       <c r="AJ147" s="3" t="n">
         <v>0.0006658528465209688</v>
       </c>
+      <c r="AK147" s="1" t="n">
+        <v>0.08998</v>
+      </c>
+      <c r="AL147" s="2" t="n">
+        <v>-0.002107130974825283</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -17109,6 +17997,12 @@
       <c r="AJ148" s="3" t="n">
         <v>0.0237905157272871</v>
       </c>
+      <c r="AK148" s="1" t="n">
+        <v>0.06272</v>
+      </c>
+      <c r="AL148" s="2" t="n">
+        <v>-0.02183406113537116</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -17221,6 +18115,12 @@
       <c r="AJ149" s="2" t="n">
         <v>-0.004039044092897967</v>
       </c>
+      <c r="AK149" s="1" t="n">
+        <v>0.05903</v>
+      </c>
+      <c r="AL149" s="2" t="n">
+        <v>-0.002534640081108555</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -17333,6 +18233,12 @@
       <c r="AJ150" s="2" t="n">
         <v>-4.088474590134511e-05</v>
       </c>
+      <c r="AK150" s="1" t="n">
+        <v>0.24304</v>
+      </c>
+      <c r="AL150" s="2" t="n">
+        <v>-0.006296508299942701</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -17445,6 +18351,12 @@
       <c r="AJ151" s="2" t="n">
         <v>-0.0008519096975720011</v>
       </c>
+      <c r="AK151" s="1" t="n">
+        <v>7.004e-05</v>
+      </c>
+      <c r="AL151" s="2" t="n">
+        <v>-0.004689498365780947</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -17557,6 +18469,12 @@
       <c r="AJ152" s="2" t="n">
         <v>-0.004257226081111265</v>
       </c>
+      <c r="AK152" s="1" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="AL152" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -17669,6 +18587,12 @@
       <c r="AJ153" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK153" s="1" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AL153" s="3" t="n">
+        <v>0.003243593902043467</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -17781,6 +18705,12 @@
       <c r="AJ154" s="2" t="n">
         <v>-0.007683863885839804</v>
       </c>
+      <c r="AK154" s="1" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AL154" s="3" t="n">
+        <v>0.001106194690265519</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -17893,6 +18823,12 @@
       <c r="AJ155" s="2" t="n">
         <v>-0.002171081198436823</v>
       </c>
+      <c r="AK155" s="1" t="n">
+        <v>0.2307</v>
+      </c>
+      <c r="AL155" s="3" t="n">
+        <v>0.003916449086161811</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -18005,6 +18941,12 @@
       <c r="AJ156" s="3" t="n">
         <v>0.001734820322180932</v>
       </c>
+      <c r="AK156" s="1" t="n">
+        <v>0.08134</v>
+      </c>
+      <c r="AL156" s="3" t="n">
+        <v>0.006185056902523509</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -18117,6 +19059,12 @@
       <c r="AJ157" s="2" t="n">
         <v>-0.009009009009009012</v>
       </c>
+      <c r="AK157" s="1" t="n">
+        <v>0.23195</v>
+      </c>
+      <c r="AL157" s="2" t="n">
+        <v>-0.0006462731581215478</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -18229,6 +19177,12 @@
       <c r="AJ158" s="3" t="n">
         <v>0.001575423395037461</v>
       </c>
+      <c r="AK158" s="1" t="n">
+        <v>0.2548</v>
+      </c>
+      <c r="AL158" s="3" t="n">
+        <v>0.001966181675186789</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -18341,6 +19295,12 @@
       <c r="AJ159" s="3" t="n">
         <v>0.001029866117404776</v>
       </c>
+      <c r="AK159" s="1" t="n">
+        <v>2.915</v>
+      </c>
+      <c r="AL159" s="2" t="n">
+        <v>-0.0003429355281206756</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -18453,6 +19413,12 @@
       <c r="AJ160" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK160" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="AL160" s="2" t="n">
+        <v>-0.002018163471241089</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -18565,6 +19531,12 @@
       <c r="AJ161" s="2" t="n">
         <v>-0.003709198813056346</v>
       </c>
+      <c r="AK161" s="1" t="n">
+        <v>0.14719</v>
+      </c>
+      <c r="AL161" s="2" t="n">
+        <v>-0.003655317132606869</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -18677,6 +19649,12 @@
       <c r="AJ162" s="2" t="n">
         <v>-0.008729680915111364</v>
       </c>
+      <c r="AK162" s="1" t="n">
+        <v>0.003294</v>
+      </c>
+      <c r="AL162" s="3" t="n">
+        <v>0.0003036744609778721</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -18789,6 +19767,12 @@
       <c r="AJ163" s="2" t="n">
         <v>-0.008523290386521236</v>
       </c>
+      <c r="AK163" s="1" t="n">
+        <v>0.005024</v>
+      </c>
+      <c r="AL163" s="3" t="n">
+        <v>0.004398240703718402</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -18901,6 +19885,12 @@
       <c r="AJ164" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK164" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="AL164" s="2" t="n">
+        <v>-0.003112033195020692</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -19013,6 +20003,12 @@
       <c r="AJ165" s="2" t="n">
         <v>-0.01028938906752405</v>
       </c>
+      <c r="AK165" s="1" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="AL165" s="2" t="n">
+        <v>-0.004873294346978562</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -19125,6 +20121,12 @@
       <c r="AJ166" s="2" t="n">
         <v>-0.0001431844215349212</v>
       </c>
+      <c r="AK166" s="1" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="AL166" s="2" t="n">
+        <v>-0.001861664041243132</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -19237,6 +20239,12 @@
       <c r="AJ167" s="2" t="n">
         <v>-0.0007137758743753675</v>
       </c>
+      <c r="AK167" s="1" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="AL167" s="2" t="n">
+        <v>-0.006428571428571513</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -19349,6 +20357,12 @@
       <c r="AJ168" s="2" t="n">
         <v>-0.003205128205128208</v>
       </c>
+      <c r="AK168" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AL168" s="2" t="n">
+        <v>-0.003215434083601289</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -19461,6 +20475,12 @@
       <c r="AJ169" s="2" t="n">
         <v>-0.003313452617627548</v>
       </c>
+      <c r="AK169" s="1" t="n">
+        <v>0.02998</v>
+      </c>
+      <c r="AL169" s="2" t="n">
+        <v>-0.003324468085106363</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -19573,6 +20593,12 @@
       <c r="AJ170" s="2" t="n">
         <v>-0.002538656819755342</v>
       </c>
+      <c r="AK170" s="1" t="n">
+        <v>0.04339</v>
+      </c>
+      <c r="AL170" s="3" t="n">
+        <v>0.003933364183248416</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -19685,6 +20711,12 @@
       <c r="AJ171" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK171" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="AL171" s="2" t="n">
+        <v>-0.005988023952095772</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -19797,6 +20829,12 @@
       <c r="AJ172" s="3" t="n">
         <v>0.01562499999999998</v>
       </c>
+      <c r="AK172" s="1" t="n">
+        <v>1.29e-05</v>
+      </c>
+      <c r="AL172" s="2" t="n">
+        <v>-0.007692307692307619</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -19909,6 +20947,12 @@
       <c r="AJ173" s="2" t="n">
         <v>-0.001885014137605955</v>
       </c>
+      <c r="AK173" s="1" t="n">
+        <v>0.02111</v>
+      </c>
+      <c r="AL173" s="2" t="n">
+        <v>-0.003305004721435345</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -20021,6 +21065,12 @@
       <c r="AJ174" s="2" t="n">
         <v>-0.005418555789007967</v>
       </c>
+      <c r="AK174" s="1" t="n">
+        <v>0.08961</v>
+      </c>
+      <c r="AL174" s="2" t="n">
+        <v>-0.003669112741828006</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -20133,6 +21183,12 @@
       <c r="AJ175" s="2" t="n">
         <v>-0.003580280914348576</v>
       </c>
+      <c r="AK175" s="1" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="AL175" s="2" t="n">
+        <v>-0.002763957987838587</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -20245,6 +21301,12 @@
       <c r="AJ176" s="2" t="n">
         <v>-0.001405810684161305</v>
       </c>
+      <c r="AK176" s="1" t="n">
+        <v>0.02126</v>
+      </c>
+      <c r="AL176" s="2" t="n">
+        <v>-0.002346316283434912</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -20357,6 +21419,12 @@
       <c r="AJ177" s="2" t="n">
         <v>-0.003826530612244853</v>
       </c>
+      <c r="AK177" s="1" t="n">
+        <v>0.00788</v>
+      </c>
+      <c r="AL177" s="3" t="n">
+        <v>0.008962868117797663</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -20469,6 +21537,12 @@
       <c r="AJ178" s="2" t="n">
         <v>-0.00104821802935013</v>
       </c>
+      <c r="AK178" s="1" t="n">
+        <v>0.000949</v>
+      </c>
+      <c r="AL178" s="2" t="n">
+        <v>-0.004197271773347313</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -20581,6 +21655,12 @@
       <c r="AJ179" s="2" t="n">
         <v>-0.00140000875005457</v>
       </c>
+      <c r="AK179" s="1" t="n">
+        <v>0.022763</v>
+      </c>
+      <c r="AL179" s="2" t="n">
+        <v>-0.002716319824753692</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -20693,6 +21773,12 @@
       <c r="AJ180" s="2" t="n">
         <v>-0.005337214944201902</v>
       </c>
+      <c r="AK180" s="1" t="n">
+        <v>4.094</v>
+      </c>
+      <c r="AL180" s="2" t="n">
+        <v>-0.00146341463414618</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -20805,6 +21891,12 @@
       <c r="AJ181" s="2" t="n">
         <v>-0.002624212736179052</v>
       </c>
+      <c r="AK181" s="1" t="n">
+        <v>0.5677</v>
+      </c>
+      <c r="AL181" s="2" t="n">
+        <v>-0.004209787756534062</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -20917,6 +22009,12 @@
       <c r="AJ182" s="2" t="n">
         <v>-0.005486968449931326</v>
       </c>
+      <c r="AK182" s="1" t="n">
+        <v>0.05045</v>
+      </c>
+      <c r="AL182" s="2" t="n">
+        <v>-0.005911330049261116</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -21029,6 +22127,12 @@
       <c r="AJ183" s="2" t="n">
         <v>-0.003649635036496434</v>
       </c>
+      <c r="AK183" s="1" t="n">
+        <v>5.434</v>
+      </c>
+      <c r="AL183" s="2" t="n">
+        <v>-0.004761904761904726</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -21141,6 +22245,12 @@
       <c r="AJ184" s="2" t="n">
         <v>-0.003456619426201224</v>
       </c>
+      <c r="AK184" s="1" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="AL184" s="2" t="n">
+        <v>-0.001734304543877806</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -21253,6 +22363,12 @@
       <c r="AJ185" s="2" t="n">
         <v>-0.00479999999999999</v>
       </c>
+      <c r="AK185" s="1" t="n">
+        <v>0.01848</v>
+      </c>
+      <c r="AL185" s="2" t="n">
+        <v>-0.009646302250803838</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -21365,6 +22481,12 @@
       <c r="AJ186" s="2" t="n">
         <v>-0.003236245954692416</v>
       </c>
+      <c r="AK186" s="1" t="n">
+        <v>3.07e-05</v>
+      </c>
+      <c r="AL186" s="2" t="n">
+        <v>-0.003246753246753325</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -21477,6 +22599,12 @@
       <c r="AJ187" s="2" t="n">
         <v>-0.00127469725940084</v>
       </c>
+      <c r="AK187" s="1" t="n">
+        <v>0.01566</v>
+      </c>
+      <c r="AL187" s="2" t="n">
+        <v>-0.0006381620931716396</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -21589,6 +22717,12 @@
       <c r="AJ188" s="2" t="n">
         <v>-0.002693437806072453</v>
       </c>
+      <c r="AK188" s="1" t="n">
+        <v>0.04068</v>
+      </c>
+      <c r="AL188" s="2" t="n">
+        <v>-0.001227596366314791</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -21701,6 +22835,12 @@
       <c r="AJ189" s="2" t="n">
         <v>-0.000446528242911375</v>
       </c>
+      <c r="AK189" s="1" t="n">
+        <v>0.0004443</v>
+      </c>
+      <c r="AL189" s="2" t="n">
+        <v>-0.00759437123073481</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -21813,6 +22953,12 @@
       <c r="AJ190" s="2" t="n">
         <v>-0.00345572354211664</v>
       </c>
+      <c r="AK190" s="1" t="n">
+        <v>0.02303</v>
+      </c>
+      <c r="AL190" s="2" t="n">
+        <v>-0.001733853489380227</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -21925,6 +23071,12 @@
       <c r="AJ191" s="2" t="n">
         <v>-0.001902346227013239</v>
       </c>
+      <c r="AK191" s="1" t="n">
+        <v>0.01567</v>
+      </c>
+      <c r="AL191" s="2" t="n">
+        <v>-0.004447268106734474</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -22037,6 +23189,12 @@
       <c r="AJ192" s="2" t="n">
         <v>-0.002682403433476348</v>
       </c>
+      <c r="AK192" s="1" t="n">
+        <v>0.05563</v>
+      </c>
+      <c r="AL192" s="2" t="n">
+        <v>-0.002510310202617917</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -22149,6 +23307,12 @@
       <c r="AJ193" s="2" t="n">
         <v>-0.004769475357710715</v>
       </c>
+      <c r="AK193" s="1" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="AL193" s="2" t="n">
+        <v>-0.004259850905218292</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -22261,6 +23425,12 @@
       <c r="AJ194" s="2" t="n">
         <v>-0.001551189245087838</v>
       </c>
+      <c r="AK194" s="1" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="AL194" s="2" t="n">
+        <v>-0.003107198342827603</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -22373,6 +23543,12 @@
       <c r="AJ195" s="2" t="n">
         <v>-0.005857544517338337</v>
       </c>
+      <c r="AK195" s="1" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="AL195" s="2" t="n">
+        <v>-0.0007070469007778046</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -22485,6 +23661,12 @@
       <c r="AJ196" s="2" t="n">
         <v>-0.00162469536961813</v>
       </c>
+      <c r="AK196" s="1" t="n">
+        <v>0.01225</v>
+      </c>
+      <c r="AL196" s="2" t="n">
+        <v>-0.00325467860048821</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -22597,6 +23779,12 @@
       <c r="AJ197" s="2" t="n">
         <v>-0.005767998290963457</v>
       </c>
+      <c r="AK197" s="1" t="n">
+        <v>0.04628</v>
+      </c>
+      <c r="AL197" s="2" t="n">
+        <v>-0.005586592178770872</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -22709,6 +23897,12 @@
       <c r="AJ198" s="3" t="n">
         <v>0.001358695652173979</v>
       </c>
+      <c r="AK198" s="1" t="n">
+        <v>0.5139</v>
+      </c>
+      <c r="AL198" s="2" t="n">
+        <v>-0.003876720294630746</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -22821,6 +24015,12 @@
       <c r="AJ199" s="3" t="n">
         <v>0.01136363636363637</v>
       </c>
+      <c r="AK199" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AL199" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -22933,6 +24133,12 @@
       <c r="AJ200" s="2" t="n">
         <v>-0.004024144869215325</v>
       </c>
+      <c r="AK200" s="1" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="AL200" s="2" t="n">
+        <v>-0.002020202020201977</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -23045,6 +24251,12 @@
       <c r="AJ201" s="2" t="n">
         <v>-0.00264177527298349</v>
       </c>
+      <c r="AK201" s="1" t="n">
+        <v>0.005647</v>
+      </c>
+      <c r="AL201" s="2" t="n">
+        <v>-0.002825357584319181</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -23157,6 +24369,12 @@
       <c r="AJ202" s="3" t="n">
         <v>0.001085870651088073</v>
       </c>
+      <c r="AK202" s="1" t="n">
+        <v>0.023015</v>
+      </c>
+      <c r="AL202" s="2" t="n">
+        <v>-0.001431794515793054</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -23269,6 +24487,12 @@
       <c r="AJ203" s="2" t="n">
         <v>-0.007299270072992783</v>
       </c>
+      <c r="AK203" s="1" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="AL203" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -23381,6 +24605,12 @@
       <c r="AJ204" s="2" t="n">
         <v>-0.007140731925022436</v>
       </c>
+      <c r="AK204" s="1" t="n">
+        <v>0.03325</v>
+      </c>
+      <c r="AL204" s="2" t="n">
+        <v>-0.003596044351213519</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -23493,6 +24723,12 @@
       <c r="AJ205" s="2" t="n">
         <v>-0.0004769854519436632</v>
       </c>
+      <c r="AK205" s="1" t="n">
+        <v>4.184</v>
+      </c>
+      <c r="AL205" s="2" t="n">
+        <v>-0.001670245764733876</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -23605,6 +24841,12 @@
       <c r="AJ206" s="2" t="n">
         <v>-0.002754820936639121</v>
       </c>
+      <c r="AK206" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AL206" s="2" t="n">
+        <v>-0.002762430939226522</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -23717,6 +24959,12 @@
       <c r="AJ207" s="3" t="n">
         <v>0.02182886172408316</v>
       </c>
+      <c r="AK207" s="1" t="n">
+        <v>0.0012665</v>
+      </c>
+      <c r="AL207" s="2" t="n">
+        <v>-0.01615784976306988</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -23829,6 +25077,12 @@
       <c r="AJ208" s="2" t="n">
         <v>-0.005720664155155487</v>
       </c>
+      <c r="AK208" s="1" t="n">
+        <v>0.007105</v>
+      </c>
+      <c r="AL208" s="2" t="n">
+        <v>-0.002946954813359555</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -23941,6 +25195,12 @@
       <c r="AJ209" s="2" t="n">
         <v>-0.003327787021630595</v>
       </c>
+      <c r="AK209" s="1" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="AL209" s="2" t="n">
+        <v>-0.001669449081803053</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -24053,6 +25313,12 @@
       <c r="AJ210" s="2" t="n">
         <v>-0.003849114703618172</v>
       </c>
+      <c r="AK210" s="1" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AL210" s="2" t="n">
+        <v>-0.003091190108191528</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -24165,6 +25431,12 @@
       <c r="AJ211" s="2" t="n">
         <v>-0.002518186905428062</v>
       </c>
+      <c r="AK211" s="1" t="n">
+        <v>0.007111</v>
+      </c>
+      <c r="AL211" s="2" t="n">
+        <v>-0.002664796633941083</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -24277,6 +25549,12 @@
       <c r="AJ212" s="3" t="n">
         <v>0.0006891798759475464</v>
       </c>
+      <c r="AK212" s="1" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="AL212" s="3" t="n">
+        <v>0.009986225895316852</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -24389,6 +25667,12 @@
       <c r="AJ213" s="2" t="n">
         <v>-0.01112529637060003</v>
       </c>
+      <c r="AK213" s="1" t="n">
+        <v>0.05454</v>
+      </c>
+      <c r="AL213" s="3" t="n">
+        <v>0.00590188122464037</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -24501,6 +25785,12 @@
       <c r="AJ214" s="2" t="n">
         <v>-0.006845708267509338</v>
       </c>
+      <c r="AK214" s="1" t="n">
+        <v>0.1882</v>
+      </c>
+      <c r="AL214" s="2" t="n">
+        <v>-0.002120890774125046</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -24613,6 +25903,12 @@
       <c r="AJ215" s="2" t="n">
         <v>-0.004480119469852477</v>
       </c>
+      <c r="AK215" s="1" t="n">
+        <v>0.05339</v>
+      </c>
+      <c r="AL215" s="3" t="n">
+        <v>0.00112507031689476</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -24725,6 +26021,12 @@
       <c r="AJ216" s="2" t="n">
         <v>-0.01486097794822637</v>
       </c>
+      <c r="AK216" s="1" t="n">
+        <v>0.002054</v>
+      </c>
+      <c r="AL216" s="2" t="n">
+        <v>-0.0004866180048662446</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -24837,6 +26139,12 @@
       <c r="AJ217" s="2" t="n">
         <v>-0.003307972213033487</v>
       </c>
+      <c r="AK217" s="1" t="n">
+        <v>6.013</v>
+      </c>
+      <c r="AL217" s="2" t="n">
+        <v>-0.002157318287421159</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -24949,6 +26257,12 @@
       <c r="AJ218" s="2" t="n">
         <v>-0.01092769123459674</v>
       </c>
+      <c r="AK218" s="1" t="n">
+        <v>4.231</v>
+      </c>
+      <c r="AL218" s="2" t="n">
+        <v>-0.005406676069581498</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -25061,6 +26375,12 @@
       <c r="AJ219" s="3" t="n">
         <v>0.0001878639864738179</v>
       </c>
+      <c r="AK219" s="1" t="n">
+        <v>0.005326</v>
+      </c>
+      <c r="AL219" s="3" t="n">
+        <v>0.0003756574004508388</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -25173,6 +26493,12 @@
       <c r="AJ220" s="2" t="n">
         <v>-0.003638127577007137</v>
       </c>
+      <c r="AK220" s="1" t="n">
+        <v>0.04096</v>
+      </c>
+      <c r="AL220" s="2" t="n">
+        <v>-0.002921129503407865</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -25285,6 +26611,12 @@
       <c r="AJ221" s="2" t="n">
         <v>-0.002079362328885784</v>
       </c>
+      <c r="AK221" s="1" t="n">
+        <v>0.005746</v>
+      </c>
+      <c r="AL221" s="2" t="n">
+        <v>-0.002257336343115123</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -25397,6 +26729,12 @@
       <c r="AJ222" s="2" t="n">
         <v>-0.004362050163576854</v>
       </c>
+      <c r="AK222" s="1" t="n">
+        <v>0.0915</v>
+      </c>
+      <c r="AL222" s="3" t="n">
+        <v>0.002190580503833426</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -25509,6 +26847,12 @@
       <c r="AJ223" s="2" t="n">
         <v>-0.004143237644273326</v>
       </c>
+      <c r="AK223" s="1" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="AL223" s="2" t="n">
+        <v>-0.000594353640416147</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -25621,6 +26965,12 @@
       <c r="AJ224" s="2" t="n">
         <v>-0.001153934918070622</v>
       </c>
+      <c r="AK224" s="1" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="AL224" s="2" t="n">
+        <v>-0.001848428835489887</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -25733,6 +27083,12 @@
       <c r="AJ225" s="2" t="n">
         <v>-0.001802018260451674</v>
       </c>
+      <c r="AK225" s="1" t="n">
+        <v>0.08296000000000001</v>
+      </c>
+      <c r="AL225" s="2" t="n">
+        <v>-0.001564568540137095</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -25845,6 +27201,12 @@
       <c r="AJ226" s="2" t="n">
         <v>-0.001068947087119329</v>
       </c>
+      <c r="AK226" s="1" t="n">
+        <v>0.01848</v>
+      </c>
+      <c r="AL226" s="2" t="n">
+        <v>-0.01123595505617969</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -25957,6 +27319,12 @@
       <c r="AJ227" s="2" t="n">
         <v>-0.0008479966080135335</v>
       </c>
+      <c r="AK227" s="1" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AL227" s="2" t="n">
+        <v>-0.003394865266284753</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -26069,6 +27437,12 @@
       <c r="AJ228" s="2" t="n">
         <v>-0.001300390117035057</v>
       </c>
+      <c r="AK228" s="1" t="n">
+        <v>0.02306</v>
+      </c>
+      <c r="AL228" s="3" t="n">
+        <v>0.0008680555555555202</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -26181,6 +27555,12 @@
       <c r="AJ229" s="2" t="n">
         <v>-0.006404391582799564</v>
       </c>
+      <c r="AK229" s="1" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="AL229" s="2" t="n">
+        <v>-0.002762430939226599</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -26293,6 +27673,12 @@
       <c r="AJ230" s="2" t="n">
         <v>-0.001798561151079105</v>
       </c>
+      <c r="AK230" s="1" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="AL230" s="2" t="n">
+        <v>-0.003003003003003006</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -26405,6 +27791,12 @@
       <c r="AJ231" s="2" t="n">
         <v>-0.0009874917709019832</v>
       </c>
+      <c r="AK231" s="1" t="n">
+        <v>0.03031</v>
+      </c>
+      <c r="AL231" s="2" t="n">
+        <v>-0.001317957166392039</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -26517,6 +27909,12 @@
       <c r="AJ232" s="2" t="n">
         <v>-0.001789709172259435</v>
       </c>
+      <c r="AK232" s="1" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="AL232" s="2" t="n">
+        <v>-0.004930524428507351</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -26629,6 +28027,12 @@
       <c r="AJ233" s="2" t="n">
         <v>-0.009558962710581081</v>
       </c>
+      <c r="AK233" s="1" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="AL233" s="3" t="n">
+        <v>0.0310559006211179</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -26741,6 +28145,12 @@
       <c r="AJ234" s="2" t="n">
         <v>-0.001967729240456515</v>
       </c>
+      <c r="AK234" s="1" t="n">
+        <v>0.2535</v>
+      </c>
+      <c r="AL234" s="2" t="n">
+        <v>-0.0003943217665614708</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -26853,6 +28263,12 @@
       <c r="AJ235" s="2" t="n">
         <v>-0.002757219561747144</v>
       </c>
+      <c r="AK235" s="1" t="n">
+        <v>0.06869</v>
+      </c>
+      <c r="AL235" s="2" t="n">
+        <v>-0.000436554132712489</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -26965,6 +28381,12 @@
       <c r="AJ236" s="2" t="n">
         <v>-0.002228944435599446</v>
       </c>
+      <c r="AK236" s="1" t="n">
+        <v>0.12513</v>
+      </c>
+      <c r="AL236" s="2" t="n">
+        <v>-0.001675442795596104</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -27077,6 +28499,12 @@
       <c r="AJ237" s="2" t="n">
         <v>-0.004632012352032928</v>
       </c>
+      <c r="AK237" s="1" t="n">
+        <v>0.03858</v>
+      </c>
+      <c r="AL237" s="2" t="n">
+        <v>-0.002585315408479729</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -27189,6 +28617,12 @@
       <c r="AJ238" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK238" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AL238" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -27301,6 +28735,12 @@
       <c r="AJ239" s="2" t="n">
         <v>-0.004268139593271534</v>
       </c>
+      <c r="AK239" s="1" t="n">
+        <v>0.003965</v>
+      </c>
+      <c r="AL239" s="2" t="n">
+        <v>-0.0002521432173474868</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -27413,6 +28853,12 @@
       <c r="AJ240" s="2" t="n">
         <v>-0.003625815808556903</v>
       </c>
+      <c r="AK240" s="1" t="n">
+        <v>0.01371</v>
+      </c>
+      <c r="AL240" s="2" t="n">
+        <v>-0.002183406113537155</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -27525,6 +28971,12 @@
       <c r="AJ241" s="2" t="n">
         <v>-0.008066323101053086</v>
       </c>
+      <c r="AK241" s="1" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="AL241" s="3" t="n">
+        <v>0.002258866049243282</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -27637,6 +29089,12 @@
       <c r="AJ242" s="2" t="n">
         <v>-0.005312084993359907</v>
       </c>
+      <c r="AK242" s="1" t="n">
+        <v>0.00745</v>
+      </c>
+      <c r="AL242" s="2" t="n">
+        <v>-0.005340453938584793</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -27749,6 +29207,12 @@
       <c r="AJ243" s="2" t="n">
         <v>-0.004395604395604369</v>
       </c>
+      <c r="AK243" s="1" t="n">
+        <v>0.02263</v>
+      </c>
+      <c r="AL243" s="2" t="n">
+        <v>-0.0008830022075054828</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -27861,6 +29325,12 @@
       <c r="AJ244" s="2" t="n">
         <v>-0.002935995302407524</v>
       </c>
+      <c r="AK244" s="1" t="n">
+        <v>0.001684</v>
+      </c>
+      <c r="AL244" s="2" t="n">
+        <v>-0.008244994110718565</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -27973,6 +29443,12 @@
       <c r="AJ245" s="2" t="n">
         <v>-0.006060606060606023</v>
       </c>
+      <c r="AK245" s="1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="AL245" s="2" t="n">
+        <v>-0.001524390243902483</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -28085,6 +29561,12 @@
       <c r="AJ246" s="2" t="n">
         <v>-0.006556353418670054</v>
       </c>
+      <c r="AK246" s="1" t="n">
+        <v>0.03162</v>
+      </c>
+      <c r="AL246" s="2" t="n">
+        <v>-0.006285355122564387</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -28197,6 +29679,12 @@
       <c r="AJ247" s="2" t="n">
         <v>-0.002245929253228588</v>
       </c>
+      <c r="AK247" s="1" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="AL247" s="2" t="n">
+        <v>-0.003939223410242016</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -28309,6 +29797,12 @@
       <c r="AJ248" s="2" t="n">
         <v>-0.003610108303249064</v>
       </c>
+      <c r="AK248" s="1" t="n">
+        <v>0.03026</v>
+      </c>
+      <c r="AL248" s="2" t="n">
+        <v>-0.003293807641633823</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -28421,6 +29915,12 @@
       <c r="AJ249" s="2" t="n">
         <v>-0.0144613159797542</v>
       </c>
+      <c r="AK249" s="1" t="n">
+        <v>0.00818</v>
+      </c>
+      <c r="AL249" s="3" t="n">
+        <v>0.0002445585717779733</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -28533,6 +30033,12 @@
       <c r="AJ250" s="2" t="n">
         <v>-0.002507522567703007</v>
       </c>
+      <c r="AK250" s="1" t="n">
+        <v>0.01971</v>
+      </c>
+      <c r="AL250" s="2" t="n">
+        <v>-0.009049773755656262</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -28645,6 +30151,12 @@
       <c r="AJ251" s="2" t="n">
         <v>-0.001291155584247849</v>
       </c>
+      <c r="AK251" s="1" t="n">
+        <v>0.04636</v>
+      </c>
+      <c r="AL251" s="2" t="n">
+        <v>-0.00107735401853052</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -28757,6 +30269,12 @@
       <c r="AJ252" s="2" t="n">
         <v>-0.003010653080129687</v>
       </c>
+      <c r="AK252" s="1" t="n">
+        <v>0.008605</v>
+      </c>
+      <c r="AL252" s="2" t="n">
+        <v>-0.0005807200929151912</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -28869,6 +30387,12 @@
       <c r="AJ253" s="2" t="n">
         <v>-0.003365260160496976</v>
       </c>
+      <c r="AK253" s="1" t="n">
+        <v>0.03845</v>
+      </c>
+      <c r="AL253" s="2" t="n">
+        <v>-0.001298701298701336</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -28981,6 +30505,12 @@
       <c r="AJ254" s="2" t="n">
         <v>-0.00309951060358895</v>
       </c>
+      <c r="AK254" s="1" t="n">
+        <v>0.06101</v>
+      </c>
+      <c r="AL254" s="2" t="n">
+        <v>-0.001636393388970642</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -29093,6 +30623,12 @@
       <c r="AJ255" s="2" t="n">
         <v>-0.007862959842740751</v>
       </c>
+      <c r="AK255" s="1" t="n">
+        <v>0.003527</v>
+      </c>
+      <c r="AL255" s="2" t="n">
+        <v>-0.001698273422020925</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -29205,6 +30741,12 @@
       <c r="AJ256" s="3" t="n">
         <v>0.0006722940165832769</v>
       </c>
+      <c r="AK256" s="1" t="n">
+        <v>0.013442</v>
+      </c>
+      <c r="AL256" s="3" t="n">
+        <v>0.003433860853986332</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -29317,6 +30859,12 @@
       <c r="AJ257" s="2" t="n">
         <v>-5.502756881200206e-05</v>
       </c>
+      <c r="AK257" s="1" t="n">
+        <v>0.999443</v>
+      </c>
+      <c r="AL257" s="2" t="n">
+        <v>-1.000556309336747e-06</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -29429,6 +30977,12 @@
       <c r="AJ258" s="2" t="n">
         <v>-0.0005654189754607542</v>
       </c>
+      <c r="AK258" s="1" t="n">
+        <v>0.08837</v>
+      </c>
+      <c r="AL258" s="2" t="n">
+        <v>-0.0001131477709888677</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -29541,6 +31095,12 @@
       <c r="AJ259" s="2" t="n">
         <v>-0.004768770100920481</v>
       </c>
+      <c r="AK259" s="1" t="n">
+        <v>0.08924</v>
+      </c>
+      <c r="AL259" s="2" t="n">
+        <v>-0.005571651437486076</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -29653,6 +31213,12 @@
       <c r="AJ260" s="2" t="n">
         <v>-0.003546099290780124</v>
       </c>
+      <c r="AK260" s="1" t="n">
+        <v>0.08134</v>
+      </c>
+      <c r="AL260" s="2" t="n">
+        <v>-0.001840716652350119</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -29765,6 +31331,12 @@
       <c r="AJ261" s="2" t="n">
         <v>-0.002657218777679463</v>
       </c>
+      <c r="AK261" s="1" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="AL261" s="3" t="n">
+        <v>0.006216696269982343</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -29877,6 +31449,12 @@
       <c r="AJ262" s="3" t="n">
         <v>0.01122715404699741</v>
       </c>
+      <c r="AK262" s="1" t="n">
+        <v>0.00389</v>
+      </c>
+      <c r="AL262" s="3" t="n">
+        <v>0.004389362251484548</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -29989,6 +31567,12 @@
       <c r="AJ263" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK263" s="1" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="AL263" s="2" t="n">
+        <v>-0.01908065915004331</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -30101,6 +31685,12 @@
       <c r="AJ264" s="2" t="n">
         <v>-0.009826030927835029</v>
       </c>
+      <c r="AK264" s="1" t="n">
+        <v>0.000612</v>
+      </c>
+      <c r="AL264" s="2" t="n">
+        <v>-0.00439238653001466</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -30213,6 +31803,12 @@
       <c r="AJ265" s="2" t="n">
         <v>-0.006126616746085759</v>
       </c>
+      <c r="AK265" s="1" t="n">
+        <v>0.01456</v>
+      </c>
+      <c r="AL265" s="2" t="n">
+        <v>-0.002739726027397267</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -30325,6 +31921,12 @@
       <c r="AJ266" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK266" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="AL266" s="2" t="n">
+        <v>-0.006299212598425159</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -30437,6 +32039,12 @@
       <c r="AJ267" s="2" t="n">
         <v>-0.003069367710251563</v>
       </c>
+      <c r="AK267" s="1" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="AL267" s="2" t="n">
+        <v>-0.0006157635467980044</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -30549,6 +32157,12 @@
       <c r="AJ268" s="3" t="n">
         <v>0.002530480791350418</v>
       </c>
+      <c r="AK268" s="1" t="n">
+        <v>0.0004327</v>
+      </c>
+      <c r="AL268" s="2" t="n">
+        <v>-0.007113354749885317</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -30661,6 +32275,12 @@
       <c r="AJ269" s="2" t="n">
         <v>-0.004318618042226478</v>
       </c>
+      <c r="AK269" s="1" t="n">
+        <v>0.02074</v>
+      </c>
+      <c r="AL269" s="2" t="n">
+        <v>-0.0004819277108433538</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -30773,6 +32393,12 @@
       <c r="AJ270" s="2" t="n">
         <v>-0.003844041735310303</v>
       </c>
+      <c r="AK270" s="1" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="AL270" s="3" t="n">
+        <v>0.001102535832414585</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -30885,6 +32511,12 @@
       <c r="AJ271" s="3" t="n">
         <v>0.001355932203389869</v>
       </c>
+      <c r="AK271" s="1" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="AL271" s="2" t="n">
+        <v>-0.001354096140826037</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -30997,6 +32629,12 @@
       <c r="AJ272" s="2" t="n">
         <v>-0.002773575390821962</v>
       </c>
+      <c r="AK272" s="1" t="n">
+        <v>0.03953</v>
+      </c>
+      <c r="AL272" s="2" t="n">
+        <v>-0.0005056890012642019</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -31109,6 +32747,12 @@
       <c r="AJ273" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK273" s="1" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="AL273" s="2" t="n">
+        <v>-0.005387931034482763</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -31221,6 +32865,12 @@
       <c r="AJ274" s="2" t="n">
         <v>-0.0009457755359393943</v>
       </c>
+      <c r="AK274" s="1" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="AL274" s="2" t="n">
+        <v>-0.001104449353108241</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -31333,6 +32983,12 @@
       <c r="AJ275" s="3" t="n">
         <v>0.002652519893899096</v>
       </c>
+      <c r="AK275" s="1" t="n">
+        <v>0.01127</v>
+      </c>
+      <c r="AL275" s="2" t="n">
+        <v>-0.006172839506172741</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -31445,6 +33101,12 @@
       <c r="AJ276" s="3" t="n">
         <v>0.001916443081640435</v>
       </c>
+      <c r="AK276" s="1" t="n">
+        <v>2.611</v>
+      </c>
+      <c r="AL276" s="2" t="n">
+        <v>-0.00114766641162956</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -31557,6 +33219,12 @@
       <c r="AJ277" s="2" t="n">
         <v>-0.003095238095238217</v>
       </c>
+      <c r="AK277" s="1" t="n">
+        <v>0.04183</v>
+      </c>
+      <c r="AL277" s="2" t="n">
+        <v>-0.0009553379508000566</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -31669,6 +33337,12 @@
       <c r="AJ278" s="2" t="n">
         <v>-0.002041858090862602</v>
       </c>
+      <c r="AK278" s="1" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="AL278" s="2" t="n">
+        <v>-0.002557544757033321</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -31781,6 +33455,12 @@
       <c r="AJ279" s="2" t="n">
         <v>-0.01392030624673746</v>
       </c>
+      <c r="AK279" s="1" t="n">
+        <v>0.005671</v>
+      </c>
+      <c r="AL279" s="3" t="n">
+        <v>0.0007058408328921234</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -31893,6 +33573,12 @@
       <c r="AJ280" s="2" t="n">
         <v>-0.001797175866495523</v>
       </c>
+      <c r="AK280" s="1" t="n">
+        <v>0.03878</v>
+      </c>
+      <c r="AL280" s="2" t="n">
+        <v>-0.002572016460905245</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -32005,6 +33691,12 @@
       <c r="AJ281" s="2" t="n">
         <v>-0.004400440044004405</v>
       </c>
+      <c r="AK281" s="1" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="AL281" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -32117,6 +33809,12 @@
       <c r="AJ282" s="2" t="n">
         <v>-0.001446829033035965</v>
       </c>
+      <c r="AK282" s="1" t="n">
+        <v>0.0004126</v>
+      </c>
+      <c r="AL282" s="2" t="n">
+        <v>-0.003622313450857238</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -32229,6 +33927,12 @@
       <c r="AJ283" s="3" t="n">
         <v>0.001221001221001256</v>
       </c>
+      <c r="AK283" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AL283" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -32341,6 +34045,12 @@
       <c r="AJ284" s="2" t="n">
         <v>-0.006850933144342041</v>
       </c>
+      <c r="AK284" s="1" t="n">
+        <v>0.04203</v>
+      </c>
+      <c r="AL284" s="2" t="n">
+        <v>-0.0002378686964796161</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -32453,6 +34163,12 @@
       <c r="AJ285" s="2" t="n">
         <v>-0.00471698113207544</v>
       </c>
+      <c r="AK285" s="1" t="n">
+        <v>0.10632</v>
+      </c>
+      <c r="AL285" s="2" t="n">
+        <v>-0.0119877334820184</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -32565,6 +34281,12 @@
       <c r="AJ286" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK286" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="AL286" s="2" t="n">
+        <v>-0.004750593824228041</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -32677,6 +34399,12 @@
       <c r="AJ287" s="2" t="n">
         <v>-0.0001920737563224422</v>
       </c>
+      <c r="AK287" s="1" t="n">
+        <v>0.15666</v>
+      </c>
+      <c r="AL287" s="3" t="n">
+        <v>0.003201844262295085</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -32789,6 +34517,12 @@
       <c r="AJ288" s="2" t="n">
         <v>-0.004980630879911521</v>
       </c>
+      <c r="AK288" s="1" t="n">
+        <v>0.1801</v>
+      </c>
+      <c r="AL288" s="3" t="n">
+        <v>0.001668520578420592</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -32901,6 +34635,12 @@
       <c r="AJ289" s="2" t="n">
         <v>-0.005277044854881112</v>
       </c>
+      <c r="AK289" s="1" t="n">
+        <v>4.129</v>
+      </c>
+      <c r="AL289" s="2" t="n">
+        <v>-0.004340487099107953</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -33013,6 +34753,12 @@
       <c r="AJ290" s="2" t="n">
         <v>-0.001633415004083552</v>
       </c>
+      <c r="AK290" s="1" t="n">
+        <v>0.08541</v>
+      </c>
+      <c r="AL290" s="2" t="n">
+        <v>-0.001869814187215069</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -33125,6 +34871,12 @@
       <c r="AJ291" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK291" s="1" t="n">
+        <v>0.03544</v>
+      </c>
+      <c r="AL291" s="3" t="n">
+        <v>0.0002822466836013582</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -33237,6 +34989,12 @@
       <c r="AJ292" s="3" t="n">
         <v>0.0003416233943700088</v>
       </c>
+      <c r="AK292" s="1" t="n">
+        <v>1.4692</v>
+      </c>
+      <c r="AL292" s="3" t="n">
+        <v>0.003483368622361932</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -33349,6 +35107,12 @@
       <c r="AJ293" s="2" t="n">
         <v>-0.001190678686851516</v>
       </c>
+      <c r="AK293" s="1" t="n">
+        <v>0.005844</v>
+      </c>
+      <c r="AL293" s="2" t="n">
+        <v>-0.004768392370572101</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -33461,6 +35225,12 @@
       <c r="AJ294" s="2" t="n">
         <v>-0.005224963715529817</v>
       </c>
+      <c r="AK294" s="1" t="n">
+        <v>0.003419</v>
+      </c>
+      <c r="AL294" s="2" t="n">
+        <v>-0.002334403268164506</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -33573,6 +35343,12 @@
       <c r="AJ295" s="2" t="n">
         <v>-0.002222222222222388</v>
       </c>
+      <c r="AK295" s="1" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="AL295" s="2" t="n">
+        <v>-0.003340757238307188</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -33685,6 +35461,12 @@
       <c r="AJ296" s="2" t="n">
         <v>-0.003544528134692072</v>
       </c>
+      <c r="AK296" s="1" t="n">
+        <v>2.248</v>
+      </c>
+      <c r="AL296" s="2" t="n">
+        <v>-0.000444642063139124</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -33797,6 +35579,12 @@
       <c r="AJ297" s="2" t="n">
         <v>-0.01011302795954789</v>
       </c>
+      <c r="AK297" s="1" t="n">
+        <v>0.01666</v>
+      </c>
+      <c r="AL297" s="3" t="n">
+        <v>0.001201923076923237</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -33909,6 +35697,12 @@
       <c r="AJ298" s="3" t="n">
         <v>0.0008174386920981539</v>
       </c>
+      <c r="AK298" s="1" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AL298" s="2" t="n">
+        <v>-0.0008167710318541314</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -34021,6 +35815,12 @@
       <c r="AJ299" s="2" t="n">
         <v>-0.003597122302158283</v>
       </c>
+      <c r="AK299" s="1" t="n">
+        <v>0.01105</v>
+      </c>
+      <c r="AL299" s="2" t="n">
+        <v>-0.002707581227436713</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -34133,6 +35933,12 @@
       <c r="AJ300" s="2" t="n">
         <v>-0.00240269101393551</v>
       </c>
+      <c r="AK300" s="1" t="n">
+        <v>0.02047</v>
+      </c>
+      <c r="AL300" s="2" t="n">
+        <v>-0.01396917148362245</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -34245,6 +36051,12 @@
       <c r="AJ301" s="2" t="n">
         <v>-0.005266622778143483</v>
       </c>
+      <c r="AK301" s="1" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AL301" s="3" t="n">
+        <v>0.002647253474520077</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -34357,6 +36169,12 @@
       <c r="AJ302" s="3" t="n">
         <v>0.002169197396963161</v>
       </c>
+      <c r="AK302" s="1" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="AL302" s="2" t="n">
+        <v>-0.004329004329004403</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -34469,6 +36287,12 @@
       <c r="AJ303" s="2" t="n">
         <v>-0.002025931928687161</v>
       </c>
+      <c r="AK303" s="1" t="n">
+        <v>0.07360999999999999</v>
+      </c>
+      <c r="AL303" s="2" t="n">
+        <v>-0.003789416700500778</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -34581,6 +36405,12 @@
       <c r="AJ304" s="2" t="n">
         <v>-0.003764115432873339</v>
       </c>
+      <c r="AK304" s="1" t="n">
+        <v>0.01583</v>
+      </c>
+      <c r="AL304" s="2" t="n">
+        <v>-0.003148614609571661</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -34693,6 +36523,12 @@
       <c r="AJ305" s="2" t="n">
         <v>-0.004810676598385953</v>
       </c>
+      <c r="AK305" s="1" t="n">
+        <v>0.06399000000000001</v>
+      </c>
+      <c r="AL305" s="2" t="n">
+        <v>-0.002183065647902717</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -34805,6 +36641,12 @@
       <c r="AJ306" s="2" t="n">
         <v>-0.004236433326608873</v>
       </c>
+      <c r="AK306" s="1" t="n">
+        <v>0.04939</v>
+      </c>
+      <c r="AL306" s="3" t="n">
+        <v>0.0006077795786062043</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -34917,6 +36759,12 @@
       <c r="AJ307" s="2" t="n">
         <v>-0.006458557588805172</v>
       </c>
+      <c r="AK307" s="1" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="AL307" s="3" t="n">
+        <v>0.001083423618634887</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -35029,6 +36877,12 @@
       <c r="AJ308" s="2" t="n">
         <v>-0.003011292346298497</v>
       </c>
+      <c r="AK308" s="1" t="n">
+        <v>0.03967</v>
+      </c>
+      <c r="AL308" s="2" t="n">
+        <v>-0.001510193808205499</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -35141,6 +36995,12 @@
       <c r="AJ309" s="2" t="n">
         <v>-0.0051413881748071</v>
       </c>
+      <c r="AK309" s="1" t="n">
+        <v>0.01547</v>
+      </c>
+      <c r="AL309" s="2" t="n">
+        <v>-0.0006459948320414293</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -35253,6 +37113,12 @@
       <c r="AJ310" s="2" t="n">
         <v>-0.001279239766081883</v>
       </c>
+      <c r="AK310" s="1" t="n">
+        <v>0.05447</v>
+      </c>
+      <c r="AL310" s="2" t="n">
+        <v>-0.003293687099725519</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -35365,6 +37231,12 @@
       <c r="AJ311" s="3" t="n">
         <v>0.004248658318425742</v>
       </c>
+      <c r="AK311" s="1" t="n">
+        <v>0.004462</v>
+      </c>
+      <c r="AL311" s="2" t="n">
+        <v>-0.006457359162770068</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -35477,6 +37349,12 @@
       <c r="AJ312" s="2" t="n">
         <v>-0.002238190599599431</v>
       </c>
+      <c r="AK312" s="1" t="n">
+        <v>0.08464000000000001</v>
+      </c>
+      <c r="AL312" s="2" t="n">
+        <v>-0.000708382526564234</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -35589,6 +37467,12 @@
       <c r="AJ313" s="2" t="n">
         <v>-0.003074044373162177</v>
       </c>
+      <c r="AK313" s="1" t="n">
+        <v>0.07437000000000001</v>
+      </c>
+      <c r="AL313" s="2" t="n">
+        <v>-0.002949457031773669</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -35701,6 +37585,12 @@
       <c r="AJ314" s="2" t="n">
         <v>-0.0006535947712417581</v>
       </c>
+      <c r="AK314" s="1" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="AL314" s="2" t="n">
+        <v>-0.001308044473512137</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -35813,6 +37703,12 @@
       <c r="AJ315" s="2" t="n">
         <v>-0.003128911138923658</v>
       </c>
+      <c r="AK315" s="1" t="n">
+        <v>0.1589</v>
+      </c>
+      <c r="AL315" s="2" t="n">
+        <v>-0.002510985561832917</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -35925,6 +37821,12 @@
       <c r="AJ316" s="2" t="n">
         <v>-0.0005534034311012119</v>
       </c>
+      <c r="AK316" s="1" t="n">
+        <v>0.1802</v>
+      </c>
+      <c r="AL316" s="2" t="n">
+        <v>-0.002214839424141813</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -36037,6 +37939,12 @@
       <c r="AJ317" s="2" t="n">
         <v>-0.00332667997338654</v>
       </c>
+      <c r="AK317" s="1" t="n">
+        <v>0.007458</v>
+      </c>
+      <c r="AL317" s="2" t="n">
+        <v>-0.004272363150867812</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -36149,6 +38057,12 @@
       <c r="AJ318" s="2" t="n">
         <v>-0.003534956794972498</v>
       </c>
+      <c r="AK318" s="1" t="n">
+        <v>0.05088</v>
+      </c>
+      <c r="AL318" s="3" t="n">
+        <v>0.002759164367363052</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -36261,6 +38175,12 @@
       <c r="AJ319" s="3" t="n">
         <v>0.001144778735734937</v>
       </c>
+      <c r="AK319" s="1" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="AL319" s="2" t="n">
+        <v>-0.0002501340003573861</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -36373,6 +38293,12 @@
       <c r="AJ320" s="2" t="n">
         <v>-0.001587661601270206</v>
       </c>
+      <c r="AK320" s="1" t="n">
+        <v>0.4384</v>
+      </c>
+      <c r="AL320" s="2" t="n">
+        <v>-0.004089050431621918</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -36485,6 +38411,12 @@
       <c r="AJ321" s="2" t="n">
         <v>-0.003345342254245964</v>
       </c>
+      <c r="AK321" s="1" t="n">
+        <v>0.07742</v>
+      </c>
+      <c r="AL321" s="2" t="n">
+        <v>-0.0005163955589981715</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -36597,6 +38529,12 @@
       <c r="AJ322" s="3" t="n">
         <v>0.001859888406695566</v>
       </c>
+      <c r="AK322" s="1" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="AL322" s="2" t="n">
+        <v>-0.001856435643564324</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -36709,6 +38647,12 @@
       <c r="AJ323" s="2" t="n">
         <v>-0.00252270433905141</v>
       </c>
+      <c r="AK323" s="1" t="n">
+        <v>1.973</v>
+      </c>
+      <c r="AL323" s="2" t="n">
+        <v>-0.002023267577137078</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -36821,6 +38765,12 @@
       <c r="AJ324" s="2" t="n">
         <v>-0.002474458712156589</v>
       </c>
+      <c r="AK324" s="1" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="AL324" s="2" t="n">
+        <v>-0.0002443012045929766</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -36933,6 +38883,12 @@
       <c r="AJ325" s="2" t="n">
         <v>-0.005020538566864399</v>
       </c>
+      <c r="AK325" s="1" t="n">
+        <v>0.15294</v>
+      </c>
+      <c r="AL325" s="3" t="n">
+        <v>0.002228047182175486</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -37045,6 +39001,12 @@
       <c r="AJ326" s="2" t="n">
         <v>-0.002628324056895432</v>
       </c>
+      <c r="AK326" s="1" t="n">
+        <v>0.006457</v>
+      </c>
+      <c r="AL326" s="3" t="n">
+        <v>0.0009300883583940364</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -37157,6 +39119,12 @@
       <c r="AJ327" s="2" t="n">
         <v>-0.005118110236220469</v>
       </c>
+      <c r="AK327" s="1" t="n">
+        <v>0.01516</v>
+      </c>
+      <c r="AL327" s="2" t="n">
+        <v>-0.0001319087191663544</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -37269,6 +39237,12 @@
       <c r="AJ328" s="2" t="n">
         <v>-0.005181347150259072</v>
       </c>
+      <c r="AK328" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="AL328" s="2" t="n">
+        <v>-0.002083333333333393</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -37381,6 +39355,12 @@
       <c r="AJ329" s="2" t="n">
         <v>-0.004096495220755725</v>
       </c>
+      <c r="AK329" s="1" t="n">
+        <v>0.004364</v>
+      </c>
+      <c r="AL329" s="2" t="n">
+        <v>-0.002742230347349145</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -37493,6 +39473,12 @@
       <c r="AJ330" s="2" t="n">
         <v>-0.0005763688760807348</v>
       </c>
+      <c r="AK330" s="1" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="AL330" s="2" t="n">
+        <v>-0.00615148019992299</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -37605,6 +39591,12 @@
       <c r="AJ331" s="2" t="n">
         <v>-0.002232142857142766</v>
       </c>
+      <c r="AK331" s="1" t="n">
+        <v>0.03565</v>
+      </c>
+      <c r="AL331" s="2" t="n">
+        <v>-0.003076062639821001</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -37717,6 +39709,12 @@
       <c r="AJ332" s="2" t="n">
         <v>-0.004704301075268673</v>
       </c>
+      <c r="AK332" s="1" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="AL332" s="2" t="n">
+        <v>-0.002700877785280293</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -37829,6 +39827,12 @@
       <c r="AJ333" s="2" t="n">
         <v>-0.002074688796680557</v>
       </c>
+      <c r="AK333" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="AL333" s="2" t="n">
+        <v>-0.002079002079001995</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -37941,6 +39945,12 @@
       <c r="AJ334" s="3" t="n">
         <v>0.002500568310979745</v>
       </c>
+      <c r="AK334" s="1" t="n">
+        <v>0.04404</v>
+      </c>
+      <c r="AL334" s="2" t="n">
+        <v>-0.001360544217687019</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -38053,6 +40063,12 @@
       <c r="AJ335" s="2" t="n">
         <v>-0.006839276990718015</v>
       </c>
+      <c r="AK335" s="1" t="n">
+        <v>0.08125</v>
+      </c>
+      <c r="AL335" s="2" t="n">
+        <v>-0.0008607968519429491</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -38165,6 +40181,12 @@
       <c r="AJ336" s="2" t="n">
         <v>-0.0009680542110358457</v>
       </c>
+      <c r="AK336" s="1" t="n">
+        <v>0.2062</v>
+      </c>
+      <c r="AL336" s="2" t="n">
+        <v>-0.0009689922480620432</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -38277,6 +40299,12 @@
       <c r="AJ337" s="2" t="n">
         <v>-0.001976284584980328</v>
       </c>
+      <c r="AK337" s="1" t="n">
+        <v>0.01008</v>
+      </c>
+      <c r="AL337" s="2" t="n">
+        <v>-0.0019801980198019</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -38389,6 +40417,12 @@
       <c r="AJ338" s="2" t="n">
         <v>-0.001755926251097504</v>
       </c>
+      <c r="AK338" s="1" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="AL338" s="2" t="n">
+        <v>-0.002638522427440587</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -38501,6 +40535,12 @@
       <c r="AJ339" s="2" t="n">
         <v>-0.003825136612021892</v>
       </c>
+      <c r="AK339" s="1" t="n">
+        <v>0.01818</v>
+      </c>
+      <c r="AL339" s="2" t="n">
+        <v>-0.002742731760833679</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -38613,6 +40653,12 @@
       <c r="AJ340" s="3" t="n">
         <v>0.008384819064430732</v>
       </c>
+      <c r="AK340" s="1" t="n">
+        <v>0.27711</v>
+      </c>
+      <c r="AL340" s="3" t="n">
+        <v>0.01061269146608324</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -38725,6 +40771,12 @@
       <c r="AJ341" s="2" t="n">
         <v>-0.004426840633737248</v>
       </c>
+      <c r="AK341" s="1" t="n">
+        <v>0.04274</v>
+      </c>
+      <c r="AL341" s="3" t="n">
+        <v>0.0002340276152586722</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -38837,6 +40889,12 @@
       <c r="AJ342" s="2" t="n">
         <v>-0.005443727054057474</v>
       </c>
+      <c r="AK342" s="1" t="n">
+        <v>0.07874</v>
+      </c>
+      <c r="AL342" s="3" t="n">
+        <v>0.002291242362525453</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -38949,6 +41007,12 @@
       <c r="AJ343" s="2" t="n">
         <v>-0.002483010977522233</v>
       </c>
+      <c r="AK343" s="1" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="AL343" s="2" t="n">
+        <v>-0.001703131141097852</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -39061,6 +41125,12 @@
       <c r="AJ344" s="2" t="n">
         <v>-0.001821493624772297</v>
       </c>
+      <c r="AK344" s="1" t="n">
+        <v>0.6024</v>
+      </c>
+      <c r="AL344" s="2" t="n">
+        <v>-0.000663570006635627</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -39173,6 +41243,12 @@
       <c r="AJ345" s="2" t="n">
         <v>-0.005594033031433003</v>
       </c>
+      <c r="AK345" s="1" t="n">
+        <v>0.03725</v>
+      </c>
+      <c r="AL345" s="2" t="n">
+        <v>-0.002143048486472105</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -39285,6 +41361,12 @@
       <c r="AJ346" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK346" s="1" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="AL346" s="2" t="n">
+        <v>-0.002403846153846056</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -39397,6 +41479,12 @@
       <c r="AJ347" s="2" t="n">
         <v>-0.001710376282782182</v>
       </c>
+      <c r="AK347" s="1" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="AL347" s="2" t="n">
+        <v>-0.001713306681896029</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -39509,6 +41597,12 @@
       <c r="AJ348" s="3" t="n">
         <v>9.62000962000962e-05</v>
       </c>
+      <c r="AK348" s="1" t="n">
+        <v>5197.1</v>
+      </c>
+      <c r="AL348" s="2" t="n">
+        <v>-0.0001731435167371366</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -39621,6 +41715,12 @@
       <c r="AJ349" s="2" t="n">
         <v>-0.006578947368421038</v>
       </c>
+      <c r="AK349" s="1" t="n">
+        <v>0.01363</v>
+      </c>
+      <c r="AL349" s="3" t="n">
+        <v>0.00294334069168507</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -39733,6 +41833,12 @@
       <c r="AJ350" s="3" t="n">
         <v>0.003211303789338452</v>
       </c>
+      <c r="AK350" s="1" t="n">
+        <v>0.01561</v>
+      </c>
+      <c r="AL350" s="2" t="n">
+        <v>-0.0006402048655569522</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -39845,6 +41951,12 @@
       <c r="AJ351" s="2" t="n">
         <v>-0.002262443438913907</v>
       </c>
+      <c r="AK351" s="1" t="n">
+        <v>0.0006143</v>
+      </c>
+      <c r="AL351" s="2" t="n">
+        <v>-0.005021056041464239</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -39957,6 +42069,12 @@
       <c r="AJ352" s="2" t="n">
         <v>-0.001512096774193487</v>
       </c>
+      <c r="AK352" s="1" t="n">
+        <v>0.01969</v>
+      </c>
+      <c r="AL352" s="2" t="n">
+        <v>-0.0060575466935892</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -40069,6 +42187,12 @@
       <c r="AJ353" s="2" t="n">
         <v>-0.002998500749625214</v>
       </c>
+      <c r="AK353" s="1" t="n">
+        <v>0.09327000000000001</v>
+      </c>
+      <c r="AL353" s="3" t="n">
+        <v>0.001825993555316901</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -40181,6 +42305,12 @@
       <c r="AJ354" s="2" t="n">
         <v>-0.003311258278145637</v>
       </c>
+      <c r="AK354" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="AL354" s="2" t="n">
+        <v>-0.004429678848283626</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -40293,6 +42423,12 @@
       <c r="AJ355" s="3" t="n">
         <v>0.009847365829640633</v>
       </c>
+      <c r="AK355" s="1" t="n">
+        <v>0.0006106</v>
+      </c>
+      <c r="AL355" s="2" t="n">
+        <v>-0.007638550300666439</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -40405,6 +42541,12 @@
       <c r="AJ356" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK356" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL356" s="2" t="n">
+        <v>-0.01039089559623944</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -40517,6 +42659,12 @@
       <c r="AJ357" s="2" t="n">
         <v>-0.0004361098996947053</v>
       </c>
+      <c r="AK357" s="1" t="n">
+        <v>0.02292</v>
+      </c>
+      <c r="AL357" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -40629,6 +42777,12 @@
       <c r="AJ358" s="3" t="n">
         <v>0.002450980392156922</v>
       </c>
+      <c r="AK358" s="1" t="n">
+        <v>0.000407</v>
+      </c>
+      <c r="AL358" s="2" t="n">
+        <v>-0.004889975550122235</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -40741,6 +42895,12 @@
       <c r="AJ359" s="2" t="n">
         <v>-0.002033898305084663</v>
       </c>
+      <c r="AK359" s="1" t="n">
+        <v>0.01472</v>
+      </c>
+      <c r="AL359" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -40853,6 +43013,12 @@
       <c r="AJ360" s="2" t="n">
         <v>-0.004185351270552972</v>
       </c>
+      <c r="AK360" s="1" t="n">
+        <v>0.003321</v>
+      </c>
+      <c r="AL360" s="2" t="n">
+        <v>-0.003002101471029728</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -40965,6 +43131,12 @@
       <c r="AJ361" s="2" t="n">
         <v>-0.004691898654989057</v>
       </c>
+      <c r="AK361" s="1" t="n">
+        <v>0.6337</v>
+      </c>
+      <c r="AL361" s="2" t="n">
+        <v>-0.004242614707730868</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -41077,6 +43249,12 @@
       <c r="AJ362" s="2" t="n">
         <v>-0.002961082910321515</v>
       </c>
+      <c r="AK362" s="1" t="n">
+        <v>0.02358</v>
+      </c>
+      <c r="AL362" s="3" t="n">
+        <v>0.0004242681374628592</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -41189,6 +43367,12 @@
       <c r="AJ363" s="2" t="n">
         <v>-0.001529987760097963</v>
       </c>
+      <c r="AK363" s="1" t="n">
+        <v>0.06489</v>
+      </c>
+      <c r="AL363" s="2" t="n">
+        <v>-0.005669629175605199</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -41301,6 +43485,12 @@
       <c r="AJ364" s="2" t="n">
         <v>-0.002755988976044075</v>
       </c>
+      <c r="AK364" s="1" t="n">
+        <v>4.695</v>
+      </c>
+      <c r="AL364" s="2" t="n">
+        <v>-0.001913265306122333</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -41413,6 +43603,12 @@
       <c r="AJ365" s="3" t="n">
         <v>0.0001391207568168631</v>
       </c>
+      <c r="AK365" s="1" t="n">
+        <v>0.07192999999999999</v>
+      </c>
+      <c r="AL365" s="3" t="n">
+        <v>0.0005564056196967363</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -41525,6 +43721,12 @@
       <c r="AJ366" s="2" t="n">
         <v>-0.003563791874554628</v>
       </c>
+      <c r="AK366" s="1" t="n">
+        <v>0.05565</v>
+      </c>
+      <c r="AL366" s="2" t="n">
+        <v>-0.004828326180257501</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -41637,6 +43839,12 @@
       <c r="AJ367" s="2" t="n">
         <v>-0.0013696284882725</v>
       </c>
+      <c r="AK367" s="1" t="n">
+        <v>0.05812</v>
+      </c>
+      <c r="AL367" s="2" t="n">
+        <v>-0.00360020572604152</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -41749,6 +43957,12 @@
       <c r="AJ368" s="2" t="n">
         <v>-0.004543071815481448</v>
       </c>
+      <c r="AK368" s="1" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="AL368" s="2" t="n">
+        <v>-0.002984026680709084</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -41861,6 +44075,12 @@
       <c r="AJ369" s="2" t="n">
         <v>-0.003534704370179916</v>
       </c>
+      <c r="AK369" s="1" t="n">
+        <v>0.03095</v>
+      </c>
+      <c r="AL369" s="2" t="n">
+        <v>-0.00193485972267014</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -41973,6 +44193,12 @@
       <c r="AJ370" s="2" t="n">
         <v>-0.002470660901791289</v>
       </c>
+      <c r="AK370" s="1" t="n">
+        <v>0.0001611</v>
+      </c>
+      <c r="AL370" s="2" t="n">
+        <v>-0.002476780185758407</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -42085,6 +44311,12 @@
       <c r="AJ371" s="2" t="n">
         <v>-0.0001466920932961908</v>
       </c>
+      <c r="AK371" s="1" t="n">
+        <v>0.006796</v>
+      </c>
+      <c r="AL371" s="2" t="n">
+        <v>-0.002934272300469491</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -42197,6 +44429,12 @@
       <c r="AJ372" s="2" t="n">
         <v>-0.001148930058882569</v>
       </c>
+      <c r="AK372" s="1" t="n">
+        <v>0.006893</v>
+      </c>
+      <c r="AL372" s="2" t="n">
+        <v>-0.008914450035945423</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -42309,6 +44547,12 @@
       <c r="AJ373" s="3" t="n">
         <v>0.007550117156990345</v>
       </c>
+      <c r="AK373" s="1" t="n">
+        <v>3.836</v>
+      </c>
+      <c r="AL373" s="2" t="n">
+        <v>-0.008785529715762339</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -42421,6 +44665,12 @@
       <c r="AJ374" s="2" t="n">
         <v>-0.003979533826037556</v>
       </c>
+      <c r="AK374" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AL374" s="2" t="n">
+        <v>-0.001141552511415479</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -42533,6 +44783,12 @@
       <c r="AJ375" s="2" t="n">
         <v>-0.004507324402153489</v>
       </c>
+      <c r="AK375" s="1" t="n">
+        <v>0.07897</v>
+      </c>
+      <c r="AL375" s="2" t="n">
+        <v>-0.006791598541064002</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -42645,6 +44901,12 @@
       <c r="AJ376" s="3" t="n">
         <v>0.0006351222610354438</v>
       </c>
+      <c r="AK376" s="1" t="n">
+        <v>0.06289</v>
+      </c>
+      <c r="AL376" s="2" t="n">
+        <v>-0.002062837194541496</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -42757,6 +45019,12 @@
       <c r="AJ377" s="3" t="n">
         <v>0.001693149257619238</v>
       </c>
+      <c r="AK377" s="1" t="n">
+        <v>0.07672</v>
+      </c>
+      <c r="AL377" s="2" t="n">
+        <v>-0.002470419971395262</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -42869,6 +45137,12 @@
       <c r="AJ378" s="2" t="n">
         <v>-0.005392156862745096</v>
       </c>
+      <c r="AK378" s="1" t="n">
+        <v>0.0004041</v>
+      </c>
+      <c r="AL378" s="2" t="n">
+        <v>-0.004189255791030033</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -42981,6 +45255,12 @@
       <c r="AJ379" s="2" t="n">
         <v>-0.0006776904310110395</v>
       </c>
+      <c r="AK379" s="1" t="n">
+        <v>0.07371</v>
+      </c>
+      <c r="AL379" s="2" t="n">
+        <v>-0.0002712600027126831</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -43093,6 +45373,12 @@
       <c r="AJ380" s="2" t="n">
         <v>-0.0108538350217077</v>
       </c>
+      <c r="AK380" s="1" t="n">
+        <v>0.001376</v>
+      </c>
+      <c r="AL380" s="3" t="n">
+        <v>0.006583760058522393</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -43205,6 +45491,12 @@
       <c r="AJ381" s="2" t="n">
         <v>-0.002355527638191044</v>
       </c>
+      <c r="AK381" s="1" t="n">
+        <v>6.328</v>
+      </c>
+      <c r="AL381" s="2" t="n">
+        <v>-0.003935148748622614</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -43317,6 +45609,12 @@
       <c r="AJ382" s="3" t="n">
         <v>0.012847965738758</v>
       </c>
+      <c r="AK382" s="1" t="n">
+        <v>0.01402</v>
+      </c>
+      <c r="AL382" s="2" t="n">
+        <v>-0.01198026779422128</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -43429,6 +45727,12 @@
       <c r="AJ383" s="2" t="n">
         <v>-0.002283105022831155</v>
       </c>
+      <c r="AK383" s="1" t="n">
+        <v>0.01746</v>
+      </c>
+      <c r="AL383" s="2" t="n">
+        <v>-0.001144164759725354</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -43541,6 +45845,12 @@
       <c r="AJ384" s="2" t="n">
         <v>-0.0009823182711198709</v>
       </c>
+      <c r="AK384" s="1" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="AL384" s="2" t="n">
+        <v>-0.002949852507374579</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -43653,6 +45963,12 @@
       <c r="AJ385" s="2" t="n">
         <v>-0.003552397868561085</v>
       </c>
+      <c r="AK385" s="1" t="n">
+        <v>4.477</v>
+      </c>
+      <c r="AL385" s="2" t="n">
+        <v>-0.00245098039215689</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -43765,6 +46081,12 @@
       <c r="AJ386" s="2" t="n">
         <v>-0.005351681957186426</v>
       </c>
+      <c r="AK386" s="1" t="n">
+        <v>0.001302</v>
+      </c>
+      <c r="AL386" s="3" t="n">
+        <v>0.0007686395080706501</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -43877,6 +46199,12 @@
       <c r="AJ387" s="2" t="n">
         <v>-0.003208375548801067</v>
       </c>
+      <c r="AK387" s="1" t="n">
+        <v>0.000589</v>
+      </c>
+      <c r="AL387" s="2" t="n">
+        <v>-0.002202270032186985</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -43989,6 +46317,12 @@
       <c r="AJ388" s="3" t="n">
         <v>0.002631578947368314</v>
       </c>
+      <c r="AK388" s="1" t="n">
+        <v>0.01138</v>
+      </c>
+      <c r="AL388" s="2" t="n">
+        <v>-0.004374453193350805</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -44101,6 +46435,12 @@
       <c r="AJ389" s="2" t="n">
         <v>-0.004400440044004411</v>
       </c>
+      <c r="AK389" s="1" t="n">
+        <v>0.00903</v>
+      </c>
+      <c r="AL389" s="2" t="n">
+        <v>-0.002209944751381317</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -44213,6 +46553,12 @@
       <c r="AJ390" s="2" t="n">
         <v>-0.001771030993042394</v>
       </c>
+      <c r="AK390" s="1" t="n">
+        <v>0.07868</v>
+      </c>
+      <c r="AL390" s="2" t="n">
+        <v>-0.002914712964136283</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -44325,6 +46671,12 @@
       <c r="AJ391" s="3" t="n">
         <v>0.0005767012687428345</v>
       </c>
+      <c r="AK391" s="1" t="n">
+        <v>0.05179</v>
+      </c>
+      <c r="AL391" s="2" t="n">
+        <v>-0.00499519692603259</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -44437,6 +46789,12 @@
       <c r="AJ392" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK392" s="1" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="AL392" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -44549,6 +46907,12 @@
       <c r="AJ393" s="2" t="n">
         <v>-0.01030444964871201</v>
       </c>
+      <c r="AK393" s="1" t="n">
+        <v>0.02109</v>
+      </c>
+      <c r="AL393" s="2" t="n">
+        <v>-0.001893043066729691</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -44661,6 +47025,12 @@
       <c r="AJ394" s="2" t="n">
         <v>-0.005432098765432185</v>
       </c>
+      <c r="AK394" s="1" t="n">
+        <v>0.2011</v>
+      </c>
+      <c r="AL394" s="2" t="n">
+        <v>-0.001489572989076439</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -44773,6 +47143,12 @@
       <c r="AJ395" s="3" t="n">
         <v>0.001024590163934313</v>
       </c>
+      <c r="AK395" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="AL395" s="2" t="n">
+        <v>-0.002047082906857645</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -44885,6 +47261,12 @@
       <c r="AJ396" s="2" t="n">
         <v>-0.003979739507959362</v>
       </c>
+      <c r="AK396" s="1" t="n">
+        <v>2.744</v>
+      </c>
+      <c r="AL396" s="2" t="n">
+        <v>-0.003269160915365019</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -44997,6 +47379,12 @@
       <c r="AJ397" s="2" t="n">
         <v>-0.0007898894154819209</v>
       </c>
+      <c r="AK397" s="1" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="AL397" s="2" t="n">
+        <v>-0.001581027667984191</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -45109,6 +47497,12 @@
       <c r="AJ398" s="3" t="n">
         <v>0.0005329780146568505</v>
       </c>
+      <c r="AK398" s="1" t="n">
+        <v>0.007496</v>
+      </c>
+      <c r="AL398" s="2" t="n">
+        <v>-0.001731255826341722</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -45221,6 +47615,12 @@
       <c r="AJ399" s="2" t="n">
         <v>-0.002707930367504967</v>
       </c>
+      <c r="AK399" s="1" t="n">
+        <v>0.2571</v>
+      </c>
+      <c r="AL399" s="2" t="n">
+        <v>-0.002715283165244292</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -45333,6 +47733,12 @@
       <c r="AJ400" s="2" t="n">
         <v>-0.0003136762860727384</v>
       </c>
+      <c r="AK400" s="1" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AL400" s="2" t="n">
+        <v>-0.002510197678067046</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -45445,6 +47851,12 @@
       <c r="AJ401" s="2" t="n">
         <v>-0.008076659822039702</v>
       </c>
+      <c r="AK401" s="1" t="n">
+        <v>0.007249</v>
+      </c>
+      <c r="AL401" s="3" t="n">
+        <v>0.0004140215291195692</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -45557,6 +47969,12 @@
       <c r="AJ402" s="2" t="n">
         <v>-0.00391730141458102</v>
       </c>
+      <c r="AK402" s="1" t="n">
+        <v>0.004567</v>
+      </c>
+      <c r="AL402" s="2" t="n">
+        <v>-0.002184837229626493</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -45669,6 +48087,12 @@
       <c r="AJ403" s="2" t="n">
         <v>-0.004874390701162234</v>
       </c>
+      <c r="AK403" s="1" t="n">
+        <v>0.2649</v>
+      </c>
+      <c r="AL403" s="2" t="n">
+        <v>-0.001883948756593822</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -45781,6 +48205,12 @@
       <c r="AJ404" s="2" t="n">
         <v>-0.002082465639316953</v>
       </c>
+      <c r="AK404" s="1" t="n">
+        <v>0.2379</v>
+      </c>
+      <c r="AL404" s="2" t="n">
+        <v>-0.0070951585976628</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -45893,6 +48323,12 @@
       <c r="AJ405" s="2" t="n">
         <v>-0.006498781478472693</v>
       </c>
+      <c r="AK405" s="1" t="n">
+        <v>0.0008555</v>
+      </c>
+      <c r="AL405" s="2" t="n">
+        <v>-0.0007008527041233671</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -46005,6 +48441,12 @@
       <c r="AJ406" s="2" t="n">
         <v>-0.005719921104536393</v>
       </c>
+      <c r="AK406" s="1" t="n">
+        <v>0.005033</v>
+      </c>
+      <c r="AL406" s="2" t="n">
+        <v>-0.001586986708986351</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -46117,6 +48559,12 @@
       <c r="AJ407" s="2" t="n">
         <v>-0.005804311774460936</v>
       </c>
+      <c r="AK407" s="1" t="n">
+        <v>0.01197</v>
+      </c>
+      <c r="AL407" s="2" t="n">
+        <v>-0.00166805671392835</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -46229,6 +48677,12 @@
       <c r="AJ408" s="3" t="n">
         <v>0.002027027027027003</v>
       </c>
+      <c r="AK408" s="1" t="n">
+        <v>0.001486</v>
+      </c>
+      <c r="AL408" s="3" t="n">
+        <v>0.002022926500337131</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -46341,6 +48795,12 @@
       <c r="AJ409" s="3" t="n">
         <v>0.01210092687950562</v>
       </c>
+      <c r="AK409" s="1" t="n">
+        <v>0.03931</v>
+      </c>
+      <c r="AL409" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -46453,6 +48913,12 @@
       <c r="AJ410" s="2" t="n">
         <v>-0.006123698714023232</v>
       </c>
+      <c r="AK410" s="1" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="AL410" s="2" t="n">
+        <v>-0.0006161429451634665</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -46565,6 +49031,12 @@
       <c r="AJ411" s="2" t="n">
         <v>-0.003144654088050259</v>
       </c>
+      <c r="AK411" s="1" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="AL411" s="2" t="n">
+        <v>-0.002628811777076764</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -46677,6 +49149,12 @@
       <c r="AJ412" s="2" t="n">
         <v>-0.001481700992739502</v>
       </c>
+      <c r="AK412" s="1" t="n">
+        <v>0.06744</v>
+      </c>
+      <c r="AL412" s="3" t="n">
+        <v>0.0007419498441904509</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -46789,6 +49267,12 @@
       <c r="AJ413" s="2" t="n">
         <v>-0.001577909270216962</v>
       </c>
+      <c r="AK413" s="1" t="n">
+        <v>2528</v>
+      </c>
+      <c r="AL413" s="2" t="n">
+        <v>-0.001185302252074279</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -46901,6 +49385,12 @@
       <c r="AJ414" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK414" s="1" t="n">
+        <v>0.05248</v>
+      </c>
+      <c r="AL414" s="2" t="n">
+        <v>-0.00152207001522077</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -47013,6 +49503,12 @@
       <c r="AJ415" s="3" t="n">
         <v>0.001717229536347963</v>
       </c>
+      <c r="AK415" s="1" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL415" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -47125,6 +49621,12 @@
       <c r="AJ416" s="2" t="n">
         <v>-0.001448225923244068</v>
       </c>
+      <c r="AK416" s="1" t="n">
+        <v>0.06872</v>
+      </c>
+      <c r="AL416" s="2" t="n">
+        <v>-0.003335750543872286</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -47237,6 +49739,12 @@
       <c r="AJ417" s="2" t="n">
         <v>-0.01333333333333335</v>
       </c>
+      <c r="AK417" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AL417" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -47349,6 +49857,12 @@
       <c r="AJ418" s="2" t="n">
         <v>-0.003952569169960405</v>
       </c>
+      <c r="AK418" s="1" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="AL418" s="2" t="n">
+        <v>-0.001984126984126949</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -47461,6 +49975,12 @@
       <c r="AJ419" s="3" t="n">
         <v>0.008130081300812959</v>
       </c>
+      <c r="AK419" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="AL419" s="2" t="n">
+        <v>-0.008064516129032209</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -47573,6 +50093,12 @@
       <c r="AJ420" s="2" t="n">
         <v>-0.00622406639004142</v>
       </c>
+      <c r="AK420" s="1" t="n">
+        <v>0.01907</v>
+      </c>
+      <c r="AL420" s="2" t="n">
+        <v>-0.004697286012526085</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -47685,6 +50211,12 @@
       <c r="AJ421" s="2" t="n">
         <v>-0.002210115131579018</v>
       </c>
+      <c r="AK421" s="1" t="n">
+        <v>0.19375</v>
+      </c>
+      <c r="AL421" s="2" t="n">
+        <v>-0.001957451192499827</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -47797,6 +50329,12 @@
       <c r="AJ422" s="2" t="n">
         <v>-0.006707494896471305</v>
       </c>
+      <c r="AK422" s="1" t="n">
+        <v>0.03398</v>
+      </c>
+      <c r="AL422" s="2" t="n">
+        <v>-0.002348796241925917</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -47909,6 +50447,12 @@
       <c r="AJ423" s="2" t="n">
         <v>-0.001411432604093195</v>
       </c>
+      <c r="AK423" s="1" t="n">
+        <v>0.1412</v>
+      </c>
+      <c r="AL423" s="2" t="n">
+        <v>-0.002120141342756147</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -48021,6 +50565,12 @@
       <c r="AJ424" s="2" t="n">
         <v>-0.001886792452830112</v>
       </c>
+      <c r="AK424" s="1" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="AL424" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -48133,6 +50683,12 @@
       <c r="AJ425" s="3" t="n">
         <v>0.001915708812260458</v>
       </c>
+      <c r="AK425" s="1" t="n">
+        <v>0.1043</v>
+      </c>
+      <c r="AL425" s="2" t="n">
+        <v>-0.002868068833651957</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -48245,6 +50801,12 @@
       <c r="AJ426" s="2" t="n">
         <v>-0.002816901408450711</v>
       </c>
+      <c r="AK426" s="1" t="n">
+        <v>0.007063</v>
+      </c>
+      <c r="AL426" s="2" t="n">
+        <v>-0.002401129943502898</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -48357,6 +50919,12 @@
       <c r="AJ427" s="2" t="n">
         <v>-0.0003921568627450821</v>
       </c>
+      <c r="AK427" s="1" t="n">
+        <v>0.02546</v>
+      </c>
+      <c r="AL427" s="2" t="n">
+        <v>-0.001176932130247108</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -48469,6 +51037,12 @@
       <c r="AJ428" s="2" t="n">
         <v>-0.00556999628666913</v>
       </c>
+      <c r="AK428" s="1" t="n">
+        <v>0.008023000000000001</v>
+      </c>
+      <c r="AL428" s="2" t="n">
+        <v>-0.001369180980831324</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -48581,6 +51155,12 @@
       <c r="AJ429" s="2" t="n">
         <v>-0.0008103727714748454</v>
       </c>
+      <c r="AK429" s="1" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="AL429" s="2" t="n">
+        <v>-0.004055150040551616</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -48693,6 +51273,12 @@
       <c r="AJ430" s="2" t="n">
         <v>-0.002846868444710755</v>
       </c>
+      <c r="AK430" s="1" t="n">
+        <v>0.06652</v>
+      </c>
+      <c r="AL430" s="2" t="n">
+        <v>-0.0004507888805409804</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -48805,6 +51391,12 @@
       <c r="AJ431" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK431" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="AL431" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -48917,6 +51509,12 @@
       <c r="AJ432" s="3" t="n">
         <v>0.003241999581677632</v>
       </c>
+      <c r="AK432" s="1" t="n">
+        <v>0.009563</v>
+      </c>
+      <c r="AL432" s="2" t="n">
+        <v>-0.003127280308558377</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -49029,6 +51627,12 @@
       <c r="AJ433" s="2" t="n">
         <v>-0.001696147322510313</v>
       </c>
+      <c r="AK433" s="1" t="n">
+        <v>0.04107</v>
+      </c>
+      <c r="AL433" s="2" t="n">
+        <v>-0.003155339805825198</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -49141,6 +51745,12 @@
       <c r="AJ434" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK434" s="1" t="n">
+        <v>0.04288</v>
+      </c>
+      <c r="AL434" s="3" t="n">
+        <v>0.008466603951081824</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -49253,6 +51863,12 @@
       <c r="AJ435" s="2" t="n">
         <v>-0.003215434083601295</v>
       </c>
+      <c r="AK435" s="1" t="n">
+        <v>0.001548</v>
+      </c>
+      <c r="AL435" s="2" t="n">
+        <v>-0.001290322580645193</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -49365,6 +51981,12 @@
       <c r="AJ436" s="2" t="n">
         <v>-0.00363108206245459</v>
       </c>
+      <c r="AK436" s="1" t="n">
+        <v>0.02742</v>
+      </c>
+      <c r="AL436" s="2" t="n">
+        <v>-0.0007288629737609032</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -49477,6 +52099,12 @@
       <c r="AJ437" s="2" t="n">
         <v>-0.009079903147699766</v>
       </c>
+      <c r="AK437" s="1" t="n">
+        <v>0.08225</v>
+      </c>
+      <c r="AL437" s="3" t="n">
+        <v>0.004886988393402535</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -49589,6 +52217,12 @@
       <c r="AJ438" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK438" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AL438" s="2" t="n">
+        <v>-0.00173611111111104</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -49701,6 +52335,12 @@
       <c r="AJ439" s="2" t="n">
         <v>-0.0006430868167201865</v>
       </c>
+      <c r="AK439" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL439" s="2" t="n">
+        <v>-0.002574002574002576</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -49813,6 +52453,12 @@
       <c r="AJ440" s="2" t="n">
         <v>-0.001097092704333543</v>
       </c>
+      <c r="AK440" s="1" t="n">
+        <v>0.001815</v>
+      </c>
+      <c r="AL440" s="2" t="n">
+        <v>-0.003294892915980192</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -49925,6 +52571,12 @@
       <c r="AJ441" s="2" t="n">
         <v>-0.004353741496598651</v>
       </c>
+      <c r="AK441" s="1" t="n">
+        <v>0.03652</v>
+      </c>
+      <c r="AL441" s="2" t="n">
+        <v>-0.001913091008472277</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -50037,6 +52689,12 @@
       <c r="AJ442" s="2" t="n">
         <v>-0.004357298474945545</v>
       </c>
+      <c r="AK442" s="1" t="n">
+        <v>0.01824</v>
+      </c>
+      <c r="AL442" s="2" t="n">
+        <v>-0.002188183807439925</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -50149,6 +52807,12 @@
       <c r="AJ443" s="2" t="n">
         <v>-0.001889317484058807</v>
       </c>
+      <c r="AK443" s="1" t="n">
+        <v>0.12669</v>
+      </c>
+      <c r="AL443" s="2" t="n">
+        <v>-0.0007887057338908174</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -50261,6 +52925,12 @@
       <c r="AJ444" s="3" t="n">
         <v>0.0003467706978760755</v>
       </c>
+      <c r="AK444" s="1" t="n">
+        <v>0.01159</v>
+      </c>
+      <c r="AL444" s="3" t="n">
+        <v>0.004419793742958571</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -50373,6 +53043,12 @@
       <c r="AJ445" s="2" t="n">
         <v>-0.003219016961743176</v>
       </c>
+      <c r="AK445" s="1" t="n">
+        <v>0.0803</v>
+      </c>
+      <c r="AL445" s="2" t="n">
+        <v>-0.002608371630853333</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -50485,6 +53161,12 @@
       <c r="AJ446" s="2" t="n">
         <v>-0.002791996277338239</v>
       </c>
+      <c r="AK446" s="1" t="n">
+        <v>0.0002139</v>
+      </c>
+      <c r="AL446" s="2" t="n">
+        <v>-0.001866542230518011</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -50597,6 +53279,12 @@
       <c r="AJ447" s="3" t="n">
         <v>0.001506024096385481</v>
       </c>
+      <c r="AK447" s="1" t="n">
+        <v>0.00662</v>
+      </c>
+      <c r="AL447" s="2" t="n">
+        <v>-0.004511278195488668</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -50709,6 +53397,12 @@
       <c r="AJ448" s="3" t="n">
         <v>0.004501278772378475</v>
       </c>
+      <c r="AK448" s="1" t="n">
+        <v>0.09946000000000001</v>
+      </c>
+      <c r="AL448" s="3" t="n">
+        <v>0.01293410734290668</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -50821,6 +53515,12 @@
       <c r="AJ449" s="2" t="n">
         <v>-0.0005966587112171336</v>
       </c>
+      <c r="AK449" s="1" t="n">
+        <v>0.001676</v>
+      </c>
+      <c r="AL449" s="3" t="n">
+        <v>0.0005970149253730841</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -50933,6 +53633,12 @@
       <c r="AJ450" s="2" t="n">
         <v>-0.00239923224568131</v>
       </c>
+      <c r="AK450" s="1" t="n">
+        <v>0.0002073</v>
+      </c>
+      <c r="AL450" s="2" t="n">
+        <v>-0.002886002886002956</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -51045,6 +53751,12 @@
       <c r="AJ451" s="2" t="n">
         <v>-0.003403933434190615</v>
       </c>
+      <c r="AK451" s="1" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="AL451" s="2" t="n">
+        <v>-0.007210626185958302</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -51157,6 +53869,12 @@
       <c r="AJ452" s="2" t="n">
         <v>-0.001481481481481524</v>
       </c>
+      <c r="AK452" s="1" t="n">
+        <v>0.1345</v>
+      </c>
+      <c r="AL452" s="2" t="n">
+        <v>-0.002225519287833789</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -51269,6 +53987,12 @@
       <c r="AJ453" s="2" t="n">
         <v>-0.002292263610315242</v>
       </c>
+      <c r="AK453" s="1" t="n">
+        <v>0.0001732</v>
+      </c>
+      <c r="AL453" s="2" t="n">
+        <v>-0.005169442848937362</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -51381,6 +54105,12 @@
       <c r="AJ454" s="2" t="n">
         <v>-0.002442775716999967</v>
       </c>
+      <c r="AK454" s="1" t="n">
+        <v>0.11106</v>
+      </c>
+      <c r="AL454" s="3" t="n">
+        <v>0.007255577725376466</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -51493,6 +54223,12 @@
       <c r="AJ455" s="2" t="n">
         <v>-0.004975124378109347</v>
       </c>
+      <c r="AK455" s="1" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="AL455" s="2" t="n">
+        <v>-0.002399999999999958</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -51605,6 +54341,12 @@
       <c r="AJ456" s="3" t="n">
         <v>0.0005634155502693166</v>
       </c>
+      <c r="AK456" s="1" t="n">
+        <v>0.015996</v>
+      </c>
+      <c r="AL456" s="3" t="n">
+        <v>0.0008133641994618735</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -51717,6 +54459,12 @@
       <c r="AJ457" s="2" t="n">
         <v>-0.0004491017964072452</v>
       </c>
+      <c r="AK457" s="1" t="n">
+        <v>0.006675</v>
+      </c>
+      <c r="AL457" s="2" t="n">
+        <v>-0.0002995357196344763</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -51829,6 +54577,12 @@
       <c r="AJ458" s="2" t="n">
         <v>-0.000207168013258845</v>
       </c>
+      <c r="AK458" s="1" t="n">
+        <v>0.4823</v>
+      </c>
+      <c r="AL458" s="2" t="n">
+        <v>-0.0006216328222129444</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -51941,6 +54695,12 @@
       <c r="AJ459" s="2" t="n">
         <v>-0.002359603586597355</v>
       </c>
+      <c r="AK459" s="1" t="n">
+        <v>0.006336</v>
+      </c>
+      <c r="AL459" s="2" t="n">
+        <v>-0.0009460737937560385</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -52053,6 +54813,12 @@
       <c r="AJ460" s="2" t="n">
         <v>-0.004357298474945457</v>
       </c>
+      <c r="AK460" s="1" t="n">
+        <v>0.1371</v>
+      </c>
+      <c r="AL460" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -52165,6 +54931,12 @@
       <c r="AJ461" s="2" t="n">
         <v>-0.0014430014430015</v>
       </c>
+      <c r="AK461" s="1" t="n">
+        <v>0.09014999999999999</v>
+      </c>
+      <c r="AL461" s="3" t="n">
+        <v>0.002112049799911024</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -52277,6 +55049,12 @@
       <c r="AJ462" s="2" t="n">
         <v>-0.001108893324462218</v>
       </c>
+      <c r="AK462" s="1" t="n">
+        <v>0.04507</v>
+      </c>
+      <c r="AL462" s="3" t="n">
+        <v>0.0006660746003552897</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -52389,6 +55167,12 @@
       <c r="AJ463" s="2" t="n">
         <v>-0.001426533523537745</v>
       </c>
+      <c r="AK463" s="1" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="AL463" s="2" t="n">
+        <v>-0.001428571428571494</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -52501,6 +55285,12 @@
       <c r="AJ464" s="2" t="n">
         <v>-0.003828483920367623</v>
       </c>
+      <c r="AK464" s="1" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="AL464" s="2" t="n">
+        <v>-0.003843197540353492</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -52613,6 +55403,12 @@
       <c r="AJ465" s="2" t="n">
         <v>-0.003230437903804781</v>
       </c>
+      <c r="AK465" s="1" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="AL465" s="2" t="n">
+        <v>-0.001080302484695796</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -52725,6 +55521,12 @@
       <c r="AJ466" s="2" t="n">
         <v>-0.002109704641350135</v>
       </c>
+      <c r="AK466" s="1" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="AL466" s="2" t="n">
+        <v>-0.001409443269908387</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -52837,6 +55639,12 @@
       <c r="AJ467" s="2" t="n">
         <v>-0.003642039542143632</v>
       </c>
+      <c r="AK467" s="1" t="n">
+        <v>0.01911</v>
+      </c>
+      <c r="AL467" s="2" t="n">
+        <v>-0.002088772845953099</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -52949,6 +55757,12 @@
       <c r="AJ468" s="3" t="n">
         <v>0.006930693069306992</v>
       </c>
+      <c r="AK468" s="1" t="n">
+        <v>0.01007</v>
+      </c>
+      <c r="AL468" s="2" t="n">
+        <v>-0.009832841691248711</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -53061,6 +55875,12 @@
       <c r="AJ469" s="2" t="n">
         <v>-0.004016064257028089</v>
       </c>
+      <c r="AK469" s="1" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="AL469" s="2" t="n">
+        <v>-0.002520161290322583</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -53173,6 +55993,12 @@
       <c r="AJ470" s="2" t="n">
         <v>-0.002272727272727275</v>
       </c>
+      <c r="AK470" s="1" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="AL470" s="2" t="n">
+        <v>-0.002277904328018225</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -53285,6 +56111,12 @@
       <c r="AJ471" s="2" t="n">
         <v>-0.004638218923933248</v>
       </c>
+      <c r="AK471" s="1" t="n">
+        <v>3.211</v>
+      </c>
+      <c r="AL471" s="2" t="n">
+        <v>-0.002485243864554212</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -53397,6 +56229,12 @@
       <c r="AJ472" s="3" t="n">
         <v>0.0004774409166867063</v>
       </c>
+      <c r="AK472" s="1" t="n">
+        <v>0.04195</v>
+      </c>
+      <c r="AL472" s="3" t="n">
+        <v>0.0009544261512765061</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -53509,6 +56347,12 @@
       <c r="AJ473" s="2" t="n">
         <v>-0.001594896331738438</v>
       </c>
+      <c r="AK473" s="1" t="n">
+        <v>1.248</v>
+      </c>
+      <c r="AL473" s="2" t="n">
+        <v>-0.003194888178913741</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -53621,6 +56465,12 @@
       <c r="AJ474" s="2" t="n">
         <v>-0.001401541695865435</v>
       </c>
+      <c r="AK474" s="1" t="n">
+        <v>0.008534999999999999</v>
+      </c>
+      <c r="AL474" s="2" t="n">
+        <v>-0.001754385964912412</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -53733,6 +56583,12 @@
       <c r="AJ475" s="2" t="n">
         <v>-0.004308281474389651</v>
       </c>
+      <c r="AK475" s="1" t="n">
+        <v>0.04147</v>
+      </c>
+      <c r="AL475" s="2" t="n">
+        <v>-0.003124999999999956</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -53845,6 +56701,12 @@
       <c r="AJ476" s="2" t="n">
         <v>-0.00454430699318353</v>
       </c>
+      <c r="AK476" s="1" t="n">
+        <v>0.07861</v>
+      </c>
+      <c r="AL476" s="2" t="n">
+        <v>-0.003170174993659653</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -53957,6 +56819,12 @@
       <c r="AJ477" s="2" t="n">
         <v>-0.0009534286762008891</v>
       </c>
+      <c r="AK477" s="1" t="n">
+        <v>0.1364</v>
+      </c>
+      <c r="AL477" s="3" t="n">
+        <v>0.001321391866098853</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -54069,6 +56937,12 @@
       <c r="AJ478" s="2" t="n">
         <v>-0.0006315789473684683</v>
       </c>
+      <c r="AK478" s="1" t="n">
+        <v>0.04737</v>
+      </c>
+      <c r="AL478" s="2" t="n">
+        <v>-0.002106593638087127</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -54181,6 +57055,12 @@
       <c r="AJ479" s="2" t="n">
         <v>-0.002619760479041939</v>
       </c>
+      <c r="AK479" s="1" t="n">
+        <v>0.005315</v>
+      </c>
+      <c r="AL479" s="2" t="n">
+        <v>-0.002814258911819773</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -54293,6 +57173,12 @@
       <c r="AJ480" s="2" t="n">
         <v>-0.005687877710629187</v>
       </c>
+      <c r="AK480" s="1" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="AL480" s="3" t="n">
+        <v>0.0003575259206292063</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -54405,6 +57291,12 @@
       <c r="AJ481" s="2" t="n">
         <v>-0.001315962626661441</v>
       </c>
+      <c r="AK481" s="1" t="n">
+        <v>0.07578</v>
+      </c>
+      <c r="AL481" s="2" t="n">
+        <v>-0.001449466332850164</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -54517,6 +57409,12 @@
       <c r="AJ482" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK482" s="1" t="n">
+        <v>0.01489</v>
+      </c>
+      <c r="AL482" s="2" t="n">
+        <v>-0.00201072386058973</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -54629,6 +57527,12 @@
       <c r="AJ483" s="2" t="n">
         <v>-0.003968253968253945</v>
       </c>
+      <c r="AK483" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AL483" s="2" t="n">
+        <v>-0.003984063745019896</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -54741,6 +57645,12 @@
       <c r="AJ484" s="2" t="n">
         <v>-0.002780352177942426</v>
       </c>
+      <c r="AK484" s="1" t="n">
+        <v>0.02146</v>
+      </c>
+      <c r="AL484" s="2" t="n">
+        <v>-0.002788104089219378</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -54853,6 +57763,12 @@
       <c r="AJ485" s="3" t="n">
         <v>0.003236245954692674</v>
       </c>
+      <c r="AK485" s="1" t="n">
+        <v>0.008364</v>
+      </c>
+      <c r="AL485" s="2" t="n">
+        <v>-0.0007168458781362958</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -54965,6 +57881,12 @@
       <c r="AJ486" s="2" t="n">
         <v>-0.003603363138929567</v>
       </c>
+      <c r="AK486" s="1" t="n">
+        <v>0.007458</v>
+      </c>
+      <c r="AL486" s="2" t="n">
+        <v>-0.001071524243236029</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -55077,6 +57999,12 @@
       <c r="AJ487" s="2" t="n">
         <v>-0.00616197183098597</v>
       </c>
+      <c r="AK487" s="1" t="n">
+        <v>0.1119</v>
+      </c>
+      <c r="AL487" s="2" t="n">
+        <v>-0.008857395925597882</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -55189,6 +58117,12 @@
       <c r="AJ488" s="3" t="n">
         <v>0.004771199306007443</v>
       </c>
+      <c r="AK488" s="1" t="n">
+        <v>0.009283</v>
+      </c>
+      <c r="AL488" s="3" t="n">
+        <v>0.001834664364342721</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -55301,6 +58235,12 @@
       <c r="AJ489" s="2" t="n">
         <v>-0.008653601425299058</v>
       </c>
+      <c r="AK489" s="1" t="n">
+        <v>0.03879</v>
+      </c>
+      <c r="AL489" s="2" t="n">
+        <v>-0.004107830551989741</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -55413,6 +58353,12 @@
       <c r="AJ490" s="2" t="n">
         <v>-0.003773584905660343</v>
       </c>
+      <c r="AK490" s="1" t="n">
+        <v>0.05747</v>
+      </c>
+      <c r="AL490" s="2" t="n">
+        <v>-0.01050275482093663</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -55525,6 +58471,12 @@
       <c r="AJ491" s="2" t="n">
         <v>-0.001024590163934456</v>
       </c>
+      <c r="AK491" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="AL491" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -55637,6 +58589,12 @@
       <c r="AJ492" s="2" t="n">
         <v>-0.003018867924528305</v>
       </c>
+      <c r="AK492" s="1" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="AL492" s="2" t="n">
+        <v>-0.003028009084027255</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -55749,6 +58707,12 @@
       <c r="AJ493" s="2" t="n">
         <v>-0.003402324922030112</v>
       </c>
+      <c r="AK493" s="1" t="n">
+        <v>0.03502</v>
+      </c>
+      <c r="AL493" s="2" t="n">
+        <v>-0.003698435277382594</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -55861,6 +58825,12 @@
       <c r="AJ494" s="2" t="n">
         <v>-0.002949852507374716</v>
       </c>
+      <c r="AK494" s="1" t="n">
+        <v>0.01687</v>
+      </c>
+      <c r="AL494" s="2" t="n">
+        <v>-0.001775147928994011</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -55973,6 +58943,12 @@
       <c r="AJ495" s="2" t="n">
         <v>-0.00465904277848365</v>
       </c>
+      <c r="AK495" s="1" t="n">
+        <v>0.04696</v>
+      </c>
+      <c r="AL495" s="2" t="n">
+        <v>-0.0008510638297871993</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -56085,6 +59061,12 @@
       <c r="AJ496" s="2" t="n">
         <v>-0.006194507536650871</v>
       </c>
+      <c r="AK496" s="1" t="n">
+        <v>0.04813</v>
+      </c>
+      <c r="AL496" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -56197,6 +59179,12 @@
       <c r="AJ497" s="2" t="n">
         <v>-0.003012653143201532</v>
       </c>
+      <c r="AK497" s="1" t="n">
+        <v>0.04957</v>
+      </c>
+      <c r="AL497" s="2" t="n">
+        <v>-0.001410153102336698</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -56309,6 +59297,12 @@
       <c r="AJ498" s="3" t="n">
         <v>0.001730103806228375</v>
       </c>
+      <c r="AK498" s="1" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="AL498" s="2" t="n">
+        <v>-0.0003454231433505665</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -56421,6 +59415,12 @@
       <c r="AJ499" s="2" t="n">
         <v>-0.005837285662167057</v>
       </c>
+      <c r="AK499" s="1" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="AL499" s="2" t="n">
+        <v>-0.001834862385321102</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -56533,6 +59533,12 @@
       <c r="AJ500" s="2" t="n">
         <v>-0.003745318352059935</v>
       </c>
+      <c r="AK500" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="AL500" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -56645,6 +59651,12 @@
       <c r="AJ501" s="2" t="n">
         <v>-0.005305780508237996</v>
       </c>
+      <c r="AK501" s="1" t="n">
+        <v>0.03543</v>
+      </c>
+      <c r="AL501" s="2" t="n">
+        <v>-0.005334081976417623</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -56757,6 +59769,12 @@
       <c r="AJ502" s="3" t="n">
         <v>0.0009413241292750332</v>
       </c>
+      <c r="AK502" s="1" t="n">
+        <v>0.03189</v>
+      </c>
+      <c r="AL502" s="2" t="n">
+        <v>-0.0003134796238243299</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -56869,6 +59887,12 @@
       <c r="AJ503" s="3" t="n">
         <v>0.0002566735112935573</v>
       </c>
+      <c r="AK503" s="1" t="n">
+        <v>0.00778</v>
+      </c>
+      <c r="AL503" s="2" t="n">
+        <v>-0.001796253528355161</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -56981,6 +60005,12 @@
       <c r="AJ504" s="2" t="n">
         <v>-0.0006600660066005874</v>
       </c>
+      <c r="AK504" s="1" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AL504" s="2" t="n">
+        <v>-0.00264200792602378</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -57093,6 +60123,12 @@
       <c r="AJ505" s="2" t="n">
         <v>-0.00429934166330791</v>
       </c>
+      <c r="AK505" s="1" t="n">
+        <v>0.0007403000000000001</v>
+      </c>
+      <c r="AL505" s="2" t="n">
+        <v>-0.001079476453919729</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -57205,6 +60241,12 @@
       <c r="AJ506" s="2" t="n">
         <v>-0.002741603838245452</v>
       </c>
+      <c r="AK506" s="1" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="AL506" s="2" t="n">
+        <v>-0.001374570446735244</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -57317,6 +60359,12 @@
       <c r="AJ507" s="2" t="n">
         <v>-0.006620209059233572</v>
       </c>
+      <c r="AK507" s="1" t="n">
+        <v>0.002841</v>
+      </c>
+      <c r="AL507" s="2" t="n">
+        <v>-0.003507541213609117</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -57429,6 +60477,12 @@
       <c r="AJ508" s="2" t="n">
         <v>-0.002681388012618352</v>
       </c>
+      <c r="AK508" s="1" t="n">
+        <v>0.06319</v>
+      </c>
+      <c r="AL508" s="2" t="n">
+        <v>-0.0006326111023248201</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -57541,6 +60595,12 @@
       <c r="AJ509" s="3" t="n">
         <v>0.001346499102333783</v>
       </c>
+      <c r="AK509" s="1" t="n">
+        <v>2.236</v>
+      </c>
+      <c r="AL509" s="3" t="n">
+        <v>0.002241147467503513</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -57653,6 +60713,12 @@
       <c r="AJ510" s="2" t="n">
         <v>-0.003804864791411969</v>
       </c>
+      <c r="AK510" s="1" t="n">
+        <v>0.0007309</v>
+      </c>
+      <c r="AL510" s="2" t="n">
+        <v>-0.003000954849270147</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -57765,6 +60831,12 @@
       <c r="AJ511" s="2" t="n">
         <v>-0.002902757619738835</v>
       </c>
+      <c r="AK511" s="1" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="AL511" s="2" t="n">
+        <v>-0.0003639010189228129</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -57877,6 +60949,12 @@
       <c r="AJ512" s="2" t="n">
         <v>-0.0006207324643078984</v>
       </c>
+      <c r="AK512" s="1" t="n">
+        <v>0.0004836</v>
+      </c>
+      <c r="AL512" s="3" t="n">
+        <v>0.001242236024844751</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -57989,6 +61067,12 @@
       <c r="AJ513" s="2" t="n">
         <v>-0.002709048221058412</v>
       </c>
+      <c r="AK513" s="1" t="n">
+        <v>0.05493</v>
+      </c>
+      <c r="AL513" s="2" t="n">
+        <v>-0.005251720391162597</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -58101,6 +61185,12 @@
       <c r="AJ514" s="2" t="n">
         <v>-0.0003303600925008124</v>
       </c>
+      <c r="AK514" s="1" t="n">
+        <v>0.03015</v>
+      </c>
+      <c r="AL514" s="2" t="n">
+        <v>-0.003635161929940482</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -58213,6 +61303,12 @@
       <c r="AJ515" s="3" t="n">
         <v>0.0008779631255486531</v>
       </c>
+      <c r="AK515" s="1" t="n">
+        <v>0.001139</v>
+      </c>
+      <c r="AL515" s="2" t="n">
+        <v>-0.0008771929824560666</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -58325,6 +61421,12 @@
       <c r="AJ516" s="2" t="n">
         <v>-0.00482945970419558</v>
       </c>
+      <c r="AK516" s="1" t="n">
+        <v>0.00659</v>
+      </c>
+      <c r="AL516" s="2" t="n">
+        <v>-0.0006066120715801734</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -58437,6 +61539,12 @@
       <c r="AJ517" s="2" t="n">
         <v>-0.001003009027081203</v>
       </c>
+      <c r="AK517" s="1" t="n">
+        <v>0.03985</v>
+      </c>
+      <c r="AL517" s="3" t="n">
+        <v>0.0002510040160641597</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -58549,6 +61657,12 @@
       <c r="AJ518" s="2" t="n">
         <v>-0.001928640308582505</v>
       </c>
+      <c r="AK518" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="AL518" s="2" t="n">
+        <v>-0.00289855072463763</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -58661,6 +61775,12 @@
       <c r="AJ519" s="2" t="n">
         <v>-0.004581901489117996</v>
       </c>
+      <c r="AK519" s="1" t="n">
+        <v>0.008670000000000001</v>
+      </c>
+      <c r="AL519" s="2" t="n">
+        <v>-0.002301495972381955</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -58773,6 +61893,12 @@
       <c r="AJ520" s="2" t="n">
         <v>-0.003733665214685856</v>
       </c>
+      <c r="AK520" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="AL520" s="2" t="n">
+        <v>-0.001249219237976301</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -58885,6 +62011,12 @@
       <c r="AJ521" s="2" t="n">
         <v>-0.002788622420524341</v>
       </c>
+      <c r="AK521" s="1" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AL521" s="2" t="n">
+        <v>-0.001118568232662147</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -58997,6 +62129,12 @@
       <c r="AJ522" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AK522" s="1" t="n">
+        <v>0.01639</v>
+      </c>
+      <c r="AL522" s="2" t="n">
+        <v>-0.002434570906877775</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -59109,6 +62247,12 @@
       <c r="AJ523" s="3" t="n">
         <v>0.0007235890014470648</v>
       </c>
+      <c r="AK523" s="1" t="n">
+        <v>0.004124</v>
+      </c>
+      <c r="AL523" s="2" t="n">
+        <v>-0.006025548324897529</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -59221,6 +62365,12 @@
       <c r="AJ524" s="2" t="n">
         <v>-0.005602240896358437</v>
       </c>
+      <c r="AK524" s="1" t="n">
+        <v>0.01421</v>
+      </c>
+      <c r="AL524" s="3" t="n">
+        <v>0.0007042253521126474</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -59333,6 +62483,12 @@
       <c r="AJ525" s="2" t="n">
         <v>-0.002819170358437399</v>
       </c>
+      <c r="AK525" s="1" t="n">
+        <v>0.02469</v>
+      </c>
+      <c r="AL525" s="2" t="n">
+        <v>-0.002827140549273046</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -59445,6 +62601,12 @@
       <c r="AJ526" s="2" t="n">
         <v>-0.002493765586034984</v>
       </c>
+      <c r="AK526" s="1" t="n">
+        <v>0.1199</v>
+      </c>
+      <c r="AL526" s="2" t="n">
+        <v>-0.0008333333333332416</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -59557,6 +62719,12 @@
       <c r="AJ527" s="2" t="n">
         <v>-0.001390433815350429</v>
       </c>
+      <c r="AK527" s="1" t="n">
+        <v>0.07147000000000001</v>
+      </c>
+      <c r="AL527" s="2" t="n">
+        <v>-0.004873294346978407</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -59669,6 +62837,12 @@
       <c r="AJ528" s="2" t="n">
         <v>-0.004613610149942302</v>
       </c>
+      <c r="AK528" s="1" t="n">
+        <v>0.04307</v>
+      </c>
+      <c r="AL528" s="2" t="n">
+        <v>-0.001853997682502982</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -59781,6 +62955,12 @@
       <c r="AJ529" s="2" t="n">
         <v>-0.003481563538534546</v>
       </c>
+      <c r="AK529" s="1" t="n">
+        <v>0.06287</v>
+      </c>
+      <c r="AL529" s="2" t="n">
+        <v>-0.001588057805304159</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -59893,6 +63073,12 @@
       <c r="AJ530" s="2" t="n">
         <v>-0.001793185893604369</v>
       </c>
+      <c r="AK530" s="1" t="n">
+        <v>0.005003</v>
+      </c>
+      <c r="AL530" s="2" t="n">
+        <v>-0.001397205588822368</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -60005,6 +63191,12 @@
       <c r="AJ531" s="2" t="n">
         <v>-0.0007686395080706303</v>
       </c>
+      <c r="AK531" s="1" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="AL531" s="2" t="n">
+        <v>-0.002307692307692267</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -60117,6 +63309,12 @@
       <c r="AJ532" s="2" t="n">
         <v>-0.0009333582228859703</v>
       </c>
+      <c r="AK532" s="1" t="n">
+        <v>0.05339</v>
+      </c>
+      <c r="AL532" s="2" t="n">
+        <v>-0.002428998505231655</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -60229,6 +63427,12 @@
       <c r="AJ533" s="2" t="n">
         <v>-0.008222811671087474</v>
       </c>
+      <c r="AK533" s="1" t="n">
+        <v>0.003734</v>
+      </c>
+      <c r="AL533" s="2" t="n">
+        <v>-0.001337255950789042</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -60341,6 +63545,12 @@
       <c r="AJ534" s="2" t="n">
         <v>-0.005810575246949453</v>
       </c>
+      <c r="AK534" s="1" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="AL534" s="2" t="n">
+        <v>-0.0005844535359438281</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -60453,6 +63663,12 @@
       <c r="AJ535" s="3" t="n">
         <v>0.008928571428571494</v>
       </c>
+      <c r="AK535" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="AL535" s="2" t="n">
+        <v>-0.00884955752212396</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -60565,6 +63781,12 @@
       <c r="AJ536" s="2" t="n">
         <v>-0.004082558403266023</v>
       </c>
+      <c r="AK536" s="1" t="n">
+        <v>0.0004394</v>
+      </c>
+      <c r="AL536" s="3" t="n">
+        <v>0.0006832156684126789</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -60677,6 +63899,12 @@
       <c r="AJ537" s="2" t="n">
         <v>-0.004136504653567746</v>
       </c>
+      <c r="AK537" s="1" t="n">
+        <v>0.00959</v>
+      </c>
+      <c r="AL537" s="2" t="n">
+        <v>-0.004153686396677062</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -60789,6 +64017,12 @@
       <c r="AJ538" s="2" t="n">
         <v>-0.001098699871818304</v>
       </c>
+      <c r="AK538" s="1" t="n">
+        <v>0.05449</v>
+      </c>
+      <c r="AL538" s="2" t="n">
+        <v>-0.001099908340971668</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -60901,6 +64135,12 @@
       <c r="AJ539" s="3" t="n">
         <v>0.000880540064573004</v>
       </c>
+      <c r="AK539" s="1" t="n">
+        <v>0.6808999999999999</v>
+      </c>
+      <c r="AL539" s="2" t="n">
+        <v>-0.001612903225806599</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -61013,6 +64253,12 @@
       <c r="AJ540" s="2" t="n">
         <v>-0.001324503311258316</v>
       </c>
+      <c r="AK540" s="1" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="AL540" s="2" t="n">
+        <v>-0.001326259946949456</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -61125,6 +64371,12 @@
       <c r="AJ541" s="3" t="n">
         <v>0.002311248073959978</v>
       </c>
+      <c r="AK541" s="1" t="n">
+        <v>0.01297</v>
+      </c>
+      <c r="AL541" s="2" t="n">
+        <v>-0.003074558032282867</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -61237,6 +64489,12 @@
       <c r="AJ542" s="3" t="n">
         <v>0.004341534008683016</v>
       </c>
+      <c r="AK542" s="1" t="n">
+        <v>0.01387</v>
+      </c>
+      <c r="AL542" s="2" t="n">
+        <v>-0.0007204610951008352</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -61349,6 +64607,12 @@
       <c r="AJ543" s="2" t="n">
         <v>-0.00314685314685314</v>
       </c>
+      <c r="AK543" s="1" t="n">
+        <v>0.05701</v>
+      </c>
+      <c r="AL543" s="2" t="n">
+        <v>-0.0001753770606805167</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
